--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="284">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 09/04/2026 16:56:12</t>
+    <t xml:space="preserve">Emitido em: 10/04/2026 15:09:21</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -427,138 +427,123 @@
     <t xml:space="preserve">42260381604803000157550010008593781386563768</t>
   </si>
   <si>
+    <t xml:space="preserve">986 - PADO S A INDUSTRIAL COMERCIAL E IMPORTADORA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.255.820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.370,87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260361144150000678550010012558201979933211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.576 - GRUPO METAL DESIGN LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.599,23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260386895448000560550010000005531327125998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.932 - VERDECO INDUSTRIA COMERCIO E IMPORTACAO DE ARTEFATOS PARA JA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.213,01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260308031381000188550010000376881002430254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.051.936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">681,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050519361143368467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.051.935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">687,84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050519351842337318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.768 - TOPMAX ACESSORIOS PARA CONSTRUCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.673,98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260345123710000147550010000123481646954616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">863.503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.415,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260452618139002817550030008635031891067185</t>
+  </si>
+  <si>
     <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">600.313</t>
+    <t xml:space="preserve">607.481</t>
   </si>
   <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">27/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.925,32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260375339051000141550080006003131379274666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">986 - PADO S A INDUSTRIAL COMERCIAL E IMPORTADORA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.255.820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.370,87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260361144150000678550010012558201979933211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.576 - GRUPO METAL DESIGN LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.599,23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260386895448000560550010000005531327125998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.932 - VERDECO INDUSTRIA COMERCIO E IMPORTACAO DE ARTEFATOS PARA JA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.213,01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260308031381000188550010000376881002430254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.051.936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">681,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050519361143368467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.051.935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">687,84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050519351842337318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.768 - TOPMAX ACESSORIOS PARA CONSTRUCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.673,98</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260345123710000147550010000123481646954616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">863.503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.415,02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260452618139002817550030008635031891067185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">607.481</t>
-  </si>
-  <si>
     <t xml:space="preserve">30/04/2026</t>
   </si>
   <si>
@@ -625,24 +610,12 @@
     <t xml:space="preserve">41260414624251000151550010000458691000329515</t>
   </si>
   <si>
-    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.279.916</t>
+    <t xml:space="preserve">609.316</t>
   </si>
   <si>
     <t xml:space="preserve">05/05/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">25.106,90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260350949528001232550010022799161942773225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">609.316</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.455,75</t>
   </si>
   <si>
@@ -809,6 +782,39 @@
   </si>
   <si>
     <t xml:space="preserve">42260482901000001441550100003783781282056610</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.977 - COMFORT DOOR IMPORTACAO E DISTRIBUICAO DE UTILIDADES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.725,68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260418455453000178550040000188251810396895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.951 - QUALITRONIX TECNOLOGIA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">128.728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.990,99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31260402803462000172550030001287281653625632</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -19145,7 +19151,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>303947</v>
+        <v>304124</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>135</v>
@@ -19157,10 +19163,10 @@
         <v>136</v>
       </c>
       <c r="G14" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>137</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>138</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>138</v>
@@ -19172,25 +19178,25 @@
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>1925.32</v>
+        <v>8370.87</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>1925.32</v>
+        <v>8370.87</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.006628</v>
+        <v>0.14134</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>4.46</v>
+        <v>100.96</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
@@ -19202,7 +19208,7 @@
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
@@ -19214,10 +19220,10 @@
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>1925.32</v>
+        <v>8370.87</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>134.77</v>
+        <v>585.97</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19336,7 +19342,7 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>304124</v>
+        <v>304306</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>142</v>
@@ -19351,64 +19357,64 @@
         <v>83</v>
       </c>
       <c r="H15" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="J15" s="9" t="s">
         <v>145</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>146</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>8370.87</v>
+        <v>32599.23</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>8370.87</v>
+        <v>31660.33</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.14134</v>
+        <v>0</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>100.96</v>
+        <v>0</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>0</v>
+        <v>938.9</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>8370.87</v>
+        <v>31660.33</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>585.97</v>
+        <v>1266.38</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19513,7 +19519,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19527,43 +19533,43 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>304306</v>
+        <v>304344</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>152</v>
+        <v>78</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>32599.23</v>
+        <v>1213.01</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>31660.33</v>
+        <v>1139</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
@@ -19572,34 +19578,34 @@
         <v>0</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>0</v>
+        <v>93.18</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>938.9</v>
+        <v>74.01</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>31660.33</v>
+        <v>1139</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>1266.38</v>
+        <v>79.73</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19668,7 +19674,7 @@
         <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19704,7 +19710,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19718,25 +19724,25 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>304344</v>
+        <v>304391</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>155</v>
+        <v>97</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>78</v>
@@ -19745,31 +19751,31 @@
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1213.01</v>
+        <v>681.6</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>1139</v>
+        <v>651.08</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0</v>
+        <v>0.109581</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>93.18</v>
+        <v>2.46</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19781,16 +19787,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>74.01</v>
+        <v>30.52</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>1139</v>
+        <v>651.08</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>79.73</v>
+        <v>31.5</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19859,7 +19865,7 @@
         <v>76</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>75</v>
@@ -19895,7 +19901,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19909,7 +19915,7 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>304391</v>
+        <v>304392</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>97</v>
@@ -19918,16 +19924,16 @@
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="J18" s="9" t="s">
         <v>78</v>
@@ -19936,7 +19942,7 @@
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>681.6</v>
+        <v>687.84</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -19945,22 +19951,22 @@
         <v>4</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>651.08</v>
+        <v>656.94</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.109581</v>
+        <v>0.146516</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>2.46</v>
+        <v>2.23</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
@@ -19972,16 +19978,16 @@
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>30.52</v>
+        <v>30.9</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>651.08</v>
+        <v>656.94</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>31.5</v>
+        <v>31.74</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20050,7 +20056,7 @@
         <v>76</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -20086,7 +20092,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20100,79 +20106,79 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>304392</v>
+        <v>304453</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>687.84</v>
+        <v>15673.98</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>656.94</v>
+        <v>15673.98</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.146516</v>
+        <v>0.40995</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>2.23</v>
+        <v>132.6</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>656.94</v>
+        <v>15673.98</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>31.74</v>
+        <v>1097.14</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20241,7 +20247,7 @@
         <v>76</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20277,7 +20283,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20291,79 +20297,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>304453</v>
+        <v>304525</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>145</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>152</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>15673.98</v>
+        <v>2415.02</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>15673.98</v>
+        <v>2339</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.40995</v>
+        <v>0.004</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>132.6</v>
+        <v>0.1</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>0</v>
+        <v>76.02</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>15673.98</v>
+        <v>2339</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>1097.14</v>
+        <v>163.73</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20468,7 +20474,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20482,34 +20488,34 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>304525</v>
+        <v>304536</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="G21" s="10" t="s">
-        <v>66</v>
-      </c>
       <c r="H21" s="9" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="I21" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>175</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>2415.02</v>
+        <v>6516.28</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20518,43 +20524,43 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>2339</v>
+        <v>6516.28</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.004</v>
+        <v>0.092604</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>76.02</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>2339</v>
+        <v>6516.28</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>163.73</v>
+        <v>456.14</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20620,7 +20626,7 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX21" s="10" t="s">
         <v>77</v>
@@ -20659,7 +20665,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20673,10 +20679,10 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>304536</v>
+        <v>304540</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>135</v>
+        <v>177</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -20685,37 +20691,37 @@
         <v>178</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="I22" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>179</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>6516.28</v>
+        <v>3349.44</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>6516.28</v>
+        <v>3244</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.092604</v>
+        <v>0</v>
       </c>
       <c r="R22" s="12" t="n">
         <v>0</v>
@@ -20724,28 +20730,28 @@
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>0</v>
+        <v>105.44</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>6516.28</v>
+        <v>3244</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>456.14</v>
+        <v>227.08</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20811,7 +20817,7 @@
         <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
         <v>77</v>
@@ -20850,7 +20856,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20864,79 +20870,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>304540</v>
+        <v>304541</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>83</v>
+        <v>173</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>3349.44</v>
+        <v>63.18</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>3244</v>
+        <v>63.18</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0</v>
+        <v>0.000372</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>105.44</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>3244</v>
+        <v>63.18</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>227.08</v>
+        <v>4.42</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21041,7 +21047,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21055,10 +21061,10 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>304541</v>
+        <v>304591</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -21067,22 +21073,22 @@
         <v>186</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>187</v>
+        <v>78</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>63.18</v>
+        <v>21.58</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -21091,43 +21097,43 @@
         <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>63.18</v>
+        <v>19.66</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.000372</v>
+        <v>0</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>63.18</v>
+        <v>19.66</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>4.42</v>
+        <v>1.38</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21193,10 +21199,10 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21232,7 +21238,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21246,25 +21252,25 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>304591</v>
+        <v>304596</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>78</v>
@@ -21273,16 +21279,16 @@
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>21.58</v>
+        <v>383.74</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>19.66</v>
+        <v>360.32</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
@@ -21291,13 +21297,13 @@
         <v>0</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>0</v>
+        <v>28.68</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
@@ -21309,16 +21315,16 @@
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>1.92</v>
+        <v>23.42</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>19.66</v>
+        <v>360.32</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>1.38</v>
+        <v>25.23</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21384,7 +21390,7 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX25" s="10" t="s">
         <v>88</v>
@@ -21423,7 +21429,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21437,79 +21443,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>304596</v>
+        <v>304599</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>383.74</v>
+        <v>6769.12</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>360.32</v>
+        <v>6223.01</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>28.68</v>
+        <v>34.8</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>23.42</v>
+        <v>546.11</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>360.32</v>
+        <v>6223.01</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>25.23</v>
+        <v>267.58</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21578,7 +21584,7 @@
         <v>76</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21614,7 +21620,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21628,79 +21634,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>304599</v>
+        <v>304630</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>83</v>
+        <v>173</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>6769.12</v>
+        <v>2455.75</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>6223.01</v>
+        <v>2455.75</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>1.3</v>
+        <v>0.008285</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>34.8</v>
+        <v>5.58</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>546.11</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>6223.01</v>
+        <v>2455.75</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>267.58</v>
+        <v>171.9</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21766,7 +21772,7 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX27" s="10" t="s">
         <v>77</v>
@@ -21805,7 +21811,7 @@
         <v>78</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21819,79 +21825,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>304602</v>
+        <v>304647</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="I28" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="J28" s="9" t="s">
         <v>174</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>203</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>25106.9</v>
+        <v>2081.39</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>24618.7</v>
+        <v>1896.48</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.955384</v>
+        <v>0</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>961.82</v>
+        <v>0</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>77</v>
+        <v>31.19</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>488.2</v>
+        <v>184.91</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>24618.7</v>
+        <v>1896.48</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>1723.29</v>
+        <v>132.75</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21996,7 +22002,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22010,79 +22016,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>304630</v>
+        <v>304653</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>137</v>
-      </c>
       <c r="H29" s="9" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>2455.75</v>
+        <v>9176.74</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>2455.75</v>
+        <v>7866.24</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>0</v>
+        <v>689.84</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.008285</v>
+        <v>6E-006</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>5.58</v>
+        <v>0.37</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>0</v>
+        <v>620.66</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>2455.75</v>
+        <v>8556.08</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>171.9</v>
+        <v>342.24</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22187,7 +22193,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22201,79 +22207,79 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>304647</v>
+        <v>304676</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>179</v>
+        <v>105</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2081.39</v>
+        <v>11590</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>1896.48</v>
+        <v>11590</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0</v>
+        <v>0.08227</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>0</v>
+        <v>44.35</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>31.19</v>
+        <v>60</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>184.91</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>1896.48</v>
+        <v>11590</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>132.75</v>
+        <v>811.3</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22378,7 +22384,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22392,79 +22398,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>304653</v>
+        <v>304693</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>213</v>
+        <v>171</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>215</v>
+        <v>173</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>169</v>
+        <v>126</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>216</v>
+        <v>78</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>9176.74</v>
+        <v>215.05</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>7866.24</v>
+        <v>215.05</v>
       </c>
       <c r="P31" s="12" t="n">
-        <v>689.84</v>
+        <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>6E-006</v>
+        <v>0.001636</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>0.37</v>
+        <v>0.15</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>174</v>
+        <v>212</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>620.66</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>8556.08</v>
+        <v>215.05</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>342.24</v>
+        <v>15.05</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22530,10 +22536,10 @@
         <v>74</v>
       </c>
       <c r="AW31" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22569,7 +22575,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22583,79 +22589,79 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>304676</v>
+        <v>304714</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G32" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="G32" s="10" t="s">
-        <v>66</v>
-      </c>
       <c r="H32" s="9" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>11590</v>
+        <v>164.77</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>11590</v>
+        <v>164.77</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.08227</v>
+        <v>0</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>44.35</v>
+        <v>0</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>11590</v>
+        <v>164.77</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>811.3</v>
+        <v>19.77</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22760,7 +22766,7 @@
         <v>78</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22774,79 +22780,79 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>304693</v>
+        <v>304715</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>135</v>
+        <v>218</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>126</v>
+        <v>162</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>78</v>
+        <v>207</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>215.05</v>
+        <v>2551.37</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>215.05</v>
+        <v>2551.37</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.001636</v>
+        <v>0</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="Y33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>215.05</v>
+        <v>2551.37</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>15.05</v>
+        <v>306.16</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22915,7 +22921,7 @@
         <v>76</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>162</v>
+        <v>77</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -22951,7 +22957,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -22965,34 +22971,34 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>304714</v>
+        <v>304716</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>164.77</v>
+        <v>1160.42</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -23001,7 +23007,7 @@
         <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>164.77</v>
+        <v>1089.6</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
@@ -23016,7 +23022,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
@@ -23028,16 +23034,16 @@
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>0</v>
+        <v>70.82</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>164.77</v>
+        <v>1089.6</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>19.77</v>
+        <v>43.58</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23142,7 +23148,7 @@
         <v>78</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23156,34 +23162,34 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>304715</v>
+        <v>304729</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>2551.37</v>
+        <v>4573.08</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23192,43 +23198,43 @@
         <v>2</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>2551.37</v>
+        <v>4573.08</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0</v>
+        <v>0.000332</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="Y35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>2551.37</v>
+        <v>4573.08</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>306.16</v>
+        <v>320.11</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23333,7 +23339,7 @@
         <v>78</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23347,34 +23353,34 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>304716</v>
+        <v>304733</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>1160.42</v>
+        <v>24.23</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
@@ -23383,7 +23389,7 @@
         <v>1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>1089.6</v>
+        <v>22.08</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
@@ -23398,28 +23404,28 @@
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>70.82</v>
+        <v>2.15</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>1089.6</v>
+        <v>22.08</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>43.58</v>
+        <v>0.88</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23485,10 +23491,10 @@
         <v>74</v>
       </c>
       <c r="AW36" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX36" s="10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AY36" s="14" t="s">
         <v>75</v>
@@ -23524,7 +23530,7 @@
         <v>78</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23538,58 +23544,58 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>304729</v>
+        <v>304766</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>221</v>
+        <v>101</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>4573.08</v>
+        <v>5259.16</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>4573.08</v>
+        <v>5259.16</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.000332</v>
+        <v>0.017</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
@@ -23601,16 +23607,16 @@
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>221</v>
+        <v>101</v>
       </c>
       <c r="Y37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>4573.08</v>
+        <v>5259.16</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>320.11</v>
+        <v>368.14</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23715,7 +23721,7 @@
         <v>78</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23729,34 +23735,34 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>304733</v>
+        <v>304798</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="I38" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="J38" s="9" t="s">
         <v>244</v>
-      </c>
-      <c r="G38" s="10" t="s">
-        <v>215</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="I38" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>24.23</v>
+        <v>8379</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -23765,7 +23771,7 @@
         <v>1</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>22.08</v>
+        <v>8379</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
@@ -23774,7 +23780,7 @@
         <v>0</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>0</v>
+        <v>341.1</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
@@ -23786,22 +23792,22 @@
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>221</v>
+        <v>101</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>22.08</v>
+        <v>8379</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>0.88</v>
+        <v>586.53</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23867,10 +23873,10 @@
         <v>74</v>
       </c>
       <c r="AW38" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX38" s="10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AY38" s="14" t="s">
         <v>75</v>
@@ -23920,10 +23926,10 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>304766</v>
+        <v>304807</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
@@ -23932,22 +23938,22 @@
         <v>247</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>101</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>5259.16</v>
+        <v>276.83</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
@@ -23956,28 +23962,28 @@
         <v>1</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>5259.16</v>
+        <v>252.24</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>2.91</v>
+        <v>2.4</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
@@ -23986,13 +23992,13 @@
         <v>101</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>0</v>
+        <v>24.59</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>5259.16</v>
+        <v>252.24</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>368.14</v>
+        <v>10.09</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24058,7 +24064,7 @@
         <v>74</v>
       </c>
       <c r="AW39" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX39" s="10" t="s">
         <v>77</v>
@@ -24097,7 +24103,7 @@
         <v>78</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24111,10 +24117,10 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>304798</v>
+        <v>304808</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>250</v>
+        <v>226</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -24123,31 +24129,31 @@
         <v>251</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="I40" s="9" t="s">
         <v>101</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>253</v>
+        <v>207</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>8379</v>
+        <v>2961.42</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>8379</v>
+        <v>2730.6</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
@@ -24156,19 +24162,19 @@
         <v>0</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>341.1</v>
+        <v>0</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="W40" s="9" t="s">
         <v>73</v>
@@ -24177,13 +24183,13 @@
         <v>101</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>0</v>
+        <v>230.82</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>8379</v>
+        <v>2730.6</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>586.53</v>
+        <v>109.22</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24288,7 +24294,7 @@
         <v>78</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24302,52 +24308,52 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>304807</v>
+        <v>304824</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>235</v>
+        <v>254</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="G41" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="G41" s="10" t="s">
-        <v>229</v>
-      </c>
       <c r="H41" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="I41" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="I41" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="J41" s="9" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>276.83</v>
+        <v>5725.68</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>252.24</v>
+        <v>5507.6</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0</v>
+        <v>3.74397</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>2.4</v>
+        <v>36.7</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
@@ -24359,22 +24365,22 @@
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="W41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>101</v>
+        <v>257</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>24.59</v>
+        <v>218.08</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>252.24</v>
+        <v>5507.6</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>10.09</v>
+        <v>288.16</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24440,7 +24446,7 @@
         <v>74</v>
       </c>
       <c r="AW41" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX41" s="10" t="s">
         <v>77</v>
@@ -24493,79 +24499,79 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>304808</v>
+        <v>304827</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>229</v>
+        <v>66</v>
       </c>
       <c r="H42" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="I42" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="I42" s="9" t="s">
-        <v>101</v>
-      </c>
       <c r="J42" s="9" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>2961.42</v>
+        <v>2990.99</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>2730.6</v>
+        <v>2848.92</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0</v>
+        <v>0.149136</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>0</v>
+        <v>21.17</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="W42" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>101</v>
+        <v>257</v>
       </c>
       <c r="Y42" s="12" t="n">
-        <v>230.82</v>
+        <v>142.07</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>2730.6</v>
+        <v>2848.92</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>109.22</v>
+        <v>199.42</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24670,7 +24676,7 @@
         <v>78</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24687,7 +24693,7 @@
     </row>
     <row r="44" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
@@ -24713,7 +24719,7 @@
     </row>
     <row r="45" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="18" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B45" s="18" t="s">
         <v>12</v>
@@ -24722,7 +24728,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E45" s="18" t="s">
         <v>24</v>
@@ -24737,7 +24743,7 @@
         <v>27</v>
       </c>
       <c r="I45" s="18" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J45" s="18" t="s">
         <v>29</v>
@@ -24749,7 +24755,7 @@
         <v>30</v>
       </c>
       <c r="M45" s="18" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N45" s="18" t="s">
         <v>32</v>
@@ -24767,10 +24773,10 @@
         <v>16</v>
       </c>
       <c r="S45" s="18" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="T45" s="18" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="U45" s="18" t="s">
         <v>36</v>
@@ -24793,13 +24799,13 @@
         <v>0</v>
       </c>
       <c r="E46" s="19" t="n">
-        <v>4525.84</v>
+        <v>4397.79</v>
       </c>
       <c r="F46" s="19" t="n">
-        <v>219573.58</v>
+        <v>201386.08</v>
       </c>
       <c r="G46" s="19" t="n">
-        <v>13667.13</v>
+        <v>12296.65</v>
       </c>
       <c r="H46" s="19" t="n">
         <v>0</v>
@@ -24811,7 +24817,7 @@
         <v>0</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>224099.42</v>
+        <v>205783.87</v>
       </c>
       <c r="L46" s="19" t="n">
         <v>0</v>
@@ -24832,13 +24838,13 @@
         <v>0</v>
       </c>
       <c r="R46" s="20" t="n">
-        <v>9.239924</v>
+        <v>12.171018</v>
       </c>
       <c r="S46" s="19" t="n">
-        <v>218883.74</v>
+        <v>200696.24</v>
       </c>
       <c r="T46" s="19" t="n">
-        <v>224099.42</v>
+        <v>205783.87</v>
       </c>
       <c r="U46" s="19" t="n">
         <v>0</v>
@@ -24879,18 +24885,18 @@
         <v>45</v>
       </c>
       <c r="K47" s="18" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="L47" s="18" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="M47" s="18" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="n">
-        <v>5463.45</v>
+        <v>4555.03</v>
       </c>
       <c r="B48" s="19" t="n">
         <v>0</v>
@@ -24899,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="19" t="n">
-        <v>44.03</v>
+        <v>39.73</v>
       </c>
       <c r="E48" s="19" t="n">
         <v>0</v>
@@ -24934,7 +24940,7 @@
     </row>
     <row r="50" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="21" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B50" s="21"/>
       <c r="C50" s="21"/>
@@ -25072,7 +25078,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -25141,7 +25147,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -25210,7 +25216,7 @@
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -25348,7 +25354,7 @@
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -25417,7 +25423,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -25486,7 +25492,7 @@
     </row>
     <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -25555,7 +25561,7 @@
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -25624,7 +25630,7 @@
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1632" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1792" uniqueCount="296">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 10/04/2026 15:09:21</t>
+    <t xml:space="preserve">Emitido em: 14/04/2026 11:16:21</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -292,27 +292,6 @@
     <t xml:space="preserve">35260124855633000140550010000731981500237788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">287.740</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.430,32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260310691158000370550010002877401377243501</t>
-  </si>
-  <si>
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
@@ -598,18 +577,6 @@
     <t xml:space="preserve">35260408031381000188550010000377401002435022</t>
   </si>
   <si>
-    <t xml:space="preserve">20.116 - MS DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.769,12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260414624251000151550010000458691000329515</t>
-  </si>
-  <si>
     <t xml:space="preserve">609.316</t>
   </si>
   <si>
@@ -622,18 +589,6 @@
     <t xml:space="preserve">42260475339051000141550080006093161746898680</t>
   </si>
   <si>
-    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">257.716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.081,39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260458329608000144550010002577161002577176</t>
-  </si>
-  <si>
     <t xml:space="preserve">777 - IRMAOS FISCHER S.A IND. E COM.</t>
   </si>
   <si>
@@ -745,45 +700,6 @@
     <t xml:space="preserve">42260475339051000141550080006109591826854771</t>
   </si>
   <si>
-    <t xml:space="preserve">983 - AKZO NOBEL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.956.666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.379,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460561719009503550210019566661752518134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">378.387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">276,83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260482901000001441550100003783871691759640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">378.378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.961,42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260482901000001441550100003783781282056610</t>
-  </si>
-  <si>
     <t xml:space="preserve">32.977 - COMFORT DOOR IMPORTACAO E DISTRIBUICAO DE UTILIDADES</t>
   </si>
   <si>
@@ -815,6 +731,126 @@
   </si>
   <si>
     <t xml:space="preserve">31260402803462000172550030001287281653625632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.101 - SIMON MATERIAIS ELETRICOS E ELETRONICOS LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.614,34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31260407159430000361550010000871951461498240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">199.089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.808,67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260467718726000135550010001990891146023854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.410 - SAN HO COMERCIO IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.495,57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260417328359000195550010000829531413915718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.167 - ATLAS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">678.786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.798,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260489723837000172550000006787861159089544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">678.478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.702,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260489723837000172550000006784781707847980</t>
+  </si>
+  <si>
+    <t xml:space="preserve">691 - CARDAL ELETRO METALURGICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">167.788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.016,86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260443562859000105550010001677881991677880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.660 - DEXCO S.A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">834,40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181005963550010000422971206588350</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181005963550010000423031899818122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.056.783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93,88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050567831226868515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.056.785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050567851477858809</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17060,7 +17096,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM60"/>
+  <dimension ref="A1:BM64"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17814,7 +17850,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>302637</v>
+        <v>303022</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>90</v>
@@ -17841,25 +17877,25 @@
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>2430.32</v>
+        <v>835.52</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>2214.42</v>
+        <v>835.52</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0</v>
+        <v>0.000144</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>0.84</v>
+        <v>0.19</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
@@ -17871,7 +17907,7 @@
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
@@ -17880,13 +17916,13 @@
         <v>93</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>215.9</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>2214.42</v>
+        <v>835.52</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>88.57</v>
+        <v>58.49</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17952,7 +17988,7 @@
         <v>74</v>
       </c>
       <c r="AW7" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX7" s="10" t="s">
         <v>77</v>
@@ -18005,34 +18041,34 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>303022</v>
+        <v>303029</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>835.52</v>
+        <v>3316.88</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
@@ -18041,43 +18077,43 @@
         <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>835.52</v>
+        <v>3114.44</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.000144</v>
+        <v>0.012495</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>0.19</v>
+        <v>3.16</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>0</v>
+        <v>202.44</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>835.52</v>
+        <v>3114.44</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>58.49</v>
+        <v>218.01</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -18182,7 +18218,7 @@
         <v>78</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18196,25 +18232,25 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>303029</v>
+        <v>303204</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>105</v>
@@ -18223,25 +18259,25 @@
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>3316.88</v>
+        <v>2398.04</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>3114.44</v>
+        <v>2185</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.012495</v>
+        <v>0.2646</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
@@ -18253,22 +18289,22 @@
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>202.44</v>
+        <v>213.04</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>3114.44</v>
+        <v>2185</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>218.01</v>
+        <v>152.95</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18387,7 +18423,7 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>303204</v>
+        <v>303318</v>
       </c>
       <c r="B10" s="9" t="s">
         <v>108</v>
@@ -18399,67 +18435,67 @@
         <v>109</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>2398.04</v>
+        <v>31382.82</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>2185</v>
+        <v>31382.82</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.2646</v>
+        <v>4.8951</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>0</v>
+        <v>3571.2</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>213.04</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>2185</v>
+        <v>31382.82</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>152.95</v>
+        <v>2196.8</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18564,7 +18600,7 @@
         <v>78</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18578,19 +18614,19 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>303318</v>
+        <v>303868</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="H11" s="9" t="s">
         <v>118</v>
@@ -18605,25 +18641,25 @@
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>31382.82</v>
+        <v>2049.43</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>31382.82</v>
+        <v>2022.71</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>4.8951</v>
+        <v>0.195114</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>3571.2</v>
+        <v>12.34</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
@@ -18635,7 +18671,7 @@
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
@@ -18644,13 +18680,13 @@
         <v>119</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>0</v>
+        <v>26.72</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>31382.82</v>
+        <v>2022.71</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>2196.8</v>
+        <v>141.58</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18769,7 +18805,7 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>303868</v>
+        <v>303888</v>
       </c>
       <c r="B12" s="9" t="s">
         <v>123</v>
@@ -18787,61 +18823,61 @@
         <v>125</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2049.43</v>
+        <v>24133.88</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>2022.71</v>
+        <v>23742.79</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.195114</v>
+        <v>0.58142</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>12.34</v>
+        <v>113.07</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>26.72</v>
+        <v>391.09</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>2022.71</v>
+        <v>23742.79</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>141.58</v>
+        <v>1416.6</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18946,7 +18982,7 @@
         <v>78</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18960,52 +18996,52 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>303888</v>
+        <v>304124</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H13" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="J13" s="9" t="s">
         <v>132</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>127</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>24133.88</v>
+        <v>8370.87</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>23742.79</v>
+        <v>8370.87</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.58142</v>
+        <v>0.14134</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>113.07</v>
+        <v>100.96</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
@@ -19017,22 +19053,22 @@
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>391.09</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>23742.79</v>
+        <v>8370.87</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>1416.6</v>
+        <v>585.97</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19151,7 +19187,7 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>304124</v>
+        <v>304306</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>135</v>
@@ -19166,64 +19202,64 @@
         <v>83</v>
       </c>
       <c r="H14" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I14" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="J14" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="J14" s="9" t="s">
-        <v>139</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>8370.87</v>
+        <v>32599.23</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>8370.87</v>
+        <v>31660.33</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.14134</v>
+        <v>0</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>100.96</v>
+        <v>0</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>0</v>
+        <v>938.9</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>8370.87</v>
+        <v>31660.33</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>585.97</v>
+        <v>1266.38</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19328,7 +19364,7 @@
         <v>78</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19342,43 +19378,43 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>304306</v>
+        <v>304344</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>145</v>
+        <v>78</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>32599.23</v>
+        <v>1213.01</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>31660.33</v>
+        <v>1139</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
@@ -19387,34 +19423,34 @@
         <v>0</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>0</v>
+        <v>93.18</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>938.9</v>
+        <v>74.01</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>31660.33</v>
+        <v>1139</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>1266.38</v>
+        <v>79.73</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19483,7 +19519,7 @@
         <v>76</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19519,7 +19555,7 @@
         <v>78</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19533,25 +19569,25 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>304344</v>
+        <v>304391</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J16" s="9" t="s">
         <v>78</v>
@@ -19560,31 +19596,31 @@
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>1213.01</v>
+        <v>681.6</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>1139</v>
+        <v>651.08</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0</v>
+        <v>0.109581</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>93.18</v>
+        <v>2.46</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
@@ -19596,16 +19632,16 @@
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>74.01</v>
+        <v>30.52</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>1139</v>
+        <v>651.08</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>79.73</v>
+        <v>31.5</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19674,7 +19710,7 @@
         <v>76</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19710,7 +19746,7 @@
         <v>78</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19724,25 +19760,25 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>304391</v>
+        <v>304392</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>78</v>
@@ -19751,7 +19787,7 @@
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>681.6</v>
+        <v>687.84</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19760,22 +19796,22 @@
         <v>4</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>651.08</v>
+        <v>656.94</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.109581</v>
+        <v>0.146516</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>2.46</v>
+        <v>2.23</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19787,16 +19823,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>30.52</v>
+        <v>30.9</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>651.08</v>
+        <v>656.94</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>31.5</v>
+        <v>31.74</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19865,7 +19901,7 @@
         <v>76</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>75</v>
@@ -19901,7 +19937,7 @@
         <v>78</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19915,79 +19951,79 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>304392</v>
+        <v>304453</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>687.84</v>
+        <v>15673.98</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>656.94</v>
+        <v>15673.98</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.146516</v>
+        <v>0.40995</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>2.23</v>
+        <v>132.6</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>30.9</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>656.94</v>
+        <v>15673.98</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>31.74</v>
+        <v>1097.14</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20056,7 +20092,7 @@
         <v>76</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -20092,7 +20128,7 @@
         <v>78</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20106,79 +20142,79 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>304453</v>
+        <v>304525</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>161</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>145</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>15673.98</v>
+        <v>2415.02</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>15673.98</v>
+        <v>2339</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.40995</v>
+        <v>0.004</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>132.6</v>
+        <v>0.1</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>0</v>
+        <v>76.02</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>15673.98</v>
+        <v>2339</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>1097.14</v>
+        <v>163.73</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20283,7 +20319,7 @@
         <v>78</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20297,34 +20333,34 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>304525</v>
+        <v>304536</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G20" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>66</v>
-      </c>
       <c r="H20" s="9" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="I20" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="J20" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="J20" s="9" t="s">
-        <v>168</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2415.02</v>
+        <v>6516.28</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -20333,43 +20369,43 @@
         <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>2339</v>
+        <v>6516.28</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.004</v>
+        <v>0.092604</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>76.02</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>2339</v>
+        <v>6516.28</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>163.73</v>
+        <v>456.14</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20435,7 +20471,7 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX20" s="10" t="s">
         <v>77</v>
@@ -20474,7 +20510,7 @@
         <v>78</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20488,49 +20524,49 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>304536</v>
+        <v>304540</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="I21" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="J21" s="9" t="s">
         <v>167</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>174</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>6516.28</v>
+        <v>3349.44</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>6516.28</v>
+        <v>3244</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.092604</v>
+        <v>0</v>
       </c>
       <c r="R21" s="12" t="n">
         <v>0</v>
@@ -20539,28 +20575,28 @@
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>0</v>
+        <v>105.44</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>6516.28</v>
+        <v>3244</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>456.14</v>
+        <v>227.08</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20626,7 +20662,7 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX21" s="10" t="s">
         <v>77</v>
@@ -20665,7 +20701,7 @@
         <v>78</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20679,79 +20715,79 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>304540</v>
+        <v>304541</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>3349.44</v>
+        <v>63.18</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>3244</v>
+        <v>63.18</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0</v>
+        <v>0.000372</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>0</v>
+        <v>0.42</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>105.44</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>3244</v>
+        <v>63.18</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>227.08</v>
+        <v>4.42</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20856,7 +20892,7 @@
         <v>78</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20870,34 +20906,34 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>304541</v>
+        <v>304591</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>63.18</v>
+        <v>21.58</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20906,43 +20942,43 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>63.18</v>
+        <v>19.66</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.000372</v>
+        <v>0</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>63.18</v>
+        <v>19.66</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>4.42</v>
+        <v>1.38</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21008,10 +21044,10 @@
         <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21047,7 +21083,7 @@
         <v>78</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21061,25 +21097,25 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>304591</v>
+        <v>304596</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>78</v>
@@ -21088,16 +21124,16 @@
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>21.58</v>
+        <v>383.74</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>19.66</v>
+        <v>360.32</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
@@ -21106,13 +21142,13 @@
         <v>0</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>0</v>
+        <v>28.68</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
@@ -21124,16 +21160,16 @@
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>1.92</v>
+        <v>23.42</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>19.66</v>
+        <v>360.32</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>1.38</v>
+        <v>25.23</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21199,7 +21235,7 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX24" s="10" t="s">
         <v>88</v>
@@ -21238,7 +21274,7 @@
         <v>78</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21252,79 +21288,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>304596</v>
+        <v>304630</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>383.74</v>
+        <v>2455.75</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>360.32</v>
+        <v>2455.75</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0</v>
+        <v>0.008285</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>28.68</v>
+        <v>5.58</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>23.42</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>360.32</v>
+        <v>2455.75</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>25.23</v>
+        <v>171.9</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21390,10 +21426,10 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21429,7 +21465,7 @@
         <v>78</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21443,34 +21479,34 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>304599</v>
+        <v>304653</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>83</v>
+        <v>191</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>6769.12</v>
+        <v>9176.74</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -21479,43 +21515,43 @@
         <v>2</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>6223.01</v>
+        <v>7866.24</v>
       </c>
       <c r="P26" s="12" t="n">
-        <v>0</v>
+        <v>689.84</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>1.3</v>
+        <v>6E-006</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>34.8</v>
+        <v>0.37</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>546.11</v>
+        <v>620.66</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>6223.01</v>
+        <v>8556.08</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>267.58</v>
+        <v>342.24</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21581,7 +21617,7 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX26" s="10" t="s">
         <v>77</v>
@@ -21620,7 +21656,7 @@
         <v>78</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21634,10 +21670,10 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>304630</v>
+        <v>304676</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -21646,40 +21682,40 @@
         <v>196</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>197</v>
+        <v>98</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2455.75</v>
+        <v>11590</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>2455.75</v>
+        <v>11590</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.008285</v>
+        <v>0.08227</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>5.58</v>
+        <v>44.35</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
@@ -21691,22 +21727,22 @@
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="Y27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>2455.75</v>
+        <v>11590</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>171.9</v>
+        <v>811.3</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21772,7 +21808,7 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX27" s="10" t="s">
         <v>77</v>
@@ -21825,34 +21861,34 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>304647</v>
+        <v>304693</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>200</v>
+        <v>164</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>153</v>
+        <v>119</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>2081.39</v>
+        <v>215.05</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -21861,43 +21897,43 @@
         <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>1896.48</v>
+        <v>215.05</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0</v>
+        <v>0.001636</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>31.19</v>
+        <v>0</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>184.91</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>1896.48</v>
+        <v>215.05</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>132.75</v>
+        <v>15.05</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21966,7 +22002,7 @@
         <v>76</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>77</v>
+        <v>148</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -22002,7 +22038,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22016,79 +22052,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>304653</v>
+        <v>304714</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="G29" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="G29" s="10" t="s">
-        <v>206</v>
-      </c>
       <c r="H29" s="9" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>9176.74</v>
+        <v>164.77</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>7866.24</v>
+        <v>164.77</v>
       </c>
       <c r="P29" s="12" t="n">
-        <v>689.84</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>6E-006</v>
+        <v>0</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>0.37</v>
+        <v>0</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>620.66</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>8556.08</v>
+        <v>164.77</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>342.24</v>
+        <v>19.77</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22154,7 +22190,7 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX29" s="10" t="s">
         <v>77</v>
@@ -22193,7 +22229,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22207,34 +22243,34 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>304676</v>
+        <v>304715</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>66</v>
+        <v>205</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>11590</v>
+        <v>2551.37</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22243,43 +22279,43 @@
         <v>2</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>11590</v>
+        <v>2551.37</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.08227</v>
+        <v>0</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>44.35</v>
+        <v>0</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>11590</v>
+        <v>2551.37</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>811.3</v>
+        <v>306.16</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22384,7 +22420,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22398,34 +22434,34 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>304693</v>
+        <v>304716</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>126</v>
+        <v>160</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>78</v>
+        <v>186</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>215.05</v>
+        <v>1160.42</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -22434,43 +22470,43 @@
         <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>215.05</v>
+        <v>1089.6</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.001636</v>
+        <v>0</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>0</v>
+        <v>70.82</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>215.05</v>
+        <v>1089.6</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>15.05</v>
+        <v>43.58</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22539,7 +22575,7 @@
         <v>76</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22575,7 +22611,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22589,79 +22625,79 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>304714</v>
+        <v>304729</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>218</v>
+        <v>164</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>220</v>
+        <v>166</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>164.77</v>
+        <v>4573.08</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>164.77</v>
+        <v>4573.08</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0</v>
+        <v>0.000332</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>164.77</v>
+        <v>4573.08</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>19.77</v>
+        <v>320.11</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22766,7 +22802,7 @@
         <v>78</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22780,43 +22816,43 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>304715</v>
+        <v>304733</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>2551.37</v>
+        <v>24.23</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>2551.37</v>
+        <v>22.08</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
@@ -22831,28 +22867,28 @@
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>2551.37</v>
+        <v>22.08</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>306.16</v>
+        <v>0.88</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22918,10 +22954,10 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -22957,7 +22993,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -22971,34 +23007,34 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>304716</v>
+        <v>304766</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>220</v>
+        <v>166</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1160.42</v>
+        <v>5259.16</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -23007,43 +23043,43 @@
         <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>1089.6</v>
+        <v>5259.16</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0</v>
+        <v>0.017</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>70.82</v>
+        <v>0</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>1089.6</v>
+        <v>5259.16</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>43.58</v>
+        <v>368.14</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23148,7 +23184,7 @@
         <v>78</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23162,58 +23198,58 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>304729</v>
+        <v>304824</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>171</v>
+        <v>226</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>173</v>
+        <v>228</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>4573.08</v>
+        <v>5725.68</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>4573.08</v>
+        <v>5507.6</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.000332</v>
+        <v>3.74397</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>2.9</v>
+        <v>36.7</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
@@ -23225,16 +23261,16 @@
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>0</v>
+        <v>218.08</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>4573.08</v>
+        <v>5507.6</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>320.11</v>
+        <v>288.16</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23339,7 +23375,7 @@
         <v>78</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23353,79 +23389,79 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>304733</v>
+        <v>304827</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>206</v>
+        <v>66</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>24.23</v>
+        <v>2990.99</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>22.08</v>
+        <v>2848.92</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0</v>
+        <v>0.149136</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>0</v>
+        <v>21.17</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>2.15</v>
+        <v>142.07</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>22.08</v>
+        <v>2848.92</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>0.88</v>
+        <v>199.42</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23491,10 +23527,10 @@
         <v>74</v>
       </c>
       <c r="AW36" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX36" s="10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AY36" s="14" t="s">
         <v>75</v>
@@ -23530,7 +23566,7 @@
         <v>78</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23544,10 +23580,10 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>304766</v>
+        <v>304903</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>171</v>
+        <v>237</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
@@ -23556,67 +23592,67 @@
         <v>238</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>5259.16</v>
+        <v>1614.34</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>5259.16</v>
+        <v>1522.97</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.017</v>
+        <v>0.0617</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>2.91</v>
+        <v>5.1</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W37" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>0</v>
+        <v>91.37</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>5259.16</v>
+        <v>1522.97</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>368.14</v>
+        <v>106.61</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23721,7 +23757,7 @@
         <v>78</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23735,10 +23771,10 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>304798</v>
+        <v>304907</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>241</v>
+        <v>170</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -23747,31 +23783,31 @@
         <v>242</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>243</v>
+        <v>83</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>212</v>
+        <v>94</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>244</v>
+        <v>98</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>8379</v>
+        <v>13808.67</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>8379</v>
+        <v>13374</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
@@ -23780,34 +23816,34 @@
         <v>0</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>341.1</v>
+        <v>0</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="W38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>0</v>
+        <v>434.67</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>8379</v>
+        <v>13374</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>586.53</v>
+        <v>936.18</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23912,7 +23948,7 @@
         <v>78</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -23926,43 +23962,43 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>304807</v>
+        <v>304917</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>226</v>
+        <v>245</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="J39" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>276.83</v>
+        <v>6495.57</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>252.24</v>
+        <v>6005.86</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
@@ -23971,34 +24007,34 @@
         <v>0</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>2.4</v>
+        <v>120.9</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>101</v>
+        <v>229</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>24.59</v>
+        <v>489.71</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>252.24</v>
+        <v>6005.86</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>10.09</v>
+        <v>240.24</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24064,7 +24100,7 @@
         <v>74</v>
       </c>
       <c r="AW39" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX39" s="10" t="s">
         <v>77</v>
@@ -24103,7 +24139,7 @@
         <v>78</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24117,10 +24153,10 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>304808</v>
+        <v>304949</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>226</v>
+        <v>250</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
@@ -24129,67 +24165,67 @@
         <v>251</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>220</v>
+        <v>252</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>2961.42</v>
+        <v>4798.19</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>2730.6</v>
+        <v>4713</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0</v>
+        <v>0.49266</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>0</v>
+        <v>48.65</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="W40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>230.82</v>
+        <v>85.19</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>2730.6</v>
+        <v>4713</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>109.22</v>
+        <v>267.39</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24294,7 +24330,7 @@
         <v>78</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24308,52 +24344,52 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>304824</v>
+        <v>304950</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>257</v>
+        <v>105</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>5725.68</v>
+        <v>15702.6</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>5507.6</v>
+        <v>15378.6</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>3.74397</v>
+        <v>4.875648</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>36.7</v>
+        <v>325.2</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
@@ -24365,22 +24401,22 @@
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W41" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>257</v>
+        <v>105</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>218.08</v>
+        <v>324</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>5507.6</v>
+        <v>15378.6</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>288.16</v>
+        <v>1076.5</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24499,7 +24535,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>304827</v>
+        <v>304990</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>260</v>
@@ -24511,13 +24547,13 @@
         <v>261</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>257</v>
+        <v>105</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>262</v>
@@ -24526,25 +24562,25 @@
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>2990.99</v>
+        <v>28016.86</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>2848.92</v>
+        <v>24793.68</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.149136</v>
+        <v>0.164424</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>21.17</v>
+        <v>63.6</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
@@ -24556,22 +24592,22 @@
         <v>72</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="W42" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>257</v>
+        <v>105</v>
       </c>
       <c r="Y42" s="12" t="n">
-        <v>142.07</v>
+        <v>3223.18</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>2848.92</v>
+        <v>24793.68</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>199.42</v>
+        <v>1735.56</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24689,603 +24725,1091 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4"/>
+      <c r="A43" s="8" t="n">
+        <v>305036</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>834.4</v>
+      </c>
+      <c r="M43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="12" t="n">
+        <v>834.4</v>
+      </c>
+      <c r="P43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="13" t="n">
+        <v>0.859248</v>
+      </c>
+      <c r="R43" s="12" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="S43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="U43" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X43" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="12" t="n">
+        <v>834.4</v>
+      </c>
+      <c r="AA43" s="12" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="AB43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW43" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX43" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG43" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI43" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ43" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="BK43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM43" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="44" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="17" t="s">
+    <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="n">
+        <v>305037</v>
+      </c>
+      <c r="B44" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="17"/>
-      <c r="F44" s="17"/>
-      <c r="G44" s="17"/>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-      <c r="T44" s="17"/>
-      <c r="U44" s="17"/>
-      <c r="V44" s="17"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>834.4</v>
+      </c>
+      <c r="M44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" s="12" t="n">
+        <v>834.4</v>
+      </c>
+      <c r="P44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="13" t="n">
+        <v>0.859248</v>
+      </c>
+      <c r="R44" s="12" t="n">
+        <v>50.49</v>
+      </c>
+      <c r="S44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="U44" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X44" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="12" t="n">
+        <v>834.4</v>
+      </c>
+      <c r="AA44" s="12" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="AB44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW44" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX44" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI44" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ44" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="BK44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM44" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="45" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="18" t="s">
-        <v>266</v>
-      </c>
-      <c r="B45" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C45" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="18" t="s">
+    <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="8" t="n">
+        <v>305038</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I45" s="9" t="s">
         <v>267</v>
       </c>
-      <c r="E45" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F45" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G45" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H45" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I45" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="J45" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K45" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L45" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M45" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="N45" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O45" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P45" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q45" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R45" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S45" s="18" t="s">
-        <v>270</v>
-      </c>
-      <c r="T45" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="U45" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V45" s="18" t="s">
-        <v>37</v>
+      <c r="J45" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="M45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" s="12" t="n">
+        <v>88.15</v>
+      </c>
+      <c r="P45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="13" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="R45" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="U45" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X45" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y45" s="12" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Z45" s="12" t="n">
+        <v>88.15</v>
+      </c>
+      <c r="AA45" s="12" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW45" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX45" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF45" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG45" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI45" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ45" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="BK45" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL45" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM45" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="19" t="n">
+      <c r="A46" s="8" t="n">
+        <v>305039</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>93.88</v>
+      </c>
+      <c r="M46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O46" s="12" t="n">
+        <v>88.15</v>
+      </c>
+      <c r="P46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="13" t="n">
+        <v>0.000408</v>
+      </c>
+      <c r="R46" s="12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="U46" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X46" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="Y46" s="12" t="n">
+        <v>5.73</v>
+      </c>
+      <c r="Z46" s="12" t="n">
+        <v>88.15</v>
+      </c>
+      <c r="AA46" s="12" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="AB46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW46" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX46" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="AY46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG46" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI46" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ46" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="BK46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM46" s="16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="4"/>
+    </row>
+    <row r="48" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="B48" s="17"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
+      <c r="N48" s="17"/>
+      <c r="O48" s="17"/>
+      <c r="P48" s="17"/>
+      <c r="Q48" s="17"/>
+      <c r="R48" s="17"/>
+      <c r="S48" s="17"/>
+      <c r="T48" s="17"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="17"/>
+    </row>
+    <row r="49" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="18" t="s">
+        <v>278</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="E49" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F49" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G49" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H49" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I49" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="J49" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L49" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M49" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="N49" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O49" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P49" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q49" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R49" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S49" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="T49" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="U49" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V49" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="19" t="n">
+        <v>42</v>
+      </c>
+      <c r="B50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="19" t="n">
+        <v>689.84</v>
+      </c>
+      <c r="D50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="19" t="n">
+        <v>7855.04</v>
+      </c>
+      <c r="F50" s="19" t="n">
+        <v>247323.54</v>
+      </c>
+      <c r="G50" s="19" t="n">
+        <v>15538.21</v>
+      </c>
+      <c r="H50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="19" t="n">
+        <v>255178.58</v>
+      </c>
+      <c r="L50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" s="20" t="n">
+        <v>18.184762</v>
+      </c>
+      <c r="S50" s="19" t="n">
+        <v>246633.7</v>
+      </c>
+      <c r="T50" s="19" t="n">
+        <v>255178.58</v>
+      </c>
+      <c r="U50" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B51" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="19" t="n">
-        <v>689.84</v>
-      </c>
-      <c r="D46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="19" t="n">
-        <v>4397.79</v>
-      </c>
-      <c r="F46" s="19" t="n">
-        <v>201386.08</v>
-      </c>
-      <c r="G46" s="19" t="n">
-        <v>12296.65</v>
-      </c>
-      <c r="H46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="19" t="n">
-        <v>205783.87</v>
-      </c>
-      <c r="L46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="20" t="n">
-        <v>12.171018</v>
-      </c>
-      <c r="S46" s="19" t="n">
-        <v>200696.24</v>
-      </c>
-      <c r="T46" s="19" t="n">
-        <v>205783.87</v>
-      </c>
-      <c r="U46" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C47" s="18" t="s">
+      <c r="C51" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D51" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E47" s="18" t="s">
+      <c r="E51" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F47" s="18" t="s">
+      <c r="F51" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G47" s="18" t="s">
+      <c r="G51" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H47" s="18" t="s">
+      <c r="H51" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I47" s="18" t="s">
+      <c r="I51" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="J47" s="18" t="s">
+      <c r="J51" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K47" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="L47" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="M47" s="18" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="19" t="n">
-        <v>4555.03</v>
-      </c>
-      <c r="B48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="19" t="n">
-        <v>39.73</v>
-      </c>
-      <c r="E48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4"/>
-    </row>
-    <row r="50" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21" t="s">
-        <v>275</v>
-      </c>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
-      <c r="K50" s="21"/>
-      <c r="L50" s="21"/>
-      <c r="M50" s="21"/>
-      <c r="N50" s="21"/>
-      <c r="O50" s="21"/>
-      <c r="P50" s="21"/>
-      <c r="Q50" s="21"/>
-      <c r="R50" s="21"/>
-      <c r="S50" s="21"/>
-      <c r="T50" s="21"/>
-      <c r="U50" s="21"/>
-      <c r="V50" s="21"/>
-      <c r="W50" s="21"/>
-      <c r="X50" s="21"/>
-      <c r="Y50" s="21"/>
-      <c r="Z50" s="21"/>
-      <c r="AA50" s="21"/>
-      <c r="AB50" s="21"/>
-      <c r="AC50" s="21"/>
-      <c r="AD50" s="21"/>
-      <c r="AE50" s="21"/>
-      <c r="AF50" s="21"/>
-      <c r="AG50" s="21"/>
-      <c r="AH50" s="21"/>
-      <c r="AI50" s="21"/>
-      <c r="AJ50" s="21"/>
-      <c r="AK50" s="21"/>
-      <c r="AL50" s="21"/>
-      <c r="AM50" s="21"/>
-      <c r="AN50" s="21"/>
-      <c r="AO50" s="21"/>
-      <c r="AP50" s="21"/>
-      <c r="AQ50" s="21"/>
-      <c r="AR50" s="21"/>
-      <c r="AS50" s="21"/>
-      <c r="AT50" s="21"/>
-      <c r="AU50" s="21"/>
-      <c r="AV50" s="21"/>
-      <c r="AW50" s="21"/>
-      <c r="AX50" s="21"/>
-      <c r="AY50" s="21"/>
-      <c r="AZ50" s="21"/>
-      <c r="BA50" s="21"/>
-      <c r="BB50" s="21"/>
-      <c r="BC50" s="21"/>
-      <c r="BD50" s="21"/>
-      <c r="BE50" s="21"/>
-      <c r="BF50" s="21"/>
-      <c r="BG50" s="21"/>
-      <c r="BH50" s="21"/>
-      <c r="BI50" s="21"/>
-      <c r="BJ50" s="21"/>
-      <c r="BK50" s="21"/>
-      <c r="BL50" s="21"/>
-      <c r="BM50" s="21"/>
-    </row>
-    <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="4"/>
-      <c r="AC51" s="4"/>
-      <c r="AD51" s="4"/>
-      <c r="AE51" s="4"/>
-      <c r="AF51" s="4"/>
-      <c r="AG51" s="4"/>
-      <c r="AH51" s="4"/>
-      <c r="AI51" s="4"/>
-      <c r="AJ51" s="4"/>
-      <c r="AK51" s="4"/>
-      <c r="AL51" s="4"/>
-      <c r="AM51" s="4"/>
-      <c r="AN51" s="4"/>
-      <c r="AO51" s="4"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="4"/>
-      <c r="AR51" s="4"/>
-      <c r="AS51" s="4"/>
-      <c r="AT51" s="4"/>
-      <c r="AU51" s="4"/>
-      <c r="AV51" s="4"/>
-      <c r="AW51" s="4"/>
-      <c r="AX51" s="4"/>
-      <c r="AY51" s="4"/>
-      <c r="AZ51" s="4"/>
-      <c r="BA51" s="4"/>
-      <c r="BB51" s="4"/>
-      <c r="BC51" s="4"/>
-      <c r="BD51" s="4"/>
-      <c r="BE51" s="4"/>
-      <c r="BF51" s="4"/>
-      <c r="BG51" s="4"/>
-      <c r="BH51" s="4"/>
-      <c r="BI51" s="4"/>
-      <c r="BJ51" s="4"/>
-      <c r="BK51" s="4"/>
-      <c r="BL51" s="4"/>
-      <c r="BM51" s="4"/>
+      <c r="K51" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="L51" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="M51" s="18" t="s">
+        <v>286</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-      <c r="W52" s="4"/>
-      <c r="X52" s="4"/>
-      <c r="Y52" s="4"/>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
-      <c r="AB52" s="4"/>
-      <c r="AC52" s="4"/>
-      <c r="AD52" s="4"/>
-      <c r="AE52" s="4"/>
-      <c r="AF52" s="4"/>
-      <c r="AG52" s="4"/>
-      <c r="AH52" s="4"/>
-      <c r="AI52" s="4"/>
-      <c r="AJ52" s="4"/>
-      <c r="AK52" s="4"/>
-      <c r="AL52" s="4"/>
-      <c r="AM52" s="4"/>
-      <c r="AN52" s="4"/>
-      <c r="AO52" s="4"/>
-      <c r="AP52" s="4"/>
-      <c r="AQ52" s="4"/>
-      <c r="AR52" s="4"/>
-      <c r="AS52" s="4"/>
-      <c r="AT52" s="4"/>
-      <c r="AU52" s="4"/>
-      <c r="AV52" s="4"/>
-      <c r="AW52" s="4"/>
-      <c r="AX52" s="4"/>
-      <c r="AY52" s="4"/>
-      <c r="AZ52" s="4"/>
-      <c r="BA52" s="4"/>
-      <c r="BB52" s="4"/>
-      <c r="BC52" s="4"/>
-      <c r="BD52" s="4"/>
-      <c r="BE52" s="4"/>
-      <c r="BF52" s="4"/>
-      <c r="BG52" s="4"/>
-      <c r="BH52" s="4"/>
-      <c r="BI52" s="4"/>
-      <c r="BJ52" s="4"/>
-      <c r="BK52" s="4"/>
-      <c r="BL52" s="4"/>
-      <c r="BM52" s="4"/>
+      <c r="A52" s="19" t="n">
+        <v>4841.92</v>
+      </c>
+      <c r="B52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="19" t="n">
+        <v>44.38</v>
+      </c>
+      <c r="E52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
-      <c r="AB53" s="4"/>
-      <c r="AC53" s="4"/>
-      <c r="AD53" s="4"/>
-      <c r="AE53" s="4"/>
-      <c r="AF53" s="4"/>
-      <c r="AG53" s="4"/>
-      <c r="AH53" s="4"/>
-      <c r="AI53" s="4"/>
-      <c r="AJ53" s="4"/>
-      <c r="AK53" s="4"/>
-      <c r="AL53" s="4"/>
-      <c r="AM53" s="4"/>
-      <c r="AN53" s="4"/>
-      <c r="AO53" s="4"/>
-      <c r="AP53" s="4"/>
-      <c r="AQ53" s="4"/>
-      <c r="AR53" s="4"/>
-      <c r="AS53" s="4"/>
-      <c r="AT53" s="4"/>
-      <c r="AU53" s="4"/>
-      <c r="AV53" s="4"/>
-      <c r="AW53" s="4"/>
-      <c r="AX53" s="4"/>
-      <c r="AY53" s="4"/>
-      <c r="AZ53" s="4"/>
-      <c r="BA53" s="4"/>
-      <c r="BB53" s="4"/>
-      <c r="BC53" s="4"/>
-      <c r="BD53" s="4"/>
-      <c r="BE53" s="4"/>
-      <c r="BF53" s="4"/>
-      <c r="BG53" s="4"/>
-      <c r="BH53" s="4"/>
-      <c r="BI53" s="4"/>
-      <c r="BJ53" s="4"/>
-      <c r="BK53" s="4"/>
-      <c r="BL53" s="4"/>
-      <c r="BM53" s="4"/>
+      <c r="A53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
-      <c r="Z54" s="4"/>
-      <c r="AA54" s="4"/>
-      <c r="AB54" s="4"/>
-      <c r="AC54" s="4"/>
-      <c r="AD54" s="4"/>
-      <c r="AE54" s="4"/>
-      <c r="AF54" s="4"/>
-      <c r="AG54" s="4"/>
-      <c r="AH54" s="4"/>
-      <c r="AI54" s="4"/>
-      <c r="AJ54" s="4"/>
-      <c r="AK54" s="4"/>
-      <c r="AL54" s="4"/>
-      <c r="AM54" s="4"/>
-      <c r="AN54" s="4"/>
-      <c r="AO54" s="4"/>
-      <c r="AP54" s="4"/>
-      <c r="AQ54" s="4"/>
-      <c r="AR54" s="4"/>
-      <c r="AS54" s="4"/>
-      <c r="AT54" s="4"/>
-      <c r="AU54" s="4"/>
-      <c r="AV54" s="4"/>
-      <c r="AW54" s="4"/>
-      <c r="AX54" s="4"/>
-      <c r="AY54" s="4"/>
-      <c r="AZ54" s="4"/>
-      <c r="BA54" s="4"/>
-      <c r="BB54" s="4"/>
-      <c r="BC54" s="4"/>
-      <c r="BD54" s="4"/>
-      <c r="BE54" s="4"/>
-      <c r="BF54" s="4"/>
-      <c r="BG54" s="4"/>
-      <c r="BH54" s="4"/>
-      <c r="BI54" s="4"/>
-      <c r="BJ54" s="4"/>
-      <c r="BK54" s="4"/>
-      <c r="BL54" s="4"/>
-      <c r="BM54" s="4"/>
+    <row r="54" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="21"/>
+      <c r="P54" s="21"/>
+      <c r="Q54" s="21"/>
+      <c r="R54" s="21"/>
+      <c r="S54" s="21"/>
+      <c r="T54" s="21"/>
+      <c r="U54" s="21"/>
+      <c r="V54" s="21"/>
+      <c r="W54" s="21"/>
+      <c r="X54" s="21"/>
+      <c r="Y54" s="21"/>
+      <c r="Z54" s="21"/>
+      <c r="AA54" s="21"/>
+      <c r="AB54" s="21"/>
+      <c r="AC54" s="21"/>
+      <c r="AD54" s="21"/>
+      <c r="AE54" s="21"/>
+      <c r="AF54" s="21"/>
+      <c r="AG54" s="21"/>
+      <c r="AH54" s="21"/>
+      <c r="AI54" s="21"/>
+      <c r="AJ54" s="21"/>
+      <c r="AK54" s="21"/>
+      <c r="AL54" s="21"/>
+      <c r="AM54" s="21"/>
+      <c r="AN54" s="21"/>
+      <c r="AO54" s="21"/>
+      <c r="AP54" s="21"/>
+      <c r="AQ54" s="21"/>
+      <c r="AR54" s="21"/>
+      <c r="AS54" s="21"/>
+      <c r="AT54" s="21"/>
+      <c r="AU54" s="21"/>
+      <c r="AV54" s="21"/>
+      <c r="AW54" s="21"/>
+      <c r="AX54" s="21"/>
+      <c r="AY54" s="21"/>
+      <c r="AZ54" s="21"/>
+      <c r="BA54" s="21"/>
+      <c r="BB54" s="21"/>
+      <c r="BC54" s="21"/>
+      <c r="BD54" s="21"/>
+      <c r="BE54" s="21"/>
+      <c r="BF54" s="21"/>
+      <c r="BG54" s="21"/>
+      <c r="BH54" s="21"/>
+      <c r="BI54" s="21"/>
+      <c r="BJ54" s="21"/>
+      <c r="BK54" s="21"/>
+      <c r="BL54" s="21"/>
+      <c r="BM54" s="21"/>
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="4" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -25354,7 +25878,7 @@
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -25423,7 +25947,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -25492,7 +26016,7 @@
     </row>
     <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="4" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -25561,7 +26085,7 @@
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>282</v>
+        <v>22</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -25630,7 +26154,7 @@
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -25697,8 +26221,284 @@
       <c r="BL60" s="4"/>
       <c r="BM60" s="4"/>
     </row>
+    <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="4"/>
+      <c r="AB61" s="4"/>
+      <c r="AC61" s="4"/>
+      <c r="AD61" s="4"/>
+      <c r="AE61" s="4"/>
+      <c r="AF61" s="4"/>
+      <c r="AG61" s="4"/>
+      <c r="AH61" s="4"/>
+      <c r="AI61" s="4"/>
+      <c r="AJ61" s="4"/>
+      <c r="AK61" s="4"/>
+      <c r="AL61" s="4"/>
+      <c r="AM61" s="4"/>
+      <c r="AN61" s="4"/>
+      <c r="AO61" s="4"/>
+      <c r="AP61" s="4"/>
+      <c r="AQ61" s="4"/>
+      <c r="AR61" s="4"/>
+      <c r="AS61" s="4"/>
+      <c r="AT61" s="4"/>
+      <c r="AU61" s="4"/>
+      <c r="AV61" s="4"/>
+      <c r="AW61" s="4"/>
+      <c r="AX61" s="4"/>
+      <c r="AY61" s="4"/>
+      <c r="AZ61" s="4"/>
+      <c r="BA61" s="4"/>
+      <c r="BB61" s="4"/>
+      <c r="BC61" s="4"/>
+      <c r="BD61" s="4"/>
+      <c r="BE61" s="4"/>
+      <c r="BF61" s="4"/>
+      <c r="BG61" s="4"/>
+      <c r="BH61" s="4"/>
+      <c r="BI61" s="4"/>
+      <c r="BJ61" s="4"/>
+      <c r="BK61" s="4"/>
+      <c r="BL61" s="4"/>
+      <c r="BM61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="4"/>
+      <c r="AB62" s="4"/>
+      <c r="AC62" s="4"/>
+      <c r="AD62" s="4"/>
+      <c r="AE62" s="4"/>
+      <c r="AF62" s="4"/>
+      <c r="AG62" s="4"/>
+      <c r="AH62" s="4"/>
+      <c r="AI62" s="4"/>
+      <c r="AJ62" s="4"/>
+      <c r="AK62" s="4"/>
+      <c r="AL62" s="4"/>
+      <c r="AM62" s="4"/>
+      <c r="AN62" s="4"/>
+      <c r="AO62" s="4"/>
+      <c r="AP62" s="4"/>
+      <c r="AQ62" s="4"/>
+      <c r="AR62" s="4"/>
+      <c r="AS62" s="4"/>
+      <c r="AT62" s="4"/>
+      <c r="AU62" s="4"/>
+      <c r="AV62" s="4"/>
+      <c r="AW62" s="4"/>
+      <c r="AX62" s="4"/>
+      <c r="AY62" s="4"/>
+      <c r="AZ62" s="4"/>
+      <c r="BA62" s="4"/>
+      <c r="BB62" s="4"/>
+      <c r="BC62" s="4"/>
+      <c r="BD62" s="4"/>
+      <c r="BE62" s="4"/>
+      <c r="BF62" s="4"/>
+      <c r="BG62" s="4"/>
+      <c r="BH62" s="4"/>
+      <c r="BI62" s="4"/>
+      <c r="BJ62" s="4"/>
+      <c r="BK62" s="4"/>
+      <c r="BL62" s="4"/>
+      <c r="BM62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
+      <c r="AB63" s="4"/>
+      <c r="AC63" s="4"/>
+      <c r="AD63" s="4"/>
+      <c r="AE63" s="4"/>
+      <c r="AF63" s="4"/>
+      <c r="AG63" s="4"/>
+      <c r="AH63" s="4"/>
+      <c r="AI63" s="4"/>
+      <c r="AJ63" s="4"/>
+      <c r="AK63" s="4"/>
+      <c r="AL63" s="4"/>
+      <c r="AM63" s="4"/>
+      <c r="AN63" s="4"/>
+      <c r="AO63" s="4"/>
+      <c r="AP63" s="4"/>
+      <c r="AQ63" s="4"/>
+      <c r="AR63" s="4"/>
+      <c r="AS63" s="4"/>
+      <c r="AT63" s="4"/>
+      <c r="AU63" s="4"/>
+      <c r="AV63" s="4"/>
+      <c r="AW63" s="4"/>
+      <c r="AX63" s="4"/>
+      <c r="AY63" s="4"/>
+      <c r="AZ63" s="4"/>
+      <c r="BA63" s="4"/>
+      <c r="BB63" s="4"/>
+      <c r="BC63" s="4"/>
+      <c r="BD63" s="4"/>
+      <c r="BE63" s="4"/>
+      <c r="BF63" s="4"/>
+      <c r="BG63" s="4"/>
+      <c r="BH63" s="4"/>
+      <c r="BI63" s="4"/>
+      <c r="BJ63" s="4"/>
+      <c r="BK63" s="4"/>
+      <c r="BL63" s="4"/>
+      <c r="BM63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
+      <c r="AB64" s="4"/>
+      <c r="AC64" s="4"/>
+      <c r="AD64" s="4"/>
+      <c r="AE64" s="4"/>
+      <c r="AF64" s="4"/>
+      <c r="AG64" s="4"/>
+      <c r="AH64" s="4"/>
+      <c r="AI64" s="4"/>
+      <c r="AJ64" s="4"/>
+      <c r="AK64" s="4"/>
+      <c r="AL64" s="4"/>
+      <c r="AM64" s="4"/>
+      <c r="AN64" s="4"/>
+      <c r="AO64" s="4"/>
+      <c r="AP64" s="4"/>
+      <c r="AQ64" s="4"/>
+      <c r="AR64" s="4"/>
+      <c r="AS64" s="4"/>
+      <c r="AT64" s="4"/>
+      <c r="AU64" s="4"/>
+      <c r="AV64" s="4"/>
+      <c r="AW64" s="4"/>
+      <c r="AX64" s="4"/>
+      <c r="AY64" s="4"/>
+      <c r="AZ64" s="4"/>
+      <c r="BA64" s="4"/>
+      <c r="BB64" s="4"/>
+      <c r="BC64" s="4"/>
+      <c r="BD64" s="4"/>
+      <c r="BE64" s="4"/>
+      <c r="BF64" s="4"/>
+      <c r="BG64" s="4"/>
+      <c r="BH64" s="4"/>
+      <c r="BI64" s="4"/>
+      <c r="BJ64" s="4"/>
+      <c r="BK64" s="4"/>
+      <c r="BL64" s="4"/>
+      <c r="BM64" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="54">
+  <mergeCells count="58">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -25741,11 +26541,11 @@
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B42:E42"/>
-    <mergeCell ref="A44:V44"/>
-    <mergeCell ref="A50:BM50"/>
-    <mergeCell ref="A51:BM51"/>
-    <mergeCell ref="A52:BM52"/>
-    <mergeCell ref="A53:BM53"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="A48:V48"/>
     <mergeCell ref="A54:BM54"/>
     <mergeCell ref="A55:BM55"/>
     <mergeCell ref="A56:BM56"/>
@@ -25753,6 +26553,10 @@
     <mergeCell ref="A58:BM58"/>
     <mergeCell ref="A59:BM59"/>
     <mergeCell ref="A60:BM60"/>
+    <mergeCell ref="A61:BM61"/>
+    <mergeCell ref="A62:BM62"/>
+    <mergeCell ref="A63:BM63"/>
+    <mergeCell ref="A64:BM64"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3392" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3912" uniqueCount="447">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 24/04/2026 09:30:17</t>
+    <t xml:space="preserve">Emitido em: 27/04/2026 08:59:35</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -1148,6 +1148,162 @@
   </si>
   <si>
     <t xml:space="preserve">35260410713221000160550020000077651000094964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.582 - GRUPO MARMO E HIME COMERCIO, IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.727,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260420587017000285550010000391691109851164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.474 - ILUMI INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">429.259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.535,46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">397.405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">667,52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260404081167000185550000004292591357278494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260411389565000200570050003974051000835508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.264 - ATLAS GLOBAL COMERCIAL LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.073,12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260462939379000157550010000001151603202517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.069.507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">873,53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002190550010050695071552499815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.940 - BLUMENAU ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812.489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.809,19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260479416459000120550010008124891626818371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">622.733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.775,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006227331929481400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">622.722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.802,22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006227221129423673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">622.410</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.928,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006224101440180968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">620.129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.015,38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006201291390092137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.855 - DEXCO S.A - LOUCAS DECA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.145.854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.487,40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260497837181002271550010021458541827498190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">682.390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.593,36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260489723837000172550000006823901225625450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.808 - ABCC -REJUNTABRAS INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">788,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260454542238000178550010000965331000963341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.268,87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260429244900000247550010000667481169109514</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17393,7 +17549,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM104"/>
+  <dimension ref="A1:BM117"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -18380,10 +18536,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.49266</v>
+        <v>0.798872</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>48.65</v>
+        <v>110</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
@@ -18571,10 +18727,10 @@
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>4.875648</v>
+        <v>4.672608</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>325.2</v>
+        <v>331.44</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
@@ -20481,10 +20637,10 @@
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>1.50132</v>
+        <v>0.122892</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>14.29</v>
+        <v>16.63</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
@@ -33426,1016 +33582,3499 @@
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="4"/>
+      <c r="A87" s="8" t="n">
+        <v>305782</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>9727.81</v>
+      </c>
+      <c r="M87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O87" s="12" t="n">
+        <v>8735.3</v>
+      </c>
+      <c r="P87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="12" t="n">
+        <v>103.75</v>
+      </c>
+      <c r="S87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="14" t="s">
+        <v>378</v>
+      </c>
+      <c r="U87" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V87" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="W87" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X87" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y87" s="12" t="n">
+        <v>992.51</v>
+      </c>
+      <c r="Z87" s="12" t="n">
+        <v>8735.3</v>
+      </c>
+      <c r="AA87" s="12" t="n">
+        <v>349.42</v>
+      </c>
+      <c r="AB87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW87" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX87" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG87" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI87" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ87" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="BK87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM87" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="88" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="17" t="s">
-        <v>376</v>
-      </c>
-      <c r="B88" s="17"/>
-      <c r="C88" s="17"/>
-      <c r="D88" s="17"/>
-      <c r="E88" s="17"/>
-      <c r="F88" s="17"/>
-      <c r="G88" s="17"/>
-      <c r="H88" s="17"/>
-      <c r="I88" s="17"/>
-      <c r="J88" s="17"/>
-      <c r="K88" s="17"/>
-      <c r="L88" s="17"/>
-      <c r="M88" s="17"/>
-      <c r="N88" s="17"/>
-      <c r="O88" s="17"/>
-      <c r="P88" s="17"/>
-      <c r="Q88" s="17"/>
-      <c r="R88" s="17"/>
-      <c r="S88" s="17"/>
-      <c r="T88" s="17"/>
-      <c r="U88" s="17"/>
-      <c r="V88" s="17"/>
+    <row r="88" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="8" t="n">
+        <v>305789</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>19535.46</v>
+      </c>
+      <c r="M88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="O88" s="12" t="n">
+        <v>17883.94</v>
+      </c>
+      <c r="P88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="12" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="S88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="U88" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V88" s="12" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="W88" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X88" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y88" s="12" t="n">
+        <v>1651.52</v>
+      </c>
+      <c r="Z88" s="12" t="n">
+        <v>17883.94</v>
+      </c>
+      <c r="AA88" s="12" t="n">
+        <v>1251.88</v>
+      </c>
+      <c r="AB88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="12" t="n">
+        <v>667.52</v>
+      </c>
+      <c r="AE88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW88" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX88" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE88" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="BF88" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="BG88" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="BH88" s="14" t="s">
+        <v>385</v>
+      </c>
+      <c r="BI88" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="BJ88" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="BK88" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="BL88" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM88" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="89" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="18" t="s">
-        <v>377</v>
-      </c>
-      <c r="B89" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C89" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D89" s="18" t="s">
-        <v>378</v>
-      </c>
-      <c r="E89" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F89" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G89" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I89" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="J89" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K89" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L89" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M89" s="18" t="s">
-        <v>380</v>
-      </c>
-      <c r="N89" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O89" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P89" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q89" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R89" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S89" s="18" t="s">
-        <v>381</v>
-      </c>
-      <c r="T89" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="U89" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V89" s="18" t="s">
-        <v>37</v>
+    <row r="89" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="8" t="n">
+        <v>305791</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L89" s="12" t="n">
+        <v>8073.12</v>
+      </c>
+      <c r="M89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" s="12" t="n">
+        <v>7713.42</v>
+      </c>
+      <c r="P89" s="12" t="n">
+        <v>159.9</v>
+      </c>
+      <c r="Q89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="12" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="T89" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="U89" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V89" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="W89" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X89" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="12" t="n">
+        <v>7713.42</v>
+      </c>
+      <c r="AA89" s="12" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="AB89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW89" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="AX89" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG89" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI89" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ89" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="BK89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM89" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="19" t="n">
-        <v>82</v>
-      </c>
-      <c r="B90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="19" t="n">
-        <v>1457.89</v>
-      </c>
-      <c r="D90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="19" t="n">
-        <v>13268.68</v>
-      </c>
-      <c r="F90" s="19" t="n">
-        <v>541541.33</v>
-      </c>
-      <c r="G90" s="19" t="n">
-        <v>32518.17</v>
-      </c>
-      <c r="H90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K90" s="19" t="n">
-        <v>555113.34</v>
-      </c>
-      <c r="L90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R90" s="20" t="n">
-        <v>15.349029</v>
-      </c>
-      <c r="S90" s="19" t="n">
-        <v>540386.77</v>
-      </c>
-      <c r="T90" s="19" t="n">
-        <v>555113.34</v>
-      </c>
-      <c r="U90" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V90" s="19" t="n">
-        <v>0</v>
+      <c r="A90" s="8" t="n">
+        <v>305803</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>873.53</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O90" s="12" t="n">
+        <v>873.53</v>
+      </c>
+      <c r="P90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="13" t="n">
+        <v>0.000884</v>
+      </c>
+      <c r="R90" s="12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="U90" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V90" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W90" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X90" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="12" t="n">
+        <v>873.53</v>
+      </c>
+      <c r="AA90" s="12" t="n">
+        <v>61.15</v>
+      </c>
+      <c r="AB90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW90" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX90" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG90" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI90" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ90" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="BK90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM90" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B91" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C91" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D91" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E91" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F91" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G91" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H91" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I91" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J91" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K91" s="18" t="s">
-        <v>383</v>
-      </c>
-      <c r="L91" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="M91" s="18" t="s">
-        <v>385</v>
+    <row r="91" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="8" t="n">
+        <v>305806</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="K91" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <v>10809.19</v>
+      </c>
+      <c r="M91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O91" s="12" t="n">
+        <v>9859.84</v>
+      </c>
+      <c r="P91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="13" t="n">
+        <v>0.005008</v>
+      </c>
+      <c r="R91" s="12" t="n">
+        <v>9.3</v>
+      </c>
+      <c r="S91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="U91" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V91" s="12" t="n">
+        <v>79.08</v>
+      </c>
+      <c r="W91" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X91" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y91" s="12" t="n">
+        <v>949.35</v>
+      </c>
+      <c r="Z91" s="12" t="n">
+        <v>9859.84</v>
+      </c>
+      <c r="AA91" s="12" t="n">
+        <v>394.38</v>
+      </c>
+      <c r="AB91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW91" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX91" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG91" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI91" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ91" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="BK91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM91" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="19" t="n">
-        <v>2259.55</v>
-      </c>
-      <c r="B92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="19" t="n">
-        <v>37.66</v>
-      </c>
-      <c r="E92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M92" s="19" t="n">
-        <v>0</v>
+      <c r="A92" s="8" t="n">
+        <v>305820</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C92" s="9"/>
+      <c r="D92" s="9"/>
+      <c r="E92" s="9"/>
+      <c r="F92" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H92" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="I92" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J92" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="K92" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L92" s="12" t="n">
+        <v>1775.28</v>
+      </c>
+      <c r="M92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O92" s="12" t="n">
+        <v>1775.28</v>
+      </c>
+      <c r="P92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="13" t="n">
+        <v>0.005548</v>
+      </c>
+      <c r="R92" s="12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T92" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="U92" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V92" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W92" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X92" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="12" t="n">
+        <v>1775.28</v>
+      </c>
+      <c r="AA92" s="12" t="n">
+        <v>124.27</v>
+      </c>
+      <c r="AB92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV92" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW92" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX92" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF92" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG92" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH92" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI92" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ92" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="BK92" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL92" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM92" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4"/>
+      <c r="A93" s="8" t="n">
+        <v>305823</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C93" s="9"/>
+      <c r="D93" s="9"/>
+      <c r="E93" s="9"/>
+      <c r="F93" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="I93" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="K93" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L93" s="12" t="n">
+        <v>1802.22</v>
+      </c>
+      <c r="M93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" s="12" t="n">
+        <v>1802.22</v>
+      </c>
+      <c r="P93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="13" t="n">
+        <v>0.008001</v>
+      </c>
+      <c r="R93" s="12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="S93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T93" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="U93" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V93" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W93" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X93" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z93" s="12" t="n">
+        <v>1802.22</v>
+      </c>
+      <c r="AA93" s="12" t="n">
+        <v>126.16</v>
+      </c>
+      <c r="AB93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV93" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW93" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX93" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF93" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG93" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH93" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI93" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ93" s="9" t="s">
+        <v>404</v>
+      </c>
+      <c r="BK93" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL93" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM93" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="94" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="21" t="s">
-        <v>386</v>
-      </c>
-      <c r="B94" s="21"/>
-      <c r="C94" s="21"/>
-      <c r="D94" s="21"/>
-      <c r="E94" s="21"/>
-      <c r="F94" s="21"/>
-      <c r="G94" s="21"/>
-      <c r="H94" s="21"/>
-      <c r="I94" s="21"/>
-      <c r="J94" s="21"/>
-      <c r="K94" s="21"/>
-      <c r="L94" s="21"/>
-      <c r="M94" s="21"/>
-      <c r="N94" s="21"/>
-      <c r="O94" s="21"/>
-      <c r="P94" s="21"/>
-      <c r="Q94" s="21"/>
-      <c r="R94" s="21"/>
-      <c r="S94" s="21"/>
-      <c r="T94" s="21"/>
-      <c r="U94" s="21"/>
-      <c r="V94" s="21"/>
-      <c r="W94" s="21"/>
-      <c r="X94" s="21"/>
-      <c r="Y94" s="21"/>
-      <c r="Z94" s="21"/>
-      <c r="AA94" s="21"/>
-      <c r="AB94" s="21"/>
-      <c r="AC94" s="21"/>
-      <c r="AD94" s="21"/>
-      <c r="AE94" s="21"/>
-      <c r="AF94" s="21"/>
-      <c r="AG94" s="21"/>
-      <c r="AH94" s="21"/>
-      <c r="AI94" s="21"/>
-      <c r="AJ94" s="21"/>
-      <c r="AK94" s="21"/>
-      <c r="AL94" s="21"/>
-      <c r="AM94" s="21"/>
-      <c r="AN94" s="21"/>
-      <c r="AO94" s="21"/>
-      <c r="AP94" s="21"/>
-      <c r="AQ94" s="21"/>
-      <c r="AR94" s="21"/>
-      <c r="AS94" s="21"/>
-      <c r="AT94" s="21"/>
-      <c r="AU94" s="21"/>
-      <c r="AV94" s="21"/>
-      <c r="AW94" s="21"/>
-      <c r="AX94" s="21"/>
-      <c r="AY94" s="21"/>
-      <c r="AZ94" s="21"/>
-      <c r="BA94" s="21"/>
-      <c r="BB94" s="21"/>
-      <c r="BC94" s="21"/>
-      <c r="BD94" s="21"/>
-      <c r="BE94" s="21"/>
-      <c r="BF94" s="21"/>
-      <c r="BG94" s="21"/>
-      <c r="BH94" s="21"/>
-      <c r="BI94" s="21"/>
-      <c r="BJ94" s="21"/>
-      <c r="BK94" s="21"/>
-      <c r="BL94" s="21"/>
-      <c r="BM94" s="21"/>
+    <row r="94" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="8" t="n">
+        <v>305828</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H94" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="I94" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J94" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="K94" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L94" s="12" t="n">
+        <v>2928.48</v>
+      </c>
+      <c r="M94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" s="12" t="n">
+        <v>2928.48</v>
+      </c>
+      <c r="P94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="13" t="n">
+        <v>0.004946</v>
+      </c>
+      <c r="R94" s="12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="U94" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V94" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W94" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X94" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z94" s="12" t="n">
+        <v>2928.48</v>
+      </c>
+      <c r="AA94" s="12" t="n">
+        <v>204.99</v>
+      </c>
+      <c r="AB94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV94" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW94" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX94" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF94" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG94" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH94" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI94" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ94" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="BK94" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL94" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM94" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4"/>
-      <c r="S95" s="4"/>
-      <c r="T95" s="4"/>
-      <c r="U95" s="4"/>
-      <c r="V95" s="4"/>
-      <c r="W95" s="4"/>
-      <c r="X95" s="4"/>
-      <c r="Y95" s="4"/>
-      <c r="Z95" s="4"/>
-      <c r="AA95" s="4"/>
-      <c r="AB95" s="4"/>
-      <c r="AC95" s="4"/>
-      <c r="AD95" s="4"/>
-      <c r="AE95" s="4"/>
-      <c r="AF95" s="4"/>
-      <c r="AG95" s="4"/>
-      <c r="AH95" s="4"/>
-      <c r="AI95" s="4"/>
-      <c r="AJ95" s="4"/>
-      <c r="AK95" s="4"/>
-      <c r="AL95" s="4"/>
-      <c r="AM95" s="4"/>
-      <c r="AN95" s="4"/>
-      <c r="AO95" s="4"/>
-      <c r="AP95" s="4"/>
-      <c r="AQ95" s="4"/>
-      <c r="AR95" s="4"/>
-      <c r="AS95" s="4"/>
-      <c r="AT95" s="4"/>
-      <c r="AU95" s="4"/>
-      <c r="AV95" s="4"/>
-      <c r="AW95" s="4"/>
-      <c r="AX95" s="4"/>
-      <c r="AY95" s="4"/>
-      <c r="AZ95" s="4"/>
-      <c r="BA95" s="4"/>
-      <c r="BB95" s="4"/>
-      <c r="BC95" s="4"/>
-      <c r="BD95" s="4"/>
-      <c r="BE95" s="4"/>
-      <c r="BF95" s="4"/>
-      <c r="BG95" s="4"/>
-      <c r="BH95" s="4"/>
-      <c r="BI95" s="4"/>
-      <c r="BJ95" s="4"/>
-      <c r="BK95" s="4"/>
-      <c r="BL95" s="4"/>
-      <c r="BM95" s="4"/>
+      <c r="A95" s="8" t="n">
+        <v>305833</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="9" t="s">
+        <v>408</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="I95" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J95" s="9" t="s">
+        <v>200</v>
+      </c>
+      <c r="K95" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L95" s="12" t="n">
+        <v>43015.38</v>
+      </c>
+      <c r="M95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="O95" s="12" t="n">
+        <v>41146.7</v>
+      </c>
+      <c r="P95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="13" t="n">
+        <v>0.164217</v>
+      </c>
+      <c r="R95" s="12" t="n">
+        <v>74.73</v>
+      </c>
+      <c r="S95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T95" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="U95" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V95" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W95" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X95" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y95" s="12" t="n">
+        <v>1868.68</v>
+      </c>
+      <c r="Z95" s="12" t="n">
+        <v>41146.7</v>
+      </c>
+      <c r="AA95" s="12" t="n">
+        <v>2880.29</v>
+      </c>
+      <c r="AB95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV95" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW95" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX95" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF95" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG95" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH95" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI95" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ95" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="BK95" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL95" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM95" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
-      <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
-      <c r="V96" s="4"/>
-      <c r="W96" s="4"/>
-      <c r="X96" s="4"/>
-      <c r="Y96" s="4"/>
-      <c r="Z96" s="4"/>
-      <c r="AA96" s="4"/>
-      <c r="AB96" s="4"/>
-      <c r="AC96" s="4"/>
-      <c r="AD96" s="4"/>
-      <c r="AE96" s="4"/>
-      <c r="AF96" s="4"/>
-      <c r="AG96" s="4"/>
-      <c r="AH96" s="4"/>
-      <c r="AI96" s="4"/>
-      <c r="AJ96" s="4"/>
-      <c r="AK96" s="4"/>
-      <c r="AL96" s="4"/>
-      <c r="AM96" s="4"/>
-      <c r="AN96" s="4"/>
-      <c r="AO96" s="4"/>
-      <c r="AP96" s="4"/>
-      <c r="AQ96" s="4"/>
-      <c r="AR96" s="4"/>
-      <c r="AS96" s="4"/>
-      <c r="AT96" s="4"/>
-      <c r="AU96" s="4"/>
-      <c r="AV96" s="4"/>
-      <c r="AW96" s="4"/>
-      <c r="AX96" s="4"/>
-      <c r="AY96" s="4"/>
-      <c r="AZ96" s="4"/>
-      <c r="BA96" s="4"/>
-      <c r="BB96" s="4"/>
-      <c r="BC96" s="4"/>
-      <c r="BD96" s="4"/>
-      <c r="BE96" s="4"/>
-      <c r="BF96" s="4"/>
-      <c r="BG96" s="4"/>
-      <c r="BH96" s="4"/>
-      <c r="BI96" s="4"/>
-      <c r="BJ96" s="4"/>
-      <c r="BK96" s="4"/>
-      <c r="BL96" s="4"/>
-      <c r="BM96" s="4"/>
+      <c r="A96" s="8" t="n">
+        <v>305861</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="9"/>
+      <c r="F96" s="9" t="s">
+        <v>412</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H96" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="I96" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J96" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="K96" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L96" s="12" t="n">
+        <v>4487.4</v>
+      </c>
+      <c r="M96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O96" s="12" t="n">
+        <v>4487.4</v>
+      </c>
+      <c r="P96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="13" t="n">
+        <v>0.20424</v>
+      </c>
+      <c r="R96" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="S96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="U96" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V96" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="W96" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X96" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="12" t="n">
+        <v>4487.4</v>
+      </c>
+      <c r="AA96" s="12" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AB96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV96" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW96" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX96" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF96" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG96" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH96" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI96" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ96" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="BK96" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL96" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM96" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="s">
-        <v>388</v>
-      </c>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="4"/>
-      <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
-      <c r="N97" s="4"/>
-      <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
-      <c r="R97" s="4"/>
-      <c r="S97" s="4"/>
-      <c r="T97" s="4"/>
-      <c r="U97" s="4"/>
-      <c r="V97" s="4"/>
-      <c r="W97" s="4"/>
-      <c r="X97" s="4"/>
-      <c r="Y97" s="4"/>
-      <c r="Z97" s="4"/>
-      <c r="AA97" s="4"/>
-      <c r="AB97" s="4"/>
-      <c r="AC97" s="4"/>
-      <c r="AD97" s="4"/>
-      <c r="AE97" s="4"/>
-      <c r="AF97" s="4"/>
-      <c r="AG97" s="4"/>
-      <c r="AH97" s="4"/>
-      <c r="AI97" s="4"/>
-      <c r="AJ97" s="4"/>
-      <c r="AK97" s="4"/>
-      <c r="AL97" s="4"/>
-      <c r="AM97" s="4"/>
-      <c r="AN97" s="4"/>
-      <c r="AO97" s="4"/>
-      <c r="AP97" s="4"/>
-      <c r="AQ97" s="4"/>
-      <c r="AR97" s="4"/>
-      <c r="AS97" s="4"/>
-      <c r="AT97" s="4"/>
-      <c r="AU97" s="4"/>
-      <c r="AV97" s="4"/>
-      <c r="AW97" s="4"/>
-      <c r="AX97" s="4"/>
-      <c r="AY97" s="4"/>
-      <c r="AZ97" s="4"/>
-      <c r="BA97" s="4"/>
-      <c r="BB97" s="4"/>
-      <c r="BC97" s="4"/>
-      <c r="BD97" s="4"/>
-      <c r="BE97" s="4"/>
-      <c r="BF97" s="4"/>
-      <c r="BG97" s="4"/>
-      <c r="BH97" s="4"/>
-      <c r="BI97" s="4"/>
-      <c r="BJ97" s="4"/>
-      <c r="BK97" s="4"/>
-      <c r="BL97" s="4"/>
-      <c r="BM97" s="4"/>
+      <c r="A97" s="8" t="n">
+        <v>305864</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C97" s="9"/>
+      <c r="D97" s="9"/>
+      <c r="E97" s="9"/>
+      <c r="F97" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="I97" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="K97" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>1593.36</v>
+      </c>
+      <c r="M97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O97" s="12" t="n">
+        <v>1593.36</v>
+      </c>
+      <c r="P97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="13" t="n">
+        <v>0.105336</v>
+      </c>
+      <c r="R97" s="12" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="S97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T97" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="U97" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V97" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="W97" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X97" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z97" s="12" t="n">
+        <v>1593.36</v>
+      </c>
+      <c r="AA97" s="12" t="n">
+        <v>63.73</v>
+      </c>
+      <c r="AB97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV97" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW97" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX97" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF97" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG97" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH97" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI97" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ97" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="BK97" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL97" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM97" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="4"/>
-      <c r="M98" s="4"/>
-      <c r="N98" s="4"/>
-      <c r="O98" s="4"/>
-      <c r="P98" s="4"/>
-      <c r="Q98" s="4"/>
-      <c r="R98" s="4"/>
-      <c r="S98" s="4"/>
-      <c r="T98" s="4"/>
-      <c r="U98" s="4"/>
-      <c r="V98" s="4"/>
-      <c r="W98" s="4"/>
-      <c r="X98" s="4"/>
-      <c r="Y98" s="4"/>
-      <c r="Z98" s="4"/>
-      <c r="AA98" s="4"/>
-      <c r="AB98" s="4"/>
-      <c r="AC98" s="4"/>
-      <c r="AD98" s="4"/>
-      <c r="AE98" s="4"/>
-      <c r="AF98" s="4"/>
-      <c r="AG98" s="4"/>
-      <c r="AH98" s="4"/>
-      <c r="AI98" s="4"/>
-      <c r="AJ98" s="4"/>
-      <c r="AK98" s="4"/>
-      <c r="AL98" s="4"/>
-      <c r="AM98" s="4"/>
-      <c r="AN98" s="4"/>
-      <c r="AO98" s="4"/>
-      <c r="AP98" s="4"/>
-      <c r="AQ98" s="4"/>
-      <c r="AR98" s="4"/>
-      <c r="AS98" s="4"/>
-      <c r="AT98" s="4"/>
-      <c r="AU98" s="4"/>
-      <c r="AV98" s="4"/>
-      <c r="AW98" s="4"/>
-      <c r="AX98" s="4"/>
-      <c r="AY98" s="4"/>
-      <c r="AZ98" s="4"/>
-      <c r="BA98" s="4"/>
-      <c r="BB98" s="4"/>
-      <c r="BC98" s="4"/>
-      <c r="BD98" s="4"/>
-      <c r="BE98" s="4"/>
-      <c r="BF98" s="4"/>
-      <c r="BG98" s="4"/>
-      <c r="BH98" s="4"/>
-      <c r="BI98" s="4"/>
-      <c r="BJ98" s="4"/>
-      <c r="BK98" s="4"/>
-      <c r="BL98" s="4"/>
-      <c r="BM98" s="4"/>
+      <c r="A98" s="8" t="n">
+        <v>305865</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="C98" s="9"/>
+      <c r="D98" s="9"/>
+      <c r="E98" s="9"/>
+      <c r="F98" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H98" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="I98" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J98" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="K98" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>788.62</v>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O98" s="12" t="n">
+        <v>788.62</v>
+      </c>
+      <c r="P98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="13" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="R98" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="S98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T98" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="U98" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V98" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="W98" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X98" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="12" t="n">
+        <v>788.62</v>
+      </c>
+      <c r="AA98" s="12" t="n">
+        <v>55.2</v>
+      </c>
+      <c r="AB98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV98" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW98" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX98" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF98" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG98" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH98" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI98" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ98" s="9" t="s">
+        <v>424</v>
+      </c>
+      <c r="BK98" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL98" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM98" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="4"/>
-      <c r="S99" s="4"/>
-      <c r="T99" s="4"/>
-      <c r="U99" s="4"/>
-      <c r="V99" s="4"/>
-      <c r="W99" s="4"/>
-      <c r="X99" s="4"/>
-      <c r="Y99" s="4"/>
-      <c r="Z99" s="4"/>
-      <c r="AA99" s="4"/>
-      <c r="AB99" s="4"/>
-      <c r="AC99" s="4"/>
-      <c r="AD99" s="4"/>
-      <c r="AE99" s="4"/>
-      <c r="AF99" s="4"/>
-      <c r="AG99" s="4"/>
-      <c r="AH99" s="4"/>
-      <c r="AI99" s="4"/>
-      <c r="AJ99" s="4"/>
-      <c r="AK99" s="4"/>
-      <c r="AL99" s="4"/>
-      <c r="AM99" s="4"/>
-      <c r="AN99" s="4"/>
-      <c r="AO99" s="4"/>
-      <c r="AP99" s="4"/>
-      <c r="AQ99" s="4"/>
-      <c r="AR99" s="4"/>
-      <c r="AS99" s="4"/>
-      <c r="AT99" s="4"/>
-      <c r="AU99" s="4"/>
-      <c r="AV99" s="4"/>
-      <c r="AW99" s="4"/>
-      <c r="AX99" s="4"/>
-      <c r="AY99" s="4"/>
-      <c r="AZ99" s="4"/>
-      <c r="BA99" s="4"/>
-      <c r="BB99" s="4"/>
-      <c r="BC99" s="4"/>
-      <c r="BD99" s="4"/>
-      <c r="BE99" s="4"/>
-      <c r="BF99" s="4"/>
-      <c r="BG99" s="4"/>
-      <c r="BH99" s="4"/>
-      <c r="BI99" s="4"/>
-      <c r="BJ99" s="4"/>
-      <c r="BK99" s="4"/>
-      <c r="BL99" s="4"/>
-      <c r="BM99" s="4"/>
+      <c r="A99" s="8" t="n">
+        <v>305866</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9" t="s">
+        <v>425</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="I99" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="J99" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="K99" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>4268.87</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O99" s="12" t="n">
+        <v>3805.45</v>
+      </c>
+      <c r="P99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T99" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="U99" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V99" s="12" t="n">
+        <v>52.96</v>
+      </c>
+      <c r="W99" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X99" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="Y99" s="12" t="n">
+        <v>463.42</v>
+      </c>
+      <c r="Z99" s="12" t="n">
+        <v>3805.45</v>
+      </c>
+      <c r="AA99" s="12" t="n">
+        <v>152.22</v>
+      </c>
+      <c r="AB99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV99" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW99" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX99" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF99" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG99" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH99" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI99" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ99" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="BK99" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL99" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM99" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="100" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="B100" s="4"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="4"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="4"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
-      <c r="N100" s="4"/>
-      <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
-      <c r="Q100" s="4"/>
-      <c r="R100" s="4"/>
-      <c r="S100" s="4"/>
-      <c r="T100" s="4"/>
-      <c r="U100" s="4"/>
-      <c r="V100" s="4"/>
-      <c r="W100" s="4"/>
-      <c r="X100" s="4"/>
-      <c r="Y100" s="4"/>
-      <c r="Z100" s="4"/>
-      <c r="AA100" s="4"/>
-      <c r="AB100" s="4"/>
-      <c r="AC100" s="4"/>
-      <c r="AD100" s="4"/>
-      <c r="AE100" s="4"/>
-      <c r="AF100" s="4"/>
-      <c r="AG100" s="4"/>
-      <c r="AH100" s="4"/>
-      <c r="AI100" s="4"/>
-      <c r="AJ100" s="4"/>
-      <c r="AK100" s="4"/>
-      <c r="AL100" s="4"/>
-      <c r="AM100" s="4"/>
-      <c r="AN100" s="4"/>
-      <c r="AO100" s="4"/>
-      <c r="AP100" s="4"/>
-      <c r="AQ100" s="4"/>
-      <c r="AR100" s="4"/>
-      <c r="AS100" s="4"/>
-      <c r="AT100" s="4"/>
-      <c r="AU100" s="4"/>
-      <c r="AV100" s="4"/>
-      <c r="AW100" s="4"/>
-      <c r="AX100" s="4"/>
-      <c r="AY100" s="4"/>
-      <c r="AZ100" s="4"/>
-      <c r="BA100" s="4"/>
-      <c r="BB100" s="4"/>
-      <c r="BC100" s="4"/>
-      <c r="BD100" s="4"/>
-      <c r="BE100" s="4"/>
-      <c r="BF100" s="4"/>
-      <c r="BG100" s="4"/>
-      <c r="BH100" s="4"/>
-      <c r="BI100" s="4"/>
-      <c r="BJ100" s="4"/>
-      <c r="BK100" s="4"/>
-      <c r="BL100" s="4"/>
-      <c r="BM100" s="4"/>
+      <c r="A100" s="4"/>
     </row>
-    <row r="101" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="4"/>
-      <c r="L101" s="4"/>
-      <c r="M101" s="4"/>
-      <c r="N101" s="4"/>
-      <c r="O101" s="4"/>
-      <c r="P101" s="4"/>
-      <c r="Q101" s="4"/>
-      <c r="R101" s="4"/>
-      <c r="S101" s="4"/>
-      <c r="T101" s="4"/>
-      <c r="U101" s="4"/>
-      <c r="V101" s="4"/>
-      <c r="W101" s="4"/>
-      <c r="X101" s="4"/>
-      <c r="Y101" s="4"/>
-      <c r="Z101" s="4"/>
-      <c r="AA101" s="4"/>
-      <c r="AB101" s="4"/>
-      <c r="AC101" s="4"/>
-      <c r="AD101" s="4"/>
-      <c r="AE101" s="4"/>
-      <c r="AF101" s="4"/>
-      <c r="AG101" s="4"/>
-      <c r="AH101" s="4"/>
-      <c r="AI101" s="4"/>
-      <c r="AJ101" s="4"/>
-      <c r="AK101" s="4"/>
-      <c r="AL101" s="4"/>
-      <c r="AM101" s="4"/>
-      <c r="AN101" s="4"/>
-      <c r="AO101" s="4"/>
-      <c r="AP101" s="4"/>
-      <c r="AQ101" s="4"/>
-      <c r="AR101" s="4"/>
-      <c r="AS101" s="4"/>
-      <c r="AT101" s="4"/>
-      <c r="AU101" s="4"/>
-      <c r="AV101" s="4"/>
-      <c r="AW101" s="4"/>
-      <c r="AX101" s="4"/>
-      <c r="AY101" s="4"/>
-      <c r="AZ101" s="4"/>
-      <c r="BA101" s="4"/>
-      <c r="BB101" s="4"/>
-      <c r="BC101" s="4"/>
-      <c r="BD101" s="4"/>
-      <c r="BE101" s="4"/>
-      <c r="BF101" s="4"/>
-      <c r="BG101" s="4"/>
-      <c r="BH101" s="4"/>
-      <c r="BI101" s="4"/>
-      <c r="BJ101" s="4"/>
-      <c r="BK101" s="4"/>
-      <c r="BL101" s="4"/>
-      <c r="BM101" s="4"/>
+    <row r="101" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="17" t="s">
+        <v>428</v>
+      </c>
+      <c r="B101" s="17"/>
+      <c r="C101" s="17"/>
+      <c r="D101" s="17"/>
+      <c r="E101" s="17"/>
+      <c r="F101" s="17"/>
+      <c r="G101" s="17"/>
+      <c r="H101" s="17"/>
+      <c r="I101" s="17"/>
+      <c r="J101" s="17"/>
+      <c r="K101" s="17"/>
+      <c r="L101" s="17"/>
+      <c r="M101" s="17"/>
+      <c r="N101" s="17"/>
+      <c r="O101" s="17"/>
+      <c r="P101" s="17"/>
+      <c r="Q101" s="17"/>
+      <c r="R101" s="17"/>
+      <c r="S101" s="17"/>
+      <c r="T101" s="17"/>
+      <c r="U101" s="17"/>
+      <c r="V101" s="17"/>
     </row>
-    <row r="102" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="B102" s="4"/>
-      <c r="C102" s="4"/>
-      <c r="D102" s="4"/>
-      <c r="E102" s="4"/>
-      <c r="F102" s="4"/>
-      <c r="G102" s="4"/>
-      <c r="H102" s="4"/>
-      <c r="I102" s="4"/>
-      <c r="J102" s="4"/>
-      <c r="K102" s="4"/>
-      <c r="L102" s="4"/>
-      <c r="M102" s="4"/>
-      <c r="N102" s="4"/>
-      <c r="O102" s="4"/>
-      <c r="P102" s="4"/>
-      <c r="Q102" s="4"/>
-      <c r="R102" s="4"/>
-      <c r="S102" s="4"/>
-      <c r="T102" s="4"/>
-      <c r="U102" s="4"/>
-      <c r="V102" s="4"/>
-      <c r="W102" s="4"/>
-      <c r="X102" s="4"/>
-      <c r="Y102" s="4"/>
-      <c r="Z102" s="4"/>
-      <c r="AA102" s="4"/>
-      <c r="AB102" s="4"/>
-      <c r="AC102" s="4"/>
-      <c r="AD102" s="4"/>
-      <c r="AE102" s="4"/>
-      <c r="AF102" s="4"/>
-      <c r="AG102" s="4"/>
-      <c r="AH102" s="4"/>
-      <c r="AI102" s="4"/>
-      <c r="AJ102" s="4"/>
-      <c r="AK102" s="4"/>
-      <c r="AL102" s="4"/>
-      <c r="AM102" s="4"/>
-      <c r="AN102" s="4"/>
-      <c r="AO102" s="4"/>
-      <c r="AP102" s="4"/>
-      <c r="AQ102" s="4"/>
-      <c r="AR102" s="4"/>
-      <c r="AS102" s="4"/>
-      <c r="AT102" s="4"/>
-      <c r="AU102" s="4"/>
-      <c r="AV102" s="4"/>
-      <c r="AW102" s="4"/>
-      <c r="AX102" s="4"/>
-      <c r="AY102" s="4"/>
-      <c r="AZ102" s="4"/>
-      <c r="BA102" s="4"/>
-      <c r="BB102" s="4"/>
-      <c r="BC102" s="4"/>
-      <c r="BD102" s="4"/>
-      <c r="BE102" s="4"/>
-      <c r="BF102" s="4"/>
-      <c r="BG102" s="4"/>
-      <c r="BH102" s="4"/>
-      <c r="BI102" s="4"/>
-      <c r="BJ102" s="4"/>
-      <c r="BK102" s="4"/>
-      <c r="BL102" s="4"/>
-      <c r="BM102" s="4"/>
+    <row r="102" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="B102" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="E102" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F102" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G102" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H102" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I102" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="J102" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K102" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L102" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M102" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="N102" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O102" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P102" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q102" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R102" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S102" s="18" t="s">
+        <v>433</v>
+      </c>
+      <c r="T102" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="U102" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V102" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="B103" s="4"/>
-      <c r="C103" s="4"/>
-      <c r="D103" s="4"/>
-      <c r="E103" s="4"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="4"/>
-      <c r="H103" s="4"/>
-      <c r="I103" s="4"/>
-      <c r="J103" s="4"/>
-      <c r="K103" s="4"/>
-      <c r="L103" s="4"/>
-      <c r="M103" s="4"/>
-      <c r="N103" s="4"/>
-      <c r="O103" s="4"/>
-      <c r="P103" s="4"/>
-      <c r="Q103" s="4"/>
-      <c r="R103" s="4"/>
-      <c r="S103" s="4"/>
-      <c r="T103" s="4"/>
-      <c r="U103" s="4"/>
-      <c r="V103" s="4"/>
-      <c r="W103" s="4"/>
-      <c r="X103" s="4"/>
-      <c r="Y103" s="4"/>
-      <c r="Z103" s="4"/>
-      <c r="AA103" s="4"/>
-      <c r="AB103" s="4"/>
-      <c r="AC103" s="4"/>
-      <c r="AD103" s="4"/>
-      <c r="AE103" s="4"/>
-      <c r="AF103" s="4"/>
-      <c r="AG103" s="4"/>
-      <c r="AH103" s="4"/>
-      <c r="AI103" s="4"/>
-      <c r="AJ103" s="4"/>
-      <c r="AK103" s="4"/>
-      <c r="AL103" s="4"/>
-      <c r="AM103" s="4"/>
-      <c r="AN103" s="4"/>
-      <c r="AO103" s="4"/>
-      <c r="AP103" s="4"/>
-      <c r="AQ103" s="4"/>
-      <c r="AR103" s="4"/>
-      <c r="AS103" s="4"/>
-      <c r="AT103" s="4"/>
-      <c r="AU103" s="4"/>
-      <c r="AV103" s="4"/>
-      <c r="AW103" s="4"/>
-      <c r="AX103" s="4"/>
-      <c r="AY103" s="4"/>
-      <c r="AZ103" s="4"/>
-      <c r="BA103" s="4"/>
-      <c r="BB103" s="4"/>
-      <c r="BC103" s="4"/>
-      <c r="BD103" s="4"/>
-      <c r="BE103" s="4"/>
-      <c r="BF103" s="4"/>
-      <c r="BG103" s="4"/>
-      <c r="BH103" s="4"/>
-      <c r="BI103" s="4"/>
-      <c r="BJ103" s="4"/>
-      <c r="BK103" s="4"/>
-      <c r="BL103" s="4"/>
-      <c r="BM103" s="4"/>
+      <c r="A103" s="19" t="n">
+        <v>95</v>
+      </c>
+      <c r="B103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="19" t="n">
+        <v>1617.79</v>
+      </c>
+      <c r="D103" s="19" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="E103" s="19" t="n">
+        <v>19194.16</v>
+      </c>
+      <c r="F103" s="19" t="n">
+        <v>644934.87</v>
+      </c>
+      <c r="G103" s="19" t="n">
+        <v>38466.26</v>
+      </c>
+      <c r="H103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="19" t="n">
+        <v>667.52</v>
+      </c>
+      <c r="K103" s="19" t="n">
+        <v>664792.06</v>
+      </c>
+      <c r="L103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" s="20" t="n">
+        <v>14.829953</v>
+      </c>
+      <c r="S103" s="19" t="n">
+        <v>643780.31</v>
+      </c>
+      <c r="T103" s="19" t="n">
+        <v>664792.06</v>
+      </c>
+      <c r="U103" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V103" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="104" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="B104" s="4"/>
-      <c r="C104" s="4"/>
-      <c r="D104" s="4"/>
-      <c r="E104" s="4"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="4"/>
-      <c r="H104" s="4"/>
-      <c r="I104" s="4"/>
-      <c r="J104" s="4"/>
-      <c r="K104" s="4"/>
-      <c r="L104" s="4"/>
-      <c r="M104" s="4"/>
-      <c r="N104" s="4"/>
-      <c r="O104" s="4"/>
-      <c r="P104" s="4"/>
-      <c r="Q104" s="4"/>
-      <c r="R104" s="4"/>
-      <c r="S104" s="4"/>
-      <c r="T104" s="4"/>
-      <c r="U104" s="4"/>
-      <c r="V104" s="4"/>
-      <c r="W104" s="4"/>
-      <c r="X104" s="4"/>
-      <c r="Y104" s="4"/>
-      <c r="Z104" s="4"/>
-      <c r="AA104" s="4"/>
-      <c r="AB104" s="4"/>
-      <c r="AC104" s="4"/>
-      <c r="AD104" s="4"/>
-      <c r="AE104" s="4"/>
-      <c r="AF104" s="4"/>
-      <c r="AG104" s="4"/>
-      <c r="AH104" s="4"/>
-      <c r="AI104" s="4"/>
-      <c r="AJ104" s="4"/>
-      <c r="AK104" s="4"/>
-      <c r="AL104" s="4"/>
-      <c r="AM104" s="4"/>
-      <c r="AN104" s="4"/>
-      <c r="AO104" s="4"/>
-      <c r="AP104" s="4"/>
-      <c r="AQ104" s="4"/>
-      <c r="AR104" s="4"/>
-      <c r="AS104" s="4"/>
-      <c r="AT104" s="4"/>
-      <c r="AU104" s="4"/>
-      <c r="AV104" s="4"/>
-      <c r="AW104" s="4"/>
-      <c r="AX104" s="4"/>
-      <c r="AY104" s="4"/>
-      <c r="AZ104" s="4"/>
-      <c r="BA104" s="4"/>
-      <c r="BB104" s="4"/>
-      <c r="BC104" s="4"/>
-      <c r="BD104" s="4"/>
-      <c r="BE104" s="4"/>
-      <c r="BF104" s="4"/>
-      <c r="BG104" s="4"/>
-      <c r="BH104" s="4"/>
-      <c r="BI104" s="4"/>
-      <c r="BJ104" s="4"/>
-      <c r="BK104" s="4"/>
-      <c r="BL104" s="4"/>
-      <c r="BM104" s="4"/>
+    <row r="104" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B104" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G104" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H104" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I104" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J104" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K104" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="L104" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="M104" s="18" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="19" t="n">
+        <v>2734.67</v>
+      </c>
+      <c r="B105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="19" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="E105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4"/>
+    </row>
+    <row r="107" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="B107" s="21"/>
+      <c r="C107" s="21"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="21"/>
+      <c r="F107" s="21"/>
+      <c r="G107" s="21"/>
+      <c r="H107" s="21"/>
+      <c r="I107" s="21"/>
+      <c r="J107" s="21"/>
+      <c r="K107" s="21"/>
+      <c r="L107" s="21"/>
+      <c r="M107" s="21"/>
+      <c r="N107" s="21"/>
+      <c r="O107" s="21"/>
+      <c r="P107" s="21"/>
+      <c r="Q107" s="21"/>
+      <c r="R107" s="21"/>
+      <c r="S107" s="21"/>
+      <c r="T107" s="21"/>
+      <c r="U107" s="21"/>
+      <c r="V107" s="21"/>
+      <c r="W107" s="21"/>
+      <c r="X107" s="21"/>
+      <c r="Y107" s="21"/>
+      <c r="Z107" s="21"/>
+      <c r="AA107" s="21"/>
+      <c r="AB107" s="21"/>
+      <c r="AC107" s="21"/>
+      <c r="AD107" s="21"/>
+      <c r="AE107" s="21"/>
+      <c r="AF107" s="21"/>
+      <c r="AG107" s="21"/>
+      <c r="AH107" s="21"/>
+      <c r="AI107" s="21"/>
+      <c r="AJ107" s="21"/>
+      <c r="AK107" s="21"/>
+      <c r="AL107" s="21"/>
+      <c r="AM107" s="21"/>
+      <c r="AN107" s="21"/>
+      <c r="AO107" s="21"/>
+      <c r="AP107" s="21"/>
+      <c r="AQ107" s="21"/>
+      <c r="AR107" s="21"/>
+      <c r="AS107" s="21"/>
+      <c r="AT107" s="21"/>
+      <c r="AU107" s="21"/>
+      <c r="AV107" s="21"/>
+      <c r="AW107" s="21"/>
+      <c r="AX107" s="21"/>
+      <c r="AY107" s="21"/>
+      <c r="AZ107" s="21"/>
+      <c r="BA107" s="21"/>
+      <c r="BB107" s="21"/>
+      <c r="BC107" s="21"/>
+      <c r="BD107" s="21"/>
+      <c r="BE107" s="21"/>
+      <c r="BF107" s="21"/>
+      <c r="BG107" s="21"/>
+      <c r="BH107" s="21"/>
+      <c r="BI107" s="21"/>
+      <c r="BJ107" s="21"/>
+      <c r="BK107" s="21"/>
+      <c r="BL107" s="21"/>
+      <c r="BM107" s="21"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="4"/>
+      <c r="S108" s="4"/>
+      <c r="T108" s="4"/>
+      <c r="U108" s="4"/>
+      <c r="V108" s="4"/>
+      <c r="W108" s="4"/>
+      <c r="X108" s="4"/>
+      <c r="Y108" s="4"/>
+      <c r="Z108" s="4"/>
+      <c r="AA108" s="4"/>
+      <c r="AB108" s="4"/>
+      <c r="AC108" s="4"/>
+      <c r="AD108" s="4"/>
+      <c r="AE108" s="4"/>
+      <c r="AF108" s="4"/>
+      <c r="AG108" s="4"/>
+      <c r="AH108" s="4"/>
+      <c r="AI108" s="4"/>
+      <c r="AJ108" s="4"/>
+      <c r="AK108" s="4"/>
+      <c r="AL108" s="4"/>
+      <c r="AM108" s="4"/>
+      <c r="AN108" s="4"/>
+      <c r="AO108" s="4"/>
+      <c r="AP108" s="4"/>
+      <c r="AQ108" s="4"/>
+      <c r="AR108" s="4"/>
+      <c r="AS108" s="4"/>
+      <c r="AT108" s="4"/>
+      <c r="AU108" s="4"/>
+      <c r="AV108" s="4"/>
+      <c r="AW108" s="4"/>
+      <c r="AX108" s="4"/>
+      <c r="AY108" s="4"/>
+      <c r="AZ108" s="4"/>
+      <c r="BA108" s="4"/>
+      <c r="BB108" s="4"/>
+      <c r="BC108" s="4"/>
+      <c r="BD108" s="4"/>
+      <c r="BE108" s="4"/>
+      <c r="BF108" s="4"/>
+      <c r="BG108" s="4"/>
+      <c r="BH108" s="4"/>
+      <c r="BI108" s="4"/>
+      <c r="BJ108" s="4"/>
+      <c r="BK108" s="4"/>
+      <c r="BL108" s="4"/>
+      <c r="BM108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="4"/>
+      <c r="R109" s="4"/>
+      <c r="S109" s="4"/>
+      <c r="T109" s="4"/>
+      <c r="U109" s="4"/>
+      <c r="V109" s="4"/>
+      <c r="W109" s="4"/>
+      <c r="X109" s="4"/>
+      <c r="Y109" s="4"/>
+      <c r="Z109" s="4"/>
+      <c r="AA109" s="4"/>
+      <c r="AB109" s="4"/>
+      <c r="AC109" s="4"/>
+      <c r="AD109" s="4"/>
+      <c r="AE109" s="4"/>
+      <c r="AF109" s="4"/>
+      <c r="AG109" s="4"/>
+      <c r="AH109" s="4"/>
+      <c r="AI109" s="4"/>
+      <c r="AJ109" s="4"/>
+      <c r="AK109" s="4"/>
+      <c r="AL109" s="4"/>
+      <c r="AM109" s="4"/>
+      <c r="AN109" s="4"/>
+      <c r="AO109" s="4"/>
+      <c r="AP109" s="4"/>
+      <c r="AQ109" s="4"/>
+      <c r="AR109" s="4"/>
+      <c r="AS109" s="4"/>
+      <c r="AT109" s="4"/>
+      <c r="AU109" s="4"/>
+      <c r="AV109" s="4"/>
+      <c r="AW109" s="4"/>
+      <c r="AX109" s="4"/>
+      <c r="AY109" s="4"/>
+      <c r="AZ109" s="4"/>
+      <c r="BA109" s="4"/>
+      <c r="BB109" s="4"/>
+      <c r="BC109" s="4"/>
+      <c r="BD109" s="4"/>
+      <c r="BE109" s="4"/>
+      <c r="BF109" s="4"/>
+      <c r="BG109" s="4"/>
+      <c r="BH109" s="4"/>
+      <c r="BI109" s="4"/>
+      <c r="BJ109" s="4"/>
+      <c r="BK109" s="4"/>
+      <c r="BL109" s="4"/>
+      <c r="BM109" s="4"/>
+    </row>
+    <row r="110" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A110" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="B110" s="4"/>
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="4"/>
+      <c r="R110" s="4"/>
+      <c r="S110" s="4"/>
+      <c r="T110" s="4"/>
+      <c r="U110" s="4"/>
+      <c r="V110" s="4"/>
+      <c r="W110" s="4"/>
+      <c r="X110" s="4"/>
+      <c r="Y110" s="4"/>
+      <c r="Z110" s="4"/>
+      <c r="AA110" s="4"/>
+      <c r="AB110" s="4"/>
+      <c r="AC110" s="4"/>
+      <c r="AD110" s="4"/>
+      <c r="AE110" s="4"/>
+      <c r="AF110" s="4"/>
+      <c r="AG110" s="4"/>
+      <c r="AH110" s="4"/>
+      <c r="AI110" s="4"/>
+      <c r="AJ110" s="4"/>
+      <c r="AK110" s="4"/>
+      <c r="AL110" s="4"/>
+      <c r="AM110" s="4"/>
+      <c r="AN110" s="4"/>
+      <c r="AO110" s="4"/>
+      <c r="AP110" s="4"/>
+      <c r="AQ110" s="4"/>
+      <c r="AR110" s="4"/>
+      <c r="AS110" s="4"/>
+      <c r="AT110" s="4"/>
+      <c r="AU110" s="4"/>
+      <c r="AV110" s="4"/>
+      <c r="AW110" s="4"/>
+      <c r="AX110" s="4"/>
+      <c r="AY110" s="4"/>
+      <c r="AZ110" s="4"/>
+      <c r="BA110" s="4"/>
+      <c r="BB110" s="4"/>
+      <c r="BC110" s="4"/>
+      <c r="BD110" s="4"/>
+      <c r="BE110" s="4"/>
+      <c r="BF110" s="4"/>
+      <c r="BG110" s="4"/>
+      <c r="BH110" s="4"/>
+      <c r="BI110" s="4"/>
+      <c r="BJ110" s="4"/>
+      <c r="BK110" s="4"/>
+      <c r="BL110" s="4"/>
+      <c r="BM110" s="4"/>
+    </row>
+    <row r="111" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A111" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="B111" s="4"/>
+      <c r="C111" s="4"/>
+      <c r="D111" s="4"/>
+      <c r="E111" s="4"/>
+      <c r="F111" s="4"/>
+      <c r="G111" s="4"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4"/>
+      <c r="L111" s="4"/>
+      <c r="M111" s="4"/>
+      <c r="N111" s="4"/>
+      <c r="O111" s="4"/>
+      <c r="P111" s="4"/>
+      <c r="Q111" s="4"/>
+      <c r="R111" s="4"/>
+      <c r="S111" s="4"/>
+      <c r="T111" s="4"/>
+      <c r="U111" s="4"/>
+      <c r="V111" s="4"/>
+      <c r="W111" s="4"/>
+      <c r="X111" s="4"/>
+      <c r="Y111" s="4"/>
+      <c r="Z111" s="4"/>
+      <c r="AA111" s="4"/>
+      <c r="AB111" s="4"/>
+      <c r="AC111" s="4"/>
+      <c r="AD111" s="4"/>
+      <c r="AE111" s="4"/>
+      <c r="AF111" s="4"/>
+      <c r="AG111" s="4"/>
+      <c r="AH111" s="4"/>
+      <c r="AI111" s="4"/>
+      <c r="AJ111" s="4"/>
+      <c r="AK111" s="4"/>
+      <c r="AL111" s="4"/>
+      <c r="AM111" s="4"/>
+      <c r="AN111" s="4"/>
+      <c r="AO111" s="4"/>
+      <c r="AP111" s="4"/>
+      <c r="AQ111" s="4"/>
+      <c r="AR111" s="4"/>
+      <c r="AS111" s="4"/>
+      <c r="AT111" s="4"/>
+      <c r="AU111" s="4"/>
+      <c r="AV111" s="4"/>
+      <c r="AW111" s="4"/>
+      <c r="AX111" s="4"/>
+      <c r="AY111" s="4"/>
+      <c r="AZ111" s="4"/>
+      <c r="BA111" s="4"/>
+      <c r="BB111" s="4"/>
+      <c r="BC111" s="4"/>
+      <c r="BD111" s="4"/>
+      <c r="BE111" s="4"/>
+      <c r="BF111" s="4"/>
+      <c r="BG111" s="4"/>
+      <c r="BH111" s="4"/>
+      <c r="BI111" s="4"/>
+      <c r="BJ111" s="4"/>
+      <c r="BK111" s="4"/>
+      <c r="BL111" s="4"/>
+      <c r="BM111" s="4"/>
+    </row>
+    <row r="112" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A112" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B112" s="4"/>
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4"/>
+      <c r="Q112" s="4"/>
+      <c r="R112" s="4"/>
+      <c r="S112" s="4"/>
+      <c r="T112" s="4"/>
+      <c r="U112" s="4"/>
+      <c r="V112" s="4"/>
+      <c r="W112" s="4"/>
+      <c r="X112" s="4"/>
+      <c r="Y112" s="4"/>
+      <c r="Z112" s="4"/>
+      <c r="AA112" s="4"/>
+      <c r="AB112" s="4"/>
+      <c r="AC112" s="4"/>
+      <c r="AD112" s="4"/>
+      <c r="AE112" s="4"/>
+      <c r="AF112" s="4"/>
+      <c r="AG112" s="4"/>
+      <c r="AH112" s="4"/>
+      <c r="AI112" s="4"/>
+      <c r="AJ112" s="4"/>
+      <c r="AK112" s="4"/>
+      <c r="AL112" s="4"/>
+      <c r="AM112" s="4"/>
+      <c r="AN112" s="4"/>
+      <c r="AO112" s="4"/>
+      <c r="AP112" s="4"/>
+      <c r="AQ112" s="4"/>
+      <c r="AR112" s="4"/>
+      <c r="AS112" s="4"/>
+      <c r="AT112" s="4"/>
+      <c r="AU112" s="4"/>
+      <c r="AV112" s="4"/>
+      <c r="AW112" s="4"/>
+      <c r="AX112" s="4"/>
+      <c r="AY112" s="4"/>
+      <c r="AZ112" s="4"/>
+      <c r="BA112" s="4"/>
+      <c r="BB112" s="4"/>
+      <c r="BC112" s="4"/>
+      <c r="BD112" s="4"/>
+      <c r="BE112" s="4"/>
+      <c r="BF112" s="4"/>
+      <c r="BG112" s="4"/>
+      <c r="BH112" s="4"/>
+      <c r="BI112" s="4"/>
+      <c r="BJ112" s="4"/>
+      <c r="BK112" s="4"/>
+      <c r="BL112" s="4"/>
+      <c r="BM112" s="4"/>
+    </row>
+    <row r="113" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B113" s="4"/>
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="4"/>
+      <c r="R113" s="4"/>
+      <c r="S113" s="4"/>
+      <c r="T113" s="4"/>
+      <c r="U113" s="4"/>
+      <c r="V113" s="4"/>
+      <c r="W113" s="4"/>
+      <c r="X113" s="4"/>
+      <c r="Y113" s="4"/>
+      <c r="Z113" s="4"/>
+      <c r="AA113" s="4"/>
+      <c r="AB113" s="4"/>
+      <c r="AC113" s="4"/>
+      <c r="AD113" s="4"/>
+      <c r="AE113" s="4"/>
+      <c r="AF113" s="4"/>
+      <c r="AG113" s="4"/>
+      <c r="AH113" s="4"/>
+      <c r="AI113" s="4"/>
+      <c r="AJ113" s="4"/>
+      <c r="AK113" s="4"/>
+      <c r="AL113" s="4"/>
+      <c r="AM113" s="4"/>
+      <c r="AN113" s="4"/>
+      <c r="AO113" s="4"/>
+      <c r="AP113" s="4"/>
+      <c r="AQ113" s="4"/>
+      <c r="AR113" s="4"/>
+      <c r="AS113" s="4"/>
+      <c r="AT113" s="4"/>
+      <c r="AU113" s="4"/>
+      <c r="AV113" s="4"/>
+      <c r="AW113" s="4"/>
+      <c r="AX113" s="4"/>
+      <c r="AY113" s="4"/>
+      <c r="AZ113" s="4"/>
+      <c r="BA113" s="4"/>
+      <c r="BB113" s="4"/>
+      <c r="BC113" s="4"/>
+      <c r="BD113" s="4"/>
+      <c r="BE113" s="4"/>
+      <c r="BF113" s="4"/>
+      <c r="BG113" s="4"/>
+      <c r="BH113" s="4"/>
+      <c r="BI113" s="4"/>
+      <c r="BJ113" s="4"/>
+      <c r="BK113" s="4"/>
+      <c r="BL113" s="4"/>
+      <c r="BM113" s="4"/>
+    </row>
+    <row r="114" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B114" s="4"/>
+      <c r="C114" s="4"/>
+      <c r="D114" s="4"/>
+      <c r="E114" s="4"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="4"/>
+      <c r="I114" s="4"/>
+      <c r="J114" s="4"/>
+      <c r="K114" s="4"/>
+      <c r="L114" s="4"/>
+      <c r="M114" s="4"/>
+      <c r="N114" s="4"/>
+      <c r="O114" s="4"/>
+      <c r="P114" s="4"/>
+      <c r="Q114" s="4"/>
+      <c r="R114" s="4"/>
+      <c r="S114" s="4"/>
+      <c r="T114" s="4"/>
+      <c r="U114" s="4"/>
+      <c r="V114" s="4"/>
+      <c r="W114" s="4"/>
+      <c r="X114" s="4"/>
+      <c r="Y114" s="4"/>
+      <c r="Z114" s="4"/>
+      <c r="AA114" s="4"/>
+      <c r="AB114" s="4"/>
+      <c r="AC114" s="4"/>
+      <c r="AD114" s="4"/>
+      <c r="AE114" s="4"/>
+      <c r="AF114" s="4"/>
+      <c r="AG114" s="4"/>
+      <c r="AH114" s="4"/>
+      <c r="AI114" s="4"/>
+      <c r="AJ114" s="4"/>
+      <c r="AK114" s="4"/>
+      <c r="AL114" s="4"/>
+      <c r="AM114" s="4"/>
+      <c r="AN114" s="4"/>
+      <c r="AO114" s="4"/>
+      <c r="AP114" s="4"/>
+      <c r="AQ114" s="4"/>
+      <c r="AR114" s="4"/>
+      <c r="AS114" s="4"/>
+      <c r="AT114" s="4"/>
+      <c r="AU114" s="4"/>
+      <c r="AV114" s="4"/>
+      <c r="AW114" s="4"/>
+      <c r="AX114" s="4"/>
+      <c r="AY114" s="4"/>
+      <c r="AZ114" s="4"/>
+      <c r="BA114" s="4"/>
+      <c r="BB114" s="4"/>
+      <c r="BC114" s="4"/>
+      <c r="BD114" s="4"/>
+      <c r="BE114" s="4"/>
+      <c r="BF114" s="4"/>
+      <c r="BG114" s="4"/>
+      <c r="BH114" s="4"/>
+      <c r="BI114" s="4"/>
+      <c r="BJ114" s="4"/>
+      <c r="BK114" s="4"/>
+      <c r="BL114" s="4"/>
+      <c r="BM114" s="4"/>
+    </row>
+    <row r="115" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="B115" s="4"/>
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="4"/>
+      <c r="R115" s="4"/>
+      <c r="S115" s="4"/>
+      <c r="T115" s="4"/>
+      <c r="U115" s="4"/>
+      <c r="V115" s="4"/>
+      <c r="W115" s="4"/>
+      <c r="X115" s="4"/>
+      <c r="Y115" s="4"/>
+      <c r="Z115" s="4"/>
+      <c r="AA115" s="4"/>
+      <c r="AB115" s="4"/>
+      <c r="AC115" s="4"/>
+      <c r="AD115" s="4"/>
+      <c r="AE115" s="4"/>
+      <c r="AF115" s="4"/>
+      <c r="AG115" s="4"/>
+      <c r="AH115" s="4"/>
+      <c r="AI115" s="4"/>
+      <c r="AJ115" s="4"/>
+      <c r="AK115" s="4"/>
+      <c r="AL115" s="4"/>
+      <c r="AM115" s="4"/>
+      <c r="AN115" s="4"/>
+      <c r="AO115" s="4"/>
+      <c r="AP115" s="4"/>
+      <c r="AQ115" s="4"/>
+      <c r="AR115" s="4"/>
+      <c r="AS115" s="4"/>
+      <c r="AT115" s="4"/>
+      <c r="AU115" s="4"/>
+      <c r="AV115" s="4"/>
+      <c r="AW115" s="4"/>
+      <c r="AX115" s="4"/>
+      <c r="AY115" s="4"/>
+      <c r="AZ115" s="4"/>
+      <c r="BA115" s="4"/>
+      <c r="BB115" s="4"/>
+      <c r="BC115" s="4"/>
+      <c r="BD115" s="4"/>
+      <c r="BE115" s="4"/>
+      <c r="BF115" s="4"/>
+      <c r="BG115" s="4"/>
+      <c r="BH115" s="4"/>
+      <c r="BI115" s="4"/>
+      <c r="BJ115" s="4"/>
+      <c r="BK115" s="4"/>
+      <c r="BL115" s="4"/>
+      <c r="BM115" s="4"/>
+    </row>
+    <row r="116" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B116" s="4"/>
+      <c r="C116" s="4"/>
+      <c r="D116" s="4"/>
+      <c r="E116" s="4"/>
+      <c r="F116" s="4"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="4"/>
+      <c r="J116" s="4"/>
+      <c r="K116" s="4"/>
+      <c r="L116" s="4"/>
+      <c r="M116" s="4"/>
+      <c r="N116" s="4"/>
+      <c r="O116" s="4"/>
+      <c r="P116" s="4"/>
+      <c r="Q116" s="4"/>
+      <c r="R116" s="4"/>
+      <c r="S116" s="4"/>
+      <c r="T116" s="4"/>
+      <c r="U116" s="4"/>
+      <c r="V116" s="4"/>
+      <c r="W116" s="4"/>
+      <c r="X116" s="4"/>
+      <c r="Y116" s="4"/>
+      <c r="Z116" s="4"/>
+      <c r="AA116" s="4"/>
+      <c r="AB116" s="4"/>
+      <c r="AC116" s="4"/>
+      <c r="AD116" s="4"/>
+      <c r="AE116" s="4"/>
+      <c r="AF116" s="4"/>
+      <c r="AG116" s="4"/>
+      <c r="AH116" s="4"/>
+      <c r="AI116" s="4"/>
+      <c r="AJ116" s="4"/>
+      <c r="AK116" s="4"/>
+      <c r="AL116" s="4"/>
+      <c r="AM116" s="4"/>
+      <c r="AN116" s="4"/>
+      <c r="AO116" s="4"/>
+      <c r="AP116" s="4"/>
+      <c r="AQ116" s="4"/>
+      <c r="AR116" s="4"/>
+      <c r="AS116" s="4"/>
+      <c r="AT116" s="4"/>
+      <c r="AU116" s="4"/>
+      <c r="AV116" s="4"/>
+      <c r="AW116" s="4"/>
+      <c r="AX116" s="4"/>
+      <c r="AY116" s="4"/>
+      <c r="AZ116" s="4"/>
+      <c r="BA116" s="4"/>
+      <c r="BB116" s="4"/>
+      <c r="BC116" s="4"/>
+      <c r="BD116" s="4"/>
+      <c r="BE116" s="4"/>
+      <c r="BF116" s="4"/>
+      <c r="BG116" s="4"/>
+      <c r="BH116" s="4"/>
+      <c r="BI116" s="4"/>
+      <c r="BJ116" s="4"/>
+      <c r="BK116" s="4"/>
+      <c r="BL116" s="4"/>
+      <c r="BM116" s="4"/>
+    </row>
+    <row r="117" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="B117" s="4"/>
+      <c r="C117" s="4"/>
+      <c r="D117" s="4"/>
+      <c r="E117" s="4"/>
+      <c r="F117" s="4"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="4"/>
+      <c r="I117" s="4"/>
+      <c r="J117" s="4"/>
+      <c r="K117" s="4"/>
+      <c r="L117" s="4"/>
+      <c r="M117" s="4"/>
+      <c r="N117" s="4"/>
+      <c r="O117" s="4"/>
+      <c r="P117" s="4"/>
+      <c r="Q117" s="4"/>
+      <c r="R117" s="4"/>
+      <c r="S117" s="4"/>
+      <c r="T117" s="4"/>
+      <c r="U117" s="4"/>
+      <c r="V117" s="4"/>
+      <c r="W117" s="4"/>
+      <c r="X117" s="4"/>
+      <c r="Y117" s="4"/>
+      <c r="Z117" s="4"/>
+      <c r="AA117" s="4"/>
+      <c r="AB117" s="4"/>
+      <c r="AC117" s="4"/>
+      <c r="AD117" s="4"/>
+      <c r="AE117" s="4"/>
+      <c r="AF117" s="4"/>
+      <c r="AG117" s="4"/>
+      <c r="AH117" s="4"/>
+      <c r="AI117" s="4"/>
+      <c r="AJ117" s="4"/>
+      <c r="AK117" s="4"/>
+      <c r="AL117" s="4"/>
+      <c r="AM117" s="4"/>
+      <c r="AN117" s="4"/>
+      <c r="AO117" s="4"/>
+      <c r="AP117" s="4"/>
+      <c r="AQ117" s="4"/>
+      <c r="AR117" s="4"/>
+      <c r="AS117" s="4"/>
+      <c r="AT117" s="4"/>
+      <c r="AU117" s="4"/>
+      <c r="AV117" s="4"/>
+      <c r="AW117" s="4"/>
+      <c r="AX117" s="4"/>
+      <c r="AY117" s="4"/>
+      <c r="AZ117" s="4"/>
+      <c r="BA117" s="4"/>
+      <c r="BB117" s="4"/>
+      <c r="BC117" s="4"/>
+      <c r="BD117" s="4"/>
+      <c r="BE117" s="4"/>
+      <c r="BF117" s="4"/>
+      <c r="BG117" s="4"/>
+      <c r="BH117" s="4"/>
+      <c r="BI117" s="4"/>
+      <c r="BJ117" s="4"/>
+      <c r="BK117" s="4"/>
+      <c r="BL117" s="4"/>
+      <c r="BM117" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="98">
+  <mergeCells count="111">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -34522,18 +37161,31 @@
     <mergeCell ref="B84:E84"/>
     <mergeCell ref="B85:E85"/>
     <mergeCell ref="B86:E86"/>
-    <mergeCell ref="A88:V88"/>
-    <mergeCell ref="A94:BM94"/>
-    <mergeCell ref="A95:BM95"/>
-    <mergeCell ref="A96:BM96"/>
-    <mergeCell ref="A97:BM97"/>
-    <mergeCell ref="A98:BM98"/>
-    <mergeCell ref="A99:BM99"/>
-    <mergeCell ref="A100:BM100"/>
-    <mergeCell ref="A101:BM101"/>
-    <mergeCell ref="A102:BM102"/>
-    <mergeCell ref="A103:BM103"/>
-    <mergeCell ref="A104:BM104"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="B92:E92"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="A101:V101"/>
+    <mergeCell ref="A107:BM107"/>
+    <mergeCell ref="A108:BM108"/>
+    <mergeCell ref="A109:BM109"/>
+    <mergeCell ref="A110:BM110"/>
+    <mergeCell ref="A111:BM111"/>
+    <mergeCell ref="A112:BM112"/>
+    <mergeCell ref="A113:BM113"/>
+    <mergeCell ref="A114:BM114"/>
+    <mergeCell ref="A115:BM115"/>
+    <mergeCell ref="A116:BM116"/>
+    <mergeCell ref="A117:BM117"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3112" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3392" uniqueCount="388">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 30/04/2026 05:30:25</t>
+    <t xml:space="preserve">Emitido em: 04/05/2026 07:42:43</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -769,33 +769,6 @@
     <t xml:space="preserve">35260497837181002190550010050695191228099948</t>
   </si>
   <si>
-    <t xml:space="preserve">983 - AKZO NOBEL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.962.853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.802,34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460561719009503550210019628531644291599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.962.849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260460561719009503550210019628491699396209</t>
-  </si>
-  <si>
     <t xml:space="preserve">5.069.523</t>
   </si>
   <si>
@@ -1049,6 +1022,111 @@
   </si>
   <si>
     <t xml:space="preserve">41260414570742000329550010000099901697130676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">755 - CERAMICA ATLAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">326.645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.103,53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260472050636000159550010003266451418089235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">628.101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.954,70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006281011602129727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">628.408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.372,82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006284081972692075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">628.412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">807,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006284121851006564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.576 - GRUPO METAL DESIGN LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.766,18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260486895448000560550010000006971860491054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">936,27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260486895448000560550010000006991505141518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">785 - MEBER METAIS S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">317.522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.349,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260487547907000153550050003175221341934744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">709 - MAX EBERHARDT UTILIDADES DOMESTICAS IMPORTACAO E REPRES LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">156.111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.472,29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260456991334000129550010001561111437026545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260.154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.706,42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260458329608000144550010002601541002601557</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17294,7 +17372,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM97"/>
+  <dimension ref="A1:BM104"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -25879,34 +25957,34 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>305909</v>
+        <v>305926</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>249</v>
+        <v>110</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="I48" s="9" t="s">
         <v>246</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>252</v>
+        <v>78</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>1802.34</v>
+        <v>366.64</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
@@ -25915,28 +25993,28 @@
         <v>1</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>1802.34</v>
+        <v>344.26</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0.321741</v>
+        <v>0.007989</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>221.4</v>
+        <v>1.76</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="14" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="U48" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V48" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>73</v>
@@ -25945,13 +26023,13 @@
         <v>246</v>
       </c>
       <c r="Y48" s="12" t="n">
-        <v>0</v>
+        <v>22.38</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>1802.34</v>
+        <v>344.26</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>126.16</v>
+        <v>13.77</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -26020,7 +26098,7 @@
         <v>76</v>
       </c>
       <c r="AX48" s="10" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AY48" s="14" t="s">
         <v>75</v>
@@ -26056,7 +26134,7 @@
         <v>78</v>
       </c>
       <c r="BJ48" s="9" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="BK48" s="9" t="s">
         <v>75</v>
@@ -26070,34 +26148,34 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>305912</v>
+        <v>305928</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>249</v>
+        <v>110</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>246</v>
+        <v>178</v>
       </c>
       <c r="I49" s="9" t="s">
         <v>246</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>252</v>
+        <v>78</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>180.24</v>
+        <v>366.64</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
@@ -26106,28 +26184,28 @@
         <v>1</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>180.24</v>
+        <v>344.26</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0</v>
+        <v>0.007989</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>14.1</v>
+        <v>1.76</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
@@ -26136,13 +26214,13 @@
         <v>246</v>
       </c>
       <c r="Y49" s="12" t="n">
-        <v>0</v>
+        <v>22.38</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>180.24</v>
+        <v>344.26</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>12.62</v>
+        <v>13.77</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26211,7 +26289,7 @@
         <v>76</v>
       </c>
       <c r="AX49" s="10" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="AY49" s="14" t="s">
         <v>75</v>
@@ -26247,7 +26325,7 @@
         <v>78</v>
       </c>
       <c r="BJ49" s="9" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="BK49" s="9" t="s">
         <v>75</v>
@@ -26261,7 +26339,7 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>305926</v>
+        <v>305930</v>
       </c>
       <c r="B50" s="9" t="s">
         <v>110</v>
@@ -26270,7 +26348,7 @@
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="G50" s="10" t="s">
         <v>83</v>
@@ -26438,7 +26516,7 @@
         <v>78</v>
       </c>
       <c r="BJ50" s="9" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="BK50" s="9" t="s">
         <v>75</v>
@@ -26452,7 +26530,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>305928</v>
+        <v>305941</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>110</v>
@@ -26461,7 +26539,7 @@
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="G51" s="10" t="s">
         <v>83</v>
@@ -26479,7 +26557,7 @@
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>366.64</v>
+        <v>42.44</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
@@ -26488,22 +26566,22 @@
         <v>1</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>344.26</v>
+        <v>39.85</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0.007989</v>
+        <v>0.002284</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>1.76</v>
+        <v>0.8</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>72</v>
@@ -26518,13 +26596,13 @@
         <v>246</v>
       </c>
       <c r="Y51" s="12" t="n">
-        <v>22.38</v>
+        <v>2.59</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>344.26</v>
+        <v>39.85</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>13.77</v>
+        <v>1.59</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26629,7 +26707,7 @@
         <v>78</v>
       </c>
       <c r="BJ51" s="9" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="BK51" s="9" t="s">
         <v>75</v>
@@ -26643,7 +26721,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>305930</v>
+        <v>305943</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>110</v>
@@ -26652,7 +26730,7 @@
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>83</v>
@@ -26670,7 +26748,7 @@
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>366.64</v>
+        <v>42.44</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
@@ -26679,22 +26757,22 @@
         <v>1</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>344.26</v>
+        <v>39.85</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>0.007989</v>
+        <v>0.002284</v>
       </c>
       <c r="R52" s="12" t="n">
-        <v>1.76</v>
+        <v>0.8</v>
       </c>
       <c r="S52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="14" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="U52" s="15" t="s">
         <v>72</v>
@@ -26709,13 +26787,13 @@
         <v>246</v>
       </c>
       <c r="Y52" s="12" t="n">
-        <v>22.38</v>
+        <v>2.59</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>344.26</v>
+        <v>39.85</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>13.77</v>
+        <v>1.59</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26820,7 +26898,7 @@
         <v>78</v>
       </c>
       <c r="BJ52" s="9" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="BK52" s="9" t="s">
         <v>75</v>
@@ -26834,7 +26912,7 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>305941</v>
+        <v>305944</v>
       </c>
       <c r="B53" s="9" t="s">
         <v>110</v>
@@ -26843,7 +26921,7 @@
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G53" s="10" t="s">
         <v>83</v>
@@ -26885,7 +26963,7 @@
         <v>0</v>
       </c>
       <c r="T53" s="14" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="U53" s="15" t="s">
         <v>72</v>
@@ -27011,7 +27089,7 @@
         <v>78</v>
       </c>
       <c r="BJ53" s="9" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="BK53" s="9" t="s">
         <v>75</v>
@@ -27025,7 +27103,7 @@
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>305943</v>
+        <v>305945</v>
       </c>
       <c r="B54" s="9" t="s">
         <v>110</v>
@@ -27034,7 +27112,7 @@
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G54" s="10" t="s">
         <v>83</v>
@@ -27076,7 +27154,7 @@
         <v>0</v>
       </c>
       <c r="T54" s="14" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="U54" s="15" t="s">
         <v>72</v>
@@ -27202,7 +27280,7 @@
         <v>78</v>
       </c>
       <c r="BJ54" s="9" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="BK54" s="9" t="s">
         <v>75</v>
@@ -27216,7 +27294,7 @@
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>305944</v>
+        <v>305946</v>
       </c>
       <c r="B55" s="9" t="s">
         <v>110</v>
@@ -27225,7 +27303,7 @@
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="G55" s="10" t="s">
         <v>83</v>
@@ -27243,7 +27321,7 @@
         <v>70</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>42.44</v>
+        <v>329.55</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
@@ -27252,13 +27330,13 @@
         <v>1</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>39.85</v>
+        <v>309.44</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.017132</v>
       </c>
       <c r="R55" s="12" t="n">
         <v>0.8</v>
@@ -27282,13 +27360,13 @@
         <v>246</v>
       </c>
       <c r="Y55" s="12" t="n">
-        <v>2.59</v>
+        <v>20.11</v>
       </c>
       <c r="Z55" s="12" t="n">
-        <v>39.85</v>
+        <v>309.44</v>
       </c>
       <c r="AA55" s="12" t="n">
-        <v>1.59</v>
+        <v>12.38</v>
       </c>
       <c r="AB55" s="12" t="n">
         <v>0</v>
@@ -27393,7 +27471,7 @@
         <v>78</v>
       </c>
       <c r="BJ55" s="9" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="BK55" s="9" t="s">
         <v>75</v>
@@ -27407,7 +27485,7 @@
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>305945</v>
+        <v>305950</v>
       </c>
       <c r="B56" s="9" t="s">
         <v>110</v>
@@ -27416,7 +27494,7 @@
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="G56" s="10" t="s">
         <v>83</v>
@@ -27434,7 +27512,7 @@
         <v>70</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>42.44</v>
+        <v>329.55</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>0</v>
@@ -27443,13 +27521,13 @@
         <v>1</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>39.85</v>
+        <v>309.44</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.017132</v>
       </c>
       <c r="R56" s="12" t="n">
         <v>0.8</v>
@@ -27473,13 +27551,13 @@
         <v>246</v>
       </c>
       <c r="Y56" s="12" t="n">
-        <v>2.59</v>
+        <v>20.11</v>
       </c>
       <c r="Z56" s="12" t="n">
-        <v>39.85</v>
+        <v>309.44</v>
       </c>
       <c r="AA56" s="12" t="n">
-        <v>1.59</v>
+        <v>12.38</v>
       </c>
       <c r="AB56" s="12" t="n">
         <v>0</v>
@@ -27584,7 +27662,7 @@
         <v>78</v>
       </c>
       <c r="BJ56" s="9" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="BK56" s="9" t="s">
         <v>75</v>
@@ -27598,7 +27676,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
-        <v>305946</v>
+        <v>305951</v>
       </c>
       <c r="B57" s="9" t="s">
         <v>110</v>
@@ -27607,7 +27685,7 @@
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="G57" s="10" t="s">
         <v>83</v>
@@ -27649,7 +27727,7 @@
         <v>0</v>
       </c>
       <c r="T57" s="14" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="U57" s="15" t="s">
         <v>72</v>
@@ -27775,7 +27853,7 @@
         <v>78</v>
       </c>
       <c r="BJ57" s="9" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="BK57" s="9" t="s">
         <v>75</v>
@@ -27789,7 +27867,7 @@
     </row>
     <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
-        <v>305950</v>
+        <v>305952</v>
       </c>
       <c r="B58" s="9" t="s">
         <v>110</v>
@@ -27798,7 +27876,7 @@
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
       <c r="F58" s="9" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="G58" s="10" t="s">
         <v>83</v>
@@ -27840,7 +27918,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="14" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="U58" s="15" t="s">
         <v>72</v>
@@ -27966,7 +28044,7 @@
         <v>78</v>
       </c>
       <c r="BJ58" s="9" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="BK58" s="9" t="s">
         <v>75</v>
@@ -27980,7 +28058,7 @@
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
-        <v>305951</v>
+        <v>305959</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>110</v>
@@ -27989,13 +28067,13 @@
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
       <c r="F59" s="9" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="I59" s="9" t="s">
         <v>246</v>
@@ -28007,7 +28085,7 @@
         <v>70</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>329.55</v>
+        <v>126.7</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>0</v>
@@ -28016,16 +28094,16 @@
         <v>1</v>
       </c>
       <c r="O59" s="12" t="n">
-        <v>309.44</v>
+        <v>118.97</v>
       </c>
       <c r="P59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="13" t="n">
-        <v>0.017132</v>
+        <v>0.001512</v>
       </c>
       <c r="R59" s="12" t="n">
-        <v>0.8</v>
+        <v>1.58</v>
       </c>
       <c r="S59" s="12" t="n">
         <v>0</v>
@@ -28046,13 +28124,13 @@
         <v>246</v>
       </c>
       <c r="Y59" s="12" t="n">
-        <v>20.11</v>
+        <v>7.73</v>
       </c>
       <c r="Z59" s="12" t="n">
-        <v>309.44</v>
+        <v>118.97</v>
       </c>
       <c r="AA59" s="12" t="n">
-        <v>12.38</v>
+        <v>4.76</v>
       </c>
       <c r="AB59" s="12" t="n">
         <v>0</v>
@@ -28157,7 +28235,7 @@
         <v>78</v>
       </c>
       <c r="BJ59" s="9" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="BK59" s="9" t="s">
         <v>75</v>
@@ -28171,7 +28249,7 @@
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
-        <v>305952</v>
+        <v>305961</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>110</v>
@@ -28180,13 +28258,13 @@
       <c r="D60" s="9"/>
       <c r="E60" s="9"/>
       <c r="F60" s="9" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G60" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H60" s="9" t="s">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="I60" s="9" t="s">
         <v>246</v>
@@ -28198,7 +28276,7 @@
         <v>70</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>329.55</v>
+        <v>126.7</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>0</v>
@@ -28207,16 +28285,16 @@
         <v>1</v>
       </c>
       <c r="O60" s="12" t="n">
-        <v>309.44</v>
+        <v>118.97</v>
       </c>
       <c r="P60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="13" t="n">
-        <v>0.017132</v>
+        <v>0.001512</v>
       </c>
       <c r="R60" s="12" t="n">
-        <v>0.8</v>
+        <v>1.58</v>
       </c>
       <c r="S60" s="12" t="n">
         <v>0</v>
@@ -28237,13 +28315,13 @@
         <v>246</v>
       </c>
       <c r="Y60" s="12" t="n">
-        <v>20.11</v>
+        <v>7.73</v>
       </c>
       <c r="Z60" s="12" t="n">
-        <v>309.44</v>
+        <v>118.97</v>
       </c>
       <c r="AA60" s="12" t="n">
-        <v>12.38</v>
+        <v>4.76</v>
       </c>
       <c r="AB60" s="12" t="n">
         <v>0</v>
@@ -28348,7 +28426,7 @@
         <v>78</v>
       </c>
       <c r="BJ60" s="9" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="BK60" s="9" t="s">
         <v>75</v>
@@ -28362,7 +28440,7 @@
     </row>
     <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
-        <v>305959</v>
+        <v>305963</v>
       </c>
       <c r="B61" s="9" t="s">
         <v>110</v>
@@ -28371,7 +28449,7 @@
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
       <c r="F61" s="9" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G61" s="10" t="s">
         <v>83</v>
@@ -28413,7 +28491,7 @@
         <v>0</v>
       </c>
       <c r="T61" s="14" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="U61" s="15" t="s">
         <v>72</v>
@@ -28539,7 +28617,7 @@
         <v>78</v>
       </c>
       <c r="BJ61" s="9" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="BK61" s="9" t="s">
         <v>75</v>
@@ -28553,7 +28631,7 @@
     </row>
     <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
-        <v>305961</v>
+        <v>305965</v>
       </c>
       <c r="B62" s="9" t="s">
         <v>110</v>
@@ -28562,7 +28640,7 @@
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
       <c r="F62" s="9" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>83</v>
@@ -28580,31 +28658,31 @@
         <v>70</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>126.7</v>
+        <v>290.09</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O62" s="12" t="n">
-        <v>118.97</v>
+        <v>272.38</v>
       </c>
       <c r="P62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q62" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.003202</v>
       </c>
       <c r="R62" s="12" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="S62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T62" s="14" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="U62" s="15" t="s">
         <v>72</v>
@@ -28619,13 +28697,13 @@
         <v>246</v>
       </c>
       <c r="Y62" s="12" t="n">
-        <v>7.73</v>
+        <v>17.71</v>
       </c>
       <c r="Z62" s="12" t="n">
-        <v>118.97</v>
+        <v>272.38</v>
       </c>
       <c r="AA62" s="12" t="n">
-        <v>4.76</v>
+        <v>10.89</v>
       </c>
       <c r="AB62" s="12" t="n">
         <v>0</v>
@@ -28730,7 +28808,7 @@
         <v>78</v>
       </c>
       <c r="BJ62" s="9" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="BK62" s="9" t="s">
         <v>75</v>
@@ -28744,7 +28822,7 @@
     </row>
     <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
-        <v>305963</v>
+        <v>305967</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>110</v>
@@ -28753,7 +28831,7 @@
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
       <c r="F63" s="9" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="G63" s="10" t="s">
         <v>83</v>
@@ -28771,31 +28849,31 @@
         <v>70</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>126.7</v>
+        <v>290.09</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O63" s="12" t="n">
-        <v>118.97</v>
+        <v>272.38</v>
       </c>
       <c r="P63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.003202</v>
       </c>
       <c r="R63" s="12" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="S63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T63" s="14" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="U63" s="15" t="s">
         <v>72</v>
@@ -28810,13 +28888,13 @@
         <v>246</v>
       </c>
       <c r="Y63" s="12" t="n">
-        <v>7.73</v>
+        <v>17.71</v>
       </c>
       <c r="Z63" s="12" t="n">
-        <v>118.97</v>
+        <v>272.38</v>
       </c>
       <c r="AA63" s="12" t="n">
-        <v>4.76</v>
+        <v>10.89</v>
       </c>
       <c r="AB63" s="12" t="n">
         <v>0</v>
@@ -28921,7 +28999,7 @@
         <v>78</v>
       </c>
       <c r="BJ63" s="9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="BK63" s="9" t="s">
         <v>75</v>
@@ -28935,7 +29013,7 @@
     </row>
     <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
-        <v>305965</v>
+        <v>305968</v>
       </c>
       <c r="B64" s="9" t="s">
         <v>110</v>
@@ -28944,7 +29022,7 @@
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
       <c r="F64" s="9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G64" s="10" t="s">
         <v>83</v>
@@ -28986,7 +29064,7 @@
         <v>0</v>
       </c>
       <c r="T64" s="14" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="U64" s="15" t="s">
         <v>72</v>
@@ -29112,7 +29190,7 @@
         <v>78</v>
       </c>
       <c r="BJ64" s="9" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="BK64" s="9" t="s">
         <v>75</v>
@@ -29126,7 +29204,7 @@
     </row>
     <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
-        <v>305967</v>
+        <v>305969</v>
       </c>
       <c r="B65" s="9" t="s">
         <v>110</v>
@@ -29135,7 +29213,7 @@
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
       <c r="F65" s="9" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>83</v>
@@ -29177,7 +29255,7 @@
         <v>0</v>
       </c>
       <c r="T65" s="14" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="U65" s="15" t="s">
         <v>72</v>
@@ -29303,7 +29381,7 @@
         <v>78</v>
       </c>
       <c r="BJ65" s="9" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="BK65" s="9" t="s">
         <v>75</v>
@@ -29317,7 +29395,7 @@
     </row>
     <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
-        <v>305968</v>
+        <v>305970</v>
       </c>
       <c r="B66" s="9" t="s">
         <v>110</v>
@@ -29326,7 +29404,7 @@
       <c r="D66" s="9"/>
       <c r="E66" s="9"/>
       <c r="F66" s="9" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="G66" s="10" t="s">
         <v>83</v>
@@ -29344,31 +29422,31 @@
         <v>70</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>290.09</v>
+        <v>126.7</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" s="12" t="n">
-        <v>272.38</v>
+        <v>118.97</v>
       </c>
       <c r="P66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.001512</v>
       </c>
       <c r="R66" s="12" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="S66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T66" s="14" t="s">
-        <v>290</v>
+        <v>274</v>
       </c>
       <c r="U66" s="15" t="s">
         <v>72</v>
@@ -29383,13 +29461,13 @@
         <v>246</v>
       </c>
       <c r="Y66" s="12" t="n">
-        <v>17.71</v>
+        <v>7.73</v>
       </c>
       <c r="Z66" s="12" t="n">
-        <v>272.38</v>
+        <v>118.97</v>
       </c>
       <c r="AA66" s="12" t="n">
-        <v>10.89</v>
+        <v>4.76</v>
       </c>
       <c r="AB66" s="12" t="n">
         <v>0</v>
@@ -29494,7 +29572,7 @@
         <v>78</v>
       </c>
       <c r="BJ66" s="9" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="BK66" s="9" t="s">
         <v>75</v>
@@ -29508,64 +29586,64 @@
     </row>
     <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
-        <v>305969</v>
+        <v>305977</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
       <c r="F67" s="9" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="G67" s="10" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="I67" s="9" t="s">
         <v>246</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>78</v>
+        <v>293</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>290.09</v>
+        <v>557.39</v>
       </c>
       <c r="M67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O67" s="12" t="n">
-        <v>272.38</v>
+        <v>557.39</v>
       </c>
       <c r="P67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.005136</v>
       </c>
       <c r="R67" s="12" t="n">
-        <v>1.93</v>
+        <v>1.07</v>
       </c>
       <c r="S67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T67" s="14" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="U67" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V67" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W67" s="9" t="s">
         <v>73</v>
@@ -29574,13 +29652,13 @@
         <v>246</v>
       </c>
       <c r="Y67" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z67" s="12" t="n">
-        <v>272.38</v>
+        <v>557.39</v>
       </c>
       <c r="AA67" s="12" t="n">
-        <v>10.89</v>
+        <v>39.02</v>
       </c>
       <c r="AB67" s="12" t="n">
         <v>0</v>
@@ -29649,7 +29727,7 @@
         <v>76</v>
       </c>
       <c r="AX67" s="10" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AY67" s="14" t="s">
         <v>75</v>
@@ -29685,7 +29763,7 @@
         <v>78</v>
       </c>
       <c r="BJ67" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="BK67" s="9" t="s">
         <v>75</v>
@@ -29699,64 +29777,64 @@
     </row>
     <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
-        <v>305970</v>
+        <v>305979</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>110</v>
+        <v>296</v>
       </c>
       <c r="C68" s="9"/>
       <c r="D68" s="9"/>
       <c r="E68" s="9"/>
       <c r="F68" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H68" s="9" t="s">
         <v>298</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H68" s="9" t="s">
-        <v>246</v>
       </c>
       <c r="I68" s="9" t="s">
         <v>246</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>126.7</v>
+        <v>2235.86</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O68" s="12" t="n">
-        <v>118.97</v>
+        <v>2094.8</v>
       </c>
       <c r="P68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.0136</v>
       </c>
       <c r="R68" s="12" t="n">
-        <v>1.58</v>
+        <v>2.44</v>
       </c>
       <c r="S68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T68" s="14" t="s">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="U68" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V68" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W68" s="9" t="s">
         <v>73</v>
@@ -29765,13 +29843,13 @@
         <v>246</v>
       </c>
       <c r="Y68" s="12" t="n">
-        <v>7.73</v>
+        <v>141.06</v>
       </c>
       <c r="Z68" s="12" t="n">
-        <v>118.97</v>
+        <v>2094.8</v>
       </c>
       <c r="AA68" s="12" t="n">
-        <v>4.76</v>
+        <v>146.64</v>
       </c>
       <c r="AB68" s="12" t="n">
         <v>0</v>
@@ -29840,7 +29918,7 @@
         <v>76</v>
       </c>
       <c r="AX68" s="10" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="AY68" s="14" t="s">
         <v>75</v>
@@ -29876,7 +29954,7 @@
         <v>78</v>
       </c>
       <c r="BJ68" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="BK68" s="9" t="s">
         <v>75</v>
@@ -29890,7 +29968,7 @@
     </row>
     <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
-        <v>305977</v>
+        <v>305999</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>90</v>
@@ -29899,25 +29977,25 @@
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
       <c r="F69" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="G69" s="10" t="s">
         <v>92</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>301</v>
+        <v>205</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>302</v>
+        <v>194</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>557.39</v>
+        <v>1430.23</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>0</v>
@@ -29926,16 +30004,16 @@
         <v>1</v>
       </c>
       <c r="O69" s="12" t="n">
-        <v>557.39</v>
+        <v>1342.94</v>
       </c>
       <c r="P69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="13" t="n">
-        <v>0.005136</v>
+        <v>0</v>
       </c>
       <c r="R69" s="12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="S69" s="12" t="n">
         <v>0</v>
@@ -29953,16 +30031,16 @@
         <v>73</v>
       </c>
       <c r="X69" s="9" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="Y69" s="12" t="n">
-        <v>0</v>
+        <v>87.29</v>
       </c>
       <c r="Z69" s="12" t="n">
-        <v>557.39</v>
+        <v>1342.94</v>
       </c>
       <c r="AA69" s="12" t="n">
-        <v>39.02</v>
+        <v>94.01</v>
       </c>
       <c r="AB69" s="12" t="n">
         <v>0</v>
@@ -30081,79 +30159,79 @@
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
-        <v>305979</v>
+        <v>306002</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>305</v>
+        <v>90</v>
       </c>
       <c r="C70" s="9"/>
       <c r="D70" s="9"/>
       <c r="E70" s="9"/>
       <c r="F70" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>308</v>
+        <v>206</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>2235.86</v>
+        <v>2665.63</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O70" s="12" t="n">
-        <v>2094.8</v>
+        <v>2502.94</v>
       </c>
       <c r="P70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="13" t="n">
-        <v>0.0136</v>
+        <v>0.027908</v>
       </c>
       <c r="R70" s="12" t="n">
-        <v>2.44</v>
+        <v>3.56</v>
       </c>
       <c r="S70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T70" s="14" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="U70" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V70" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="W70" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X70" s="9" t="s">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="Y70" s="12" t="n">
-        <v>141.06</v>
+        <v>162.69</v>
       </c>
       <c r="Z70" s="12" t="n">
-        <v>2094.8</v>
+        <v>2502.94</v>
       </c>
       <c r="AA70" s="12" t="n">
-        <v>146.64</v>
+        <v>175.21</v>
       </c>
       <c r="AB70" s="12" t="n">
         <v>0</v>
@@ -30258,7 +30336,7 @@
         <v>78</v>
       </c>
       <c r="BJ70" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="BK70" s="9" t="s">
         <v>75</v>
@@ -30272,7 +30350,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
-        <v>305999</v>
+        <v>306047</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>90</v>
@@ -30281,25 +30359,25 @@
       <c r="D71" s="9"/>
       <c r="E71" s="9"/>
       <c r="F71" s="9" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G71" s="10" t="s">
         <v>92</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="I71" s="9" t="s">
         <v>174</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>194</v>
+        <v>309</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>1430.23</v>
+        <v>1021.1</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>0</v>
@@ -30308,22 +30386,22 @@
         <v>1</v>
       </c>
       <c r="O71" s="12" t="n">
-        <v>1342.94</v>
+        <v>1021.1</v>
       </c>
       <c r="P71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="13" t="n">
-        <v>0</v>
+        <v>0.010608</v>
       </c>
       <c r="R71" s="12" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="S71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T71" s="14" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="U71" s="15" t="s">
         <v>72</v>
@@ -30338,13 +30416,13 @@
         <v>174</v>
       </c>
       <c r="Y71" s="12" t="n">
-        <v>87.29</v>
+        <v>0</v>
       </c>
       <c r="Z71" s="12" t="n">
-        <v>1342.94</v>
+        <v>1021.1</v>
       </c>
       <c r="AA71" s="12" t="n">
-        <v>94.01</v>
+        <v>40.84</v>
       </c>
       <c r="AB71" s="12" t="n">
         <v>0</v>
@@ -30449,7 +30527,7 @@
         <v>78</v>
       </c>
       <c r="BJ71" s="9" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="BK71" s="9" t="s">
         <v>75</v>
@@ -30463,34 +30541,34 @@
     </row>
     <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
-        <v>306002</v>
+        <v>306049</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>90</v>
+        <v>296</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
       <c r="F72" s="9" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="I72" s="9" t="s">
         <v>174</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>206</v>
+        <v>299</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>2665.63</v>
+        <v>3660.21</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>0</v>
@@ -30499,28 +30577,28 @@
         <v>1</v>
       </c>
       <c r="O72" s="12" t="n">
-        <v>2502.94</v>
+        <v>3545</v>
       </c>
       <c r="P72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="13" t="n">
-        <v>0.027908</v>
+        <v>0.0105</v>
       </c>
       <c r="R72" s="12" t="n">
-        <v>3.56</v>
+        <v>16</v>
       </c>
       <c r="S72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T72" s="14" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="U72" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V72" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="W72" s="9" t="s">
         <v>73</v>
@@ -30529,13 +30607,13 @@
         <v>174</v>
       </c>
       <c r="Y72" s="12" t="n">
-        <v>162.69</v>
+        <v>115.21</v>
       </c>
       <c r="Z72" s="12" t="n">
-        <v>2502.94</v>
+        <v>3545</v>
       </c>
       <c r="AA72" s="12" t="n">
-        <v>175.21</v>
+        <v>141.8</v>
       </c>
       <c r="AB72" s="12" t="n">
         <v>0</v>
@@ -30640,7 +30718,7 @@
         <v>78</v>
       </c>
       <c r="BJ72" s="9" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="BK72" s="9" t="s">
         <v>75</v>
@@ -30654,64 +30732,64 @@
     </row>
     <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
-        <v>306047</v>
+        <v>306050</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>90</v>
+        <v>296</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
       <c r="F73" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>174</v>
+        <v>298</v>
       </c>
       <c r="I73" s="9" t="s">
         <v>174</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>318</v>
+        <v>299</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>1021.1</v>
+        <v>4151.64</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O73" s="12" t="n">
-        <v>1021.1</v>
+        <v>3993.25</v>
       </c>
       <c r="P73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="13" t="n">
-        <v>0.010608</v>
+        <v>0.01002</v>
       </c>
       <c r="R73" s="12" t="n">
-        <v>2.67</v>
+        <v>18.95</v>
       </c>
       <c r="S73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T73" s="14" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="U73" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V73" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="W73" s="9" t="s">
         <v>73</v>
@@ -30720,13 +30798,13 @@
         <v>174</v>
       </c>
       <c r="Y73" s="12" t="n">
-        <v>0</v>
+        <v>158.39</v>
       </c>
       <c r="Z73" s="12" t="n">
-        <v>1021.1</v>
+        <v>3993.25</v>
       </c>
       <c r="AA73" s="12" t="n">
-        <v>40.84</v>
+        <v>175.78</v>
       </c>
       <c r="AB73" s="12" t="n">
         <v>0</v>
@@ -30831,7 +30909,7 @@
         <v>78</v>
       </c>
       <c r="BJ73" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="BK73" s="9" t="s">
         <v>75</v>
@@ -30845,64 +30923,64 @@
     </row>
     <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
-        <v>306049</v>
+        <v>306060</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
       <c r="F74" s="9" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>307</v>
+        <v>246</v>
       </c>
       <c r="I74" s="9" t="s">
         <v>174</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>308</v>
+        <v>166</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>3660.21</v>
+        <v>4228.44</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O74" s="12" t="n">
-        <v>3545</v>
+        <v>4152.95</v>
       </c>
       <c r="P74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="13" t="n">
-        <v>0.0105</v>
+        <v>0</v>
       </c>
       <c r="R74" s="12" t="n">
-        <v>16</v>
+        <v>208.9</v>
       </c>
       <c r="S74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T74" s="14" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="U74" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V74" s="12" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="W74" s="9" t="s">
         <v>73</v>
@@ -30911,13 +30989,13 @@
         <v>174</v>
       </c>
       <c r="Y74" s="12" t="n">
-        <v>115.21</v>
+        <v>75.49</v>
       </c>
       <c r="Z74" s="12" t="n">
-        <v>3545</v>
+        <v>4152.95</v>
       </c>
       <c r="AA74" s="12" t="n">
-        <v>141.8</v>
+        <v>284.08</v>
       </c>
       <c r="AB74" s="12" t="n">
         <v>0</v>
@@ -31022,7 +31100,7 @@
         <v>78</v>
       </c>
       <c r="BJ74" s="9" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="BK74" s="9" t="s">
         <v>75</v>
@@ -31036,34 +31114,34 @@
     </row>
     <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
-        <v>306050</v>
+        <v>306156</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
       <c r="E75" s="9"/>
       <c r="F75" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>307</v>
+        <v>146</v>
       </c>
       <c r="I75" s="9" t="s">
         <v>174</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>308</v>
+        <v>156</v>
       </c>
       <c r="K75" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>4151.64</v>
+        <v>2733.03</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>0</v>
@@ -31072,28 +31150,28 @@
         <v>3</v>
       </c>
       <c r="O75" s="12" t="n">
-        <v>3993.25</v>
+        <v>2647</v>
       </c>
       <c r="P75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="13" t="n">
-        <v>0.01002</v>
+        <v>0.000135</v>
       </c>
       <c r="R75" s="12" t="n">
-        <v>18.95</v>
+        <v>500</v>
       </c>
       <c r="S75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T75" s="14" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="U75" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V75" s="12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="W75" s="9" t="s">
         <v>73</v>
@@ -31102,13 +31180,13 @@
         <v>174</v>
       </c>
       <c r="Y75" s="12" t="n">
-        <v>158.39</v>
+        <v>86.03</v>
       </c>
       <c r="Z75" s="12" t="n">
-        <v>3993.25</v>
+        <v>2647</v>
       </c>
       <c r="AA75" s="12" t="n">
-        <v>175.78</v>
+        <v>185.29</v>
       </c>
       <c r="AB75" s="12" t="n">
         <v>0</v>
@@ -31213,7 +31291,7 @@
         <v>78</v>
       </c>
       <c r="BJ75" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="BK75" s="9" t="s">
         <v>75</v>
@@ -31227,58 +31305,58 @@
     </row>
     <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
-        <v>306060</v>
+        <v>306160</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>327</v>
+        <v>98</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
       <c r="E76" s="9"/>
       <c r="F76" s="9" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="I76" s="9" t="s">
         <v>174</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>166</v>
+        <v>327</v>
       </c>
       <c r="K76" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>4228.44</v>
+        <v>84810.62</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="O76" s="12" t="n">
-        <v>4152.95</v>
+        <v>83193.37</v>
       </c>
       <c r="P76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="13" t="n">
-        <v>0</v>
+        <v>8.867016</v>
       </c>
       <c r="R76" s="12" t="n">
-        <v>208.9</v>
+        <v>1910.81</v>
       </c>
       <c r="S76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T76" s="14" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="U76" s="15" t="s">
         <v>72</v>
@@ -31293,13 +31371,13 @@
         <v>174</v>
       </c>
       <c r="Y76" s="12" t="n">
-        <v>75.49</v>
+        <v>1617.25</v>
       </c>
       <c r="Z76" s="12" t="n">
-        <v>4152.95</v>
+        <v>83193.37</v>
       </c>
       <c r="AA76" s="12" t="n">
-        <v>284.08</v>
+        <v>5525.86</v>
       </c>
       <c r="AB76" s="12" t="n">
         <v>0</v>
@@ -31404,7 +31482,7 @@
         <v>78</v>
       </c>
       <c r="BJ76" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="BK76" s="9" t="s">
         <v>75</v>
@@ -31418,64 +31496,64 @@
     </row>
     <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
-        <v>306156</v>
+        <v>306184</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
       <c r="E77" s="9"/>
       <c r="F77" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>146</v>
+        <v>205</v>
       </c>
       <c r="I77" s="9" t="s">
         <v>174</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="K77" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>2733.03</v>
+        <v>43715.28</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0</v>
+        <v>2236.39</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O77" s="12" t="n">
-        <v>2647</v>
+        <v>44727.8</v>
       </c>
       <c r="P77" s="12" t="n">
-        <v>0</v>
+        <v>635</v>
       </c>
       <c r="Q77" s="13" t="n">
-        <v>0.000135</v>
+        <v>0.02844</v>
       </c>
       <c r="R77" s="12" t="n">
-        <v>500</v>
+        <v>67.83</v>
       </c>
       <c r="S77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T77" s="14" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="U77" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V77" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W77" s="9" t="s">
         <v>73</v>
@@ -31484,13 +31562,13 @@
         <v>174</v>
       </c>
       <c r="Y77" s="12" t="n">
-        <v>86.03</v>
+        <v>588.87</v>
       </c>
       <c r="Z77" s="12" t="n">
-        <v>2647</v>
+        <v>43126.41</v>
       </c>
       <c r="AA77" s="12" t="n">
-        <v>185.29</v>
+        <v>2687.18</v>
       </c>
       <c r="AB77" s="12" t="n">
         <v>0</v>
@@ -31556,7 +31634,7 @@
         <v>74</v>
       </c>
       <c r="AW77" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX77" s="10" t="s">
         <v>77</v>
@@ -31595,7 +31673,7 @@
         <v>78</v>
       </c>
       <c r="BJ77" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="BK77" s="9" t="s">
         <v>75</v>
@@ -31609,10 +31687,10 @@
     </row>
     <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
-        <v>306160</v>
+        <v>306299</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>98</v>
+        <v>334</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
@@ -31621,40 +31699,40 @@
         <v>335</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>301</v>
+        <v>239</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>174</v>
+        <v>336</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>336</v>
+        <v>161</v>
       </c>
       <c r="K78" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>84810.62</v>
+        <v>100103.53</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="O78" s="12" t="n">
-        <v>83193.37</v>
+        <v>99457.05</v>
       </c>
       <c r="P78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="13" t="n">
-        <v>8.867016</v>
+        <v>0.637687</v>
       </c>
       <c r="R78" s="12" t="n">
-        <v>1910.81</v>
+        <v>15558.85</v>
       </c>
       <c r="S78" s="12" t="n">
         <v>0</v>
@@ -31666,22 +31744,22 @@
         <v>72</v>
       </c>
       <c r="V78" s="12" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="W78" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X78" s="9" t="s">
-        <v>174</v>
+        <v>336</v>
       </c>
       <c r="Y78" s="12" t="n">
-        <v>1617.25</v>
+        <v>646.48</v>
       </c>
       <c r="Z78" s="12" t="n">
-        <v>83193.37</v>
+        <v>99457.05</v>
       </c>
       <c r="AA78" s="12" t="n">
-        <v>5525.86</v>
+        <v>6961.99</v>
       </c>
       <c r="AB78" s="12" t="n">
         <v>0</v>
@@ -31800,58 +31878,58 @@
     </row>
     <row r="79" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
-        <v>306184</v>
+        <v>306328</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>339</v>
+        <v>90</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
       <c r="F79" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>174</v>
+        <v>336</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>194</v>
+        <v>309</v>
       </c>
       <c r="K79" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>43715.28</v>
+        <v>3954.7</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>2236.39</v>
+        <v>0</v>
       </c>
       <c r="N79" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O79" s="12" t="n">
-        <v>44727.8</v>
+        <v>3954.7</v>
       </c>
       <c r="P79" s="12" t="n">
-        <v>635</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="13" t="n">
-        <v>0.02844</v>
+        <v>0.05525</v>
       </c>
       <c r="R79" s="12" t="n">
-        <v>67.83</v>
+        <v>14.5</v>
       </c>
       <c r="S79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T79" s="14" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="U79" s="15" t="s">
         <v>72</v>
@@ -31863,16 +31941,16 @@
         <v>73</v>
       </c>
       <c r="X79" s="9" t="s">
-        <v>174</v>
+        <v>336</v>
       </c>
       <c r="Y79" s="12" t="n">
-        <v>588.87</v>
+        <v>0</v>
       </c>
       <c r="Z79" s="12" t="n">
-        <v>43126.41</v>
+        <v>3954.7</v>
       </c>
       <c r="AA79" s="12" t="n">
-        <v>2687.18</v>
+        <v>276.83</v>
       </c>
       <c r="AB79" s="12" t="n">
         <v>0</v>
@@ -31938,7 +32016,7 @@
         <v>74</v>
       </c>
       <c r="AW79" s="14" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="AX79" s="10" t="s">
         <v>77</v>
@@ -31977,7 +32055,7 @@
         <v>78</v>
       </c>
       <c r="BJ79" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="BK79" s="9" t="s">
         <v>75</v>
@@ -31990,810 +32068,1664 @@
       </c>
     </row>
     <row r="80" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="4"/>
+      <c r="A80" s="8" t="n">
+        <v>306330</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C80" s="9"/>
+      <c r="D80" s="9"/>
+      <c r="E80" s="9"/>
+      <c r="F80" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K80" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L80" s="12" t="n">
+        <v>2372.82</v>
+      </c>
+      <c r="M80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O80" s="12" t="n">
+        <v>2372.82</v>
+      </c>
+      <c r="P80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="13" t="n">
+        <v>0.03315</v>
+      </c>
+      <c r="R80" s="12" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="S80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" s="14" t="s">
+        <v>343</v>
+      </c>
+      <c r="U80" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V80" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W80" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X80" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="12" t="n">
+        <v>2372.82</v>
+      </c>
+      <c r="AA80" s="12" t="n">
+        <v>166.1</v>
+      </c>
+      <c r="AB80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV80" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW80" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX80" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF80" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG80" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH80" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI80" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ80" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="BK80" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL80" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM80" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="81" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="17" t="s">
-        <v>343</v>
-      </c>
-      <c r="B81" s="17"/>
-      <c r="C81" s="17"/>
-      <c r="D81" s="17"/>
-      <c r="E81" s="17"/>
-      <c r="F81" s="17"/>
-      <c r="G81" s="17"/>
-      <c r="H81" s="17"/>
-      <c r="I81" s="17"/>
-      <c r="J81" s="17"/>
-      <c r="K81" s="17"/>
-      <c r="L81" s="17"/>
-      <c r="M81" s="17"/>
-      <c r="N81" s="17"/>
-      <c r="O81" s="17"/>
-      <c r="P81" s="17"/>
-      <c r="Q81" s="17"/>
-      <c r="R81" s="17"/>
-      <c r="S81" s="17"/>
-      <c r="T81" s="17"/>
-      <c r="U81" s="17"/>
-      <c r="V81" s="17"/>
+    <row r="81" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="8" t="n">
+        <v>306333</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81" s="9"/>
+      <c r="D81" s="9"/>
+      <c r="E81" s="9"/>
+      <c r="F81" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J81" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K81" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L81" s="12" t="n">
+        <v>807.1</v>
+      </c>
+      <c r="M81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O81" s="12" t="n">
+        <v>807.1</v>
+      </c>
+      <c r="P81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="13" t="n">
+        <v>0.01105</v>
+      </c>
+      <c r="R81" s="12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T81" s="14" t="s">
+        <v>346</v>
+      </c>
+      <c r="U81" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V81" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W81" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X81" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="12" t="n">
+        <v>807.1</v>
+      </c>
+      <c r="AA81" s="12" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="AB81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV81" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW81" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX81" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF81" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG81" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH81" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI81" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ81" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="BK81" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL81" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM81" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="82" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="B82" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C82" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D82" s="18" t="s">
-        <v>345</v>
-      </c>
-      <c r="E82" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F82" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G82" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H82" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I82" s="18" t="s">
-        <v>346</v>
-      </c>
-      <c r="J82" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K82" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L82" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M82" s="18" t="s">
-        <v>347</v>
-      </c>
-      <c r="N82" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O82" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P82" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q82" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R82" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S82" s="18" t="s">
+    <row r="82" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="8" t="n">
+        <v>306339</v>
+      </c>
+      <c r="B82" s="9" t="s">
         <v>348</v>
       </c>
-      <c r="T82" s="18" t="s">
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="9" t="s">
         <v>349</v>
       </c>
-      <c r="U82" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V82" s="18" t="s">
-        <v>37</v>
+      <c r="G82" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="I82" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J82" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="K82" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L82" s="12" t="n">
+        <v>3766.18</v>
+      </c>
+      <c r="M82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O82" s="12" t="n">
+        <v>3766.18</v>
+      </c>
+      <c r="P82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T82" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="U82" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V82" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="W82" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X82" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="12" t="n">
+        <v>3766.18</v>
+      </c>
+      <c r="AA82" s="12" t="n">
+        <v>150.65</v>
+      </c>
+      <c r="AB82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV82" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW82" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX82" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF82" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG82" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI82" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ82" s="9" t="s">
+        <v>352</v>
+      </c>
+      <c r="BK82" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL82" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM82" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="19" t="n">
-        <v>75</v>
-      </c>
-      <c r="B83" s="19" t="n">
-        <v>2236.39</v>
-      </c>
-      <c r="C83" s="19" t="n">
-        <v>635</v>
-      </c>
-      <c r="D83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="19" t="n">
-        <v>11478.72</v>
-      </c>
-      <c r="F83" s="19" t="n">
-        <v>339560.91</v>
-      </c>
-      <c r="G83" s="19" t="n">
-        <v>20811.37</v>
-      </c>
-      <c r="H83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K83" s="19" t="n">
-        <v>351039.63</v>
-      </c>
-      <c r="L83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" s="20" t="n">
-        <v>12.004619</v>
-      </c>
-      <c r="S83" s="19" t="n">
-        <v>341162.3</v>
-      </c>
-      <c r="T83" s="19" t="n">
-        <v>351039.63</v>
-      </c>
-      <c r="U83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V83" s="19" t="n">
-        <v>0</v>
+      <c r="A83" s="8" t="n">
+        <v>306340</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L83" s="12" t="n">
+        <v>936.27</v>
+      </c>
+      <c r="M83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O83" s="12" t="n">
+        <v>915.61</v>
+      </c>
+      <c r="P83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="U83" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V83" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="W83" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X83" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y83" s="12" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="Z83" s="12" t="n">
+        <v>915.61</v>
+      </c>
+      <c r="AA83" s="12" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="AB83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW83" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX83" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG83" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI83" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ83" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="BK83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM83" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B84" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C84" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D84" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E84" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F84" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G84" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H84" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I84" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J84" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K84" s="18" t="s">
-        <v>350</v>
-      </c>
-      <c r="L84" s="18" t="s">
-        <v>351</v>
-      </c>
-      <c r="M84" s="18" t="s">
-        <v>352</v>
+    <row r="84" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="8" t="n">
+        <v>306378</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>95349.48</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="O84" s="12" t="n">
+        <v>91519.49</v>
+      </c>
+      <c r="P84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="13" t="n">
+        <v>0.80555</v>
+      </c>
+      <c r="R84" s="12" t="n">
+        <v>424.1</v>
+      </c>
+      <c r="S84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="14" t="s">
+        <v>359</v>
+      </c>
+      <c r="U84" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="W84" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X84" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y84" s="12" t="n">
+        <v>3829.99</v>
+      </c>
+      <c r="Z84" s="12" t="n">
+        <v>91519.49</v>
+      </c>
+      <c r="AA84" s="12" t="n">
+        <v>6406.35</v>
+      </c>
+      <c r="AB84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW84" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX84" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG84" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI84" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ84" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="BK84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM84" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="19" t="n">
-        <v>3807.11</v>
-      </c>
-      <c r="B85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="19" t="n">
-        <v>41.9</v>
-      </c>
-      <c r="E85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" s="19" t="n">
-        <v>0</v>
+      <c r="A85" s="8" t="n">
+        <v>306397</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>361</v>
+      </c>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I85" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J85" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="K85" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <v>2472.29</v>
+      </c>
+      <c r="M85" s="12" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="N85" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O85" s="12" t="n">
+        <v>2381.5</v>
+      </c>
+      <c r="P85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="13" t="n">
+        <v>0.00163</v>
+      </c>
+      <c r="R85" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="S85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="14" t="s">
+        <v>363</v>
+      </c>
+      <c r="U85" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V85" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W85" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X85" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y85" s="12" t="n">
+        <v>150.89</v>
+      </c>
+      <c r="Z85" s="12" t="n">
+        <v>2321.4</v>
+      </c>
+      <c r="AA85" s="12" t="n">
+        <v>162.5</v>
+      </c>
+      <c r="AB85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW85" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX85" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG85" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI85" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ85" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="BK85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM85" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="4"/>
+      <c r="A86" s="8" t="n">
+        <v>306401</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>9706.42</v>
+      </c>
+      <c r="M86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O86" s="12" t="n">
+        <v>8844.12</v>
+      </c>
+      <c r="P86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="U86" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V86" s="12" t="n">
+        <v>44.58</v>
+      </c>
+      <c r="W86" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X86" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="Y86" s="12" t="n">
+        <v>862.3</v>
+      </c>
+      <c r="Z86" s="12" t="n">
+        <v>8844.12</v>
+      </c>
+      <c r="AA86" s="12" t="n">
+        <v>619.09</v>
+      </c>
+      <c r="AB86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW86" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX86" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG86" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI86" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ86" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="BK86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM86" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="87" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="B87" s="21"/>
-      <c r="C87" s="21"/>
-      <c r="D87" s="21"/>
-      <c r="E87" s="21"/>
-      <c r="F87" s="21"/>
-      <c r="G87" s="21"/>
-      <c r="H87" s="21"/>
-      <c r="I87" s="21"/>
-      <c r="J87" s="21"/>
-      <c r="K87" s="21"/>
-      <c r="L87" s="21"/>
-      <c r="M87" s="21"/>
-      <c r="N87" s="21"/>
-      <c r="O87" s="21"/>
-      <c r="P87" s="21"/>
-      <c r="Q87" s="21"/>
-      <c r="R87" s="21"/>
-      <c r="S87" s="21"/>
-      <c r="T87" s="21"/>
-      <c r="U87" s="21"/>
-      <c r="V87" s="21"/>
-      <c r="W87" s="21"/>
-      <c r="X87" s="21"/>
-      <c r="Y87" s="21"/>
-      <c r="Z87" s="21"/>
-      <c r="AA87" s="21"/>
-      <c r="AB87" s="21"/>
-      <c r="AC87" s="21"/>
-      <c r="AD87" s="21"/>
-      <c r="AE87" s="21"/>
-      <c r="AF87" s="21"/>
-      <c r="AG87" s="21"/>
-      <c r="AH87" s="21"/>
-      <c r="AI87" s="21"/>
-      <c r="AJ87" s="21"/>
-      <c r="AK87" s="21"/>
-      <c r="AL87" s="21"/>
-      <c r="AM87" s="21"/>
-      <c r="AN87" s="21"/>
-      <c r="AO87" s="21"/>
-      <c r="AP87" s="21"/>
-      <c r="AQ87" s="21"/>
-      <c r="AR87" s="21"/>
-      <c r="AS87" s="21"/>
-      <c r="AT87" s="21"/>
-      <c r="AU87" s="21"/>
-      <c r="AV87" s="21"/>
-      <c r="AW87" s="21"/>
-      <c r="AX87" s="21"/>
-      <c r="AY87" s="21"/>
-      <c r="AZ87" s="21"/>
-      <c r="BA87" s="21"/>
-      <c r="BB87" s="21"/>
-      <c r="BC87" s="21"/>
-      <c r="BD87" s="21"/>
-      <c r="BE87" s="21"/>
-      <c r="BF87" s="21"/>
-      <c r="BG87" s="21"/>
-      <c r="BH87" s="21"/>
-      <c r="BI87" s="21"/>
-      <c r="BJ87" s="21"/>
-      <c r="BK87" s="21"/>
-      <c r="BL87" s="21"/>
-      <c r="BM87" s="21"/>
+    <row r="87" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="4"/>
     </row>
-    <row r="88" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B88" s="4"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="4"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="4"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="4"/>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4"/>
-      <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="4"/>
-      <c r="S88" s="4"/>
-      <c r="T88" s="4"/>
-      <c r="U88" s="4"/>
-      <c r="V88" s="4"/>
-      <c r="W88" s="4"/>
-      <c r="X88" s="4"/>
-      <c r="Y88" s="4"/>
-      <c r="Z88" s="4"/>
-      <c r="AA88" s="4"/>
-      <c r="AB88" s="4"/>
-      <c r="AC88" s="4"/>
-      <c r="AD88" s="4"/>
-      <c r="AE88" s="4"/>
-      <c r="AF88" s="4"/>
-      <c r="AG88" s="4"/>
-      <c r="AH88" s="4"/>
-      <c r="AI88" s="4"/>
-      <c r="AJ88" s="4"/>
-      <c r="AK88" s="4"/>
-      <c r="AL88" s="4"/>
-      <c r="AM88" s="4"/>
-      <c r="AN88" s="4"/>
-      <c r="AO88" s="4"/>
-      <c r="AP88" s="4"/>
-      <c r="AQ88" s="4"/>
-      <c r="AR88" s="4"/>
-      <c r="AS88" s="4"/>
-      <c r="AT88" s="4"/>
-      <c r="AU88" s="4"/>
-      <c r="AV88" s="4"/>
-      <c r="AW88" s="4"/>
-      <c r="AX88" s="4"/>
-      <c r="AY88" s="4"/>
-      <c r="AZ88" s="4"/>
-      <c r="BA88" s="4"/>
-      <c r="BB88" s="4"/>
-      <c r="BC88" s="4"/>
-      <c r="BD88" s="4"/>
-      <c r="BE88" s="4"/>
-      <c r="BF88" s="4"/>
-      <c r="BG88" s="4"/>
-      <c r="BH88" s="4"/>
-      <c r="BI88" s="4"/>
-      <c r="BJ88" s="4"/>
-      <c r="BK88" s="4"/>
-      <c r="BL88" s="4"/>
-      <c r="BM88" s="4"/>
+    <row r="88" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="B88" s="17"/>
+      <c r="C88" s="17"/>
+      <c r="D88" s="17"/>
+      <c r="E88" s="17"/>
+      <c r="F88" s="17"/>
+      <c r="G88" s="17"/>
+      <c r="H88" s="17"/>
+      <c r="I88" s="17"/>
+      <c r="J88" s="17"/>
+      <c r="K88" s="17"/>
+      <c r="L88" s="17"/>
+      <c r="M88" s="17"/>
+      <c r="N88" s="17"/>
+      <c r="O88" s="17"/>
+      <c r="P88" s="17"/>
+      <c r="Q88" s="17"/>
+      <c r="R88" s="17"/>
+      <c r="S88" s="17"/>
+      <c r="T88" s="17"/>
+      <c r="U88" s="17"/>
+      <c r="V88" s="17"/>
     </row>
-    <row r="89" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="B89" s="4"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="4"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="4"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="4"/>
-      <c r="M89" s="4"/>
-      <c r="N89" s="4"/>
-      <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
-      <c r="Q89" s="4"/>
-      <c r="R89" s="4"/>
-      <c r="S89" s="4"/>
-      <c r="T89" s="4"/>
-      <c r="U89" s="4"/>
-      <c r="V89" s="4"/>
-      <c r="W89" s="4"/>
-      <c r="X89" s="4"/>
-      <c r="Y89" s="4"/>
-      <c r="Z89" s="4"/>
-      <c r="AA89" s="4"/>
-      <c r="AB89" s="4"/>
-      <c r="AC89" s="4"/>
-      <c r="AD89" s="4"/>
-      <c r="AE89" s="4"/>
-      <c r="AF89" s="4"/>
-      <c r="AG89" s="4"/>
-      <c r="AH89" s="4"/>
-      <c r="AI89" s="4"/>
-      <c r="AJ89" s="4"/>
-      <c r="AK89" s="4"/>
-      <c r="AL89" s="4"/>
-      <c r="AM89" s="4"/>
-      <c r="AN89" s="4"/>
-      <c r="AO89" s="4"/>
-      <c r="AP89" s="4"/>
-      <c r="AQ89" s="4"/>
-      <c r="AR89" s="4"/>
-      <c r="AS89" s="4"/>
-      <c r="AT89" s="4"/>
-      <c r="AU89" s="4"/>
-      <c r="AV89" s="4"/>
-      <c r="AW89" s="4"/>
-      <c r="AX89" s="4"/>
-      <c r="AY89" s="4"/>
-      <c r="AZ89" s="4"/>
-      <c r="BA89" s="4"/>
-      <c r="BB89" s="4"/>
-      <c r="BC89" s="4"/>
-      <c r="BD89" s="4"/>
-      <c r="BE89" s="4"/>
-      <c r="BF89" s="4"/>
-      <c r="BG89" s="4"/>
-      <c r="BH89" s="4"/>
-      <c r="BI89" s="4"/>
-      <c r="BJ89" s="4"/>
-      <c r="BK89" s="4"/>
-      <c r="BL89" s="4"/>
-      <c r="BM89" s="4"/>
+    <row r="89" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F89" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G89" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H89" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I89" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="J89" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K89" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L89" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M89" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="N89" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O89" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P89" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q89" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R89" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S89" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="T89" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="U89" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V89" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="B90" s="4"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="4"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="4"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4"/>
-      <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
-      <c r="Q90" s="4"/>
-      <c r="R90" s="4"/>
-      <c r="S90" s="4"/>
-      <c r="T90" s="4"/>
-      <c r="U90" s="4"/>
-      <c r="V90" s="4"/>
-      <c r="W90" s="4"/>
-      <c r="X90" s="4"/>
-      <c r="Y90" s="4"/>
-      <c r="Z90" s="4"/>
-      <c r="AA90" s="4"/>
-      <c r="AB90" s="4"/>
-      <c r="AC90" s="4"/>
-      <c r="AD90" s="4"/>
-      <c r="AE90" s="4"/>
-      <c r="AF90" s="4"/>
-      <c r="AG90" s="4"/>
-      <c r="AH90" s="4"/>
-      <c r="AI90" s="4"/>
-      <c r="AJ90" s="4"/>
-      <c r="AK90" s="4"/>
-      <c r="AL90" s="4"/>
-      <c r="AM90" s="4"/>
-      <c r="AN90" s="4"/>
-      <c r="AO90" s="4"/>
-      <c r="AP90" s="4"/>
-      <c r="AQ90" s="4"/>
-      <c r="AR90" s="4"/>
-      <c r="AS90" s="4"/>
-      <c r="AT90" s="4"/>
-      <c r="AU90" s="4"/>
-      <c r="AV90" s="4"/>
-      <c r="AW90" s="4"/>
-      <c r="AX90" s="4"/>
-      <c r="AY90" s="4"/>
-      <c r="AZ90" s="4"/>
-      <c r="BA90" s="4"/>
-      <c r="BB90" s="4"/>
-      <c r="BC90" s="4"/>
-      <c r="BD90" s="4"/>
-      <c r="BE90" s="4"/>
-      <c r="BF90" s="4"/>
-      <c r="BG90" s="4"/>
-      <c r="BH90" s="4"/>
-      <c r="BI90" s="4"/>
-      <c r="BJ90" s="4"/>
-      <c r="BK90" s="4"/>
-      <c r="BL90" s="4"/>
-      <c r="BM90" s="4"/>
+      <c r="A90" s="19" t="n">
+        <v>82</v>
+      </c>
+      <c r="B90" s="19" t="n">
+        <v>2296.49</v>
+      </c>
+      <c r="C90" s="19" t="n">
+        <v>635</v>
+      </c>
+      <c r="D90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="19" t="n">
+        <v>16989.04</v>
+      </c>
+      <c r="F90" s="19" t="n">
+        <v>551536.8</v>
+      </c>
+      <c r="G90" s="19" t="n">
+        <v>35509.22</v>
+      </c>
+      <c r="H90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="19" t="n">
+        <v>568525.84</v>
+      </c>
+      <c r="L90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="20" t="n">
+        <v>13.227195</v>
+      </c>
+      <c r="S90" s="19" t="n">
+        <v>553198.29</v>
+      </c>
+      <c r="T90" s="19" t="n">
+        <v>568525.84</v>
+      </c>
+      <c r="U90" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V90" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="91" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
-      <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
-      <c r="V91" s="4"/>
-      <c r="W91" s="4"/>
-      <c r="X91" s="4"/>
-      <c r="Y91" s="4"/>
-      <c r="Z91" s="4"/>
-      <c r="AA91" s="4"/>
-      <c r="AB91" s="4"/>
-      <c r="AC91" s="4"/>
-      <c r="AD91" s="4"/>
-      <c r="AE91" s="4"/>
-      <c r="AF91" s="4"/>
-      <c r="AG91" s="4"/>
-      <c r="AH91" s="4"/>
-      <c r="AI91" s="4"/>
-      <c r="AJ91" s="4"/>
-      <c r="AK91" s="4"/>
-      <c r="AL91" s="4"/>
-      <c r="AM91" s="4"/>
-      <c r="AN91" s="4"/>
-      <c r="AO91" s="4"/>
-      <c r="AP91" s="4"/>
-      <c r="AQ91" s="4"/>
-      <c r="AR91" s="4"/>
-      <c r="AS91" s="4"/>
-      <c r="AT91" s="4"/>
-      <c r="AU91" s="4"/>
-      <c r="AV91" s="4"/>
-      <c r="AW91" s="4"/>
-      <c r="AX91" s="4"/>
-      <c r="AY91" s="4"/>
-      <c r="AZ91" s="4"/>
-      <c r="BA91" s="4"/>
-      <c r="BB91" s="4"/>
-      <c r="BC91" s="4"/>
-      <c r="BD91" s="4"/>
-      <c r="BE91" s="4"/>
-      <c r="BF91" s="4"/>
-      <c r="BG91" s="4"/>
-      <c r="BH91" s="4"/>
-      <c r="BI91" s="4"/>
-      <c r="BJ91" s="4"/>
-      <c r="BK91" s="4"/>
-      <c r="BL91" s="4"/>
-      <c r="BM91" s="4"/>
+    <row r="91" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C91" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D91" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E91" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F91" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G91" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H91" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I91" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J91" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K91" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="L91" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="M91" s="18" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
-      <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
-      <c r="V92" s="4"/>
-      <c r="W92" s="4"/>
-      <c r="X92" s="4"/>
-      <c r="Y92" s="4"/>
-      <c r="Z92" s="4"/>
-      <c r="AA92" s="4"/>
-      <c r="AB92" s="4"/>
-      <c r="AC92" s="4"/>
-      <c r="AD92" s="4"/>
-      <c r="AE92" s="4"/>
-      <c r="AF92" s="4"/>
-      <c r="AG92" s="4"/>
-      <c r="AH92" s="4"/>
-      <c r="AI92" s="4"/>
-      <c r="AJ92" s="4"/>
-      <c r="AK92" s="4"/>
-      <c r="AL92" s="4"/>
-      <c r="AM92" s="4"/>
-      <c r="AN92" s="4"/>
-      <c r="AO92" s="4"/>
-      <c r="AP92" s="4"/>
-      <c r="AQ92" s="4"/>
-      <c r="AR92" s="4"/>
-      <c r="AS92" s="4"/>
-      <c r="AT92" s="4"/>
-      <c r="AU92" s="4"/>
-      <c r="AV92" s="4"/>
-      <c r="AW92" s="4"/>
-      <c r="AX92" s="4"/>
-      <c r="AY92" s="4"/>
-      <c r="AZ92" s="4"/>
-      <c r="BA92" s="4"/>
-      <c r="BB92" s="4"/>
-      <c r="BC92" s="4"/>
-      <c r="BD92" s="4"/>
-      <c r="BE92" s="4"/>
-      <c r="BF92" s="4"/>
-      <c r="BG92" s="4"/>
-      <c r="BH92" s="4"/>
-      <c r="BI92" s="4"/>
-      <c r="BJ92" s="4"/>
-      <c r="BK92" s="4"/>
-      <c r="BL92" s="4"/>
-      <c r="BM92" s="4"/>
+      <c r="A92" s="19" t="n">
+        <v>19595.66</v>
+      </c>
+      <c r="B92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="19" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="E92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
-      <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="4"/>
-      <c r="X93" s="4"/>
-      <c r="Y93" s="4"/>
-      <c r="Z93" s="4"/>
-      <c r="AA93" s="4"/>
-      <c r="AB93" s="4"/>
-      <c r="AC93" s="4"/>
-      <c r="AD93" s="4"/>
-      <c r="AE93" s="4"/>
-      <c r="AF93" s="4"/>
-      <c r="AG93" s="4"/>
-      <c r="AH93" s="4"/>
-      <c r="AI93" s="4"/>
-      <c r="AJ93" s="4"/>
-      <c r="AK93" s="4"/>
-      <c r="AL93" s="4"/>
-      <c r="AM93" s="4"/>
-      <c r="AN93" s="4"/>
-      <c r="AO93" s="4"/>
-      <c r="AP93" s="4"/>
-      <c r="AQ93" s="4"/>
-      <c r="AR93" s="4"/>
-      <c r="AS93" s="4"/>
-      <c r="AT93" s="4"/>
-      <c r="AU93" s="4"/>
-      <c r="AV93" s="4"/>
-      <c r="AW93" s="4"/>
-      <c r="AX93" s="4"/>
-      <c r="AY93" s="4"/>
-      <c r="AZ93" s="4"/>
-      <c r="BA93" s="4"/>
-      <c r="BB93" s="4"/>
-      <c r="BC93" s="4"/>
-      <c r="BD93" s="4"/>
-      <c r="BE93" s="4"/>
-      <c r="BF93" s="4"/>
-      <c r="BG93" s="4"/>
-      <c r="BH93" s="4"/>
-      <c r="BI93" s="4"/>
-      <c r="BJ93" s="4"/>
-      <c r="BK93" s="4"/>
-      <c r="BL93" s="4"/>
-      <c r="BM93" s="4"/>
+      <c r="A93" s="4"/>
     </row>
-    <row r="94" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
-      <c r="S94" s="4"/>
-      <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
-      <c r="V94" s="4"/>
-      <c r="W94" s="4"/>
-      <c r="X94" s="4"/>
-      <c r="Y94" s="4"/>
-      <c r="Z94" s="4"/>
-      <c r="AA94" s="4"/>
-      <c r="AB94" s="4"/>
-      <c r="AC94" s="4"/>
-      <c r="AD94" s="4"/>
-      <c r="AE94" s="4"/>
-      <c r="AF94" s="4"/>
-      <c r="AG94" s="4"/>
-      <c r="AH94" s="4"/>
-      <c r="AI94" s="4"/>
-      <c r="AJ94" s="4"/>
-      <c r="AK94" s="4"/>
-      <c r="AL94" s="4"/>
-      <c r="AM94" s="4"/>
-      <c r="AN94" s="4"/>
-      <c r="AO94" s="4"/>
-      <c r="AP94" s="4"/>
-      <c r="AQ94" s="4"/>
-      <c r="AR94" s="4"/>
-      <c r="AS94" s="4"/>
-      <c r="AT94" s="4"/>
-      <c r="AU94" s="4"/>
-      <c r="AV94" s="4"/>
-      <c r="AW94" s="4"/>
-      <c r="AX94" s="4"/>
-      <c r="AY94" s="4"/>
-      <c r="AZ94" s="4"/>
-      <c r="BA94" s="4"/>
-      <c r="BB94" s="4"/>
-      <c r="BC94" s="4"/>
-      <c r="BD94" s="4"/>
-      <c r="BE94" s="4"/>
-      <c r="BF94" s="4"/>
-      <c r="BG94" s="4"/>
-      <c r="BH94" s="4"/>
-      <c r="BI94" s="4"/>
-      <c r="BJ94" s="4"/>
-      <c r="BK94" s="4"/>
-      <c r="BL94" s="4"/>
-      <c r="BM94" s="4"/>
+    <row r="94" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="B94" s="21"/>
+      <c r="C94" s="21"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="21"/>
+      <c r="F94" s="21"/>
+      <c r="G94" s="21"/>
+      <c r="H94" s="21"/>
+      <c r="I94" s="21"/>
+      <c r="J94" s="21"/>
+      <c r="K94" s="21"/>
+      <c r="L94" s="21"/>
+      <c r="M94" s="21"/>
+      <c r="N94" s="21"/>
+      <c r="O94" s="21"/>
+      <c r="P94" s="21"/>
+      <c r="Q94" s="21"/>
+      <c r="R94" s="21"/>
+      <c r="S94" s="21"/>
+      <c r="T94" s="21"/>
+      <c r="U94" s="21"/>
+      <c r="V94" s="21"/>
+      <c r="W94" s="21"/>
+      <c r="X94" s="21"/>
+      <c r="Y94" s="21"/>
+      <c r="Z94" s="21"/>
+      <c r="AA94" s="21"/>
+      <c r="AB94" s="21"/>
+      <c r="AC94" s="21"/>
+      <c r="AD94" s="21"/>
+      <c r="AE94" s="21"/>
+      <c r="AF94" s="21"/>
+      <c r="AG94" s="21"/>
+      <c r="AH94" s="21"/>
+      <c r="AI94" s="21"/>
+      <c r="AJ94" s="21"/>
+      <c r="AK94" s="21"/>
+      <c r="AL94" s="21"/>
+      <c r="AM94" s="21"/>
+      <c r="AN94" s="21"/>
+      <c r="AO94" s="21"/>
+      <c r="AP94" s="21"/>
+      <c r="AQ94" s="21"/>
+      <c r="AR94" s="21"/>
+      <c r="AS94" s="21"/>
+      <c r="AT94" s="21"/>
+      <c r="AU94" s="21"/>
+      <c r="AV94" s="21"/>
+      <c r="AW94" s="21"/>
+      <c r="AX94" s="21"/>
+      <c r="AY94" s="21"/>
+      <c r="AZ94" s="21"/>
+      <c r="BA94" s="21"/>
+      <c r="BB94" s="21"/>
+      <c r="BC94" s="21"/>
+      <c r="BD94" s="21"/>
+      <c r="BE94" s="21"/>
+      <c r="BF94" s="21"/>
+      <c r="BG94" s="21"/>
+      <c r="BH94" s="21"/>
+      <c r="BI94" s="21"/>
+      <c r="BJ94" s="21"/>
+      <c r="BK94" s="21"/>
+      <c r="BL94" s="21"/>
+      <c r="BM94" s="21"/>
     </row>
     <row r="95" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>359</v>
+        <v>75</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -32862,7 +33794,7 @@
     </row>
     <row r="96" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -32931,7 +33863,7 @@
     </row>
     <row r="97" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>361</v>
+        <v>381</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -32998,8 +33930,491 @@
       <c r="BL97" s="4"/>
       <c r="BM97" s="4"/>
     </row>
+    <row r="98" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A98" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B98" s="4"/>
+      <c r="C98" s="4"/>
+      <c r="D98" s="4"/>
+      <c r="E98" s="4"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="4"/>
+      <c r="H98" s="4"/>
+      <c r="I98" s="4"/>
+      <c r="J98" s="4"/>
+      <c r="K98" s="4"/>
+      <c r="L98" s="4"/>
+      <c r="M98" s="4"/>
+      <c r="N98" s="4"/>
+      <c r="O98" s="4"/>
+      <c r="P98" s="4"/>
+      <c r="Q98" s="4"/>
+      <c r="R98" s="4"/>
+      <c r="S98" s="4"/>
+      <c r="T98" s="4"/>
+      <c r="U98" s="4"/>
+      <c r="V98" s="4"/>
+      <c r="W98" s="4"/>
+      <c r="X98" s="4"/>
+      <c r="Y98" s="4"/>
+      <c r="Z98" s="4"/>
+      <c r="AA98" s="4"/>
+      <c r="AB98" s="4"/>
+      <c r="AC98" s="4"/>
+      <c r="AD98" s="4"/>
+      <c r="AE98" s="4"/>
+      <c r="AF98" s="4"/>
+      <c r="AG98" s="4"/>
+      <c r="AH98" s="4"/>
+      <c r="AI98" s="4"/>
+      <c r="AJ98" s="4"/>
+      <c r="AK98" s="4"/>
+      <c r="AL98" s="4"/>
+      <c r="AM98" s="4"/>
+      <c r="AN98" s="4"/>
+      <c r="AO98" s="4"/>
+      <c r="AP98" s="4"/>
+      <c r="AQ98" s="4"/>
+      <c r="AR98" s="4"/>
+      <c r="AS98" s="4"/>
+      <c r="AT98" s="4"/>
+      <c r="AU98" s="4"/>
+      <c r="AV98" s="4"/>
+      <c r="AW98" s="4"/>
+      <c r="AX98" s="4"/>
+      <c r="AY98" s="4"/>
+      <c r="AZ98" s="4"/>
+      <c r="BA98" s="4"/>
+      <c r="BB98" s="4"/>
+      <c r="BC98" s="4"/>
+      <c r="BD98" s="4"/>
+      <c r="BE98" s="4"/>
+      <c r="BF98" s="4"/>
+      <c r="BG98" s="4"/>
+      <c r="BH98" s="4"/>
+      <c r="BI98" s="4"/>
+      <c r="BJ98" s="4"/>
+      <c r="BK98" s="4"/>
+      <c r="BL98" s="4"/>
+      <c r="BM98" s="4"/>
+    </row>
+    <row r="99" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="4"/>
+      <c r="C99" s="4"/>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="4"/>
+      <c r="G99" s="4"/>
+      <c r="H99" s="4"/>
+      <c r="I99" s="4"/>
+      <c r="J99" s="4"/>
+      <c r="K99" s="4"/>
+      <c r="L99" s="4"/>
+      <c r="M99" s="4"/>
+      <c r="N99" s="4"/>
+      <c r="O99" s="4"/>
+      <c r="P99" s="4"/>
+      <c r="Q99" s="4"/>
+      <c r="R99" s="4"/>
+      <c r="S99" s="4"/>
+      <c r="T99" s="4"/>
+      <c r="U99" s="4"/>
+      <c r="V99" s="4"/>
+      <c r="W99" s="4"/>
+      <c r="X99" s="4"/>
+      <c r="Y99" s="4"/>
+      <c r="Z99" s="4"/>
+      <c r="AA99" s="4"/>
+      <c r="AB99" s="4"/>
+      <c r="AC99" s="4"/>
+      <c r="AD99" s="4"/>
+      <c r="AE99" s="4"/>
+      <c r="AF99" s="4"/>
+      <c r="AG99" s="4"/>
+      <c r="AH99" s="4"/>
+      <c r="AI99" s="4"/>
+      <c r="AJ99" s="4"/>
+      <c r="AK99" s="4"/>
+      <c r="AL99" s="4"/>
+      <c r="AM99" s="4"/>
+      <c r="AN99" s="4"/>
+      <c r="AO99" s="4"/>
+      <c r="AP99" s="4"/>
+      <c r="AQ99" s="4"/>
+      <c r="AR99" s="4"/>
+      <c r="AS99" s="4"/>
+      <c r="AT99" s="4"/>
+      <c r="AU99" s="4"/>
+      <c r="AV99" s="4"/>
+      <c r="AW99" s="4"/>
+      <c r="AX99" s="4"/>
+      <c r="AY99" s="4"/>
+      <c r="AZ99" s="4"/>
+      <c r="BA99" s="4"/>
+      <c r="BB99" s="4"/>
+      <c r="BC99" s="4"/>
+      <c r="BD99" s="4"/>
+      <c r="BE99" s="4"/>
+      <c r="BF99" s="4"/>
+      <c r="BG99" s="4"/>
+      <c r="BH99" s="4"/>
+      <c r="BI99" s="4"/>
+      <c r="BJ99" s="4"/>
+      <c r="BK99" s="4"/>
+      <c r="BL99" s="4"/>
+      <c r="BM99" s="4"/>
+    </row>
+    <row r="100" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B100" s="4"/>
+      <c r="C100" s="4"/>
+      <c r="D100" s="4"/>
+      <c r="E100" s="4"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="4"/>
+      <c r="H100" s="4"/>
+      <c r="I100" s="4"/>
+      <c r="J100" s="4"/>
+      <c r="K100" s="4"/>
+      <c r="L100" s="4"/>
+      <c r="M100" s="4"/>
+      <c r="N100" s="4"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="4"/>
+      <c r="R100" s="4"/>
+      <c r="S100" s="4"/>
+      <c r="T100" s="4"/>
+      <c r="U100" s="4"/>
+      <c r="V100" s="4"/>
+      <c r="W100" s="4"/>
+      <c r="X100" s="4"/>
+      <c r="Y100" s="4"/>
+      <c r="Z100" s="4"/>
+      <c r="AA100" s="4"/>
+      <c r="AB100" s="4"/>
+      <c r="AC100" s="4"/>
+      <c r="AD100" s="4"/>
+      <c r="AE100" s="4"/>
+      <c r="AF100" s="4"/>
+      <c r="AG100" s="4"/>
+      <c r="AH100" s="4"/>
+      <c r="AI100" s="4"/>
+      <c r="AJ100" s="4"/>
+      <c r="AK100" s="4"/>
+      <c r="AL100" s="4"/>
+      <c r="AM100" s="4"/>
+      <c r="AN100" s="4"/>
+      <c r="AO100" s="4"/>
+      <c r="AP100" s="4"/>
+      <c r="AQ100" s="4"/>
+      <c r="AR100" s="4"/>
+      <c r="AS100" s="4"/>
+      <c r="AT100" s="4"/>
+      <c r="AU100" s="4"/>
+      <c r="AV100" s="4"/>
+      <c r="AW100" s="4"/>
+      <c r="AX100" s="4"/>
+      <c r="AY100" s="4"/>
+      <c r="AZ100" s="4"/>
+      <c r="BA100" s="4"/>
+      <c r="BB100" s="4"/>
+      <c r="BC100" s="4"/>
+      <c r="BD100" s="4"/>
+      <c r="BE100" s="4"/>
+      <c r="BF100" s="4"/>
+      <c r="BG100" s="4"/>
+      <c r="BH100" s="4"/>
+      <c r="BI100" s="4"/>
+      <c r="BJ100" s="4"/>
+      <c r="BK100" s="4"/>
+      <c r="BL100" s="4"/>
+      <c r="BM100" s="4"/>
+    </row>
+    <row r="101" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4"/>
+      <c r="P101" s="4"/>
+      <c r="Q101" s="4"/>
+      <c r="R101" s="4"/>
+      <c r="S101" s="4"/>
+      <c r="T101" s="4"/>
+      <c r="U101" s="4"/>
+      <c r="V101" s="4"/>
+      <c r="W101" s="4"/>
+      <c r="X101" s="4"/>
+      <c r="Y101" s="4"/>
+      <c r="Z101" s="4"/>
+      <c r="AA101" s="4"/>
+      <c r="AB101" s="4"/>
+      <c r="AC101" s="4"/>
+      <c r="AD101" s="4"/>
+      <c r="AE101" s="4"/>
+      <c r="AF101" s="4"/>
+      <c r="AG101" s="4"/>
+      <c r="AH101" s="4"/>
+      <c r="AI101" s="4"/>
+      <c r="AJ101" s="4"/>
+      <c r="AK101" s="4"/>
+      <c r="AL101" s="4"/>
+      <c r="AM101" s="4"/>
+      <c r="AN101" s="4"/>
+      <c r="AO101" s="4"/>
+      <c r="AP101" s="4"/>
+      <c r="AQ101" s="4"/>
+      <c r="AR101" s="4"/>
+      <c r="AS101" s="4"/>
+      <c r="AT101" s="4"/>
+      <c r="AU101" s="4"/>
+      <c r="AV101" s="4"/>
+      <c r="AW101" s="4"/>
+      <c r="AX101" s="4"/>
+      <c r="AY101" s="4"/>
+      <c r="AZ101" s="4"/>
+      <c r="BA101" s="4"/>
+      <c r="BB101" s="4"/>
+      <c r="BC101" s="4"/>
+      <c r="BD101" s="4"/>
+      <c r="BE101" s="4"/>
+      <c r="BF101" s="4"/>
+      <c r="BG101" s="4"/>
+      <c r="BH101" s="4"/>
+      <c r="BI101" s="4"/>
+      <c r="BJ101" s="4"/>
+      <c r="BK101" s="4"/>
+      <c r="BL101" s="4"/>
+      <c r="BM101" s="4"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4"/>
+      <c r="S102" s="4"/>
+      <c r="T102" s="4"/>
+      <c r="U102" s="4"/>
+      <c r="V102" s="4"/>
+      <c r="W102" s="4"/>
+      <c r="X102" s="4"/>
+      <c r="Y102" s="4"/>
+      <c r="Z102" s="4"/>
+      <c r="AA102" s="4"/>
+      <c r="AB102" s="4"/>
+      <c r="AC102" s="4"/>
+      <c r="AD102" s="4"/>
+      <c r="AE102" s="4"/>
+      <c r="AF102" s="4"/>
+      <c r="AG102" s="4"/>
+      <c r="AH102" s="4"/>
+      <c r="AI102" s="4"/>
+      <c r="AJ102" s="4"/>
+      <c r="AK102" s="4"/>
+      <c r="AL102" s="4"/>
+      <c r="AM102" s="4"/>
+      <c r="AN102" s="4"/>
+      <c r="AO102" s="4"/>
+      <c r="AP102" s="4"/>
+      <c r="AQ102" s="4"/>
+      <c r="AR102" s="4"/>
+      <c r="AS102" s="4"/>
+      <c r="AT102" s="4"/>
+      <c r="AU102" s="4"/>
+      <c r="AV102" s="4"/>
+      <c r="AW102" s="4"/>
+      <c r="AX102" s="4"/>
+      <c r="AY102" s="4"/>
+      <c r="AZ102" s="4"/>
+      <c r="BA102" s="4"/>
+      <c r="BB102" s="4"/>
+      <c r="BC102" s="4"/>
+      <c r="BD102" s="4"/>
+      <c r="BE102" s="4"/>
+      <c r="BF102" s="4"/>
+      <c r="BG102" s="4"/>
+      <c r="BH102" s="4"/>
+      <c r="BI102" s="4"/>
+      <c r="BJ102" s="4"/>
+      <c r="BK102" s="4"/>
+      <c r="BL102" s="4"/>
+      <c r="BM102" s="4"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="4"/>
+      <c r="S103" s="4"/>
+      <c r="T103" s="4"/>
+      <c r="U103" s="4"/>
+      <c r="V103" s="4"/>
+      <c r="W103" s="4"/>
+      <c r="X103" s="4"/>
+      <c r="Y103" s="4"/>
+      <c r="Z103" s="4"/>
+      <c r="AA103" s="4"/>
+      <c r="AB103" s="4"/>
+      <c r="AC103" s="4"/>
+      <c r="AD103" s="4"/>
+      <c r="AE103" s="4"/>
+      <c r="AF103" s="4"/>
+      <c r="AG103" s="4"/>
+      <c r="AH103" s="4"/>
+      <c r="AI103" s="4"/>
+      <c r="AJ103" s="4"/>
+      <c r="AK103" s="4"/>
+      <c r="AL103" s="4"/>
+      <c r="AM103" s="4"/>
+      <c r="AN103" s="4"/>
+      <c r="AO103" s="4"/>
+      <c r="AP103" s="4"/>
+      <c r="AQ103" s="4"/>
+      <c r="AR103" s="4"/>
+      <c r="AS103" s="4"/>
+      <c r="AT103" s="4"/>
+      <c r="AU103" s="4"/>
+      <c r="AV103" s="4"/>
+      <c r="AW103" s="4"/>
+      <c r="AX103" s="4"/>
+      <c r="AY103" s="4"/>
+      <c r="AZ103" s="4"/>
+      <c r="BA103" s="4"/>
+      <c r="BB103" s="4"/>
+      <c r="BC103" s="4"/>
+      <c r="BD103" s="4"/>
+      <c r="BE103" s="4"/>
+      <c r="BF103" s="4"/>
+      <c r="BG103" s="4"/>
+      <c r="BH103" s="4"/>
+      <c r="BI103" s="4"/>
+      <c r="BJ103" s="4"/>
+      <c r="BK103" s="4"/>
+      <c r="BL103" s="4"/>
+      <c r="BM103" s="4"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="4"/>
+      <c r="S104" s="4"/>
+      <c r="T104" s="4"/>
+      <c r="U104" s="4"/>
+      <c r="V104" s="4"/>
+      <c r="W104" s="4"/>
+      <c r="X104" s="4"/>
+      <c r="Y104" s="4"/>
+      <c r="Z104" s="4"/>
+      <c r="AA104" s="4"/>
+      <c r="AB104" s="4"/>
+      <c r="AC104" s="4"/>
+      <c r="AD104" s="4"/>
+      <c r="AE104" s="4"/>
+      <c r="AF104" s="4"/>
+      <c r="AG104" s="4"/>
+      <c r="AH104" s="4"/>
+      <c r="AI104" s="4"/>
+      <c r="AJ104" s="4"/>
+      <c r="AK104" s="4"/>
+      <c r="AL104" s="4"/>
+      <c r="AM104" s="4"/>
+      <c r="AN104" s="4"/>
+      <c r="AO104" s="4"/>
+      <c r="AP104" s="4"/>
+      <c r="AQ104" s="4"/>
+      <c r="AR104" s="4"/>
+      <c r="AS104" s="4"/>
+      <c r="AT104" s="4"/>
+      <c r="AU104" s="4"/>
+      <c r="AV104" s="4"/>
+      <c r="AW104" s="4"/>
+      <c r="AX104" s="4"/>
+      <c r="AY104" s="4"/>
+      <c r="AZ104" s="4"/>
+      <c r="BA104" s="4"/>
+      <c r="BB104" s="4"/>
+      <c r="BC104" s="4"/>
+      <c r="BD104" s="4"/>
+      <c r="BE104" s="4"/>
+      <c r="BF104" s="4"/>
+      <c r="BG104" s="4"/>
+      <c r="BH104" s="4"/>
+      <c r="BI104" s="4"/>
+      <c r="BJ104" s="4"/>
+      <c r="BK104" s="4"/>
+      <c r="BL104" s="4"/>
+      <c r="BM104" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="91">
+  <mergeCells count="98">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -33079,18 +34494,25 @@
     <mergeCell ref="B77:E77"/>
     <mergeCell ref="B78:E78"/>
     <mergeCell ref="B79:E79"/>
-    <mergeCell ref="A81:V81"/>
-    <mergeCell ref="A87:BM87"/>
-    <mergeCell ref="A88:BM88"/>
-    <mergeCell ref="A89:BM89"/>
-    <mergeCell ref="A90:BM90"/>
-    <mergeCell ref="A91:BM91"/>
-    <mergeCell ref="A92:BM92"/>
-    <mergeCell ref="A93:BM93"/>
+    <mergeCell ref="B80:E80"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="A88:V88"/>
     <mergeCell ref="A94:BM94"/>
     <mergeCell ref="A95:BM95"/>
     <mergeCell ref="A96:BM96"/>
     <mergeCell ref="A97:BM97"/>
+    <mergeCell ref="A98:BM98"/>
+    <mergeCell ref="A99:BM99"/>
+    <mergeCell ref="A100:BM100"/>
+    <mergeCell ref="A101:BM101"/>
+    <mergeCell ref="A102:BM102"/>
+    <mergeCell ref="A103:BM103"/>
+    <mergeCell ref="A104:BM104"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3272" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3232" uniqueCount="381">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 05/05/2026 07:39:20</t>
+    <t xml:space="preserve">Emitido em: 05/05/2026 10:35:14</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -539,15 +539,6 @@
   </si>
   <si>
     <t xml:space="preserve">35260454542238000178550010000965331000963341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.268,87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29260429244900000247550010000667481169109514</t>
   </si>
   <si>
     <t xml:space="preserve">5.069.519</t>
@@ -17360,7 +17351,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM101"/>
+  <dimension ref="A1:BM100"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -22125,10 +22116,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>305866</v>
+        <v>305908</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -22140,64 +22131,64 @@
         <v>83</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>4268.87</v>
+        <v>366.64</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>3805.45</v>
+        <v>344.26</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0</v>
+        <v>0.007989</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>52.96</v>
+        <v>0</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>463.42</v>
+        <v>22.38</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>3805.45</v>
+        <v>344.26</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>152.22</v>
+        <v>13.77</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22266,7 +22257,7 @@
         <v>76</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -22302,7 +22293,7 @@
         <v>78</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22316,7 +22307,7 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>305908</v>
+        <v>305926</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>97</v>
@@ -22325,7 +22316,7 @@
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>83</v>
@@ -22334,7 +22325,7 @@
         <v>141</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>78</v>
@@ -22367,7 +22358,7 @@
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
@@ -22379,7 +22370,7 @@
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y29" s="12" t="n">
         <v>22.38</v>
@@ -22493,7 +22484,7 @@
         <v>78</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22507,7 +22498,7 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>305926</v>
+        <v>305928</v>
       </c>
       <c r="B30" s="9" t="s">
         <v>97</v>
@@ -22516,7 +22507,7 @@
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>83</v>
@@ -22525,7 +22516,7 @@
         <v>141</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J30" s="9" t="s">
         <v>78</v>
@@ -22558,7 +22549,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
@@ -22570,7 +22561,7 @@
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>22.38</v>
@@ -22684,7 +22675,7 @@
         <v>78</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22698,7 +22689,7 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>305928</v>
+        <v>305930</v>
       </c>
       <c r="B31" s="9" t="s">
         <v>97</v>
@@ -22707,7 +22698,7 @@
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>83</v>
@@ -22716,7 +22707,7 @@
         <v>141</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>78</v>
@@ -22749,7 +22740,7 @@
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
@@ -22761,7 +22752,7 @@
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y31" s="12" t="n">
         <v>22.38</v>
@@ -22875,7 +22866,7 @@
         <v>78</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22889,7 +22880,7 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>305930</v>
+        <v>305941</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>97</v>
@@ -22898,7 +22889,7 @@
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>83</v>
@@ -22907,7 +22898,7 @@
         <v>141</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>78</v>
@@ -22916,7 +22907,7 @@
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>366.64</v>
+        <v>42.44</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -22925,22 +22916,22 @@
         <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>344.26</v>
+        <v>39.85</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.007989</v>
+        <v>0.002284</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>1.76</v>
+        <v>0.8</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
@@ -22952,16 +22943,16 @@
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>22.38</v>
+        <v>2.59</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>344.26</v>
+        <v>39.85</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>13.77</v>
+        <v>1.59</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -23080,7 +23071,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>305941</v>
+        <v>305943</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>97</v>
@@ -23098,7 +23089,7 @@
         <v>141</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>78</v>
@@ -23131,7 +23122,7 @@
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
@@ -23143,7 +23134,7 @@
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y33" s="12" t="n">
         <v>2.59</v>
@@ -23257,7 +23248,7 @@
         <v>78</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23271,7 +23262,7 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>305943</v>
+        <v>305944</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>97</v>
@@ -23280,7 +23271,7 @@
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>83</v>
@@ -23289,7 +23280,7 @@
         <v>141</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J34" s="9" t="s">
         <v>78</v>
@@ -23322,7 +23313,7 @@
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
@@ -23334,7 +23325,7 @@
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y34" s="12" t="n">
         <v>2.59</v>
@@ -23448,7 +23439,7 @@
         <v>78</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23462,7 +23453,7 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>305944</v>
+        <v>305945</v>
       </c>
       <c r="B35" s="9" t="s">
         <v>97</v>
@@ -23471,7 +23462,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>83</v>
@@ -23480,7 +23471,7 @@
         <v>141</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>78</v>
@@ -23513,7 +23504,7 @@
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
@@ -23525,7 +23516,7 @@
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y35" s="12" t="n">
         <v>2.59</v>
@@ -23639,7 +23630,7 @@
         <v>78</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23653,7 +23644,7 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>305945</v>
+        <v>305946</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>97</v>
@@ -23662,7 +23653,7 @@
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>83</v>
@@ -23671,7 +23662,7 @@
         <v>141</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>78</v>
@@ -23680,7 +23671,7 @@
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>42.44</v>
+        <v>329.55</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
@@ -23689,13 +23680,13 @@
         <v>1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>39.85</v>
+        <v>309.44</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.002284</v>
+        <v>0.017132</v>
       </c>
       <c r="R36" s="12" t="n">
         <v>0.8</v>
@@ -23704,7 +23695,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
@@ -23716,16 +23707,16 @@
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>2.59</v>
+        <v>20.11</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>39.85</v>
+        <v>309.44</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>1.59</v>
+        <v>12.38</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23844,7 +23835,7 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>305946</v>
+        <v>305950</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>97</v>
@@ -23862,7 +23853,7 @@
         <v>141</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>78</v>
@@ -23895,7 +23886,7 @@
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
@@ -23907,7 +23898,7 @@
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y37" s="12" t="n">
         <v>20.11</v>
@@ -24021,7 +24012,7 @@
         <v>78</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -24035,7 +24026,7 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>305950</v>
+        <v>305951</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>97</v>
@@ -24044,7 +24035,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>83</v>
@@ -24053,7 +24044,7 @@
         <v>141</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>78</v>
@@ -24086,7 +24077,7 @@
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
@@ -24098,7 +24089,7 @@
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y38" s="12" t="n">
         <v>20.11</v>
@@ -24212,7 +24203,7 @@
         <v>78</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -24226,7 +24217,7 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>305951</v>
+        <v>305952</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>97</v>
@@ -24235,7 +24226,7 @@
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>83</v>
@@ -24244,7 +24235,7 @@
         <v>141</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>78</v>
@@ -24277,7 +24268,7 @@
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
@@ -24289,7 +24280,7 @@
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y39" s="12" t="n">
         <v>20.11</v>
@@ -24403,7 +24394,7 @@
         <v>78</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24417,7 +24408,7 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>305952</v>
+        <v>305959</v>
       </c>
       <c r="B40" s="9" t="s">
         <v>97</v>
@@ -24426,16 +24417,16 @@
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>141</v>
+        <v>174</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J40" s="9" t="s">
         <v>78</v>
@@ -24444,7 +24435,7 @@
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>329.55</v>
+        <v>126.7</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
@@ -24453,22 +24444,22 @@
         <v>1</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>309.44</v>
+        <v>118.97</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.017132</v>
+        <v>0.001512</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>0.8</v>
+        <v>1.58</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
@@ -24480,16 +24471,16 @@
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>20.11</v>
+        <v>7.73</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>309.44</v>
+        <v>118.97</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>12.38</v>
+        <v>4.76</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24608,7 +24599,7 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>305959</v>
+        <v>305961</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>97</v>
@@ -24623,10 +24614,10 @@
         <v>83</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>78</v>
@@ -24659,7 +24650,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
@@ -24671,7 +24662,7 @@
         <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y41" s="12" t="n">
         <v>7.73</v>
@@ -24785,7 +24776,7 @@
         <v>78</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24799,7 +24790,7 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>305961</v>
+        <v>305963</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>97</v>
@@ -24808,16 +24799,16 @@
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J42" s="9" t="s">
         <v>78</v>
@@ -24850,7 +24841,7 @@
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
@@ -24862,7 +24853,7 @@
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y42" s="12" t="n">
         <v>7.73</v>
@@ -24976,7 +24967,7 @@
         <v>78</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24990,7 +24981,7 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>305963</v>
+        <v>305965</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>97</v>
@@ -24999,16 +24990,16 @@
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>78</v>
@@ -25017,31 +25008,31 @@
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>126.7</v>
+        <v>290.09</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>118.97</v>
+        <v>272.38</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.003202</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>1.58</v>
+        <v>1.93</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
@@ -25053,16 +25044,16 @@
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>7.73</v>
+        <v>17.71</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>118.97</v>
+        <v>272.38</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>4.76</v>
+        <v>10.89</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -25181,7 +25172,7 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>305965</v>
+        <v>305967</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>97</v>
@@ -25196,10 +25187,10 @@
         <v>83</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J44" s="9" t="s">
         <v>78</v>
@@ -25232,7 +25223,7 @@
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
@@ -25244,7 +25235,7 @@
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y44" s="12" t="n">
         <v>17.71</v>
@@ -25358,7 +25349,7 @@
         <v>78</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25372,7 +25363,7 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>305967</v>
+        <v>305968</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>97</v>
@@ -25381,16 +25372,16 @@
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>78</v>
@@ -25423,7 +25414,7 @@
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
@@ -25435,7 +25426,7 @@
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y45" s="12" t="n">
         <v>17.71</v>
@@ -25549,7 +25540,7 @@
         <v>78</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25563,7 +25554,7 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>305968</v>
+        <v>305969</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>97</v>
@@ -25572,16 +25563,16 @@
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J46" s="9" t="s">
         <v>78</v>
@@ -25614,7 +25605,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
@@ -25626,7 +25617,7 @@
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y46" s="12" t="n">
         <v>17.71</v>
@@ -25740,7 +25731,7 @@
         <v>78</v>
       </c>
       <c r="BJ46" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="BK46" s="9" t="s">
         <v>75</v>
@@ -25754,7 +25745,7 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>305969</v>
+        <v>305970</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>97</v>
@@ -25763,16 +25754,16 @@
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>78</v>
@@ -25781,31 +25772,31 @@
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>290.09</v>
+        <v>126.7</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>272.38</v>
+        <v>118.97</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.001512</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
@@ -25817,16 +25808,16 @@
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y47" s="12" t="n">
-        <v>17.71</v>
+        <v>7.73</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>272.38</v>
+        <v>118.97</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>10.89</v>
+        <v>4.76</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25931,7 +25922,7 @@
         <v>78</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="BK47" s="9" t="s">
         <v>75</v>
@@ -25945,34 +25936,34 @@
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>305970</v>
+        <v>305977</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>97</v>
+        <v>155</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H48" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="G48" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>177</v>
-      </c>
       <c r="I48" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>78</v>
+        <v>221</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>126.7</v>
+        <v>557.39</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
@@ -25981,43 +25972,43 @@
         <v>1</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>118.97</v>
+        <v>557.39</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.005136</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>1.58</v>
+        <v>1.07</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="14" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="U48" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V48" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X48" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y48" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>118.97</v>
+        <v>557.39</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>4.76</v>
+        <v>39.02</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -26086,7 +26077,7 @@
         <v>76</v>
       </c>
       <c r="AX48" s="10" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="AY48" s="14" t="s">
         <v>75</v>
@@ -26122,7 +26113,7 @@
         <v>78</v>
       </c>
       <c r="BJ48" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="BK48" s="9" t="s">
         <v>75</v>
@@ -26136,79 +26127,79 @@
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>305977</v>
+        <v>305979</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>155</v>
+        <v>224</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="G49" s="10" t="s">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>557.39</v>
+        <v>2235.86</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>557.39</v>
+        <v>2094.8</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0.005136</v>
+        <v>0.0136</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>1.07</v>
+        <v>2.44</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="Y49" s="12" t="n">
-        <v>0</v>
+        <v>141.06</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>557.39</v>
+        <v>2094.8</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>39.02</v>
+        <v>146.64</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26313,7 +26304,7 @@
         <v>78</v>
       </c>
       <c r="BJ49" s="9" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="BK49" s="9" t="s">
         <v>75</v>
@@ -26327,52 +26318,52 @@
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>305979</v>
+        <v>305999</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>227</v>
+        <v>155</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>229</v>
+        <v>151</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>230</v>
+        <v>142</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>2235.86</v>
+        <v>1430.23</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>2094.8</v>
+        <v>1342.94</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.0136</v>
+        <v>0</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>0</v>
@@ -26384,22 +26375,22 @@
         <v>72</v>
       </c>
       <c r="V50" s="12" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="W50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="Y50" s="12" t="n">
-        <v>141.06</v>
+        <v>87.29</v>
       </c>
       <c r="Z50" s="12" t="n">
-        <v>2094.8</v>
+        <v>1342.94</v>
       </c>
       <c r="AA50" s="12" t="n">
-        <v>146.64</v>
+        <v>94.01</v>
       </c>
       <c r="AB50" s="12" t="n">
         <v>0</v>
@@ -26518,7 +26509,7 @@
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>305999</v>
+        <v>306002</v>
       </c>
       <c r="B51" s="9" t="s">
         <v>155</v>
@@ -26533,19 +26524,19 @@
         <v>157</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>151</v>
+        <v>226</v>
       </c>
       <c r="I51" s="9" t="s">
         <v>135</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>142</v>
+        <v>234</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>1430.23</v>
+        <v>2665.63</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
@@ -26554,22 +26545,22 @@
         <v>1</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>1342.94</v>
+        <v>2502.94</v>
       </c>
       <c r="P51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0</v>
+        <v>0.027908</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>72</v>
@@ -26584,13 +26575,13 @@
         <v>135</v>
       </c>
       <c r="Y51" s="12" t="n">
-        <v>87.29</v>
+        <v>162.69</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>1342.94</v>
+        <v>2502.94</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>94.01</v>
+        <v>175.21</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26695,7 +26686,7 @@
         <v>78</v>
       </c>
       <c r="BJ51" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="BK51" s="9" t="s">
         <v>75</v>
@@ -26709,7 +26700,7 @@
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>306002</v>
+        <v>306047</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>155</v>
@@ -26718,25 +26709,25 @@
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G52" s="10" t="s">
         <v>157</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>229</v>
+        <v>135</v>
       </c>
       <c r="I52" s="9" t="s">
         <v>135</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>2665.63</v>
+        <v>1021.1</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
@@ -26745,22 +26736,22 @@
         <v>1</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>2502.94</v>
+        <v>1021.1</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>0.027908</v>
+        <v>0.010608</v>
       </c>
       <c r="R52" s="12" t="n">
-        <v>3.56</v>
+        <v>2.67</v>
       </c>
       <c r="S52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="U52" s="15" t="s">
         <v>72</v>
@@ -26775,13 +26766,13 @@
         <v>135</v>
       </c>
       <c r="Y52" s="12" t="n">
-        <v>162.69</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>2502.94</v>
+        <v>1021.1</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>175.21</v>
+        <v>40.84</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26886,7 +26877,7 @@
         <v>78</v>
       </c>
       <c r="BJ52" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="BK52" s="9" t="s">
         <v>75</v>
@@ -26900,34 +26891,34 @@
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>306047</v>
+        <v>306049</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>155</v>
+        <v>224</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>135</v>
+        <v>226</v>
       </c>
       <c r="I53" s="9" t="s">
         <v>135</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>1021.1</v>
+        <v>3660.21</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
@@ -26936,16 +26927,16 @@
         <v>1</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>1021.1</v>
+        <v>3545</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>0.010608</v>
+        <v>0.0105</v>
       </c>
       <c r="R53" s="12" t="n">
-        <v>2.67</v>
+        <v>16</v>
       </c>
       <c r="S53" s="12" t="n">
         <v>0</v>
@@ -26957,7 +26948,7 @@
         <v>72</v>
       </c>
       <c r="V53" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="W53" s="9" t="s">
         <v>73</v>
@@ -26966,13 +26957,13 @@
         <v>135</v>
       </c>
       <c r="Y53" s="12" t="n">
-        <v>0</v>
+        <v>115.21</v>
       </c>
       <c r="Z53" s="12" t="n">
-        <v>1021.1</v>
+        <v>3545</v>
       </c>
       <c r="AA53" s="12" t="n">
-        <v>40.84</v>
+        <v>141.8</v>
       </c>
       <c r="AB53" s="12" t="n">
         <v>0</v>
@@ -27091,10 +27082,10 @@
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>306049</v>
+        <v>306050</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
@@ -27106,37 +27097,37 @@
         <v>66</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I54" s="9" t="s">
         <v>135</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>3660.21</v>
+        <v>4151.64</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>3545</v>
+        <v>3993.25</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>0.0105</v>
+        <v>0.01002</v>
       </c>
       <c r="R54" s="12" t="n">
-        <v>16</v>
+        <v>18.95</v>
       </c>
       <c r="S54" s="12" t="n">
         <v>0</v>
@@ -27157,13 +27148,13 @@
         <v>135</v>
       </c>
       <c r="Y54" s="12" t="n">
-        <v>115.21</v>
+        <v>158.39</v>
       </c>
       <c r="Z54" s="12" t="n">
-        <v>3545</v>
+        <v>3993.25</v>
       </c>
       <c r="AA54" s="12" t="n">
-        <v>141.8</v>
+        <v>175.78</v>
       </c>
       <c r="AB54" s="12" t="n">
         <v>0</v>
@@ -27282,64 +27273,64 @@
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>306050</v>
+        <v>306060</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>229</v>
+        <v>174</v>
       </c>
       <c r="I55" s="9" t="s">
         <v>135</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>4151.64</v>
+        <v>4228.44</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>3993.25</v>
+        <v>4152.95</v>
       </c>
       <c r="P55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q55" s="13" t="n">
-        <v>0.01002</v>
+        <v>0</v>
       </c>
       <c r="R55" s="12" t="n">
-        <v>18.95</v>
+        <v>208.9</v>
       </c>
       <c r="S55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="U55" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V55" s="12" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="W55" s="9" t="s">
         <v>73</v>
@@ -27348,13 +27339,13 @@
         <v>135</v>
       </c>
       <c r="Y55" s="12" t="n">
-        <v>158.39</v>
+        <v>75.49</v>
       </c>
       <c r="Z55" s="12" t="n">
-        <v>3993.25</v>
+        <v>4152.95</v>
       </c>
       <c r="AA55" s="12" t="n">
-        <v>175.78</v>
+        <v>284.08</v>
       </c>
       <c r="AB55" s="12" t="n">
         <v>0</v>
@@ -27459,7 +27450,7 @@
         <v>78</v>
       </c>
       <c r="BJ55" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BK55" s="9" t="s">
         <v>75</v>
@@ -27473,64 +27464,64 @@
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>306060</v>
+        <v>306156</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G56" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="I56" s="9" t="s">
         <v>135</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>252</v>
+        <v>147</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>4228.44</v>
+        <v>2733.03</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>4152.95</v>
+        <v>2647</v>
       </c>
       <c r="P56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q56" s="13" t="n">
-        <v>0</v>
+        <v>0.000135</v>
       </c>
       <c r="R56" s="12" t="n">
-        <v>208.9</v>
+        <v>500</v>
       </c>
       <c r="S56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T56" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="U56" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V56" s="12" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="W56" s="9" t="s">
         <v>73</v>
@@ -27539,13 +27530,13 @@
         <v>135</v>
       </c>
       <c r="Y56" s="12" t="n">
-        <v>75.49</v>
+        <v>86.03</v>
       </c>
       <c r="Z56" s="12" t="n">
-        <v>4152.95</v>
+        <v>2647</v>
       </c>
       <c r="AA56" s="12" t="n">
-        <v>284.08</v>
+        <v>185.29</v>
       </c>
       <c r="AB56" s="12" t="n">
         <v>0</v>
@@ -27650,7 +27641,7 @@
         <v>78</v>
       </c>
       <c r="BJ56" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="BK56" s="9" t="s">
         <v>75</v>
@@ -27664,64 +27655,64 @@
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="n">
-        <v>306156</v>
+        <v>306160</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="9"/>
       <c r="E57" s="9"/>
       <c r="F57" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G57" s="10" t="s">
-        <v>83</v>
+        <v>258</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="I57" s="9" t="s">
         <v>135</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>147</v>
+        <v>259</v>
       </c>
       <c r="K57" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>2733.03</v>
+        <v>84810.62</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="O57" s="12" t="n">
-        <v>2647</v>
+        <v>83193.37</v>
       </c>
       <c r="P57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q57" s="13" t="n">
-        <v>0.000135</v>
+        <v>8.867016</v>
       </c>
       <c r="R57" s="12" t="n">
-        <v>500</v>
+        <v>1910.81</v>
       </c>
       <c r="S57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T57" s="14" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="U57" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V57" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="W57" s="9" t="s">
         <v>73</v>
@@ -27730,13 +27721,13 @@
         <v>135</v>
       </c>
       <c r="Y57" s="12" t="n">
-        <v>86.03</v>
+        <v>1617.25</v>
       </c>
       <c r="Z57" s="12" t="n">
-        <v>2647</v>
+        <v>83193.37</v>
       </c>
       <c r="AA57" s="12" t="n">
-        <v>185.29</v>
+        <v>5525.86</v>
       </c>
       <c r="AB57" s="12" t="n">
         <v>0</v>
@@ -27841,7 +27832,7 @@
         <v>78</v>
       </c>
       <c r="BJ57" s="9" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="BK57" s="9" t="s">
         <v>75</v>
@@ -27855,79 +27846,79 @@
     </row>
     <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="8" t="n">
-        <v>306160</v>
+        <v>306328</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>259</v>
+        <v>155</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
       <c r="E58" s="9"/>
       <c r="F58" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>261</v>
+        <v>157</v>
       </c>
       <c r="H58" s="9" t="s">
-        <v>223</v>
+        <v>135</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>135</v>
+        <v>263</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>262</v>
+        <v>238</v>
       </c>
       <c r="K58" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>84810.62</v>
+        <v>3954.7</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="O58" s="12" t="n">
-        <v>83193.37</v>
+        <v>3954.7</v>
       </c>
       <c r="P58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q58" s="13" t="n">
-        <v>8.867016</v>
+        <v>0.05525</v>
       </c>
       <c r="R58" s="12" t="n">
-        <v>1910.81</v>
+        <v>14.5</v>
       </c>
       <c r="S58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T58" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="U58" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V58" s="12" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="W58" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X58" s="9" t="s">
-        <v>135</v>
+        <v>263</v>
       </c>
       <c r="Y58" s="12" t="n">
-        <v>1617.25</v>
+        <v>0</v>
       </c>
       <c r="Z58" s="12" t="n">
-        <v>83193.37</v>
+        <v>3954.7</v>
       </c>
       <c r="AA58" s="12" t="n">
-        <v>5525.86</v>
+        <v>276.83</v>
       </c>
       <c r="AB58" s="12" t="n">
         <v>0</v>
@@ -28032,7 +28023,7 @@
         <v>78</v>
       </c>
       <c r="BJ58" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="BK58" s="9" t="s">
         <v>75</v>
@@ -28046,7 +28037,7 @@
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="8" t="n">
-        <v>306328</v>
+        <v>306330</v>
       </c>
       <c r="B59" s="9" t="s">
         <v>155</v>
@@ -28055,25 +28046,25 @@
       <c r="D59" s="9"/>
       <c r="E59" s="9"/>
       <c r="F59" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G59" s="10" t="s">
         <v>157</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="K59" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>3954.7</v>
+        <v>2372.82</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>0</v>
@@ -28082,16 +28073,16 @@
         <v>1</v>
       </c>
       <c r="O59" s="12" t="n">
-        <v>3954.7</v>
+        <v>2372.82</v>
       </c>
       <c r="P59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q59" s="13" t="n">
-        <v>0.05525</v>
+        <v>0.03315</v>
       </c>
       <c r="R59" s="12" t="n">
-        <v>14.5</v>
+        <v>8.7</v>
       </c>
       <c r="S59" s="12" t="n">
         <v>0</v>
@@ -28109,16 +28100,16 @@
         <v>73</v>
       </c>
       <c r="X59" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Y59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z59" s="12" t="n">
-        <v>3954.7</v>
+        <v>2372.82</v>
       </c>
       <c r="AA59" s="12" t="n">
-        <v>276.83</v>
+        <v>166.1</v>
       </c>
       <c r="AB59" s="12" t="n">
         <v>0</v>
@@ -28237,7 +28228,7 @@
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="8" t="n">
-        <v>306330</v>
+        <v>306333</v>
       </c>
       <c r="B60" s="9" t="s">
         <v>155</v>
@@ -28255,16 +28246,16 @@
         <v>170</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="K60" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>2372.82</v>
+        <v>807.1</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>0</v>
@@ -28273,16 +28264,16 @@
         <v>1</v>
       </c>
       <c r="O60" s="12" t="n">
-        <v>2372.82</v>
+        <v>807.1</v>
       </c>
       <c r="P60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q60" s="13" t="n">
-        <v>0.03315</v>
+        <v>0.01105</v>
       </c>
       <c r="R60" s="12" t="n">
-        <v>8.7</v>
+        <v>2.9</v>
       </c>
       <c r="S60" s="12" t="n">
         <v>0</v>
@@ -28300,16 +28291,16 @@
         <v>73</v>
       </c>
       <c r="X60" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Y60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z60" s="12" t="n">
-        <v>2372.82</v>
+        <v>807.1</v>
       </c>
       <c r="AA60" s="12" t="n">
-        <v>166.1</v>
+        <v>56.5</v>
       </c>
       <c r="AB60" s="12" t="n">
         <v>0</v>
@@ -28428,34 +28419,34 @@
     </row>
     <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="8" t="n">
-        <v>306333</v>
+        <v>306339</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>155</v>
+        <v>272</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="9"/>
       <c r="E61" s="9"/>
       <c r="F61" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G61" s="10" t="s">
-        <v>157</v>
+        <v>83</v>
       </c>
       <c r="H61" s="9" t="s">
         <v>170</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>252</v>
+        <v>274</v>
       </c>
       <c r="K61" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>807.1</v>
+        <v>3766.18</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>0</v>
@@ -28464,43 +28455,43 @@
         <v>1</v>
       </c>
       <c r="O61" s="12" t="n">
-        <v>807.1</v>
+        <v>3766.18</v>
       </c>
       <c r="P61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q61" s="13" t="n">
-        <v>0.01105</v>
+        <v>0</v>
       </c>
       <c r="R61" s="12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="S61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T61" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="U61" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V61" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="W61" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X61" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Y61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z61" s="12" t="n">
-        <v>807.1</v>
+        <v>3766.18</v>
       </c>
       <c r="AA61" s="12" t="n">
-        <v>56.5</v>
+        <v>150.65</v>
       </c>
       <c r="AB61" s="12" t="n">
         <v>0</v>
@@ -28605,7 +28596,7 @@
         <v>78</v>
       </c>
       <c r="BJ61" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="BK61" s="9" t="s">
         <v>75</v>
@@ -28619,16 +28610,16 @@
     </row>
     <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="8" t="n">
-        <v>306339</v>
+        <v>306340</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="9"/>
       <c r="E62" s="9"/>
       <c r="F62" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G62" s="10" t="s">
         <v>83</v>
@@ -28637,25 +28628,25 @@
         <v>170</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>3766.18</v>
+        <v>936.27</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O62" s="12" t="n">
-        <v>3766.18</v>
+        <v>915.61</v>
       </c>
       <c r="P62" s="12" t="n">
         <v>0</v>
@@ -28682,16 +28673,16 @@
         <v>73</v>
       </c>
       <c r="X62" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Y62" s="12" t="n">
-        <v>0</v>
+        <v>20.66</v>
       </c>
       <c r="Z62" s="12" t="n">
-        <v>3766.18</v>
+        <v>915.61</v>
       </c>
       <c r="AA62" s="12" t="n">
-        <v>150.65</v>
+        <v>36.62</v>
       </c>
       <c r="AB62" s="12" t="n">
         <v>0</v>
@@ -28810,79 +28801,79 @@
     </row>
     <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="8" t="n">
-        <v>306340</v>
+        <v>306378</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="9"/>
       <c r="E63" s="9"/>
       <c r="F63" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G63" s="10" t="s">
-        <v>83</v>
+        <v>282</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="K63" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>936.27</v>
+        <v>95349.48</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="O63" s="12" t="n">
-        <v>915.61</v>
+        <v>91519.49</v>
       </c>
       <c r="P63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q63" s="13" t="n">
-        <v>0</v>
+        <v>0.80555</v>
       </c>
       <c r="R63" s="12" t="n">
-        <v>0</v>
+        <v>424.1</v>
       </c>
       <c r="S63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T63" s="14" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="U63" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V63" s="12" t="n">
-        <v>39</v>
+        <v>82.61</v>
       </c>
       <c r="W63" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X63" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Y63" s="12" t="n">
-        <v>20.66</v>
+        <v>3829.99</v>
       </c>
       <c r="Z63" s="12" t="n">
-        <v>915.61</v>
+        <v>91519.49</v>
       </c>
       <c r="AA63" s="12" t="n">
-        <v>36.62</v>
+        <v>6406.35</v>
       </c>
       <c r="AB63" s="12" t="n">
         <v>0</v>
@@ -28987,7 +28978,7 @@
         <v>78</v>
       </c>
       <c r="BJ63" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="BK63" s="9" t="s">
         <v>75</v>
@@ -29001,79 +28992,79 @@
     </row>
     <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="8" t="n">
-        <v>306378</v>
+        <v>306397</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C64" s="9"/>
       <c r="D64" s="9"/>
       <c r="E64" s="9"/>
       <c r="F64" s="9" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="G64" s="10" t="s">
-        <v>285</v>
+        <v>83</v>
       </c>
       <c r="H64" s="9" t="s">
         <v>135</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>286</v>
+        <v>238</v>
       </c>
       <c r="K64" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>95349.48</v>
+        <v>2472.29</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0</v>
+        <v>60.1</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="O64" s="12" t="n">
-        <v>91519.49</v>
+        <v>2381.5</v>
       </c>
       <c r="P64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q64" s="13" t="n">
-        <v>0.80555</v>
+        <v>0.00163</v>
       </c>
       <c r="R64" s="12" t="n">
-        <v>424.1</v>
+        <v>15</v>
       </c>
       <c r="S64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T64" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="U64" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V64" s="12" t="n">
-        <v>82.61</v>
+        <v>28</v>
       </c>
       <c r="W64" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X64" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Y64" s="12" t="n">
-        <v>3829.99</v>
+        <v>150.89</v>
       </c>
       <c r="Z64" s="12" t="n">
-        <v>91519.49</v>
+        <v>2321.4</v>
       </c>
       <c r="AA64" s="12" t="n">
-        <v>6406.35</v>
+        <v>162.5</v>
       </c>
       <c r="AB64" s="12" t="n">
         <v>0</v>
@@ -29178,7 +29169,7 @@
         <v>78</v>
       </c>
       <c r="BJ64" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="BK64" s="9" t="s">
         <v>75</v>
@@ -29192,79 +29183,79 @@
     </row>
     <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="8" t="n">
-        <v>306397</v>
+        <v>306401</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="9"/>
       <c r="E65" s="9"/>
       <c r="F65" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G65" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="K65" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>2472.29</v>
+        <v>9706.42</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>60.1</v>
+        <v>0</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O65" s="12" t="n">
-        <v>2381.5</v>
+        <v>8844.12</v>
       </c>
       <c r="P65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q65" s="13" t="n">
-        <v>0.00163</v>
+        <v>0</v>
       </c>
       <c r="R65" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T65" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="U65" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V65" s="12" t="n">
-        <v>28</v>
+        <v>44.58</v>
       </c>
       <c r="W65" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X65" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Y65" s="12" t="n">
-        <v>150.89</v>
+        <v>862.3</v>
       </c>
       <c r="Z65" s="12" t="n">
-        <v>2321.4</v>
+        <v>8844.12</v>
       </c>
       <c r="AA65" s="12" t="n">
-        <v>162.5</v>
+        <v>619.09</v>
       </c>
       <c r="AB65" s="12" t="n">
         <v>0</v>
@@ -29369,7 +29360,7 @@
         <v>78</v>
       </c>
       <c r="BJ65" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="BK65" s="9" t="s">
         <v>75</v>
@@ -29383,10 +29374,10 @@
     </row>
     <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="8" t="n">
-        <v>306401</v>
+        <v>306494</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>293</v>
+        <v>155</v>
       </c>
       <c r="C66" s="9"/>
       <c r="D66" s="9"/>
@@ -29395,67 +29386,67 @@
         <v>294</v>
       </c>
       <c r="G66" s="10" t="s">
-        <v>83</v>
+        <v>157</v>
       </c>
       <c r="H66" s="9" t="s">
-        <v>170</v>
+        <v>263</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="K66" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>9706.42</v>
+        <v>40206.95</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" s="12" t="n">
-        <v>8844.12</v>
+        <v>37753</v>
       </c>
       <c r="P66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q66" s="13" t="n">
-        <v>0</v>
+        <v>0.24</v>
       </c>
       <c r="R66" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S66" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T66" s="14" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="U66" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V66" s="12" t="n">
-        <v>44.58</v>
+        <v>28</v>
       </c>
       <c r="W66" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X66" s="9" t="s">
-        <v>266</v>
+        <v>295</v>
       </c>
       <c r="Y66" s="12" t="n">
-        <v>862.3</v>
+        <v>2453.95</v>
       </c>
       <c r="Z66" s="12" t="n">
-        <v>8844.12</v>
+        <v>37753</v>
       </c>
       <c r="AA66" s="12" t="n">
-        <v>619.09</v>
+        <v>2642.71</v>
       </c>
       <c r="AB66" s="12" t="n">
         <v>0</v>
@@ -29560,7 +29551,7 @@
         <v>78</v>
       </c>
       <c r="BJ66" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="BK66" s="9" t="s">
         <v>75</v>
@@ -29574,7 +29565,7 @@
     </row>
     <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="8" t="n">
-        <v>306494</v>
+        <v>306496</v>
       </c>
       <c r="B67" s="9" t="s">
         <v>155</v>
@@ -29583,43 +29574,43 @@
       <c r="D67" s="9"/>
       <c r="E67" s="9"/>
       <c r="F67" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G67" s="10" t="s">
         <v>157</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K67" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>40206.95</v>
+        <v>79798.26</v>
       </c>
       <c r="M67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O67" s="12" t="n">
-        <v>37753</v>
+        <v>79696.44</v>
       </c>
       <c r="P67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q67" s="13" t="n">
-        <v>0.24</v>
+        <v>0.990242</v>
       </c>
       <c r="R67" s="12" t="n">
-        <v>1</v>
+        <v>316.25</v>
       </c>
       <c r="S67" s="12" t="n">
         <v>0</v>
@@ -29637,16 +29628,16 @@
         <v>73</v>
       </c>
       <c r="X67" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y67" s="12" t="n">
-        <v>2453.95</v>
+        <v>101.82</v>
       </c>
       <c r="Z67" s="12" t="n">
-        <v>37753</v>
+        <v>79696.44</v>
       </c>
       <c r="AA67" s="12" t="n">
-        <v>2642.71</v>
+        <v>5578.75</v>
       </c>
       <c r="AB67" s="12" t="n">
         <v>0</v>
@@ -29765,7 +29756,7 @@
     </row>
     <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="8" t="n">
-        <v>306496</v>
+        <v>306497</v>
       </c>
       <c r="B68" s="9" t="s">
         <v>155</v>
@@ -29780,43 +29771,43 @@
         <v>157</v>
       </c>
       <c r="H68" s="9" t="s">
-        <v>266</v>
+        <v>303</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K68" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>79798.26</v>
+        <v>5331.26</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="12" t="n">
-        <v>79696.44</v>
+        <v>5005.88</v>
       </c>
       <c r="P68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q68" s="13" t="n">
-        <v>0.990242</v>
+        <v>0.055816</v>
       </c>
       <c r="R68" s="12" t="n">
-        <v>316.25</v>
+        <v>7.12</v>
       </c>
       <c r="S68" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T68" s="14" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="U68" s="15" t="s">
         <v>72</v>
@@ -29828,16 +29819,16 @@
         <v>73</v>
       </c>
       <c r="X68" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y68" s="12" t="n">
-        <v>101.82</v>
+        <v>325.38</v>
       </c>
       <c r="Z68" s="12" t="n">
-        <v>79696.44</v>
+        <v>5005.88</v>
       </c>
       <c r="AA68" s="12" t="n">
-        <v>5578.75</v>
+        <v>350.41</v>
       </c>
       <c r="AB68" s="12" t="n">
         <v>0</v>
@@ -29942,7 +29933,7 @@
         <v>78</v>
       </c>
       <c r="BJ68" s="9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="BK68" s="9" t="s">
         <v>75</v>
@@ -29956,7 +29947,7 @@
     </row>
     <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="8" t="n">
-        <v>306497</v>
+        <v>306498</v>
       </c>
       <c r="B69" s="9" t="s">
         <v>155</v>
@@ -29965,25 +29956,25 @@
       <c r="D69" s="9"/>
       <c r="E69" s="9"/>
       <c r="F69" s="9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G69" s="10" t="s">
         <v>157</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K69" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>5331.26</v>
+        <v>3005.56</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>0</v>
@@ -29992,16 +29983,16 @@
         <v>1</v>
       </c>
       <c r="O69" s="12" t="n">
-        <v>5005.88</v>
+        <v>3005.56</v>
       </c>
       <c r="P69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q69" s="13" t="n">
-        <v>0.055816</v>
+        <v>0.008736</v>
       </c>
       <c r="R69" s="12" t="n">
-        <v>7.12</v>
+        <v>2.32</v>
       </c>
       <c r="S69" s="12" t="n">
         <v>0</v>
@@ -30019,16 +30010,16 @@
         <v>73</v>
       </c>
       <c r="X69" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y69" s="12" t="n">
-        <v>325.38</v>
+        <v>0</v>
       </c>
       <c r="Z69" s="12" t="n">
-        <v>5005.88</v>
+        <v>3005.56</v>
       </c>
       <c r="AA69" s="12" t="n">
-        <v>350.41</v>
+        <v>210.39</v>
       </c>
       <c r="AB69" s="12" t="n">
         <v>0</v>
@@ -30147,7 +30138,7 @@
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="8" t="n">
-        <v>306498</v>
+        <v>306501</v>
       </c>
       <c r="B70" s="9" t="s">
         <v>155</v>
@@ -30162,19 +30153,19 @@
         <v>157</v>
       </c>
       <c r="H70" s="9" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="K70" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>3005.56</v>
+        <v>5779.28</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>0</v>
@@ -30183,16 +30174,16 @@
         <v>1</v>
       </c>
       <c r="O70" s="12" t="n">
-        <v>3005.56</v>
+        <v>5779.28</v>
       </c>
       <c r="P70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q70" s="13" t="n">
-        <v>0.008736</v>
+        <v>0.00943</v>
       </c>
       <c r="R70" s="12" t="n">
-        <v>2.32</v>
+        <v>4.8</v>
       </c>
       <c r="S70" s="12" t="n">
         <v>0</v>
@@ -30210,16 +30201,16 @@
         <v>73</v>
       </c>
       <c r="X70" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z70" s="12" t="n">
-        <v>3005.56</v>
+        <v>5779.28</v>
       </c>
       <c r="AA70" s="12" t="n">
-        <v>210.39</v>
+        <v>404.55</v>
       </c>
       <c r="AB70" s="12" t="n">
         <v>0</v>
@@ -30338,10 +30329,10 @@
     </row>
     <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="8" t="n">
-        <v>306501</v>
+        <v>306519</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>155</v>
+        <v>224</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="9"/>
@@ -30350,67 +30341,67 @@
         <v>313</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>157</v>
+        <v>66</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>306</v>
+        <v>263</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="K71" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>5779.28</v>
+        <v>9630.34</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O71" s="12" t="n">
-        <v>5779.28</v>
+        <v>8827.8</v>
       </c>
       <c r="P71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q71" s="13" t="n">
-        <v>0.00943</v>
+        <v>0.1212</v>
       </c>
       <c r="R71" s="12" t="n">
-        <v>4.8</v>
+        <v>84.02</v>
       </c>
       <c r="S71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T71" s="14" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="U71" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V71" s="12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="W71" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X71" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y71" s="12" t="n">
-        <v>0</v>
+        <v>802.54</v>
       </c>
       <c r="Z71" s="12" t="n">
-        <v>5779.28</v>
+        <v>8827.8</v>
       </c>
       <c r="AA71" s="12" t="n">
-        <v>404.55</v>
+        <v>617.95</v>
       </c>
       <c r="AB71" s="12" t="n">
         <v>0</v>
@@ -30515,7 +30506,7 @@
         <v>78</v>
       </c>
       <c r="BJ71" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="BK71" s="9" t="s">
         <v>75</v>
@@ -30529,79 +30520,79 @@
     </row>
     <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="8" t="n">
-        <v>306519</v>
+        <v>306521</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C72" s="9"/>
       <c r="D72" s="9"/>
       <c r="E72" s="9"/>
       <c r="F72" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G72" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H72" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K72" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>9630.34</v>
+        <v>2473.87</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O72" s="12" t="n">
-        <v>8827.8</v>
+        <v>2396</v>
       </c>
       <c r="P72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q72" s="13" t="n">
-        <v>0.1212</v>
+        <v>0.0896</v>
       </c>
       <c r="R72" s="12" t="n">
-        <v>84.02</v>
+        <v>7.2</v>
       </c>
       <c r="S72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T72" s="14" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="U72" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V72" s="12" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="W72" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X72" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y72" s="12" t="n">
-        <v>802.54</v>
+        <v>77.87</v>
       </c>
       <c r="Z72" s="12" t="n">
-        <v>8827.8</v>
+        <v>2396</v>
       </c>
       <c r="AA72" s="12" t="n">
-        <v>617.95</v>
+        <v>167.72</v>
       </c>
       <c r="AB72" s="12" t="n">
         <v>0</v>
@@ -30706,7 +30697,7 @@
         <v>78</v>
       </c>
       <c r="BJ72" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="BK72" s="9" t="s">
         <v>75</v>
@@ -30720,34 +30711,34 @@
     </row>
     <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="8" t="n">
-        <v>306521</v>
+        <v>306529</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="9"/>
       <c r="E73" s="9"/>
       <c r="F73" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G73" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="K73" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>2473.87</v>
+        <v>3222.43</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>0</v>
@@ -30756,16 +30747,16 @@
         <v>1</v>
       </c>
       <c r="O73" s="12" t="n">
-        <v>2396</v>
+        <v>3121</v>
       </c>
       <c r="P73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q73" s="13" t="n">
-        <v>0.0896</v>
+        <v>0.0021</v>
       </c>
       <c r="R73" s="12" t="n">
-        <v>7.2</v>
+        <v>3.2</v>
       </c>
       <c r="S73" s="12" t="n">
         <v>0</v>
@@ -30777,22 +30768,22 @@
         <v>72</v>
       </c>
       <c r="V73" s="12" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="W73" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X73" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y73" s="12" t="n">
-        <v>77.87</v>
+        <v>101.43</v>
       </c>
       <c r="Z73" s="12" t="n">
-        <v>2396</v>
+        <v>3121</v>
       </c>
       <c r="AA73" s="12" t="n">
-        <v>167.72</v>
+        <v>218.47</v>
       </c>
       <c r="AB73" s="12" t="n">
         <v>0</v>
@@ -30911,79 +30902,79 @@
     </row>
     <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="8" t="n">
-        <v>306529</v>
+        <v>306535</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>227</v>
+        <v>324</v>
       </c>
       <c r="C74" s="9"/>
       <c r="D74" s="9"/>
       <c r="E74" s="9"/>
       <c r="F74" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="H74" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>317</v>
+        <v>78</v>
       </c>
       <c r="K74" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>3222.43</v>
+        <v>5384.2</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O74" s="12" t="n">
-        <v>3121</v>
+        <v>5384.2</v>
       </c>
       <c r="P74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q74" s="13" t="n">
-        <v>0.0021</v>
+        <v>0.023054</v>
       </c>
       <c r="R74" s="12" t="n">
-        <v>3.2</v>
+        <v>28.62</v>
       </c>
       <c r="S74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T74" s="14" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="U74" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V74" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W74" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X74" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y74" s="12" t="n">
-        <v>101.43</v>
+        <v>0</v>
       </c>
       <c r="Z74" s="12" t="n">
-        <v>3121</v>
+        <v>0</v>
       </c>
       <c r="AA74" s="12" t="n">
-        <v>218.47</v>
+        <v>0</v>
       </c>
       <c r="AB74" s="12" t="n">
         <v>0</v>
@@ -31052,7 +31043,7 @@
         <v>76</v>
       </c>
       <c r="AX74" s="10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AY74" s="14" t="s">
         <v>75</v>
@@ -31088,7 +31079,7 @@
         <v>78</v>
       </c>
       <c r="BJ74" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="BK74" s="9" t="s">
         <v>75</v>
@@ -31102,10 +31093,10 @@
     </row>
     <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="8" t="n">
-        <v>306535</v>
+        <v>306536</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="9"/>
@@ -31117,10 +31108,10 @@
         <v>83</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J75" s="9" t="s">
         <v>78</v>
@@ -31129,25 +31120,25 @@
         <v>70</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>5384.2</v>
+        <v>8305.8</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O75" s="12" t="n">
-        <v>5384.2</v>
+        <v>8305.8</v>
       </c>
       <c r="P75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q75" s="13" t="n">
-        <v>0.023054</v>
+        <v>0.02159</v>
       </c>
       <c r="R75" s="12" t="n">
-        <v>28.62</v>
+        <v>29.29</v>
       </c>
       <c r="S75" s="12" t="n">
         <v>0</v>
@@ -31165,7 +31156,7 @@
         <v>73</v>
       </c>
       <c r="X75" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y75" s="12" t="n">
         <v>0</v>
@@ -31293,10 +31284,10 @@
     </row>
     <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="8" t="n">
-        <v>306536</v>
+        <v>306537</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C76" s="9"/>
       <c r="D76" s="9"/>
@@ -31308,10 +31299,10 @@
         <v>83</v>
       </c>
       <c r="H76" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J76" s="9" t="s">
         <v>78</v>
@@ -31320,7 +31311,7 @@
         <v>70</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>8305.8</v>
+        <v>18545.08</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
@@ -31329,16 +31320,16 @@
         <v>2</v>
       </c>
       <c r="O76" s="12" t="n">
-        <v>8305.8</v>
+        <v>18545.08</v>
       </c>
       <c r="P76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q76" s="13" t="n">
-        <v>0.02159</v>
+        <v>0.582728</v>
       </c>
       <c r="R76" s="12" t="n">
-        <v>29.29</v>
+        <v>76.55</v>
       </c>
       <c r="S76" s="12" t="n">
         <v>0</v>
@@ -31356,7 +31347,7 @@
         <v>73</v>
       </c>
       <c r="X76" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y76" s="12" t="n">
         <v>0</v>
@@ -31484,10 +31475,10 @@
     </row>
     <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="8" t="n">
-        <v>306537</v>
+        <v>306566</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>327</v>
+        <v>138</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="9"/>
@@ -31496,67 +31487,67 @@
         <v>334</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>83</v>
+        <v>140</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J77" s="9" t="s">
-        <v>78</v>
+        <v>335</v>
       </c>
       <c r="K77" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>18545.08</v>
+        <v>19173.58</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O77" s="12" t="n">
-        <v>18545.08</v>
+        <v>17759.1</v>
       </c>
       <c r="P77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q77" s="13" t="n">
-        <v>0.582728</v>
+        <v>10.05579</v>
       </c>
       <c r="R77" s="12" t="n">
-        <v>76.55</v>
+        <v>44.3</v>
       </c>
       <c r="S77" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T77" s="14" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="U77" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V77" s="12" t="n">
-        <v>0</v>
+        <v>71.68</v>
       </c>
       <c r="W77" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X77" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y77" s="12" t="n">
-        <v>0</v>
+        <v>1414.48</v>
       </c>
       <c r="Z77" s="12" t="n">
-        <v>0</v>
+        <v>17759.1</v>
       </c>
       <c r="AA77" s="12" t="n">
-        <v>0</v>
+        <v>710.36</v>
       </c>
       <c r="AB77" s="12" t="n">
         <v>0</v>
@@ -31625,7 +31616,7 @@
         <v>76</v>
       </c>
       <c r="AX77" s="10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AY77" s="14" t="s">
         <v>75</v>
@@ -31661,7 +31652,7 @@
         <v>78</v>
       </c>
       <c r="BJ77" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="BK77" s="9" t="s">
         <v>75</v>
@@ -31675,79 +31666,79 @@
     </row>
     <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="8" t="n">
-        <v>306566</v>
+        <v>306568</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>138</v>
+        <v>280</v>
       </c>
       <c r="C78" s="9"/>
       <c r="D78" s="9"/>
       <c r="E78" s="9"/>
       <c r="F78" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>140</v>
+        <v>282</v>
       </c>
       <c r="H78" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K78" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>19173.58</v>
+        <v>32775.54</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="O78" s="12" t="n">
-        <v>17759.1</v>
+        <v>31565.22</v>
       </c>
       <c r="P78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q78" s="13" t="n">
-        <v>10.05579</v>
+        <v>1.03129</v>
       </c>
       <c r="R78" s="12" t="n">
-        <v>44.3</v>
+        <v>102.16</v>
       </c>
       <c r="S78" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T78" s="14" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="U78" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V78" s="12" t="n">
-        <v>71.68</v>
+        <v>83.35</v>
       </c>
       <c r="W78" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X78" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y78" s="12" t="n">
-        <v>1414.48</v>
+        <v>1210.32</v>
       </c>
       <c r="Z78" s="12" t="n">
-        <v>17759.1</v>
+        <v>31565.22</v>
       </c>
       <c r="AA78" s="12" t="n">
-        <v>710.36</v>
+        <v>2209.57</v>
       </c>
       <c r="AB78" s="12" t="n">
         <v>0</v>
@@ -31852,7 +31843,7 @@
         <v>78</v>
       </c>
       <c r="BJ78" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="BK78" s="9" t="s">
         <v>75</v>
@@ -31866,79 +31857,79 @@
     </row>
     <row r="79" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="8" t="n">
-        <v>306568</v>
+        <v>306573</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>283</v>
+        <v>342</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="9"/>
       <c r="E79" s="9"/>
       <c r="F79" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>285</v>
+        <v>83</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="K79" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>32775.54</v>
+        <v>19668.42</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N79" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="O79" s="12" t="n">
-        <v>31565.22</v>
+        <v>18202.54</v>
       </c>
       <c r="P79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q79" s="13" t="n">
-        <v>1.03129</v>
+        <v>12.4342</v>
       </c>
       <c r="R79" s="12" t="n">
-        <v>102.16</v>
+        <v>1442.54</v>
       </c>
       <c r="S79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T79" s="14" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="U79" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V79" s="12" t="n">
-        <v>83.35</v>
+        <v>60</v>
       </c>
       <c r="W79" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X79" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y79" s="12" t="n">
-        <v>1210.32</v>
+        <v>1465.88</v>
       </c>
       <c r="Z79" s="12" t="n">
-        <v>31565.22</v>
+        <v>18202.54</v>
       </c>
       <c r="AA79" s="12" t="n">
-        <v>2209.57</v>
+        <v>1274.17</v>
       </c>
       <c r="AB79" s="12" t="n">
         <v>0</v>
@@ -32043,7 +32034,7 @@
         <v>78</v>
       </c>
       <c r="BJ79" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="BK79" s="9" t="s">
         <v>75</v>
@@ -32057,79 +32048,79 @@
     </row>
     <row r="80" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="8" t="n">
-        <v>306573</v>
+        <v>306574</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C80" s="9"/>
       <c r="D80" s="9"/>
       <c r="E80" s="9"/>
       <c r="F80" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H80" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J80" s="9" t="s">
-        <v>338</v>
+        <v>78</v>
       </c>
       <c r="K80" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>19668.42</v>
+        <v>1417.54</v>
       </c>
       <c r="M80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N80" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="O80" s="12" t="n">
-        <v>18202.54</v>
+        <v>1417.54</v>
       </c>
       <c r="P80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q80" s="13" t="n">
-        <v>12.4342</v>
+        <v>0.037428</v>
       </c>
       <c r="R80" s="12" t="n">
-        <v>1442.54</v>
+        <v>10.46</v>
       </c>
       <c r="S80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T80" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="U80" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V80" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W80" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X80" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y80" s="12" t="n">
-        <v>1465.88</v>
+        <v>0</v>
       </c>
       <c r="Z80" s="12" t="n">
-        <v>18202.54</v>
+        <v>1417.54</v>
       </c>
       <c r="AA80" s="12" t="n">
-        <v>1274.17</v>
+        <v>99.23</v>
       </c>
       <c r="AB80" s="12" t="n">
         <v>0</v>
@@ -32138,7 +32129,7 @@
         <v>0</v>
       </c>
       <c r="AD80" s="12" t="n">
-        <v>0</v>
+        <v>107.43</v>
       </c>
       <c r="AE80" s="12" t="n">
         <v>0</v>
@@ -32198,7 +32189,7 @@
         <v>76</v>
       </c>
       <c r="AX80" s="10" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AY80" s="14" t="s">
         <v>75</v>
@@ -32219,25 +32210,25 @@
         <v>75</v>
       </c>
       <c r="BE80" s="14" t="s">
-        <v>75</v>
+        <v>349</v>
       </c>
       <c r="BF80" s="9" t="s">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="BG80" s="9" t="s">
-        <v>78</v>
+        <v>263</v>
       </c>
       <c r="BH80" s="14" t="s">
-        <v>75</v>
+        <v>351</v>
       </c>
       <c r="BI80" s="9" t="s">
-        <v>78</v>
+        <v>295</v>
       </c>
       <c r="BJ80" s="9" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="BK80" s="9" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="BL80" s="9" t="s">
         <v>75</v>
@@ -32248,79 +32239,79 @@
     </row>
     <row r="81" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="8" t="n">
-        <v>306574</v>
+        <v>306576</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="9"/>
       <c r="E81" s="9"/>
       <c r="F81" s="9" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J81" s="9" t="s">
-        <v>78</v>
+        <v>296</v>
       </c>
       <c r="K81" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>1417.54</v>
+        <v>9523.2</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O81" s="12" t="n">
-        <v>1417.54</v>
+        <v>8677.15</v>
       </c>
       <c r="P81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q81" s="13" t="n">
-        <v>0.037428</v>
+        <v>0.775365</v>
       </c>
       <c r="R81" s="12" t="n">
-        <v>10.46</v>
+        <v>149.8</v>
       </c>
       <c r="S81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T81" s="14" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="U81" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V81" s="12" t="n">
-        <v>0</v>
+        <v>79.02</v>
       </c>
       <c r="W81" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X81" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y81" s="12" t="n">
-        <v>0</v>
+        <v>846.05</v>
       </c>
       <c r="Z81" s="12" t="n">
-        <v>1417.54</v>
+        <v>8677.15</v>
       </c>
       <c r="AA81" s="12" t="n">
-        <v>99.23</v>
+        <v>347.09</v>
       </c>
       <c r="AB81" s="12" t="n">
         <v>0</v>
@@ -32329,7 +32320,7 @@
         <v>0</v>
       </c>
       <c r="AD81" s="12" t="n">
-        <v>107.43</v>
+        <v>0</v>
       </c>
       <c r="AE81" s="12" t="n">
         <v>0</v>
@@ -32389,7 +32380,7 @@
         <v>76</v>
       </c>
       <c r="AX81" s="10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AY81" s="14" t="s">
         <v>75</v>
@@ -32410,25 +32401,25 @@
         <v>75</v>
       </c>
       <c r="BE81" s="14" t="s">
-        <v>352</v>
+        <v>75</v>
       </c>
       <c r="BF81" s="9" t="s">
-        <v>353</v>
+        <v>75</v>
       </c>
       <c r="BG81" s="9" t="s">
-        <v>266</v>
+        <v>78</v>
       </c>
       <c r="BH81" s="14" t="s">
-        <v>354</v>
+        <v>75</v>
       </c>
       <c r="BI81" s="9" t="s">
-        <v>298</v>
+        <v>78</v>
       </c>
       <c r="BJ81" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="BK81" s="9" t="s">
-        <v>356</v>
+        <v>75</v>
       </c>
       <c r="BL81" s="9" t="s">
         <v>75</v>
@@ -32439,79 +32430,79 @@
     </row>
     <row r="82" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="8" t="n">
-        <v>306576</v>
+        <v>306578</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C82" s="9"/>
       <c r="D82" s="9"/>
       <c r="E82" s="9"/>
       <c r="F82" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>83</v>
       </c>
       <c r="H82" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="J82" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K82" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>9523.2</v>
+        <v>5440.76</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N82" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O82" s="12" t="n">
-        <v>8677.15</v>
+        <v>5440.76</v>
       </c>
       <c r="P82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q82" s="13" t="n">
-        <v>0.775365</v>
+        <v>0.903754</v>
       </c>
       <c r="R82" s="12" t="n">
-        <v>149.8</v>
+        <v>1285.52</v>
       </c>
       <c r="S82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T82" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U82" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V82" s="12" t="n">
-        <v>79.02</v>
+        <v>55.99</v>
       </c>
       <c r="W82" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X82" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Y82" s="12" t="n">
-        <v>846.05</v>
+        <v>0</v>
       </c>
       <c r="Z82" s="12" t="n">
-        <v>8677.15</v>
+        <v>5440.76</v>
       </c>
       <c r="AA82" s="12" t="n">
-        <v>347.09</v>
+        <v>380.85</v>
       </c>
       <c r="AB82" s="12" t="n">
         <v>0</v>
@@ -32577,7 +32568,7 @@
         <v>74</v>
       </c>
       <c r="AW82" s="14" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="AX82" s="10" t="s">
         <v>77</v>
@@ -32616,7 +32607,7 @@
         <v>78</v>
       </c>
       <c r="BJ82" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="BK82" s="9" t="s">
         <v>75</v>
@@ -32629,518 +32620,396 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="8" t="n">
-        <v>306578</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="C83" s="9"/>
-      <c r="D83" s="9"/>
-      <c r="E83" s="9"/>
-      <c r="F83" s="9" t="s">
+      <c r="A83" s="4"/>
+    </row>
+    <row r="84" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="G83" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="J83" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="K83" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L83" s="12" t="n">
-        <v>5440.76</v>
-      </c>
-      <c r="M83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O83" s="12" t="n">
-        <v>5440.76</v>
-      </c>
-      <c r="P83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q83" s="13" t="n">
-        <v>0.903754</v>
-      </c>
-      <c r="R83" s="12" t="n">
-        <v>1285.52</v>
-      </c>
-      <c r="S83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T83" s="14" t="s">
-        <v>363</v>
-      </c>
-      <c r="U83" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V83" s="12" t="n">
-        <v>55.99</v>
-      </c>
-      <c r="W83" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X83" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="Y83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z83" s="12" t="n">
-        <v>5440.76</v>
-      </c>
-      <c r="AA83" s="12" t="n">
-        <v>380.85</v>
-      </c>
-      <c r="AB83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO83" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV83" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW83" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="AX83" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY83" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ83" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA83" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB83" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC83" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD83" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE83" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF83" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG83" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH83" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI83" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ83" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="BK83" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL83" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM83" s="16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="4"/>
+      <c r="B84" s="17"/>
+      <c r="C84" s="17"/>
+      <c r="D84" s="17"/>
+      <c r="E84" s="17"/>
+      <c r="F84" s="17"/>
+      <c r="G84" s="17"/>
+      <c r="H84" s="17"/>
+      <c r="I84" s="17"/>
+      <c r="J84" s="17"/>
+      <c r="K84" s="17"/>
+      <c r="L84" s="17"/>
+      <c r="M84" s="17"/>
+      <c r="N84" s="17"/>
+      <c r="O84" s="17"/>
+      <c r="P84" s="17"/>
+      <c r="Q84" s="17"/>
+      <c r="R84" s="17"/>
+      <c r="S84" s="17"/>
+      <c r="T84" s="17"/>
+      <c r="U84" s="17"/>
+      <c r="V84" s="17"/>
     </row>
     <row r="85" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="17" t="s">
+      <c r="A85" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F85" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G85" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H85" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I85" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="B85" s="17"/>
-      <c r="C85" s="17"/>
-      <c r="D85" s="17"/>
-      <c r="E85" s="17"/>
-      <c r="F85" s="17"/>
-      <c r="G85" s="17"/>
-      <c r="H85" s="17"/>
-      <c r="I85" s="17"/>
-      <c r="J85" s="17"/>
-      <c r="K85" s="17"/>
-      <c r="L85" s="17"/>
-      <c r="M85" s="17"/>
-      <c r="N85" s="17"/>
-      <c r="O85" s="17"/>
-      <c r="P85" s="17"/>
-      <c r="Q85" s="17"/>
-      <c r="R85" s="17"/>
-      <c r="S85" s="17"/>
-      <c r="T85" s="17"/>
-      <c r="U85" s="17"/>
-      <c r="V85" s="17"/>
+      <c r="J85" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K85" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L85" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M85" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="N85" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O85" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P85" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q85" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R85" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S85" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="T85" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="U85" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V85" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="86" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="B86" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C86" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D86" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="E86" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F86" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G86" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I86" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="J86" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K86" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L86" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M86" s="18" t="s">
+    <row r="86" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="19" t="n">
+        <v>78</v>
+      </c>
+      <c r="B86" s="19" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="C86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="19" t="n">
+        <v>18640.65</v>
+      </c>
+      <c r="F86" s="19" t="n">
+        <v>494561.46</v>
+      </c>
+      <c r="G86" s="19" t="n">
+        <v>32008.57</v>
+      </c>
+      <c r="H86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="19" t="n">
+        <v>107.43</v>
+      </c>
+      <c r="K86" s="19" t="n">
+        <v>545437.19</v>
+      </c>
+      <c r="L86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="20" t="n">
+        <v>39.214749</v>
+      </c>
+      <c r="S86" s="19" t="n">
+        <v>526856.64</v>
+      </c>
+      <c r="T86" s="19" t="n">
+        <v>545437.19</v>
+      </c>
+      <c r="U86" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F87" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G87" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H87" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I87" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J87" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K87" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="N86" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O86" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P86" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q86" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R86" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S86" s="18" t="s">
+      <c r="L87" s="18" t="s">
         <v>370</v>
       </c>
-      <c r="T86" s="18" t="s">
+      <c r="M87" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="U86" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V86" s="18" t="s">
-        <v>37</v>
-      </c>
     </row>
-    <row r="87" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="19" t="n">
-        <v>79</v>
-      </c>
-      <c r="B87" s="19" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="C87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="19" t="n">
-        <v>19104.07</v>
-      </c>
-      <c r="F87" s="19" t="n">
-        <v>498366.91</v>
-      </c>
-      <c r="G87" s="19" t="n">
-        <v>32160.79</v>
-      </c>
-      <c r="H87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" s="19" t="n">
-        <v>107.43</v>
-      </c>
-      <c r="K87" s="19" t="n">
-        <v>549706.06</v>
-      </c>
-      <c r="L87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" s="20" t="n">
-        <v>39.214749</v>
-      </c>
-      <c r="S87" s="19" t="n">
-        <v>530662.09</v>
-      </c>
-      <c r="T87" s="19" t="n">
-        <v>549706.06</v>
-      </c>
-      <c r="U87" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V87" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B88" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C88" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D88" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E88" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F88" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G88" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H88" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I88" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J88" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K88" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="L88" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="M88" s="18" t="s">
-        <v>374</v>
+    <row r="88" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="19" t="n">
+        <v>7266.21</v>
+      </c>
+      <c r="B88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="19" t="n">
+        <v>49.51</v>
+      </c>
+      <c r="E88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="19" t="n">
-        <v>7266.21</v>
-      </c>
-      <c r="B89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="19" t="n">
-        <v>49.54</v>
-      </c>
-      <c r="E89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L89" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A89" s="4"/>
     </row>
-    <row r="90" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="4"/>
+    <row r="90" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="B90" s="21"/>
+      <c r="C90" s="21"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="21"/>
+      <c r="F90" s="21"/>
+      <c r="G90" s="21"/>
+      <c r="H90" s="21"/>
+      <c r="I90" s="21"/>
+      <c r="J90" s="21"/>
+      <c r="K90" s="21"/>
+      <c r="L90" s="21"/>
+      <c r="M90" s="21"/>
+      <c r="N90" s="21"/>
+      <c r="O90" s="21"/>
+      <c r="P90" s="21"/>
+      <c r="Q90" s="21"/>
+      <c r="R90" s="21"/>
+      <c r="S90" s="21"/>
+      <c r="T90" s="21"/>
+      <c r="U90" s="21"/>
+      <c r="V90" s="21"/>
+      <c r="W90" s="21"/>
+      <c r="X90" s="21"/>
+      <c r="Y90" s="21"/>
+      <c r="Z90" s="21"/>
+      <c r="AA90" s="21"/>
+      <c r="AB90" s="21"/>
+      <c r="AC90" s="21"/>
+      <c r="AD90" s="21"/>
+      <c r="AE90" s="21"/>
+      <c r="AF90" s="21"/>
+      <c r="AG90" s="21"/>
+      <c r="AH90" s="21"/>
+      <c r="AI90" s="21"/>
+      <c r="AJ90" s="21"/>
+      <c r="AK90" s="21"/>
+      <c r="AL90" s="21"/>
+      <c r="AM90" s="21"/>
+      <c r="AN90" s="21"/>
+      <c r="AO90" s="21"/>
+      <c r="AP90" s="21"/>
+      <c r="AQ90" s="21"/>
+      <c r="AR90" s="21"/>
+      <c r="AS90" s="21"/>
+      <c r="AT90" s="21"/>
+      <c r="AU90" s="21"/>
+      <c r="AV90" s="21"/>
+      <c r="AW90" s="21"/>
+      <c r="AX90" s="21"/>
+      <c r="AY90" s="21"/>
+      <c r="AZ90" s="21"/>
+      <c r="BA90" s="21"/>
+      <c r="BB90" s="21"/>
+      <c r="BC90" s="21"/>
+      <c r="BD90" s="21"/>
+      <c r="BE90" s="21"/>
+      <c r="BF90" s="21"/>
+      <c r="BG90" s="21"/>
+      <c r="BH90" s="21"/>
+      <c r="BI90" s="21"/>
+      <c r="BJ90" s="21"/>
+      <c r="BK90" s="21"/>
+      <c r="BL90" s="21"/>
+      <c r="BM90" s="21"/>
     </row>
-    <row r="91" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="B91" s="21"/>
-      <c r="C91" s="21"/>
-      <c r="D91" s="21"/>
-      <c r="E91" s="21"/>
-      <c r="F91" s="21"/>
-      <c r="G91" s="21"/>
-      <c r="H91" s="21"/>
-      <c r="I91" s="21"/>
-      <c r="J91" s="21"/>
-      <c r="K91" s="21"/>
-      <c r="L91" s="21"/>
-      <c r="M91" s="21"/>
-      <c r="N91" s="21"/>
-      <c r="O91" s="21"/>
-      <c r="P91" s="21"/>
-      <c r="Q91" s="21"/>
-      <c r="R91" s="21"/>
-      <c r="S91" s="21"/>
-      <c r="T91" s="21"/>
-      <c r="U91" s="21"/>
-      <c r="V91" s="21"/>
-      <c r="W91" s="21"/>
-      <c r="X91" s="21"/>
-      <c r="Y91" s="21"/>
-      <c r="Z91" s="21"/>
-      <c r="AA91" s="21"/>
-      <c r="AB91" s="21"/>
-      <c r="AC91" s="21"/>
-      <c r="AD91" s="21"/>
-      <c r="AE91" s="21"/>
-      <c r="AF91" s="21"/>
-      <c r="AG91" s="21"/>
-      <c r="AH91" s="21"/>
-      <c r="AI91" s="21"/>
-      <c r="AJ91" s="21"/>
-      <c r="AK91" s="21"/>
-      <c r="AL91" s="21"/>
-      <c r="AM91" s="21"/>
-      <c r="AN91" s="21"/>
-      <c r="AO91" s="21"/>
-      <c r="AP91" s="21"/>
-      <c r="AQ91" s="21"/>
-      <c r="AR91" s="21"/>
-      <c r="AS91" s="21"/>
-      <c r="AT91" s="21"/>
-      <c r="AU91" s="21"/>
-      <c r="AV91" s="21"/>
-      <c r="AW91" s="21"/>
-      <c r="AX91" s="21"/>
-      <c r="AY91" s="21"/>
-      <c r="AZ91" s="21"/>
-      <c r="BA91" s="21"/>
-      <c r="BB91" s="21"/>
-      <c r="BC91" s="21"/>
-      <c r="BD91" s="21"/>
-      <c r="BE91" s="21"/>
-      <c r="BF91" s="21"/>
-      <c r="BG91" s="21"/>
-      <c r="BH91" s="21"/>
-      <c r="BI91" s="21"/>
-      <c r="BJ91" s="21"/>
-      <c r="BK91" s="21"/>
-      <c r="BL91" s="21"/>
-      <c r="BM91" s="21"/>
+    <row r="91" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A91" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B91" s="4"/>
+      <c r="C91" s="4"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="4"/>
+      <c r="I91" s="4"/>
+      <c r="J91" s="4"/>
+      <c r="K91" s="4"/>
+      <c r="L91" s="4"/>
+      <c r="M91" s="4"/>
+      <c r="N91" s="4"/>
+      <c r="O91" s="4"/>
+      <c r="P91" s="4"/>
+      <c r="Q91" s="4"/>
+      <c r="R91" s="4"/>
+      <c r="S91" s="4"/>
+      <c r="T91" s="4"/>
+      <c r="U91" s="4"/>
+      <c r="V91" s="4"/>
+      <c r="W91" s="4"/>
+      <c r="X91" s="4"/>
+      <c r="Y91" s="4"/>
+      <c r="Z91" s="4"/>
+      <c r="AA91" s="4"/>
+      <c r="AB91" s="4"/>
+      <c r="AC91" s="4"/>
+      <c r="AD91" s="4"/>
+      <c r="AE91" s="4"/>
+      <c r="AF91" s="4"/>
+      <c r="AG91" s="4"/>
+      <c r="AH91" s="4"/>
+      <c r="AI91" s="4"/>
+      <c r="AJ91" s="4"/>
+      <c r="AK91" s="4"/>
+      <c r="AL91" s="4"/>
+      <c r="AM91" s="4"/>
+      <c r="AN91" s="4"/>
+      <c r="AO91" s="4"/>
+      <c r="AP91" s="4"/>
+      <c r="AQ91" s="4"/>
+      <c r="AR91" s="4"/>
+      <c r="AS91" s="4"/>
+      <c r="AT91" s="4"/>
+      <c r="AU91" s="4"/>
+      <c r="AV91" s="4"/>
+      <c r="AW91" s="4"/>
+      <c r="AX91" s="4"/>
+      <c r="AY91" s="4"/>
+      <c r="AZ91" s="4"/>
+      <c r="BA91" s="4"/>
+      <c r="BB91" s="4"/>
+      <c r="BC91" s="4"/>
+      <c r="BD91" s="4"/>
+      <c r="BE91" s="4"/>
+      <c r="BF91" s="4"/>
+      <c r="BG91" s="4"/>
+      <c r="BH91" s="4"/>
+      <c r="BI91" s="4"/>
+      <c r="BJ91" s="4"/>
+      <c r="BK91" s="4"/>
+      <c r="BL91" s="4"/>
+      <c r="BM91" s="4"/>
     </row>
     <row r="92" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="4" t="s">
-        <v>75</v>
+        <v>373</v>
       </c>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -33209,7 +33078,7 @@
     </row>
     <row r="93" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -33278,7 +33147,7 @@
     </row>
     <row r="94" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -33347,7 +33216,7 @@
     </row>
     <row r="95" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="4" t="s">
-        <v>378</v>
+        <v>22</v>
       </c>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -33416,7 +33285,7 @@
     </row>
     <row r="96" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="4" t="s">
-        <v>22</v>
+        <v>376</v>
       </c>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -33485,7 +33354,7 @@
     </row>
     <row r="97" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -33554,7 +33423,7 @@
     </row>
     <row r="98" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -33623,7 +33492,7 @@
     </row>
     <row r="99" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -33692,7 +33561,7 @@
     </row>
     <row r="100" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -33759,77 +33628,8 @@
       <c r="BL100" s="4"/>
       <c r="BM100" s="4"/>
     </row>
-    <row r="101" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="B101" s="4"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="4"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="4"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="4"/>
-      <c r="L101" s="4"/>
-      <c r="M101" s="4"/>
-      <c r="N101" s="4"/>
-      <c r="O101" s="4"/>
-      <c r="P101" s="4"/>
-      <c r="Q101" s="4"/>
-      <c r="R101" s="4"/>
-      <c r="S101" s="4"/>
-      <c r="T101" s="4"/>
-      <c r="U101" s="4"/>
-      <c r="V101" s="4"/>
-      <c r="W101" s="4"/>
-      <c r="X101" s="4"/>
-      <c r="Y101" s="4"/>
-      <c r="Z101" s="4"/>
-      <c r="AA101" s="4"/>
-      <c r="AB101" s="4"/>
-      <c r="AC101" s="4"/>
-      <c r="AD101" s="4"/>
-      <c r="AE101" s="4"/>
-      <c r="AF101" s="4"/>
-      <c r="AG101" s="4"/>
-      <c r="AH101" s="4"/>
-      <c r="AI101" s="4"/>
-      <c r="AJ101" s="4"/>
-      <c r="AK101" s="4"/>
-      <c r="AL101" s="4"/>
-      <c r="AM101" s="4"/>
-      <c r="AN101" s="4"/>
-      <c r="AO101" s="4"/>
-      <c r="AP101" s="4"/>
-      <c r="AQ101" s="4"/>
-      <c r="AR101" s="4"/>
-      <c r="AS101" s="4"/>
-      <c r="AT101" s="4"/>
-      <c r="AU101" s="4"/>
-      <c r="AV101" s="4"/>
-      <c r="AW101" s="4"/>
-      <c r="AX101" s="4"/>
-      <c r="AY101" s="4"/>
-      <c r="AZ101" s="4"/>
-      <c r="BA101" s="4"/>
-      <c r="BB101" s="4"/>
-      <c r="BC101" s="4"/>
-      <c r="BD101" s="4"/>
-      <c r="BE101" s="4"/>
-      <c r="BF101" s="4"/>
-      <c r="BG101" s="4"/>
-      <c r="BH101" s="4"/>
-      <c r="BI101" s="4"/>
-      <c r="BJ101" s="4"/>
-      <c r="BK101" s="4"/>
-      <c r="BL101" s="4"/>
-      <c r="BM101" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="95">
+  <mergeCells count="94">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -33912,8 +33712,8 @@
     <mergeCell ref="B80:E80"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="B82:E82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="A85:V85"/>
+    <mergeCell ref="A84:V84"/>
+    <mergeCell ref="A90:BM90"/>
     <mergeCell ref="A91:BM91"/>
     <mergeCell ref="A92:BM92"/>
     <mergeCell ref="A93:BM93"/>
@@ -33924,7 +33724,6 @@
     <mergeCell ref="A98:BM98"/>
     <mergeCell ref="A99:BM99"/>
     <mergeCell ref="A100:BM100"/>
-    <mergeCell ref="A101:BM101"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3232" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3592" uniqueCount="415">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 05/05/2026 10:35:14</t>
+    <t xml:space="preserve">Emitido em: 06/05/2026 08:38:37</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -1106,6 +1106,108 @@
   </si>
   <si>
     <t xml:space="preserve">41260407855544000184550010002418301330223975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">633.546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.703,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006335461841845162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">633.523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.460,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006335231488772186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">633.512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.604,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006335121026499000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.300 - INTELBRAS S/A IND TELEC ELETR BRASILEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640,37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13260582901000001522550100001462471179714429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.201,85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13260582901000001522550100001462541960234960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">633.073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.496,09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006330731926027430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158,47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260487547907000153550050003168441492652194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.264,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260505890658000300550030000780241405676762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.806,37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260535635346000140550020001114151168111482</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17351,7 +17453,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM100"/>
+  <dimension ref="A1:BM109"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -32620,948 +32722,2046 @@
       </c>
     </row>
     <row r="83" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="4"/>
+      <c r="A83" s="8" t="n">
+        <v>306659</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="I83" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="J83" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="K83" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L83" s="12" t="n">
+        <v>3703.1</v>
+      </c>
+      <c r="M83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O83" s="12" t="n">
+        <v>3703.1</v>
+      </c>
+      <c r="P83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="13" t="n">
+        <v>0.040904</v>
+      </c>
+      <c r="R83" s="12" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="S83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T83" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="U83" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V83" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W83" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X83" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="12" t="n">
+        <v>3703.1</v>
+      </c>
+      <c r="AA83" s="12" t="n">
+        <v>259.22</v>
+      </c>
+      <c r="AB83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW83" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX83" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG83" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH83" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI83" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ83" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="BK83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL83" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM83" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="84" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="17"/>
-      <c r="G84" s="17"/>
-      <c r="H84" s="17"/>
-      <c r="I84" s="17"/>
-      <c r="J84" s="17"/>
-      <c r="K84" s="17"/>
-      <c r="L84" s="17"/>
-      <c r="M84" s="17"/>
-      <c r="N84" s="17"/>
-      <c r="O84" s="17"/>
-      <c r="P84" s="17"/>
-      <c r="Q84" s="17"/>
-      <c r="R84" s="17"/>
-      <c r="S84" s="17"/>
-      <c r="T84" s="17"/>
-      <c r="U84" s="17"/>
-      <c r="V84" s="17"/>
+    <row r="84" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="8" t="n">
+        <v>306661</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H84" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="I84" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="J84" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="K84" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>2460.96</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O84" s="12" t="n">
+        <v>2460.96</v>
+      </c>
+      <c r="P84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="13" t="n">
+        <v>0.009892</v>
+      </c>
+      <c r="R84" s="12" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="S84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="U84" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W84" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X84" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="12" t="n">
+        <v>2460.96</v>
+      </c>
+      <c r="AA84" s="12" t="n">
+        <v>172.27</v>
+      </c>
+      <c r="AB84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV84" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW84" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX84" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG84" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH84" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI84" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ84" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="BK84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL84" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM84" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="85" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="18" t="s">
+    <row r="85" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="8" t="n">
+        <v>306662</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C85" s="9"/>
+      <c r="D85" s="9"/>
+      <c r="E85" s="9"/>
+      <c r="F85" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H85" s="9" t="s">
         <v>363</v>
       </c>
-      <c r="B85" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C85" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D85" s="18" t="s">
+      <c r="I85" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="J85" s="9" t="s">
         <v>364</v>
       </c>
-      <c r="E85" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F85" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G85" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I85" s="18" t="s">
-        <v>365</v>
-      </c>
-      <c r="J85" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K85" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L85" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M85" s="18" t="s">
-        <v>366</v>
-      </c>
-      <c r="N85" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O85" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P85" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q85" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R85" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S85" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="T85" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="U85" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V85" s="18" t="s">
-        <v>37</v>
+      <c r="K85" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L85" s="12" t="n">
+        <v>1604</v>
+      </c>
+      <c r="M85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O85" s="12" t="n">
+        <v>1604</v>
+      </c>
+      <c r="P85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="13" t="n">
+        <v>0.009968</v>
+      </c>
+      <c r="R85" s="12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="S85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T85" s="14" t="s">
+        <v>371</v>
+      </c>
+      <c r="U85" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V85" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W85" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X85" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="12" t="n">
+        <v>1604</v>
+      </c>
+      <c r="AA85" s="12" t="n">
+        <v>112.28</v>
+      </c>
+      <c r="AB85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV85" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW85" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX85" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG85" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH85" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI85" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ85" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="BK85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL85" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM85" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="19" t="n">
+      <c r="A86" s="8" t="n">
+        <v>306668</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="C86" s="9"/>
+      <c r="D86" s="9"/>
+      <c r="E86" s="9"/>
+      <c r="F86" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="H86" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="I86" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="J86" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="K86" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>640.37</v>
+      </c>
+      <c r="M86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O86" s="12" t="n">
+        <v>640.37</v>
+      </c>
+      <c r="P86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T86" s="14" t="s">
+        <v>376</v>
+      </c>
+      <c r="U86" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V86" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="W86" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X86" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="12" t="n">
+        <v>640.37</v>
+      </c>
+      <c r="AA86" s="12" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="AB86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV86" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW86" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX86" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG86" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="B86" s="19" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="C86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="19" t="n">
-        <v>18640.65</v>
-      </c>
-      <c r="F86" s="19" t="n">
-        <v>494561.46</v>
-      </c>
-      <c r="G86" s="19" t="n">
-        <v>32008.57</v>
-      </c>
-      <c r="H86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="19" t="n">
-        <v>107.43</v>
-      </c>
-      <c r="K86" s="19" t="n">
-        <v>545437.19</v>
-      </c>
-      <c r="L86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R86" s="20" t="n">
-        <v>39.214749</v>
-      </c>
-      <c r="S86" s="19" t="n">
-        <v>526856.64</v>
-      </c>
-      <c r="T86" s="19" t="n">
-        <v>545437.19</v>
-      </c>
-      <c r="U86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V86" s="19" t="n">
-        <v>0</v>
+      <c r="BH86" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI86" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ86" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="BK86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL86" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM86" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B87" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C87" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D87" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E87" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F87" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G87" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H87" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I87" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J87" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K87" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="L87" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="M87" s="18" t="s">
-        <v>371</v>
+    <row r="87" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="8" t="n">
+        <v>306669</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="C87" s="9"/>
+      <c r="D87" s="9"/>
+      <c r="E87" s="9"/>
+      <c r="F87" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="I87" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="J87" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="K87" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L87" s="12" t="n">
+        <v>3201.85</v>
+      </c>
+      <c r="M87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O87" s="12" t="n">
+        <v>3201.85</v>
+      </c>
+      <c r="P87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="14" t="s">
+        <v>379</v>
+      </c>
+      <c r="U87" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V87" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="W87" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X87" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="12" t="n">
+        <v>3201.85</v>
+      </c>
+      <c r="AA87" s="12" t="n">
+        <v>384.22</v>
+      </c>
+      <c r="AB87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV87" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW87" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX87" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG87" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH87" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI87" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ87" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="BK87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL87" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM87" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="19" t="n">
-        <v>7266.21</v>
-      </c>
-      <c r="B88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="19" t="n">
-        <v>49.51</v>
-      </c>
-      <c r="E88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="19" t="n">
-        <v>0</v>
+      <c r="A88" s="8" t="n">
+        <v>306672</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C88" s="9"/>
+      <c r="D88" s="9"/>
+      <c r="E88" s="9"/>
+      <c r="F88" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="K88" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>4496.09</v>
+      </c>
+      <c r="M88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O88" s="12" t="n">
+        <v>4496.09</v>
+      </c>
+      <c r="P88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="13" t="n">
+        <v>0.015408</v>
+      </c>
+      <c r="R88" s="12" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="S88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="U88" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V88" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W88" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X88" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="12" t="n">
+        <v>4496.09</v>
+      </c>
+      <c r="AA88" s="12" t="n">
+        <v>314.73</v>
+      </c>
+      <c r="AB88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV88" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW88" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX88" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF88" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG88" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH88" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI88" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ88" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="BK88" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL88" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM88" s="16" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="4"/>
+      <c r="A89" s="8" t="n">
+        <v>306716</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="C89" s="9"/>
+      <c r="D89" s="9"/>
+      <c r="E89" s="9"/>
+      <c r="F89" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="I89" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="K89" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L89" s="12" t="n">
+        <v>158.47</v>
+      </c>
+      <c r="M89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O89" s="12" t="n">
+        <v>148.8</v>
+      </c>
+      <c r="P89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T89" s="14" t="s">
+        <v>387</v>
+      </c>
+      <c r="U89" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W89" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X89" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y89" s="12" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="Z89" s="12" t="n">
+        <v>158.47</v>
+      </c>
+      <c r="AA89" s="12" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="AB89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV89" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW89" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX89" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AY89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG89" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH89" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI89" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ89" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="BK89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL89" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM89" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
-    <row r="90" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="21" t="s">
-        <v>372</v>
-      </c>
-      <c r="B90" s="21"/>
-      <c r="C90" s="21"/>
-      <c r="D90" s="21"/>
-      <c r="E90" s="21"/>
-      <c r="F90" s="21"/>
-      <c r="G90" s="21"/>
-      <c r="H90" s="21"/>
-      <c r="I90" s="21"/>
-      <c r="J90" s="21"/>
-      <c r="K90" s="21"/>
-      <c r="L90" s="21"/>
-      <c r="M90" s="21"/>
-      <c r="N90" s="21"/>
-      <c r="O90" s="21"/>
-      <c r="P90" s="21"/>
-      <c r="Q90" s="21"/>
-      <c r="R90" s="21"/>
-      <c r="S90" s="21"/>
-      <c r="T90" s="21"/>
-      <c r="U90" s="21"/>
-      <c r="V90" s="21"/>
-      <c r="W90" s="21"/>
-      <c r="X90" s="21"/>
-      <c r="Y90" s="21"/>
-      <c r="Z90" s="21"/>
-      <c r="AA90" s="21"/>
-      <c r="AB90" s="21"/>
-      <c r="AC90" s="21"/>
-      <c r="AD90" s="21"/>
-      <c r="AE90" s="21"/>
-      <c r="AF90" s="21"/>
-      <c r="AG90" s="21"/>
-      <c r="AH90" s="21"/>
-      <c r="AI90" s="21"/>
-      <c r="AJ90" s="21"/>
-      <c r="AK90" s="21"/>
-      <c r="AL90" s="21"/>
-      <c r="AM90" s="21"/>
-      <c r="AN90" s="21"/>
-      <c r="AO90" s="21"/>
-      <c r="AP90" s="21"/>
-      <c r="AQ90" s="21"/>
-      <c r="AR90" s="21"/>
-      <c r="AS90" s="21"/>
-      <c r="AT90" s="21"/>
-      <c r="AU90" s="21"/>
-      <c r="AV90" s="21"/>
-      <c r="AW90" s="21"/>
-      <c r="AX90" s="21"/>
-      <c r="AY90" s="21"/>
-      <c r="AZ90" s="21"/>
-      <c r="BA90" s="21"/>
-      <c r="BB90" s="21"/>
-      <c r="BC90" s="21"/>
-      <c r="BD90" s="21"/>
-      <c r="BE90" s="21"/>
-      <c r="BF90" s="21"/>
-      <c r="BG90" s="21"/>
-      <c r="BH90" s="21"/>
-      <c r="BI90" s="21"/>
-      <c r="BJ90" s="21"/>
-      <c r="BK90" s="21"/>
-      <c r="BL90" s="21"/>
-      <c r="BM90" s="21"/>
+    <row r="90" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="8" t="n">
+        <v>306718</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C90" s="9"/>
+      <c r="D90" s="9"/>
+      <c r="E90" s="9"/>
+      <c r="F90" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H90" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="I90" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="J90" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="K90" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>13264.17</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O90" s="12" t="n">
+        <v>12355.2</v>
+      </c>
+      <c r="P90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="13" t="n">
+        <v>1.05026</v>
+      </c>
+      <c r="R90" s="12" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="S90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T90" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="U90" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V90" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="W90" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X90" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y90" s="12" t="n">
+        <v>908.97</v>
+      </c>
+      <c r="Z90" s="12" t="n">
+        <v>12355.2</v>
+      </c>
+      <c r="AA90" s="12" t="n">
+        <v>864.86</v>
+      </c>
+      <c r="AB90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV90" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW90" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX90" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG90" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH90" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI90" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ90" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="BK90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL90" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM90" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="4"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="4"/>
-      <c r="M91" s="4"/>
-      <c r="N91" s="4"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
-      <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
-      <c r="V91" s="4"/>
-      <c r="W91" s="4"/>
-      <c r="X91" s="4"/>
-      <c r="Y91" s="4"/>
-      <c r="Z91" s="4"/>
-      <c r="AA91" s="4"/>
-      <c r="AB91" s="4"/>
-      <c r="AC91" s="4"/>
-      <c r="AD91" s="4"/>
-      <c r="AE91" s="4"/>
-      <c r="AF91" s="4"/>
-      <c r="AG91" s="4"/>
-      <c r="AH91" s="4"/>
-      <c r="AI91" s="4"/>
-      <c r="AJ91" s="4"/>
-      <c r="AK91" s="4"/>
-      <c r="AL91" s="4"/>
-      <c r="AM91" s="4"/>
-      <c r="AN91" s="4"/>
-      <c r="AO91" s="4"/>
-      <c r="AP91" s="4"/>
-      <c r="AQ91" s="4"/>
-      <c r="AR91" s="4"/>
-      <c r="AS91" s="4"/>
-      <c r="AT91" s="4"/>
-      <c r="AU91" s="4"/>
-      <c r="AV91" s="4"/>
-      <c r="AW91" s="4"/>
-      <c r="AX91" s="4"/>
-      <c r="AY91" s="4"/>
-      <c r="AZ91" s="4"/>
-      <c r="BA91" s="4"/>
-      <c r="BB91" s="4"/>
-      <c r="BC91" s="4"/>
-      <c r="BD91" s="4"/>
-      <c r="BE91" s="4"/>
-      <c r="BF91" s="4"/>
-      <c r="BG91" s="4"/>
-      <c r="BH91" s="4"/>
-      <c r="BI91" s="4"/>
-      <c r="BJ91" s="4"/>
-      <c r="BK91" s="4"/>
-      <c r="BL91" s="4"/>
-      <c r="BM91" s="4"/>
+      <c r="A91" s="8" t="n">
+        <v>306754</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C91" s="9"/>
+      <c r="D91" s="9"/>
+      <c r="E91" s="9"/>
+      <c r="F91" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="I91" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="K91" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <v>7806.37</v>
+      </c>
+      <c r="M91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="O91" s="12" t="n">
+        <v>7108.5</v>
+      </c>
+      <c r="P91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="13" t="n">
+        <v>0.00259</v>
+      </c>
+      <c r="R91" s="12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="U91" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V91" s="12" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="W91" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X91" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="Y91" s="12" t="n">
+        <v>697.87</v>
+      </c>
+      <c r="Z91" s="12" t="n">
+        <v>7108.5</v>
+      </c>
+      <c r="AA91" s="12" t="n">
+        <v>284.34</v>
+      </c>
+      <c r="AB91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV91" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW91" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX91" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AY91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG91" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BH91" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI91" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="BJ91" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="BK91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL91" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM91" s="16" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="B92" s="4"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="4"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="4"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="4"/>
-      <c r="M92" s="4"/>
-      <c r="N92" s="4"/>
-      <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-      <c r="Q92" s="4"/>
-      <c r="R92" s="4"/>
-      <c r="S92" s="4"/>
-      <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
-      <c r="V92" s="4"/>
-      <c r="W92" s="4"/>
-      <c r="X92" s="4"/>
-      <c r="Y92" s="4"/>
-      <c r="Z92" s="4"/>
-      <c r="AA92" s="4"/>
-      <c r="AB92" s="4"/>
-      <c r="AC92" s="4"/>
-      <c r="AD92" s="4"/>
-      <c r="AE92" s="4"/>
-      <c r="AF92" s="4"/>
-      <c r="AG92" s="4"/>
-      <c r="AH92" s="4"/>
-      <c r="AI92" s="4"/>
-      <c r="AJ92" s="4"/>
-      <c r="AK92" s="4"/>
-      <c r="AL92" s="4"/>
-      <c r="AM92" s="4"/>
-      <c r="AN92" s="4"/>
-      <c r="AO92" s="4"/>
-      <c r="AP92" s="4"/>
-      <c r="AQ92" s="4"/>
-      <c r="AR92" s="4"/>
-      <c r="AS92" s="4"/>
-      <c r="AT92" s="4"/>
-      <c r="AU92" s="4"/>
-      <c r="AV92" s="4"/>
-      <c r="AW92" s="4"/>
-      <c r="AX92" s="4"/>
-      <c r="AY92" s="4"/>
-      <c r="AZ92" s="4"/>
-      <c r="BA92" s="4"/>
-      <c r="BB92" s="4"/>
-      <c r="BC92" s="4"/>
-      <c r="BD92" s="4"/>
-      <c r="BE92" s="4"/>
-      <c r="BF92" s="4"/>
-      <c r="BG92" s="4"/>
-      <c r="BH92" s="4"/>
-      <c r="BI92" s="4"/>
-      <c r="BJ92" s="4"/>
-      <c r="BK92" s="4"/>
-      <c r="BL92" s="4"/>
-      <c r="BM92" s="4"/>
+      <c r="A92" s="4"/>
     </row>
-    <row r="93" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B93" s="4"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="4"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="4"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="4"/>
-      <c r="M93" s="4"/>
-      <c r="N93" s="4"/>
-      <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-      <c r="Q93" s="4"/>
-      <c r="R93" s="4"/>
-      <c r="S93" s="4"/>
-      <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="4"/>
-      <c r="X93" s="4"/>
-      <c r="Y93" s="4"/>
-      <c r="Z93" s="4"/>
-      <c r="AA93" s="4"/>
-      <c r="AB93" s="4"/>
-      <c r="AC93" s="4"/>
-      <c r="AD93" s="4"/>
-      <c r="AE93" s="4"/>
-      <c r="AF93" s="4"/>
-      <c r="AG93" s="4"/>
-      <c r="AH93" s="4"/>
-      <c r="AI93" s="4"/>
-      <c r="AJ93" s="4"/>
-      <c r="AK93" s="4"/>
-      <c r="AL93" s="4"/>
-      <c r="AM93" s="4"/>
-      <c r="AN93" s="4"/>
-      <c r="AO93" s="4"/>
-      <c r="AP93" s="4"/>
-      <c r="AQ93" s="4"/>
-      <c r="AR93" s="4"/>
-      <c r="AS93" s="4"/>
-      <c r="AT93" s="4"/>
-      <c r="AU93" s="4"/>
-      <c r="AV93" s="4"/>
-      <c r="AW93" s="4"/>
-      <c r="AX93" s="4"/>
-      <c r="AY93" s="4"/>
-      <c r="AZ93" s="4"/>
-      <c r="BA93" s="4"/>
-      <c r="BB93" s="4"/>
-      <c r="BC93" s="4"/>
-      <c r="BD93" s="4"/>
-      <c r="BE93" s="4"/>
-      <c r="BF93" s="4"/>
-      <c r="BG93" s="4"/>
-      <c r="BH93" s="4"/>
-      <c r="BI93" s="4"/>
-      <c r="BJ93" s="4"/>
-      <c r="BK93" s="4"/>
-      <c r="BL93" s="4"/>
-      <c r="BM93" s="4"/>
+    <row r="93" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="B93" s="17"/>
+      <c r="C93" s="17"/>
+      <c r="D93" s="17"/>
+      <c r="E93" s="17"/>
+      <c r="F93" s="17"/>
+      <c r="G93" s="17"/>
+      <c r="H93" s="17"/>
+      <c r="I93" s="17"/>
+      <c r="J93" s="17"/>
+      <c r="K93" s="17"/>
+      <c r="L93" s="17"/>
+      <c r="M93" s="17"/>
+      <c r="N93" s="17"/>
+      <c r="O93" s="17"/>
+      <c r="P93" s="17"/>
+      <c r="Q93" s="17"/>
+      <c r="R93" s="17"/>
+      <c r="S93" s="17"/>
+      <c r="T93" s="17"/>
+      <c r="U93" s="17"/>
+      <c r="V93" s="17"/>
     </row>
-    <row r="94" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B94" s="4"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="4"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="4"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="4"/>
-      <c r="M94" s="4"/>
-      <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-      <c r="Q94" s="4"/>
-      <c r="R94" s="4"/>
-      <c r="S94" s="4"/>
-      <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
-      <c r="V94" s="4"/>
-      <c r="W94" s="4"/>
-      <c r="X94" s="4"/>
-      <c r="Y94" s="4"/>
-      <c r="Z94" s="4"/>
-      <c r="AA94" s="4"/>
-      <c r="AB94" s="4"/>
-      <c r="AC94" s="4"/>
-      <c r="AD94" s="4"/>
-      <c r="AE94" s="4"/>
-      <c r="AF94" s="4"/>
-      <c r="AG94" s="4"/>
-      <c r="AH94" s="4"/>
-      <c r="AI94" s="4"/>
-      <c r="AJ94" s="4"/>
-      <c r="AK94" s="4"/>
-      <c r="AL94" s="4"/>
-      <c r="AM94" s="4"/>
-      <c r="AN94" s="4"/>
-      <c r="AO94" s="4"/>
-      <c r="AP94" s="4"/>
-      <c r="AQ94" s="4"/>
-      <c r="AR94" s="4"/>
-      <c r="AS94" s="4"/>
-      <c r="AT94" s="4"/>
-      <c r="AU94" s="4"/>
-      <c r="AV94" s="4"/>
-      <c r="AW94" s="4"/>
-      <c r="AX94" s="4"/>
-      <c r="AY94" s="4"/>
-      <c r="AZ94" s="4"/>
-      <c r="BA94" s="4"/>
-      <c r="BB94" s="4"/>
-      <c r="BC94" s="4"/>
-      <c r="BD94" s="4"/>
-      <c r="BE94" s="4"/>
-      <c r="BF94" s="4"/>
-      <c r="BG94" s="4"/>
-      <c r="BH94" s="4"/>
-      <c r="BI94" s="4"/>
-      <c r="BJ94" s="4"/>
-      <c r="BK94" s="4"/>
-      <c r="BL94" s="4"/>
-      <c r="BM94" s="4"/>
+    <row r="94" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="E94" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F94" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H94" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I94" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="J94" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K94" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L94" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M94" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="N94" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O94" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P94" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q94" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R94" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S94" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="T94" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="U94" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V94" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="95" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B95" s="4"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="4"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="4"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4"/>
-      <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-      <c r="Q95" s="4"/>
-      <c r="R95" s="4"/>
-      <c r="S95" s="4"/>
-      <c r="T95" s="4"/>
-      <c r="U95" s="4"/>
-      <c r="V95" s="4"/>
-      <c r="W95" s="4"/>
-      <c r="X95" s="4"/>
-      <c r="Y95" s="4"/>
-      <c r="Z95" s="4"/>
-      <c r="AA95" s="4"/>
-      <c r="AB95" s="4"/>
-      <c r="AC95" s="4"/>
-      <c r="AD95" s="4"/>
-      <c r="AE95" s="4"/>
-      <c r="AF95" s="4"/>
-      <c r="AG95" s="4"/>
-      <c r="AH95" s="4"/>
-      <c r="AI95" s="4"/>
-      <c r="AJ95" s="4"/>
-      <c r="AK95" s="4"/>
-      <c r="AL95" s="4"/>
-      <c r="AM95" s="4"/>
-      <c r="AN95" s="4"/>
-      <c r="AO95" s="4"/>
-      <c r="AP95" s="4"/>
-      <c r="AQ95" s="4"/>
-      <c r="AR95" s="4"/>
-      <c r="AS95" s="4"/>
-      <c r="AT95" s="4"/>
-      <c r="AU95" s="4"/>
-      <c r="AV95" s="4"/>
-      <c r="AW95" s="4"/>
-      <c r="AX95" s="4"/>
-      <c r="AY95" s="4"/>
-      <c r="AZ95" s="4"/>
-      <c r="BA95" s="4"/>
-      <c r="BB95" s="4"/>
-      <c r="BC95" s="4"/>
-      <c r="BD95" s="4"/>
-      <c r="BE95" s="4"/>
-      <c r="BF95" s="4"/>
-      <c r="BG95" s="4"/>
-      <c r="BH95" s="4"/>
-      <c r="BI95" s="4"/>
-      <c r="BJ95" s="4"/>
-      <c r="BK95" s="4"/>
-      <c r="BL95" s="4"/>
-      <c r="BM95" s="4"/>
+      <c r="A95" s="19" t="n">
+        <v>87</v>
+      </c>
+      <c r="B95" s="19" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="C95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="19" t="n">
+        <v>20257.16</v>
+      </c>
+      <c r="F95" s="19" t="n">
+        <v>530290</v>
+      </c>
+      <c r="G95" s="19" t="n">
+        <v>34488.42</v>
+      </c>
+      <c r="H95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="19" t="n">
+        <v>107.43</v>
+      </c>
+      <c r="K95" s="19" t="n">
+        <v>582772.57</v>
+      </c>
+      <c r="L95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="20" t="n">
+        <v>40.343771</v>
+      </c>
+      <c r="S95" s="19" t="n">
+        <v>562575.51</v>
+      </c>
+      <c r="T95" s="19" t="n">
+        <v>582772.57</v>
+      </c>
+      <c r="U95" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V95" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="96" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="B96" s="4"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="4"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="4"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4"/>
-      <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-      <c r="Q96" s="4"/>
-      <c r="R96" s="4"/>
-      <c r="S96" s="4"/>
-      <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
-      <c r="V96" s="4"/>
-      <c r="W96" s="4"/>
-      <c r="X96" s="4"/>
-      <c r="Y96" s="4"/>
-      <c r="Z96" s="4"/>
-      <c r="AA96" s="4"/>
-      <c r="AB96" s="4"/>
-      <c r="AC96" s="4"/>
-      <c r="AD96" s="4"/>
-      <c r="AE96" s="4"/>
-      <c r="AF96" s="4"/>
-      <c r="AG96" s="4"/>
-      <c r="AH96" s="4"/>
-      <c r="AI96" s="4"/>
-      <c r="AJ96" s="4"/>
-      <c r="AK96" s="4"/>
-      <c r="AL96" s="4"/>
-      <c r="AM96" s="4"/>
-      <c r="AN96" s="4"/>
-      <c r="AO96" s="4"/>
-      <c r="AP96" s="4"/>
-      <c r="AQ96" s="4"/>
-      <c r="AR96" s="4"/>
-      <c r="AS96" s="4"/>
-      <c r="AT96" s="4"/>
-      <c r="AU96" s="4"/>
-      <c r="AV96" s="4"/>
-      <c r="AW96" s="4"/>
-      <c r="AX96" s="4"/>
-      <c r="AY96" s="4"/>
-      <c r="AZ96" s="4"/>
-      <c r="BA96" s="4"/>
-      <c r="BB96" s="4"/>
-      <c r="BC96" s="4"/>
-      <c r="BD96" s="4"/>
-      <c r="BE96" s="4"/>
-      <c r="BF96" s="4"/>
-      <c r="BG96" s="4"/>
-      <c r="BH96" s="4"/>
-      <c r="BI96" s="4"/>
-      <c r="BJ96" s="4"/>
-      <c r="BK96" s="4"/>
-      <c r="BL96" s="4"/>
-      <c r="BM96" s="4"/>
+    <row r="96" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A96" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D96" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G96" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H96" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I96" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J96" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K96" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="L96" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="M96" s="18" t="s">
+        <v>405</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="B97" s="4"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="4"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="4"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="4"/>
-      <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
-      <c r="N97" s="4"/>
-      <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
-      <c r="R97" s="4"/>
-      <c r="S97" s="4"/>
-      <c r="T97" s="4"/>
-      <c r="U97" s="4"/>
-      <c r="V97" s="4"/>
-      <c r="W97" s="4"/>
-      <c r="X97" s="4"/>
-      <c r="Y97" s="4"/>
-      <c r="Z97" s="4"/>
-      <c r="AA97" s="4"/>
-      <c r="AB97" s="4"/>
-      <c r="AC97" s="4"/>
-      <c r="AD97" s="4"/>
-      <c r="AE97" s="4"/>
-      <c r="AF97" s="4"/>
-      <c r="AG97" s="4"/>
-      <c r="AH97" s="4"/>
-      <c r="AI97" s="4"/>
-      <c r="AJ97" s="4"/>
-      <c r="AK97" s="4"/>
-      <c r="AL97" s="4"/>
-      <c r="AM97" s="4"/>
-      <c r="AN97" s="4"/>
-      <c r="AO97" s="4"/>
-      <c r="AP97" s="4"/>
-      <c r="AQ97" s="4"/>
-      <c r="AR97" s="4"/>
-      <c r="AS97" s="4"/>
-      <c r="AT97" s="4"/>
-      <c r="AU97" s="4"/>
-      <c r="AV97" s="4"/>
-      <c r="AW97" s="4"/>
-      <c r="AX97" s="4"/>
-      <c r="AY97" s="4"/>
-      <c r="AZ97" s="4"/>
-      <c r="BA97" s="4"/>
-      <c r="BB97" s="4"/>
-      <c r="BC97" s="4"/>
-      <c r="BD97" s="4"/>
-      <c r="BE97" s="4"/>
-      <c r="BF97" s="4"/>
-      <c r="BG97" s="4"/>
-      <c r="BH97" s="4"/>
-      <c r="BI97" s="4"/>
-      <c r="BJ97" s="4"/>
-      <c r="BK97" s="4"/>
-      <c r="BL97" s="4"/>
-      <c r="BM97" s="4"/>
+      <c r="A97" s="19" t="n">
+        <v>7378.94</v>
+      </c>
+      <c r="B97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="19" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="E97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="B98" s="4"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="4"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="4"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="4"/>
-      <c r="M98" s="4"/>
-      <c r="N98" s="4"/>
-      <c r="O98" s="4"/>
-      <c r="P98" s="4"/>
-      <c r="Q98" s="4"/>
-      <c r="R98" s="4"/>
-      <c r="S98" s="4"/>
-      <c r="T98" s="4"/>
-      <c r="U98" s="4"/>
-      <c r="V98" s="4"/>
-      <c r="W98" s="4"/>
-      <c r="X98" s="4"/>
-      <c r="Y98" s="4"/>
-      <c r="Z98" s="4"/>
-      <c r="AA98" s="4"/>
-      <c r="AB98" s="4"/>
-      <c r="AC98" s="4"/>
-      <c r="AD98" s="4"/>
-      <c r="AE98" s="4"/>
-      <c r="AF98" s="4"/>
-      <c r="AG98" s="4"/>
-      <c r="AH98" s="4"/>
-      <c r="AI98" s="4"/>
-      <c r="AJ98" s="4"/>
-      <c r="AK98" s="4"/>
-      <c r="AL98" s="4"/>
-      <c r="AM98" s="4"/>
-      <c r="AN98" s="4"/>
-      <c r="AO98" s="4"/>
-      <c r="AP98" s="4"/>
-      <c r="AQ98" s="4"/>
-      <c r="AR98" s="4"/>
-      <c r="AS98" s="4"/>
-      <c r="AT98" s="4"/>
-      <c r="AU98" s="4"/>
-      <c r="AV98" s="4"/>
-      <c r="AW98" s="4"/>
-      <c r="AX98" s="4"/>
-      <c r="AY98" s="4"/>
-      <c r="AZ98" s="4"/>
-      <c r="BA98" s="4"/>
-      <c r="BB98" s="4"/>
-      <c r="BC98" s="4"/>
-      <c r="BD98" s="4"/>
-      <c r="BE98" s="4"/>
-      <c r="BF98" s="4"/>
-      <c r="BG98" s="4"/>
-      <c r="BH98" s="4"/>
-      <c r="BI98" s="4"/>
-      <c r="BJ98" s="4"/>
-      <c r="BK98" s="4"/>
-      <c r="BL98" s="4"/>
-      <c r="BM98" s="4"/>
+      <c r="A98" s="4"/>
     </row>
-    <row r="99" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="B99" s="4"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="4"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="4"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4"/>
-      <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
-      <c r="Q99" s="4"/>
-      <c r="R99" s="4"/>
-      <c r="S99" s="4"/>
-      <c r="T99" s="4"/>
-      <c r="U99" s="4"/>
-      <c r="V99" s="4"/>
-      <c r="W99" s="4"/>
-      <c r="X99" s="4"/>
-      <c r="Y99" s="4"/>
-      <c r="Z99" s="4"/>
-      <c r="AA99" s="4"/>
-      <c r="AB99" s="4"/>
-      <c r="AC99" s="4"/>
-      <c r="AD99" s="4"/>
-      <c r="AE99" s="4"/>
-      <c r="AF99" s="4"/>
-      <c r="AG99" s="4"/>
-      <c r="AH99" s="4"/>
-      <c r="AI99" s="4"/>
-      <c r="AJ99" s="4"/>
-      <c r="AK99" s="4"/>
-      <c r="AL99" s="4"/>
-      <c r="AM99" s="4"/>
-      <c r="AN99" s="4"/>
-      <c r="AO99" s="4"/>
-      <c r="AP99" s="4"/>
-      <c r="AQ99" s="4"/>
-      <c r="AR99" s="4"/>
-      <c r="AS99" s="4"/>
-      <c r="AT99" s="4"/>
-      <c r="AU99" s="4"/>
-      <c r="AV99" s="4"/>
-      <c r="AW99" s="4"/>
-      <c r="AX99" s="4"/>
-      <c r="AY99" s="4"/>
-      <c r="AZ99" s="4"/>
-      <c r="BA99" s="4"/>
-      <c r="BB99" s="4"/>
-      <c r="BC99" s="4"/>
-      <c r="BD99" s="4"/>
-      <c r="BE99" s="4"/>
-      <c r="BF99" s="4"/>
-      <c r="BG99" s="4"/>
-      <c r="BH99" s="4"/>
-      <c r="BI99" s="4"/>
-      <c r="BJ99" s="4"/>
-      <c r="BK99" s="4"/>
-      <c r="BL99" s="4"/>
-      <c r="BM99" s="4"/>
+    <row r="99" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="B99" s="21"/>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="21"/>
+      <c r="G99" s="21"/>
+      <c r="H99" s="21"/>
+      <c r="I99" s="21"/>
+      <c r="J99" s="21"/>
+      <c r="K99" s="21"/>
+      <c r="L99" s="21"/>
+      <c r="M99" s="21"/>
+      <c r="N99" s="21"/>
+      <c r="O99" s="21"/>
+      <c r="P99" s="21"/>
+      <c r="Q99" s="21"/>
+      <c r="R99" s="21"/>
+      <c r="S99" s="21"/>
+      <c r="T99" s="21"/>
+      <c r="U99" s="21"/>
+      <c r="V99" s="21"/>
+      <c r="W99" s="21"/>
+      <c r="X99" s="21"/>
+      <c r="Y99" s="21"/>
+      <c r="Z99" s="21"/>
+      <c r="AA99" s="21"/>
+      <c r="AB99" s="21"/>
+      <c r="AC99" s="21"/>
+      <c r="AD99" s="21"/>
+      <c r="AE99" s="21"/>
+      <c r="AF99" s="21"/>
+      <c r="AG99" s="21"/>
+      <c r="AH99" s="21"/>
+      <c r="AI99" s="21"/>
+      <c r="AJ99" s="21"/>
+      <c r="AK99" s="21"/>
+      <c r="AL99" s="21"/>
+      <c r="AM99" s="21"/>
+      <c r="AN99" s="21"/>
+      <c r="AO99" s="21"/>
+      <c r="AP99" s="21"/>
+      <c r="AQ99" s="21"/>
+      <c r="AR99" s="21"/>
+      <c r="AS99" s="21"/>
+      <c r="AT99" s="21"/>
+      <c r="AU99" s="21"/>
+      <c r="AV99" s="21"/>
+      <c r="AW99" s="21"/>
+      <c r="AX99" s="21"/>
+      <c r="AY99" s="21"/>
+      <c r="AZ99" s="21"/>
+      <c r="BA99" s="21"/>
+      <c r="BB99" s="21"/>
+      <c r="BC99" s="21"/>
+      <c r="BD99" s="21"/>
+      <c r="BE99" s="21"/>
+      <c r="BF99" s="21"/>
+      <c r="BG99" s="21"/>
+      <c r="BH99" s="21"/>
+      <c r="BI99" s="21"/>
+      <c r="BJ99" s="21"/>
+      <c r="BK99" s="21"/>
+      <c r="BL99" s="21"/>
+      <c r="BM99" s="21"/>
     </row>
     <row r="100" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="4" t="s">
-        <v>380</v>
+        <v>75</v>
       </c>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -33628,8 +34828,629 @@
       <c r="BL100" s="4"/>
       <c r="BM100" s="4"/>
     </row>
+    <row r="101" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B101" s="4"/>
+      <c r="C101" s="4"/>
+      <c r="D101" s="4"/>
+      <c r="E101" s="4"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="4"/>
+      <c r="H101" s="4"/>
+      <c r="I101" s="4"/>
+      <c r="J101" s="4"/>
+      <c r="K101" s="4"/>
+      <c r="L101" s="4"/>
+      <c r="M101" s="4"/>
+      <c r="N101" s="4"/>
+      <c r="O101" s="4"/>
+      <c r="P101" s="4"/>
+      <c r="Q101" s="4"/>
+      <c r="R101" s="4"/>
+      <c r="S101" s="4"/>
+      <c r="T101" s="4"/>
+      <c r="U101" s="4"/>
+      <c r="V101" s="4"/>
+      <c r="W101" s="4"/>
+      <c r="X101" s="4"/>
+      <c r="Y101" s="4"/>
+      <c r="Z101" s="4"/>
+      <c r="AA101" s="4"/>
+      <c r="AB101" s="4"/>
+      <c r="AC101" s="4"/>
+      <c r="AD101" s="4"/>
+      <c r="AE101" s="4"/>
+      <c r="AF101" s="4"/>
+      <c r="AG101" s="4"/>
+      <c r="AH101" s="4"/>
+      <c r="AI101" s="4"/>
+      <c r="AJ101" s="4"/>
+      <c r="AK101" s="4"/>
+      <c r="AL101" s="4"/>
+      <c r="AM101" s="4"/>
+      <c r="AN101" s="4"/>
+      <c r="AO101" s="4"/>
+      <c r="AP101" s="4"/>
+      <c r="AQ101" s="4"/>
+      <c r="AR101" s="4"/>
+      <c r="AS101" s="4"/>
+      <c r="AT101" s="4"/>
+      <c r="AU101" s="4"/>
+      <c r="AV101" s="4"/>
+      <c r="AW101" s="4"/>
+      <c r="AX101" s="4"/>
+      <c r="AY101" s="4"/>
+      <c r="AZ101" s="4"/>
+      <c r="BA101" s="4"/>
+      <c r="BB101" s="4"/>
+      <c r="BC101" s="4"/>
+      <c r="BD101" s="4"/>
+      <c r="BE101" s="4"/>
+      <c r="BF101" s="4"/>
+      <c r="BG101" s="4"/>
+      <c r="BH101" s="4"/>
+      <c r="BI101" s="4"/>
+      <c r="BJ101" s="4"/>
+      <c r="BK101" s="4"/>
+      <c r="BL101" s="4"/>
+      <c r="BM101" s="4"/>
+    </row>
+    <row r="102" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B102" s="4"/>
+      <c r="C102" s="4"/>
+      <c r="D102" s="4"/>
+      <c r="E102" s="4"/>
+      <c r="F102" s="4"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="4"/>
+      <c r="I102" s="4"/>
+      <c r="J102" s="4"/>
+      <c r="K102" s="4"/>
+      <c r="L102" s="4"/>
+      <c r="M102" s="4"/>
+      <c r="N102" s="4"/>
+      <c r="O102" s="4"/>
+      <c r="P102" s="4"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4"/>
+      <c r="S102" s="4"/>
+      <c r="T102" s="4"/>
+      <c r="U102" s="4"/>
+      <c r="V102" s="4"/>
+      <c r="W102" s="4"/>
+      <c r="X102" s="4"/>
+      <c r="Y102" s="4"/>
+      <c r="Z102" s="4"/>
+      <c r="AA102" s="4"/>
+      <c r="AB102" s="4"/>
+      <c r="AC102" s="4"/>
+      <c r="AD102" s="4"/>
+      <c r="AE102" s="4"/>
+      <c r="AF102" s="4"/>
+      <c r="AG102" s="4"/>
+      <c r="AH102" s="4"/>
+      <c r="AI102" s="4"/>
+      <c r="AJ102" s="4"/>
+      <c r="AK102" s="4"/>
+      <c r="AL102" s="4"/>
+      <c r="AM102" s="4"/>
+      <c r="AN102" s="4"/>
+      <c r="AO102" s="4"/>
+      <c r="AP102" s="4"/>
+      <c r="AQ102" s="4"/>
+      <c r="AR102" s="4"/>
+      <c r="AS102" s="4"/>
+      <c r="AT102" s="4"/>
+      <c r="AU102" s="4"/>
+      <c r="AV102" s="4"/>
+      <c r="AW102" s="4"/>
+      <c r="AX102" s="4"/>
+      <c r="AY102" s="4"/>
+      <c r="AZ102" s="4"/>
+      <c r="BA102" s="4"/>
+      <c r="BB102" s="4"/>
+      <c r="BC102" s="4"/>
+      <c r="BD102" s="4"/>
+      <c r="BE102" s="4"/>
+      <c r="BF102" s="4"/>
+      <c r="BG102" s="4"/>
+      <c r="BH102" s="4"/>
+      <c r="BI102" s="4"/>
+      <c r="BJ102" s="4"/>
+      <c r="BK102" s="4"/>
+      <c r="BL102" s="4"/>
+      <c r="BM102" s="4"/>
+    </row>
+    <row r="103" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B103" s="4"/>
+      <c r="C103" s="4"/>
+      <c r="D103" s="4"/>
+      <c r="E103" s="4"/>
+      <c r="F103" s="4"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="4"/>
+      <c r="I103" s="4"/>
+      <c r="J103" s="4"/>
+      <c r="K103" s="4"/>
+      <c r="L103" s="4"/>
+      <c r="M103" s="4"/>
+      <c r="N103" s="4"/>
+      <c r="O103" s="4"/>
+      <c r="P103" s="4"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="4"/>
+      <c r="S103" s="4"/>
+      <c r="T103" s="4"/>
+      <c r="U103" s="4"/>
+      <c r="V103" s="4"/>
+      <c r="W103" s="4"/>
+      <c r="X103" s="4"/>
+      <c r="Y103" s="4"/>
+      <c r="Z103" s="4"/>
+      <c r="AA103" s="4"/>
+      <c r="AB103" s="4"/>
+      <c r="AC103" s="4"/>
+      <c r="AD103" s="4"/>
+      <c r="AE103" s="4"/>
+      <c r="AF103" s="4"/>
+      <c r="AG103" s="4"/>
+      <c r="AH103" s="4"/>
+      <c r="AI103" s="4"/>
+      <c r="AJ103" s="4"/>
+      <c r="AK103" s="4"/>
+      <c r="AL103" s="4"/>
+      <c r="AM103" s="4"/>
+      <c r="AN103" s="4"/>
+      <c r="AO103" s="4"/>
+      <c r="AP103" s="4"/>
+      <c r="AQ103" s="4"/>
+      <c r="AR103" s="4"/>
+      <c r="AS103" s="4"/>
+      <c r="AT103" s="4"/>
+      <c r="AU103" s="4"/>
+      <c r="AV103" s="4"/>
+      <c r="AW103" s="4"/>
+      <c r="AX103" s="4"/>
+      <c r="AY103" s="4"/>
+      <c r="AZ103" s="4"/>
+      <c r="BA103" s="4"/>
+      <c r="BB103" s="4"/>
+      <c r="BC103" s="4"/>
+      <c r="BD103" s="4"/>
+      <c r="BE103" s="4"/>
+      <c r="BF103" s="4"/>
+      <c r="BG103" s="4"/>
+      <c r="BH103" s="4"/>
+      <c r="BI103" s="4"/>
+      <c r="BJ103" s="4"/>
+      <c r="BK103" s="4"/>
+      <c r="BL103" s="4"/>
+      <c r="BM103" s="4"/>
+    </row>
+    <row r="104" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A104" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B104" s="4"/>
+      <c r="C104" s="4"/>
+      <c r="D104" s="4"/>
+      <c r="E104" s="4"/>
+      <c r="F104" s="4"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="4"/>
+      <c r="I104" s="4"/>
+      <c r="J104" s="4"/>
+      <c r="K104" s="4"/>
+      <c r="L104" s="4"/>
+      <c r="M104" s="4"/>
+      <c r="N104" s="4"/>
+      <c r="O104" s="4"/>
+      <c r="P104" s="4"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="4"/>
+      <c r="S104" s="4"/>
+      <c r="T104" s="4"/>
+      <c r="U104" s="4"/>
+      <c r="V104" s="4"/>
+      <c r="W104" s="4"/>
+      <c r="X104" s="4"/>
+      <c r="Y104" s="4"/>
+      <c r="Z104" s="4"/>
+      <c r="AA104" s="4"/>
+      <c r="AB104" s="4"/>
+      <c r="AC104" s="4"/>
+      <c r="AD104" s="4"/>
+      <c r="AE104" s="4"/>
+      <c r="AF104" s="4"/>
+      <c r="AG104" s="4"/>
+      <c r="AH104" s="4"/>
+      <c r="AI104" s="4"/>
+      <c r="AJ104" s="4"/>
+      <c r="AK104" s="4"/>
+      <c r="AL104" s="4"/>
+      <c r="AM104" s="4"/>
+      <c r="AN104" s="4"/>
+      <c r="AO104" s="4"/>
+      <c r="AP104" s="4"/>
+      <c r="AQ104" s="4"/>
+      <c r="AR104" s="4"/>
+      <c r="AS104" s="4"/>
+      <c r="AT104" s="4"/>
+      <c r="AU104" s="4"/>
+      <c r="AV104" s="4"/>
+      <c r="AW104" s="4"/>
+      <c r="AX104" s="4"/>
+      <c r="AY104" s="4"/>
+      <c r="AZ104" s="4"/>
+      <c r="BA104" s="4"/>
+      <c r="BB104" s="4"/>
+      <c r="BC104" s="4"/>
+      <c r="BD104" s="4"/>
+      <c r="BE104" s="4"/>
+      <c r="BF104" s="4"/>
+      <c r="BG104" s="4"/>
+      <c r="BH104" s="4"/>
+      <c r="BI104" s="4"/>
+      <c r="BJ104" s="4"/>
+      <c r="BK104" s="4"/>
+      <c r="BL104" s="4"/>
+      <c r="BM104" s="4"/>
+    </row>
+    <row r="105" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B105" s="4"/>
+      <c r="C105" s="4"/>
+      <c r="D105" s="4"/>
+      <c r="E105" s="4"/>
+      <c r="F105" s="4"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="4"/>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4"/>
+      <c r="L105" s="4"/>
+      <c r="M105" s="4"/>
+      <c r="N105" s="4"/>
+      <c r="O105" s="4"/>
+      <c r="P105" s="4"/>
+      <c r="Q105" s="4"/>
+      <c r="R105" s="4"/>
+      <c r="S105" s="4"/>
+      <c r="T105" s="4"/>
+      <c r="U105" s="4"/>
+      <c r="V105" s="4"/>
+      <c r="W105" s="4"/>
+      <c r="X105" s="4"/>
+      <c r="Y105" s="4"/>
+      <c r="Z105" s="4"/>
+      <c r="AA105" s="4"/>
+      <c r="AB105" s="4"/>
+      <c r="AC105" s="4"/>
+      <c r="AD105" s="4"/>
+      <c r="AE105" s="4"/>
+      <c r="AF105" s="4"/>
+      <c r="AG105" s="4"/>
+      <c r="AH105" s="4"/>
+      <c r="AI105" s="4"/>
+      <c r="AJ105" s="4"/>
+      <c r="AK105" s="4"/>
+      <c r="AL105" s="4"/>
+      <c r="AM105" s="4"/>
+      <c r="AN105" s="4"/>
+      <c r="AO105" s="4"/>
+      <c r="AP105" s="4"/>
+      <c r="AQ105" s="4"/>
+      <c r="AR105" s="4"/>
+      <c r="AS105" s="4"/>
+      <c r="AT105" s="4"/>
+      <c r="AU105" s="4"/>
+      <c r="AV105" s="4"/>
+      <c r="AW105" s="4"/>
+      <c r="AX105" s="4"/>
+      <c r="AY105" s="4"/>
+      <c r="AZ105" s="4"/>
+      <c r="BA105" s="4"/>
+      <c r="BB105" s="4"/>
+      <c r="BC105" s="4"/>
+      <c r="BD105" s="4"/>
+      <c r="BE105" s="4"/>
+      <c r="BF105" s="4"/>
+      <c r="BG105" s="4"/>
+      <c r="BH105" s="4"/>
+      <c r="BI105" s="4"/>
+      <c r="BJ105" s="4"/>
+      <c r="BK105" s="4"/>
+      <c r="BL105" s="4"/>
+      <c r="BM105" s="4"/>
+    </row>
+    <row r="106" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B106" s="4"/>
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="4"/>
+      <c r="S106" s="4"/>
+      <c r="T106" s="4"/>
+      <c r="U106" s="4"/>
+      <c r="V106" s="4"/>
+      <c r="W106" s="4"/>
+      <c r="X106" s="4"/>
+      <c r="Y106" s="4"/>
+      <c r="Z106" s="4"/>
+      <c r="AA106" s="4"/>
+      <c r="AB106" s="4"/>
+      <c r="AC106" s="4"/>
+      <c r="AD106" s="4"/>
+      <c r="AE106" s="4"/>
+      <c r="AF106" s="4"/>
+      <c r="AG106" s="4"/>
+      <c r="AH106" s="4"/>
+      <c r="AI106" s="4"/>
+      <c r="AJ106" s="4"/>
+      <c r="AK106" s="4"/>
+      <c r="AL106" s="4"/>
+      <c r="AM106" s="4"/>
+      <c r="AN106" s="4"/>
+      <c r="AO106" s="4"/>
+      <c r="AP106" s="4"/>
+      <c r="AQ106" s="4"/>
+      <c r="AR106" s="4"/>
+      <c r="AS106" s="4"/>
+      <c r="AT106" s="4"/>
+      <c r="AU106" s="4"/>
+      <c r="AV106" s="4"/>
+      <c r="AW106" s="4"/>
+      <c r="AX106" s="4"/>
+      <c r="AY106" s="4"/>
+      <c r="AZ106" s="4"/>
+      <c r="BA106" s="4"/>
+      <c r="BB106" s="4"/>
+      <c r="BC106" s="4"/>
+      <c r="BD106" s="4"/>
+      <c r="BE106" s="4"/>
+      <c r="BF106" s="4"/>
+      <c r="BG106" s="4"/>
+      <c r="BH106" s="4"/>
+      <c r="BI106" s="4"/>
+      <c r="BJ106" s="4"/>
+      <c r="BK106" s="4"/>
+      <c r="BL106" s="4"/>
+      <c r="BM106" s="4"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="B107" s="4"/>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="4"/>
+      <c r="T107" s="4"/>
+      <c r="U107" s="4"/>
+      <c r="V107" s="4"/>
+      <c r="W107" s="4"/>
+      <c r="X107" s="4"/>
+      <c r="Y107" s="4"/>
+      <c r="Z107" s="4"/>
+      <c r="AA107" s="4"/>
+      <c r="AB107" s="4"/>
+      <c r="AC107" s="4"/>
+      <c r="AD107" s="4"/>
+      <c r="AE107" s="4"/>
+      <c r="AF107" s="4"/>
+      <c r="AG107" s="4"/>
+      <c r="AH107" s="4"/>
+      <c r="AI107" s="4"/>
+      <c r="AJ107" s="4"/>
+      <c r="AK107" s="4"/>
+      <c r="AL107" s="4"/>
+      <c r="AM107" s="4"/>
+      <c r="AN107" s="4"/>
+      <c r="AO107" s="4"/>
+      <c r="AP107" s="4"/>
+      <c r="AQ107" s="4"/>
+      <c r="AR107" s="4"/>
+      <c r="AS107" s="4"/>
+      <c r="AT107" s="4"/>
+      <c r="AU107" s="4"/>
+      <c r="AV107" s="4"/>
+      <c r="AW107" s="4"/>
+      <c r="AX107" s="4"/>
+      <c r="AY107" s="4"/>
+      <c r="AZ107" s="4"/>
+      <c r="BA107" s="4"/>
+      <c r="BB107" s="4"/>
+      <c r="BC107" s="4"/>
+      <c r="BD107" s="4"/>
+      <c r="BE107" s="4"/>
+      <c r="BF107" s="4"/>
+      <c r="BG107" s="4"/>
+      <c r="BH107" s="4"/>
+      <c r="BI107" s="4"/>
+      <c r="BJ107" s="4"/>
+      <c r="BK107" s="4"/>
+      <c r="BL107" s="4"/>
+      <c r="BM107" s="4"/>
+    </row>
+    <row r="108" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A108" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="B108" s="4"/>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="4"/>
+      <c r="S108" s="4"/>
+      <c r="T108" s="4"/>
+      <c r="U108" s="4"/>
+      <c r="V108" s="4"/>
+      <c r="W108" s="4"/>
+      <c r="X108" s="4"/>
+      <c r="Y108" s="4"/>
+      <c r="Z108" s="4"/>
+      <c r="AA108" s="4"/>
+      <c r="AB108" s="4"/>
+      <c r="AC108" s="4"/>
+      <c r="AD108" s="4"/>
+      <c r="AE108" s="4"/>
+      <c r="AF108" s="4"/>
+      <c r="AG108" s="4"/>
+      <c r="AH108" s="4"/>
+      <c r="AI108" s="4"/>
+      <c r="AJ108" s="4"/>
+      <c r="AK108" s="4"/>
+      <c r="AL108" s="4"/>
+      <c r="AM108" s="4"/>
+      <c r="AN108" s="4"/>
+      <c r="AO108" s="4"/>
+      <c r="AP108" s="4"/>
+      <c r="AQ108" s="4"/>
+      <c r="AR108" s="4"/>
+      <c r="AS108" s="4"/>
+      <c r="AT108" s="4"/>
+      <c r="AU108" s="4"/>
+      <c r="AV108" s="4"/>
+      <c r="AW108" s="4"/>
+      <c r="AX108" s="4"/>
+      <c r="AY108" s="4"/>
+      <c r="AZ108" s="4"/>
+      <c r="BA108" s="4"/>
+      <c r="BB108" s="4"/>
+      <c r="BC108" s="4"/>
+      <c r="BD108" s="4"/>
+      <c r="BE108" s="4"/>
+      <c r="BF108" s="4"/>
+      <c r="BG108" s="4"/>
+      <c r="BH108" s="4"/>
+      <c r="BI108" s="4"/>
+      <c r="BJ108" s="4"/>
+      <c r="BK108" s="4"/>
+      <c r="BL108" s="4"/>
+      <c r="BM108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A109" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B109" s="4"/>
+      <c r="C109" s="4"/>
+      <c r="D109" s="4"/>
+      <c r="E109" s="4"/>
+      <c r="F109" s="4"/>
+      <c r="G109" s="4"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
+      <c r="J109" s="4"/>
+      <c r="K109" s="4"/>
+      <c r="L109" s="4"/>
+      <c r="M109" s="4"/>
+      <c r="N109" s="4"/>
+      <c r="O109" s="4"/>
+      <c r="P109" s="4"/>
+      <c r="Q109" s="4"/>
+      <c r="R109" s="4"/>
+      <c r="S109" s="4"/>
+      <c r="T109" s="4"/>
+      <c r="U109" s="4"/>
+      <c r="V109" s="4"/>
+      <c r="W109" s="4"/>
+      <c r="X109" s="4"/>
+      <c r="Y109" s="4"/>
+      <c r="Z109" s="4"/>
+      <c r="AA109" s="4"/>
+      <c r="AB109" s="4"/>
+      <c r="AC109" s="4"/>
+      <c r="AD109" s="4"/>
+      <c r="AE109" s="4"/>
+      <c r="AF109" s="4"/>
+      <c r="AG109" s="4"/>
+      <c r="AH109" s="4"/>
+      <c r="AI109" s="4"/>
+      <c r="AJ109" s="4"/>
+      <c r="AK109" s="4"/>
+      <c r="AL109" s="4"/>
+      <c r="AM109" s="4"/>
+      <c r="AN109" s="4"/>
+      <c r="AO109" s="4"/>
+      <c r="AP109" s="4"/>
+      <c r="AQ109" s="4"/>
+      <c r="AR109" s="4"/>
+      <c r="AS109" s="4"/>
+      <c r="AT109" s="4"/>
+      <c r="AU109" s="4"/>
+      <c r="AV109" s="4"/>
+      <c r="AW109" s="4"/>
+      <c r="AX109" s="4"/>
+      <c r="AY109" s="4"/>
+      <c r="AZ109" s="4"/>
+      <c r="BA109" s="4"/>
+      <c r="BB109" s="4"/>
+      <c r="BC109" s="4"/>
+      <c r="BD109" s="4"/>
+      <c r="BE109" s="4"/>
+      <c r="BF109" s="4"/>
+      <c r="BG109" s="4"/>
+      <c r="BH109" s="4"/>
+      <c r="BI109" s="4"/>
+      <c r="BJ109" s="4"/>
+      <c r="BK109" s="4"/>
+      <c r="BL109" s="4"/>
+      <c r="BM109" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="94">
+  <mergeCells count="103">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -33712,18 +35533,27 @@
     <mergeCell ref="B80:E80"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="B82:E82"/>
-    <mergeCell ref="A84:V84"/>
-    <mergeCell ref="A90:BM90"/>
-    <mergeCell ref="A91:BM91"/>
-    <mergeCell ref="A92:BM92"/>
-    <mergeCell ref="A93:BM93"/>
-    <mergeCell ref="A94:BM94"/>
-    <mergeCell ref="A95:BM95"/>
-    <mergeCell ref="A96:BM96"/>
-    <mergeCell ref="A97:BM97"/>
-    <mergeCell ref="A98:BM98"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="B88:E88"/>
+    <mergeCell ref="B89:E89"/>
+    <mergeCell ref="B90:E90"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="A93:V93"/>
     <mergeCell ref="A99:BM99"/>
     <mergeCell ref="A100:BM100"/>
+    <mergeCell ref="A101:BM101"/>
+    <mergeCell ref="A102:BM102"/>
+    <mergeCell ref="A103:BM103"/>
+    <mergeCell ref="A104:BM104"/>
+    <mergeCell ref="A105:BM105"/>
+    <mergeCell ref="A106:BM106"/>
+    <mergeCell ref="A107:BM107"/>
+    <mergeCell ref="A108:BM108"/>
+    <mergeCell ref="A109:BM109"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="316">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 12/05/2026 07:50:03</t>
+    <t xml:space="preserve">Emitido em: 14/05/2026 07:28:18</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -214,691 +214,703 @@
     <t xml:space="preserve">Fornecedor substituto tributário</t>
   </si>
   <si>
-    <t xml:space="preserve">34.619 - STECK INDUSTRIA ELETRICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.359</t>
+    <t xml:space="preserve">22.715 - LUMIERE COMERCIO INTERNACIONAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/01/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/02/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">XML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ag. chegada da mercadoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - OBJETIVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260124855633000140550010000731981500237788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.065 - LUXMUNDO COMERCIO IMPORTACAO EXPORTACAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">164,52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260429244900000247550010000665271143138443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">736 - BEMFIXA INDUSTRIAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210.282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.263,18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461801973000114550010002102821579343693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.808 - ABCC -REJUNTABRAS INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">788,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260454542238000178550010000965331000963341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">785 - MEBER METAIS S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">317.522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.349,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260487547907000153550050003175221341934744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">631.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.206,95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006310141648214276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">631.471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">79.798,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260475339051000141550080006314711916432042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">631.499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.331,26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006314991770838133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">631.549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.005,56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006315491224798781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">631.624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.779,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006316241955056484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.972.380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.384,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.972.384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.305,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461413282000143550010029723841503152901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.972.382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.545,08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461413282000143550010029723821252250954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">317.678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.775,54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260487547907000153550050003176781577672540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">633.546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.703,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006335461841845162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">633.523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.460,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006335231488772186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">633.512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.604,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006335121026499000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.300 - INTELBRAS S/A IND TELEC ELETR BRASILEIRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640,37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13260582901000001522550100001462471179714429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">146.254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.201,85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13260582901000001522550100001462541960234960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">633.073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.496,09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006330731926027430</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158,47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260487547907000153550050003168441492652194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.615 - MADELUSTRE INDUSTRIAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.012,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260589616460000152550020000713281306751109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.875,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763591705951920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.076.360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.917,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050763601270059044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.973.037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.434,01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461413282000143550010029730371035091800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.321 - S&amp;P BRASIL VENTILACAO LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.901,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260592659507000412550010000355511160008339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600 - CENSI INDUSTRIA E COMERCIO DE REPAROS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450.441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.531,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260502308456000149550050004504411200487782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">634.749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.103,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006347491202405390</t>
+  </si>
+  <si>
+    <t xml:space="preserve">636.071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.022,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006360711913994222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.976.319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.756,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">777 - IRMAOS FISCHER S.A IND. E COM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780.743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582984287000104550020017807431502859010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780.742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.332,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582984287000104550020017807421113944451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780.741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.549,24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582984287000104550020017807411668968281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">635.121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.912,10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006351211513869799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.975.491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.092,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260561413282000143550010029754911228653957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">790 - JACKWAL S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.196</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
   </si>
   <si>
-    <t xml:space="preserve">27/01/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/01/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/02/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">866,21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ag. chegada da mercadoria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - OBJETIVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          </t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260105890658000300550030000603591859316475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Não</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.715 - LUMIERE COMERCIO INTERNACIONAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">73.198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/01/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/02/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260124855633000140550010000731981500237788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.065 - LUXMUNDO COMERCIO IMPORTACAO EXPORTACAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164,52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29260429244900000247550010000665271143138443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">736 - BEMFIXA INDUSTRIAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.263,18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461801973000114550010002102821579343693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.855 - DEXCO S.A - LOUCAS DECA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.145.854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.487,40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002271550010021458541827498190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.808 - ABCC -REJUNTABRAS INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">788,62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260454542238000178550010000965331000963341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126,70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714681660144540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714691387530892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714701216651343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">290,09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714721287224973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714741354275702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714761015568582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050714751108646462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.071.518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260497837181002190550010050715181446546113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.576 - GRUPO METAL DESIGN LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">936,27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260486895448000560550010000006991505141518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">785 - MEBER METAIS S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.349,48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260487547907000153550050003175221341934744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">709 - MAX EBERHARDT UTILIDADES DOMESTICAS IMPORTACAO E REPRES LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156.111</t>
+    <t xml:space="preserve">7.834,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260592782366000188550030002751961654432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.265,79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - FILIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">637.255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.761,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006372551066202512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.376 - ELETRO ZAGONEL LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">662.150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.581,90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260581365223000154550020006621501364814580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">870.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.603,35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008700041500773535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">637.784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.890,24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006377841750929843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">870.017</t>
   </si>
   <si>
     <t xml:space="preserve">26/05/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.472,29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260456991334000129550010001561111437026545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">631.014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.206,95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006310141648214276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">631.471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.798,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006314711916432042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">631.499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.331,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006314991770838133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">631.549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.005,56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006315491224798781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">631.624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.779,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006316241955056484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972.380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.384,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972.384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.305,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029723841503152901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972.382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.545,08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029723821252250954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.134 - NISSILIGHT COMERCIAL DE MATERIAIS ELETRICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.173,58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260435635346000140550020001113171687660083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.775,54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260487547907000153550050003176781577672540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">633.546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.703,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006335461841845162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">633.523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.460,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006335231488772186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">633.512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.604,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006335121026499000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.300 - INTELBRAS S/A IND TELEC ELETR BRASILEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">640,37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13260582901000001522550100001462471179714429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.201,85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13260582901000001522550100001462541960234960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">633.073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.496,09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006330731926027430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158,47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260487547907000153550050003168441492652194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.264,17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260505890658000300550030000780241405676762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">111.415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.806,37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260535635346000140550020001114151168111482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.615 - MADELUSTRE INDUSTRIAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.012,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260589616460000152550020000713281306751109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260524855633000140550010000766541471008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.076.359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.875,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050763591705951920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.076.360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.917,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050763601270059044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.973.037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.434,01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029730371035091800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">78.088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.908,53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260505890658000300550030000780881358185394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.321 - S&amp;P BRASIL VENTILACAO LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.901,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260592659507000412550010000355511160008339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">600 - CENSI INDUSTRIA E COMERCIO DE REPAROS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.531,62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260502308456000149550050004504411200487782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">869.042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.861,19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008690421845374790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">634.749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.103,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006347491202405390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.718 - STELLA IMPORTACAO E EXPORTACAO DE LUMINARIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">292.593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.518,38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260510691158000370550010002925931234036708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">636.071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.022,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006360711913994222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.976.319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.756,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">777 - IRMAOS FISCHER S.A IND. E COM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807431502859010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.332,17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807421113944451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.549,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807411668968281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">635.121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.912,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006351211513869799</t>
+    <t xml:space="preserve">1.185,87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008700171161145098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804111200730267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804981991793601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804121347149640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.304.071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">426,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260550949528001232550010023040711903090311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">870.047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.695,18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008700471155162406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.929,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829821661840971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">461,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829961140036509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">638.725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.887,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006387251174884389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.702,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260527254297000178550010000105531584622070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.709,55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260581604803000157550010008671441582155041</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17144,7 +17156,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM75"/>
+  <dimension ref="A1:BM74"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17516,7 +17528,7 @@
     </row>
     <row r="5" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="n">
-        <v>300155</v>
+        <v>300446</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>64</v>
@@ -17543,7 +17555,7 @@
         <v>70</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>866.21</v>
+        <v>40</v>
       </c>
       <c r="M5" s="12" t="n">
         <v>0</v>
@@ -17552,16 +17564,16 @@
         <v>1</v>
       </c>
       <c r="O5" s="12" t="n">
-        <v>838.95</v>
+        <v>40</v>
       </c>
       <c r="P5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q5" s="13" t="n">
-        <v>0.015147</v>
+        <v>0</v>
       </c>
       <c r="R5" s="12" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S5" s="12" t="n">
         <v>0</v>
@@ -17573,7 +17585,7 @@
         <v>72</v>
       </c>
       <c r="V5" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W5" s="9" t="s">
         <v>73</v>
@@ -17582,13 +17594,13 @@
         <v>68</v>
       </c>
       <c r="Y5" s="12" t="n">
-        <v>27.26</v>
+        <v>0</v>
       </c>
       <c r="Z5" s="12" t="n">
-        <v>838.95</v>
+        <v>40</v>
       </c>
       <c r="AA5" s="12" t="n">
-        <v>58.73</v>
+        <v>1.6</v>
       </c>
       <c r="AB5" s="12" t="n">
         <v>0</v>
@@ -17684,57 +17696,57 @@
         <v>75</v>
       </c>
       <c r="BG5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH5" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI5" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ5" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="BH5" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI5" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ5" s="9" t="s">
+      <c r="BK5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM5" s="16" t="s">
         <v>79</v>
-      </c>
-      <c r="BK5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL5" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM5" s="16" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>300446</v>
+        <v>305624</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="I6" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="J6" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>40</v>
+        <v>164.52</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
@@ -17743,7 +17755,7 @@
         <v>1</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>40</v>
+        <v>149.9</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
@@ -17758,28 +17770,28 @@
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="Y6" s="12" t="n">
-        <v>0</v>
+        <v>14.62</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>40</v>
+        <v>149.9</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17845,47 +17857,47 @@
         <v>74</v>
       </c>
       <c r="AW6" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="AX6" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF6" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG6" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH6" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI6" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ6" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="AX6" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="AY6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF6" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG6" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH6" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI6" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ6" s="9" t="s">
-        <v>89</v>
-      </c>
       <c r="BK6" s="9" t="s">
         <v>75</v>
       </c>
@@ -17893,153 +17905,153 @@
         <v>75</v>
       </c>
       <c r="BM6" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>305624</v>
+        <v>305716</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>94</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>164.52</v>
+        <v>2263.18</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>149.9</v>
+        <v>2184.42</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0</v>
+        <v>0.00198</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y7" s="12" t="n">
+        <v>78.76</v>
+      </c>
+      <c r="Z7" s="12" t="n">
+        <v>2184.42</v>
+      </c>
+      <c r="AA7" s="12" t="n">
+        <v>152.91</v>
+      </c>
+      <c r="AB7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO7" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV7" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW7" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="Y7" s="12" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="Z7" s="12" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="AA7" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO7" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW7" s="14" t="s">
-        <v>87</v>
-      </c>
       <c r="AX7" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>75</v>
@@ -18066,16 +18078,16 @@
         <v>75</v>
       </c>
       <c r="BG7" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH7" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI7" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -18084,84 +18096,84 @@
         <v>75</v>
       </c>
       <c r="BM7" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>305716</v>
+        <v>305865</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="I8" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>2263.18</v>
+        <v>788.62</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>2184.42</v>
+        <v>788.62</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.00198</v>
+        <v>0.258</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>2.04</v>
+        <v>43</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>78.76</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>2184.42</v>
+        <v>788.62</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>152.91</v>
+        <v>55.2</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -18227,10 +18239,10 @@
         <v>74</v>
       </c>
       <c r="AW8" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -18257,16 +18269,16 @@
         <v>75</v>
       </c>
       <c r="BG8" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH8" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI8" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18275,84 +18287,84 @@
         <v>75</v>
       </c>
       <c r="BM8" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>305861</v>
+        <v>306378</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H9" s="9" t="s">
+      <c r="J9" s="9" t="s">
         <v>105</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>4487.4</v>
+        <v>95349.48</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>4487.4</v>
+        <v>91519.49</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.20424</v>
+        <v>0.80555</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>81</v>
+        <v>424.1</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>84</v>
+        <v>82.61</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>0</v>
+        <v>3829.99</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>4487.4</v>
+        <v>91519.49</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>179.5</v>
+        <v>6406.35</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18418,10 +18430,10 @@
         <v>74</v>
       </c>
       <c r="AW9" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18448,16 +18460,16 @@
         <v>75</v>
       </c>
       <c r="BG9" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH9" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI9" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18466,39 +18478,39 @@
         <v>75</v>
       </c>
       <c r="BM9" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>305865</v>
+        <v>306494</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>83</v>
-      </c>
       <c r="H10" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>788.62</v>
+        <v>40206.95</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
@@ -18507,43 +18519,43 @@
         <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>788.62</v>
+        <v>37753</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.258</v>
+        <v>0.24</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>0</v>
+        <v>2453.95</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>788.62</v>
+        <v>37753</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>55.2</v>
+        <v>2642.71</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18609,10 +18621,10 @@
         <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18639,16 +18651,16 @@
         <v>75</v>
       </c>
       <c r="BG10" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH10" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI10" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18657,15 +18669,15 @@
         <v>75</v>
       </c>
       <c r="BM10" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>305959</v>
+        <v>306496</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -18674,67 +18686,67 @@
         <v>115</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>126.7</v>
+        <v>79798.26</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>118.97</v>
+        <v>79696.44</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.990242</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>1.58</v>
+        <v>316.25</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>7.73</v>
+        <v>101.82</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>118.97</v>
+        <v>79696.44</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>4.76</v>
+        <v>5578.75</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18800,10 +18812,10 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18830,16 +18842,16 @@
         <v>75</v>
       </c>
       <c r="BG11" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH11" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI11" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18848,39 +18860,39 @@
         <v>75</v>
       </c>
       <c r="BM11" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>305961</v>
+        <v>306497</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="I12" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="J12" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="J12" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>126.7</v>
+        <v>5331.26</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18889,43 +18901,43 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>118.97</v>
+        <v>5005.88</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.055816</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>1.58</v>
+        <v>7.12</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>7.73</v>
+        <v>325.38</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>118.97</v>
+        <v>5005.88</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>4.76</v>
+        <v>350.41</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18991,10 +19003,10 @@
         <v>74</v>
       </c>
       <c r="AW12" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>75</v>
@@ -19021,16 +19033,16 @@
         <v>75</v>
       </c>
       <c r="BG12" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH12" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI12" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19039,39 +19051,39 @@
         <v>75</v>
       </c>
       <c r="BM12" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>305963</v>
+        <v>306498</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>126.7</v>
+        <v>3005.56</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -19080,43 +19092,43 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>118.97</v>
+        <v>3005.56</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.001512</v>
+        <v>0.008736</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>1.58</v>
+        <v>2.32</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>7.73</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>118.97</v>
+        <v>3005.56</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>4.76</v>
+        <v>210.39</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19182,10 +19194,10 @@
         <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -19212,16 +19224,16 @@
         <v>75</v>
       </c>
       <c r="BG13" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH13" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI13" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19230,84 +19242,84 @@
         <v>75</v>
       </c>
       <c r="BM13" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>305965</v>
+        <v>306501</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>290.09</v>
+        <v>5779.28</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>272.38</v>
+        <v>5779.28</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.00943</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>1.93</v>
+        <v>4.8</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>272.38</v>
+        <v>5779.28</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>10.89</v>
+        <v>404.55</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19373,10 +19385,10 @@
         <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>75</v>
@@ -19403,16 +19415,16 @@
         <v>75</v>
       </c>
       <c r="BG14" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH14" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI14" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19421,63 +19433,63 @@
         <v>75</v>
       </c>
       <c r="BM14" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>305967</v>
+        <v>306535</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>290.09</v>
+        <v>5384.2</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>272.38</v>
+        <v>5384.2</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.023054</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>1.93</v>
+        <v>28.62</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
@@ -19489,16 +19501,16 @@
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>272.38</v>
+        <v>0</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>10.89</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19564,10 +19576,10 @@
         <v>74</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19594,16 +19606,16 @@
         <v>75</v>
       </c>
       <c r="BG15" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH15" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI15" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19612,39 +19624,39 @@
         <v>75</v>
       </c>
       <c r="BM15" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>305968</v>
+        <v>306536</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>290.09</v>
+        <v>8305.8</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19653,22 +19665,22 @@
         <v>2</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>272.38</v>
+        <v>8305.8</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.02159</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>1.93</v>
+        <v>29.29</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
@@ -19680,16 +19692,16 @@
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>272.38</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>10.89</v>
+        <v>0</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19755,10 +19767,10 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19785,16 +19797,16 @@
         <v>75</v>
       </c>
       <c r="BG16" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH16" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI16" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19803,39 +19815,39 @@
         <v>75</v>
       </c>
       <c r="BM16" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>305969</v>
+        <v>306537</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>290.09</v>
+        <v>18545.08</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19844,22 +19856,22 @@
         <v>2</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>272.38</v>
+        <v>18545.08</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.003202</v>
+        <v>0.582728</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>1.93</v>
+        <v>76.55</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19871,16 +19883,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>17.71</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>272.38</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>10.89</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19946,10 +19958,10 @@
         <v>74</v>
       </c>
       <c r="AW17" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>75</v>
@@ -19976,16 +19988,16 @@
         <v>75</v>
       </c>
       <c r="BG17" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH17" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI17" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19994,84 +20006,84 @@
         <v>75</v>
       </c>
       <c r="BM17" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>305970</v>
+        <v>306568</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>126.7</v>
+        <v>32775.54</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>118.97</v>
+        <v>31565.22</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.001512</v>
+        <v>1.03129</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>1.58</v>
+        <v>102.16</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>0</v>
+        <v>83.35</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>7.73</v>
+        <v>1210.32</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>118.97</v>
+        <v>31565.22</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>4.76</v>
+        <v>2209.57</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20137,10 +20149,10 @@
         <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -20167,16 +20179,16 @@
         <v>75</v>
       </c>
       <c r="BG18" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH18" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI18" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20185,84 +20197,84 @@
         <v>75</v>
       </c>
       <c r="BM18" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>306340</v>
+        <v>306659</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>111</v>
+        <v>144</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>936.27</v>
+        <v>3703.1</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>915.61</v>
+        <v>3703.1</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0</v>
+        <v>0.040904</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>0</v>
+        <v>9.34</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>20.66</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>915.61</v>
+        <v>3703.1</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>36.62</v>
+        <v>259.22</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20328,10 +20340,10 @@
         <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20358,16 +20370,16 @@
         <v>75</v>
       </c>
       <c r="BG19" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH19" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI19" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20376,84 +20388,84 @@
         <v>75</v>
       </c>
       <c r="BM19" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>306378</v>
+        <v>306661</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>95349.48</v>
+        <v>2460.96</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>91519.49</v>
+        <v>2460.96</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.80555</v>
+        <v>0.009892</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>424.1</v>
+        <v>3.51</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>82.61</v>
+        <v>28</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>3829.99</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>91519.49</v>
+        <v>2460.96</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>6406.35</v>
+        <v>172.27</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20519,10 +20531,10 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20549,16 +20561,16 @@
         <v>75</v>
       </c>
       <c r="BG20" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH20" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI20" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20567,63 +20579,63 @@
         <v>75</v>
       </c>
       <c r="BM20" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>306397</v>
+        <v>306662</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>147</v>
+        <v>108</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>2472.29</v>
+        <v>1604</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>60.1</v>
+        <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>2381.5</v>
+        <v>1604</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.00163</v>
+        <v>0.009968</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>15</v>
+        <v>2.28</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
@@ -20635,16 +20647,16 @@
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>150.89</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>2321.4</v>
+        <v>1604</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>162.5</v>
+        <v>112.28</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20710,10 +20722,10 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20740,16 +20752,16 @@
         <v>75</v>
       </c>
       <c r="BG21" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH21" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI21" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20758,39 +20770,39 @@
         <v>75</v>
       </c>
       <c r="BM21" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>306494</v>
+        <v>306668</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>40206.95</v>
+        <v>640.37</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20799,16 +20811,16 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>37753</v>
+        <v>640.37</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
@@ -20820,22 +20832,22 @@
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>2453.95</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>37753</v>
+        <v>640.37</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>2642.71</v>
+        <v>76.84</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20901,10 +20913,10 @@
         <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20931,13 +20943,13 @@
         <v>75</v>
       </c>
       <c r="BG22" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH22" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI22" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
         <v>158</v>
@@ -20949,15 +20961,15 @@
         <v>75</v>
       </c>
       <c r="BM22" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>306496</v>
+        <v>306669</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -20966,40 +20978,40 @@
         <v>159</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>79798.26</v>
+        <v>3201.85</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>79696.44</v>
+        <v>3201.85</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.990242</v>
+        <v>0</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>316.25</v>
+        <v>0</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
@@ -21011,22 +21023,22 @@
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>101.82</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>79696.44</v>
+        <v>3201.85</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>5578.75</v>
+        <v>384.22</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21092,10 +21104,10 @@
         <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21122,13 +21134,13 @@
         <v>75</v>
       </c>
       <c r="BG23" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH23" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI23" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
         <v>161</v>
@@ -21140,15 +21152,15 @@
         <v>75</v>
       </c>
       <c r="BM23" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>306497</v>
+        <v>306672</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
@@ -21157,46 +21169,46 @@
         <v>162</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="H24" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="J24" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="J24" s="9" t="s">
-        <v>164</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>5331.26</v>
+        <v>4496.09</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>5005.88</v>
+        <v>4496.09</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.055816</v>
+        <v>0.015408</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>7.12</v>
+        <v>4.43</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
@@ -21208,16 +21220,16 @@
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>325.38</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>5005.88</v>
+        <v>4496.09</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>350.41</v>
+        <v>314.73</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21283,10 +21295,10 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21313,16 +21325,16 @@
         <v>75</v>
       </c>
       <c r="BG24" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH24" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI24" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21331,39 +21343,39 @@
         <v>75</v>
       </c>
       <c r="BM24" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>306498</v>
+        <v>306716</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>163</v>
-      </c>
       <c r="I25" s="9" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>164</v>
+        <v>69</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>3005.56</v>
+        <v>158.47</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21372,16 +21384,16 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>3005.56</v>
+        <v>148.8</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.008736</v>
+        <v>0</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
@@ -21393,22 +21405,22 @@
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>0</v>
+        <v>9.67</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>3005.56</v>
+        <v>158.47</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>210.39</v>
+        <v>11.09</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21474,10 +21486,10 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21504,16 +21516,16 @@
         <v>75</v>
       </c>
       <c r="BG25" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH25" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI25" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21522,84 +21534,84 @@
         <v>75</v>
       </c>
       <c r="BM25" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>306501</v>
+        <v>306769</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>152</v>
+        <v>171</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>5779.28</v>
+        <v>5012.28</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>5779.28</v>
+        <v>4567</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.00943</v>
+        <v>0</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>28</v>
+        <v>40.75</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>0</v>
+        <v>445.28</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>5779.28</v>
+        <v>4567</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>404.55</v>
+        <v>319.68</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21668,7 +21680,7 @@
         <v>76</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21695,16 +21707,16 @@
         <v>75</v>
       </c>
       <c r="BG26" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH26" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI26" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21713,63 +21725,63 @@
         <v>75</v>
       </c>
       <c r="BM26" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>306535</v>
+        <v>306783</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="I27" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>155</v>
-      </c>
       <c r="J27" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>5384.2</v>
+        <v>2875.92</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>5384.2</v>
+        <v>2700.39</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.023054</v>
+        <v>0</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>28.62</v>
+        <v>0</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
@@ -21781,16 +21793,16 @@
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>0</v>
+        <v>175.53</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>0</v>
+        <v>2700.39</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>0</v>
+        <v>108.02</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21859,7 +21871,7 @@
         <v>76</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21886,16 +21898,16 @@
         <v>75</v>
       </c>
       <c r="BG27" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH27" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI27" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21904,63 +21916,63 @@
         <v>75</v>
       </c>
       <c r="BM27" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>306536</v>
+        <v>306784</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>8305.8</v>
+        <v>1917.28</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>8305.8</v>
+        <v>1800.26</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.02159</v>
+        <v>0</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>29.29</v>
+        <v>0</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
@@ -21972,16 +21984,16 @@
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>0</v>
+        <v>117.02</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>0</v>
+        <v>1800.26</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>0</v>
+        <v>72.01</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22047,10 +22059,10 @@
         <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -22077,16 +22089,16 @@
         <v>75</v>
       </c>
       <c r="BG28" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH28" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI28" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22095,84 +22107,84 @@
         <v>75</v>
       </c>
       <c r="BM28" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>306537</v>
+        <v>306801</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>137</v>
+        <v>104</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>78</v>
+        <v>185</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>18545.08</v>
+        <v>26434.01</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>18545.08</v>
+        <v>25783.04</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.582728</v>
+        <v>0.47642</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>76.55</v>
+        <v>56.65</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>0</v>
+        <v>650.97</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>0</v>
+        <v>25783.04</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>0</v>
+        <v>1265.66</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22238,10 +22250,10 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -22268,16 +22280,16 @@
         <v>75</v>
       </c>
       <c r="BG29" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH29" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI29" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22286,84 +22298,84 @@
         <v>75</v>
       </c>
       <c r="BM29" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>306566</v>
+        <v>306816</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>186</v>
+        <v>145</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>19173.58</v>
+        <v>7901.28</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>17759.1</v>
+        <v>7901.28</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>10.05579</v>
+        <v>0</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>44.3</v>
+        <v>0</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>71.68</v>
+        <v>28</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>1414.48</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>17759.1</v>
+        <v>7901.28</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>710.36</v>
+        <v>316.05</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22429,10 +22441,10 @@
         <v>74</v>
       </c>
       <c r="AW30" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX30" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY30" s="14" t="s">
         <v>75</v>
@@ -22459,16 +22471,16 @@
         <v>75</v>
       </c>
       <c r="BG30" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH30" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI30" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22477,84 +22489,84 @@
         <v>75</v>
       </c>
       <c r="BM30" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>306568</v>
+        <v>306826</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>141</v>
+        <v>192</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>143</v>
+        <v>103</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>32775.54</v>
+        <v>4531.62</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>31565.22</v>
+        <v>4473.82</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>1.03129</v>
+        <v>0.180978</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>102.16</v>
+        <v>29.27</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>83.35</v>
+        <v>75.75</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>1210.32</v>
+        <v>57.8</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>31565.22</v>
+        <v>4473.82</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>2209.57</v>
+        <v>183</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22623,7 +22635,7 @@
         <v>76</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22650,16 +22662,16 @@
         <v>75</v>
       </c>
       <c r="BG31" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH31" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI31" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22668,39 +22680,39 @@
         <v>75</v>
       </c>
       <c r="BM31" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>306659</v>
+        <v>306879</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>154</v>
+        <v>110</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>3703.1</v>
+        <v>19103.8</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -22709,22 +22721,22 @@
         <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>3703.1</v>
+        <v>19103.8</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.040904</v>
+        <v>0.0507</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>9.34</v>
+        <v>54.16</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
@@ -22736,16 +22748,16 @@
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>3703.1</v>
+        <v>19103.8</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>259.22</v>
+        <v>1337.27</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22811,10 +22823,10 @@
         <v>74</v>
       </c>
       <c r="AW32" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX32" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY32" s="14" t="s">
         <v>75</v>
@@ -22841,16 +22853,16 @@
         <v>75</v>
       </c>
       <c r="BG32" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH32" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI32" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22859,39 +22871,39 @@
         <v>75</v>
       </c>
       <c r="BM32" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>306661</v>
+        <v>306945</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="G33" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="H33" s="9" t="s">
+      <c r="I33" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="I33" s="9" t="s">
-        <v>194</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>195</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>2460.96</v>
+        <v>11022.8</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -22900,22 +22912,22 @@
         <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>2460.96</v>
+        <v>11022.8</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.009892</v>
+        <v>0.0217</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>3.51</v>
+        <v>2.44</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
@@ -22927,16 +22939,16 @@
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="Y33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>2460.96</v>
+        <v>11022.8</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>172.27</v>
+        <v>771.6</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -23002,10 +23014,10 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -23032,16 +23044,16 @@
         <v>75</v>
       </c>
       <c r="BG33" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH33" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI33" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23050,39 +23062,39 @@
         <v>75</v>
       </c>
       <c r="BM33" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>306662</v>
+        <v>307020</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>152</v>
+        <v>129</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1604</v>
+        <v>1756.8</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -23091,43 +23103,43 @@
         <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>1604</v>
+        <v>1756.8</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.009968</v>
+        <v>0.142272</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>2.28</v>
+        <v>3.42</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="Y34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>1604</v>
+        <v>1756.8</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>112.28</v>
+        <v>122.98</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23193,10 +23205,10 @@
         <v>74</v>
       </c>
       <c r="AW34" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX34" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY34" s="14" t="s">
         <v>75</v>
@@ -23223,16 +23235,16 @@
         <v>75</v>
       </c>
       <c r="BG34" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH34" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI34" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23241,39 +23253,39 @@
         <v>75</v>
       </c>
       <c r="BM34" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>306668</v>
+        <v>307044</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>640.37</v>
+        <v>760.8</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23282,43 +23294,43 @@
         <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>640.37</v>
+        <v>760.8</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0</v>
+        <v>0.09178</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>0</v>
+        <v>14.15</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="Y35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>640.37</v>
+        <v>760.8</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>76.84</v>
+        <v>53.26</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23384,7 +23396,7 @@
         <v>74</v>
       </c>
       <c r="AW35" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX35" s="10" t="s">
         <v>77</v>
@@ -23414,16 +23426,16 @@
         <v>75</v>
       </c>
       <c r="BG35" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH35" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI35" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23432,39 +23444,39 @@
         <v>75</v>
       </c>
       <c r="BM35" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>306669</v>
+        <v>307045</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>206</v>
+        <v>173</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>3201.85</v>
+        <v>1332.17</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
@@ -23473,43 +23485,43 @@
         <v>1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>3201.85</v>
+        <v>1332.17</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0</v>
+        <v>0.017488</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>0</v>
+        <v>8.85</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="Y36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>3201.85</v>
+        <v>1332.17</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>384.22</v>
+        <v>53.29</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23575,7 +23587,7 @@
         <v>74</v>
       </c>
       <c r="AW36" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX36" s="10" t="s">
         <v>77</v>
@@ -23605,16 +23617,16 @@
         <v>75</v>
       </c>
       <c r="BG36" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH36" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI36" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23623,84 +23635,84 @@
         <v>75</v>
       </c>
       <c r="BM36" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>306672</v>
+        <v>307046</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>152</v>
+        <v>211</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>4496.09</v>
+        <v>39549.24</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>4496.09</v>
+        <v>36406.48</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>0</v>
+        <v>1877.94</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.015408</v>
+        <v>2.71203</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>4.43</v>
+        <v>520.9</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="W37" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>0</v>
+        <v>1264.82</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>4496.09</v>
+        <v>38284.42</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>314.73</v>
+        <v>2330.38</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23766,10 +23778,10 @@
         <v>74</v>
       </c>
       <c r="AW37" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX37" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY37" s="14" t="s">
         <v>75</v>
@@ -23796,16 +23808,16 @@
         <v>75</v>
       </c>
       <c r="BG37" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH37" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI37" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23814,39 +23826,39 @@
         <v>75</v>
       </c>
       <c r="BM37" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>306716</v>
+        <v>307048</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="I38" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="J38" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>158.47</v>
+        <v>7912.1</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -23855,7 +23867,7 @@
         <v>1</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>148.8</v>
+        <v>7912.1</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
@@ -23870,28 +23882,28 @@
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>9.67</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>158.47</v>
+        <v>7912.1</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>11.09</v>
+        <v>553.85</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23957,10 +23969,10 @@
         <v>74</v>
       </c>
       <c r="AW38" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX38" s="10" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="AY38" s="14" t="s">
         <v>75</v>
@@ -23987,16 +23999,16 @@
         <v>75</v>
       </c>
       <c r="BG38" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH38" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI38" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -24005,84 +24017,84 @@
         <v>75</v>
       </c>
       <c r="BM38" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>306718</v>
+        <v>307062</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>13264.17</v>
+        <v>94092.8</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>12355.2</v>
+        <v>93172</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>1.05026</v>
+        <v>2.122527</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>92.08</v>
+        <v>493.99</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>908.97</v>
+        <v>920.8</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>12355.2</v>
+        <v>92335.42</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>864.86</v>
+        <v>5743.16</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24148,10 +24160,10 @@
         <v>74</v>
       </c>
       <c r="AW39" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX39" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY39" s="14" t="s">
         <v>75</v>
@@ -24178,16 +24190,16 @@
         <v>75</v>
       </c>
       <c r="BG39" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH39" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI39" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24196,84 +24208,84 @@
         <v>75</v>
       </c>
       <c r="BM39" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>306754</v>
+        <v>307073</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>183</v>
+        <v>230</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="I40" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="J40" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>221</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>7806.37</v>
+        <v>7834.72</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>7108.5</v>
+        <v>7524.33</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.00259</v>
+        <v>0</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>57.32</v>
+        <v>35</v>
       </c>
       <c r="W40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>697.87</v>
+        <v>310.39</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>7108.5</v>
+        <v>7524.33</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>284.34</v>
+        <v>526.7</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24339,10 +24351,10 @@
         <v>74</v>
       </c>
       <c r="AW40" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX40" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY40" s="14" t="s">
         <v>75</v>
@@ -24369,16 +24381,16 @@
         <v>75</v>
       </c>
       <c r="BG40" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH40" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI40" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24387,84 +24399,84 @@
         <v>75</v>
       </c>
       <c r="BM40" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>306769</v>
+        <v>307133</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>195</v>
+        <v>237</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>5012.28</v>
+        <v>4265.79</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>4567</v>
+        <v>4222.88</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0</v>
+        <v>0.484131</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>40.75</v>
+        <v>63</v>
       </c>
       <c r="W41" s="9" t="s">
-        <v>73</v>
+        <v>239</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>445.28</v>
+        <v>42.91</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>4567</v>
+        <v>4222.88</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>319.68</v>
+        <v>281.12</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24530,10 +24542,10 @@
         <v>74</v>
       </c>
       <c r="AW41" s="14" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AX41" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY41" s="14" t="s">
         <v>75</v>
@@ -24560,16 +24572,16 @@
         <v>75</v>
       </c>
       <c r="BG41" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH41" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI41" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24578,39 +24590,39 @@
         <v>75</v>
       </c>
       <c r="BM41" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>306771</v>
+        <v>307142</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>130</v>
+        <v>20761.14</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
@@ -24619,43 +24631,43 @@
         <v>1</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>130</v>
+        <v>20761.14</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0</v>
+        <v>0.01152</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W42" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>130</v>
+        <v>20761.14</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>5.2</v>
+        <v>1453.28</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24721,10 +24733,10 @@
         <v>74</v>
       </c>
       <c r="AW42" s="14" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AX42" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AY42" s="14" t="s">
         <v>75</v>
@@ -24751,16 +24763,16 @@
         <v>75</v>
       </c>
       <c r="BG42" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH42" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI42" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24769,39 +24781,39 @@
         <v>75</v>
       </c>
       <c r="BM42" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>306783</v>
+        <v>307146</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>114</v>
+        <v>245</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>83</v>
+        <v>173</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>2875.92</v>
+        <v>6581.9</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
@@ -24810,7 +24822,7 @@
         <v>1</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>2700.39</v>
+        <v>6581.9</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
@@ -24819,34 +24831,34 @@
         <v>0</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>0</v>
+        <v>416.22</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V43" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W43" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>175.53</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>2700.39</v>
+        <v>6581.9</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>108.02</v>
+        <v>460.73</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -24912,10 +24924,10 @@
         <v>74</v>
       </c>
       <c r="AW43" s="14" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AX43" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AY43" s="14" t="s">
         <v>75</v>
@@ -24942,16 +24954,16 @@
         <v>75</v>
       </c>
       <c r="BG43" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH43" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI43" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -24960,39 +24972,39 @@
         <v>75</v>
       </c>
       <c r="BM43" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>306784</v>
+        <v>307159</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>83</v>
+        <v>232</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>78</v>
+        <v>251</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>1917.28</v>
+        <v>1603.35</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
@@ -25001,43 +25013,43 @@
         <v>1</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>1800.26</v>
+        <v>1527</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0</v>
+        <v>0.05265</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>117.02</v>
+        <v>76.35</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>1800.26</v>
+        <v>1527</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>72.01</v>
+        <v>106.89</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25103,10 +25115,10 @@
         <v>74</v>
       </c>
       <c r="AW44" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX44" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AY44" s="14" t="s">
         <v>75</v>
@@ -25133,16 +25145,16 @@
         <v>75</v>
       </c>
       <c r="BG44" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH44" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI44" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25151,30 +25163,30 @@
         <v>75</v>
       </c>
       <c r="BM44" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>306801</v>
+        <v>307161</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>83</v>
+        <v>110</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>242</v>
@@ -25183,52 +25195,52 @@
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>26434.01</v>
+        <v>4890.24</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>25783.04</v>
+        <v>4890.24</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.47642</v>
+        <v>0.001296</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>56.65</v>
+        <v>2.22</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y45" s="12" t="n">
-        <v>650.97</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>25783.04</v>
+        <v>4890.24</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>1265.66</v>
+        <v>342.32</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25294,10 +25306,10 @@
         <v>74</v>
       </c>
       <c r="AW45" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX45" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY45" s="14" t="s">
         <v>75</v>
@@ -25324,16 +25336,16 @@
         <v>75</v>
       </c>
       <c r="BG45" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH45" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI45" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25342,84 +25354,84 @@
         <v>75</v>
       </c>
       <c r="BM45" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>306806</v>
+        <v>307162</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>64</v>
+        <v>249</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>66</v>
+        <v>232</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>29908.53</v>
+        <v>1185.87</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>56</v>
+        <v>1</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>28002.68</v>
+        <v>1129.4</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>0</v>
+        <v>0.0351</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>37.32</v>
+        <v>20</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>1905.85</v>
+        <v>56.47</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>28002.68</v>
+        <v>1129.4</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>1120.05</v>
+        <v>79.06</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25485,10 +25497,10 @@
         <v>74</v>
       </c>
       <c r="AW46" s="14" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AX46" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY46" s="14" t="s">
         <v>75</v>
@@ -25515,16 +25527,16 @@
         <v>75</v>
       </c>
       <c r="BG46" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH46" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI46" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ46" s="9" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="BK46" s="9" t="s">
         <v>75</v>
@@ -25533,84 +25545,84 @@
         <v>75</v>
       </c>
       <c r="BM46" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>306816</v>
+        <v>307171</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>249</v>
+        <v>177</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="G47" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>7901.28</v>
+        <v>404.81</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>7901.28</v>
+        <v>404.81</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0</v>
+        <v>0.000858</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>7901.28</v>
+        <v>404.81</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>316.05</v>
+        <v>16.19</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25676,10 +25688,10 @@
         <v>74</v>
       </c>
       <c r="AW47" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX47" s="10" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="AY47" s="14" t="s">
         <v>75</v>
@@ -25706,16 +25718,16 @@
         <v>75</v>
       </c>
       <c r="BG47" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH47" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI47" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="BK47" s="9" t="s">
         <v>75</v>
@@ -25724,84 +25736,84 @@
         <v>75</v>
       </c>
       <c r="BM47" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="8" t="n">
-        <v>306826</v>
+        <v>307173</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>253</v>
+        <v>177</v>
       </c>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
       <c r="F48" s="9" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="G48" s="10" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="H48" s="9" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>246</v>
+        <v>69</v>
       </c>
       <c r="K48" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>4531.62</v>
+        <v>404.81</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O48" s="12" t="n">
-        <v>4473.82</v>
+        <v>404.81</v>
       </c>
       <c r="P48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q48" s="13" t="n">
-        <v>0.180978</v>
+        <v>0.000858</v>
       </c>
       <c r="R48" s="12" t="n">
-        <v>29.27</v>
+        <v>2.43</v>
       </c>
       <c r="S48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T48" s="14" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="U48" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V48" s="12" t="n">
-        <v>75.75</v>
+        <v>0</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X48" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y48" s="12" t="n">
-        <v>57.8</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="12" t="n">
-        <v>4473.82</v>
+        <v>404.81</v>
       </c>
       <c r="AA48" s="12" t="n">
-        <v>183</v>
+        <v>16.19</v>
       </c>
       <c r="AB48" s="12" t="n">
         <v>0</v>
@@ -25867,10 +25879,10 @@
         <v>74</v>
       </c>
       <c r="AW48" s="14" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="AX48" s="10" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="AY48" s="14" t="s">
         <v>75</v>
@@ -25897,16 +25909,16 @@
         <v>75</v>
       </c>
       <c r="BG48" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH48" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI48" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ48" s="9" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="BK48" s="9" t="s">
         <v>75</v>
@@ -25915,84 +25927,84 @@
         <v>75</v>
       </c>
       <c r="BM48" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="8" t="n">
-        <v>306850</v>
+        <v>307174</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>257</v>
+        <v>177</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="9"/>
       <c r="E49" s="9"/>
       <c r="F49" s="9" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="G49" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>259</v>
+        <v>69</v>
       </c>
       <c r="K49" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>1861.19</v>
+        <v>404.81</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O49" s="12" t="n">
-        <v>1802.6</v>
+        <v>404.81</v>
       </c>
       <c r="P49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q49" s="13" t="n">
-        <v>0.22621</v>
+        <v>0.000858</v>
       </c>
       <c r="R49" s="12" t="n">
-        <v>7.52</v>
+        <v>2.43</v>
       </c>
       <c r="S49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U49" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V49" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X49" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Y49" s="12" t="n">
-        <v>58.59</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="12" t="n">
-        <v>1802.6</v>
+        <v>404.81</v>
       </c>
       <c r="AA49" s="12" t="n">
-        <v>74.73</v>
+        <v>16.19</v>
       </c>
       <c r="AB49" s="12" t="n">
         <v>0</v>
@@ -26058,10 +26070,10 @@
         <v>74</v>
       </c>
       <c r="AW49" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX49" s="10" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="AY49" s="14" t="s">
         <v>75</v>
@@ -26088,16 +26100,16 @@
         <v>75</v>
       </c>
       <c r="BG49" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH49" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI49" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ49" s="9" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="BK49" s="9" t="s">
         <v>75</v>
@@ -26106,84 +26118,84 @@
         <v>75</v>
       </c>
       <c r="BM49" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="8" t="n">
-        <v>306879</v>
+        <v>307181</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>152</v>
+        <v>268</v>
       </c>
       <c r="C50" s="9"/>
       <c r="D50" s="9"/>
       <c r="E50" s="9"/>
       <c r="F50" s="9" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="G50" s="10" t="s">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="H50" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>221</v>
+        <v>270</v>
       </c>
       <c r="K50" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>19103.8</v>
+        <v>426.2</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" s="12" t="n">
-        <v>19103.8</v>
+        <v>426.2</v>
       </c>
       <c r="P50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q50" s="13" t="n">
-        <v>0.0507</v>
+        <v>0.0025</v>
       </c>
       <c r="R50" s="12" t="n">
-        <v>54.16</v>
+        <v>10</v>
       </c>
       <c r="S50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T50" s="14" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="U50" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V50" s="12" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="W50" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X50" s="9" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="Y50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z50" s="12" t="n">
-        <v>19103.8</v>
+        <v>426.2</v>
       </c>
       <c r="AA50" s="12" t="n">
-        <v>1337.27</v>
+        <v>29.84</v>
       </c>
       <c r="AB50" s="12" t="n">
         <v>0</v>
@@ -26249,10 +26261,10 @@
         <v>74</v>
       </c>
       <c r="AW50" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX50" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY50" s="14" t="s">
         <v>75</v>
@@ -26279,16 +26291,16 @@
         <v>75</v>
       </c>
       <c r="BG50" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH50" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI50" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ50" s="9" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="BK50" s="9" t="s">
         <v>75</v>
@@ -26297,84 +26309,84 @@
         <v>75</v>
       </c>
       <c r="BM50" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="8" t="n">
-        <v>306894</v>
+        <v>307183</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="9"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G51" s="10" t="s">
-        <v>83</v>
+        <v>232</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="K51" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>16518.38</v>
+        <v>12695.18</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O51" s="12" t="n">
-        <v>14973.46</v>
+        <v>11935.6</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="13" t="n">
-        <v>0.011534</v>
+        <v>0.0698</v>
       </c>
       <c r="R51" s="12" t="n">
-        <v>20.58</v>
+        <v>31.68</v>
       </c>
       <c r="S51" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="U51" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V51" s="12" t="n">
-        <v>55.86</v>
+        <v>14</v>
       </c>
       <c r="W51" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X51" s="9" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="Y51" s="12" t="n">
-        <v>1459.92</v>
+        <v>759.58</v>
       </c>
       <c r="Z51" s="12" t="n">
-        <v>15058.46</v>
+        <v>11935.6</v>
       </c>
       <c r="AA51" s="12" t="n">
-        <v>602.33</v>
+        <v>614.43</v>
       </c>
       <c r="AB51" s="12" t="n">
         <v>0</v>
@@ -26440,10 +26452,10 @@
         <v>74</v>
       </c>
       <c r="AW51" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX51" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY51" s="14" t="s">
         <v>75</v>
@@ -26470,16 +26482,16 @@
         <v>75</v>
       </c>
       <c r="BG51" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH51" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI51" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ51" s="9" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="BK51" s="9" t="s">
         <v>75</v>
@@ -26488,39 +26500,39 @@
         <v>75</v>
       </c>
       <c r="BM51" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="n">
-        <v>306945</v>
+        <v>307231</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C52" s="9"/>
       <c r="D52" s="9"/>
       <c r="E52" s="9"/>
       <c r="F52" s="9" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="G52" s="10" t="s">
-        <v>154</v>
+        <v>66</v>
       </c>
       <c r="H52" s="9" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>246</v>
+        <v>278</v>
       </c>
       <c r="K52" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>11022.8</v>
+        <v>2929.6</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
@@ -26529,43 +26541,43 @@
         <v>1</v>
       </c>
       <c r="O52" s="12" t="n">
-        <v>11022.8</v>
+        <v>2929.6</v>
       </c>
       <c r="P52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q52" s="13" t="n">
-        <v>0.0217</v>
+        <v>0.000484</v>
       </c>
       <c r="R52" s="12" t="n">
-        <v>2.44</v>
+        <v>3.22</v>
       </c>
       <c r="S52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T52" s="14" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="U52" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V52" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W52" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X52" s="9" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="Y52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z52" s="12" t="n">
-        <v>11022.8</v>
+        <v>2929.6</v>
       </c>
       <c r="AA52" s="12" t="n">
-        <v>771.6</v>
+        <v>205.07</v>
       </c>
       <c r="AB52" s="12" t="n">
         <v>0</v>
@@ -26631,10 +26643,10 @@
         <v>74</v>
       </c>
       <c r="AW52" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX52" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY52" s="14" t="s">
         <v>75</v>
@@ -26661,16 +26673,16 @@
         <v>75</v>
       </c>
       <c r="BG52" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH52" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI52" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ52" s="9" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="BK52" s="9" t="s">
         <v>75</v>
@@ -26679,39 +26691,39 @@
         <v>75</v>
       </c>
       <c r="BM52" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="n">
-        <v>307020</v>
+        <v>307235</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="9"/>
       <c r="E53" s="9"/>
       <c r="F53" s="9" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>271</v>
+        <v>226</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>276</v>
+        <v>69</v>
       </c>
       <c r="K53" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>1756.8</v>
+        <v>461.96</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
@@ -26720,43 +26732,43 @@
         <v>1</v>
       </c>
       <c r="O53" s="12" t="n">
-        <v>1756.8</v>
+        <v>461.96</v>
       </c>
       <c r="P53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q53" s="13" t="n">
-        <v>0.142272</v>
+        <v>0.002057</v>
       </c>
       <c r="R53" s="12" t="n">
-        <v>3.42</v>
+        <v>2.43</v>
       </c>
       <c r="S53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T53" s="14" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="U53" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V53" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="W53" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X53" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Y53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z53" s="12" t="n">
-        <v>1756.8</v>
+        <v>461.96</v>
       </c>
       <c r="AA53" s="12" t="n">
-        <v>122.98</v>
+        <v>18.48</v>
       </c>
       <c r="AB53" s="12" t="n">
         <v>0</v>
@@ -26822,10 +26834,10 @@
         <v>74</v>
       </c>
       <c r="AW53" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX53" s="10" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="AY53" s="14" t="s">
         <v>75</v>
@@ -26852,16 +26864,16 @@
         <v>75</v>
       </c>
       <c r="BG53" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH53" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI53" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ53" s="9" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="BK53" s="9" t="s">
         <v>75</v>
@@ -26870,39 +26882,39 @@
         <v>75</v>
       </c>
       <c r="BM53" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="n">
-        <v>307044</v>
+        <v>307242</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="C54" s="9"/>
       <c r="D54" s="9"/>
       <c r="E54" s="9"/>
       <c r="F54" s="9" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G54" s="10" t="s">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="H54" s="9" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>78</v>
+        <v>285</v>
       </c>
       <c r="K54" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>760.8</v>
+        <v>1887.04</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>0</v>
@@ -26911,43 +26923,43 @@
         <v>1</v>
       </c>
       <c r="O54" s="12" t="n">
-        <v>760.8</v>
+        <v>1887.04</v>
       </c>
       <c r="P54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q54" s="13" t="n">
-        <v>0.09178</v>
+        <v>0.007832</v>
       </c>
       <c r="R54" s="12" t="n">
-        <v>14.15</v>
+        <v>1.9</v>
       </c>
       <c r="S54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T54" s="14" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="U54" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V54" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W54" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X54" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Y54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z54" s="12" t="n">
-        <v>760.8</v>
+        <v>1887.04</v>
       </c>
       <c r="AA54" s="12" t="n">
-        <v>53.26</v>
+        <v>132.09</v>
       </c>
       <c r="AB54" s="12" t="n">
         <v>0</v>
@@ -27013,10 +27025,10 @@
         <v>74</v>
       </c>
       <c r="AW54" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX54" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AY54" s="14" t="s">
         <v>75</v>
@@ -27043,16 +27055,16 @@
         <v>75</v>
       </c>
       <c r="BG54" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH54" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI54" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ54" s="9" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="BK54" s="9" t="s">
         <v>75</v>
@@ -27061,39 +27073,39 @@
         <v>75</v>
       </c>
       <c r="BM54" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="n">
-        <v>307045</v>
+        <v>307265</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="9"/>
       <c r="E55" s="9"/>
       <c r="F55" s="9" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="G55" s="10" t="s">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="K55" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>1332.17</v>
+        <v>3702.49</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
@@ -27102,43 +27114,43 @@
         <v>1</v>
       </c>
       <c r="O55" s="12" t="n">
-        <v>1332.17</v>
+        <v>3437.49</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q55" s="13" t="n">
-        <v>0.017488</v>
+        <v>0</v>
       </c>
       <c r="R55" s="12" t="n">
-        <v>8.85</v>
+        <v>3.5</v>
       </c>
       <c r="S55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T55" s="14" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="U55" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V55" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W55" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X55" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Y55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z55" s="12" t="n">
-        <v>1332.17</v>
+        <v>3702.49</v>
       </c>
       <c r="AA55" s="12" t="n">
-        <v>53.29</v>
+        <v>259.17</v>
       </c>
       <c r="AB55" s="12" t="n">
         <v>0</v>
@@ -27204,10 +27216,10 @@
         <v>74</v>
       </c>
       <c r="AW55" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX55" s="10" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AY55" s="14" t="s">
         <v>75</v>
@@ -27234,16 +27246,16 @@
         <v>75</v>
       </c>
       <c r="BG55" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH55" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI55" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ55" s="9" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="BK55" s="9" t="s">
         <v>75</v>
@@ -27252,84 +27264,84 @@
         <v>75</v>
       </c>
       <c r="BM55" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="n">
-        <v>307046</v>
+        <v>307278</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="C56" s="9"/>
       <c r="D56" s="9"/>
       <c r="E56" s="9"/>
       <c r="F56" s="9" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="G56" s="10" t="s">
-        <v>185</v>
+        <v>66</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>263</v>
+        <v>226</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="K56" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>39549.24</v>
+        <v>29709.55</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="O56" s="12" t="n">
-        <v>36406.48</v>
+        <v>29280.46</v>
       </c>
       <c r="P56" s="12" t="n">
-        <v>1877.94</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="13" t="n">
-        <v>2.71203</v>
+        <v>0.69578</v>
       </c>
       <c r="R56" s="12" t="n">
-        <v>520.9</v>
+        <v>130.96</v>
       </c>
       <c r="S56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T56" s="14" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="U56" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V56" s="12" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="W56" s="9" t="s">
-        <v>73</v>
+        <v>239</v>
       </c>
       <c r="X56" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Y56" s="12" t="n">
-        <v>1264.82</v>
+        <v>429.09</v>
       </c>
       <c r="Z56" s="12" t="n">
-        <v>38284.42</v>
+        <v>29280.46</v>
       </c>
       <c r="AA56" s="12" t="n">
-        <v>2330.38</v>
+        <v>1794.18</v>
       </c>
       <c r="AB56" s="12" t="n">
         <v>0</v>
@@ -27395,10 +27407,10 @@
         <v>74</v>
       </c>
       <c r="AW56" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX56" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY56" s="14" t="s">
         <v>75</v>
@@ -27425,16 +27437,16 @@
         <v>75</v>
       </c>
       <c r="BG56" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BH56" s="14" t="s">
         <v>75</v>
       </c>
       <c r="BI56" s="9" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="BJ56" s="9" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="BK56" s="9" t="s">
         <v>75</v>
@@ -27443,522 +27455,400 @@
         <v>75</v>
       </c>
       <c r="BM56" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="n">
-        <v>307048</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>154</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>263</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>7912.1</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" s="12" t="n">
-        <v>7912.1</v>
-      </c>
-      <c r="P57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="U57" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V57" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W57" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X57" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="Y57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="12" t="n">
-        <v>7912.1</v>
-      </c>
-      <c r="AA57" s="12" t="n">
-        <v>553.85</v>
-      </c>
-      <c r="AB57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW57" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="AX57" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AY57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG57" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BH57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI57" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="BJ57" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="BK57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM57" s="16" t="s">
-        <v>80</v>
-      </c>
+      <c r="A57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4"/>
+    <row r="58" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="B58" s="17"/>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17"/>
+      <c r="N58" s="17"/>
+      <c r="O58" s="17"/>
+      <c r="P58" s="17"/>
+      <c r="Q58" s="17"/>
+      <c r="R58" s="17"/>
+      <c r="S58" s="17"/>
+      <c r="T58" s="17"/>
+      <c r="U58" s="17"/>
+      <c r="V58" s="17"/>
     </row>
     <row r="59" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="B59" s="17"/>
-      <c r="C59" s="17"/>
-      <c r="D59" s="17"/>
-      <c r="E59" s="17"/>
-      <c r="F59" s="17"/>
-      <c r="G59" s="17"/>
-      <c r="H59" s="17"/>
-      <c r="I59" s="17"/>
-      <c r="J59" s="17"/>
-      <c r="K59" s="17"/>
-      <c r="L59" s="17"/>
-      <c r="M59" s="17"/>
-      <c r="N59" s="17"/>
-      <c r="O59" s="17"/>
-      <c r="P59" s="17"/>
-      <c r="Q59" s="17"/>
-      <c r="R59" s="17"/>
-      <c r="S59" s="17"/>
-      <c r="T59" s="17"/>
-      <c r="U59" s="17"/>
-      <c r="V59" s="17"/>
+      <c r="A59" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="E59" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F59" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G59" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H59" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I59" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="J59" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K59" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L59" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M59" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="N59" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O59" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P59" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q59" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R59" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S59" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="T59" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="U59" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V59" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="60" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="B60" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C60" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F60" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G60" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I60" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="J60" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K60" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L60" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M60" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="N60" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O60" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P60" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q60" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R60" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S60" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="T60" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="U60" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V60" s="18" t="s">
-        <v>37</v>
+    <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="19" t="n">
+        <v>52</v>
+      </c>
+      <c r="B60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="19" t="n">
+        <v>2142.94</v>
+      </c>
+      <c r="D60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="19" t="n">
+        <v>13331.52</v>
+      </c>
+      <c r="F60" s="19" t="n">
+        <v>591961.42</v>
+      </c>
+      <c r="G60" s="19" t="n">
+        <v>38931.23</v>
+      </c>
+      <c r="H60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="19" t="n">
+        <v>638354.93</v>
+      </c>
+      <c r="L60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" s="20" t="n">
+        <v>11.286207</v>
+      </c>
+      <c r="S60" s="19" t="n">
+        <v>622880.47</v>
+      </c>
+      <c r="T60" s="19" t="n">
+        <v>638354.93</v>
+      </c>
+      <c r="U60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="19" t="n">
-        <v>53</v>
-      </c>
-      <c r="B61" s="19" t="n">
-        <v>60.1</v>
-      </c>
-      <c r="C61" s="19" t="n">
-        <v>1962.94</v>
-      </c>
-      <c r="D61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="19" t="n">
-        <v>17482.18</v>
-      </c>
-      <c r="F61" s="19" t="n">
-        <v>493496.63</v>
-      </c>
-      <c r="G61" s="19" t="n">
-        <v>30997.96</v>
-      </c>
-      <c r="H61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="19" t="n">
-        <v>543204.22</v>
-      </c>
-      <c r="L61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R61" s="20" t="n">
-        <v>19.384213</v>
-      </c>
-      <c r="S61" s="19" t="n">
-        <v>523819.2</v>
-      </c>
-      <c r="T61" s="19" t="n">
-        <v>543204.22</v>
-      </c>
-      <c r="U61" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" s="19" t="n">
-        <v>0</v>
+    <row r="61" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E61" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F61" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G61" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H61" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I61" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J61" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K61" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="L61" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="M61" s="18" t="s">
+        <v>306</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C62" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G62" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H62" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I62" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J62" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K62" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="L62" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="M62" s="18" t="s">
-        <v>302</v>
+    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="19" t="n">
+        <v>2973.66</v>
+      </c>
+      <c r="B62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="19" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="E62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="19" t="n">
-        <v>2060.75</v>
-      </c>
-      <c r="B63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="19" t="n">
-        <v>49.78</v>
-      </c>
-      <c r="E63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A63" s="4"/>
     </row>
-    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4"/>
+    <row r="64" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="21"/>
+      <c r="H64" s="21"/>
+      <c r="I64" s="21"/>
+      <c r="J64" s="21"/>
+      <c r="K64" s="21"/>
+      <c r="L64" s="21"/>
+      <c r="M64" s="21"/>
+      <c r="N64" s="21"/>
+      <c r="O64" s="21"/>
+      <c r="P64" s="21"/>
+      <c r="Q64" s="21"/>
+      <c r="R64" s="21"/>
+      <c r="S64" s="21"/>
+      <c r="T64" s="21"/>
+      <c r="U64" s="21"/>
+      <c r="V64" s="21"/>
+      <c r="W64" s="21"/>
+      <c r="X64" s="21"/>
+      <c r="Y64" s="21"/>
+      <c r="Z64" s="21"/>
+      <c r="AA64" s="21"/>
+      <c r="AB64" s="21"/>
+      <c r="AC64" s="21"/>
+      <c r="AD64" s="21"/>
+      <c r="AE64" s="21"/>
+      <c r="AF64" s="21"/>
+      <c r="AG64" s="21"/>
+      <c r="AH64" s="21"/>
+      <c r="AI64" s="21"/>
+      <c r="AJ64" s="21"/>
+      <c r="AK64" s="21"/>
+      <c r="AL64" s="21"/>
+      <c r="AM64" s="21"/>
+      <c r="AN64" s="21"/>
+      <c r="AO64" s="21"/>
+      <c r="AP64" s="21"/>
+      <c r="AQ64" s="21"/>
+      <c r="AR64" s="21"/>
+      <c r="AS64" s="21"/>
+      <c r="AT64" s="21"/>
+      <c r="AU64" s="21"/>
+      <c r="AV64" s="21"/>
+      <c r="AW64" s="21"/>
+      <c r="AX64" s="21"/>
+      <c r="AY64" s="21"/>
+      <c r="AZ64" s="21"/>
+      <c r="BA64" s="21"/>
+      <c r="BB64" s="21"/>
+      <c r="BC64" s="21"/>
+      <c r="BD64" s="21"/>
+      <c r="BE64" s="21"/>
+      <c r="BF64" s="21"/>
+      <c r="BG64" s="21"/>
+      <c r="BH64" s="21"/>
+      <c r="BI64" s="21"/>
+      <c r="BJ64" s="21"/>
+      <c r="BK64" s="21"/>
+      <c r="BL64" s="21"/>
+      <c r="BM64" s="21"/>
     </row>
-    <row r="65" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="B65" s="21"/>
-      <c r="C65" s="21"/>
-      <c r="D65" s="21"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="21"/>
-      <c r="G65" s="21"/>
-      <c r="H65" s="21"/>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21"/>
-      <c r="K65" s="21"/>
-      <c r="L65" s="21"/>
-      <c r="M65" s="21"/>
-      <c r="N65" s="21"/>
-      <c r="O65" s="21"/>
-      <c r="P65" s="21"/>
-      <c r="Q65" s="21"/>
-      <c r="R65" s="21"/>
-      <c r="S65" s="21"/>
-      <c r="T65" s="21"/>
-      <c r="U65" s="21"/>
-      <c r="V65" s="21"/>
-      <c r="W65" s="21"/>
-      <c r="X65" s="21"/>
-      <c r="Y65" s="21"/>
-      <c r="Z65" s="21"/>
-      <c r="AA65" s="21"/>
-      <c r="AB65" s="21"/>
-      <c r="AC65" s="21"/>
-      <c r="AD65" s="21"/>
-      <c r="AE65" s="21"/>
-      <c r="AF65" s="21"/>
-      <c r="AG65" s="21"/>
-      <c r="AH65" s="21"/>
-      <c r="AI65" s="21"/>
-      <c r="AJ65" s="21"/>
-      <c r="AK65" s="21"/>
-      <c r="AL65" s="21"/>
-      <c r="AM65" s="21"/>
-      <c r="AN65" s="21"/>
-      <c r="AO65" s="21"/>
-      <c r="AP65" s="21"/>
-      <c r="AQ65" s="21"/>
-      <c r="AR65" s="21"/>
-      <c r="AS65" s="21"/>
-      <c r="AT65" s="21"/>
-      <c r="AU65" s="21"/>
-      <c r="AV65" s="21"/>
-      <c r="AW65" s="21"/>
-      <c r="AX65" s="21"/>
-      <c r="AY65" s="21"/>
-      <c r="AZ65" s="21"/>
-      <c r="BA65" s="21"/>
-      <c r="BB65" s="21"/>
-      <c r="BC65" s="21"/>
-      <c r="BD65" s="21"/>
-      <c r="BE65" s="21"/>
-      <c r="BF65" s="21"/>
-      <c r="BG65" s="21"/>
-      <c r="BH65" s="21"/>
-      <c r="BI65" s="21"/>
-      <c r="BJ65" s="21"/>
-      <c r="BK65" s="21"/>
-      <c r="BL65" s="21"/>
-      <c r="BM65" s="21"/>
+    <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
+      <c r="AB65" s="4"/>
+      <c r="AC65" s="4"/>
+      <c r="AD65" s="4"/>
+      <c r="AE65" s="4"/>
+      <c r="AF65" s="4"/>
+      <c r="AG65" s="4"/>
+      <c r="AH65" s="4"/>
+      <c r="AI65" s="4"/>
+      <c r="AJ65" s="4"/>
+      <c r="AK65" s="4"/>
+      <c r="AL65" s="4"/>
+      <c r="AM65" s="4"/>
+      <c r="AN65" s="4"/>
+      <c r="AO65" s="4"/>
+      <c r="AP65" s="4"/>
+      <c r="AQ65" s="4"/>
+      <c r="AR65" s="4"/>
+      <c r="AS65" s="4"/>
+      <c r="AT65" s="4"/>
+      <c r="AU65" s="4"/>
+      <c r="AV65" s="4"/>
+      <c r="AW65" s="4"/>
+      <c r="AX65" s="4"/>
+      <c r="AY65" s="4"/>
+      <c r="AZ65" s="4"/>
+      <c r="BA65" s="4"/>
+      <c r="BB65" s="4"/>
+      <c r="BC65" s="4"/>
+      <c r="BD65" s="4"/>
+      <c r="BE65" s="4"/>
+      <c r="BF65" s="4"/>
+      <c r="BG65" s="4"/>
+      <c r="BH65" s="4"/>
+      <c r="BI65" s="4"/>
+      <c r="BJ65" s="4"/>
+      <c r="BK65" s="4"/>
+      <c r="BL65" s="4"/>
+      <c r="BM65" s="4"/>
     </row>
     <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="4" t="s">
-        <v>75</v>
+        <v>308</v>
       </c>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -28027,7 +27917,7 @@
     </row>
     <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="4" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -28096,7 +27986,7 @@
     </row>
     <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="4" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -28165,7 +28055,7 @@
     </row>
     <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>306</v>
+        <v>22</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -28234,7 +28124,7 @@
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>22</v>
+        <v>311</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -28303,7 +28193,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -28372,7 +28262,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -28441,7 +28331,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -28510,7 +28400,7 @@
     </row>
     <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -28577,77 +28467,8 @@
       <c r="BL74" s="4"/>
       <c r="BM74" s="4"/>
     </row>
-    <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="4"/>
-      <c r="U75" s="4"/>
-      <c r="V75" s="4"/>
-      <c r="W75" s="4"/>
-      <c r="X75" s="4"/>
-      <c r="Y75" s="4"/>
-      <c r="Z75" s="4"/>
-      <c r="AA75" s="4"/>
-      <c r="AB75" s="4"/>
-      <c r="AC75" s="4"/>
-      <c r="AD75" s="4"/>
-      <c r="AE75" s="4"/>
-      <c r="AF75" s="4"/>
-      <c r="AG75" s="4"/>
-      <c r="AH75" s="4"/>
-      <c r="AI75" s="4"/>
-      <c r="AJ75" s="4"/>
-      <c r="AK75" s="4"/>
-      <c r="AL75" s="4"/>
-      <c r="AM75" s="4"/>
-      <c r="AN75" s="4"/>
-      <c r="AO75" s="4"/>
-      <c r="AP75" s="4"/>
-      <c r="AQ75" s="4"/>
-      <c r="AR75" s="4"/>
-      <c r="AS75" s="4"/>
-      <c r="AT75" s="4"/>
-      <c r="AU75" s="4"/>
-      <c r="AV75" s="4"/>
-      <c r="AW75" s="4"/>
-      <c r="AX75" s="4"/>
-      <c r="AY75" s="4"/>
-      <c r="AZ75" s="4"/>
-      <c r="BA75" s="4"/>
-      <c r="BB75" s="4"/>
-      <c r="BC75" s="4"/>
-      <c r="BD75" s="4"/>
-      <c r="BE75" s="4"/>
-      <c r="BF75" s="4"/>
-      <c r="BG75" s="4"/>
-      <c r="BH75" s="4"/>
-      <c r="BI75" s="4"/>
-      <c r="BJ75" s="4"/>
-      <c r="BK75" s="4"/>
-      <c r="BL75" s="4"/>
-      <c r="BM75" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="69">
+  <mergeCells count="68">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -28704,8 +28525,8 @@
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="A59:V59"/>
+    <mergeCell ref="A58:V58"/>
+    <mergeCell ref="A64:BM64"/>
     <mergeCell ref="A65:BM65"/>
     <mergeCell ref="A66:BM66"/>
     <mergeCell ref="A67:BM67"/>
@@ -28716,7 +28537,6 @@
     <mergeCell ref="A72:BM72"/>
     <mergeCell ref="A73:BM73"/>
     <mergeCell ref="A74:BM74"/>
-    <mergeCell ref="A75:BM75"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2192" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="332">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 14/05/2026 07:28:18</t>
+    <t xml:space="preserve">Emitido em: 15/05/2026 07:59:54</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -911,6 +911,54 @@
   </si>
   <si>
     <t xml:space="preserve">42260581604803000157550010008671441582155041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">750 - COPLAS INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.314,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260567718726000135550010002002511236212733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.078,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006397451885129080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640.215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.963,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006402151526143499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640.584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.104,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006405841317875822</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17156,7 +17204,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM74"/>
+  <dimension ref="A1:BM78"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -27459,603 +27507,1091 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4"/>
+      <c r="A57" s="8" t="n">
+        <v>307297</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H57" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="I57" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="J57" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="K57" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L57" s="12" t="n">
+        <v>3314.33</v>
+      </c>
+      <c r="M57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" s="12" t="n">
+        <v>3210</v>
+      </c>
+      <c r="P57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="U57" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V57" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="W57" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X57" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y57" s="12" t="n">
+        <v>104.33</v>
+      </c>
+      <c r="Z57" s="12" t="n">
+        <v>3210</v>
+      </c>
+      <c r="AA57" s="12" t="n">
+        <v>224.7</v>
+      </c>
+      <c r="AB57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV57" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW57" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AX57" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF57" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG57" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH57" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI57" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ57" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="BK57" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL57" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM57" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="58" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="B58" s="17"/>
-      <c r="C58" s="17"/>
-      <c r="D58" s="17"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-      <c r="K58" s="17"/>
-      <c r="L58" s="17"/>
-      <c r="M58" s="17"/>
-      <c r="N58" s="17"/>
-      <c r="O58" s="17"/>
-      <c r="P58" s="17"/>
-      <c r="Q58" s="17"/>
-      <c r="R58" s="17"/>
-      <c r="S58" s="17"/>
-      <c r="T58" s="17"/>
-      <c r="U58" s="17"/>
-      <c r="V58" s="17"/>
+    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="8" t="n">
+        <v>307330</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H58" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="J58" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="K58" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L58" s="12" t="n">
+        <v>7078.63</v>
+      </c>
+      <c r="M58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O58" s="12" t="n">
+        <v>6646.6</v>
+      </c>
+      <c r="P58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="13" t="n">
+        <v>0.0425</v>
+      </c>
+      <c r="R58" s="12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="S58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="14" t="s">
+        <v>304</v>
+      </c>
+      <c r="U58" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V58" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W58" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X58" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y58" s="12" t="n">
+        <v>432.03</v>
+      </c>
+      <c r="Z58" s="12" t="n">
+        <v>6646.6</v>
+      </c>
+      <c r="AA58" s="12" t="n">
+        <v>465.26</v>
+      </c>
+      <c r="AB58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV58" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW58" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AX58" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF58" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG58" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH58" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI58" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ58" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="BK58" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL58" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM58" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="59" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="B59" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C59" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D59" s="18" t="s">
+    <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="n">
+        <v>307334</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="E59" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F59" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G59" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H59" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I59" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="J59" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K59" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L59" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M59" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="N59" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O59" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P59" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q59" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R59" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S59" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="T59" s="18" t="s">
-        <v>303</v>
-      </c>
-      <c r="U59" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V59" s="18" t="s">
-        <v>37</v>
+      <c r="I59" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="J59" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L59" s="12" t="n">
+        <v>4963.92</v>
+      </c>
+      <c r="M59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O59" s="12" t="n">
+        <v>4963.92</v>
+      </c>
+      <c r="P59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="13" t="n">
+        <v>0.029904</v>
+      </c>
+      <c r="R59" s="12" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="S59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="U59" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V59" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W59" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X59" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="12" t="n">
+        <v>4963.92</v>
+      </c>
+      <c r="AA59" s="12" t="n">
+        <v>347.47</v>
+      </c>
+      <c r="AB59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV59" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW59" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AX59" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF59" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG59" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH59" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI59" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ59" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="BK59" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL59" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM59" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="19" t="n">
-        <v>52</v>
-      </c>
-      <c r="B60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="19" t="n">
+      <c r="A60" s="8" t="n">
+        <v>307356</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9" t="s">
+        <v>310</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H60" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="J60" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L60" s="12" t="n">
+        <v>2104.02</v>
+      </c>
+      <c r="M60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O60" s="12" t="n">
+        <v>2104.02</v>
+      </c>
+      <c r="P60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="13" t="n">
+        <v>0.005548</v>
+      </c>
+      <c r="R60" s="12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="U60" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V60" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W60" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X60" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="Y60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="12" t="n">
+        <v>2104.02</v>
+      </c>
+      <c r="AA60" s="12" t="n">
+        <v>147.28</v>
+      </c>
+      <c r="AB60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV60" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW60" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AX60" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF60" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG60" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH60" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI60" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ60" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="BK60" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL60" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM60" s="16" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="B62" s="17"/>
+      <c r="C62" s="17"/>
+      <c r="D62" s="17"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
+      <c r="L62" s="17"/>
+      <c r="M62" s="17"/>
+      <c r="N62" s="17"/>
+      <c r="O62" s="17"/>
+      <c r="P62" s="17"/>
+      <c r="Q62" s="17"/>
+      <c r="R62" s="17"/>
+      <c r="S62" s="17"/>
+      <c r="T62" s="17"/>
+      <c r="U62" s="17"/>
+      <c r="V62" s="17"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="18" t="s">
+        <v>314</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="E63" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F63" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G63" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H63" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="J63" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K63" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L63" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M63" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="N63" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O63" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P63" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q63" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R63" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S63" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="T63" s="18" t="s">
+        <v>319</v>
+      </c>
+      <c r="U63" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V63" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="19" t="n">
+        <v>56</v>
+      </c>
+      <c r="B64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="19" t="n">
         <v>2142.94</v>
       </c>
-      <c r="D60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="19" t="n">
-        <v>13331.52</v>
-      </c>
-      <c r="F60" s="19" t="n">
-        <v>591961.42</v>
-      </c>
-      <c r="G60" s="19" t="n">
-        <v>38931.23</v>
-      </c>
-      <c r="H60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="19" t="n">
-        <v>638354.93</v>
-      </c>
-      <c r="L60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="20" t="n">
-        <v>11.286207</v>
-      </c>
-      <c r="S60" s="19" t="n">
-        <v>622880.47</v>
-      </c>
-      <c r="T60" s="19" t="n">
-        <v>638354.93</v>
-      </c>
-      <c r="U60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" s="19" t="n">
+      <c r="D64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="19" t="n">
+        <v>13867.88</v>
+      </c>
+      <c r="F64" s="19" t="n">
+        <v>608885.96</v>
+      </c>
+      <c r="G64" s="19" t="n">
+        <v>40115.94</v>
+      </c>
+      <c r="H64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="19" t="n">
+        <v>655815.83</v>
+      </c>
+      <c r="L64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" s="20" t="n">
+        <v>11.364159</v>
+      </c>
+      <c r="S64" s="19" t="n">
+        <v>639805.01</v>
+      </c>
+      <c r="T64" s="19" t="n">
+        <v>655815.83</v>
+      </c>
+      <c r="U64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="19" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="18" t="s">
+    <row r="65" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B61" s="18" t="s">
+      <c r="B65" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="C65" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="D65" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E61" s="18" t="s">
+      <c r="E65" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="F61" s="18" t="s">
+      <c r="F65" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="G61" s="18" t="s">
+      <c r="G65" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H61" s="18" t="s">
+      <c r="H65" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I61" s="18" t="s">
+      <c r="I65" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="J61" s="18" t="s">
+      <c r="J65" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="K61" s="18" t="s">
-        <v>304</v>
-      </c>
-      <c r="L61" s="18" t="s">
-        <v>305</v>
-      </c>
-      <c r="M61" s="18" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="19" t="n">
-        <v>2973.66</v>
-      </c>
-      <c r="B62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="19" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="E62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4"/>
-    </row>
-    <row r="64" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="21" t="s">
-        <v>307</v>
-      </c>
-      <c r="B64" s="21"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="21"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="21"/>
-      <c r="G64" s="21"/>
-      <c r="H64" s="21"/>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21"/>
-      <c r="K64" s="21"/>
-      <c r="L64" s="21"/>
-      <c r="M64" s="21"/>
-      <c r="N64" s="21"/>
-      <c r="O64" s="21"/>
-      <c r="P64" s="21"/>
-      <c r="Q64" s="21"/>
-      <c r="R64" s="21"/>
-      <c r="S64" s="21"/>
-      <c r="T64" s="21"/>
-      <c r="U64" s="21"/>
-      <c r="V64" s="21"/>
-      <c r="W64" s="21"/>
-      <c r="X64" s="21"/>
-      <c r="Y64" s="21"/>
-      <c r="Z64" s="21"/>
-      <c r="AA64" s="21"/>
-      <c r="AB64" s="21"/>
-      <c r="AC64" s="21"/>
-      <c r="AD64" s="21"/>
-      <c r="AE64" s="21"/>
-      <c r="AF64" s="21"/>
-      <c r="AG64" s="21"/>
-      <c r="AH64" s="21"/>
-      <c r="AI64" s="21"/>
-      <c r="AJ64" s="21"/>
-      <c r="AK64" s="21"/>
-      <c r="AL64" s="21"/>
-      <c r="AM64" s="21"/>
-      <c r="AN64" s="21"/>
-      <c r="AO64" s="21"/>
-      <c r="AP64" s="21"/>
-      <c r="AQ64" s="21"/>
-      <c r="AR64" s="21"/>
-      <c r="AS64" s="21"/>
-      <c r="AT64" s="21"/>
-      <c r="AU64" s="21"/>
-      <c r="AV64" s="21"/>
-      <c r="AW64" s="21"/>
-      <c r="AX64" s="21"/>
-      <c r="AY64" s="21"/>
-      <c r="AZ64" s="21"/>
-      <c r="BA64" s="21"/>
-      <c r="BB64" s="21"/>
-      <c r="BC64" s="21"/>
-      <c r="BD64" s="21"/>
-      <c r="BE64" s="21"/>
-      <c r="BF64" s="21"/>
-      <c r="BG64" s="21"/>
-      <c r="BH64" s="21"/>
-      <c r="BI64" s="21"/>
-      <c r="BJ64" s="21"/>
-      <c r="BK64" s="21"/>
-      <c r="BL64" s="21"/>
-      <c r="BM64" s="21"/>
-    </row>
-    <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4"/>
-      <c r="U65" s="4"/>
-      <c r="V65" s="4"/>
-      <c r="W65" s="4"/>
-      <c r="X65" s="4"/>
-      <c r="Y65" s="4"/>
-      <c r="Z65" s="4"/>
-      <c r="AA65" s="4"/>
-      <c r="AB65" s="4"/>
-      <c r="AC65" s="4"/>
-      <c r="AD65" s="4"/>
-      <c r="AE65" s="4"/>
-      <c r="AF65" s="4"/>
-      <c r="AG65" s="4"/>
-      <c r="AH65" s="4"/>
-      <c r="AI65" s="4"/>
-      <c r="AJ65" s="4"/>
-      <c r="AK65" s="4"/>
-      <c r="AL65" s="4"/>
-      <c r="AM65" s="4"/>
-      <c r="AN65" s="4"/>
-      <c r="AO65" s="4"/>
-      <c r="AP65" s="4"/>
-      <c r="AQ65" s="4"/>
-      <c r="AR65" s="4"/>
-      <c r="AS65" s="4"/>
-      <c r="AT65" s="4"/>
-      <c r="AU65" s="4"/>
-      <c r="AV65" s="4"/>
-      <c r="AW65" s="4"/>
-      <c r="AX65" s="4"/>
-      <c r="AY65" s="4"/>
-      <c r="AZ65" s="4"/>
-      <c r="BA65" s="4"/>
-      <c r="BB65" s="4"/>
-      <c r="BC65" s="4"/>
-      <c r="BD65" s="4"/>
-      <c r="BE65" s="4"/>
-      <c r="BF65" s="4"/>
-      <c r="BG65" s="4"/>
-      <c r="BH65" s="4"/>
-      <c r="BI65" s="4"/>
-      <c r="BJ65" s="4"/>
-      <c r="BK65" s="4"/>
-      <c r="BL65" s="4"/>
-      <c r="BM65" s="4"/>
+      <c r="K65" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="L65" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="M65" s="18" t="s">
+        <v>322</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
-      <c r="Y66" s="4"/>
-      <c r="Z66" s="4"/>
-      <c r="AA66" s="4"/>
-      <c r="AB66" s="4"/>
-      <c r="AC66" s="4"/>
-      <c r="AD66" s="4"/>
-      <c r="AE66" s="4"/>
-      <c r="AF66" s="4"/>
-      <c r="AG66" s="4"/>
-      <c r="AH66" s="4"/>
-      <c r="AI66" s="4"/>
-      <c r="AJ66" s="4"/>
-      <c r="AK66" s="4"/>
-      <c r="AL66" s="4"/>
-      <c r="AM66" s="4"/>
-      <c r="AN66" s="4"/>
-      <c r="AO66" s="4"/>
-      <c r="AP66" s="4"/>
-      <c r="AQ66" s="4"/>
-      <c r="AR66" s="4"/>
-      <c r="AS66" s="4"/>
-      <c r="AT66" s="4"/>
-      <c r="AU66" s="4"/>
-      <c r="AV66" s="4"/>
-      <c r="AW66" s="4"/>
-      <c r="AX66" s="4"/>
-      <c r="AY66" s="4"/>
-      <c r="AZ66" s="4"/>
-      <c r="BA66" s="4"/>
-      <c r="BB66" s="4"/>
-      <c r="BC66" s="4"/>
-      <c r="BD66" s="4"/>
-      <c r="BE66" s="4"/>
-      <c r="BF66" s="4"/>
-      <c r="BG66" s="4"/>
-      <c r="BH66" s="4"/>
-      <c r="BI66" s="4"/>
-      <c r="BJ66" s="4"/>
-      <c r="BK66" s="4"/>
-      <c r="BL66" s="4"/>
-      <c r="BM66" s="4"/>
+      <c r="A66" s="19" t="n">
+        <v>2991.18</v>
+      </c>
+      <c r="B66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="19" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="E66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="4"/>
-      <c r="U67" s="4"/>
-      <c r="V67" s="4"/>
-      <c r="W67" s="4"/>
-      <c r="X67" s="4"/>
-      <c r="Y67" s="4"/>
-      <c r="Z67" s="4"/>
-      <c r="AA67" s="4"/>
-      <c r="AB67" s="4"/>
-      <c r="AC67" s="4"/>
-      <c r="AD67" s="4"/>
-      <c r="AE67" s="4"/>
-      <c r="AF67" s="4"/>
-      <c r="AG67" s="4"/>
-      <c r="AH67" s="4"/>
-      <c r="AI67" s="4"/>
-      <c r="AJ67" s="4"/>
-      <c r="AK67" s="4"/>
-      <c r="AL67" s="4"/>
-      <c r="AM67" s="4"/>
-      <c r="AN67" s="4"/>
-      <c r="AO67" s="4"/>
-      <c r="AP67" s="4"/>
-      <c r="AQ67" s="4"/>
-      <c r="AR67" s="4"/>
-      <c r="AS67" s="4"/>
-      <c r="AT67" s="4"/>
-      <c r="AU67" s="4"/>
-      <c r="AV67" s="4"/>
-      <c r="AW67" s="4"/>
-      <c r="AX67" s="4"/>
-      <c r="AY67" s="4"/>
-      <c r="AZ67" s="4"/>
-      <c r="BA67" s="4"/>
-      <c r="BB67" s="4"/>
-      <c r="BC67" s="4"/>
-      <c r="BD67" s="4"/>
-      <c r="BE67" s="4"/>
-      <c r="BF67" s="4"/>
-      <c r="BG67" s="4"/>
-      <c r="BH67" s="4"/>
-      <c r="BI67" s="4"/>
-      <c r="BJ67" s="4"/>
-      <c r="BK67" s="4"/>
-      <c r="BL67" s="4"/>
-      <c r="BM67" s="4"/>
+      <c r="A67" s="4"/>
     </row>
-    <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="4"/>
-      <c r="U68" s="4"/>
-      <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
-      <c r="X68" s="4"/>
-      <c r="Y68" s="4"/>
-      <c r="Z68" s="4"/>
-      <c r="AA68" s="4"/>
-      <c r="AB68" s="4"/>
-      <c r="AC68" s="4"/>
-      <c r="AD68" s="4"/>
-      <c r="AE68" s="4"/>
-      <c r="AF68" s="4"/>
-      <c r="AG68" s="4"/>
-      <c r="AH68" s="4"/>
-      <c r="AI68" s="4"/>
-      <c r="AJ68" s="4"/>
-      <c r="AK68" s="4"/>
-      <c r="AL68" s="4"/>
-      <c r="AM68" s="4"/>
-      <c r="AN68" s="4"/>
-      <c r="AO68" s="4"/>
-      <c r="AP68" s="4"/>
-      <c r="AQ68" s="4"/>
-      <c r="AR68" s="4"/>
-      <c r="AS68" s="4"/>
-      <c r="AT68" s="4"/>
-      <c r="AU68" s="4"/>
-      <c r="AV68" s="4"/>
-      <c r="AW68" s="4"/>
-      <c r="AX68" s="4"/>
-      <c r="AY68" s="4"/>
-      <c r="AZ68" s="4"/>
-      <c r="BA68" s="4"/>
-      <c r="BB68" s="4"/>
-      <c r="BC68" s="4"/>
-      <c r="BD68" s="4"/>
-      <c r="BE68" s="4"/>
-      <c r="BF68" s="4"/>
-      <c r="BG68" s="4"/>
-      <c r="BH68" s="4"/>
-      <c r="BI68" s="4"/>
-      <c r="BJ68" s="4"/>
-      <c r="BK68" s="4"/>
-      <c r="BL68" s="4"/>
-      <c r="BM68" s="4"/>
+    <row r="68" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="B68" s="21"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="21"/>
+      <c r="E68" s="21"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="21"/>
+      <c r="H68" s="21"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="21"/>
+      <c r="K68" s="21"/>
+      <c r="L68" s="21"/>
+      <c r="M68" s="21"/>
+      <c r="N68" s="21"/>
+      <c r="O68" s="21"/>
+      <c r="P68" s="21"/>
+      <c r="Q68" s="21"/>
+      <c r="R68" s="21"/>
+      <c r="S68" s="21"/>
+      <c r="T68" s="21"/>
+      <c r="U68" s="21"/>
+      <c r="V68" s="21"/>
+      <c r="W68" s="21"/>
+      <c r="X68" s="21"/>
+      <c r="Y68" s="21"/>
+      <c r="Z68" s="21"/>
+      <c r="AA68" s="21"/>
+      <c r="AB68" s="21"/>
+      <c r="AC68" s="21"/>
+      <c r="AD68" s="21"/>
+      <c r="AE68" s="21"/>
+      <c r="AF68" s="21"/>
+      <c r="AG68" s="21"/>
+      <c r="AH68" s="21"/>
+      <c r="AI68" s="21"/>
+      <c r="AJ68" s="21"/>
+      <c r="AK68" s="21"/>
+      <c r="AL68" s="21"/>
+      <c r="AM68" s="21"/>
+      <c r="AN68" s="21"/>
+      <c r="AO68" s="21"/>
+      <c r="AP68" s="21"/>
+      <c r="AQ68" s="21"/>
+      <c r="AR68" s="21"/>
+      <c r="AS68" s="21"/>
+      <c r="AT68" s="21"/>
+      <c r="AU68" s="21"/>
+      <c r="AV68" s="21"/>
+      <c r="AW68" s="21"/>
+      <c r="AX68" s="21"/>
+      <c r="AY68" s="21"/>
+      <c r="AZ68" s="21"/>
+      <c r="BA68" s="21"/>
+      <c r="BB68" s="21"/>
+      <c r="BC68" s="21"/>
+      <c r="BD68" s="21"/>
+      <c r="BE68" s="21"/>
+      <c r="BF68" s="21"/>
+      <c r="BG68" s="21"/>
+      <c r="BH68" s="21"/>
+      <c r="BI68" s="21"/>
+      <c r="BJ68" s="21"/>
+      <c r="BK68" s="21"/>
+      <c r="BL68" s="21"/>
+      <c r="BM68" s="21"/>
     </row>
     <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="4" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -28124,7 +28660,7 @@
     </row>
     <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="4" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -28193,7 +28729,7 @@
     </row>
     <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="4" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -28262,7 +28798,7 @@
     </row>
     <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="4" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -28331,7 +28867,7 @@
     </row>
     <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="4" t="s">
-        <v>314</v>
+        <v>22</v>
       </c>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -28400,7 +28936,7 @@
     </row>
     <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="4" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -28467,8 +29003,284 @@
       <c r="BL74" s="4"/>
       <c r="BM74" s="4"/>
     </row>
+    <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="4"/>
+      <c r="H75" s="4"/>
+      <c r="I75" s="4"/>
+      <c r="J75" s="4"/>
+      <c r="K75" s="4"/>
+      <c r="L75" s="4"/>
+      <c r="M75" s="4"/>
+      <c r="N75" s="4"/>
+      <c r="O75" s="4"/>
+      <c r="P75" s="4"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="4"/>
+      <c r="T75" s="4"/>
+      <c r="U75" s="4"/>
+      <c r="V75" s="4"/>
+      <c r="W75" s="4"/>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+      <c r="AA75" s="4"/>
+      <c r="AB75" s="4"/>
+      <c r="AC75" s="4"/>
+      <c r="AD75" s="4"/>
+      <c r="AE75" s="4"/>
+      <c r="AF75" s="4"/>
+      <c r="AG75" s="4"/>
+      <c r="AH75" s="4"/>
+      <c r="AI75" s="4"/>
+      <c r="AJ75" s="4"/>
+      <c r="AK75" s="4"/>
+      <c r="AL75" s="4"/>
+      <c r="AM75" s="4"/>
+      <c r="AN75" s="4"/>
+      <c r="AO75" s="4"/>
+      <c r="AP75" s="4"/>
+      <c r="AQ75" s="4"/>
+      <c r="AR75" s="4"/>
+      <c r="AS75" s="4"/>
+      <c r="AT75" s="4"/>
+      <c r="AU75" s="4"/>
+      <c r="AV75" s="4"/>
+      <c r="AW75" s="4"/>
+      <c r="AX75" s="4"/>
+      <c r="AY75" s="4"/>
+      <c r="AZ75" s="4"/>
+      <c r="BA75" s="4"/>
+      <c r="BB75" s="4"/>
+      <c r="BC75" s="4"/>
+      <c r="BD75" s="4"/>
+      <c r="BE75" s="4"/>
+      <c r="BF75" s="4"/>
+      <c r="BG75" s="4"/>
+      <c r="BH75" s="4"/>
+      <c r="BI75" s="4"/>
+      <c r="BJ75" s="4"/>
+      <c r="BK75" s="4"/>
+      <c r="BL75" s="4"/>
+      <c r="BM75" s="4"/>
+    </row>
+    <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="4"/>
+      <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
+      <c r="G76" s="4"/>
+      <c r="H76" s="4"/>
+      <c r="I76" s="4"/>
+      <c r="J76" s="4"/>
+      <c r="K76" s="4"/>
+      <c r="L76" s="4"/>
+      <c r="M76" s="4"/>
+      <c r="N76" s="4"/>
+      <c r="O76" s="4"/>
+      <c r="P76" s="4"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="4"/>
+      <c r="T76" s="4"/>
+      <c r="U76" s="4"/>
+      <c r="V76" s="4"/>
+      <c r="W76" s="4"/>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+      <c r="AA76" s="4"/>
+      <c r="AB76" s="4"/>
+      <c r="AC76" s="4"/>
+      <c r="AD76" s="4"/>
+      <c r="AE76" s="4"/>
+      <c r="AF76" s="4"/>
+      <c r="AG76" s="4"/>
+      <c r="AH76" s="4"/>
+      <c r="AI76" s="4"/>
+      <c r="AJ76" s="4"/>
+      <c r="AK76" s="4"/>
+      <c r="AL76" s="4"/>
+      <c r="AM76" s="4"/>
+      <c r="AN76" s="4"/>
+      <c r="AO76" s="4"/>
+      <c r="AP76" s="4"/>
+      <c r="AQ76" s="4"/>
+      <c r="AR76" s="4"/>
+      <c r="AS76" s="4"/>
+      <c r="AT76" s="4"/>
+      <c r="AU76" s="4"/>
+      <c r="AV76" s="4"/>
+      <c r="AW76" s="4"/>
+      <c r="AX76" s="4"/>
+      <c r="AY76" s="4"/>
+      <c r="AZ76" s="4"/>
+      <c r="BA76" s="4"/>
+      <c r="BB76" s="4"/>
+      <c r="BC76" s="4"/>
+      <c r="BD76" s="4"/>
+      <c r="BE76" s="4"/>
+      <c r="BF76" s="4"/>
+      <c r="BG76" s="4"/>
+      <c r="BH76" s="4"/>
+      <c r="BI76" s="4"/>
+      <c r="BJ76" s="4"/>
+      <c r="BK76" s="4"/>
+      <c r="BL76" s="4"/>
+      <c r="BM76" s="4"/>
+    </row>
+    <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B77" s="4"/>
+      <c r="C77" s="4"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="4"/>
+      <c r="I77" s="4"/>
+      <c r="J77" s="4"/>
+      <c r="K77" s="4"/>
+      <c r="L77" s="4"/>
+      <c r="M77" s="4"/>
+      <c r="N77" s="4"/>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="4"/>
+      <c r="U77" s="4"/>
+      <c r="V77" s="4"/>
+      <c r="W77" s="4"/>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="4"/>
+      <c r="AB77" s="4"/>
+      <c r="AC77" s="4"/>
+      <c r="AD77" s="4"/>
+      <c r="AE77" s="4"/>
+      <c r="AF77" s="4"/>
+      <c r="AG77" s="4"/>
+      <c r="AH77" s="4"/>
+      <c r="AI77" s="4"/>
+      <c r="AJ77" s="4"/>
+      <c r="AK77" s="4"/>
+      <c r="AL77" s="4"/>
+      <c r="AM77" s="4"/>
+      <c r="AN77" s="4"/>
+      <c r="AO77" s="4"/>
+      <c r="AP77" s="4"/>
+      <c r="AQ77" s="4"/>
+      <c r="AR77" s="4"/>
+      <c r="AS77" s="4"/>
+      <c r="AT77" s="4"/>
+      <c r="AU77" s="4"/>
+      <c r="AV77" s="4"/>
+      <c r="AW77" s="4"/>
+      <c r="AX77" s="4"/>
+      <c r="AY77" s="4"/>
+      <c r="AZ77" s="4"/>
+      <c r="BA77" s="4"/>
+      <c r="BB77" s="4"/>
+      <c r="BC77" s="4"/>
+      <c r="BD77" s="4"/>
+      <c r="BE77" s="4"/>
+      <c r="BF77" s="4"/>
+      <c r="BG77" s="4"/>
+      <c r="BH77" s="4"/>
+      <c r="BI77" s="4"/>
+      <c r="BJ77" s="4"/>
+      <c r="BK77" s="4"/>
+      <c r="BL77" s="4"/>
+      <c r="BM77" s="4"/>
+    </row>
+    <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+      <c r="I78" s="4"/>
+      <c r="J78" s="4"/>
+      <c r="K78" s="4"/>
+      <c r="L78" s="4"/>
+      <c r="M78" s="4"/>
+      <c r="N78" s="4"/>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+      <c r="T78" s="4"/>
+      <c r="U78" s="4"/>
+      <c r="V78" s="4"/>
+      <c r="W78" s="4"/>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+      <c r="AA78" s="4"/>
+      <c r="AB78" s="4"/>
+      <c r="AC78" s="4"/>
+      <c r="AD78" s="4"/>
+      <c r="AE78" s="4"/>
+      <c r="AF78" s="4"/>
+      <c r="AG78" s="4"/>
+      <c r="AH78" s="4"/>
+      <c r="AI78" s="4"/>
+      <c r="AJ78" s="4"/>
+      <c r="AK78" s="4"/>
+      <c r="AL78" s="4"/>
+      <c r="AM78" s="4"/>
+      <c r="AN78" s="4"/>
+      <c r="AO78" s="4"/>
+      <c r="AP78" s="4"/>
+      <c r="AQ78" s="4"/>
+      <c r="AR78" s="4"/>
+      <c r="AS78" s="4"/>
+      <c r="AT78" s="4"/>
+      <c r="AU78" s="4"/>
+      <c r="AV78" s="4"/>
+      <c r="AW78" s="4"/>
+      <c r="AX78" s="4"/>
+      <c r="AY78" s="4"/>
+      <c r="AZ78" s="4"/>
+      <c r="BA78" s="4"/>
+      <c r="BB78" s="4"/>
+      <c r="BC78" s="4"/>
+      <c r="BD78" s="4"/>
+      <c r="BE78" s="4"/>
+      <c r="BF78" s="4"/>
+      <c r="BG78" s="4"/>
+      <c r="BH78" s="4"/>
+      <c r="BI78" s="4"/>
+      <c r="BJ78" s="4"/>
+      <c r="BK78" s="4"/>
+      <c r="BL78" s="4"/>
+      <c r="BM78" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="68">
+  <mergeCells count="72">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -28525,11 +29337,11 @@
     <mergeCell ref="B54:E54"/>
     <mergeCell ref="B55:E55"/>
     <mergeCell ref="B56:E56"/>
-    <mergeCell ref="A58:V58"/>
-    <mergeCell ref="A64:BM64"/>
-    <mergeCell ref="A65:BM65"/>
-    <mergeCell ref="A66:BM66"/>
-    <mergeCell ref="A67:BM67"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B58:E58"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="A62:V62"/>
     <mergeCell ref="A68:BM68"/>
     <mergeCell ref="A69:BM69"/>
     <mergeCell ref="A70:BM70"/>
@@ -28537,6 +29349,10 @@
     <mergeCell ref="A72:BM72"/>
     <mergeCell ref="A73:BM73"/>
     <mergeCell ref="A74:BM74"/>
+    <mergeCell ref="A75:BM75"/>
+    <mergeCell ref="A76:BM76"/>
+    <mergeCell ref="A77:BM77"/>
+    <mergeCell ref="A78:BM78"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2352" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="286">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 15/05/2026 07:59:54</t>
+    <t xml:space="preserve">Emitido em: 18/05/2026 07:30:58</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -286,42 +286,24 @@
     <t xml:space="preserve">29260429244900000247550010000665271143138443</t>
   </si>
   <si>
-    <t xml:space="preserve">736 - BEMFIXA INDUSTRIAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210.282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.263,18</t>
+    <t xml:space="preserve">7.808 - ABCC -REJUNTABRAS INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">788,62</t>
   </si>
   <si>
     <t xml:space="preserve">N</t>
   </si>
   <si>
-    <t xml:space="preserve">35260461801973000114550010002102821579343693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.808 - ABCC -REJUNTABRAS INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">788,62</t>
-  </si>
-  <si>
     <t xml:space="preserve">35260454542238000178550010000965331000963341</t>
   </si>
   <si>
@@ -346,465 +328,285 @@
     <t xml:space="preserve">43260487547907000153550050003175221341934744</t>
   </si>
   <si>
+    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.972.380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.384,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.972.384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.305,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461413282000143550010029723841503152901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.972.382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.545,08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461413282000143550010029723821252250954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">317.678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.775,54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260487547907000153550050003176781577672540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158,47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260487547907000153550050003168441492652194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.615 - MADELUSTRE INDUSTRIAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.012,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260589616460000152550020000713281306751109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.973.037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.434,01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260461413282000143550010029730371035091800</t>
+  </si>
+  <si>
     <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">631.014</t>
+    <t xml:space="preserve">636.071</t>
   </si>
   <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">04/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.206,95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006310141648214276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">631.471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">79.798,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260475339051000141550080006314711916432042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">631.499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.331,26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006314991770838133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">631.549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.005,56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006315491224798781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">631.624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.779,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006316241955056484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972.380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.384,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972.384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.305,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029723841503152901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972.382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.545,08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029723821252250954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.775,54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260487547907000153550050003176781577672540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">633.546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.703,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006335461841845162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">633.523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.460,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006335231488772186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">633.512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.604,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006335121026499000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.300 - INTELBRAS S/A IND TELEC ELETR BRASILEIRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">640,37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13260582901000001522550100001462471179714429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">146.254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.201,85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13260582901000001522550100001462541960234960</t>
-  </si>
-  <si>
-    <t xml:space="preserve">633.073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">01/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.496,09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006330731926027430</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158,47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260487547907000153550050003168441492652194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.615 - MADELUSTRE INDUSTRIAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.012,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260589616460000152550020000713281306751109</t>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.022,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006360711913994222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.976.319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.756,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">777 - IRMAOS FISCHER S.A IND. E COM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780.743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582984287000104550020017807431502859010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780.742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.332,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582984287000104550020017807421113944451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780.741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.549,24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582984287000104550020017807411668968281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.975.491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.092,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260561413282000143550010029754911228653957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">790 - JACKWAL S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.834,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260592782366000188550030002751961654432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.265,79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - FILIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">637.255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.761,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006372551066202512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.376 - ELETRO ZAGONEL LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">662.150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.581,90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260581365223000154550020006621501364814580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">870.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.603,35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008700041500773535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">637.784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.890,24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006377841750929843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">870.017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.185,87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008700171161145098</t>
   </si>
   <si>
     <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
   </si>
   <si>
-    <t xml:space="preserve">5.076.359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.875,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050763591705951920</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.076.360</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.917,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050763601270059044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.973.037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.434,01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029730371035091800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.321 - S&amp;P BRASIL VENTILACAO LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.901,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260592659507000412550010000355511160008339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">600 - CENSI INDUSTRIA E COMERCIO DE REPAROS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450.441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.531,62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260502308456000149550050004504411200487782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">634.749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">03/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.103,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006347491202405390</t>
-  </si>
-  <si>
-    <t xml:space="preserve">636.071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.022,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006360711913994222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.976.319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.756,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">777 - IRMAOS FISCHER S.A IND. E COM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807431502859010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.332,17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807421113944451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.549,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807411668968281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">635.121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.912,10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006351211513869799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.975.491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.092,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260561413282000143550010029754911228653957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">790 - JACKWAL S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.834,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260592782366000188550030002751961654432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.265,79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - FILIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">637.255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.761,14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006372551066202512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.376 - ELETRO ZAGONEL LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">662.150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.581,90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260581365223000154550020006621501364814580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">870.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.603,35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008700041500773535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">637.784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.890,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006377841750929843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">870.017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.185,87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008700171161145098</t>
-  </si>
-  <si>
     <t xml:space="preserve">5.080.411</t>
   </si>
   <si>
@@ -959,6 +761,66 @@
   </si>
   <si>
     <t xml:space="preserve">42260575339051000141550080006405841317875822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.318 - CORTAG INDUSTRIA E COMERCIO LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">872.917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.671,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260500808396000521550010008729171646262800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.825,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260581604803000157550010008672241503823847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.485 - ABRILAR INDUSTRIA DE ESQUADRIAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60.289,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260511169963000130550010000470141335411420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">641.031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499,53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006410311154255425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">481,59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050855671736636271</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17204,7 +17066,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM78"/>
+  <dimension ref="A1:BM65"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17958,7 +17820,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>305716</v>
+        <v>305865</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>88</v>
@@ -17973,7 +17835,7 @@
         <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>90</v>
@@ -17985,25 +17847,25 @@
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>2263.18</v>
+        <v>788.62</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>2184.42</v>
+        <v>788.62</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.00198</v>
+        <v>0.258</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>2.04</v>
+        <v>43</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
@@ -18015,7 +17877,7 @@
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
@@ -18024,13 +17886,13 @@
         <v>90</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>78.76</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>2184.42</v>
+        <v>788.62</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>152.91</v>
+        <v>55.2</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -18149,7 +18011,7 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>305865</v>
+        <v>306378</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>95</v>
@@ -18161,67 +18023,67 @@
         <v>96</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>788.62</v>
+        <v>95349.48</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>788.62</v>
+        <v>91519.49</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.258</v>
+        <v>0.80555</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>43</v>
+        <v>424.1</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>5</v>
+        <v>82.61</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>0</v>
+        <v>3829.99</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>788.62</v>
+        <v>91519.49</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>55.2</v>
+        <v>6406.35</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -18326,7 +18188,7 @@
         <v>69</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18340,64 +18202,64 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>306378</v>
+        <v>306535</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="I9" s="9" t="s">
         <v>104</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>95349.48</v>
+        <v>5384.2</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>91519.49</v>
+        <v>5384.2</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.80555</v>
+        <v>0.023054</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>424.1</v>
+        <v>28.62</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>82.61</v>
+        <v>0</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
@@ -18406,13 +18268,13 @@
         <v>104</v>
       </c>
       <c r="Y9" s="12" t="n">
-        <v>3829.99</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>91519.49</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>6406.35</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18481,7 +18343,7 @@
         <v>93</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18517,7 +18379,7 @@
         <v>69</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18531,79 +18393,79 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>306494</v>
+        <v>306536</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="H10" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>111</v>
-      </c>
       <c r="J10" s="9" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>40206.95</v>
+        <v>8305.8</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>37753</v>
+        <v>8305.8</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.24</v>
+        <v>0.02159</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>1</v>
+        <v>29.29</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>2453.95</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>37753</v>
+        <v>0</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>2642.71</v>
+        <v>0</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18672,7 +18534,7 @@
         <v>93</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18708,7 +18570,7 @@
         <v>69</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18722,34 +18584,34 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>306496</v>
+        <v>306537</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="I11" s="9" t="s">
-        <v>111</v>
-      </c>
       <c r="J11" s="9" t="s">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>79798.26</v>
+        <v>18545.08</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
@@ -18758,43 +18620,43 @@
         <v>2</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>79696.44</v>
+        <v>18545.08</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.990242</v>
+        <v>0.582728</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>316.25</v>
+        <v>76.55</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>101.82</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>79696.44</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>5578.75</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18863,7 +18725,7 @@
         <v>93</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18899,7 +18761,7 @@
         <v>69</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18913,79 +18775,79 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>306497</v>
+        <v>306568</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>5331.26</v>
+        <v>32775.54</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>5005.88</v>
+        <v>31565.22</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.055816</v>
+        <v>1.03129</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>7.12</v>
+        <v>102.16</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>28</v>
+        <v>83.35</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>325.38</v>
+        <v>1210.32</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>5005.88</v>
+        <v>31565.22</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>350.41</v>
+        <v>2209.57</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -19090,7 +18952,7 @@
         <v>69</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19104,34 +18966,34 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>306498</v>
+        <v>306716</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="H13" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="I13" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="I13" s="9" t="s">
-        <v>111</v>
-      </c>
       <c r="J13" s="9" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>3005.56</v>
+        <v>158.47</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -19140,43 +19002,43 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>3005.56</v>
+        <v>148.8</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.008736</v>
+        <v>0</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>0</v>
+        <v>9.67</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>3005.56</v>
+        <v>158.47</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>210.39</v>
+        <v>11.09</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19245,7 +19107,7 @@
         <v>93</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -19281,7 +19143,7 @@
         <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19295,79 +19157,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>306501</v>
+        <v>306769</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>119</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>5779.28</v>
+        <v>5012.28</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>5779.28</v>
+        <v>4567</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.00943</v>
+        <v>0</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>28</v>
+        <v>40.75</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>0</v>
+        <v>445.28</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>5779.28</v>
+        <v>4567</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>404.55</v>
+        <v>319.68</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19433,7 +19295,7 @@
         <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AX14" s="10" t="s">
         <v>86</v>
@@ -19472,7 +19334,7 @@
         <v>69</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19486,10 +19348,10 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>306535</v>
+        <v>306801</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
@@ -19501,64 +19363,64 @@
         <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>69</v>
+        <v>131</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>5384.2</v>
+        <v>26434.01</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>5384.2</v>
+        <v>25783.04</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.023054</v>
+        <v>0.47642</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>28.62</v>
+        <v>56.65</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>0</v>
+        <v>650.97</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>0</v>
+        <v>25783.04</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>0</v>
+        <v>1265.66</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19627,7 +19489,7 @@
         <v>93</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19663,7 +19525,7 @@
         <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19677,79 +19539,79 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>306536</v>
+        <v>306945</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>8305.8</v>
+        <v>11022.8</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>8305.8</v>
+        <v>11022.8</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.02159</v>
+        <v>0.0217</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>29.29</v>
+        <v>2.44</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="Y16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>0</v>
+        <v>11022.8</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>0</v>
+        <v>771.6</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19818,7 +19680,7 @@
         <v>93</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19854,7 +19716,7 @@
         <v>69</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19868,79 +19730,79 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>306537</v>
+        <v>307020</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>69</v>
+        <v>144</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>18545.08</v>
+        <v>1756.8</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>18545.08</v>
+        <v>1756.8</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.582728</v>
+        <v>0.142272</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>76.55</v>
+        <v>3.42</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>0</v>
+        <v>1756.8</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>0</v>
+        <v>122.98</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -20009,7 +19871,7 @@
         <v>93</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>75</v>
@@ -20045,7 +19907,7 @@
         <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -20059,79 +19921,79 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>306568</v>
+        <v>307044</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>140</v>
+        <v>69</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>32775.54</v>
+        <v>760.8</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>31565.22</v>
+        <v>760.8</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>1.03129</v>
+        <v>0.09178</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>102.16</v>
+        <v>14.15</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>83.35</v>
+        <v>0</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>1210.32</v>
+        <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>31565.22</v>
+        <v>760.8</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>2209.57</v>
+        <v>53.26</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20200,7 +20062,7 @@
         <v>93</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -20236,7 +20098,7 @@
         <v>69</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20250,34 +20112,34 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>306659</v>
+        <v>307045</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="G19" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>144</v>
-      </c>
       <c r="J19" s="9" t="s">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>3703.1</v>
+        <v>1332.17</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -20286,43 +20148,43 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>3703.1</v>
+        <v>1332.17</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.040904</v>
+        <v>0.017488</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>9.34</v>
+        <v>8.85</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Y19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>3703.1</v>
+        <v>1332.17</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>259.22</v>
+        <v>53.29</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20391,7 +20253,7 @@
         <v>93</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20427,7 +20289,7 @@
         <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20441,79 +20303,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>306661</v>
+        <v>307046</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>2460.96</v>
+        <v>39549.24</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>2460.96</v>
+        <v>36406.48</v>
       </c>
       <c r="P20" s="12" t="n">
-        <v>0</v>
+        <v>1877.94</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.009892</v>
+        <v>2.71203</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>3.51</v>
+        <v>520.9</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>0</v>
+        <v>1264.82</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>2460.96</v>
+        <v>38284.42</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>172.27</v>
+        <v>2330.38</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20618,7 +20480,7 @@
         <v>69</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20632,79 +20494,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>306662</v>
+        <v>307062</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1604</v>
+        <v>94092.8</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>1604</v>
+        <v>93172</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.009968</v>
+        <v>2.122527</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>2.28</v>
+        <v>493.99</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>0</v>
+        <v>920.8</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>1604</v>
+        <v>92335.42</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>112.28</v>
+        <v>5743.16</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20809,7 +20671,7 @@
         <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20823,43 +20685,43 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>306668</v>
+        <v>307073</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>640.37</v>
+        <v>7834.72</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>640.37</v>
+        <v>7524.33</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
@@ -20874,28 +20736,28 @@
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>0</v>
+        <v>310.39</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>640.37</v>
+        <v>7524.33</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>76.84</v>
+        <v>526.7</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -21000,7 +20862,7 @@
         <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -21014,79 +20876,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>306669</v>
+        <v>307133</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="I23" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="I23" s="9" t="s">
-        <v>144</v>
-      </c>
       <c r="J23" s="9" t="s">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>3201.85</v>
+        <v>4265.79</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>3201.85</v>
+        <v>4222.88</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0</v>
+        <v>0.484131</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="W23" s="9" t="s">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>0</v>
+        <v>42.91</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>3201.85</v>
+        <v>4222.88</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>384.22</v>
+        <v>281.12</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21191,7 +21053,7 @@
         <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21205,58 +21067,58 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>306672</v>
+        <v>307142</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>4496.09</v>
+        <v>20761.14</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>4496.09</v>
+        <v>20761.14</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.015408</v>
+        <v>0.01152</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>4.43</v>
+        <v>2.23</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
@@ -21268,16 +21130,16 @@
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>4496.09</v>
+        <v>20761.14</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>314.73</v>
+        <v>1453.28</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21382,7 +21244,7 @@
         <v>69</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21396,34 +21258,34 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>306716</v>
+        <v>307146</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>101</v>
+        <v>178</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>158.47</v>
+        <v>6581.9</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21432,7 +21294,7 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>148.8</v>
+        <v>6581.9</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
@@ -21441,34 +21303,34 @@
         <v>0</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>0</v>
+        <v>416.22</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="Y25" s="12" t="n">
-        <v>9.67</v>
+        <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>158.47</v>
+        <v>6581.9</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>11.09</v>
+        <v>460.73</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21537,7 +21399,7 @@
         <v>93</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>169</v>
+        <v>86</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21573,7 +21435,7 @@
         <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21587,79 +21449,79 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>306769</v>
+        <v>307159</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>145</v>
+        <v>184</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>5012.28</v>
+        <v>1603.35</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>4567</v>
+        <v>1527</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0</v>
+        <v>0.05265</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>40.75</v>
+        <v>14</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>445.28</v>
+        <v>76.35</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>4567</v>
+        <v>1527</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>319.68</v>
+        <v>106.89</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21725,7 +21587,7 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX26" s="10" t="s">
         <v>86</v>
@@ -21764,7 +21626,7 @@
         <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21778,34 +21640,34 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>306783</v>
+        <v>307161</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>69</v>
+        <v>175</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2875.92</v>
+        <v>4890.24</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -21814,43 +21676,43 @@
         <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>2700.39</v>
+        <v>4890.24</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0</v>
+        <v>0.001296</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>175.53</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>2700.39</v>
+        <v>4890.24</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>108.02</v>
+        <v>342.32</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21916,10 +21778,10 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21955,7 +21817,7 @@
         <v>69</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21969,34 +21831,34 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>306784</v>
+        <v>307162</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>66</v>
+        <v>165</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>111</v>
+        <v>159</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>69</v>
+        <v>191</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1917.28</v>
+        <v>1185.87</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -22005,43 +21867,43 @@
         <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>1800.26</v>
+        <v>1129.4</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0</v>
+        <v>0.0351</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>117.02</v>
+        <v>56.47</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>1800.26</v>
+        <v>1129.4</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>72.01</v>
+        <v>79.06</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22110,7 +21972,7 @@
         <v>93</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -22146,7 +22008,7 @@
         <v>69</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22160,79 +22022,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>306801</v>
+        <v>307171</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>129</v>
+        <v>194</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>26434.01</v>
+        <v>404.81</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>25783.04</v>
+        <v>404.81</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.47642</v>
+        <v>0.000858</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>56.65</v>
+        <v>2.43</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>650.97</v>
+        <v>0</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>25783.04</v>
+        <v>404.81</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>1265.66</v>
+        <v>16.19</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22301,7 +22163,7 @@
         <v>93</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -22337,7 +22199,7 @@
         <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22351,79 +22213,79 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>306816</v>
+        <v>307173</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>7901.28</v>
+        <v>404.81</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>7901.28</v>
+        <v>404.81</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0</v>
+        <v>0.000858</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>7901.28</v>
+        <v>404.81</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>316.05</v>
+        <v>16.19</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22492,7 +22354,7 @@
         <v>93</v>
       </c>
       <c r="AX30" s="10" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="AY30" s="14" t="s">
         <v>75</v>
@@ -22528,7 +22390,7 @@
         <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22542,79 +22404,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>306826</v>
+        <v>307174</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>103</v>
+        <v>66</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>194</v>
+        <v>69</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>4531.62</v>
+        <v>404.81</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>4473.82</v>
+        <v>404.81</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.180978</v>
+        <v>0.000858</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>29.27</v>
+        <v>2.43</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>75.75</v>
+        <v>0</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>57.8</v>
+        <v>0</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>4473.82</v>
+        <v>404.81</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>183</v>
+        <v>16.19</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22680,10 +22542,10 @@
         <v>74</v>
       </c>
       <c r="AW31" s="14" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22719,7 +22581,7 @@
         <v>69</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22733,79 +22595,79 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>306879</v>
+        <v>307181</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>19103.8</v>
+        <v>426.2</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>19103.8</v>
+        <v>426.2</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.0507</v>
+        <v>0.0025</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>54.16</v>
+        <v>10</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>28</v>
+        <v>77</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="Y32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>19103.8</v>
+        <v>426.2</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>1337.27</v>
+        <v>29.84</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22910,7 +22772,7 @@
         <v>69</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22924,79 +22786,79 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>306945</v>
+        <v>307183</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>108</v>
+        <v>182</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>11022.8</v>
+        <v>12695.18</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>11022.8</v>
+        <v>11935.6</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.0217</v>
+        <v>0.0698</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>2.44</v>
+        <v>31.68</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>0</v>
+        <v>759.58</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>11022.8</v>
+        <v>11935.6</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>771.6</v>
+        <v>614.43</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -23101,7 +22963,7 @@
         <v>69</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23115,34 +22977,34 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>307020</v>
+        <v>307231</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>129</v>
+        <v>194</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>203</v>
+        <v>159</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1756.8</v>
+        <v>2929.6</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -23151,43 +23013,43 @@
         <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>1756.8</v>
+        <v>2929.6</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.142272</v>
+        <v>0.000484</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>3.42</v>
+        <v>3.22</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>90</v>
+        <v>56</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Y34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>1756.8</v>
+        <v>2929.6</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>122.98</v>
+        <v>205.07</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23292,7 +23154,7 @@
         <v>69</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23306,25 +23168,25 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>307044</v>
+        <v>307235</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>69</v>
@@ -23333,7 +23195,7 @@
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>760.8</v>
+        <v>461.96</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23342,22 +23204,22 @@
         <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>760.8</v>
+        <v>461.96</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.09178</v>
+        <v>0.002057</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>14.15</v>
+        <v>2.43</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
@@ -23369,16 +23231,16 @@
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Y35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>760.8</v>
+        <v>461.96</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>53.26</v>
+        <v>18.48</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23447,7 +23309,7 @@
         <v>93</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23483,7 +23345,7 @@
         <v>69</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23497,34 +23359,34 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>307045</v>
+        <v>307242</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>211</v>
+        <v>134</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>1332.17</v>
+        <v>1887.04</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
@@ -23533,43 +23395,43 @@
         <v>1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>1332.17</v>
+        <v>1887.04</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.017488</v>
+        <v>0.007832</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>8.85</v>
+        <v>1.9</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Y36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>1332.17</v>
+        <v>1887.04</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>53.29</v>
+        <v>132.09</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23638,7 +23500,7 @@
         <v>93</v>
       </c>
       <c r="AX36" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY36" s="14" t="s">
         <v>75</v>
@@ -23674,7 +23536,7 @@
         <v>69</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23688,79 +23550,79 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>307046</v>
+        <v>307265</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>219</v>
+        <v>175</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>39549.24</v>
+        <v>3702.49</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>36406.48</v>
+        <v>3437.49</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>1877.94</v>
+        <v>265</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>2.71203</v>
+        <v>0</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>520.9</v>
+        <v>3.5</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="W37" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>1264.82</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>38284.42</v>
+        <v>3702.49</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>2330.38</v>
+        <v>259.17</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23865,7 +23727,7 @@
         <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23879,79 +23741,79 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>307048</v>
+        <v>307278</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>108</v>
+        <v>226</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>198</v>
+        <v>159</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>7912.1</v>
+        <v>29709.55</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>7912.1</v>
+        <v>29280.46</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0</v>
+        <v>0.69578</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>0</v>
+        <v>130.96</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="W38" s="9" t="s">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>0</v>
+        <v>429.09</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>7912.1</v>
+        <v>29280.46</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>553.85</v>
+        <v>1794.18</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -24056,7 +23918,7 @@
         <v>69</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -24070,79 +23932,79 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>307062</v>
+        <v>307297</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>129</v>
+        <v>231</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>94092.8</v>
+        <v>3314.33</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>93172</v>
+        <v>3210</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>2.122527</v>
+        <v>0</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>493.99</v>
+        <v>0</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>920.8</v>
+        <v>104.33</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>92335.42</v>
+        <v>3210</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>5743.16</v>
+        <v>224.7</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24247,7 +24109,7 @@
         <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24261,79 +24123,79 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>307073</v>
+        <v>307330</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>230</v>
+        <v>134</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>232</v>
+        <v>136</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>7834.72</v>
+        <v>7078.63</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>7524.33</v>
+        <v>6646.6</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0</v>
+        <v>0.0425</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>310.39</v>
+        <v>432.03</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>7524.33</v>
+        <v>6646.6</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>526.7</v>
+        <v>465.26</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24438,7 +24300,7 @@
         <v>69</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="BK40" s="9" t="s">
         <v>75</v>
@@ -24452,79 +24314,79 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>307133</v>
+        <v>307334</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>235</v>
+        <v>134</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>66</v>
+        <v>136</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>4265.79</v>
+        <v>4963.92</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>4222.88</v>
+        <v>4963.92</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.484131</v>
+        <v>0.029904</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>71.4</v>
+        <v>6.84</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="W41" s="9" t="s">
-        <v>239</v>
+        <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="Y41" s="12" t="n">
-        <v>42.91</v>
+        <v>0</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>4222.88</v>
+        <v>4963.92</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>281.12</v>
+        <v>347.47</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24629,7 +24491,7 @@
         <v>69</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24643,34 +24505,34 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>307142</v>
+        <v>307356</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>108</v>
+        <v>134</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J42" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J42" s="9" t="s">
-        <v>242</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>20761.14</v>
+        <v>2104.02</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
@@ -24679,22 +24541,22 @@
         <v>1</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>20761.14</v>
+        <v>2104.02</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.01152</v>
+        <v>0.005548</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>2.23</v>
+        <v>1.08</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
@@ -24706,16 +24568,16 @@
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="Y42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>20761.14</v>
+        <v>2104.02</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>1453.28</v>
+        <v>147.28</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24820,7 +24682,7 @@
         <v>69</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24834,79 +24696,79 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>307146</v>
+        <v>307367</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>173</v>
+        <v>66</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>6581.9</v>
+        <v>5671.17</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>6581.9</v>
+        <v>5538.68</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0</v>
+        <v>0.314926</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>416.22</v>
+        <v>33.19</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V43" s="12" t="n">
-        <v>56</v>
+        <v>55.35</v>
       </c>
       <c r="W43" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>0</v>
+        <v>132.49</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>6581.9</v>
+        <v>4787.31</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>460.73</v>
+        <v>258.23</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -25011,7 +24873,7 @@
         <v>69</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -25025,79 +24887,79 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>307159</v>
+        <v>307369</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>249</v>
+        <v>226</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>232</v>
+        <v>66</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>251</v>
+        <v>69</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>1603.35</v>
+        <v>1825.13</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>1527</v>
+        <v>1767.68</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.05265</v>
+        <v>0.025844</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>30</v>
+        <v>6.79</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>76.35</v>
+        <v>57.45</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>1527</v>
+        <v>1767.68</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>106.89</v>
+        <v>110.47</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25166,7 +25028,7 @@
         <v>93</v>
       </c>
       <c r="AX44" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY44" s="14" t="s">
         <v>75</v>
@@ -25202,7 +25064,7 @@
         <v>69</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25216,79 +25078,79 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>307161</v>
+        <v>307372</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>108</v>
+        <v>255</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G45" s="10" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>207</v>
+        <v>233</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>4890.24</v>
+        <v>60289</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>4890.24</v>
+        <v>60289</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.001296</v>
+        <v>0</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>2.22</v>
+        <v>2625</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>28</v>
+        <v>60.6</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="Y45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>4890.24</v>
+        <v>60289</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>342.32</v>
+        <v>4220.23</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25393,7 +25255,7 @@
         <v>69</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25407,34 +25269,34 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>307162</v>
+        <v>307376</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>249</v>
+        <v>134</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>232</v>
+        <v>136</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>1185.87</v>
+        <v>499.53</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
@@ -25443,43 +25305,43 @@
         <v>1</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>1129.4</v>
+        <v>499.53</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>0.0351</v>
+        <v>0.000507</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>20</v>
+        <v>1.07</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>56.47</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>1129.4</v>
+        <v>499.53</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>79.06</v>
+        <v>34.97</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25584,7 +25446,7 @@
         <v>69</v>
       </c>
       <c r="BJ46" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="BK46" s="9" t="s">
         <v>75</v>
@@ -25598,34 +25460,34 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>307171</v>
+        <v>307386</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>177</v>
+        <v>194</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>203</v>
+        <v>249</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>69</v>
+        <v>264</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>404.81</v>
+        <v>481.59</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
@@ -25634,43 +25496,43 @@
         <v>1</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>404.81</v>
+        <v>481.59</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.002268</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>2.43</v>
+        <v>0.44</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="Y47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>404.81</v>
+        <v>481.59</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>16.19</v>
+        <v>19.26</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25739,7 +25601,7 @@
         <v>93</v>
       </c>
       <c r="AX47" s="10" t="s">
-        <v>169</v>
+        <v>86</v>
       </c>
       <c r="AY47" s="14" t="s">
         <v>75</v>
@@ -25775,7 +25637,7 @@
         <v>69</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="BK47" s="9" t="s">
         <v>75</v>
@@ -25788,3499 +25650,1016 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="n">
-        <v>307173</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K48" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L48" s="12" t="n">
-        <v>404.81</v>
-      </c>
-      <c r="M48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O48" s="12" t="n">
-        <v>404.81</v>
-      </c>
-      <c r="P48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="13" t="n">
-        <v>0.000858</v>
-      </c>
-      <c r="R48" s="12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="U48" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X48" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="12" t="n">
-        <v>404.81</v>
-      </c>
-      <c r="AA48" s="12" t="n">
-        <v>16.19</v>
-      </c>
-      <c r="AB48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW48" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX48" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="AY48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF48" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG48" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI48" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ48" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="BK48" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL48" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM48" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="n">
-        <v>307174</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9" t="s">
-        <v>266</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K49" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>404.81</v>
-      </c>
-      <c r="M49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" s="12" t="n">
-        <v>404.81</v>
-      </c>
-      <c r="P49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="13" t="n">
-        <v>0.000858</v>
-      </c>
-      <c r="R49" s="12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="U49" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X49" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="12" t="n">
-        <v>404.81</v>
-      </c>
-      <c r="AA49" s="12" t="n">
-        <v>16.19</v>
-      </c>
-      <c r="AB49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW49" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX49" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="AY49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF49" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG49" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI49" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ49" s="9" t="s">
+    <row r="49" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="s">
         <v>267</v>
       </c>
-      <c r="BK49" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL49" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM49" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17"/>
+      <c r="U49" s="17"/>
+      <c r="V49" s="17"/>
     </row>
-    <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="n">
-        <v>307181</v>
-      </c>
-      <c r="B50" s="9" t="s">
+    <row r="50" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="18" t="s">
         <v>268</v>
       </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9" t="s">
+      <c r="B50" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="G50" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J50" s="9" t="s">
+      <c r="E50" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I50" s="18" t="s">
         <v>270</v>
       </c>
-      <c r="K50" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L50" s="12" t="n">
-        <v>426.2</v>
-      </c>
-      <c r="M50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O50" s="12" t="n">
-        <v>426.2</v>
-      </c>
-      <c r="P50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="13" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="R50" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="S50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="14" t="s">
+      <c r="J50" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M50" s="18" t="s">
         <v>271</v>
       </c>
-      <c r="U50" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V50" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="W50" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X50" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="12" t="n">
-        <v>426.2</v>
-      </c>
-      <c r="AA50" s="12" t="n">
-        <v>29.84</v>
-      </c>
-      <c r="AB50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW50" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX50" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG50" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI50" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ50" s="9" t="s">
+      <c r="N50" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O50" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P50" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q50" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R50" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S50" s="18" t="s">
         <v>272</v>
       </c>
-      <c r="BK50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM50" s="16" t="s">
-        <v>79</v>
+      <c r="T50" s="18" t="s">
+        <v>273</v>
+      </c>
+      <c r="U50" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V50" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="n">
-        <v>307183</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="C51" s="9"/>
-      <c r="D51" s="9"/>
-      <c r="E51" s="9"/>
-      <c r="F51" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="K51" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>12695.18</v>
-      </c>
-      <c r="M51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="O51" s="12" t="n">
-        <v>11935.6</v>
-      </c>
-      <c r="P51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="13" t="n">
-        <v>0.0698</v>
-      </c>
-      <c r="R51" s="12" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="S51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" s="14" t="s">
+      <c r="A51" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>2142.94</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>10747.56</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>483288.47</v>
+      </c>
+      <c r="G51" s="19" t="n">
+        <v>31529.62</v>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>527849.39</v>
+      </c>
+      <c r="L51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="20" t="n">
+        <v>10.09365</v>
+      </c>
+      <c r="S51" s="19" t="n">
+        <v>514958.89</v>
+      </c>
+      <c r="T51" s="19" t="n">
+        <v>527849.39</v>
+      </c>
+      <c r="U51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G52" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I52" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J52" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K52" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="U51" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V51" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="W51" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X51" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y51" s="12" t="n">
-        <v>759.58</v>
-      </c>
-      <c r="Z51" s="12" t="n">
-        <v>11935.6</v>
-      </c>
-      <c r="AA51" s="12" t="n">
-        <v>614.43</v>
-      </c>
-      <c r="AB51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO51" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV51" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW51" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX51" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY51" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ51" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA51" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB51" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC51" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD51" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE51" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF51" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG51" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH51" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI51" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ51" s="9" t="s">
+      <c r="L52" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="BK51" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL51" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM51" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="8" t="n">
-        <v>307231</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C52" s="9"/>
-      <c r="D52" s="9"/>
-      <c r="E52" s="9"/>
-      <c r="F52" s="9" t="s">
+      <c r="M52" s="18" t="s">
         <v>276</v>
-      </c>
-      <c r="G52" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H52" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="I52" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="J52" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="K52" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L52" s="12" t="n">
-        <v>2929.6</v>
-      </c>
-      <c r="M52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O52" s="12" t="n">
-        <v>2929.6</v>
-      </c>
-      <c r="P52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="13" t="n">
-        <v>0.000484</v>
-      </c>
-      <c r="R52" s="12" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="S52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="U52" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V52" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="W52" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X52" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="12" t="n">
-        <v>2929.6</v>
-      </c>
-      <c r="AA52" s="12" t="n">
-        <v>205.07</v>
-      </c>
-      <c r="AB52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV52" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW52" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX52" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF52" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG52" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH52" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI52" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ52" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="BK52" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL52" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM52" s="16" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="8" t="n">
-        <v>307235</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C53" s="9"/>
-      <c r="D53" s="9"/>
-      <c r="E53" s="9"/>
-      <c r="F53" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="G53" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="I53" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="J53" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>461.96</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O53" s="12" t="n">
-        <v>461.96</v>
-      </c>
-      <c r="P53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="13" t="n">
-        <v>0.002057</v>
-      </c>
-      <c r="R53" s="12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="U53" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X53" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="12" t="n">
-        <v>461.96</v>
-      </c>
-      <c r="AA53" s="12" t="n">
-        <v>18.48</v>
-      </c>
-      <c r="AB53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO53" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV53" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW53" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX53" s="10" t="s">
-        <v>169</v>
-      </c>
-      <c r="AY53" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ53" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA53" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB53" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC53" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD53" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE53" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF53" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG53" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH53" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI53" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ53" s="9" t="s">
-        <v>283</v>
-      </c>
-      <c r="BK53" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL53" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM53" s="16" t="s">
-        <v>79</v>
+      <c r="A53" s="19" t="n">
+        <v>5221.16</v>
+      </c>
+      <c r="B53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="8" t="n">
-        <v>307242</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C54" s="9"/>
-      <c r="D54" s="9"/>
-      <c r="E54" s="9"/>
-      <c r="F54" s="9" t="s">
-        <v>284</v>
-      </c>
-      <c r="G54" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H54" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="I54" s="9" t="s">
+      <c r="A54" s="4"/>
+    </row>
+    <row r="55" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="J54" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="K54" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L54" s="12" t="n">
-        <v>1887.04</v>
-      </c>
-      <c r="M54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O54" s="12" t="n">
-        <v>1887.04</v>
-      </c>
-      <c r="P54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="13" t="n">
-        <v>0.007832</v>
-      </c>
-      <c r="R54" s="12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="U54" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V54" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W54" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X54" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="12" t="n">
-        <v>1887.04</v>
-      </c>
-      <c r="AA54" s="12" t="n">
-        <v>132.09</v>
-      </c>
-      <c r="AB54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO54" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV54" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW54" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX54" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY54" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ54" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA54" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB54" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC54" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD54" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE54" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF54" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG54" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH54" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI54" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ54" s="9" t="s">
-        <v>287</v>
-      </c>
-      <c r="BK54" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL54" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM54" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="8" t="n">
-        <v>307265</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="C55" s="9"/>
-      <c r="D55" s="9"/>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="G55" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="J55" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L55" s="12" t="n">
-        <v>3702.49</v>
-      </c>
-      <c r="M55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O55" s="12" t="n">
-        <v>3437.49</v>
-      </c>
-      <c r="P55" s="12" t="n">
-        <v>265</v>
-      </c>
-      <c r="Q55" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="S55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="U55" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V55" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="W55" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X55" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="12" t="n">
-        <v>3702.49</v>
-      </c>
-      <c r="AA55" s="12" t="n">
-        <v>259.17</v>
-      </c>
-      <c r="AB55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV55" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW55" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX55" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF55" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG55" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH55" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI55" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ55" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="BK55" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL55" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM55" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="21"/>
+      <c r="R55" s="21"/>
+      <c r="S55" s="21"/>
+      <c r="T55" s="21"/>
+      <c r="U55" s="21"/>
+      <c r="V55" s="21"/>
+      <c r="W55" s="21"/>
+      <c r="X55" s="21"/>
+      <c r="Y55" s="21"/>
+      <c r="Z55" s="21"/>
+      <c r="AA55" s="21"/>
+      <c r="AB55" s="21"/>
+      <c r="AC55" s="21"/>
+      <c r="AD55" s="21"/>
+      <c r="AE55" s="21"/>
+      <c r="AF55" s="21"/>
+      <c r="AG55" s="21"/>
+      <c r="AH55" s="21"/>
+      <c r="AI55" s="21"/>
+      <c r="AJ55" s="21"/>
+      <c r="AK55" s="21"/>
+      <c r="AL55" s="21"/>
+      <c r="AM55" s="21"/>
+      <c r="AN55" s="21"/>
+      <c r="AO55" s="21"/>
+      <c r="AP55" s="21"/>
+      <c r="AQ55" s="21"/>
+      <c r="AR55" s="21"/>
+      <c r="AS55" s="21"/>
+      <c r="AT55" s="21"/>
+      <c r="AU55" s="21"/>
+      <c r="AV55" s="21"/>
+      <c r="AW55" s="21"/>
+      <c r="AX55" s="21"/>
+      <c r="AY55" s="21"/>
+      <c r="AZ55" s="21"/>
+      <c r="BA55" s="21"/>
+      <c r="BB55" s="21"/>
+      <c r="BC55" s="21"/>
+      <c r="BD55" s="21"/>
+      <c r="BE55" s="21"/>
+      <c r="BF55" s="21"/>
+      <c r="BG55" s="21"/>
+      <c r="BH55" s="21"/>
+      <c r="BI55" s="21"/>
+      <c r="BJ55" s="21"/>
+      <c r="BK55" s="21"/>
+      <c r="BL55" s="21"/>
+      <c r="BM55" s="21"/>
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="8" t="n">
-        <v>307278</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>292</v>
-      </c>
-      <c r="C56" s="9"/>
-      <c r="D56" s="9"/>
-      <c r="E56" s="9"/>
-      <c r="F56" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="G56" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H56" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="J56" s="9" t="s">
-        <v>294</v>
-      </c>
-      <c r="K56" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L56" s="12" t="n">
-        <v>29709.55</v>
-      </c>
-      <c r="M56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="O56" s="12" t="n">
-        <v>29280.46</v>
-      </c>
-      <c r="P56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="13" t="n">
-        <v>0.69578</v>
-      </c>
-      <c r="R56" s="12" t="n">
-        <v>130.96</v>
-      </c>
-      <c r="S56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="U56" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V56" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="W56" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="X56" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="Y56" s="12" t="n">
-        <v>429.09</v>
-      </c>
-      <c r="Z56" s="12" t="n">
-        <v>29280.46</v>
-      </c>
-      <c r="AA56" s="12" t="n">
-        <v>1794.18</v>
-      </c>
-      <c r="AB56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV56" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW56" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX56" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF56" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG56" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH56" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI56" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ56" s="9" t="s">
-        <v>296</v>
-      </c>
-      <c r="BK56" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL56" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM56" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A56" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
+      <c r="AB56" s="4"/>
+      <c r="AC56" s="4"/>
+      <c r="AD56" s="4"/>
+      <c r="AE56" s="4"/>
+      <c r="AF56" s="4"/>
+      <c r="AG56" s="4"/>
+      <c r="AH56" s="4"/>
+      <c r="AI56" s="4"/>
+      <c r="AJ56" s="4"/>
+      <c r="AK56" s="4"/>
+      <c r="AL56" s="4"/>
+      <c r="AM56" s="4"/>
+      <c r="AN56" s="4"/>
+      <c r="AO56" s="4"/>
+      <c r="AP56" s="4"/>
+      <c r="AQ56" s="4"/>
+      <c r="AR56" s="4"/>
+      <c r="AS56" s="4"/>
+      <c r="AT56" s="4"/>
+      <c r="AU56" s="4"/>
+      <c r="AV56" s="4"/>
+      <c r="AW56" s="4"/>
+      <c r="AX56" s="4"/>
+      <c r="AY56" s="4"/>
+      <c r="AZ56" s="4"/>
+      <c r="BA56" s="4"/>
+      <c r="BB56" s="4"/>
+      <c r="BC56" s="4"/>
+      <c r="BD56" s="4"/>
+      <c r="BE56" s="4"/>
+      <c r="BF56" s="4"/>
+      <c r="BG56" s="4"/>
+      <c r="BH56" s="4"/>
+      <c r="BI56" s="4"/>
+      <c r="BJ56" s="4"/>
+      <c r="BK56" s="4"/>
+      <c r="BL56" s="4"/>
+      <c r="BM56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="8" t="n">
-        <v>307297</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>297</v>
-      </c>
-      <c r="C57" s="9"/>
-      <c r="D57" s="9"/>
-      <c r="E57" s="9"/>
-      <c r="F57" s="9" t="s">
-        <v>298</v>
-      </c>
-      <c r="G57" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="J57" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L57" s="12" t="n">
-        <v>3314.33</v>
-      </c>
-      <c r="M57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O57" s="12" t="n">
-        <v>3210</v>
-      </c>
-      <c r="P57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="14" t="s">
-        <v>301</v>
-      </c>
-      <c r="U57" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V57" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="W57" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X57" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y57" s="12" t="n">
-        <v>104.33</v>
-      </c>
-      <c r="Z57" s="12" t="n">
-        <v>3210</v>
-      </c>
-      <c r="AA57" s="12" t="n">
-        <v>224.7</v>
-      </c>
-      <c r="AB57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV57" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW57" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX57" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG57" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH57" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI57" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ57" s="9" t="s">
-        <v>302</v>
-      </c>
-      <c r="BK57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL57" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM57" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A57" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
+      <c r="AB57" s="4"/>
+      <c r="AC57" s="4"/>
+      <c r="AD57" s="4"/>
+      <c r="AE57" s="4"/>
+      <c r="AF57" s="4"/>
+      <c r="AG57" s="4"/>
+      <c r="AH57" s="4"/>
+      <c r="AI57" s="4"/>
+      <c r="AJ57" s="4"/>
+      <c r="AK57" s="4"/>
+      <c r="AL57" s="4"/>
+      <c r="AM57" s="4"/>
+      <c r="AN57" s="4"/>
+      <c r="AO57" s="4"/>
+      <c r="AP57" s="4"/>
+      <c r="AQ57" s="4"/>
+      <c r="AR57" s="4"/>
+      <c r="AS57" s="4"/>
+      <c r="AT57" s="4"/>
+      <c r="AU57" s="4"/>
+      <c r="AV57" s="4"/>
+      <c r="AW57" s="4"/>
+      <c r="AX57" s="4"/>
+      <c r="AY57" s="4"/>
+      <c r="AZ57" s="4"/>
+      <c r="BA57" s="4"/>
+      <c r="BB57" s="4"/>
+      <c r="BC57" s="4"/>
+      <c r="BD57" s="4"/>
+      <c r="BE57" s="4"/>
+      <c r="BF57" s="4"/>
+      <c r="BG57" s="4"/>
+      <c r="BH57" s="4"/>
+      <c r="BI57" s="4"/>
+      <c r="BJ57" s="4"/>
+      <c r="BK57" s="4"/>
+      <c r="BL57" s="4"/>
+      <c r="BM57" s="4"/>
     </row>
     <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="n">
-        <v>307330</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C58" s="9"/>
-      <c r="D58" s="9"/>
-      <c r="E58" s="9"/>
-      <c r="F58" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="G58" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H58" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="I58" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="J58" s="9" t="s">
-        <v>300</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L58" s="12" t="n">
-        <v>7078.63</v>
-      </c>
-      <c r="M58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O58" s="12" t="n">
-        <v>6646.6</v>
-      </c>
-      <c r="P58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="13" t="n">
-        <v>0.0425</v>
-      </c>
-      <c r="R58" s="12" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="S58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="U58" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V58" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W58" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X58" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y58" s="12" t="n">
-        <v>432.03</v>
-      </c>
-      <c r="Z58" s="12" t="n">
-        <v>6646.6</v>
-      </c>
-      <c r="AA58" s="12" t="n">
-        <v>465.26</v>
-      </c>
-      <c r="AB58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL58" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV58" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW58" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX58" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF58" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG58" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH58" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI58" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ58" s="9" t="s">
-        <v>305</v>
-      </c>
-      <c r="BK58" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL58" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM58" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A58" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="4"/>
+      <c r="AB58" s="4"/>
+      <c r="AC58" s="4"/>
+      <c r="AD58" s="4"/>
+      <c r="AE58" s="4"/>
+      <c r="AF58" s="4"/>
+      <c r="AG58" s="4"/>
+      <c r="AH58" s="4"/>
+      <c r="AI58" s="4"/>
+      <c r="AJ58" s="4"/>
+      <c r="AK58" s="4"/>
+      <c r="AL58" s="4"/>
+      <c r="AM58" s="4"/>
+      <c r="AN58" s="4"/>
+      <c r="AO58" s="4"/>
+      <c r="AP58" s="4"/>
+      <c r="AQ58" s="4"/>
+      <c r="AR58" s="4"/>
+      <c r="AS58" s="4"/>
+      <c r="AT58" s="4"/>
+      <c r="AU58" s="4"/>
+      <c r="AV58" s="4"/>
+      <c r="AW58" s="4"/>
+      <c r="AX58" s="4"/>
+      <c r="AY58" s="4"/>
+      <c r="AZ58" s="4"/>
+      <c r="BA58" s="4"/>
+      <c r="BB58" s="4"/>
+      <c r="BC58" s="4"/>
+      <c r="BD58" s="4"/>
+      <c r="BE58" s="4"/>
+      <c r="BF58" s="4"/>
+      <c r="BG58" s="4"/>
+      <c r="BH58" s="4"/>
+      <c r="BI58" s="4"/>
+      <c r="BJ58" s="4"/>
+      <c r="BK58" s="4"/>
+      <c r="BL58" s="4"/>
+      <c r="BM58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="n">
-        <v>307334</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C59" s="9"/>
-      <c r="D59" s="9"/>
-      <c r="E59" s="9"/>
-      <c r="F59" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="G59" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="I59" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="K59" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L59" s="12" t="n">
-        <v>4963.92</v>
-      </c>
-      <c r="M59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O59" s="12" t="n">
-        <v>4963.92</v>
-      </c>
-      <c r="P59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="13" t="n">
-        <v>0.029904</v>
-      </c>
-      <c r="R59" s="12" t="n">
-        <v>6.84</v>
-      </c>
-      <c r="S59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="14" t="s">
-        <v>308</v>
-      </c>
-      <c r="U59" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V59" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W59" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X59" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="12" t="n">
-        <v>4963.92</v>
-      </c>
-      <c r="AA59" s="12" t="n">
-        <v>347.47</v>
-      </c>
-      <c r="AB59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL59" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV59" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW59" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX59" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF59" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG59" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH59" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI59" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ59" s="9" t="s">
-        <v>309</v>
-      </c>
-      <c r="BK59" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL59" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM59" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A59" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B59" s="4"/>
+      <c r="C59" s="4"/>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="4"/>
+      <c r="G59" s="4"/>
+      <c r="H59" s="4"/>
+      <c r="I59" s="4"/>
+      <c r="J59" s="4"/>
+      <c r="K59" s="4"/>
+      <c r="L59" s="4"/>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
+      <c r="P59" s="4"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4"/>
+      <c r="V59" s="4"/>
+      <c r="W59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="4"/>
+      <c r="AB59" s="4"/>
+      <c r="AC59" s="4"/>
+      <c r="AD59" s="4"/>
+      <c r="AE59" s="4"/>
+      <c r="AF59" s="4"/>
+      <c r="AG59" s="4"/>
+      <c r="AH59" s="4"/>
+      <c r="AI59" s="4"/>
+      <c r="AJ59" s="4"/>
+      <c r="AK59" s="4"/>
+      <c r="AL59" s="4"/>
+      <c r="AM59" s="4"/>
+      <c r="AN59" s="4"/>
+      <c r="AO59" s="4"/>
+      <c r="AP59" s="4"/>
+      <c r="AQ59" s="4"/>
+      <c r="AR59" s="4"/>
+      <c r="AS59" s="4"/>
+      <c r="AT59" s="4"/>
+      <c r="AU59" s="4"/>
+      <c r="AV59" s="4"/>
+      <c r="AW59" s="4"/>
+      <c r="AX59" s="4"/>
+      <c r="AY59" s="4"/>
+      <c r="AZ59" s="4"/>
+      <c r="BA59" s="4"/>
+      <c r="BB59" s="4"/>
+      <c r="BC59" s="4"/>
+      <c r="BD59" s="4"/>
+      <c r="BE59" s="4"/>
+      <c r="BF59" s="4"/>
+      <c r="BG59" s="4"/>
+      <c r="BH59" s="4"/>
+      <c r="BI59" s="4"/>
+      <c r="BJ59" s="4"/>
+      <c r="BK59" s="4"/>
+      <c r="BL59" s="4"/>
+      <c r="BM59" s="4"/>
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="8" t="n">
-        <v>307356</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="C60" s="9"/>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9" t="s">
-        <v>310</v>
-      </c>
-      <c r="G60" s="10" t="s">
-        <v>110</v>
-      </c>
-      <c r="H60" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="I60" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>307</v>
-      </c>
-      <c r="K60" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L60" s="12" t="n">
-        <v>2104.02</v>
-      </c>
-      <c r="M60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O60" s="12" t="n">
-        <v>2104.02</v>
-      </c>
-      <c r="P60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="13" t="n">
-        <v>0.005548</v>
-      </c>
-      <c r="R60" s="12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="14" t="s">
-        <v>311</v>
-      </c>
-      <c r="U60" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V60" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W60" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X60" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="Y60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" s="12" t="n">
-        <v>2104.02</v>
-      </c>
-      <c r="AA60" s="12" t="n">
-        <v>147.28</v>
-      </c>
-      <c r="AB60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV60" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW60" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="AX60" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF60" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG60" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH60" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI60" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ60" s="9" t="s">
-        <v>312</v>
-      </c>
-      <c r="BK60" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL60" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM60" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A60" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="4"/>
+      <c r="C60" s="4"/>
+      <c r="D60" s="4"/>
+      <c r="E60" s="4"/>
+      <c r="F60" s="4"/>
+      <c r="G60" s="4"/>
+      <c r="H60" s="4"/>
+      <c r="I60" s="4"/>
+      <c r="J60" s="4"/>
+      <c r="K60" s="4"/>
+      <c r="L60" s="4"/>
+      <c r="M60" s="4"/>
+      <c r="N60" s="4"/>
+      <c r="O60" s="4"/>
+      <c r="P60" s="4"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="4"/>
+      <c r="T60" s="4"/>
+      <c r="U60" s="4"/>
+      <c r="V60" s="4"/>
+      <c r="W60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="4"/>
+      <c r="AB60" s="4"/>
+      <c r="AC60" s="4"/>
+      <c r="AD60" s="4"/>
+      <c r="AE60" s="4"/>
+      <c r="AF60" s="4"/>
+      <c r="AG60" s="4"/>
+      <c r="AH60" s="4"/>
+      <c r="AI60" s="4"/>
+      <c r="AJ60" s="4"/>
+      <c r="AK60" s="4"/>
+      <c r="AL60" s="4"/>
+      <c r="AM60" s="4"/>
+      <c r="AN60" s="4"/>
+      <c r="AO60" s="4"/>
+      <c r="AP60" s="4"/>
+      <c r="AQ60" s="4"/>
+      <c r="AR60" s="4"/>
+      <c r="AS60" s="4"/>
+      <c r="AT60" s="4"/>
+      <c r="AU60" s="4"/>
+      <c r="AV60" s="4"/>
+      <c r="AW60" s="4"/>
+      <c r="AX60" s="4"/>
+      <c r="AY60" s="4"/>
+      <c r="AZ60" s="4"/>
+      <c r="BA60" s="4"/>
+      <c r="BB60" s="4"/>
+      <c r="BC60" s="4"/>
+      <c r="BD60" s="4"/>
+      <c r="BE60" s="4"/>
+      <c r="BF60" s="4"/>
+      <c r="BG60" s="4"/>
+      <c r="BH60" s="4"/>
+      <c r="BI60" s="4"/>
+      <c r="BJ60" s="4"/>
+      <c r="BK60" s="4"/>
+      <c r="BL60" s="4"/>
+      <c r="BM60" s="4"/>
     </row>
     <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4"/>
+      <c r="A61" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="4"/>
+      <c r="AB61" s="4"/>
+      <c r="AC61" s="4"/>
+      <c r="AD61" s="4"/>
+      <c r="AE61" s="4"/>
+      <c r="AF61" s="4"/>
+      <c r="AG61" s="4"/>
+      <c r="AH61" s="4"/>
+      <c r="AI61" s="4"/>
+      <c r="AJ61" s="4"/>
+      <c r="AK61" s="4"/>
+      <c r="AL61" s="4"/>
+      <c r="AM61" s="4"/>
+      <c r="AN61" s="4"/>
+      <c r="AO61" s="4"/>
+      <c r="AP61" s="4"/>
+      <c r="AQ61" s="4"/>
+      <c r="AR61" s="4"/>
+      <c r="AS61" s="4"/>
+      <c r="AT61" s="4"/>
+      <c r="AU61" s="4"/>
+      <c r="AV61" s="4"/>
+      <c r="AW61" s="4"/>
+      <c r="AX61" s="4"/>
+      <c r="AY61" s="4"/>
+      <c r="AZ61" s="4"/>
+      <c r="BA61" s="4"/>
+      <c r="BB61" s="4"/>
+      <c r="BC61" s="4"/>
+      <c r="BD61" s="4"/>
+      <c r="BE61" s="4"/>
+      <c r="BF61" s="4"/>
+      <c r="BG61" s="4"/>
+      <c r="BH61" s="4"/>
+      <c r="BI61" s="4"/>
+      <c r="BJ61" s="4"/>
+      <c r="BK61" s="4"/>
+      <c r="BL61" s="4"/>
+      <c r="BM61" s="4"/>
     </row>
-    <row r="62" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
-      <c r="O62" s="17"/>
-      <c r="P62" s="17"/>
-      <c r="Q62" s="17"/>
-      <c r="R62" s="17"/>
-      <c r="S62" s="17"/>
-      <c r="T62" s="17"/>
-      <c r="U62" s="17"/>
-      <c r="V62" s="17"/>
+    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="4"/>
+      <c r="AB62" s="4"/>
+      <c r="AC62" s="4"/>
+      <c r="AD62" s="4"/>
+      <c r="AE62" s="4"/>
+      <c r="AF62" s="4"/>
+      <c r="AG62" s="4"/>
+      <c r="AH62" s="4"/>
+      <c r="AI62" s="4"/>
+      <c r="AJ62" s="4"/>
+      <c r="AK62" s="4"/>
+      <c r="AL62" s="4"/>
+      <c r="AM62" s="4"/>
+      <c r="AN62" s="4"/>
+      <c r="AO62" s="4"/>
+      <c r="AP62" s="4"/>
+      <c r="AQ62" s="4"/>
+      <c r="AR62" s="4"/>
+      <c r="AS62" s="4"/>
+      <c r="AT62" s="4"/>
+      <c r="AU62" s="4"/>
+      <c r="AV62" s="4"/>
+      <c r="AW62" s="4"/>
+      <c r="AX62" s="4"/>
+      <c r="AY62" s="4"/>
+      <c r="AZ62" s="4"/>
+      <c r="BA62" s="4"/>
+      <c r="BB62" s="4"/>
+      <c r="BC62" s="4"/>
+      <c r="BD62" s="4"/>
+      <c r="BE62" s="4"/>
+      <c r="BF62" s="4"/>
+      <c r="BG62" s="4"/>
+      <c r="BH62" s="4"/>
+      <c r="BI62" s="4"/>
+      <c r="BJ62" s="4"/>
+      <c r="BK62" s="4"/>
+      <c r="BL62" s="4"/>
+      <c r="BM62" s="4"/>
     </row>
-    <row r="63" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="B63" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C63" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D63" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="E63" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F63" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G63" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I63" s="18" t="s">
-        <v>316</v>
-      </c>
-      <c r="J63" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K63" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L63" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M63" s="18" t="s">
-        <v>317</v>
-      </c>
-      <c r="N63" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O63" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P63" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q63" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R63" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S63" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="T63" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="U63" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V63" s="18" t="s">
-        <v>37</v>
-      </c>
+    <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
+      <c r="AB63" s="4"/>
+      <c r="AC63" s="4"/>
+      <c r="AD63" s="4"/>
+      <c r="AE63" s="4"/>
+      <c r="AF63" s="4"/>
+      <c r="AG63" s="4"/>
+      <c r="AH63" s="4"/>
+      <c r="AI63" s="4"/>
+      <c r="AJ63" s="4"/>
+      <c r="AK63" s="4"/>
+      <c r="AL63" s="4"/>
+      <c r="AM63" s="4"/>
+      <c r="AN63" s="4"/>
+      <c r="AO63" s="4"/>
+      <c r="AP63" s="4"/>
+      <c r="AQ63" s="4"/>
+      <c r="AR63" s="4"/>
+      <c r="AS63" s="4"/>
+      <c r="AT63" s="4"/>
+      <c r="AU63" s="4"/>
+      <c r="AV63" s="4"/>
+      <c r="AW63" s="4"/>
+      <c r="AX63" s="4"/>
+      <c r="AY63" s="4"/>
+      <c r="AZ63" s="4"/>
+      <c r="BA63" s="4"/>
+      <c r="BB63" s="4"/>
+      <c r="BC63" s="4"/>
+      <c r="BD63" s="4"/>
+      <c r="BE63" s="4"/>
+      <c r="BF63" s="4"/>
+      <c r="BG63" s="4"/>
+      <c r="BH63" s="4"/>
+      <c r="BI63" s="4"/>
+      <c r="BJ63" s="4"/>
+      <c r="BK63" s="4"/>
+      <c r="BL63" s="4"/>
+      <c r="BM63" s="4"/>
     </row>
     <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="19" t="n">
-        <v>56</v>
-      </c>
-      <c r="B64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="19" t="n">
-        <v>2142.94</v>
-      </c>
-      <c r="D64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="19" t="n">
-        <v>13867.88</v>
-      </c>
-      <c r="F64" s="19" t="n">
-        <v>608885.96</v>
-      </c>
-      <c r="G64" s="19" t="n">
-        <v>40115.94</v>
-      </c>
-      <c r="H64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="19" t="n">
-        <v>655815.83</v>
-      </c>
-      <c r="L64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R64" s="20" t="n">
-        <v>11.364159</v>
-      </c>
-      <c r="S64" s="19" t="n">
-        <v>639805.01</v>
-      </c>
-      <c r="T64" s="19" t="n">
-        <v>655815.83</v>
-      </c>
-      <c r="U64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V64" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A64" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
+      <c r="AB64" s="4"/>
+      <c r="AC64" s="4"/>
+      <c r="AD64" s="4"/>
+      <c r="AE64" s="4"/>
+      <c r="AF64" s="4"/>
+      <c r="AG64" s="4"/>
+      <c r="AH64" s="4"/>
+      <c r="AI64" s="4"/>
+      <c r="AJ64" s="4"/>
+      <c r="AK64" s="4"/>
+      <c r="AL64" s="4"/>
+      <c r="AM64" s="4"/>
+      <c r="AN64" s="4"/>
+      <c r="AO64" s="4"/>
+      <c r="AP64" s="4"/>
+      <c r="AQ64" s="4"/>
+      <c r="AR64" s="4"/>
+      <c r="AS64" s="4"/>
+      <c r="AT64" s="4"/>
+      <c r="AU64" s="4"/>
+      <c r="AV64" s="4"/>
+      <c r="AW64" s="4"/>
+      <c r="AX64" s="4"/>
+      <c r="AY64" s="4"/>
+      <c r="AZ64" s="4"/>
+      <c r="BA64" s="4"/>
+      <c r="BB64" s="4"/>
+      <c r="BC64" s="4"/>
+      <c r="BD64" s="4"/>
+      <c r="BE64" s="4"/>
+      <c r="BF64" s="4"/>
+      <c r="BG64" s="4"/>
+      <c r="BH64" s="4"/>
+      <c r="BI64" s="4"/>
+      <c r="BJ64" s="4"/>
+      <c r="BK64" s="4"/>
+      <c r="BL64" s="4"/>
+      <c r="BM64" s="4"/>
     </row>
-    <row r="65" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B65" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C65" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D65" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F65" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G65" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I65" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J65" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K65" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="L65" s="18" t="s">
-        <v>321</v>
-      </c>
-      <c r="M65" s="18" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="19" t="n">
-        <v>2991.18</v>
-      </c>
-      <c r="B66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="19" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="E66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4"/>
-    </row>
-    <row r="68" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="21" t="s">
-        <v>323</v>
-      </c>
-      <c r="B68" s="21"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="21"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="21"/>
-      <c r="G68" s="21"/>
-      <c r="H68" s="21"/>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21"/>
-      <c r="K68" s="21"/>
-      <c r="L68" s="21"/>
-      <c r="M68" s="21"/>
-      <c r="N68" s="21"/>
-      <c r="O68" s="21"/>
-      <c r="P68" s="21"/>
-      <c r="Q68" s="21"/>
-      <c r="R68" s="21"/>
-      <c r="S68" s="21"/>
-      <c r="T68" s="21"/>
-      <c r="U68" s="21"/>
-      <c r="V68" s="21"/>
-      <c r="W68" s="21"/>
-      <c r="X68" s="21"/>
-      <c r="Y68" s="21"/>
-      <c r="Z68" s="21"/>
-      <c r="AA68" s="21"/>
-      <c r="AB68" s="21"/>
-      <c r="AC68" s="21"/>
-      <c r="AD68" s="21"/>
-      <c r="AE68" s="21"/>
-      <c r="AF68" s="21"/>
-      <c r="AG68" s="21"/>
-      <c r="AH68" s="21"/>
-      <c r="AI68" s="21"/>
-      <c r="AJ68" s="21"/>
-      <c r="AK68" s="21"/>
-      <c r="AL68" s="21"/>
-      <c r="AM68" s="21"/>
-      <c r="AN68" s="21"/>
-      <c r="AO68" s="21"/>
-      <c r="AP68" s="21"/>
-      <c r="AQ68" s="21"/>
-      <c r="AR68" s="21"/>
-      <c r="AS68" s="21"/>
-      <c r="AT68" s="21"/>
-      <c r="AU68" s="21"/>
-      <c r="AV68" s="21"/>
-      <c r="AW68" s="21"/>
-      <c r="AX68" s="21"/>
-      <c r="AY68" s="21"/>
-      <c r="AZ68" s="21"/>
-      <c r="BA68" s="21"/>
-      <c r="BB68" s="21"/>
-      <c r="BC68" s="21"/>
-      <c r="BD68" s="21"/>
-      <c r="BE68" s="21"/>
-      <c r="BF68" s="21"/>
-      <c r="BG68" s="21"/>
-      <c r="BH68" s="21"/>
-      <c r="BI68" s="21"/>
-      <c r="BJ68" s="21"/>
-      <c r="BK68" s="21"/>
-      <c r="BL68" s="21"/>
-      <c r="BM68" s="21"/>
-    </row>
-    <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B69" s="4"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="4"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="4"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4"/>
-      <c r="U69" s="4"/>
-      <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
-      <c r="X69" s="4"/>
-      <c r="Y69" s="4"/>
-      <c r="Z69" s="4"/>
-      <c r="AA69" s="4"/>
-      <c r="AB69" s="4"/>
-      <c r="AC69" s="4"/>
-      <c r="AD69" s="4"/>
-      <c r="AE69" s="4"/>
-      <c r="AF69" s="4"/>
-      <c r="AG69" s="4"/>
-      <c r="AH69" s="4"/>
-      <c r="AI69" s="4"/>
-      <c r="AJ69" s="4"/>
-      <c r="AK69" s="4"/>
-      <c r="AL69" s="4"/>
-      <c r="AM69" s="4"/>
-      <c r="AN69" s="4"/>
-      <c r="AO69" s="4"/>
-      <c r="AP69" s="4"/>
-      <c r="AQ69" s="4"/>
-      <c r="AR69" s="4"/>
-      <c r="AS69" s="4"/>
-      <c r="AT69" s="4"/>
-      <c r="AU69" s="4"/>
-      <c r="AV69" s="4"/>
-      <c r="AW69" s="4"/>
-      <c r="AX69" s="4"/>
-      <c r="AY69" s="4"/>
-      <c r="AZ69" s="4"/>
-      <c r="BA69" s="4"/>
-      <c r="BB69" s="4"/>
-      <c r="BC69" s="4"/>
-      <c r="BD69" s="4"/>
-      <c r="BE69" s="4"/>
-      <c r="BF69" s="4"/>
-      <c r="BG69" s="4"/>
-      <c r="BH69" s="4"/>
-      <c r="BI69" s="4"/>
-      <c r="BJ69" s="4"/>
-      <c r="BK69" s="4"/>
-      <c r="BL69" s="4"/>
-      <c r="BM69" s="4"/>
-    </row>
-    <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B70" s="4"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="4"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="4"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
-      <c r="Q70" s="4"/>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-      <c r="T70" s="4"/>
-      <c r="U70" s="4"/>
-      <c r="V70" s="4"/>
-      <c r="W70" s="4"/>
-      <c r="X70" s="4"/>
-      <c r="Y70" s="4"/>
-      <c r="Z70" s="4"/>
-      <c r="AA70" s="4"/>
-      <c r="AB70" s="4"/>
-      <c r="AC70" s="4"/>
-      <c r="AD70" s="4"/>
-      <c r="AE70" s="4"/>
-      <c r="AF70" s="4"/>
-      <c r="AG70" s="4"/>
-      <c r="AH70" s="4"/>
-      <c r="AI70" s="4"/>
-      <c r="AJ70" s="4"/>
-      <c r="AK70" s="4"/>
-      <c r="AL70" s="4"/>
-      <c r="AM70" s="4"/>
-      <c r="AN70" s="4"/>
-      <c r="AO70" s="4"/>
-      <c r="AP70" s="4"/>
-      <c r="AQ70" s="4"/>
-      <c r="AR70" s="4"/>
-      <c r="AS70" s="4"/>
-      <c r="AT70" s="4"/>
-      <c r="AU70" s="4"/>
-      <c r="AV70" s="4"/>
-      <c r="AW70" s="4"/>
-      <c r="AX70" s="4"/>
-      <c r="AY70" s="4"/>
-      <c r="AZ70" s="4"/>
-      <c r="BA70" s="4"/>
-      <c r="BB70" s="4"/>
-      <c r="BC70" s="4"/>
-      <c r="BD70" s="4"/>
-      <c r="BE70" s="4"/>
-      <c r="BF70" s="4"/>
-      <c r="BG70" s="4"/>
-      <c r="BH70" s="4"/>
-      <c r="BI70" s="4"/>
-      <c r="BJ70" s="4"/>
-      <c r="BK70" s="4"/>
-      <c r="BL70" s="4"/>
-      <c r="BM70" s="4"/>
-    </row>
-    <row r="71" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="4"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4"/>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-      <c r="T71" s="4"/>
-      <c r="U71" s="4"/>
-      <c r="V71" s="4"/>
-      <c r="W71" s="4"/>
-      <c r="X71" s="4"/>
-      <c r="Y71" s="4"/>
-      <c r="Z71" s="4"/>
-      <c r="AA71" s="4"/>
-      <c r="AB71" s="4"/>
-      <c r="AC71" s="4"/>
-      <c r="AD71" s="4"/>
-      <c r="AE71" s="4"/>
-      <c r="AF71" s="4"/>
-      <c r="AG71" s="4"/>
-      <c r="AH71" s="4"/>
-      <c r="AI71" s="4"/>
-      <c r="AJ71" s="4"/>
-      <c r="AK71" s="4"/>
-      <c r="AL71" s="4"/>
-      <c r="AM71" s="4"/>
-      <c r="AN71" s="4"/>
-      <c r="AO71" s="4"/>
-      <c r="AP71" s="4"/>
-      <c r="AQ71" s="4"/>
-      <c r="AR71" s="4"/>
-      <c r="AS71" s="4"/>
-      <c r="AT71" s="4"/>
-      <c r="AU71" s="4"/>
-      <c r="AV71" s="4"/>
-      <c r="AW71" s="4"/>
-      <c r="AX71" s="4"/>
-      <c r="AY71" s="4"/>
-      <c r="AZ71" s="4"/>
-      <c r="BA71" s="4"/>
-      <c r="BB71" s="4"/>
-      <c r="BC71" s="4"/>
-      <c r="BD71" s="4"/>
-      <c r="BE71" s="4"/>
-      <c r="BF71" s="4"/>
-      <c r="BG71" s="4"/>
-      <c r="BH71" s="4"/>
-      <c r="BI71" s="4"/>
-      <c r="BJ71" s="4"/>
-      <c r="BK71" s="4"/>
-      <c r="BL71" s="4"/>
-      <c r="BM71" s="4"/>
-    </row>
-    <row r="72" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-      <c r="T72" s="4"/>
-      <c r="U72" s="4"/>
-      <c r="V72" s="4"/>
-      <c r="W72" s="4"/>
-      <c r="X72" s="4"/>
-      <c r="Y72" s="4"/>
-      <c r="Z72" s="4"/>
-      <c r="AA72" s="4"/>
-      <c r="AB72" s="4"/>
-      <c r="AC72" s="4"/>
-      <c r="AD72" s="4"/>
-      <c r="AE72" s="4"/>
-      <c r="AF72" s="4"/>
-      <c r="AG72" s="4"/>
-      <c r="AH72" s="4"/>
-      <c r="AI72" s="4"/>
-      <c r="AJ72" s="4"/>
-      <c r="AK72" s="4"/>
-      <c r="AL72" s="4"/>
-      <c r="AM72" s="4"/>
-      <c r="AN72" s="4"/>
-      <c r="AO72" s="4"/>
-      <c r="AP72" s="4"/>
-      <c r="AQ72" s="4"/>
-      <c r="AR72" s="4"/>
-      <c r="AS72" s="4"/>
-      <c r="AT72" s="4"/>
-      <c r="AU72" s="4"/>
-      <c r="AV72" s="4"/>
-      <c r="AW72" s="4"/>
-      <c r="AX72" s="4"/>
-      <c r="AY72" s="4"/>
-      <c r="AZ72" s="4"/>
-      <c r="BA72" s="4"/>
-      <c r="BB72" s="4"/>
-      <c r="BC72" s="4"/>
-      <c r="BD72" s="4"/>
-      <c r="BE72" s="4"/>
-      <c r="BF72" s="4"/>
-      <c r="BG72" s="4"/>
-      <c r="BH72" s="4"/>
-      <c r="BI72" s="4"/>
-      <c r="BJ72" s="4"/>
-      <c r="BK72" s="4"/>
-      <c r="BL72" s="4"/>
-      <c r="BM72" s="4"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="4"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="4"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="4"/>
-      <c r="U73" s="4"/>
-      <c r="V73" s="4"/>
-      <c r="W73" s="4"/>
-      <c r="X73" s="4"/>
-      <c r="Y73" s="4"/>
-      <c r="Z73" s="4"/>
-      <c r="AA73" s="4"/>
-      <c r="AB73" s="4"/>
-      <c r="AC73" s="4"/>
-      <c r="AD73" s="4"/>
-      <c r="AE73" s="4"/>
-      <c r="AF73" s="4"/>
-      <c r="AG73" s="4"/>
-      <c r="AH73" s="4"/>
-      <c r="AI73" s="4"/>
-      <c r="AJ73" s="4"/>
-      <c r="AK73" s="4"/>
-      <c r="AL73" s="4"/>
-      <c r="AM73" s="4"/>
-      <c r="AN73" s="4"/>
-      <c r="AO73" s="4"/>
-      <c r="AP73" s="4"/>
-      <c r="AQ73" s="4"/>
-      <c r="AR73" s="4"/>
-      <c r="AS73" s="4"/>
-      <c r="AT73" s="4"/>
-      <c r="AU73" s="4"/>
-      <c r="AV73" s="4"/>
-      <c r="AW73" s="4"/>
-      <c r="AX73" s="4"/>
-      <c r="AY73" s="4"/>
-      <c r="AZ73" s="4"/>
-      <c r="BA73" s="4"/>
-      <c r="BB73" s="4"/>
-      <c r="BC73" s="4"/>
-      <c r="BD73" s="4"/>
-      <c r="BE73" s="4"/>
-      <c r="BF73" s="4"/>
-      <c r="BG73" s="4"/>
-      <c r="BH73" s="4"/>
-      <c r="BI73" s="4"/>
-      <c r="BJ73" s="4"/>
-      <c r="BK73" s="4"/>
-      <c r="BL73" s="4"/>
-      <c r="BM73" s="4"/>
-    </row>
-    <row r="74" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B74" s="4"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="4"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="4"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
-      <c r="T74" s="4"/>
-      <c r="U74" s="4"/>
-      <c r="V74" s="4"/>
-      <c r="W74" s="4"/>
-      <c r="X74" s="4"/>
-      <c r="Y74" s="4"/>
-      <c r="Z74" s="4"/>
-      <c r="AA74" s="4"/>
-      <c r="AB74" s="4"/>
-      <c r="AC74" s="4"/>
-      <c r="AD74" s="4"/>
-      <c r="AE74" s="4"/>
-      <c r="AF74" s="4"/>
-      <c r="AG74" s="4"/>
-      <c r="AH74" s="4"/>
-      <c r="AI74" s="4"/>
-      <c r="AJ74" s="4"/>
-      <c r="AK74" s="4"/>
-      <c r="AL74" s="4"/>
-      <c r="AM74" s="4"/>
-      <c r="AN74" s="4"/>
-      <c r="AO74" s="4"/>
-      <c r="AP74" s="4"/>
-      <c r="AQ74" s="4"/>
-      <c r="AR74" s="4"/>
-      <c r="AS74" s="4"/>
-      <c r="AT74" s="4"/>
-      <c r="AU74" s="4"/>
-      <c r="AV74" s="4"/>
-      <c r="AW74" s="4"/>
-      <c r="AX74" s="4"/>
-      <c r="AY74" s="4"/>
-      <c r="AZ74" s="4"/>
-      <c r="BA74" s="4"/>
-      <c r="BB74" s="4"/>
-      <c r="BC74" s="4"/>
-      <c r="BD74" s="4"/>
-      <c r="BE74" s="4"/>
-      <c r="BF74" s="4"/>
-      <c r="BG74" s="4"/>
-      <c r="BH74" s="4"/>
-      <c r="BI74" s="4"/>
-      <c r="BJ74" s="4"/>
-      <c r="BK74" s="4"/>
-      <c r="BL74" s="4"/>
-      <c r="BM74" s="4"/>
-    </row>
-    <row r="75" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="4"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="4"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="4"/>
-      <c r="U75" s="4"/>
-      <c r="V75" s="4"/>
-      <c r="W75" s="4"/>
-      <c r="X75" s="4"/>
-      <c r="Y75" s="4"/>
-      <c r="Z75" s="4"/>
-      <c r="AA75" s="4"/>
-      <c r="AB75" s="4"/>
-      <c r="AC75" s="4"/>
-      <c r="AD75" s="4"/>
-      <c r="AE75" s="4"/>
-      <c r="AF75" s="4"/>
-      <c r="AG75" s="4"/>
-      <c r="AH75" s="4"/>
-      <c r="AI75" s="4"/>
-      <c r="AJ75" s="4"/>
-      <c r="AK75" s="4"/>
-      <c r="AL75" s="4"/>
-      <c r="AM75" s="4"/>
-      <c r="AN75" s="4"/>
-      <c r="AO75" s="4"/>
-      <c r="AP75" s="4"/>
-      <c r="AQ75" s="4"/>
-      <c r="AR75" s="4"/>
-      <c r="AS75" s="4"/>
-      <c r="AT75" s="4"/>
-      <c r="AU75" s="4"/>
-      <c r="AV75" s="4"/>
-      <c r="AW75" s="4"/>
-      <c r="AX75" s="4"/>
-      <c r="AY75" s="4"/>
-      <c r="AZ75" s="4"/>
-      <c r="BA75" s="4"/>
-      <c r="BB75" s="4"/>
-      <c r="BC75" s="4"/>
-      <c r="BD75" s="4"/>
-      <c r="BE75" s="4"/>
-      <c r="BF75" s="4"/>
-      <c r="BG75" s="4"/>
-      <c r="BH75" s="4"/>
-      <c r="BI75" s="4"/>
-      <c r="BJ75" s="4"/>
-      <c r="BK75" s="4"/>
-      <c r="BL75" s="4"/>
-      <c r="BM75" s="4"/>
-    </row>
-    <row r="76" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B76" s="4"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="4"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="4"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="4"/>
-      <c r="M76" s="4"/>
-      <c r="N76" s="4"/>
-      <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
-      <c r="Q76" s="4"/>
-      <c r="R76" s="4"/>
-      <c r="S76" s="4"/>
-      <c r="T76" s="4"/>
-      <c r="U76" s="4"/>
-      <c r="V76" s="4"/>
-      <c r="W76" s="4"/>
-      <c r="X76" s="4"/>
-      <c r="Y76" s="4"/>
-      <c r="Z76" s="4"/>
-      <c r="AA76" s="4"/>
-      <c r="AB76" s="4"/>
-      <c r="AC76" s="4"/>
-      <c r="AD76" s="4"/>
-      <c r="AE76" s="4"/>
-      <c r="AF76" s="4"/>
-      <c r="AG76" s="4"/>
-      <c r="AH76" s="4"/>
-      <c r="AI76" s="4"/>
-      <c r="AJ76" s="4"/>
-      <c r="AK76" s="4"/>
-      <c r="AL76" s="4"/>
-      <c r="AM76" s="4"/>
-      <c r="AN76" s="4"/>
-      <c r="AO76" s="4"/>
-      <c r="AP76" s="4"/>
-      <c r="AQ76" s="4"/>
-      <c r="AR76" s="4"/>
-      <c r="AS76" s="4"/>
-      <c r="AT76" s="4"/>
-      <c r="AU76" s="4"/>
-      <c r="AV76" s="4"/>
-      <c r="AW76" s="4"/>
-      <c r="AX76" s="4"/>
-      <c r="AY76" s="4"/>
-      <c r="AZ76" s="4"/>
-      <c r="BA76" s="4"/>
-      <c r="BB76" s="4"/>
-      <c r="BC76" s="4"/>
-      <c r="BD76" s="4"/>
-      <c r="BE76" s="4"/>
-      <c r="BF76" s="4"/>
-      <c r="BG76" s="4"/>
-      <c r="BH76" s="4"/>
-      <c r="BI76" s="4"/>
-      <c r="BJ76" s="4"/>
-      <c r="BK76" s="4"/>
-      <c r="BL76" s="4"/>
-      <c r="BM76" s="4"/>
-    </row>
-    <row r="77" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B77" s="4"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="4"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="4"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="4"/>
-      <c r="M77" s="4"/>
-      <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
-      <c r="Q77" s="4"/>
-      <c r="R77" s="4"/>
-      <c r="S77" s="4"/>
-      <c r="T77" s="4"/>
-      <c r="U77" s="4"/>
-      <c r="V77" s="4"/>
-      <c r="W77" s="4"/>
-      <c r="X77" s="4"/>
-      <c r="Y77" s="4"/>
-      <c r="Z77" s="4"/>
-      <c r="AA77" s="4"/>
-      <c r="AB77" s="4"/>
-      <c r="AC77" s="4"/>
-      <c r="AD77" s="4"/>
-      <c r="AE77" s="4"/>
-      <c r="AF77" s="4"/>
-      <c r="AG77" s="4"/>
-      <c r="AH77" s="4"/>
-      <c r="AI77" s="4"/>
-      <c r="AJ77" s="4"/>
-      <c r="AK77" s="4"/>
-      <c r="AL77" s="4"/>
-      <c r="AM77" s="4"/>
-      <c r="AN77" s="4"/>
-      <c r="AO77" s="4"/>
-      <c r="AP77" s="4"/>
-      <c r="AQ77" s="4"/>
-      <c r="AR77" s="4"/>
-      <c r="AS77" s="4"/>
-      <c r="AT77" s="4"/>
-      <c r="AU77" s="4"/>
-      <c r="AV77" s="4"/>
-      <c r="AW77" s="4"/>
-      <c r="AX77" s="4"/>
-      <c r="AY77" s="4"/>
-      <c r="AZ77" s="4"/>
-      <c r="BA77" s="4"/>
-      <c r="BB77" s="4"/>
-      <c r="BC77" s="4"/>
-      <c r="BD77" s="4"/>
-      <c r="BE77" s="4"/>
-      <c r="BF77" s="4"/>
-      <c r="BG77" s="4"/>
-      <c r="BH77" s="4"/>
-      <c r="BI77" s="4"/>
-      <c r="BJ77" s="4"/>
-      <c r="BK77" s="4"/>
-      <c r="BL77" s="4"/>
-      <c r="BM77" s="4"/>
-    </row>
-    <row r="78" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="4"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="4"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4"/>
-      <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
-      <c r="Q78" s="4"/>
-      <c r="R78" s="4"/>
-      <c r="S78" s="4"/>
-      <c r="T78" s="4"/>
-      <c r="U78" s="4"/>
-      <c r="V78" s="4"/>
-      <c r="W78" s="4"/>
-      <c r="X78" s="4"/>
-      <c r="Y78" s="4"/>
-      <c r="Z78" s="4"/>
-      <c r="AA78" s="4"/>
-      <c r="AB78" s="4"/>
-      <c r="AC78" s="4"/>
-      <c r="AD78" s="4"/>
-      <c r="AE78" s="4"/>
-      <c r="AF78" s="4"/>
-      <c r="AG78" s="4"/>
-      <c r="AH78" s="4"/>
-      <c r="AI78" s="4"/>
-      <c r="AJ78" s="4"/>
-      <c r="AK78" s="4"/>
-      <c r="AL78" s="4"/>
-      <c r="AM78" s="4"/>
-      <c r="AN78" s="4"/>
-      <c r="AO78" s="4"/>
-      <c r="AP78" s="4"/>
-      <c r="AQ78" s="4"/>
-      <c r="AR78" s="4"/>
-      <c r="AS78" s="4"/>
-      <c r="AT78" s="4"/>
-      <c r="AU78" s="4"/>
-      <c r="AV78" s="4"/>
-      <c r="AW78" s="4"/>
-      <c r="AX78" s="4"/>
-      <c r="AY78" s="4"/>
-      <c r="AZ78" s="4"/>
-      <c r="BA78" s="4"/>
-      <c r="BB78" s="4"/>
-      <c r="BC78" s="4"/>
-      <c r="BD78" s="4"/>
-      <c r="BE78" s="4"/>
-      <c r="BF78" s="4"/>
-      <c r="BG78" s="4"/>
-      <c r="BH78" s="4"/>
-      <c r="BI78" s="4"/>
-      <c r="BJ78" s="4"/>
-      <c r="BK78" s="4"/>
-      <c r="BL78" s="4"/>
-      <c r="BM78" s="4"/>
+    <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
+      <c r="AB65" s="4"/>
+      <c r="AC65" s="4"/>
+      <c r="AD65" s="4"/>
+      <c r="AE65" s="4"/>
+      <c r="AF65" s="4"/>
+      <c r="AG65" s="4"/>
+      <c r="AH65" s="4"/>
+      <c r="AI65" s="4"/>
+      <c r="AJ65" s="4"/>
+      <c r="AK65" s="4"/>
+      <c r="AL65" s="4"/>
+      <c r="AM65" s="4"/>
+      <c r="AN65" s="4"/>
+      <c r="AO65" s="4"/>
+      <c r="AP65" s="4"/>
+      <c r="AQ65" s="4"/>
+      <c r="AR65" s="4"/>
+      <c r="AS65" s="4"/>
+      <c r="AT65" s="4"/>
+      <c r="AU65" s="4"/>
+      <c r="AV65" s="4"/>
+      <c r="AW65" s="4"/>
+      <c r="AX65" s="4"/>
+      <c r="AY65" s="4"/>
+      <c r="AZ65" s="4"/>
+      <c r="BA65" s="4"/>
+      <c r="BB65" s="4"/>
+      <c r="BC65" s="4"/>
+      <c r="BD65" s="4"/>
+      <c r="BE65" s="4"/>
+      <c r="BF65" s="4"/>
+      <c r="BG65" s="4"/>
+      <c r="BH65" s="4"/>
+      <c r="BI65" s="4"/>
+      <c r="BJ65" s="4"/>
+      <c r="BK65" s="4"/>
+      <c r="BL65" s="4"/>
+      <c r="BM65" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="72">
+  <mergeCells count="59">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -29328,31 +26707,18 @@
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="A62:V62"/>
-    <mergeCell ref="A68:BM68"/>
-    <mergeCell ref="A69:BM69"/>
-    <mergeCell ref="A70:BM70"/>
-    <mergeCell ref="A71:BM71"/>
-    <mergeCell ref="A72:BM72"/>
-    <mergeCell ref="A73:BM73"/>
-    <mergeCell ref="A74:BM74"/>
-    <mergeCell ref="A75:BM75"/>
-    <mergeCell ref="A76:BM76"/>
-    <mergeCell ref="A77:BM77"/>
-    <mergeCell ref="A78:BM78"/>
+    <mergeCell ref="A49:V49"/>
+    <mergeCell ref="A55:BM55"/>
+    <mergeCell ref="A56:BM56"/>
+    <mergeCell ref="A57:BM57"/>
+    <mergeCell ref="A58:BM58"/>
+    <mergeCell ref="A59:BM59"/>
+    <mergeCell ref="A60:BM60"/>
+    <mergeCell ref="A61:BM61"/>
+    <mergeCell ref="A62:BM62"/>
+    <mergeCell ref="A63:BM63"/>
+    <mergeCell ref="A64:BM64"/>
+    <mergeCell ref="A65:BM65"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="313">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 18/05/2026 07:30:58</t>
+    <t xml:space="preserve">Emitido em: 19/05/2026 05:30:31</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -262,565 +262,646 @@
     <t xml:space="preserve">Não</t>
   </si>
   <si>
+    <t xml:space="preserve">7.808 - ABCC -REJUNTABRAS INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">788,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260454542238000178550010000965331000963341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">785 - MEBER METAIS S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316.844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/04/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158,47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260487547907000153550050003168441492652194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.615 - MADELUSTRE INDUSTRIAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.012,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260589616460000152550020000713281306751109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">636.071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.022,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006360711913994222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.976.319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.756,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">777 - IRMAOS FISCHER S.A IND. E COM.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780.743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">760,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582984287000104550020017807431502859010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780.742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.332,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582984287000104550020017807421113944451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.780.741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.549,24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582984287000104550020017807411668968281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.975.491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.092,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260561413282000143550010029754911228653957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">790 - JACKWAL S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.834,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260592782366000188550030002751961654432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.265,79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - FILIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">637.255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.761,14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006372551066202512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.376 - ELETRO ZAGONEL LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">662.150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.581,90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260581365223000154550020006621501364814580</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">870.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.603,35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008700041500773535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">637.784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.890,24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006377841750929843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">870.017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.185,87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008700171161145098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804111200730267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804981991793601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804121347149640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.304.071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">426,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260550949528001232550010023040711903090311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">870.047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.695,18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008700471155162406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.929,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829821661840971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">461,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829961140036509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">638.725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.887,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006387251174884389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.702,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260527254297000178550010000105531584622070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.709,55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260581604803000157550010008671441582155041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">750 - COPLAS INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200.251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.314,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260567718726000135550010002002511236212733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.078,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006397451885129080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640.215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.963,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006402151526143499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640.584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.104,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006405841317875822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.318 - CORTAG INDUSTRIA E COMERCIO LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">872.917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.671,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260500808396000521550010008729171646262800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.825,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260581604803000157550010008672241503823847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">641.031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499,53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006410311154255425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">481,59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050855671736636271</t>
+  </si>
+  <si>
     <t xml:space="preserve">33.065 - LUXMUNDO COMERCIO IMPORTACAO EXPORTACAO</t>
   </si>
   <si>
-    <t xml:space="preserve">66.527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">164,52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29260429244900000247550010000665271143138443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.808 - ABCC -REJUNTABRAS INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">788,62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260454542238000178550010000965331000963341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">785 - MEBER METAIS S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95.349,48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260487547907000153550050003175221341934744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972.380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.384,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029723801722131595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972.384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.305,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029723841503152901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.972.382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.545,08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029723821252250954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">317.678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.775,54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260487547907000153550050003176781577672540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158,47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260487547907000153550050003168441492652194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.615 - MADELUSTRE INDUSTRIAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.012,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260589616460000152550020000713281306751109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.973.037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.434,01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260461413282000143550010029730371035091800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">636.071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.022,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006360711913994222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.976.319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.756,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">777 - IRMAOS FISCHER S.A IND. E COM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807431502859010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.332,17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807421113944451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.549,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807411668968281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.975.491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.092,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260561413282000143550010029754911228653957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">790 - JACKWAL S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.834,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260592782366000188550030002751961654432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.265,79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - FILIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">637.255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.761,14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006372551066202512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.376 - ELETRO ZAGONEL LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">662.150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.581,90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260581365223000154550020006621501364814580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">870.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.603,35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008700041500773535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">637.784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.890,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006377841750929843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">870.017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.185,87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008700171161145098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804111200730267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804981991793601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804121347149640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.304.071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">426,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260550949528001232550010023040711903090311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">870.047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.695,18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008700471155162406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.929,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829821661840971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">461,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829961140036509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">638.725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.887,04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006387251174884389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.702,49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260527254297000178550010000105531584622070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.709,55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260581604803000157550010008671441582155041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">750 - COPLAS INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.314,33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260567718726000135550010002002511236212733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.078,63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006397451885129080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">640.215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.963,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006402151526143499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">640.584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.104,02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006405841317875822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.318 - CORTAG INDUSTRIA E COMERCIO LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">872.917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.671,17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260500808396000521550010008729171646262800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.825,13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260581604803000157550010008672241503823847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.485 - ABRILAR INDUSTRIA DE ESQUADRIAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">60.289,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260511169963000130550010000470141335411420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">641.031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499,53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006410311154255425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.085.567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">481,59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050855671736636271</t>
+    <t xml:space="preserve">67.336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.783,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.647 - ACCERT TRANSPORTES E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86,50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260529244900000247550010000673361492026159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260505222092001069570010000389411006647635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">785,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007588261717357519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.802 - VINICOLOR IND. E COM. DE TINTAS, TEXTURA E GRAFIATO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">242.611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.342,94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260507855544000184550010002426111067151486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">642.487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.040,61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006424871547022207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.167 - ATLAS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.401,84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260589723837000172550000006880631168529645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.101 - SIMON MATERIAIS ELETRICOS E ELETRONICOS LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31260507159430000361550010000876141954082958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.671,51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31260507159430000361550010000876201881086441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.410 - SAN HO COMERCIO IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.610,71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.965 - RTL ENCOMENDAS E CARGAS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">652,54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260517328359000195550010000848441256212101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260531607598000105570010000932131000660870</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.238 - EURO METAIS IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">319,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260510317038000146550010000665871272565371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.015 - FOCO METALLO FABRICACAO E MONTAGEM DE LUMINARIAS E COMERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.140,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.724.082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.618 - ALFA TRANSPORTES EIRELI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">242,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260522670837000180550010000233691542222518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582110818000121570000077240821090348638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.444 - PRIME BRAS SEGURANCA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.460,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260532296669000169550030000014561732534080</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17066,7 +17147,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM65"/>
+  <dimension ref="A1:BM68"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17629,7 +17710,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>305624</v>
+        <v>305865</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>80</v>
@@ -17647,16 +17728,16 @@
         <v>82</v>
       </c>
       <c r="I6" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>84</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>164.52</v>
+        <v>788.62</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
@@ -17665,43 +17746,43 @@
         <v>1</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>149.9</v>
+        <v>788.62</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0</v>
+        <v>0.258</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="W6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Y6" s="12" t="n">
-        <v>14.62</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>149.9</v>
+        <v>788.62</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>6</v>
+        <v>55.2</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17767,7 +17848,7 @@
         <v>74</v>
       </c>
       <c r="AW6" s="14" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AX6" s="10" t="s">
         <v>86</v>
@@ -17820,7 +17901,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>305865</v>
+        <v>306716</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>88</v>
@@ -17832,22 +17913,22 @@
         <v>89</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>788.62</v>
+        <v>158.47</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17856,43 +17937,43 @@
         <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>788.62</v>
+        <v>148.8</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>0</v>
+        <v>9.67</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>788.62</v>
+        <v>158.47</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>55.2</v>
+        <v>11.09</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17958,10 +18039,10 @@
         <v>74</v>
       </c>
       <c r="AW7" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>75</v>
@@ -17997,7 +18078,7 @@
         <v>69</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -18011,79 +18092,79 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>306378</v>
+        <v>306769</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>95349.48</v>
+        <v>5012.28</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>91519.49</v>
+        <v>4567</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.80555</v>
+        <v>0</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>424.1</v>
+        <v>0</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>82.61</v>
+        <v>40.75</v>
       </c>
       <c r="W8" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>3829.99</v>
+        <v>445.28</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>91519.49</v>
+        <v>4567</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>6406.35</v>
+        <v>319.68</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -18149,7 +18230,7 @@
         <v>74</v>
       </c>
       <c r="AW8" s="14" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="AX8" s="10" t="s">
         <v>86</v>
@@ -18188,7 +18269,7 @@
         <v>69</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18202,79 +18283,79 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>306535</v>
+        <v>306945</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>5384.2</v>
+        <v>11022.8</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>5384.2</v>
+        <v>11022.8</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.023054</v>
+        <v>0.0217</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>28.62</v>
+        <v>2.44</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="Y9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>0</v>
+        <v>11022.8</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>0</v>
+        <v>771.6</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18340,10 +18421,10 @@
         <v>74</v>
       </c>
       <c r="AW9" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18379,7 +18460,7 @@
         <v>69</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18393,79 +18474,79 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>306536</v>
+        <v>307020</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G10" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>8305.8</v>
+        <v>1756.8</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>8305.8</v>
+        <v>1756.8</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.02159</v>
+        <v>0.142272</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>29.29</v>
+        <v>3.42</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="Y10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>0</v>
+        <v>1756.8</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>0</v>
+        <v>122.98</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18531,10 +18612,10 @@
         <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18570,7 +18651,7 @@
         <v>69</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18584,25 +18665,25 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>306537</v>
+        <v>307044</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>69</v>
@@ -18611,31 +18692,31 @@
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>18545.08</v>
+        <v>760.8</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>18545.08</v>
+        <v>760.8</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.582728</v>
+        <v>0.09178</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>76.55</v>
+        <v>14.15</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
@@ -18647,16 +18728,16 @@
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="Y11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>0</v>
+        <v>760.8</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>0</v>
+        <v>53.26</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18722,7 +18803,7 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX11" s="10" t="s">
         <v>77</v>
@@ -18761,7 +18842,7 @@
         <v>69</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18775,79 +18856,79 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>306568</v>
+        <v>307045</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I12" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="G12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>104</v>
-      </c>
       <c r="J12" s="9" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>32775.54</v>
+        <v>1332.17</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>31565.22</v>
+        <v>1332.17</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>1.03129</v>
+        <v>0.017488</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>102.16</v>
+        <v>8.85</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>83.35</v>
+        <v>0</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>1210.32</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>31565.22</v>
+        <v>1332.17</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>2209.57</v>
+        <v>53.29</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18913,10 +18994,10 @@
         <v>74</v>
       </c>
       <c r="AW12" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>75</v>
@@ -18952,7 +19033,7 @@
         <v>69</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18966,79 +19047,79 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>306716</v>
+        <v>307046</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>95</v>
+        <v>117</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>69</v>
+        <v>125</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>158.47</v>
+        <v>39549.24</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>148.8</v>
+        <v>36406.48</v>
       </c>
       <c r="P13" s="12" t="n">
-        <v>0</v>
+        <v>1877.94</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0</v>
+        <v>2.71203</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>0</v>
+        <v>520.9</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>9.67</v>
+        <v>1264.82</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>158.47</v>
+        <v>38284.42</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>11.09</v>
+        <v>2330.38</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19104,10 +19185,10 @@
         <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -19143,7 +19224,7 @@
         <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19157,79 +19238,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>306769</v>
+        <v>307062</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>5012.28</v>
+        <v>94092.8</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>4567</v>
+        <v>93172</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0</v>
+        <v>2.122527</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>0</v>
+        <v>493.99</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>40.75</v>
+        <v>90</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>445.28</v>
+        <v>920.8</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>4567</v>
+        <v>92335.42</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>319.68</v>
+        <v>5743.16</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19295,7 +19376,7 @@
         <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AX14" s="10" t="s">
         <v>86</v>
@@ -19334,7 +19415,7 @@
         <v>69</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19348,79 +19429,79 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>306801</v>
+        <v>307073</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>26434.01</v>
+        <v>7834.72</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>25783.04</v>
+        <v>7524.33</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.47642</v>
+        <v>0</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>56.65</v>
+        <v>0</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>650.97</v>
+        <v>310.39</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>25783.04</v>
+        <v>7524.33</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>1265.66</v>
+        <v>526.7</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19486,7 +19567,7 @@
         <v>74</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX15" s="10" t="s">
         <v>86</v>
@@ -19525,7 +19606,7 @@
         <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19539,79 +19620,79 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>306945</v>
+        <v>307133</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>11022.8</v>
+        <v>4265.79</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>11022.8</v>
+        <v>4222.88</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.0217</v>
+        <v>0.484131</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>2.44</v>
+        <v>71.4</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>0</v>
+        <v>42.91</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>11022.8</v>
+        <v>4222.88</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>771.6</v>
+        <v>281.12</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19677,7 +19758,7 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX16" s="10" t="s">
         <v>86</v>
@@ -19716,7 +19797,7 @@
         <v>69</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19730,34 +19811,34 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>307020</v>
+        <v>307142</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1756.8</v>
+        <v>20761.14</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19766,43 +19847,43 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>1756.8</v>
+        <v>20761.14</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.142272</v>
+        <v>0.01152</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>3.42</v>
+        <v>2.23</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="Y17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>1756.8</v>
+        <v>20761.14</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>122.98</v>
+        <v>1453.28</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19868,7 +19949,7 @@
         <v>74</v>
       </c>
       <c r="AW17" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX17" s="10" t="s">
         <v>86</v>
@@ -19907,7 +19988,7 @@
         <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19921,34 +20002,34 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>307044</v>
+        <v>307146</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>760.8</v>
+        <v>6581.9</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -19957,43 +20038,43 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>760.8</v>
+        <v>6581.9</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.09178</v>
+        <v>0</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>14.15</v>
+        <v>416.22</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>760.8</v>
+        <v>6581.9</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>53.26</v>
+        <v>460.73</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20059,10 +20140,10 @@
         <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -20098,7 +20179,7 @@
         <v>69</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20112,34 +20193,34 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>307045</v>
+        <v>307159</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>1332.17</v>
+        <v>1603.35</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -20148,43 +20229,43 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>1332.17</v>
+        <v>1527</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.017488</v>
+        <v>0.05265</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>8.85</v>
+        <v>30</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>0</v>
+        <v>76.35</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>1332.17</v>
+        <v>1527</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>53.29</v>
+        <v>106.89</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20250,10 +20331,10 @@
         <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20289,7 +20370,7 @@
         <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20303,79 +20384,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>307046</v>
+        <v>307161</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>147</v>
+        <v>103</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>39549.24</v>
+        <v>4890.24</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>36406.48</v>
+        <v>4890.24</v>
       </c>
       <c r="P20" s="12" t="n">
-        <v>1877.94</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>2.71203</v>
+        <v>0.001296</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>520.9</v>
+        <v>2.22</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>1264.82</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>38284.42</v>
+        <v>4890.24</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>2330.38</v>
+        <v>342.32</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20441,7 +20522,7 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX20" s="10" t="s">
         <v>86</v>
@@ -20480,7 +20561,7 @@
         <v>69</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20494,79 +20575,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>307062</v>
+        <v>307162</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>94092.8</v>
+        <v>1185.87</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>93172</v>
+        <v>1129.4</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>2.122527</v>
+        <v>0.0351</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>493.99</v>
+        <v>20</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>90</v>
+        <v>14</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>920.8</v>
+        <v>56.47</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>92335.42</v>
+        <v>1129.4</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>5743.16</v>
+        <v>79.06</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20632,7 +20713,7 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX21" s="10" t="s">
         <v>86</v>
@@ -20671,7 +20752,7 @@
         <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20685,52 +20766,52 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>307073</v>
+        <v>307171</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>139</v>
+        <v>69</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>7834.72</v>
+        <v>404.81</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>7524.33</v>
+        <v>404.81</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0</v>
+        <v>0.000858</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
@@ -20742,22 +20823,22 @@
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="Y22" s="12" t="n">
-        <v>310.39</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>7524.33</v>
+        <v>404.81</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>526.7</v>
+        <v>16.19</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20823,10 +20904,10 @@
         <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20876,79 +20957,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>307133</v>
+        <v>307173</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>170</v>
+        <v>69</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>4265.79</v>
+        <v>404.81</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>4222.88</v>
+        <v>404.81</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.484131</v>
+        <v>0.000858</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>71.4</v>
+        <v>2.43</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="W23" s="9" t="s">
-        <v>172</v>
+        <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>42.91</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>4222.88</v>
+        <v>404.81</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>281.12</v>
+        <v>16.19</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21014,10 +21095,10 @@
         <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21053,7 +21134,7 @@
         <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21067,34 +21148,34 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>307142</v>
+        <v>307174</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>20761.14</v>
+        <v>404.81</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
@@ -21103,43 +21184,43 @@
         <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>20761.14</v>
+        <v>404.81</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.01152</v>
+        <v>0.000858</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="Y24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>20761.14</v>
+        <v>404.81</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>1453.28</v>
+        <v>16.19</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21205,10 +21286,10 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21244,7 +21325,7 @@
         <v>69</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21258,79 +21339,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>307146</v>
+        <v>307181</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>125</v>
+        <v>66</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>6581.9</v>
+        <v>426.2</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>6581.9</v>
+        <v>426.2</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0</v>
+        <v>0.0025</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>416.22</v>
+        <v>10</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>6581.9</v>
+        <v>426.2</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>460.73</v>
+        <v>29.84</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21396,7 +21477,7 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX25" s="10" t="s">
         <v>86</v>
@@ -21435,7 +21516,7 @@
         <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21449,58 +21530,58 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>307159</v>
+        <v>307183</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>1603.35</v>
+        <v>12695.18</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>1527</v>
+        <v>11935.6</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.05265</v>
+        <v>0.0698</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>30</v>
+        <v>31.68</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
@@ -21512,16 +21593,16 @@
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>76.35</v>
+        <v>759.58</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>1527</v>
+        <v>11935.6</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>106.89</v>
+        <v>614.43</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21587,7 +21668,7 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX26" s="10" t="s">
         <v>86</v>
@@ -21626,7 +21707,7 @@
         <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21640,34 +21721,34 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>307161</v>
+        <v>307231</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>4890.24</v>
+        <v>2929.6</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -21676,43 +21757,43 @@
         <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>4890.24</v>
+        <v>2929.6</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.001296</v>
+        <v>0.000484</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>2.22</v>
+        <v>3.22</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="Y27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>4890.24</v>
+        <v>2929.6</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>342.32</v>
+        <v>205.07</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21778,7 +21859,7 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX27" s="10" t="s">
         <v>86</v>
@@ -21817,7 +21898,7 @@
         <v>69</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21831,34 +21912,34 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>307162</v>
+        <v>307235</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>191</v>
+        <v>69</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>1185.87</v>
+        <v>461.96</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -21867,43 +21948,43 @@
         <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>1129.4</v>
+        <v>461.96</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.0351</v>
+        <v>0.002057</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>20</v>
+        <v>2.43</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>56.47</v>
+        <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>1129.4</v>
+        <v>461.96</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>79.06</v>
+        <v>18.48</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21969,10 +22050,10 @@
         <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -22008,7 +22089,7 @@
         <v>69</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22022,34 +22103,34 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>307171</v>
+        <v>307242</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>194</v>
+        <v>103</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>69</v>
+        <v>189</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>404.81</v>
+        <v>1887.04</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -22058,43 +22139,43 @@
         <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>404.81</v>
+        <v>1887.04</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.007832</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="Y29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>404.81</v>
+        <v>1887.04</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>16.19</v>
+        <v>132.09</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22160,10 +22241,10 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -22199,7 +22280,7 @@
         <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22213,34 +22294,34 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>307173</v>
+        <v>307265</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>69</v>
+        <v>145</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>404.81</v>
+        <v>3702.49</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22249,43 +22330,43 @@
         <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>404.81</v>
+        <v>3437.49</v>
       </c>
       <c r="P30" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.000858</v>
+        <v>0</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="Y30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>404.81</v>
+        <v>3702.49</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>16.19</v>
+        <v>259.17</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22351,10 +22432,10 @@
         <v>74</v>
       </c>
       <c r="AW30" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX30" s="10" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="AY30" s="14" t="s">
         <v>75</v>
@@ -22390,7 +22471,7 @@
         <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22404,79 +22485,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>307174</v>
+        <v>307278</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>404.81</v>
+        <v>29709.55</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>404.81</v>
+        <v>29280.46</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.69578</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>2.43</v>
+        <v>130.96</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="W31" s="9" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>0</v>
+        <v>429.09</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>404.81</v>
+        <v>29280.46</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>16.19</v>
+        <v>1794.18</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22542,10 +22623,10 @@
         <v>74</v>
       </c>
       <c r="AW31" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22581,7 +22662,7 @@
         <v>69</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22595,25 +22676,25 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>307181</v>
+        <v>307297</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="J32" s="9" t="s">
         <v>204</v>
@@ -22622,25 +22703,25 @@
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>426.2</v>
+        <v>3314.33</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>426.2</v>
+        <v>3210</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.0025</v>
+        <v>0</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
@@ -22652,22 +22733,22 @@
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>0</v>
+        <v>104.33</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>426.2</v>
+        <v>3210</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>29.84</v>
+        <v>224.7</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22733,7 +22814,7 @@
         <v>74</v>
       </c>
       <c r="AW32" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX32" s="10" t="s">
         <v>86</v>
@@ -22786,10 +22867,10 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>307183</v>
+        <v>307330</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>182</v>
+        <v>103</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
@@ -22798,40 +22879,40 @@
         <v>207</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>12695.18</v>
+        <v>7078.63</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>11935.6</v>
+        <v>6646.6</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.0698</v>
+        <v>0.0425</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>31.68</v>
+        <v>9.6</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
@@ -22843,22 +22924,22 @@
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>759.58</v>
+        <v>432.03</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>11935.6</v>
+        <v>6646.6</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>614.43</v>
+        <v>465.26</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22924,7 +23005,7 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX33" s="10" t="s">
         <v>86</v>
@@ -22977,10 +23058,10 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>307231</v>
+        <v>307334</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>194</v>
+        <v>103</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -22989,22 +23070,22 @@
         <v>210</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="I34" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="J34" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="J34" s="9" t="s">
-        <v>212</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>2929.6</v>
+        <v>4963.92</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -23013,43 +23094,43 @@
         <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>2929.6</v>
+        <v>4963.92</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.000484</v>
+        <v>0.029904</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>3.22</v>
+        <v>6.84</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="Y34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>2929.6</v>
+        <v>4963.92</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>205.07</v>
+        <v>347.47</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23115,7 +23196,7 @@
         <v>74</v>
       </c>
       <c r="AW34" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX34" s="10" t="s">
         <v>86</v>
@@ -23154,7 +23235,7 @@
         <v>69</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="BK34" s="9" t="s">
         <v>75</v>
@@ -23168,34 +23249,34 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>307235</v>
+        <v>307356</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>194</v>
+        <v>103</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="I35" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="J35" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>461.96</v>
+        <v>2104.02</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
@@ -23204,43 +23285,43 @@
         <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>461.96</v>
+        <v>2104.02</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.002057</v>
+        <v>0.005548</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>2.43</v>
+        <v>1.08</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="Y35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>461.96</v>
+        <v>2104.02</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>18.48</v>
+        <v>147.28</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23306,10 +23387,10 @@
         <v>74</v>
       </c>
       <c r="AW35" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23345,7 +23426,7 @@
         <v>69</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23359,10 +23440,10 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>307242</v>
+        <v>307367</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>134</v>
+        <v>217</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
@@ -23371,40 +23452,40 @@
         <v>218</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>1887.04</v>
+        <v>5671.17</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>1887.04</v>
+        <v>5538.68</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.007832</v>
+        <v>0.314926</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>1.9</v>
+        <v>33.19</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
@@ -23416,22 +23497,22 @@
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>28</v>
+        <v>55.35</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>0</v>
+        <v>132.49</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>1887.04</v>
+        <v>4787.31</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>132.09</v>
+        <v>258.23</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23497,7 +23578,7 @@
         <v>74</v>
       </c>
       <c r="AW36" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX36" s="10" t="s">
         <v>86</v>
@@ -23550,79 +23631,79 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>307265</v>
+        <v>307369</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>222</v>
+        <v>196</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>3702.49</v>
+        <v>1825.13</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>3437.49</v>
+        <v>1767.68</v>
       </c>
       <c r="P37" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0</v>
+        <v>0.025844</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>3.5</v>
+        <v>6.79</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="W37" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>0</v>
+        <v>57.45</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>3702.49</v>
+        <v>1767.68</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>259.17</v>
+        <v>110.47</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23688,10 +23769,10 @@
         <v>74</v>
       </c>
       <c r="AW37" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX37" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY37" s="14" t="s">
         <v>75</v>
@@ -23727,7 +23808,7 @@
         <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23741,79 +23822,79 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>307278</v>
+        <v>307376</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>226</v>
+        <v>103</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>159</v>
+        <v>203</v>
       </c>
       <c r="I38" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="J38" s="9" t="s">
         <v>211</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>228</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>29709.55</v>
+        <v>499.53</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>29280.46</v>
+        <v>499.53</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.69578</v>
+        <v>0.000507</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>130.96</v>
+        <v>1.07</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="W38" s="9" t="s">
-        <v>172</v>
+        <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>429.09</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>29280.46</v>
+        <v>499.53</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>1794.18</v>
+        <v>34.97</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23879,7 +23960,7 @@
         <v>74</v>
       </c>
       <c r="AW38" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX38" s="10" t="s">
         <v>86</v>
@@ -23918,7 +23999,7 @@
         <v>69</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -23932,34 +24013,34 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>307297</v>
+        <v>307386</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>231</v>
+        <v>164</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>3314.33</v>
+        <v>481.59</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
@@ -23968,43 +24049,43 @@
         <v>1</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>3210</v>
+        <v>481.59</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0</v>
+        <v>0.002268</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>104.33</v>
+        <v>0</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>3210</v>
+        <v>481.59</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>224.7</v>
+        <v>19.26</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24070,7 +24151,7 @@
         <v>74</v>
       </c>
       <c r="AW39" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX39" s="10" t="s">
         <v>86</v>
@@ -24109,7 +24190,7 @@
         <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24123,79 +24204,79 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>307330</v>
+        <v>307424</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>234</v>
+        <v>69</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>7078.63</v>
+        <v>1783.2</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>6646.6</v>
+        <v>1624.79</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q40" s="13" t="n">
-        <v>0.0425</v>
+        <v>0</v>
       </c>
       <c r="R40" s="12" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="S40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>432.03</v>
+        <v>158.41</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>6646.6</v>
+        <v>1624.79</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>465.26</v>
+        <v>65.04</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24204,7 +24285,7 @@
         <v>0</v>
       </c>
       <c r="AD40" s="12" t="n">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="AE40" s="12" t="n">
         <v>0</v>
@@ -24261,10 +24342,10 @@
         <v>74</v>
       </c>
       <c r="AW40" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX40" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY40" s="14" t="s">
         <v>75</v>
@@ -24285,25 +24366,25 @@
         <v>75</v>
       </c>
       <c r="BE40" s="14" t="s">
-        <v>75</v>
+        <v>236</v>
       </c>
       <c r="BF40" s="9" t="s">
-        <v>75</v>
+        <v>237</v>
       </c>
       <c r="BG40" s="9" t="s">
-        <v>69</v>
+        <v>203</v>
       </c>
       <c r="BH40" s="14" t="s">
-        <v>75</v>
+        <v>238</v>
       </c>
       <c r="BI40" s="9" t="s">
-        <v>69</v>
+        <v>234</v>
       </c>
       <c r="BJ40" s="9" t="s">
         <v>239</v>
       </c>
       <c r="BK40" s="9" t="s">
-        <v>75</v>
+        <v>240</v>
       </c>
       <c r="BL40" s="9" t="s">
         <v>75</v>
@@ -24314,79 +24395,79 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>307334</v>
+        <v>307428</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>4963.92</v>
+        <v>785.04</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>4963.92</v>
+        <v>785.04</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.029904</v>
+        <v>0.06696</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>6.84</v>
+        <v>2.59</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="W41" s="9" t="s">
-        <v>73</v>
+        <v>142</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>4963.92</v>
+        <v>785.04</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>347.47</v>
+        <v>54.95</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24452,7 +24533,7 @@
         <v>74</v>
       </c>
       <c r="AW41" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX41" s="10" t="s">
         <v>86</v>
@@ -24491,7 +24572,7 @@
         <v>69</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24505,79 +24586,79 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>307356</v>
+        <v>307429</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>134</v>
+        <v>245</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G42" s="10" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>2104.02</v>
+        <v>37342.94</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>2104.02</v>
+        <v>37342.94</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>0.005548</v>
+        <v>5.83299</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>1.08</v>
+        <v>8567.6</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="W42" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Y42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>2104.02</v>
+        <v>37342.94</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>147.28</v>
+        <v>2613.99</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24643,7 +24724,7 @@
         <v>74</v>
       </c>
       <c r="AW42" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX42" s="10" t="s">
         <v>86</v>
@@ -24682,7 +24763,7 @@
         <v>69</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24696,79 +24777,79 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>307367</v>
+        <v>307433</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>247</v>
+        <v>103</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>5671.17</v>
+        <v>1040.61</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>5538.68</v>
+        <v>977.1</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0.314926</v>
+        <v>0</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>33.19</v>
+        <v>0</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V43" s="12" t="n">
-        <v>55.35</v>
+        <v>28</v>
       </c>
       <c r="W43" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>132.49</v>
+        <v>63.51</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>4787.31</v>
+        <v>977.1</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>258.23</v>
+        <v>68.4</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -24834,7 +24915,7 @@
         <v>74</v>
       </c>
       <c r="AW43" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX43" s="10" t="s">
         <v>86</v>
@@ -24873,7 +24954,7 @@
         <v>69</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -24887,79 +24968,79 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>307369</v>
+        <v>307439</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>66</v>
+        <v>256</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>69</v>
+        <v>257</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>1825.13</v>
+        <v>2401.84</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>1767.68</v>
+        <v>2401.84</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.025844</v>
+        <v>0.29576</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>6.79</v>
+        <v>31.68</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>57.45</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>1767.68</v>
+        <v>2401.84</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>110.47</v>
+        <v>149.08</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25025,10 +25106,10 @@
         <v>74</v>
       </c>
       <c r="AW44" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX44" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY44" s="14" t="s">
         <v>75</v>
@@ -25064,7 +25145,7 @@
         <v>69</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25078,79 +25159,79 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>307372</v>
+        <v>307443</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>60289</v>
+        <v>447.13</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>60289</v>
+        <v>433.06</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0</v>
+        <v>0.0219</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>2625</v>
+        <v>1.7</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T45" s="14" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="U45" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>60.6</v>
+        <v>60</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="Y45" s="12" t="n">
-        <v>0</v>
+        <v>14.07</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>60289</v>
+        <v>433.06</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>4220.23</v>
+        <v>30.31</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25216,7 +25297,7 @@
         <v>74</v>
       </c>
       <c r="AW45" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX45" s="10" t="s">
         <v>86</v>
@@ -25255,7 +25336,7 @@
         <v>69</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="BK45" s="9" t="s">
         <v>75</v>
@@ -25269,79 +25350,79 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>307376</v>
+        <v>307444</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>134</v>
+        <v>260</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>136</v>
+        <v>66</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>499.53</v>
+        <v>24671.51</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>499.53</v>
+        <v>23273.18</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>0.000507</v>
+        <v>3.54421</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>1.07</v>
+        <v>399.29</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V46" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W46" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>0</v>
+        <v>1398.33</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>499.53</v>
+        <v>23273.18</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>34.97</v>
+        <v>1629.14</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25407,7 +25488,7 @@
         <v>74</v>
       </c>
       <c r="AW46" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX46" s="10" t="s">
         <v>86</v>
@@ -25446,7 +25527,7 @@
         <v>69</v>
       </c>
       <c r="BJ46" s="9" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="BK46" s="9" t="s">
         <v>75</v>
@@ -25460,79 +25541,79 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>307386</v>
+        <v>307456</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>194</v>
+        <v>268</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>249</v>
+        <v>219</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>481.59</v>
+        <v>22610.71</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>481.59</v>
+        <v>21521.75</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0.002268</v>
+        <v>0</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>0.44</v>
+        <v>167.78</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="Y47" s="12" t="n">
-        <v>0</v>
+        <v>1088.96</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>481.59</v>
+        <v>21521.75</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>19.26</v>
+        <v>860.89</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25541,7 +25622,7 @@
         <v>0</v>
       </c>
       <c r="AD47" s="12" t="n">
-        <v>0</v>
+        <v>652.54</v>
       </c>
       <c r="AE47" s="12" t="n">
         <v>0</v>
@@ -25598,7 +25679,7 @@
         <v>74</v>
       </c>
       <c r="AW47" s="14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="AX47" s="10" t="s">
         <v>86</v>
@@ -25622,25 +25703,25 @@
         <v>75</v>
       </c>
       <c r="BE47" s="14" t="s">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="BF47" s="9" t="s">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="BG47" s="9" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
       <c r="BH47" s="14" t="s">
-        <v>75</v>
+        <v>274</v>
       </c>
       <c r="BI47" s="9" t="s">
-        <v>69</v>
+        <v>234</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="BK47" s="9" t="s">
-        <v>75</v>
+        <v>276</v>
       </c>
       <c r="BL47" s="9" t="s">
         <v>75</v>
@@ -25650,534 +25731,900 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4"/>
+      <c r="A48" s="8" t="n">
+        <v>307462</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L48" s="12" t="n">
+        <v>319.81</v>
+      </c>
+      <c r="M48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O48" s="12" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="P48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="13" t="n">
+        <v>0.002146</v>
+      </c>
+      <c r="R48" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="S48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="U48" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V48" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W48" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X48" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y48" s="12" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="Z48" s="12" t="n">
+        <v>291.4</v>
+      </c>
+      <c r="AA48" s="12" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="AB48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW48" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX48" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF48" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG48" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI48" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ48" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="BK48" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL48" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM48" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="49" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
-        <v>267</v>
-      </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
-      <c r="T49" s="17"/>
-      <c r="U49" s="17"/>
-      <c r="V49" s="17"/>
+    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="n">
+        <v>307465</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L49" s="12" t="n">
+        <v>1140.3</v>
+      </c>
+      <c r="M49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="12" t="n">
+        <v>1039</v>
+      </c>
+      <c r="P49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="13" t="n">
+        <v>0.00479</v>
+      </c>
+      <c r="R49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="U49" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V49" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W49" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X49" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y49" s="12" t="n">
+        <v>101.3</v>
+      </c>
+      <c r="Z49" s="12" t="n">
+        <v>1039</v>
+      </c>
+      <c r="AA49" s="12" t="n">
+        <v>72.73</v>
+      </c>
+      <c r="AB49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="12" t="n">
+        <v>242.33</v>
+      </c>
+      <c r="AE49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW49" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX49" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE49" s="14" t="s">
+        <v>285</v>
+      </c>
+      <c r="BF49" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="BG49" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="BH49" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="BI49" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="BJ49" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="BK49" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="BL49" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM49" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="50" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18" t="s">
-        <v>268</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F50" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G50" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H50" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I50" s="18" t="s">
+    <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="n">
+        <v>307471</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="J50" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="J50" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K50" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L50" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M50" s="18" t="s">
-        <v>271</v>
-      </c>
-      <c r="N50" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O50" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P50" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R50" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S50" s="18" t="s">
-        <v>272</v>
-      </c>
-      <c r="T50" s="18" t="s">
-        <v>273</v>
-      </c>
-      <c r="U50" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V50" s="18" t="s">
-        <v>37</v>
+      <c r="K50" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>7460</v>
+      </c>
+      <c r="M50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O50" s="12" t="n">
+        <v>7460</v>
+      </c>
+      <c r="P50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="13" t="n">
+        <v>0.16454</v>
+      </c>
+      <c r="R50" s="12" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="S50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="14" t="s">
+        <v>292</v>
+      </c>
+      <c r="U50" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V50" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="W50" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X50" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="Y50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="12" t="n">
+        <v>7460</v>
+      </c>
+      <c r="AA50" s="12" t="n">
+        <v>895.2</v>
+      </c>
+      <c r="AB50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW50" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX50" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="AY50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG50" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI50" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ50" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="BK50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM50" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="19" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="19" t="n">
-        <v>2142.94</v>
-      </c>
-      <c r="D51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="19" t="n">
-        <v>10747.56</v>
-      </c>
-      <c r="F51" s="19" t="n">
-        <v>483288.47</v>
-      </c>
-      <c r="G51" s="19" t="n">
-        <v>31529.62</v>
-      </c>
-      <c r="H51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="19" t="n">
-        <v>527849.39</v>
-      </c>
-      <c r="L51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="20" t="n">
-        <v>10.09365</v>
-      </c>
-      <c r="S51" s="19" t="n">
-        <v>514958.89</v>
-      </c>
-      <c r="T51" s="19" t="n">
-        <v>527849.39</v>
-      </c>
-      <c r="U51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A51" s="4"/>
     </row>
     <row r="52" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F52" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G52" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H52" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I52" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J52" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K52" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="L52" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="M52" s="18" t="s">
-        <v>276</v>
-      </c>
+      <c r="A52" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B52" s="17"/>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
+      <c r="L52" s="17"/>
+      <c r="M52" s="17"/>
+      <c r="N52" s="17"/>
+      <c r="O52" s="17"/>
+      <c r="P52" s="17"/>
+      <c r="Q52" s="17"/>
+      <c r="R52" s="17"/>
+      <c r="S52" s="17"/>
+      <c r="T52" s="17"/>
+      <c r="U52" s="17"/>
+      <c r="V52" s="17"/>
     </row>
-    <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="19" t="n">
-        <v>5221.16</v>
-      </c>
-      <c r="B53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="19" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="E53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="19" t="n">
-        <v>0</v>
+    <row r="53" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="E53" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H53" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I53" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="J53" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K53" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L53" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M53" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="N53" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O53" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P53" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q53" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R53" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S53" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="T53" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="U53" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V53" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4"/>
+      <c r="A54" s="19" t="n">
+        <v>46</v>
+      </c>
+      <c r="B54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="19" t="n">
+        <v>2142.94</v>
+      </c>
+      <c r="D54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="19" t="n">
+        <v>7894.65</v>
+      </c>
+      <c r="F54" s="19" t="n">
+        <v>371131.92</v>
+      </c>
+      <c r="G54" s="19" t="n">
+        <v>23873.19</v>
+      </c>
+      <c r="H54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="19" t="n">
+        <v>981.37</v>
+      </c>
+      <c r="K54" s="19" t="n">
+        <v>380604.85</v>
+      </c>
+      <c r="L54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" s="20" t="n">
+        <v>17.086314</v>
+      </c>
+      <c r="S54" s="19" t="n">
+        <v>370567.26</v>
+      </c>
+      <c r="T54" s="19" t="n">
+        <v>380604.85</v>
+      </c>
+      <c r="U54" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
-      <c r="K55" s="21"/>
-      <c r="L55" s="21"/>
-      <c r="M55" s="21"/>
-      <c r="N55" s="21"/>
-      <c r="O55" s="21"/>
-      <c r="P55" s="21"/>
-      <c r="Q55" s="21"/>
-      <c r="R55" s="21"/>
-      <c r="S55" s="21"/>
-      <c r="T55" s="21"/>
-      <c r="U55" s="21"/>
-      <c r="V55" s="21"/>
-      <c r="W55" s="21"/>
-      <c r="X55" s="21"/>
-      <c r="Y55" s="21"/>
-      <c r="Z55" s="21"/>
-      <c r="AA55" s="21"/>
-      <c r="AB55" s="21"/>
-      <c r="AC55" s="21"/>
-      <c r="AD55" s="21"/>
-      <c r="AE55" s="21"/>
-      <c r="AF55" s="21"/>
-      <c r="AG55" s="21"/>
-      <c r="AH55" s="21"/>
-      <c r="AI55" s="21"/>
-      <c r="AJ55" s="21"/>
-      <c r="AK55" s="21"/>
-      <c r="AL55" s="21"/>
-      <c r="AM55" s="21"/>
-      <c r="AN55" s="21"/>
-      <c r="AO55" s="21"/>
-      <c r="AP55" s="21"/>
-      <c r="AQ55" s="21"/>
-      <c r="AR55" s="21"/>
-      <c r="AS55" s="21"/>
-      <c r="AT55" s="21"/>
-      <c r="AU55" s="21"/>
-      <c r="AV55" s="21"/>
-      <c r="AW55" s="21"/>
-      <c r="AX55" s="21"/>
-      <c r="AY55" s="21"/>
-      <c r="AZ55" s="21"/>
-      <c r="BA55" s="21"/>
-      <c r="BB55" s="21"/>
-      <c r="BC55" s="21"/>
-      <c r="BD55" s="21"/>
-      <c r="BE55" s="21"/>
-      <c r="BF55" s="21"/>
-      <c r="BG55" s="21"/>
-      <c r="BH55" s="21"/>
-      <c r="BI55" s="21"/>
-      <c r="BJ55" s="21"/>
-      <c r="BK55" s="21"/>
-      <c r="BL55" s="21"/>
-      <c r="BM55" s="21"/>
+      <c r="A55" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H55" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I55" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K55" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="L55" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="M55" s="18" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="4"/>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
-      <c r="Z56" s="4"/>
-      <c r="AA56" s="4"/>
-      <c r="AB56" s="4"/>
-      <c r="AC56" s="4"/>
-      <c r="AD56" s="4"/>
-      <c r="AE56" s="4"/>
-      <c r="AF56" s="4"/>
-      <c r="AG56" s="4"/>
-      <c r="AH56" s="4"/>
-      <c r="AI56" s="4"/>
-      <c r="AJ56" s="4"/>
-      <c r="AK56" s="4"/>
-      <c r="AL56" s="4"/>
-      <c r="AM56" s="4"/>
-      <c r="AN56" s="4"/>
-      <c r="AO56" s="4"/>
-      <c r="AP56" s="4"/>
-      <c r="AQ56" s="4"/>
-      <c r="AR56" s="4"/>
-      <c r="AS56" s="4"/>
-      <c r="AT56" s="4"/>
-      <c r="AU56" s="4"/>
-      <c r="AV56" s="4"/>
-      <c r="AW56" s="4"/>
-      <c r="AX56" s="4"/>
-      <c r="AY56" s="4"/>
-      <c r="AZ56" s="4"/>
-      <c r="BA56" s="4"/>
-      <c r="BB56" s="4"/>
-      <c r="BC56" s="4"/>
-      <c r="BD56" s="4"/>
-      <c r="BE56" s="4"/>
-      <c r="BF56" s="4"/>
-      <c r="BG56" s="4"/>
-      <c r="BH56" s="4"/>
-      <c r="BI56" s="4"/>
-      <c r="BJ56" s="4"/>
-      <c r="BK56" s="4"/>
-      <c r="BL56" s="4"/>
-      <c r="BM56" s="4"/>
+      <c r="A56" s="19" t="n">
+        <v>11075.17</v>
+      </c>
+      <c r="B56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>56.57</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
-      <c r="W57" s="4"/>
-      <c r="X57" s="4"/>
-      <c r="Y57" s="4"/>
-      <c r="Z57" s="4"/>
-      <c r="AA57" s="4"/>
-      <c r="AB57" s="4"/>
-      <c r="AC57" s="4"/>
-      <c r="AD57" s="4"/>
-      <c r="AE57" s="4"/>
-      <c r="AF57" s="4"/>
-      <c r="AG57" s="4"/>
-      <c r="AH57" s="4"/>
-      <c r="AI57" s="4"/>
-      <c r="AJ57" s="4"/>
-      <c r="AK57" s="4"/>
-      <c r="AL57" s="4"/>
-      <c r="AM57" s="4"/>
-      <c r="AN57" s="4"/>
-      <c r="AO57" s="4"/>
-      <c r="AP57" s="4"/>
-      <c r="AQ57" s="4"/>
-      <c r="AR57" s="4"/>
-      <c r="AS57" s="4"/>
-      <c r="AT57" s="4"/>
-      <c r="AU57" s="4"/>
-      <c r="AV57" s="4"/>
-      <c r="AW57" s="4"/>
-      <c r="AX57" s="4"/>
-      <c r="AY57" s="4"/>
-      <c r="AZ57" s="4"/>
-      <c r="BA57" s="4"/>
-      <c r="BB57" s="4"/>
-      <c r="BC57" s="4"/>
-      <c r="BD57" s="4"/>
-      <c r="BE57" s="4"/>
-      <c r="BF57" s="4"/>
-      <c r="BG57" s="4"/>
-      <c r="BH57" s="4"/>
-      <c r="BI57" s="4"/>
-      <c r="BJ57" s="4"/>
-      <c r="BK57" s="4"/>
-      <c r="BL57" s="4"/>
-      <c r="BM57" s="4"/>
+      <c r="A57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4"/>
-      <c r="U58" s="4"/>
-      <c r="V58" s="4"/>
-      <c r="W58" s="4"/>
-      <c r="X58" s="4"/>
-      <c r="Y58" s="4"/>
-      <c r="Z58" s="4"/>
-      <c r="AA58" s="4"/>
-      <c r="AB58" s="4"/>
-      <c r="AC58" s="4"/>
-      <c r="AD58" s="4"/>
-      <c r="AE58" s="4"/>
-      <c r="AF58" s="4"/>
-      <c r="AG58" s="4"/>
-      <c r="AH58" s="4"/>
-      <c r="AI58" s="4"/>
-      <c r="AJ58" s="4"/>
-      <c r="AK58" s="4"/>
-      <c r="AL58" s="4"/>
-      <c r="AM58" s="4"/>
-      <c r="AN58" s="4"/>
-      <c r="AO58" s="4"/>
-      <c r="AP58" s="4"/>
-      <c r="AQ58" s="4"/>
-      <c r="AR58" s="4"/>
-      <c r="AS58" s="4"/>
-      <c r="AT58" s="4"/>
-      <c r="AU58" s="4"/>
-      <c r="AV58" s="4"/>
-      <c r="AW58" s="4"/>
-      <c r="AX58" s="4"/>
-      <c r="AY58" s="4"/>
-      <c r="AZ58" s="4"/>
-      <c r="BA58" s="4"/>
-      <c r="BB58" s="4"/>
-      <c r="BC58" s="4"/>
-      <c r="BD58" s="4"/>
-      <c r="BE58" s="4"/>
-      <c r="BF58" s="4"/>
-      <c r="BG58" s="4"/>
-      <c r="BH58" s="4"/>
-      <c r="BI58" s="4"/>
-      <c r="BJ58" s="4"/>
-      <c r="BK58" s="4"/>
-      <c r="BL58" s="4"/>
-      <c r="BM58" s="4"/>
+    <row r="58" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="B58" s="21"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
+      <c r="I58" s="21"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="21"/>
+      <c r="L58" s="21"/>
+      <c r="M58" s="21"/>
+      <c r="N58" s="21"/>
+      <c r="O58" s="21"/>
+      <c r="P58" s="21"/>
+      <c r="Q58" s="21"/>
+      <c r="R58" s="21"/>
+      <c r="S58" s="21"/>
+      <c r="T58" s="21"/>
+      <c r="U58" s="21"/>
+      <c r="V58" s="21"/>
+      <c r="W58" s="21"/>
+      <c r="X58" s="21"/>
+      <c r="Y58" s="21"/>
+      <c r="Z58" s="21"/>
+      <c r="AA58" s="21"/>
+      <c r="AB58" s="21"/>
+      <c r="AC58" s="21"/>
+      <c r="AD58" s="21"/>
+      <c r="AE58" s="21"/>
+      <c r="AF58" s="21"/>
+      <c r="AG58" s="21"/>
+      <c r="AH58" s="21"/>
+      <c r="AI58" s="21"/>
+      <c r="AJ58" s="21"/>
+      <c r="AK58" s="21"/>
+      <c r="AL58" s="21"/>
+      <c r="AM58" s="21"/>
+      <c r="AN58" s="21"/>
+      <c r="AO58" s="21"/>
+      <c r="AP58" s="21"/>
+      <c r="AQ58" s="21"/>
+      <c r="AR58" s="21"/>
+      <c r="AS58" s="21"/>
+      <c r="AT58" s="21"/>
+      <c r="AU58" s="21"/>
+      <c r="AV58" s="21"/>
+      <c r="AW58" s="21"/>
+      <c r="AX58" s="21"/>
+      <c r="AY58" s="21"/>
+      <c r="AZ58" s="21"/>
+      <c r="BA58" s="21"/>
+      <c r="BB58" s="21"/>
+      <c r="BC58" s="21"/>
+      <c r="BD58" s="21"/>
+      <c r="BE58" s="21"/>
+      <c r="BF58" s="21"/>
+      <c r="BG58" s="21"/>
+      <c r="BH58" s="21"/>
+      <c r="BI58" s="21"/>
+      <c r="BJ58" s="21"/>
+      <c r="BK58" s="21"/>
+      <c r="BL58" s="21"/>
+      <c r="BM58" s="21"/>
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>280</v>
+        <v>75</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -26246,7 +26693,7 @@
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>22</v>
+        <v>305</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -26315,7 +26762,7 @@
     </row>
     <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>281</v>
+        <v>306</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -26384,7 +26831,7 @@
     </row>
     <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -26453,7 +26900,7 @@
     </row>
     <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>283</v>
+        <v>22</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -26522,7 +26969,7 @@
     </row>
     <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>284</v>
+        <v>308</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -26591,7 +27038,7 @@
     </row>
     <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -26658,8 +27105,215 @@
       <c r="BL65" s="4"/>
       <c r="BM65" s="4"/>
     </row>
+    <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
+      <c r="AB66" s="4"/>
+      <c r="AC66" s="4"/>
+      <c r="AD66" s="4"/>
+      <c r="AE66" s="4"/>
+      <c r="AF66" s="4"/>
+      <c r="AG66" s="4"/>
+      <c r="AH66" s="4"/>
+      <c r="AI66" s="4"/>
+      <c r="AJ66" s="4"/>
+      <c r="AK66" s="4"/>
+      <c r="AL66" s="4"/>
+      <c r="AM66" s="4"/>
+      <c r="AN66" s="4"/>
+      <c r="AO66" s="4"/>
+      <c r="AP66" s="4"/>
+      <c r="AQ66" s="4"/>
+      <c r="AR66" s="4"/>
+      <c r="AS66" s="4"/>
+      <c r="AT66" s="4"/>
+      <c r="AU66" s="4"/>
+      <c r="AV66" s="4"/>
+      <c r="AW66" s="4"/>
+      <c r="AX66" s="4"/>
+      <c r="AY66" s="4"/>
+      <c r="AZ66" s="4"/>
+      <c r="BA66" s="4"/>
+      <c r="BB66" s="4"/>
+      <c r="BC66" s="4"/>
+      <c r="BD66" s="4"/>
+      <c r="BE66" s="4"/>
+      <c r="BF66" s="4"/>
+      <c r="BG66" s="4"/>
+      <c r="BH66" s="4"/>
+      <c r="BI66" s="4"/>
+      <c r="BJ66" s="4"/>
+      <c r="BK66" s="4"/>
+      <c r="BL66" s="4"/>
+      <c r="BM66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
+      <c r="AB67" s="4"/>
+      <c r="AC67" s="4"/>
+      <c r="AD67" s="4"/>
+      <c r="AE67" s="4"/>
+      <c r="AF67" s="4"/>
+      <c r="AG67" s="4"/>
+      <c r="AH67" s="4"/>
+      <c r="AI67" s="4"/>
+      <c r="AJ67" s="4"/>
+      <c r="AK67" s="4"/>
+      <c r="AL67" s="4"/>
+      <c r="AM67" s="4"/>
+      <c r="AN67" s="4"/>
+      <c r="AO67" s="4"/>
+      <c r="AP67" s="4"/>
+      <c r="AQ67" s="4"/>
+      <c r="AR67" s="4"/>
+      <c r="AS67" s="4"/>
+      <c r="AT67" s="4"/>
+      <c r="AU67" s="4"/>
+      <c r="AV67" s="4"/>
+      <c r="AW67" s="4"/>
+      <c r="AX67" s="4"/>
+      <c r="AY67" s="4"/>
+      <c r="AZ67" s="4"/>
+      <c r="BA67" s="4"/>
+      <c r="BB67" s="4"/>
+      <c r="BC67" s="4"/>
+      <c r="BD67" s="4"/>
+      <c r="BE67" s="4"/>
+      <c r="BF67" s="4"/>
+      <c r="BG67" s="4"/>
+      <c r="BH67" s="4"/>
+      <c r="BI67" s="4"/>
+      <c r="BJ67" s="4"/>
+      <c r="BK67" s="4"/>
+      <c r="BL67" s="4"/>
+      <c r="BM67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="4"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="4"/>
+      <c r="AB68" s="4"/>
+      <c r="AC68" s="4"/>
+      <c r="AD68" s="4"/>
+      <c r="AE68" s="4"/>
+      <c r="AF68" s="4"/>
+      <c r="AG68" s="4"/>
+      <c r="AH68" s="4"/>
+      <c r="AI68" s="4"/>
+      <c r="AJ68" s="4"/>
+      <c r="AK68" s="4"/>
+      <c r="AL68" s="4"/>
+      <c r="AM68" s="4"/>
+      <c r="AN68" s="4"/>
+      <c r="AO68" s="4"/>
+      <c r="AP68" s="4"/>
+      <c r="AQ68" s="4"/>
+      <c r="AR68" s="4"/>
+      <c r="AS68" s="4"/>
+      <c r="AT68" s="4"/>
+      <c r="AU68" s="4"/>
+      <c r="AV68" s="4"/>
+      <c r="AW68" s="4"/>
+      <c r="AX68" s="4"/>
+      <c r="AY68" s="4"/>
+      <c r="AZ68" s="4"/>
+      <c r="BA68" s="4"/>
+      <c r="BB68" s="4"/>
+      <c r="BC68" s="4"/>
+      <c r="BD68" s="4"/>
+      <c r="BE68" s="4"/>
+      <c r="BF68" s="4"/>
+      <c r="BG68" s="4"/>
+      <c r="BH68" s="4"/>
+      <c r="BI68" s="4"/>
+      <c r="BJ68" s="4"/>
+      <c r="BK68" s="4"/>
+      <c r="BL68" s="4"/>
+      <c r="BM68" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="62">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -26707,10 +27361,10 @@
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B47:E47"/>
-    <mergeCell ref="A49:V49"/>
-    <mergeCell ref="A55:BM55"/>
-    <mergeCell ref="A56:BM56"/>
-    <mergeCell ref="A57:BM57"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="A52:V52"/>
     <mergeCell ref="A58:BM58"/>
     <mergeCell ref="A59:BM59"/>
     <mergeCell ref="A60:BM60"/>
@@ -26719,6 +27373,9 @@
     <mergeCell ref="A63:BM63"/>
     <mergeCell ref="A64:BM64"/>
     <mergeCell ref="A65:BM65"/>
+    <mergeCell ref="A66:BM66"/>
+    <mergeCell ref="A67:BM67"/>
+    <mergeCell ref="A68:BM68"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="302">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 19/05/2026 05:30:31</t>
+    <t xml:space="preserve">Emitido em: 20/05/2026 05:30:32</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -394,18 +394,6 @@
     <t xml:space="preserve">42260582984287000104550020017807421113944451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.780.741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.549,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807411668968281</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.975.491</t>
   </si>
   <si>
@@ -466,18 +454,6 @@
     <t xml:space="preserve">42260575339051000141550080006372551066202512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.376 - ELETRO ZAGONEL LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">662.150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.581,90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260581365223000154550020006621501364814580</t>
-  </si>
-  <si>
     <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
   </si>
   <si>
@@ -757,18 +733,6 @@
     <t xml:space="preserve">42260509641520000158550010007588261717357519</t>
   </si>
   <si>
-    <t xml:space="preserve">37.802 - VINICOLOR IND. E COM. DE TINTAS, TEXTURA E GRAFIATO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">242.611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.342,94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41260507855544000184550010002426111067151486</t>
-  </si>
-  <si>
     <t xml:space="preserve">642.487</t>
   </si>
   <si>
@@ -826,82 +790,85 @@
     <t xml:space="preserve">31260507159430000361550010000876201881086441</t>
   </si>
   <si>
-    <t xml:space="preserve">31.410 - SAN HO COMERCIO IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">84.844</t>
+    <t xml:space="preserve">29.238 - EURO METAIS IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">319,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260510317038000146550010000665871272565371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.015 - FOCO METALLO FABRICACAO E MONTAGEM DE LUMINARIAS E COMERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.140,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.724.082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.618 - ALFA TRANSPORTES EIRELI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">242,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260522670837000180550010000233691542222518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582110818000121570000077240821090348638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.444 - PRIME BRAS SEGURANCA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.456</t>
   </si>
   <si>
     <t xml:space="preserve">14/06/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">22.610,71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">93.213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.965 - RTL ENCOMENDAS E CARGAS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">652,54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52260517328359000195550010000848441256212101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52260531607598000105570010000932131000660870</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.238 - EURO METAIS IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">319,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29260510317038000146550010000665871272565371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.015 - FOCO METALLO FABRICACAO E MONTAGEM DE LUMINARIAS E COMERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.140,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.724.082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.618 - ALFA TRANSPORTES EIRELI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">242,33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260522670837000180550010000233691542222518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582110818000121570000077240821090348638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.444 - PRIME BRAS SEGURANCA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.456</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.460,00</t>
   </si>
   <si>
     <t xml:space="preserve">42260532296669000169550030000014561732534080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">261.762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.247,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">399.241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">610,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260558329608000144550010002617621002617634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260511389565000200570050003992411000855094</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17147,7 +17114,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM68"/>
+  <dimension ref="A1:BM65"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -19047,10 +19014,10 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>307046</v>
+        <v>307062</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -19059,67 +19026,67 @@
         <v>124</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>106</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>39549.24</v>
+        <v>94092.8</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>36406.48</v>
+        <v>93172</v>
       </c>
       <c r="P13" s="12" t="n">
-        <v>1877.94</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>2.71203</v>
+        <v>2.122527</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>520.9</v>
+        <v>493.99</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>1264.82</v>
+        <v>920.8</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>38284.42</v>
+        <v>92335.42</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>2330.38</v>
+        <v>5743.16</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19224,7 +19191,7 @@
         <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19238,79 +19205,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>307062</v>
+        <v>307073</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>106</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>94092.8</v>
+        <v>7834.72</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>93172</v>
+        <v>7524.33</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>2.122527</v>
+        <v>0</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>493.99</v>
+        <v>0</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>920.8</v>
+        <v>310.39</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>92335.42</v>
+        <v>7524.33</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>5743.16</v>
+        <v>526.7</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19415,7 +19382,7 @@
         <v>69</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19429,79 +19396,79 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>307073</v>
+        <v>307133</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>135</v>
+        <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>7834.72</v>
+        <v>4265.79</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>7524.33</v>
+        <v>4222.88</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0</v>
+        <v>0.484131</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>310.39</v>
+        <v>42.91</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>7524.33</v>
+        <v>4222.88</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>526.7</v>
+        <v>281.12</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19606,7 +19573,7 @@
         <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19620,79 +19587,79 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>307133</v>
+        <v>307142</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>4265.79</v>
+        <v>20761.14</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>4222.88</v>
+        <v>20761.14</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.484131</v>
+        <v>0.01152</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>71.4</v>
+        <v>2.23</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>42.91</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>4222.88</v>
+        <v>20761.14</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>281.12</v>
+        <v>1453.28</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19811,34 +19778,34 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>307142</v>
+        <v>307159</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>113</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>20761.14</v>
+        <v>1603.35</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19847,43 +19814,43 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>20761.14</v>
+        <v>1527</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.01152</v>
+        <v>0.05265</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>2.23</v>
+        <v>30</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>0</v>
+        <v>76.35</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>20761.14</v>
+        <v>1527</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>1453.28</v>
+        <v>106.89</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19988,7 +19955,7 @@
         <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -20002,10 +19969,10 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>307146</v>
+        <v>307161</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
@@ -20014,22 +19981,22 @@
         <v>149</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>113</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>6581.9</v>
+        <v>4890.24</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -20038,16 +20005,16 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>6581.9</v>
+        <v>4890.24</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0</v>
+        <v>0.001296</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>416.22</v>
+        <v>2.22</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
@@ -20059,22 +20026,22 @@
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>6581.9</v>
+        <v>4890.24</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>460.73</v>
+        <v>342.32</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20193,34 +20160,34 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>307159</v>
+        <v>307162</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="J19" s="9" t="s">
         <v>153</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>154</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>1603.35</v>
+        <v>1185.87</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
@@ -20229,22 +20196,22 @@
         <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>1527</v>
+        <v>1129.4</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.05265</v>
+        <v>0.0351</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
@@ -20256,16 +20223,16 @@
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>76.35</v>
+        <v>56.47</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>1527</v>
+        <v>1129.4</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>106.89</v>
+        <v>79.06</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20370,7 +20337,7 @@
         <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20384,10 +20351,10 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>307161</v>
+        <v>307171</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>103</v>
+        <v>156</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
@@ -20396,22 +20363,22 @@
         <v>157</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>145</v>
+        <v>69</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>4890.24</v>
+        <v>404.81</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -20420,16 +20387,16 @@
         <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>4890.24</v>
+        <v>404.81</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.001296</v>
+        <v>0.000858</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>2.22</v>
+        <v>2.43</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
@@ -20441,22 +20408,22 @@
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>4890.24</v>
+        <v>404.81</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>342.32</v>
+        <v>16.19</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20525,7 +20492,7 @@
         <v>85</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20575,10 +20542,10 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>307162</v>
+        <v>307173</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
@@ -20587,22 +20554,22 @@
         <v>160</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>135</v>
+        <v>66</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1185.87</v>
+        <v>404.81</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20611,43 +20578,43 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>1129.4</v>
+        <v>404.81</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.0351</v>
+        <v>0.000858</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>20</v>
+        <v>2.43</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>56.47</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>1129.4</v>
+        <v>404.81</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>79.06</v>
+        <v>16.19</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20716,7 +20683,7 @@
         <v>85</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20752,7 +20719,7 @@
         <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20766,16 +20733,16 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>307171</v>
+        <v>307174</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>66</v>
@@ -20784,7 +20751,7 @@
         <v>107</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J22" s="9" t="s">
         <v>69</v>
@@ -20817,7 +20784,7 @@
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20829,7 +20796,7 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y22" s="12" t="n">
         <v>0</v>
@@ -20943,7 +20910,7 @@
         <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20957,7 +20924,7 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>307173</v>
+        <v>307181</v>
       </c>
       <c r="B23" s="9" t="s">
         <v>164</v>
@@ -20966,70 +20933,70 @@
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>404.81</v>
+        <v>426.2</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>404.81</v>
+        <v>426.2</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.0025</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>2.43</v>
+        <v>10</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>404.81</v>
+        <v>426.2</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>16.19</v>
+        <v>29.84</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21098,7 +21065,7 @@
         <v>85</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21134,7 +21101,7 @@
         <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21148,79 +21115,79 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>307174</v>
+        <v>307183</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>404.81</v>
+        <v>12695.18</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>404.81</v>
+        <v>11935.6</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.0698</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>2.43</v>
+        <v>31.68</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>0</v>
+        <v>759.58</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>404.81</v>
+        <v>11935.6</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>16.19</v>
+        <v>614.43</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21289,7 +21256,7 @@
         <v>85</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21339,25 +21306,25 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>307181</v>
+        <v>307231</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>174</v>
@@ -21366,25 +21333,25 @@
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>426.2</v>
+        <v>2929.6</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>426.2</v>
+        <v>2929.6</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.0025</v>
+        <v>0.000484</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>10</v>
+        <v>3.22</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
@@ -21396,22 +21363,22 @@
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>426.2</v>
+        <v>2929.6</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>29.84</v>
+        <v>205.07</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21530,10 +21497,10 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>307183</v>
+        <v>307235</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
@@ -21542,40 +21509,40 @@
         <v>177</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>135</v>
+        <v>66</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>12695.18</v>
+        <v>461.96</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>11935.6</v>
+        <v>461.96</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.0698</v>
+        <v>0.002057</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>31.68</v>
+        <v>2.43</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
@@ -21587,22 +21554,22 @@
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>759.58</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>11935.6</v>
+        <v>461.96</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>614.43</v>
+        <v>18.48</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21671,7 +21638,7 @@
         <v>85</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21721,10 +21688,10 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>307231</v>
+        <v>307242</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
@@ -21733,22 +21700,22 @@
         <v>180</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I27" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>181</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>182</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2929.6</v>
+        <v>1887.04</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
@@ -21757,43 +21724,43 @@
         <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>2929.6</v>
+        <v>1887.04</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.000484</v>
+        <v>0.007832</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>3.22</v>
+        <v>1.9</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Y27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>2929.6</v>
+        <v>1887.04</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>205.07</v>
+        <v>132.09</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21898,7 +21865,7 @@
         <v>69</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21912,10 +21879,10 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>307235</v>
+        <v>307265</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -21927,19 +21894,19 @@
         <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>69</v>
+        <v>141</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>461.96</v>
+        <v>3702.49</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -21948,16 +21915,16 @@
         <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>461.96</v>
+        <v>3437.49</v>
       </c>
       <c r="P28" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.002057</v>
+        <v>0</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
@@ -21969,22 +21936,22 @@
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="W28" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Y28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>461.96</v>
+        <v>3702.49</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>18.48</v>
+        <v>259.17</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22053,7 +22020,7 @@
         <v>85</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -22103,79 +22070,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>307242</v>
+        <v>307278</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>103</v>
+        <v>188</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1887.04</v>
+        <v>29709.55</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>1887.04</v>
+        <v>29280.46</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.007832</v>
+        <v>0.69578</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>1.9</v>
+        <v>130.96</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="W29" s="9" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>0</v>
+        <v>429.09</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>1887.04</v>
+        <v>29280.46</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>132.09</v>
+        <v>1794.18</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22280,7 +22247,7 @@
         <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22294,34 +22261,34 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>307265</v>
+        <v>307297</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G30" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>3702.49</v>
+        <v>3314.33</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
@@ -22330,43 +22297,43 @@
         <v>1</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>3437.49</v>
+        <v>3210</v>
       </c>
       <c r="P30" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>0</v>
+        <v>104.33</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>3702.49</v>
+        <v>3210</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>259.17</v>
+        <v>224.7</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22471,7 +22438,7 @@
         <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22485,79 +22452,79 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>307278</v>
+        <v>307330</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>196</v>
+        <v>103</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>29709.55</v>
+        <v>7078.63</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>29280.46</v>
+        <v>6646.6</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.69578</v>
+        <v>0.0425</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>130.96</v>
+        <v>9.6</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="W31" s="9" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>429.09</v>
+        <v>432.03</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>29280.46</v>
+        <v>6646.6</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>1794.18</v>
+        <v>465.26</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22662,7 +22629,7 @@
         <v>69</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22676,10 +22643,10 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>307297</v>
+        <v>307334</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>201</v>
+        <v>103</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -22688,22 +22655,22 @@
         <v>202</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="I32" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>3314.33</v>
+        <v>4963.92</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
@@ -22712,43 +22679,43 @@
         <v>1</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>3210</v>
+        <v>4963.92</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0</v>
+        <v>0.029904</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>104.33</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>3210</v>
+        <v>4963.92</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>224.7</v>
+        <v>347.47</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22853,7 +22820,7 @@
         <v>69</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22867,7 +22834,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>307330</v>
+        <v>307356</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>103</v>
@@ -22876,25 +22843,25 @@
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>105</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="I33" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>203</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>204</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>7078.63</v>
+        <v>2104.02</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -22903,22 +22870,22 @@
         <v>1</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>6646.6</v>
+        <v>2104.02</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.0425</v>
+        <v>0.005548</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>9.6</v>
+        <v>1.08</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
@@ -22930,16 +22897,16 @@
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>432.03</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>6646.6</v>
+        <v>2104.02</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>465.26</v>
+        <v>147.28</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -23044,7 +23011,7 @@
         <v>69</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23058,10 +23025,10 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>307334</v>
+        <v>307367</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
@@ -23070,40 +23037,40 @@
         <v>210</v>
       </c>
       <c r="G34" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>4963.92</v>
+        <v>5671.17</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>4963.92</v>
+        <v>5538.68</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.029904</v>
+        <v>0.314926</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>6.84</v>
+        <v>33.19</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
@@ -23115,22 +23082,22 @@
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>28</v>
+        <v>55.35</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>0</v>
+        <v>132.49</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>4963.92</v>
+        <v>4787.31</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>347.47</v>
+        <v>258.23</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23249,10 +23216,10 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>307356</v>
+        <v>307369</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>103</v>
+        <v>188</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
@@ -23261,40 +23228,40 @@
         <v>214</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>211</v>
+        <v>69</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>2104.02</v>
+        <v>1825.13</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>2104.02</v>
+        <v>1767.68</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.005548</v>
+        <v>0.025844</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>1.08</v>
+        <v>6.79</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
@@ -23306,22 +23273,22 @@
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>0</v>
+        <v>57.45</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>2104.02</v>
+        <v>1767.68</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>147.28</v>
+        <v>110.47</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23390,7 +23357,7 @@
         <v>85</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23440,79 +23407,79 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>307367</v>
+        <v>307376</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>217</v>
+        <v>103</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G36" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>5671.17</v>
+        <v>499.53</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>5538.68</v>
+        <v>499.53</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.314926</v>
+        <v>0.000507</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>33.19</v>
+        <v>1.07</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>55.35</v>
+        <v>28</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="Y36" s="12" t="n">
-        <v>132.49</v>
+        <v>0</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>4787.31</v>
+        <v>499.53</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>258.23</v>
+        <v>34.97</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23617,7 +23584,7 @@
         <v>69</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23631,79 +23598,79 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>307369</v>
+        <v>307386</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>196</v>
+        <v>156</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>181</v>
+        <v>211</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>69</v>
+        <v>221</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>1825.13</v>
+        <v>481.59</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>1767.68</v>
+        <v>481.59</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.025844</v>
+        <v>0.002268</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>6.79</v>
+        <v>0.44</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W37" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="Y37" s="12" t="n">
-        <v>57.45</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>1767.68</v>
+        <v>481.59</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>110.47</v>
+        <v>19.26</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23772,7 +23739,7 @@
         <v>85</v>
       </c>
       <c r="AX37" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY37" s="14" t="s">
         <v>75</v>
@@ -23808,7 +23775,7 @@
         <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23822,10 +23789,10 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>307376</v>
+        <v>307424</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>103</v>
+        <v>224</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
@@ -23834,67 +23801,67 @@
         <v>225</v>
       </c>
       <c r="G38" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>211</v>
+        <v>69</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>499.53</v>
+        <v>1783.2</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>499.53</v>
+        <v>1624.79</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.000507</v>
+        <v>0</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>0</v>
+        <v>158.41</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>499.53</v>
+        <v>1624.79</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>34.97</v>
+        <v>65.04</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23903,7 +23870,7 @@
         <v>0</v>
       </c>
       <c r="AD38" s="12" t="n">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="AE38" s="12" t="n">
         <v>0</v>
@@ -23963,7 +23930,7 @@
         <v>85</v>
       </c>
       <c r="AX38" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY38" s="14" t="s">
         <v>75</v>
@@ -23984,25 +23951,25 @@
         <v>75</v>
       </c>
       <c r="BE38" s="14" t="s">
-        <v>75</v>
+        <v>228</v>
       </c>
       <c r="BF38" s="9" t="s">
-        <v>75</v>
+        <v>229</v>
       </c>
       <c r="BG38" s="9" t="s">
-        <v>69</v>
+        <v>195</v>
       </c>
       <c r="BH38" s="14" t="s">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="BI38" s="9" t="s">
-        <v>69</v>
+        <v>226</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="BK38" s="9" t="s">
-        <v>75</v>
+        <v>232</v>
       </c>
       <c r="BL38" s="9" t="s">
         <v>75</v>
@@ -24013,79 +23980,79 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>307386</v>
+        <v>307428</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>481.59</v>
+        <v>785.04</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>481.59</v>
+        <v>785.04</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.002268</v>
+        <v>0.06696</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>0.44</v>
+        <v>2.59</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="W39" s="9" t="s">
-        <v>73</v>
+        <v>138</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="Y39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>481.59</v>
+        <v>785.04</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>19.26</v>
+        <v>54.95</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24190,7 +24157,7 @@
         <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24204,43 +24171,43 @@
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="n">
-        <v>307424</v>
+        <v>307433</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>232</v>
+        <v>103</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9"/>
       <c r="E40" s="9"/>
       <c r="F40" s="9" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G40" s="10" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>181</v>
+        <v>238</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>69</v>
+        <v>239</v>
       </c>
       <c r="K40" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>1783.2</v>
+        <v>1040.61</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O40" s="12" t="n">
-        <v>1624.79</v>
+        <v>977.1</v>
       </c>
       <c r="P40" s="12" t="n">
         <v>0</v>
@@ -24255,28 +24222,28 @@
         <v>0</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="U40" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V40" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W40" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X40" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Y40" s="12" t="n">
-        <v>158.41</v>
+        <v>63.51</v>
       </c>
       <c r="Z40" s="12" t="n">
-        <v>1624.79</v>
+        <v>977.1</v>
       </c>
       <c r="AA40" s="12" t="n">
-        <v>65.04</v>
+        <v>68.4</v>
       </c>
       <c r="AB40" s="12" t="n">
         <v>0</v>
@@ -24285,7 +24252,7 @@
         <v>0</v>
       </c>
       <c r="AD40" s="12" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="AE40" s="12" t="n">
         <v>0</v>
@@ -24345,7 +24312,7 @@
         <v>85</v>
       </c>
       <c r="AX40" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY40" s="14" t="s">
         <v>75</v>
@@ -24366,25 +24333,25 @@
         <v>75</v>
       </c>
       <c r="BE40" s="14" t="s">
-        <v>236</v>
+        <v>75</v>
       </c>
       <c r="BF40" s="9" t="s">
-        <v>237</v>
+        <v>75</v>
       </c>
       <c r="BG40" s="9" t="s">
-        <v>203</v>
+        <v>69</v>
       </c>
       <c r="BH40" s="14" t="s">
-        <v>238</v>
+        <v>75</v>
       </c>
       <c r="BI40" s="9" t="s">
-        <v>234</v>
+        <v>69</v>
       </c>
       <c r="BJ40" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="BK40" s="9" t="s">
-        <v>240</v>
+        <v>75</v>
       </c>
       <c r="BL40" s="9" t="s">
         <v>75</v>
@@ -24395,79 +24362,79 @@
     </row>
     <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="8" t="n">
-        <v>307428</v>
+        <v>307439</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>138</v>
+        <v>242</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9"/>
       <c r="E41" s="9"/>
       <c r="F41" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>66</v>
+        <v>244</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>219</v>
+        <v>238</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K41" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>785.04</v>
+        <v>2401.84</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O41" s="12" t="n">
-        <v>785.04</v>
+        <v>2401.84</v>
       </c>
       <c r="P41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q41" s="13" t="n">
-        <v>0.06696</v>
+        <v>0.29576</v>
       </c>
       <c r="R41" s="12" t="n">
-        <v>2.59</v>
+        <v>31.68</v>
       </c>
       <c r="S41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="U41" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V41" s="12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W41" s="9" t="s">
-        <v>142</v>
+        <v>73</v>
       </c>
       <c r="X41" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Y41" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z41" s="12" t="n">
-        <v>785.04</v>
+        <v>2401.84</v>
       </c>
       <c r="AA41" s="12" t="n">
-        <v>54.95</v>
+        <v>149.08</v>
       </c>
       <c r="AB41" s="12" t="n">
         <v>0</v>
@@ -24572,7 +24539,7 @@
         <v>69</v>
       </c>
       <c r="BJ41" s="9" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="BK41" s="9" t="s">
         <v>75</v>
@@ -24586,79 +24553,79 @@
     </row>
     <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="8" t="n">
-        <v>307429</v>
+        <v>307443</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C42" s="9"/>
       <c r="D42" s="9"/>
       <c r="E42" s="9"/>
       <c r="F42" s="9" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="K42" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>37342.94</v>
+        <v>447.13</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O42" s="12" t="n">
-        <v>37342.94</v>
+        <v>433.06</v>
       </c>
       <c r="P42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q42" s="13" t="n">
-        <v>5.83299</v>
+        <v>0.0219</v>
       </c>
       <c r="R42" s="12" t="n">
-        <v>8567.6</v>
+        <v>1.7</v>
       </c>
       <c r="S42" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="U42" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V42" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="W42" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X42" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Y42" s="12" t="n">
-        <v>0</v>
+        <v>14.07</v>
       </c>
       <c r="Z42" s="12" t="n">
-        <v>37342.94</v>
+        <v>433.06</v>
       </c>
       <c r="AA42" s="12" t="n">
-        <v>2613.99</v>
+        <v>30.31</v>
       </c>
       <c r="AB42" s="12" t="n">
         <v>0</v>
@@ -24763,7 +24730,7 @@
         <v>69</v>
       </c>
       <c r="BJ42" s="9" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="BK42" s="9" t="s">
         <v>75</v>
@@ -24777,79 +24744,79 @@
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="n">
-        <v>307433</v>
+        <v>307444</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>103</v>
+        <v>248</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9"/>
       <c r="E43" s="9"/>
       <c r="F43" s="9" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="G43" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H43" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="J43" s="9" t="s">
         <v>250</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>251</v>
       </c>
       <c r="K43" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>1040.61</v>
+        <v>24671.51</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O43" s="12" t="n">
-        <v>977.1</v>
+        <v>23273.18</v>
       </c>
       <c r="P43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q43" s="13" t="n">
-        <v>0</v>
+        <v>3.54421</v>
       </c>
       <c r="R43" s="12" t="n">
-        <v>0</v>
+        <v>399.29</v>
       </c>
       <c r="S43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T43" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="U43" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V43" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W43" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X43" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Y43" s="12" t="n">
-        <v>63.51</v>
+        <v>1398.33</v>
       </c>
       <c r="Z43" s="12" t="n">
-        <v>977.1</v>
+        <v>23273.18</v>
       </c>
       <c r="AA43" s="12" t="n">
-        <v>68.4</v>
+        <v>1629.14</v>
       </c>
       <c r="AB43" s="12" t="n">
         <v>0</v>
@@ -24954,7 +24921,7 @@
         <v>69</v>
       </c>
       <c r="BJ43" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="BK43" s="9" t="s">
         <v>75</v>
@@ -24968,79 +24935,79 @@
     </row>
     <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="8" t="n">
-        <v>307439</v>
+        <v>307462</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C44" s="9"/>
       <c r="D44" s="9"/>
       <c r="E44" s="9"/>
       <c r="F44" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G44" s="10" t="s">
-        <v>256</v>
+        <v>66</v>
       </c>
       <c r="H44" s="9" t="s">
-        <v>250</v>
+        <v>195</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J44" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K44" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>2401.84</v>
+        <v>319.81</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O44" s="12" t="n">
-        <v>2401.84</v>
+        <v>291.4</v>
       </c>
       <c r="P44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q44" s="13" t="n">
-        <v>0.29576</v>
+        <v>0.002146</v>
       </c>
       <c r="R44" s="12" t="n">
-        <v>31.68</v>
+        <v>0.53</v>
       </c>
       <c r="S44" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="U44" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V44" s="12" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="W44" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X44" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Y44" s="12" t="n">
-        <v>0</v>
+        <v>28.41</v>
       </c>
       <c r="Z44" s="12" t="n">
-        <v>2401.84</v>
+        <v>291.4</v>
       </c>
       <c r="AA44" s="12" t="n">
-        <v>149.08</v>
+        <v>11.65</v>
       </c>
       <c r="AB44" s="12" t="n">
         <v>0</v>
@@ -25145,7 +25112,7 @@
         <v>69</v>
       </c>
       <c r="BJ44" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="BK44" s="9" t="s">
         <v>75</v>
@@ -25159,34 +25126,34 @@
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="8" t="n">
-        <v>307443</v>
+        <v>307465</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="9"/>
       <c r="E45" s="9"/>
       <c r="F45" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>262</v>
+        <v>203</v>
       </c>
       <c r="K45" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>447.13</v>
+        <v>1140.3</v>
       </c>
       <c r="M45" s="12" t="n">
         <v>0</v>
@@ -25195,16 +25162,16 @@
         <v>1</v>
       </c>
       <c r="O45" s="12" t="n">
-        <v>433.06</v>
+        <v>1039</v>
       </c>
       <c r="P45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q45" s="13" t="n">
-        <v>0.0219</v>
+        <v>0.00479</v>
       </c>
       <c r="R45" s="12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S45" s="12" t="n">
         <v>0</v>
@@ -25216,22 +25183,22 @@
         <v>72</v>
       </c>
       <c r="V45" s="12" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="W45" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X45" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Y45" s="12" t="n">
-        <v>14.07</v>
+        <v>101.3</v>
       </c>
       <c r="Z45" s="12" t="n">
-        <v>433.06</v>
+        <v>1039</v>
       </c>
       <c r="AA45" s="12" t="n">
-        <v>30.31</v>
+        <v>72.73</v>
       </c>
       <c r="AB45" s="12" t="n">
         <v>0</v>
@@ -25240,7 +25207,7 @@
         <v>0</v>
       </c>
       <c r="AD45" s="12" t="n">
-        <v>0</v>
+        <v>242.33</v>
       </c>
       <c r="AE45" s="12" t="n">
         <v>0</v>
@@ -25321,25 +25288,25 @@
         <v>75</v>
       </c>
       <c r="BE45" s="14" t="s">
-        <v>75</v>
+        <v>264</v>
       </c>
       <c r="BF45" s="9" t="s">
-        <v>75</v>
+        <v>265</v>
       </c>
       <c r="BG45" s="9" t="s">
-        <v>69</v>
+        <v>195</v>
       </c>
       <c r="BH45" s="14" t="s">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="BI45" s="9" t="s">
-        <v>69</v>
+        <v>226</v>
       </c>
       <c r="BJ45" s="9" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="BK45" s="9" t="s">
-        <v>75</v>
+        <v>268</v>
       </c>
       <c r="BL45" s="9" t="s">
         <v>75</v>
@@ -25350,58 +25317,58 @@
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="8" t="n">
-        <v>307444</v>
+        <v>307471</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C46" s="9"/>
       <c r="D46" s="9"/>
       <c r="E46" s="9"/>
       <c r="F46" s="9" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="G46" s="10" t="s">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="K46" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>24671.51</v>
+        <v>7460</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O46" s="12" t="n">
-        <v>23273.18</v>
+        <v>7460</v>
       </c>
       <c r="P46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q46" s="13" t="n">
-        <v>3.54421</v>
+        <v>0.16454</v>
       </c>
       <c r="R46" s="12" t="n">
-        <v>399.29</v>
+        <v>25.2</v>
       </c>
       <c r="S46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="U46" s="15" t="s">
         <v>72</v>
@@ -25413,16 +25380,16 @@
         <v>73</v>
       </c>
       <c r="X46" s="9" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="Y46" s="12" t="n">
-        <v>1398.33</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="12" t="n">
-        <v>23273.18</v>
+        <v>7460</v>
       </c>
       <c r="AA46" s="12" t="n">
-        <v>1629.14</v>
+        <v>895.2</v>
       </c>
       <c r="AB46" s="12" t="n">
         <v>0</v>
@@ -25527,7 +25494,7 @@
         <v>69</v>
       </c>
       <c r="BJ46" s="9" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="BK46" s="9" t="s">
         <v>75</v>
@@ -25541,79 +25508,79 @@
     </row>
     <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="8" t="n">
-        <v>307456</v>
+        <v>307502</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="9"/>
       <c r="E47" s="9"/>
       <c r="F47" s="9" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>219</v>
+        <v>173</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="K47" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>22610.71</v>
+        <v>30247.3</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="O47" s="12" t="n">
-        <v>21521.75</v>
+        <v>27226.44</v>
       </c>
       <c r="P47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q47" s="13" t="n">
-        <v>0</v>
+        <v>0.01332</v>
       </c>
       <c r="R47" s="12" t="n">
-        <v>167.78</v>
+        <v>8.64</v>
       </c>
       <c r="S47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="U47" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V47" s="12" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X47" s="9" t="s">
-        <v>234</v>
+        <v>276</v>
       </c>
       <c r="Y47" s="12" t="n">
-        <v>1088.96</v>
+        <v>3020.86</v>
       </c>
       <c r="Z47" s="12" t="n">
-        <v>21521.75</v>
+        <v>27226.44</v>
       </c>
       <c r="AA47" s="12" t="n">
-        <v>860.89</v>
+        <v>1880.05</v>
       </c>
       <c r="AB47" s="12" t="n">
         <v>0</v>
@@ -25622,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="AD47" s="12" t="n">
-        <v>652.54</v>
+        <v>610.6</v>
       </c>
       <c r="AE47" s="12" t="n">
         <v>0</v>
@@ -25703,25 +25670,25 @@
         <v>75</v>
       </c>
       <c r="BE47" s="14" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="BF47" s="9" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="BG47" s="9" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="BH47" s="14" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="BI47" s="9" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="BJ47" s="9" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="BK47" s="9" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="BL47" s="9" t="s">
         <v>75</v>
@@ -25731,900 +25698,534 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="8" t="n">
-        <v>307462</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>277</v>
-      </c>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9" t="s">
-        <v>278</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H48" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="I48" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="K48" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L48" s="12" t="n">
-        <v>319.81</v>
-      </c>
-      <c r="M48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O48" s="12" t="n">
-        <v>291.4</v>
-      </c>
-      <c r="P48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" s="13" t="n">
-        <v>0.002146</v>
-      </c>
-      <c r="R48" s="12" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="S48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="U48" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V48" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="W48" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X48" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y48" s="12" t="n">
-        <v>28.41</v>
-      </c>
-      <c r="Z48" s="12" t="n">
-        <v>291.4</v>
-      </c>
-      <c r="AA48" s="12" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="AB48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV48" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW48" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX48" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF48" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG48" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH48" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI48" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ48" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="BK48" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL48" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM48" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="8" t="n">
-        <v>307465</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="C49" s="9"/>
-      <c r="D49" s="9"/>
-      <c r="E49" s="9"/>
-      <c r="F49" s="9" t="s">
+    <row r="49" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="s">
         <v>283</v>
       </c>
-      <c r="G49" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="K49" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L49" s="12" t="n">
-        <v>1140.3</v>
-      </c>
-      <c r="M49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O49" s="12" t="n">
-        <v>1039</v>
-      </c>
-      <c r="P49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="13" t="n">
-        <v>0.00479</v>
-      </c>
-      <c r="R49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="14" t="s">
+      <c r="B49" s="17"/>
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
+      <c r="L49" s="17"/>
+      <c r="M49" s="17"/>
+      <c r="N49" s="17"/>
+      <c r="O49" s="17"/>
+      <c r="P49" s="17"/>
+      <c r="Q49" s="17"/>
+      <c r="R49" s="17"/>
+      <c r="S49" s="17"/>
+      <c r="T49" s="17"/>
+      <c r="U49" s="17"/>
+      <c r="V49" s="17"/>
+    </row>
+    <row r="50" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="18" t="s">
         <v>284</v>
       </c>
-      <c r="U49" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V49" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W49" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X49" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y49" s="12" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="Z49" s="12" t="n">
-        <v>1039</v>
-      </c>
-      <c r="AA49" s="12" t="n">
-        <v>72.73</v>
-      </c>
-      <c r="AB49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="12" t="n">
-        <v>242.33</v>
-      </c>
-      <c r="AE49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV49" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW49" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX49" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD49" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE49" s="14" t="s">
+      <c r="B50" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D50" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="BF49" s="9" t="s">
+      <c r="E50" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F50" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G50" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H50" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I50" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="BG49" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="BH49" s="14" t="s">
+      <c r="J50" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M50" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="BI49" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="BJ49" s="9" t="s">
+      <c r="N50" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O50" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P50" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q50" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R50" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S50" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="BK49" s="9" t="s">
+      <c r="T50" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="BL49" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM49" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="n">
-        <v>307471</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>290</v>
-      </c>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9" t="s">
-        <v>291</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="H50" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="I50" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="J50" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="K50" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L50" s="12" t="n">
-        <v>7460</v>
-      </c>
-      <c r="M50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O50" s="12" t="n">
-        <v>7460</v>
-      </c>
-      <c r="P50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" s="13" t="n">
-        <v>0.16454</v>
-      </c>
-      <c r="R50" s="12" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="U50" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V50" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="W50" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X50" s="9" t="s">
-        <v>234</v>
-      </c>
-      <c r="Y50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="12" t="n">
-        <v>7460</v>
-      </c>
-      <c r="AA50" s="12" t="n">
-        <v>895.2</v>
-      </c>
-      <c r="AB50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL50" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV50" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW50" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX50" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG50" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH50" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI50" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ50" s="9" t="s">
-        <v>293</v>
-      </c>
-      <c r="BK50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL50" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM50" s="16" t="s">
-        <v>79</v>
+      <c r="U50" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V50" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4"/>
+      <c r="A51" s="19" t="n">
+        <v>43</v>
+      </c>
+      <c r="B51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="19" t="n">
+        <v>265</v>
+      </c>
+      <c r="D51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="19" t="n">
+        <v>8561.73</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>294627.35</v>
+      </c>
+      <c r="G51" s="19" t="n">
+        <v>19487.25</v>
+      </c>
+      <c r="H51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="19" t="n">
+        <v>939.43</v>
+      </c>
+      <c r="K51" s="19" t="n">
+        <v>304767.36</v>
+      </c>
+      <c r="L51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="20" t="n">
+        <v>8.554614</v>
+      </c>
+      <c r="S51" s="19" t="n">
+        <v>295940.63</v>
+      </c>
+      <c r="T51" s="19" t="n">
+        <v>304767.36</v>
+      </c>
+      <c r="U51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="B52" s="17"/>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17"/>
-      <c r="S52" s="17"/>
-      <c r="T52" s="17"/>
-      <c r="U52" s="17"/>
-      <c r="V52" s="17"/>
+      <c r="A52" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E52" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F52" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G52" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H52" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I52" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J52" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="L52" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="M52" s="18" t="s">
+        <v>292</v>
+      </c>
     </row>
-    <row r="53" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="B53" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C53" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="18" t="s">
-        <v>296</v>
-      </c>
-      <c r="E53" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F53" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G53" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H53" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I53" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="J53" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K53" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L53" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M53" s="18" t="s">
-        <v>298</v>
-      </c>
-      <c r="N53" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O53" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P53" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q53" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R53" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S53" s="18" t="s">
-        <v>299</v>
-      </c>
-      <c r="T53" s="18" t="s">
-        <v>300</v>
-      </c>
-      <c r="U53" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V53" s="18" t="s">
-        <v>37</v>
+    <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="19" t="n">
+        <v>1411.31</v>
+      </c>
+      <c r="B53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="19" t="n">
+        <v>57.94</v>
+      </c>
+      <c r="E53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="19" t="n">
-        <v>46</v>
-      </c>
-      <c r="B54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="19" t="n">
-        <v>2142.94</v>
-      </c>
-      <c r="D54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="19" t="n">
-        <v>7894.65</v>
-      </c>
-      <c r="F54" s="19" t="n">
-        <v>371131.92</v>
-      </c>
-      <c r="G54" s="19" t="n">
-        <v>23873.19</v>
-      </c>
-      <c r="H54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="19" t="n">
-        <v>981.37</v>
-      </c>
-      <c r="K54" s="19" t="n">
-        <v>380604.85</v>
-      </c>
-      <c r="L54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" s="20" t="n">
-        <v>17.086314</v>
-      </c>
-      <c r="S54" s="19" t="n">
-        <v>370567.26</v>
-      </c>
-      <c r="T54" s="19" t="n">
-        <v>380604.85</v>
-      </c>
-      <c r="U54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A54" s="4"/>
     </row>
     <row r="55" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B55" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C55" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F55" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G55" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I55" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J55" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K55" s="18" t="s">
-        <v>301</v>
-      </c>
-      <c r="L55" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="M55" s="18" t="s">
-        <v>303</v>
-      </c>
+      <c r="A55" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="21"/>
+      <c r="R55" s="21"/>
+      <c r="S55" s="21"/>
+      <c r="T55" s="21"/>
+      <c r="U55" s="21"/>
+      <c r="V55" s="21"/>
+      <c r="W55" s="21"/>
+      <c r="X55" s="21"/>
+      <c r="Y55" s="21"/>
+      <c r="Z55" s="21"/>
+      <c r="AA55" s="21"/>
+      <c r="AB55" s="21"/>
+      <c r="AC55" s="21"/>
+      <c r="AD55" s="21"/>
+      <c r="AE55" s="21"/>
+      <c r="AF55" s="21"/>
+      <c r="AG55" s="21"/>
+      <c r="AH55" s="21"/>
+      <c r="AI55" s="21"/>
+      <c r="AJ55" s="21"/>
+      <c r="AK55" s="21"/>
+      <c r="AL55" s="21"/>
+      <c r="AM55" s="21"/>
+      <c r="AN55" s="21"/>
+      <c r="AO55" s="21"/>
+      <c r="AP55" s="21"/>
+      <c r="AQ55" s="21"/>
+      <c r="AR55" s="21"/>
+      <c r="AS55" s="21"/>
+      <c r="AT55" s="21"/>
+      <c r="AU55" s="21"/>
+      <c r="AV55" s="21"/>
+      <c r="AW55" s="21"/>
+      <c r="AX55" s="21"/>
+      <c r="AY55" s="21"/>
+      <c r="AZ55" s="21"/>
+      <c r="BA55" s="21"/>
+      <c r="BB55" s="21"/>
+      <c r="BC55" s="21"/>
+      <c r="BD55" s="21"/>
+      <c r="BE55" s="21"/>
+      <c r="BF55" s="21"/>
+      <c r="BG55" s="21"/>
+      <c r="BH55" s="21"/>
+      <c r="BI55" s="21"/>
+      <c r="BJ55" s="21"/>
+      <c r="BK55" s="21"/>
+      <c r="BL55" s="21"/>
+      <c r="BM55" s="21"/>
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="19" t="n">
-        <v>11075.17</v>
-      </c>
-      <c r="B56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="19" t="n">
-        <v>56.57</v>
-      </c>
-      <c r="E56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A56" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="4"/>
+      <c r="J56" s="4"/>
+      <c r="K56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4"/>
+      <c r="V56" s="4"/>
+      <c r="W56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="4"/>
+      <c r="AB56" s="4"/>
+      <c r="AC56" s="4"/>
+      <c r="AD56" s="4"/>
+      <c r="AE56" s="4"/>
+      <c r="AF56" s="4"/>
+      <c r="AG56" s="4"/>
+      <c r="AH56" s="4"/>
+      <c r="AI56" s="4"/>
+      <c r="AJ56" s="4"/>
+      <c r="AK56" s="4"/>
+      <c r="AL56" s="4"/>
+      <c r="AM56" s="4"/>
+      <c r="AN56" s="4"/>
+      <c r="AO56" s="4"/>
+      <c r="AP56" s="4"/>
+      <c r="AQ56" s="4"/>
+      <c r="AR56" s="4"/>
+      <c r="AS56" s="4"/>
+      <c r="AT56" s="4"/>
+      <c r="AU56" s="4"/>
+      <c r="AV56" s="4"/>
+      <c r="AW56" s="4"/>
+      <c r="AX56" s="4"/>
+      <c r="AY56" s="4"/>
+      <c r="AZ56" s="4"/>
+      <c r="BA56" s="4"/>
+      <c r="BB56" s="4"/>
+      <c r="BC56" s="4"/>
+      <c r="BD56" s="4"/>
+      <c r="BE56" s="4"/>
+      <c r="BF56" s="4"/>
+      <c r="BG56" s="4"/>
+      <c r="BH56" s="4"/>
+      <c r="BI56" s="4"/>
+      <c r="BJ56" s="4"/>
+      <c r="BK56" s="4"/>
+      <c r="BL56" s="4"/>
+      <c r="BM56" s="4"/>
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4"/>
+      <c r="A57" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="4"/>
+      <c r="I57" s="4"/>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4"/>
+      <c r="L57" s="4"/>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
+      <c r="P57" s="4"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4"/>
+      <c r="V57" s="4"/>
+      <c r="W57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="4"/>
+      <c r="AB57" s="4"/>
+      <c r="AC57" s="4"/>
+      <c r="AD57" s="4"/>
+      <c r="AE57" s="4"/>
+      <c r="AF57" s="4"/>
+      <c r="AG57" s="4"/>
+      <c r="AH57" s="4"/>
+      <c r="AI57" s="4"/>
+      <c r="AJ57" s="4"/>
+      <c r="AK57" s="4"/>
+      <c r="AL57" s="4"/>
+      <c r="AM57" s="4"/>
+      <c r="AN57" s="4"/>
+      <c r="AO57" s="4"/>
+      <c r="AP57" s="4"/>
+      <c r="AQ57" s="4"/>
+      <c r="AR57" s="4"/>
+      <c r="AS57" s="4"/>
+      <c r="AT57" s="4"/>
+      <c r="AU57" s="4"/>
+      <c r="AV57" s="4"/>
+      <c r="AW57" s="4"/>
+      <c r="AX57" s="4"/>
+      <c r="AY57" s="4"/>
+      <c r="AZ57" s="4"/>
+      <c r="BA57" s="4"/>
+      <c r="BB57" s="4"/>
+      <c r="BC57" s="4"/>
+      <c r="BD57" s="4"/>
+      <c r="BE57" s="4"/>
+      <c r="BF57" s="4"/>
+      <c r="BG57" s="4"/>
+      <c r="BH57" s="4"/>
+      <c r="BI57" s="4"/>
+      <c r="BJ57" s="4"/>
+      <c r="BK57" s="4"/>
+      <c r="BL57" s="4"/>
+      <c r="BM57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="21" t="s">
-        <v>304</v>
-      </c>
-      <c r="B58" s="21"/>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21"/>
-      <c r="K58" s="21"/>
-      <c r="L58" s="21"/>
-      <c r="M58" s="21"/>
-      <c r="N58" s="21"/>
-      <c r="O58" s="21"/>
-      <c r="P58" s="21"/>
-      <c r="Q58" s="21"/>
-      <c r="R58" s="21"/>
-      <c r="S58" s="21"/>
-      <c r="T58" s="21"/>
-      <c r="U58" s="21"/>
-      <c r="V58" s="21"/>
-      <c r="W58" s="21"/>
-      <c r="X58" s="21"/>
-      <c r="Y58" s="21"/>
-      <c r="Z58" s="21"/>
-      <c r="AA58" s="21"/>
-      <c r="AB58" s="21"/>
-      <c r="AC58" s="21"/>
-      <c r="AD58" s="21"/>
-      <c r="AE58" s="21"/>
-      <c r="AF58" s="21"/>
-      <c r="AG58" s="21"/>
-      <c r="AH58" s="21"/>
-      <c r="AI58" s="21"/>
-      <c r="AJ58" s="21"/>
-      <c r="AK58" s="21"/>
-      <c r="AL58" s="21"/>
-      <c r="AM58" s="21"/>
-      <c r="AN58" s="21"/>
-      <c r="AO58" s="21"/>
-      <c r="AP58" s="21"/>
-      <c r="AQ58" s="21"/>
-      <c r="AR58" s="21"/>
-      <c r="AS58" s="21"/>
-      <c r="AT58" s="21"/>
-      <c r="AU58" s="21"/>
-      <c r="AV58" s="21"/>
-      <c r="AW58" s="21"/>
-      <c r="AX58" s="21"/>
-      <c r="AY58" s="21"/>
-      <c r="AZ58" s="21"/>
-      <c r="BA58" s="21"/>
-      <c r="BB58" s="21"/>
-      <c r="BC58" s="21"/>
-      <c r="BD58" s="21"/>
-      <c r="BE58" s="21"/>
-      <c r="BF58" s="21"/>
-      <c r="BG58" s="21"/>
-      <c r="BH58" s="21"/>
-      <c r="BI58" s="21"/>
-      <c r="BJ58" s="21"/>
-      <c r="BK58" s="21"/>
-      <c r="BL58" s="21"/>
-      <c r="BM58" s="21"/>
+    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B58" s="4"/>
+      <c r="C58" s="4"/>
+      <c r="D58" s="4"/>
+      <c r="E58" s="4"/>
+      <c r="F58" s="4"/>
+      <c r="G58" s="4"/>
+      <c r="H58" s="4"/>
+      <c r="I58" s="4"/>
+      <c r="J58" s="4"/>
+      <c r="K58" s="4"/>
+      <c r="L58" s="4"/>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
+      <c r="P58" s="4"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4"/>
+      <c r="V58" s="4"/>
+      <c r="W58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="4"/>
+      <c r="AB58" s="4"/>
+      <c r="AC58" s="4"/>
+      <c r="AD58" s="4"/>
+      <c r="AE58" s="4"/>
+      <c r="AF58" s="4"/>
+      <c r="AG58" s="4"/>
+      <c r="AH58" s="4"/>
+      <c r="AI58" s="4"/>
+      <c r="AJ58" s="4"/>
+      <c r="AK58" s="4"/>
+      <c r="AL58" s="4"/>
+      <c r="AM58" s="4"/>
+      <c r="AN58" s="4"/>
+      <c r="AO58" s="4"/>
+      <c r="AP58" s="4"/>
+      <c r="AQ58" s="4"/>
+      <c r="AR58" s="4"/>
+      <c r="AS58" s="4"/>
+      <c r="AT58" s="4"/>
+      <c r="AU58" s="4"/>
+      <c r="AV58" s="4"/>
+      <c r="AW58" s="4"/>
+      <c r="AX58" s="4"/>
+      <c r="AY58" s="4"/>
+      <c r="AZ58" s="4"/>
+      <c r="BA58" s="4"/>
+      <c r="BB58" s="4"/>
+      <c r="BC58" s="4"/>
+      <c r="BD58" s="4"/>
+      <c r="BE58" s="4"/>
+      <c r="BF58" s="4"/>
+      <c r="BG58" s="4"/>
+      <c r="BH58" s="4"/>
+      <c r="BI58" s="4"/>
+      <c r="BJ58" s="4"/>
+      <c r="BK58" s="4"/>
+      <c r="BL58" s="4"/>
+      <c r="BM58" s="4"/>
     </row>
     <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="4" t="s">
-        <v>75</v>
+        <v>296</v>
       </c>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -26693,7 +26294,7 @@
     </row>
     <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="4" t="s">
-        <v>305</v>
+        <v>22</v>
       </c>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -26762,7 +26363,7 @@
     </row>
     <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="4" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -26831,7 +26432,7 @@
     </row>
     <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="4" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -26900,7 +26501,7 @@
     </row>
     <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="4" t="s">
-        <v>22</v>
+        <v>299</v>
       </c>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -26969,7 +26570,7 @@
     </row>
     <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="4" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -27038,7 +26639,7 @@
     </row>
     <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="4" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -27105,215 +26706,8 @@
       <c r="BL65" s="4"/>
       <c r="BM65" s="4"/>
     </row>
-    <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B66" s="4"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="4"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="4"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4"/>
-      <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-      <c r="Q66" s="4"/>
-      <c r="R66" s="4"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
-      <c r="X66" s="4"/>
-      <c r="Y66" s="4"/>
-      <c r="Z66" s="4"/>
-      <c r="AA66" s="4"/>
-      <c r="AB66" s="4"/>
-      <c r="AC66" s="4"/>
-      <c r="AD66" s="4"/>
-      <c r="AE66" s="4"/>
-      <c r="AF66" s="4"/>
-      <c r="AG66" s="4"/>
-      <c r="AH66" s="4"/>
-      <c r="AI66" s="4"/>
-      <c r="AJ66" s="4"/>
-      <c r="AK66" s="4"/>
-      <c r="AL66" s="4"/>
-      <c r="AM66" s="4"/>
-      <c r="AN66" s="4"/>
-      <c r="AO66" s="4"/>
-      <c r="AP66" s="4"/>
-      <c r="AQ66" s="4"/>
-      <c r="AR66" s="4"/>
-      <c r="AS66" s="4"/>
-      <c r="AT66" s="4"/>
-      <c r="AU66" s="4"/>
-      <c r="AV66" s="4"/>
-      <c r="AW66" s="4"/>
-      <c r="AX66" s="4"/>
-      <c r="AY66" s="4"/>
-      <c r="AZ66" s="4"/>
-      <c r="BA66" s="4"/>
-      <c r="BB66" s="4"/>
-      <c r="BC66" s="4"/>
-      <c r="BD66" s="4"/>
-      <c r="BE66" s="4"/>
-      <c r="BF66" s="4"/>
-      <c r="BG66" s="4"/>
-      <c r="BH66" s="4"/>
-      <c r="BI66" s="4"/>
-      <c r="BJ66" s="4"/>
-      <c r="BK66" s="4"/>
-      <c r="BL66" s="4"/>
-      <c r="BM66" s="4"/>
-    </row>
-    <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B67" s="4"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="4"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="4"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="4"/>
-      <c r="U67" s="4"/>
-      <c r="V67" s="4"/>
-      <c r="W67" s="4"/>
-      <c r="X67" s="4"/>
-      <c r="Y67" s="4"/>
-      <c r="Z67" s="4"/>
-      <c r="AA67" s="4"/>
-      <c r="AB67" s="4"/>
-      <c r="AC67" s="4"/>
-      <c r="AD67" s="4"/>
-      <c r="AE67" s="4"/>
-      <c r="AF67" s="4"/>
-      <c r="AG67" s="4"/>
-      <c r="AH67" s="4"/>
-      <c r="AI67" s="4"/>
-      <c r="AJ67" s="4"/>
-      <c r="AK67" s="4"/>
-      <c r="AL67" s="4"/>
-      <c r="AM67" s="4"/>
-      <c r="AN67" s="4"/>
-      <c r="AO67" s="4"/>
-      <c r="AP67" s="4"/>
-      <c r="AQ67" s="4"/>
-      <c r="AR67" s="4"/>
-      <c r="AS67" s="4"/>
-      <c r="AT67" s="4"/>
-      <c r="AU67" s="4"/>
-      <c r="AV67" s="4"/>
-      <c r="AW67" s="4"/>
-      <c r="AX67" s="4"/>
-      <c r="AY67" s="4"/>
-      <c r="AZ67" s="4"/>
-      <c r="BA67" s="4"/>
-      <c r="BB67" s="4"/>
-      <c r="BC67" s="4"/>
-      <c r="BD67" s="4"/>
-      <c r="BE67" s="4"/>
-      <c r="BF67" s="4"/>
-      <c r="BG67" s="4"/>
-      <c r="BH67" s="4"/>
-      <c r="BI67" s="4"/>
-      <c r="BJ67" s="4"/>
-      <c r="BK67" s="4"/>
-      <c r="BL67" s="4"/>
-      <c r="BM67" s="4"/>
-    </row>
-    <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B68" s="4"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="4"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="4"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="4"/>
-      <c r="U68" s="4"/>
-      <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
-      <c r="X68" s="4"/>
-      <c r="Y68" s="4"/>
-      <c r="Z68" s="4"/>
-      <c r="AA68" s="4"/>
-      <c r="AB68" s="4"/>
-      <c r="AC68" s="4"/>
-      <c r="AD68" s="4"/>
-      <c r="AE68" s="4"/>
-      <c r="AF68" s="4"/>
-      <c r="AG68" s="4"/>
-      <c r="AH68" s="4"/>
-      <c r="AI68" s="4"/>
-      <c r="AJ68" s="4"/>
-      <c r="AK68" s="4"/>
-      <c r="AL68" s="4"/>
-      <c r="AM68" s="4"/>
-      <c r="AN68" s="4"/>
-      <c r="AO68" s="4"/>
-      <c r="AP68" s="4"/>
-      <c r="AQ68" s="4"/>
-      <c r="AR68" s="4"/>
-      <c r="AS68" s="4"/>
-      <c r="AT68" s="4"/>
-      <c r="AU68" s="4"/>
-      <c r="AV68" s="4"/>
-      <c r="AW68" s="4"/>
-      <c r="AX68" s="4"/>
-      <c r="AY68" s="4"/>
-      <c r="AZ68" s="4"/>
-      <c r="BA68" s="4"/>
-      <c r="BB68" s="4"/>
-      <c r="BC68" s="4"/>
-      <c r="BD68" s="4"/>
-      <c r="BE68" s="4"/>
-      <c r="BF68" s="4"/>
-      <c r="BG68" s="4"/>
-      <c r="BH68" s="4"/>
-      <c r="BI68" s="4"/>
-      <c r="BJ68" s="4"/>
-      <c r="BK68" s="4"/>
-      <c r="BL68" s="4"/>
-      <c r="BM68" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="62">
+  <mergeCells count="59">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -27361,10 +26755,10 @@
     <mergeCell ref="B45:E45"/>
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B47:E47"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="A52:V52"/>
+    <mergeCell ref="A49:V49"/>
+    <mergeCell ref="A55:BM55"/>
+    <mergeCell ref="A56:BM56"/>
+    <mergeCell ref="A57:BM57"/>
     <mergeCell ref="A58:BM58"/>
     <mergeCell ref="A59:BM59"/>
     <mergeCell ref="A60:BM60"/>
@@ -27373,9 +26767,6 @@
     <mergeCell ref="A63:BM63"/>
     <mergeCell ref="A64:BM64"/>
     <mergeCell ref="A65:BM65"/>
-    <mergeCell ref="A66:BM66"/>
-    <mergeCell ref="A67:BM67"/>
-    <mergeCell ref="A68:BM68"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="264">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 20/05/2026 05:30:32</t>
+    <t xml:space="preserve">Emitido em: 21/05/2026 05:30:34</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -331,255 +331,144 @@
     <t xml:space="preserve">43260589616460000152550020000713281306751109</t>
   </si>
   <si>
+    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.976.319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.756,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">790 - JACKWAL S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">275.196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.834,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260592782366000188550030002751961654432159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.265,79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - FILIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804111200730267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804981991793601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804121347149640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.929,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829821661840971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">461,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829961140036509</t>
+  </si>
+  <si>
     <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
   </si>
   <si>
-    <t xml:space="preserve">636.071</t>
+    <t xml:space="preserve">638.725</t>
   </si>
   <si>
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.022,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006360711913994222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.976.319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.756,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">777 - IRMAOS FISCHER S.A IND. E COM.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">760,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807431502859010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.780.742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.332,17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582984287000104550020017807421113944451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.975.491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">94.092,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260561413282000143550010029754911228653957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">790 - JACKWAL S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">275.196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.834,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260592782366000188550030002751961654432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.265,79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - FILIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">637.255</t>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.887,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006387251174884389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.553</t>
   </si>
   <si>
     <t xml:space="preserve">08/06/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">20.761,14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006372551066202512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">870.004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.603,35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008700041500773535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">637.784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.890,24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006377841750929843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">870.017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.185,87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008700171161145098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804111200730267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804981991793601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804121347149640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.646 - ASTRA S.A INDUSTRIA E COMERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.304.071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">426,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260550949528001232550010023040711903090311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">870.047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.695,18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008700471155162406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.929,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829821661840971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">461,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829961140036509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">638.725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.887,04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006387251174884389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.553</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.702,49</t>
   </si>
   <si>
@@ -601,10 +490,7 @@
     <t xml:space="preserve">42260581604803000157550010008671441582155041</t>
   </si>
   <si>
-    <t xml:space="preserve">750 - COPLAS INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">200.251</t>
+    <t xml:space="preserve">639.745</t>
   </si>
   <si>
     <t xml:space="preserve">14/05/2026</t>
@@ -613,15 +499,6 @@
     <t xml:space="preserve">10/06/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.314,33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260567718726000135550010002002511236212733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.745</t>
-  </si>
-  <si>
     <t xml:space="preserve">7.078,63</t>
   </si>
   <si>
@@ -844,31 +721,40 @@
     <t xml:space="preserve">42260532296669000169550030000014561732534080</t>
   </si>
   <si>
-    <t xml:space="preserve">10.343 - INTERLIGHT SISTEMAS DE ILUMINACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">261.762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.247,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">399.241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.659 - RODO DANNY TRANSPORTES E LOGISTICAS EIRELI ME</t>
-  </si>
-  <si>
-    <t xml:space="preserve">610,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260558329608000144550010002617621002617634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260511389565000200570050003992411000855094</t>
+    <t xml:space="preserve">16.628 - VFL IMPORTADORA E DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.723,65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260505104359000122550010000046771737179198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050855751937497947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050856531939175139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050856541425368248</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17114,7 +17000,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM65"/>
+  <dimension ref="A1:BM57"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -18250,7 +18136,7 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>306945</v>
+        <v>307020</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>103</v>
@@ -18262,22 +18148,22 @@
         <v>104</v>
       </c>
       <c r="G9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="J9" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>11022.8</v>
+        <v>1756.8</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -18286,43 +18172,43 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>11022.8</v>
+        <v>1756.8</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.0217</v>
+        <v>0.142272</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>2.44</v>
+        <v>3.42</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Y9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>11022.8</v>
+        <v>1756.8</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>771.6</v>
+        <v>122.98</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18427,7 +18313,7 @@
         <v>69</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18441,79 +18327,79 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>307020</v>
+        <v>307073</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="G10" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="G10" s="10" t="s">
-        <v>66</v>
-      </c>
       <c r="H10" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>1756.8</v>
+        <v>7834.72</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>1756.8</v>
+        <v>7524.33</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.142272</v>
+        <v>0</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>0</v>
+        <v>310.39</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>1756.8</v>
+        <v>7524.33</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>122.98</v>
+        <v>526.7</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18618,7 +18504,7 @@
         <v>69</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18632,79 +18518,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>307044</v>
+        <v>307133</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>760.8</v>
+        <v>4265.79</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>760.8</v>
+        <v>4222.88</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.09178</v>
+        <v>0.484131</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>14.15</v>
+        <v>71.4</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>0</v>
+        <v>42.91</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>760.8</v>
+        <v>4222.88</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>53.26</v>
+        <v>281.12</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18773,7 +18659,7 @@
         <v>85</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18809,7 +18695,7 @@
         <v>69</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18823,25 +18709,25 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>307045</v>
+        <v>307171</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I12" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J12" s="9" t="s">
         <v>69</v>
@@ -18850,7 +18736,7 @@
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>1332.17</v>
+        <v>404.81</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18859,22 +18745,22 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>1332.17</v>
+        <v>404.81</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.017488</v>
+        <v>0.000858</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>8.85</v>
+        <v>2.43</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
@@ -18886,16 +18772,16 @@
         <v>73</v>
       </c>
       <c r="X12" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Y12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>1332.17</v>
+        <v>404.81</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>53.29</v>
+        <v>16.19</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18964,7 +18850,7 @@
         <v>85</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>75</v>
@@ -19000,7 +18886,7 @@
         <v>69</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19014,79 +18900,79 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>307062</v>
+        <v>307173</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>126</v>
+        <v>69</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>94092.8</v>
+        <v>404.81</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>93172</v>
+        <v>404.81</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>2.122527</v>
+        <v>0.000858</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>493.99</v>
+        <v>2.43</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X13" s="9" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="Y13" s="12" t="n">
-        <v>920.8</v>
+        <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>92335.42</v>
+        <v>404.81</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>5743.16</v>
+        <v>16.19</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19155,7 +19041,7 @@
         <v>85</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -19191,7 +19077,7 @@
         <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19205,10 +19091,10 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>307073</v>
+        <v>307174</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
@@ -19217,67 +19103,67 @@
         <v>130</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>108</v>
+        <v>69</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>7834.72</v>
+        <v>404.81</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>7524.33</v>
+        <v>404.81</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0</v>
+        <v>0.000858</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>310.39</v>
+        <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>7524.33</v>
+        <v>404.81</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>526.7</v>
+        <v>16.19</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19346,7 +19232,7 @@
         <v>85</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>75</v>
@@ -19382,7 +19268,7 @@
         <v>69</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19396,79 +19282,79 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>307133</v>
+        <v>307231</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>4265.79</v>
+        <v>2929.6</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>4222.88</v>
+        <v>2929.6</v>
       </c>
       <c r="P15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.484131</v>
+        <v>0.000484</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>71.4</v>
+        <v>3.22</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="W15" s="9" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>42.91</v>
+        <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>4222.88</v>
+        <v>2929.6</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>281.12</v>
+        <v>205.07</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19573,7 +19459,7 @@
         <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19587,34 +19473,34 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>307142</v>
+        <v>307235</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>20761.14</v>
+        <v>461.96</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
@@ -19623,43 +19509,43 @@
         <v>1</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>20761.14</v>
+        <v>461.96</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.01152</v>
+        <v>0.002057</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>2.23</v>
+        <v>2.43</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W16" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="Y16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>20761.14</v>
+        <v>461.96</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>1453.28</v>
+        <v>18.48</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19728,7 +19614,7 @@
         <v>85</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19764,7 +19650,7 @@
         <v>69</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19778,34 +19664,34 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>307159</v>
+        <v>307242</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1603.35</v>
+        <v>1887.04</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19814,43 +19700,43 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>1527</v>
+        <v>1887.04</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.05265</v>
+        <v>0.007832</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>30</v>
+        <v>1.9</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>76.35</v>
+        <v>0</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>1527</v>
+        <v>1887.04</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>106.89</v>
+        <v>132.09</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19955,7 +19841,7 @@
         <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19969,34 +19855,34 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>307161</v>
+        <v>307265</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>4890.24</v>
+        <v>3702.49</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -20005,43 +19891,43 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>4890.24</v>
+        <v>3437.49</v>
       </c>
       <c r="P18" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.001296</v>
+        <v>0</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>4890.24</v>
+        <v>3702.49</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>342.32</v>
+        <v>259.17</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20146,7 +20032,7 @@
         <v>69</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20160,10 +20046,10 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>307162</v>
+        <v>307278</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
@@ -20172,13 +20058,13 @@
         <v>152</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>153</v>
@@ -20187,25 +20073,25 @@
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>1185.87</v>
+        <v>29709.55</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>1129.4</v>
+        <v>29280.46</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.0351</v>
+        <v>0.69578</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>20</v>
+        <v>130.96</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
@@ -20217,22 +20103,22 @@
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="W19" s="9" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>56.47</v>
+        <v>429.09</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>1129.4</v>
+        <v>29280.46</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>79.06</v>
+        <v>1794.18</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20351,34 +20237,34 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>307171</v>
+        <v>307330</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="G20" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>125</v>
-      </c>
       <c r="J20" s="9" t="s">
-        <v>69</v>
+        <v>158</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>404.81</v>
+        <v>7078.63</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
@@ -20387,43 +20273,43 @@
         <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>404.81</v>
+        <v>6646.6</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.0425</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>2.43</v>
+        <v>9.6</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>0</v>
+        <v>432.03</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>404.81</v>
+        <v>6646.6</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>16.19</v>
+        <v>465.26</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20492,7 +20378,7 @@
         <v>85</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20528,7 +20414,7 @@
         <v>69</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20542,34 +20428,34 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>307173</v>
+        <v>307334</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>69</v>
+        <v>162</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>404.81</v>
+        <v>4963.92</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
@@ -20578,43 +20464,43 @@
         <v>1</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>404.81</v>
+        <v>4963.92</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.029904</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>2.43</v>
+        <v>6.84</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="Y21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>404.81</v>
+        <v>4963.92</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>16.19</v>
+        <v>347.47</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20683,7 +20569,7 @@
         <v>85</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20719,7 +20605,7 @@
         <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20733,34 +20619,34 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>307174</v>
+        <v>307356</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="J22" s="9" t="s">
         <v>162</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>404.81</v>
+        <v>2104.02</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20769,43 +20655,43 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>404.81</v>
+        <v>2104.02</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.005548</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>2.43</v>
+        <v>1.08</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="Y22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>404.81</v>
+        <v>2104.02</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>16.19</v>
+        <v>147.28</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20874,7 +20760,7 @@
         <v>85</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20910,7 +20796,7 @@
         <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20924,79 +20810,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>307181</v>
+        <v>307367</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>426.2</v>
+        <v>5671.17</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>426.2</v>
+        <v>5538.68</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.0025</v>
+        <v>0.314926</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>10</v>
+        <v>33.19</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>77</v>
+        <v>55.35</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>0</v>
+        <v>132.49</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>426.2</v>
+        <v>4787.31</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>29.84</v>
+        <v>258.23</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21101,7 +20987,7 @@
         <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21115,79 +21001,79 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>307183</v>
+        <v>307369</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>131</v>
+        <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="K24" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>12695.18</v>
+        <v>1825.13</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>11935.6</v>
+        <v>1767.68</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.0698</v>
+        <v>0.025844</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>31.68</v>
+        <v>6.79</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V24" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="W24" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>759.58</v>
+        <v>57.45</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>11935.6</v>
+        <v>1767.68</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>614.43</v>
+        <v>110.47</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21256,7 +21142,7 @@
         <v>85</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21292,7 +21178,7 @@
         <v>69</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="BK24" s="9" t="s">
         <v>75</v>
@@ -21306,34 +21192,34 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>307231</v>
+        <v>307376</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>2929.6</v>
+        <v>499.53</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
@@ -21342,43 +21228,43 @@
         <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>2929.6</v>
+        <v>499.53</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.000484</v>
+        <v>0.000507</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>3.22</v>
+        <v>1.07</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="W25" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>2929.6</v>
+        <v>499.53</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>205.07</v>
+        <v>34.97</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21483,7 +21369,7 @@
         <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21497,34 +21383,34 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>307235</v>
+        <v>307386</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>125</v>
+        <v>170</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>69</v>
+        <v>180</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>461.96</v>
+        <v>481.59</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -21533,43 +21419,43 @@
         <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>461.96</v>
+        <v>481.59</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.002057</v>
+        <v>0.002268</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>2.43</v>
+        <v>0.44</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V26" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W26" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Y26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>461.96</v>
+        <v>481.59</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>18.48</v>
+        <v>19.26</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21638,7 +21524,7 @@
         <v>85</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21674,7 +21560,7 @@
         <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21688,79 +21574,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>307242</v>
+        <v>307424</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>181</v>
+        <v>69</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>1887.04</v>
+        <v>1783.2</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>1887.04</v>
+        <v>1624.79</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.007832</v>
+        <v>0</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>0</v>
+        <v>158.41</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>1887.04</v>
+        <v>1624.79</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>132.09</v>
+        <v>65.04</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21769,7 +21655,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="12" t="n">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="AE27" s="12" t="n">
         <v>0</v>
@@ -21829,7 +21715,7 @@
         <v>85</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21850,25 +21736,25 @@
         <v>75</v>
       </c>
       <c r="BE27" s="14" t="s">
-        <v>75</v>
+        <v>187</v>
       </c>
       <c r="BF27" s="9" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
       <c r="BG27" s="9" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="BH27" s="14" t="s">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="BI27" s="9" t="s">
-        <v>69</v>
+        <v>185</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="BK27" s="9" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="BL27" s="9" t="s">
         <v>75</v>
@@ -21879,79 +21765,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>307265</v>
+        <v>307428</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>184</v>
+        <v>118</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>141</v>
+        <v>193</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>3702.49</v>
+        <v>785.04</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>3437.49</v>
+        <v>785.04</v>
       </c>
       <c r="P28" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0</v>
+        <v>0.06696</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>3.5</v>
+        <v>2.59</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="W28" s="9" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="Y28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>3702.49</v>
+        <v>785.04</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>259.17</v>
+        <v>54.95</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -22056,7 +21942,7 @@
         <v>69</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -22070,79 +21956,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>307278</v>
+        <v>307433</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>66</v>
+        <v>142</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>125</v>
+        <v>197</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>29709.55</v>
+        <v>1040.61</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>29280.46</v>
+        <v>977.1</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0.69578</v>
+        <v>0</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>130.96</v>
+        <v>0</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="W29" s="9" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>429.09</v>
+        <v>63.51</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>29280.46</v>
+        <v>977.1</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>1794.18</v>
+        <v>68.4</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22247,7 +22133,7 @@
         <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22261,79 +22147,79 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>307297</v>
+        <v>307439</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>66</v>
+        <v>203</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>3314.33</v>
+        <v>2401.84</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>3210</v>
+        <v>2401.84</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0</v>
+        <v>0.29576</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>0</v>
+        <v>31.68</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>104.33</v>
+        <v>0</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>3210</v>
+        <v>2401.84</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>224.7</v>
+        <v>149.08</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22438,7 +22324,7 @@
         <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22452,34 +22338,34 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>307330</v>
+        <v>307443</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="G31" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>7078.63</v>
+        <v>447.13</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -22488,43 +22374,43 @@
         <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>6646.6</v>
+        <v>433.06</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.0425</v>
+        <v>0.0219</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>9.6</v>
+        <v>1.7</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>432.03</v>
+        <v>14.07</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>6646.6</v>
+        <v>433.06</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>465.26</v>
+        <v>30.31</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22629,7 +22515,7 @@
         <v>69</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="BK31" s="9" t="s">
         <v>75</v>
@@ -22643,79 +22529,79 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>307334</v>
+        <v>307444</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>103</v>
+        <v>207</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="G32" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H32" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>4963.92</v>
+        <v>24671.51</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>4963.92</v>
+        <v>23273.18</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>0.029904</v>
+        <v>3.54421</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>6.84</v>
+        <v>399.29</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T32" s="14" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="U32" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V32" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W32" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>0</v>
+        <v>1398.33</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>4963.92</v>
+        <v>23273.18</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>347.47</v>
+        <v>1629.14</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22820,7 +22706,7 @@
         <v>69</v>
       </c>
       <c r="BJ32" s="9" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="BK32" s="9" t="s">
         <v>75</v>
@@ -22834,79 +22720,79 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>307356</v>
+        <v>307462</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>103</v>
+        <v>215</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9"/>
       <c r="E33" s="9"/>
       <c r="F33" s="9" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="G33" s="10" t="s">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="K33" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>2104.02</v>
+        <v>319.81</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>2104.02</v>
+        <v>291.4</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.005548</v>
+        <v>0.002146</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>1.08</v>
+        <v>0.53</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T33" s="14" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="U33" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>0</v>
+        <v>28.41</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>2104.02</v>
+        <v>291.4</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>147.28</v>
+        <v>11.65</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -23011,7 +22897,7 @@
         <v>69</v>
       </c>
       <c r="BJ33" s="9" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="BK33" s="9" t="s">
         <v>75</v>
@@ -23025,79 +22911,79 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>307367</v>
+        <v>307465</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>196</v>
+        <v>162</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>5671.17</v>
+        <v>1140.3</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>5538.68</v>
+        <v>1039</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.314926</v>
+        <v>0.00479</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>33.19</v>
+        <v>0</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>55.35</v>
+        <v>28</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>132.49</v>
+        <v>101.3</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>4787.31</v>
+        <v>1039</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>258.23</v>
+        <v>72.73</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -23106,7 +22992,7 @@
         <v>0</v>
       </c>
       <c r="AD34" s="12" t="n">
-        <v>0</v>
+        <v>242.33</v>
       </c>
       <c r="AE34" s="12" t="n">
         <v>0</v>
@@ -23187,25 +23073,25 @@
         <v>75</v>
       </c>
       <c r="BE34" s="14" t="s">
-        <v>75</v>
+        <v>223</v>
       </c>
       <c r="BF34" s="9" t="s">
-        <v>75</v>
+        <v>224</v>
       </c>
       <c r="BG34" s="9" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="BH34" s="14" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="BI34" s="9" t="s">
-        <v>69</v>
+        <v>185</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="BK34" s="9" t="s">
-        <v>75</v>
+        <v>227</v>
       </c>
       <c r="BL34" s="9" t="s">
         <v>75</v>
@@ -23216,79 +23102,79 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>307369</v>
+        <v>307471</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>188</v>
+        <v>228</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>66</v>
+        <v>112</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>69</v>
+        <v>230</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>1825.13</v>
+        <v>7460</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>1767.68</v>
+        <v>7460</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.025844</v>
+        <v>0.16454</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>6.79</v>
+        <v>25.2</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>211</v>
+        <v>185</v>
       </c>
       <c r="Y35" s="12" t="n">
-        <v>57.45</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>1767.68</v>
+        <v>7460</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>110.47</v>
+        <v>895.2</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23357,7 +23243,7 @@
         <v>85</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23393,7 +23279,7 @@
         <v>69</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23407,79 +23293,79 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>307376</v>
+        <v>307539</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>103</v>
+        <v>233</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H36" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="I36" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="G36" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="H36" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>211</v>
-      </c>
       <c r="J36" s="9" t="s">
-        <v>203</v>
+        <v>235</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>499.53</v>
+        <v>2723.65</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>499.53</v>
+        <v>2723.65</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.000507</v>
+        <v>0.004185</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>1.07</v>
+        <v>3.07</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>28</v>
+        <v>61.33</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>499.53</v>
+        <v>2723.65</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>34.97</v>
+        <v>108.95</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23545,7 +23431,7 @@
         <v>74</v>
       </c>
       <c r="AW36" s="14" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AX36" s="10" t="s">
         <v>86</v>
@@ -23584,7 +23470,7 @@
         <v>69</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23598,34 +23484,34 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>307386</v>
+        <v>307572</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>156</v>
+        <v>124</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>221</v>
+        <v>69</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>481.59</v>
+        <v>355.13</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -23634,43 +23520,43 @@
         <v>1</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>481.59</v>
+        <v>355.13</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.002268</v>
+        <v>0.00819</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>0.44</v>
+        <v>2.17</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W37" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="Y37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>481.59</v>
+        <v>355.13</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>19.26</v>
+        <v>14.21</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23739,7 +23625,7 @@
         <v>85</v>
       </c>
       <c r="AX37" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY37" s="14" t="s">
         <v>75</v>
@@ -23775,7 +23661,7 @@
         <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23789,25 +23675,25 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>307424</v>
+        <v>307578</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>224</v>
+        <v>124</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="J38" s="9" t="s">
         <v>69</v>
@@ -23816,31 +23702,31 @@
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>1783.2</v>
+        <v>355.13</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>1624.79</v>
+        <v>355.13</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0</v>
+        <v>0.00819</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
@@ -23852,16 +23738,16 @@
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>158.41</v>
+        <v>0</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>1624.79</v>
+        <v>355.13</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>65.04</v>
+        <v>14.21</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23870,7 +23756,7 @@
         <v>0</v>
       </c>
       <c r="AD38" s="12" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="AE38" s="12" t="n">
         <v>0</v>
@@ -23930,7 +23816,7 @@
         <v>85</v>
       </c>
       <c r="AX38" s="10" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AY38" s="14" t="s">
         <v>75</v>
@@ -23951,25 +23837,25 @@
         <v>75</v>
       </c>
       <c r="BE38" s="14" t="s">
-        <v>228</v>
+        <v>75</v>
       </c>
       <c r="BF38" s="9" t="s">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="BG38" s="9" t="s">
-        <v>195</v>
+        <v>69</v>
       </c>
       <c r="BH38" s="14" t="s">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="BI38" s="9" t="s">
-        <v>226</v>
+        <v>69</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="BK38" s="9" t="s">
-        <v>232</v>
+        <v>75</v>
       </c>
       <c r="BL38" s="9" t="s">
         <v>75</v>
@@ -23980,79 +23866,79 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>307428</v>
+        <v>307579</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>211</v>
+        <v>170</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>234</v>
+        <v>69</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>785.04</v>
+        <v>355.13</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>785.04</v>
+        <v>355.13</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.06696</v>
+        <v>0.00819</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>2.59</v>
+        <v>2.17</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="W39" s="9" t="s">
-        <v>138</v>
+        <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="Y39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>785.04</v>
+        <v>355.13</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>54.95</v>
+        <v>14.21</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24121,7 +24007,7 @@
         <v>85</v>
       </c>
       <c r="AX39" s="10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AY39" s="14" t="s">
         <v>75</v>
@@ -24157,7 +24043,7 @@
         <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24170,1855 +24056,879 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="n">
-        <v>307433</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J40" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="K40" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L40" s="12" t="n">
-        <v>1040.61</v>
-      </c>
-      <c r="M40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" s="12" t="n">
-        <v>977.1</v>
-      </c>
-      <c r="P40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="U40" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V40" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W40" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X40" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y40" s="12" t="n">
-        <v>63.51</v>
-      </c>
-      <c r="Z40" s="12" t="n">
-        <v>977.1</v>
-      </c>
-      <c r="AA40" s="12" t="n">
-        <v>68.4</v>
-      </c>
-      <c r="AB40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO40" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV40" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW40" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX40" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY40" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ40" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA40" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB40" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC40" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD40" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE40" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF40" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG40" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH40" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI40" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ40" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="BK40" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL40" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM40" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A40" s="4"/>
     </row>
-    <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="8" t="n">
-        <v>307439</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="C41" s="9"/>
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9" t="s">
-        <v>243</v>
-      </c>
-      <c r="G41" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="I41" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J41" s="9" t="s">
+    <row r="41" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="K41" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>2401.84</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="O41" s="12" t="n">
-        <v>2401.84</v>
-      </c>
-      <c r="P41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="13" t="n">
-        <v>0.29576</v>
-      </c>
-      <c r="R41" s="12" t="n">
-        <v>31.68</v>
-      </c>
-      <c r="S41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" s="14" t="s">
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
+      <c r="L41" s="17"/>
+      <c r="M41" s="17"/>
+      <c r="N41" s="17"/>
+      <c r="O41" s="17"/>
+      <c r="P41" s="17"/>
+      <c r="Q41" s="17"/>
+      <c r="R41" s="17"/>
+      <c r="S41" s="17"/>
+      <c r="T41" s="17"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="17"/>
+    </row>
+    <row r="42" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="18" t="s">
         <v>246</v>
       </c>
-      <c r="U41" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V41" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="W41" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X41" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="12" t="n">
-        <v>2401.84</v>
-      </c>
-      <c r="AA41" s="12" t="n">
-        <v>149.08</v>
-      </c>
-      <c r="AB41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO41" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV41" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW41" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX41" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY41" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ41" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA41" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB41" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC41" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD41" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE41" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF41" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG41" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH41" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI41" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ41" s="9" t="s">
+      <c r="B42" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="BK41" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL41" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM41" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="8" t="n">
-        <v>307443</v>
-      </c>
-      <c r="B42" s="9" t="s">
+      <c r="E42" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G42" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H42" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I42" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="C42" s="9"/>
-      <c r="D42" s="9"/>
-      <c r="E42" s="9"/>
-      <c r="F42" s="9" t="s">
+      <c r="J42" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K42" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L42" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M42" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="G42" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="I42" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J42" s="9" t="s">
+      <c r="N42" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O42" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P42" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q42" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R42" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S42" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="K42" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L42" s="12" t="n">
-        <v>447.13</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O42" s="12" t="n">
-        <v>433.06</v>
-      </c>
-      <c r="P42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="13" t="n">
-        <v>0.0219</v>
-      </c>
-      <c r="R42" s="12" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" s="14" t="s">
+      <c r="T42" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="U42" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V42" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="W42" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X42" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y42" s="12" t="n">
-        <v>14.07</v>
-      </c>
-      <c r="Z42" s="12" t="n">
-        <v>433.06</v>
-      </c>
-      <c r="AA42" s="12" t="n">
-        <v>30.31</v>
-      </c>
-      <c r="AB42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO42" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV42" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW42" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX42" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY42" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ42" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA42" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB42" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC42" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD42" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE42" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF42" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG42" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH42" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI42" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ42" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="BK42" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL42" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM42" s="16" t="s">
-        <v>79</v>
+      <c r="U42" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V42" s="18" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="8" t="n">
-        <v>307444</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="9"/>
-      <c r="E43" s="9"/>
-      <c r="F43" s="9" t="s">
+      <c r="A43" s="19" t="n">
+        <v>35</v>
+      </c>
+      <c r="B43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="19" t="n">
+        <v>265</v>
+      </c>
+      <c r="D43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="19" t="n">
+        <v>3623.34</v>
+      </c>
+      <c r="F43" s="19" t="n">
+        <v>121859.18</v>
+      </c>
+      <c r="G43" s="19" t="n">
+        <v>8286.95</v>
+      </c>
+      <c r="H43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="19" t="n">
+        <v>328.83</v>
+      </c>
+      <c r="K43" s="19" t="n">
+        <v>126224.22</v>
+      </c>
+      <c r="L43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="20" t="n">
+        <v>6.143688</v>
+      </c>
+      <c r="S43" s="19" t="n">
+        <v>122335.88</v>
+      </c>
+      <c r="T43" s="19" t="n">
+        <v>126224.22</v>
+      </c>
+      <c r="U43" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E44" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F44" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G44" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I44" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J44" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="L44" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="G43" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="K43" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L43" s="12" t="n">
-        <v>24671.51</v>
-      </c>
-      <c r="M43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="O43" s="12" t="n">
-        <v>23273.18</v>
-      </c>
-      <c r="P43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="13" t="n">
-        <v>3.54421</v>
-      </c>
-      <c r="R43" s="12" t="n">
-        <v>399.29</v>
-      </c>
-      <c r="S43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" s="14" t="s">
+      <c r="M44" s="18" t="s">
         <v>254</v>
-      </c>
-      <c r="U43" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V43" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="W43" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X43" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y43" s="12" t="n">
-        <v>1398.33</v>
-      </c>
-      <c r="Z43" s="12" t="n">
-        <v>23273.18</v>
-      </c>
-      <c r="AA43" s="12" t="n">
-        <v>1629.14</v>
-      </c>
-      <c r="AB43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO43" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV43" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW43" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX43" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY43" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ43" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA43" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB43" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC43" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD43" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE43" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF43" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG43" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH43" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI43" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ43" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="BK43" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL43" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM43" s="16" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="8" t="n">
-        <v>307462</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="C44" s="9"/>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="G44" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="I44" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J44" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="K44" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <v>319.81</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O44" s="12" t="n">
-        <v>291.4</v>
-      </c>
-      <c r="P44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="13" t="n">
-        <v>0.002146</v>
-      </c>
-      <c r="R44" s="12" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="S44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="U44" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V44" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="W44" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X44" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y44" s="12" t="n">
-        <v>28.41</v>
-      </c>
-      <c r="Z44" s="12" t="n">
-        <v>291.4</v>
-      </c>
-      <c r="AA44" s="12" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="AB44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO44" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV44" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW44" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX44" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY44" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ44" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA44" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB44" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC44" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD44" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE44" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF44" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG44" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH44" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI44" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ44" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="BK44" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL44" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM44" s="16" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="8" t="n">
-        <v>307465</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="C45" s="9"/>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="K45" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L45" s="12" t="n">
-        <v>1140.3</v>
-      </c>
-      <c r="M45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" s="12" t="n">
-        <v>1039</v>
-      </c>
-      <c r="P45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="13" t="n">
-        <v>0.00479</v>
-      </c>
-      <c r="R45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="U45" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V45" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="W45" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X45" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y45" s="12" t="n">
-        <v>101.3</v>
-      </c>
-      <c r="Z45" s="12" t="n">
-        <v>1039</v>
-      </c>
-      <c r="AA45" s="12" t="n">
-        <v>72.73</v>
-      </c>
-      <c r="AB45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" s="12" t="n">
-        <v>242.33</v>
-      </c>
-      <c r="AE45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO45" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV45" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW45" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX45" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY45" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ45" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA45" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB45" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC45" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD45" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE45" s="14" t="s">
-        <v>264</v>
-      </c>
-      <c r="BF45" s="9" t="s">
-        <v>265</v>
-      </c>
-      <c r="BG45" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="BH45" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="BI45" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="BJ45" s="9" t="s">
-        <v>267</v>
-      </c>
-      <c r="BK45" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="BL45" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM45" s="16" t="s">
-        <v>79</v>
+      <c r="A45" s="19" t="n">
+        <v>796.71</v>
+      </c>
+      <c r="B45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="19" t="n">
+        <v>49.43</v>
+      </c>
+      <c r="E45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="8" t="n">
-        <v>307471</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="C46" s="9"/>
-      <c r="D46" s="9"/>
-      <c r="E46" s="9"/>
-      <c r="F46" s="9" t="s">
-        <v>270</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>131</v>
-      </c>
-      <c r="H46" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="I46" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>271</v>
-      </c>
-      <c r="K46" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L46" s="12" t="n">
-        <v>7460</v>
-      </c>
-      <c r="M46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O46" s="12" t="n">
-        <v>7460</v>
-      </c>
-      <c r="P46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="13" t="n">
-        <v>0.16454</v>
-      </c>
-      <c r="R46" s="12" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="S46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="U46" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V46" s="12" t="n">
-        <v>60</v>
-      </c>
-      <c r="W46" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X46" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="Y46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="12" t="n">
-        <v>7460</v>
-      </c>
-      <c r="AA46" s="12" t="n">
-        <v>895.2</v>
-      </c>
-      <c r="AB46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO46" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV46" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW46" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX46" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY46" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ46" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA46" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB46" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC46" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD46" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE46" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BF46" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BG46" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BH46" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BI46" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="BJ46" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="BK46" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BL46" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM46" s="16" t="s">
-        <v>79</v>
-      </c>
+      <c r="A46" s="4"/>
     </row>
-    <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="8" t="n">
-        <v>307502</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>274</v>
-      </c>
-      <c r="C47" s="9"/>
-      <c r="D47" s="9"/>
-      <c r="E47" s="9"/>
-      <c r="F47" s="9" t="s">
-        <v>275</v>
-      </c>
-      <c r="G47" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="I47" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="K47" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="L47" s="12" t="n">
-        <v>30247.3</v>
-      </c>
-      <c r="M47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="O47" s="12" t="n">
-        <v>27226.44</v>
-      </c>
-      <c r="P47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="13" t="n">
-        <v>0.01332</v>
-      </c>
-      <c r="R47" s="12" t="n">
-        <v>8.64</v>
-      </c>
-      <c r="S47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="U47" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V47" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="W47" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="X47" s="9" t="s">
-        <v>276</v>
-      </c>
-      <c r="Y47" s="12" t="n">
-        <v>3020.86</v>
-      </c>
-      <c r="Z47" s="12" t="n">
-        <v>27226.44</v>
-      </c>
-      <c r="AA47" s="12" t="n">
-        <v>1880.05</v>
-      </c>
-      <c r="AB47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="12" t="n">
-        <v>610.6</v>
-      </c>
-      <c r="AE47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AI47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AN47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AO47" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AP47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AR47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AS47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AT47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AU47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AV47" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="AW47" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="AX47" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="AY47" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ47" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BA47" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BB47" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BC47" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BD47" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="BE47" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="BF47" s="9" t="s">
-        <v>279</v>
-      </c>
-      <c r="BG47" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="BH47" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="BI47" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="BJ47" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="BK47" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="BL47" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="BM47" s="16" t="s">
-        <v>79</v>
-      </c>
+    <row r="47" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="21"/>
+      <c r="H47" s="21"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="21"/>
+      <c r="K47" s="21"/>
+      <c r="L47" s="21"/>
+      <c r="M47" s="21"/>
+      <c r="N47" s="21"/>
+      <c r="O47" s="21"/>
+      <c r="P47" s="21"/>
+      <c r="Q47" s="21"/>
+      <c r="R47" s="21"/>
+      <c r="S47" s="21"/>
+      <c r="T47" s="21"/>
+      <c r="U47" s="21"/>
+      <c r="V47" s="21"/>
+      <c r="W47" s="21"/>
+      <c r="X47" s="21"/>
+      <c r="Y47" s="21"/>
+      <c r="Z47" s="21"/>
+      <c r="AA47" s="21"/>
+      <c r="AB47" s="21"/>
+      <c r="AC47" s="21"/>
+      <c r="AD47" s="21"/>
+      <c r="AE47" s="21"/>
+      <c r="AF47" s="21"/>
+      <c r="AG47" s="21"/>
+      <c r="AH47" s="21"/>
+      <c r="AI47" s="21"/>
+      <c r="AJ47" s="21"/>
+      <c r="AK47" s="21"/>
+      <c r="AL47" s="21"/>
+      <c r="AM47" s="21"/>
+      <c r="AN47" s="21"/>
+      <c r="AO47" s="21"/>
+      <c r="AP47" s="21"/>
+      <c r="AQ47" s="21"/>
+      <c r="AR47" s="21"/>
+      <c r="AS47" s="21"/>
+      <c r="AT47" s="21"/>
+      <c r="AU47" s="21"/>
+      <c r="AV47" s="21"/>
+      <c r="AW47" s="21"/>
+      <c r="AX47" s="21"/>
+      <c r="AY47" s="21"/>
+      <c r="AZ47" s="21"/>
+      <c r="BA47" s="21"/>
+      <c r="BB47" s="21"/>
+      <c r="BC47" s="21"/>
+      <c r="BD47" s="21"/>
+      <c r="BE47" s="21"/>
+      <c r="BF47" s="21"/>
+      <c r="BG47" s="21"/>
+      <c r="BH47" s="21"/>
+      <c r="BI47" s="21"/>
+      <c r="BJ47" s="21"/>
+      <c r="BK47" s="21"/>
+      <c r="BL47" s="21"/>
+      <c r="BM47" s="21"/>
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4"/>
+      <c r="A48" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="4"/>
+      <c r="I48" s="4"/>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4"/>
+      <c r="V48" s="4"/>
+      <c r="W48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="4"/>
+      <c r="AB48" s="4"/>
+      <c r="AC48" s="4"/>
+      <c r="AD48" s="4"/>
+      <c r="AE48" s="4"/>
+      <c r="AF48" s="4"/>
+      <c r="AG48" s="4"/>
+      <c r="AH48" s="4"/>
+      <c r="AI48" s="4"/>
+      <c r="AJ48" s="4"/>
+      <c r="AK48" s="4"/>
+      <c r="AL48" s="4"/>
+      <c r="AM48" s="4"/>
+      <c r="AN48" s="4"/>
+      <c r="AO48" s="4"/>
+      <c r="AP48" s="4"/>
+      <c r="AQ48" s="4"/>
+      <c r="AR48" s="4"/>
+      <c r="AS48" s="4"/>
+      <c r="AT48" s="4"/>
+      <c r="AU48" s="4"/>
+      <c r="AV48" s="4"/>
+      <c r="AW48" s="4"/>
+      <c r="AX48" s="4"/>
+      <c r="AY48" s="4"/>
+      <c r="AZ48" s="4"/>
+      <c r="BA48" s="4"/>
+      <c r="BB48" s="4"/>
+      <c r="BC48" s="4"/>
+      <c r="BD48" s="4"/>
+      <c r="BE48" s="4"/>
+      <c r="BF48" s="4"/>
+      <c r="BG48" s="4"/>
+      <c r="BH48" s="4"/>
+      <c r="BI48" s="4"/>
+      <c r="BJ48" s="4"/>
+      <c r="BK48" s="4"/>
+      <c r="BL48" s="4"/>
+      <c r="BM48" s="4"/>
     </row>
-    <row r="49" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-      <c r="H49" s="17"/>
-      <c r="I49" s="17"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
-      <c r="T49" s="17"/>
-      <c r="U49" s="17"/>
-      <c r="V49" s="17"/>
+    <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B49" s="4"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
+      <c r="G49" s="4"/>
+      <c r="H49" s="4"/>
+      <c r="I49" s="4"/>
+      <c r="J49" s="4"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4"/>
+      <c r="V49" s="4"/>
+      <c r="W49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="4"/>
+      <c r="AB49" s="4"/>
+      <c r="AC49" s="4"/>
+      <c r="AD49" s="4"/>
+      <c r="AE49" s="4"/>
+      <c r="AF49" s="4"/>
+      <c r="AG49" s="4"/>
+      <c r="AH49" s="4"/>
+      <c r="AI49" s="4"/>
+      <c r="AJ49" s="4"/>
+      <c r="AK49" s="4"/>
+      <c r="AL49" s="4"/>
+      <c r="AM49" s="4"/>
+      <c r="AN49" s="4"/>
+      <c r="AO49" s="4"/>
+      <c r="AP49" s="4"/>
+      <c r="AQ49" s="4"/>
+      <c r="AR49" s="4"/>
+      <c r="AS49" s="4"/>
+      <c r="AT49" s="4"/>
+      <c r="AU49" s="4"/>
+      <c r="AV49" s="4"/>
+      <c r="AW49" s="4"/>
+      <c r="AX49" s="4"/>
+      <c r="AY49" s="4"/>
+      <c r="AZ49" s="4"/>
+      <c r="BA49" s="4"/>
+      <c r="BB49" s="4"/>
+      <c r="BC49" s="4"/>
+      <c r="BD49" s="4"/>
+      <c r="BE49" s="4"/>
+      <c r="BF49" s="4"/>
+      <c r="BG49" s="4"/>
+      <c r="BH49" s="4"/>
+      <c r="BI49" s="4"/>
+      <c r="BJ49" s="4"/>
+      <c r="BK49" s="4"/>
+      <c r="BL49" s="4"/>
+      <c r="BM49" s="4"/>
     </row>
-    <row r="50" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="18" t="s">
-        <v>284</v>
-      </c>
-      <c r="B50" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>285</v>
-      </c>
-      <c r="E50" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F50" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G50" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H50" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I50" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="J50" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K50" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L50" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M50" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="N50" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O50" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P50" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q50" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R50" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S50" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="T50" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="U50" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V50" s="18" t="s">
-        <v>37</v>
-      </c>
+    <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B50" s="4"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="4"/>
+      <c r="H50" s="4"/>
+      <c r="I50" s="4"/>
+      <c r="J50" s="4"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4"/>
+      <c r="V50" s="4"/>
+      <c r="W50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="4"/>
+      <c r="AB50" s="4"/>
+      <c r="AC50" s="4"/>
+      <c r="AD50" s="4"/>
+      <c r="AE50" s="4"/>
+      <c r="AF50" s="4"/>
+      <c r="AG50" s="4"/>
+      <c r="AH50" s="4"/>
+      <c r="AI50" s="4"/>
+      <c r="AJ50" s="4"/>
+      <c r="AK50" s="4"/>
+      <c r="AL50" s="4"/>
+      <c r="AM50" s="4"/>
+      <c r="AN50" s="4"/>
+      <c r="AO50" s="4"/>
+      <c r="AP50" s="4"/>
+      <c r="AQ50" s="4"/>
+      <c r="AR50" s="4"/>
+      <c r="AS50" s="4"/>
+      <c r="AT50" s="4"/>
+      <c r="AU50" s="4"/>
+      <c r="AV50" s="4"/>
+      <c r="AW50" s="4"/>
+      <c r="AX50" s="4"/>
+      <c r="AY50" s="4"/>
+      <c r="AZ50" s="4"/>
+      <c r="BA50" s="4"/>
+      <c r="BB50" s="4"/>
+      <c r="BC50" s="4"/>
+      <c r="BD50" s="4"/>
+      <c r="BE50" s="4"/>
+      <c r="BF50" s="4"/>
+      <c r="BG50" s="4"/>
+      <c r="BH50" s="4"/>
+      <c r="BI50" s="4"/>
+      <c r="BJ50" s="4"/>
+      <c r="BK50" s="4"/>
+      <c r="BL50" s="4"/>
+      <c r="BM50" s="4"/>
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="19" t="n">
-        <v>43</v>
-      </c>
-      <c r="B51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C51" s="19" t="n">
-        <v>265</v>
-      </c>
-      <c r="D51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="19" t="n">
-        <v>8561.73</v>
-      </c>
-      <c r="F51" s="19" t="n">
-        <v>294627.35</v>
-      </c>
-      <c r="G51" s="19" t="n">
-        <v>19487.25</v>
-      </c>
-      <c r="H51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="19" t="n">
-        <v>939.43</v>
-      </c>
-      <c r="K51" s="19" t="n">
-        <v>304767.36</v>
-      </c>
-      <c r="L51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" s="20" t="n">
-        <v>8.554614</v>
-      </c>
-      <c r="S51" s="19" t="n">
-        <v>295940.63</v>
-      </c>
-      <c r="T51" s="19" t="n">
-        <v>304767.36</v>
-      </c>
-      <c r="U51" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A51" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B51" s="4"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="4"/>
+      <c r="G51" s="4"/>
+      <c r="H51" s="4"/>
+      <c r="I51" s="4"/>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4"/>
+      <c r="V51" s="4"/>
+      <c r="W51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="4"/>
+      <c r="AB51" s="4"/>
+      <c r="AC51" s="4"/>
+      <c r="AD51" s="4"/>
+      <c r="AE51" s="4"/>
+      <c r="AF51" s="4"/>
+      <c r="AG51" s="4"/>
+      <c r="AH51" s="4"/>
+      <c r="AI51" s="4"/>
+      <c r="AJ51" s="4"/>
+      <c r="AK51" s="4"/>
+      <c r="AL51" s="4"/>
+      <c r="AM51" s="4"/>
+      <c r="AN51" s="4"/>
+      <c r="AO51" s="4"/>
+      <c r="AP51" s="4"/>
+      <c r="AQ51" s="4"/>
+      <c r="AR51" s="4"/>
+      <c r="AS51" s="4"/>
+      <c r="AT51" s="4"/>
+      <c r="AU51" s="4"/>
+      <c r="AV51" s="4"/>
+      <c r="AW51" s="4"/>
+      <c r="AX51" s="4"/>
+      <c r="AY51" s="4"/>
+      <c r="AZ51" s="4"/>
+      <c r="BA51" s="4"/>
+      <c r="BB51" s="4"/>
+      <c r="BC51" s="4"/>
+      <c r="BD51" s="4"/>
+      <c r="BE51" s="4"/>
+      <c r="BF51" s="4"/>
+      <c r="BG51" s="4"/>
+      <c r="BH51" s="4"/>
+      <c r="BI51" s="4"/>
+      <c r="BJ51" s="4"/>
+      <c r="BK51" s="4"/>
+      <c r="BL51" s="4"/>
+      <c r="BM51" s="4"/>
     </row>
-    <row r="52" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B52" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C52" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D52" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E52" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F52" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G52" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H52" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I52" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J52" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K52" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="L52" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="M52" s="18" t="s">
-        <v>292</v>
-      </c>
+    <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="4"/>
+      <c r="F52" s="4"/>
+      <c r="G52" s="4"/>
+      <c r="H52" s="4"/>
+      <c r="I52" s="4"/>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4"/>
+      <c r="V52" s="4"/>
+      <c r="W52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="4"/>
+      <c r="AB52" s="4"/>
+      <c r="AC52" s="4"/>
+      <c r="AD52" s="4"/>
+      <c r="AE52" s="4"/>
+      <c r="AF52" s="4"/>
+      <c r="AG52" s="4"/>
+      <c r="AH52" s="4"/>
+      <c r="AI52" s="4"/>
+      <c r="AJ52" s="4"/>
+      <c r="AK52" s="4"/>
+      <c r="AL52" s="4"/>
+      <c r="AM52" s="4"/>
+      <c r="AN52" s="4"/>
+      <c r="AO52" s="4"/>
+      <c r="AP52" s="4"/>
+      <c r="AQ52" s="4"/>
+      <c r="AR52" s="4"/>
+      <c r="AS52" s="4"/>
+      <c r="AT52" s="4"/>
+      <c r="AU52" s="4"/>
+      <c r="AV52" s="4"/>
+      <c r="AW52" s="4"/>
+      <c r="AX52" s="4"/>
+      <c r="AY52" s="4"/>
+      <c r="AZ52" s="4"/>
+      <c r="BA52" s="4"/>
+      <c r="BB52" s="4"/>
+      <c r="BC52" s="4"/>
+      <c r="BD52" s="4"/>
+      <c r="BE52" s="4"/>
+      <c r="BF52" s="4"/>
+      <c r="BG52" s="4"/>
+      <c r="BH52" s="4"/>
+      <c r="BI52" s="4"/>
+      <c r="BJ52" s="4"/>
+      <c r="BK52" s="4"/>
+      <c r="BL52" s="4"/>
+      <c r="BM52" s="4"/>
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="19" t="n">
-        <v>1411.31</v>
-      </c>
-      <c r="B53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="19" t="n">
-        <v>57.94</v>
-      </c>
-      <c r="E53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="19" t="n">
-        <v>0</v>
-      </c>
+      <c r="A53" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="4"/>
+      <c r="I53" s="4"/>
+      <c r="J53" s="4"/>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4"/>
+      <c r="V53" s="4"/>
+      <c r="W53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="4"/>
+      <c r="AB53" s="4"/>
+      <c r="AC53" s="4"/>
+      <c r="AD53" s="4"/>
+      <c r="AE53" s="4"/>
+      <c r="AF53" s="4"/>
+      <c r="AG53" s="4"/>
+      <c r="AH53" s="4"/>
+      <c r="AI53" s="4"/>
+      <c r="AJ53" s="4"/>
+      <c r="AK53" s="4"/>
+      <c r="AL53" s="4"/>
+      <c r="AM53" s="4"/>
+      <c r="AN53" s="4"/>
+      <c r="AO53" s="4"/>
+      <c r="AP53" s="4"/>
+      <c r="AQ53" s="4"/>
+      <c r="AR53" s="4"/>
+      <c r="AS53" s="4"/>
+      <c r="AT53" s="4"/>
+      <c r="AU53" s="4"/>
+      <c r="AV53" s="4"/>
+      <c r="AW53" s="4"/>
+      <c r="AX53" s="4"/>
+      <c r="AY53" s="4"/>
+      <c r="AZ53" s="4"/>
+      <c r="BA53" s="4"/>
+      <c r="BB53" s="4"/>
+      <c r="BC53" s="4"/>
+      <c r="BD53" s="4"/>
+      <c r="BE53" s="4"/>
+      <c r="BF53" s="4"/>
+      <c r="BG53" s="4"/>
+      <c r="BH53" s="4"/>
+      <c r="BI53" s="4"/>
+      <c r="BJ53" s="4"/>
+      <c r="BK53" s="4"/>
+      <c r="BL53" s="4"/>
+      <c r="BM53" s="4"/>
     </row>
     <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4"/>
+      <c r="A54" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="4"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="4"/>
+      <c r="I54" s="4"/>
+      <c r="J54" s="4"/>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4"/>
+      <c r="V54" s="4"/>
+      <c r="W54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="4"/>
+      <c r="AB54" s="4"/>
+      <c r="AC54" s="4"/>
+      <c r="AD54" s="4"/>
+      <c r="AE54" s="4"/>
+      <c r="AF54" s="4"/>
+      <c r="AG54" s="4"/>
+      <c r="AH54" s="4"/>
+      <c r="AI54" s="4"/>
+      <c r="AJ54" s="4"/>
+      <c r="AK54" s="4"/>
+      <c r="AL54" s="4"/>
+      <c r="AM54" s="4"/>
+      <c r="AN54" s="4"/>
+      <c r="AO54" s="4"/>
+      <c r="AP54" s="4"/>
+      <c r="AQ54" s="4"/>
+      <c r="AR54" s="4"/>
+      <c r="AS54" s="4"/>
+      <c r="AT54" s="4"/>
+      <c r="AU54" s="4"/>
+      <c r="AV54" s="4"/>
+      <c r="AW54" s="4"/>
+      <c r="AX54" s="4"/>
+      <c r="AY54" s="4"/>
+      <c r="AZ54" s="4"/>
+      <c r="BA54" s="4"/>
+      <c r="BB54" s="4"/>
+      <c r="BC54" s="4"/>
+      <c r="BD54" s="4"/>
+      <c r="BE54" s="4"/>
+      <c r="BF54" s="4"/>
+      <c r="BG54" s="4"/>
+      <c r="BH54" s="4"/>
+      <c r="BI54" s="4"/>
+      <c r="BJ54" s="4"/>
+      <c r="BK54" s="4"/>
+      <c r="BL54" s="4"/>
+      <c r="BM54" s="4"/>
     </row>
-    <row r="55" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="B55" s="21"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
-      <c r="G55" s="21"/>
-      <c r="H55" s="21"/>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21"/>
-      <c r="K55" s="21"/>
-      <c r="L55" s="21"/>
-      <c r="M55" s="21"/>
-      <c r="N55" s="21"/>
-      <c r="O55" s="21"/>
-      <c r="P55" s="21"/>
-      <c r="Q55" s="21"/>
-      <c r="R55" s="21"/>
-      <c r="S55" s="21"/>
-      <c r="T55" s="21"/>
-      <c r="U55" s="21"/>
-      <c r="V55" s="21"/>
-      <c r="W55" s="21"/>
-      <c r="X55" s="21"/>
-      <c r="Y55" s="21"/>
-      <c r="Z55" s="21"/>
-      <c r="AA55" s="21"/>
-      <c r="AB55" s="21"/>
-      <c r="AC55" s="21"/>
-      <c r="AD55" s="21"/>
-      <c r="AE55" s="21"/>
-      <c r="AF55" s="21"/>
-      <c r="AG55" s="21"/>
-      <c r="AH55" s="21"/>
-      <c r="AI55" s="21"/>
-      <c r="AJ55" s="21"/>
-      <c r="AK55" s="21"/>
-      <c r="AL55" s="21"/>
-      <c r="AM55" s="21"/>
-      <c r="AN55" s="21"/>
-      <c r="AO55" s="21"/>
-      <c r="AP55" s="21"/>
-      <c r="AQ55" s="21"/>
-      <c r="AR55" s="21"/>
-      <c r="AS55" s="21"/>
-      <c r="AT55" s="21"/>
-      <c r="AU55" s="21"/>
-      <c r="AV55" s="21"/>
-      <c r="AW55" s="21"/>
-      <c r="AX55" s="21"/>
-      <c r="AY55" s="21"/>
-      <c r="AZ55" s="21"/>
-      <c r="BA55" s="21"/>
-      <c r="BB55" s="21"/>
-      <c r="BC55" s="21"/>
-      <c r="BD55" s="21"/>
-      <c r="BE55" s="21"/>
-      <c r="BF55" s="21"/>
-      <c r="BG55" s="21"/>
-      <c r="BH55" s="21"/>
-      <c r="BI55" s="21"/>
-      <c r="BJ55" s="21"/>
-      <c r="BK55" s="21"/>
-      <c r="BL55" s="21"/>
-      <c r="BM55" s="21"/>
+    <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="4"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="4"/>
+      <c r="I55" s="4"/>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+      <c r="V55" s="4"/>
+      <c r="W55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="4"/>
+      <c r="AB55" s="4"/>
+      <c r="AC55" s="4"/>
+      <c r="AD55" s="4"/>
+      <c r="AE55" s="4"/>
+      <c r="AF55" s="4"/>
+      <c r="AG55" s="4"/>
+      <c r="AH55" s="4"/>
+      <c r="AI55" s="4"/>
+      <c r="AJ55" s="4"/>
+      <c r="AK55" s="4"/>
+      <c r="AL55" s="4"/>
+      <c r="AM55" s="4"/>
+      <c r="AN55" s="4"/>
+      <c r="AO55" s="4"/>
+      <c r="AP55" s="4"/>
+      <c r="AQ55" s="4"/>
+      <c r="AR55" s="4"/>
+      <c r="AS55" s="4"/>
+      <c r="AT55" s="4"/>
+      <c r="AU55" s="4"/>
+      <c r="AV55" s="4"/>
+      <c r="AW55" s="4"/>
+      <c r="AX55" s="4"/>
+      <c r="AY55" s="4"/>
+      <c r="AZ55" s="4"/>
+      <c r="BA55" s="4"/>
+      <c r="BB55" s="4"/>
+      <c r="BC55" s="4"/>
+      <c r="BD55" s="4"/>
+      <c r="BE55" s="4"/>
+      <c r="BF55" s="4"/>
+      <c r="BG55" s="4"/>
+      <c r="BH55" s="4"/>
+      <c r="BI55" s="4"/>
+      <c r="BJ55" s="4"/>
+      <c r="BK55" s="4"/>
+      <c r="BL55" s="4"/>
+      <c r="BM55" s="4"/>
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="4" t="s">
-        <v>75</v>
+        <v>262</v>
       </c>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -26087,7 +24997,7 @@
     </row>
     <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="4" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -26154,560 +25064,8 @@
       <c r="BL57" s="4"/>
       <c r="BM57" s="4"/>
     </row>
-    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="4"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4"/>
-      <c r="U58" s="4"/>
-      <c r="V58" s="4"/>
-      <c r="W58" s="4"/>
-      <c r="X58" s="4"/>
-      <c r="Y58" s="4"/>
-      <c r="Z58" s="4"/>
-      <c r="AA58" s="4"/>
-      <c r="AB58" s="4"/>
-      <c r="AC58" s="4"/>
-      <c r="AD58" s="4"/>
-      <c r="AE58" s="4"/>
-      <c r="AF58" s="4"/>
-      <c r="AG58" s="4"/>
-      <c r="AH58" s="4"/>
-      <c r="AI58" s="4"/>
-      <c r="AJ58" s="4"/>
-      <c r="AK58" s="4"/>
-      <c r="AL58" s="4"/>
-      <c r="AM58" s="4"/>
-      <c r="AN58" s="4"/>
-      <c r="AO58" s="4"/>
-      <c r="AP58" s="4"/>
-      <c r="AQ58" s="4"/>
-      <c r="AR58" s="4"/>
-      <c r="AS58" s="4"/>
-      <c r="AT58" s="4"/>
-      <c r="AU58" s="4"/>
-      <c r="AV58" s="4"/>
-      <c r="AW58" s="4"/>
-      <c r="AX58" s="4"/>
-      <c r="AY58" s="4"/>
-      <c r="AZ58" s="4"/>
-      <c r="BA58" s="4"/>
-      <c r="BB58" s="4"/>
-      <c r="BC58" s="4"/>
-      <c r="BD58" s="4"/>
-      <c r="BE58" s="4"/>
-      <c r="BF58" s="4"/>
-      <c r="BG58" s="4"/>
-      <c r="BH58" s="4"/>
-      <c r="BI58" s="4"/>
-      <c r="BJ58" s="4"/>
-      <c r="BK58" s="4"/>
-      <c r="BL58" s="4"/>
-      <c r="BM58" s="4"/>
-    </row>
-    <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="4"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="4"/>
-      <c r="S59" s="4"/>
-      <c r="T59" s="4"/>
-      <c r="U59" s="4"/>
-      <c r="V59" s="4"/>
-      <c r="W59" s="4"/>
-      <c r="X59" s="4"/>
-      <c r="Y59" s="4"/>
-      <c r="Z59" s="4"/>
-      <c r="AA59" s="4"/>
-      <c r="AB59" s="4"/>
-      <c r="AC59" s="4"/>
-      <c r="AD59" s="4"/>
-      <c r="AE59" s="4"/>
-      <c r="AF59" s="4"/>
-      <c r="AG59" s="4"/>
-      <c r="AH59" s="4"/>
-      <c r="AI59" s="4"/>
-      <c r="AJ59" s="4"/>
-      <c r="AK59" s="4"/>
-      <c r="AL59" s="4"/>
-      <c r="AM59" s="4"/>
-      <c r="AN59" s="4"/>
-      <c r="AO59" s="4"/>
-      <c r="AP59" s="4"/>
-      <c r="AQ59" s="4"/>
-      <c r="AR59" s="4"/>
-      <c r="AS59" s="4"/>
-      <c r="AT59" s="4"/>
-      <c r="AU59" s="4"/>
-      <c r="AV59" s="4"/>
-      <c r="AW59" s="4"/>
-      <c r="AX59" s="4"/>
-      <c r="AY59" s="4"/>
-      <c r="AZ59" s="4"/>
-      <c r="BA59" s="4"/>
-      <c r="BB59" s="4"/>
-      <c r="BC59" s="4"/>
-      <c r="BD59" s="4"/>
-      <c r="BE59" s="4"/>
-      <c r="BF59" s="4"/>
-      <c r="BG59" s="4"/>
-      <c r="BH59" s="4"/>
-      <c r="BI59" s="4"/>
-      <c r="BJ59" s="4"/>
-      <c r="BK59" s="4"/>
-      <c r="BL59" s="4"/>
-      <c r="BM59" s="4"/>
-    </row>
-    <row r="60" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="4"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4"/>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
-      <c r="T60" s="4"/>
-      <c r="U60" s="4"/>
-      <c r="V60" s="4"/>
-      <c r="W60" s="4"/>
-      <c r="X60" s="4"/>
-      <c r="Y60" s="4"/>
-      <c r="Z60" s="4"/>
-      <c r="AA60" s="4"/>
-      <c r="AB60" s="4"/>
-      <c r="AC60" s="4"/>
-      <c r="AD60" s="4"/>
-      <c r="AE60" s="4"/>
-      <c r="AF60" s="4"/>
-      <c r="AG60" s="4"/>
-      <c r="AH60" s="4"/>
-      <c r="AI60" s="4"/>
-      <c r="AJ60" s="4"/>
-      <c r="AK60" s="4"/>
-      <c r="AL60" s="4"/>
-      <c r="AM60" s="4"/>
-      <c r="AN60" s="4"/>
-      <c r="AO60" s="4"/>
-      <c r="AP60" s="4"/>
-      <c r="AQ60" s="4"/>
-      <c r="AR60" s="4"/>
-      <c r="AS60" s="4"/>
-      <c r="AT60" s="4"/>
-      <c r="AU60" s="4"/>
-      <c r="AV60" s="4"/>
-      <c r="AW60" s="4"/>
-      <c r="AX60" s="4"/>
-      <c r="AY60" s="4"/>
-      <c r="AZ60" s="4"/>
-      <c r="BA60" s="4"/>
-      <c r="BB60" s="4"/>
-      <c r="BC60" s="4"/>
-      <c r="BD60" s="4"/>
-      <c r="BE60" s="4"/>
-      <c r="BF60" s="4"/>
-      <c r="BG60" s="4"/>
-      <c r="BH60" s="4"/>
-      <c r="BI60" s="4"/>
-      <c r="BJ60" s="4"/>
-      <c r="BK60" s="4"/>
-      <c r="BL60" s="4"/>
-      <c r="BM60" s="4"/>
-    </row>
-    <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B61" s="4"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="4"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="4"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4"/>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
-      <c r="V61" s="4"/>
-      <c r="W61" s="4"/>
-      <c r="X61" s="4"/>
-      <c r="Y61" s="4"/>
-      <c r="Z61" s="4"/>
-      <c r="AA61" s="4"/>
-      <c r="AB61" s="4"/>
-      <c r="AC61" s="4"/>
-      <c r="AD61" s="4"/>
-      <c r="AE61" s="4"/>
-      <c r="AF61" s="4"/>
-      <c r="AG61" s="4"/>
-      <c r="AH61" s="4"/>
-      <c r="AI61" s="4"/>
-      <c r="AJ61" s="4"/>
-      <c r="AK61" s="4"/>
-      <c r="AL61" s="4"/>
-      <c r="AM61" s="4"/>
-      <c r="AN61" s="4"/>
-      <c r="AO61" s="4"/>
-      <c r="AP61" s="4"/>
-      <c r="AQ61" s="4"/>
-      <c r="AR61" s="4"/>
-      <c r="AS61" s="4"/>
-      <c r="AT61" s="4"/>
-      <c r="AU61" s="4"/>
-      <c r="AV61" s="4"/>
-      <c r="AW61" s="4"/>
-      <c r="AX61" s="4"/>
-      <c r="AY61" s="4"/>
-      <c r="AZ61" s="4"/>
-      <c r="BA61" s="4"/>
-      <c r="BB61" s="4"/>
-      <c r="BC61" s="4"/>
-      <c r="BD61" s="4"/>
-      <c r="BE61" s="4"/>
-      <c r="BF61" s="4"/>
-      <c r="BG61" s="4"/>
-      <c r="BH61" s="4"/>
-      <c r="BI61" s="4"/>
-      <c r="BJ61" s="4"/>
-      <c r="BK61" s="4"/>
-      <c r="BL61" s="4"/>
-      <c r="BM61" s="4"/>
-    </row>
-    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B62" s="4"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="4"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="4"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="4"/>
-      <c r="T62" s="4"/>
-      <c r="U62" s="4"/>
-      <c r="V62" s="4"/>
-      <c r="W62" s="4"/>
-      <c r="X62" s="4"/>
-      <c r="Y62" s="4"/>
-      <c r="Z62" s="4"/>
-      <c r="AA62" s="4"/>
-      <c r="AB62" s="4"/>
-      <c r="AC62" s="4"/>
-      <c r="AD62" s="4"/>
-      <c r="AE62" s="4"/>
-      <c r="AF62" s="4"/>
-      <c r="AG62" s="4"/>
-      <c r="AH62" s="4"/>
-      <c r="AI62" s="4"/>
-      <c r="AJ62" s="4"/>
-      <c r="AK62" s="4"/>
-      <c r="AL62" s="4"/>
-      <c r="AM62" s="4"/>
-      <c r="AN62" s="4"/>
-      <c r="AO62" s="4"/>
-      <c r="AP62" s="4"/>
-      <c r="AQ62" s="4"/>
-      <c r="AR62" s="4"/>
-      <c r="AS62" s="4"/>
-      <c r="AT62" s="4"/>
-      <c r="AU62" s="4"/>
-      <c r="AV62" s="4"/>
-      <c r="AW62" s="4"/>
-      <c r="AX62" s="4"/>
-      <c r="AY62" s="4"/>
-      <c r="AZ62" s="4"/>
-      <c r="BA62" s="4"/>
-      <c r="BB62" s="4"/>
-      <c r="BC62" s="4"/>
-      <c r="BD62" s="4"/>
-      <c r="BE62" s="4"/>
-      <c r="BF62" s="4"/>
-      <c r="BG62" s="4"/>
-      <c r="BH62" s="4"/>
-      <c r="BI62" s="4"/>
-      <c r="BJ62" s="4"/>
-      <c r="BK62" s="4"/>
-      <c r="BL62" s="4"/>
-      <c r="BM62" s="4"/>
-    </row>
-    <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B63" s="4"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="4"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="4"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4"/>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4"/>
-      <c r="U63" s="4"/>
-      <c r="V63" s="4"/>
-      <c r="W63" s="4"/>
-      <c r="X63" s="4"/>
-      <c r="Y63" s="4"/>
-      <c r="Z63" s="4"/>
-      <c r="AA63" s="4"/>
-      <c r="AB63" s="4"/>
-      <c r="AC63" s="4"/>
-      <c r="AD63" s="4"/>
-      <c r="AE63" s="4"/>
-      <c r="AF63" s="4"/>
-      <c r="AG63" s="4"/>
-      <c r="AH63" s="4"/>
-      <c r="AI63" s="4"/>
-      <c r="AJ63" s="4"/>
-      <c r="AK63" s="4"/>
-      <c r="AL63" s="4"/>
-      <c r="AM63" s="4"/>
-      <c r="AN63" s="4"/>
-      <c r="AO63" s="4"/>
-      <c r="AP63" s="4"/>
-      <c r="AQ63" s="4"/>
-      <c r="AR63" s="4"/>
-      <c r="AS63" s="4"/>
-      <c r="AT63" s="4"/>
-      <c r="AU63" s="4"/>
-      <c r="AV63" s="4"/>
-      <c r="AW63" s="4"/>
-      <c r="AX63" s="4"/>
-      <c r="AY63" s="4"/>
-      <c r="AZ63" s="4"/>
-      <c r="BA63" s="4"/>
-      <c r="BB63" s="4"/>
-      <c r="BC63" s="4"/>
-      <c r="BD63" s="4"/>
-      <c r="BE63" s="4"/>
-      <c r="BF63" s="4"/>
-      <c r="BG63" s="4"/>
-      <c r="BH63" s="4"/>
-      <c r="BI63" s="4"/>
-      <c r="BJ63" s="4"/>
-      <c r="BK63" s="4"/>
-      <c r="BL63" s="4"/>
-      <c r="BM63" s="4"/>
-    </row>
-    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B64" s="4"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="4"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="4"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="4"/>
-      <c r="U64" s="4"/>
-      <c r="V64" s="4"/>
-      <c r="W64" s="4"/>
-      <c r="X64" s="4"/>
-      <c r="Y64" s="4"/>
-      <c r="Z64" s="4"/>
-      <c r="AA64" s="4"/>
-      <c r="AB64" s="4"/>
-      <c r="AC64" s="4"/>
-      <c r="AD64" s="4"/>
-      <c r="AE64" s="4"/>
-      <c r="AF64" s="4"/>
-      <c r="AG64" s="4"/>
-      <c r="AH64" s="4"/>
-      <c r="AI64" s="4"/>
-      <c r="AJ64" s="4"/>
-      <c r="AK64" s="4"/>
-      <c r="AL64" s="4"/>
-      <c r="AM64" s="4"/>
-      <c r="AN64" s="4"/>
-      <c r="AO64" s="4"/>
-      <c r="AP64" s="4"/>
-      <c r="AQ64" s="4"/>
-      <c r="AR64" s="4"/>
-      <c r="AS64" s="4"/>
-      <c r="AT64" s="4"/>
-      <c r="AU64" s="4"/>
-      <c r="AV64" s="4"/>
-      <c r="AW64" s="4"/>
-      <c r="AX64" s="4"/>
-      <c r="AY64" s="4"/>
-      <c r="AZ64" s="4"/>
-      <c r="BA64" s="4"/>
-      <c r="BB64" s="4"/>
-      <c r="BC64" s="4"/>
-      <c r="BD64" s="4"/>
-      <c r="BE64" s="4"/>
-      <c r="BF64" s="4"/>
-      <c r="BG64" s="4"/>
-      <c r="BH64" s="4"/>
-      <c r="BI64" s="4"/>
-      <c r="BJ64" s="4"/>
-      <c r="BK64" s="4"/>
-      <c r="BL64" s="4"/>
-      <c r="BM64" s="4"/>
-    </row>
-    <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B65" s="4"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="4"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="4"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4"/>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4"/>
-      <c r="U65" s="4"/>
-      <c r="V65" s="4"/>
-      <c r="W65" s="4"/>
-      <c r="X65" s="4"/>
-      <c r="Y65" s="4"/>
-      <c r="Z65" s="4"/>
-      <c r="AA65" s="4"/>
-      <c r="AB65" s="4"/>
-      <c r="AC65" s="4"/>
-      <c r="AD65" s="4"/>
-      <c r="AE65" s="4"/>
-      <c r="AF65" s="4"/>
-      <c r="AG65" s="4"/>
-      <c r="AH65" s="4"/>
-      <c r="AI65" s="4"/>
-      <c r="AJ65" s="4"/>
-      <c r="AK65" s="4"/>
-      <c r="AL65" s="4"/>
-      <c r="AM65" s="4"/>
-      <c r="AN65" s="4"/>
-      <c r="AO65" s="4"/>
-      <c r="AP65" s="4"/>
-      <c r="AQ65" s="4"/>
-      <c r="AR65" s="4"/>
-      <c r="AS65" s="4"/>
-      <c r="AT65" s="4"/>
-      <c r="AU65" s="4"/>
-      <c r="AV65" s="4"/>
-      <c r="AW65" s="4"/>
-      <c r="AX65" s="4"/>
-      <c r="AY65" s="4"/>
-      <c r="AZ65" s="4"/>
-      <c r="BA65" s="4"/>
-      <c r="BB65" s="4"/>
-      <c r="BC65" s="4"/>
-      <c r="BD65" s="4"/>
-      <c r="BE65" s="4"/>
-      <c r="BF65" s="4"/>
-      <c r="BG65" s="4"/>
-      <c r="BH65" s="4"/>
-      <c r="BI65" s="4"/>
-      <c r="BJ65" s="4"/>
-      <c r="BK65" s="4"/>
-      <c r="BL65" s="4"/>
-      <c r="BM65" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="59">
+  <mergeCells count="51">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -26747,26 +25105,18 @@
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="B47:E47"/>
-    <mergeCell ref="A49:V49"/>
+    <mergeCell ref="A41:V41"/>
+    <mergeCell ref="A47:BM47"/>
+    <mergeCell ref="A48:BM48"/>
+    <mergeCell ref="A49:BM49"/>
+    <mergeCell ref="A50:BM50"/>
+    <mergeCell ref="A51:BM51"/>
+    <mergeCell ref="A52:BM52"/>
+    <mergeCell ref="A53:BM53"/>
+    <mergeCell ref="A54:BM54"/>
     <mergeCell ref="A55:BM55"/>
     <mergeCell ref="A56:BM56"/>
     <mergeCell ref="A57:BM57"/>
-    <mergeCell ref="A58:BM58"/>
-    <mergeCell ref="A59:BM59"/>
-    <mergeCell ref="A60:BM60"/>
-    <mergeCell ref="A61:BM61"/>
-    <mergeCell ref="A62:BM62"/>
-    <mergeCell ref="A63:BM63"/>
-    <mergeCell ref="A64:BM64"/>
-    <mergeCell ref="A65:BM65"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="307">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 21/05/2026 05:30:34</t>
+    <t xml:space="preserve">Emitido em: 22/05/2026 05:30:31</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -262,499 +262,628 @@
     <t xml:space="preserve">Não</t>
   </si>
   <si>
-    <t xml:space="preserve">7.808 - ABCC -REJUNTABRAS INDUSTRIA E COMERCIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96.533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">788,62</t>
+    <t xml:space="preserve">32.615 - MADELUSTRE INDUSTRIAL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">71.328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">05/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.012,28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260589616460000152550020000713281306751109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.976.319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.756,80</t>
   </si>
   <si>
     <t xml:space="preserve">N</t>
   </si>
   <si>
-    <t xml:space="preserve">2.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260454542238000178550010000965331000963341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">785 - MEBER METAIS S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">316.844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/04/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158,47</t>
+    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.265,79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - FILIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">404,81</t>
   </si>
   <si>
     <t xml:space="preserve">2.949</t>
   </si>
   <si>
-    <t xml:space="preserve">43260487547907000153550050003168441492652194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.615 - MADELUSTRE INDUSTRIAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.012,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260589616460000152550020000713281306751109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.976.319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.756,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
+    <t xml:space="preserve">35260597837181002190550010050804111200730267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804981991793601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.080.412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050804121347149640</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.929,60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829821661840971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.082.996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">461,96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050829961140036509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">638.725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.887,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006387251174884389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.702,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260527254297000178550010000105531584622070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.709,55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260581604803000157550010008671441582155041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">639.745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.078,63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006397451885129080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640.215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.963,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006402151526143499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640.584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.104,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006405841317875822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.318 - CORTAG INDUSTRIA E COMERCIO LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">872.917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.671,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260500808396000521550010008729171646262800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.825,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260581604803000157550010008672241503823847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">641.031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">499,53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006410311154255425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">481,59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050855671736636271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.065 - LUXMUNDO COMERCIO IMPORTACAO EXPORTACAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.783,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.647 - ACCERT TRANSPORTES E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86,50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260529244900000247550010000673361492026159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260505222092001069570010000389411006647635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">758.826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">785,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007588261717357519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">642.487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.040,61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006424871547022207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.167 - ATLAS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.401,84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260589723837000172550000006880631168529645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.101 - SIMON MATERIAIS ELETRICOS E ELETRONICOS LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31260507159430000361550010000876141954082958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.671,51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31260507159430000361550010000876201881086441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.238 - EURO METAIS IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">319,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260510317038000146550010000665871272565371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.015 - FOCO METALLO FABRICACAO E MONTAGEM DE LUMINARIAS E COMERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.140,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.724.082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.618 - ALFA TRANSPORTES EIRELI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">242,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260522670837000180550010000233691542222518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582110818000121570000077240821090348638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.444 - PRIME BRAS SEGURANCA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.460,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260532296669000169550030000014561732534080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.628 - VFL IMPORTADORA E DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.723,65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260505104359000122550010000046771737179198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050855751937497947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050856531939175139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050856541425368248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">643.141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.362,82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006431411980070203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">874.261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.526,29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260500808396000521550010008742611312671522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">643.989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.012,18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006439891906994593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.228 - H. IMPORTS IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.949,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260522091324000204550030000068451624550441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">871.218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.936,45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008712181667035989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">871.209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450,89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008712091653128395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.356 - H. IMPORTS IMPORTACAO E EXPORTACAO EIRELI-EPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.398,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260522091324000115550010000517391644084487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 - TRAMONTINA PLANALTO S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.239,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260500142240000120550010007112461929672564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.765 - PLENA INDUSTRIA E COMERCIO DE ESQUADRIAS DE ALUMINIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.147,58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260510365014000162550010000461591344097371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.599 - KADESH CALCADOS PROFISSIONAIS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337.381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.424,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41260506293564000146550020003373811553217146</t>
   </si>
   <si>
     <t xml:space="preserve">790 - JACKWAL S/A</t>
   </si>
   <si>
-    <t xml:space="preserve">275.196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.834,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260592782366000188550030002751961654432159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.265,79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - FILIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804111200730267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804981991793601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804121347149640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.929,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829821661840971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">461,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829961140036509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">638.725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.887,04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006387251174884389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.702,49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260527254297000178550010000105531584622070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.709,55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260581604803000157550010008671441582155041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.078,63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006397451885129080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">640.215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.963,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006402151526143499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">640.584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.104,02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006405841317875822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.318 - CORTAG INDUSTRIA E COMERCIO LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">872.917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.671,17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260500808396000521550010008729171646262800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.825,13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260581604803000157550010008672241503823847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">641.031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499,53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006410311154255425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.085.567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">481,59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050855671736636271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.065 - LUXMUNDO COMERCIO IMPORTACAO EXPORTACAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.783,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.647 - ACCERT TRANSPORTES E LOGISTICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86,50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29260529244900000247550010000673361492026159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29260505222092001069570010000389411006647635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">785,04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007588261717357519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">642.487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.040,61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006424871547022207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.167 - ATLAS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.401,84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260589723837000172550000006880631168529645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.101 - SIMON MATERIAIS ELETRICOS E ELETRONICOS LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447,13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31260507159430000361550010000876141954082958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.671,51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31260507159430000361550010000876201881086441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.238 - EURO METAIS IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">319,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29260510317038000146550010000665871272565371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.015 - FOCO METALLO FABRICACAO E MONTAGEM DE LUMINARIAS E COMERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.140,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.724.082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.618 - ALFA TRANSPORTES EIRELI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">242,33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260522670837000180550010000233691542222518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582110818000121570000077240821090348638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.444 - PRIME BRAS SEGURANCA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.460,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260532296669000169550030000014561732534080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.628 - VFL IMPORTADORA E DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.723,65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52260505104359000122550010000046771737179198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.085.575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355,13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050855751937497947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.085.653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050856531939175139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.085.654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050856541425368248</t>
+    <t xml:space="preserve">275.511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.175,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260592782366000188550030002755111221903915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.731,40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260510365014000162550010000461611478984370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.048,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260510365014000162550010000461601448464851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">646.182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.225,93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006461821645484146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">646.237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.543,62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006462371024568064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.066,48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260510365014000162550010000461581611112280</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17000,7 +17129,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM57"/>
+  <dimension ref="A1:BM70"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17563,7 +17692,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>305865</v>
+        <v>306769</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>80</v>
@@ -17575,67 +17704,67 @@
         <v>81</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>788.62</v>
+        <v>5012.28</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>788.62</v>
+        <v>4567</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0.258</v>
+        <v>0</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>5</v>
+        <v>40.75</v>
       </c>
       <c r="W6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="Y6" s="12" t="n">
-        <v>0</v>
+        <v>445.28</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>788.62</v>
+        <v>4567</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>55.2</v>
+        <v>319.68</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17701,10 +17830,10 @@
         <v>74</v>
       </c>
       <c r="AW6" s="14" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AX6" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY6" s="14" t="s">
         <v>75</v>
@@ -17740,7 +17869,7 @@
         <v>69</v>
       </c>
       <c r="BJ6" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="BK6" s="9" t="s">
         <v>75</v>
@@ -17754,19 +17883,19 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>306716</v>
+        <v>307020</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="F7" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>91</v>
@@ -17775,13 +17904,13 @@
         <v>92</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>158.47</v>
+        <v>1756.8</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
@@ -17790,28 +17919,28 @@
         <v>1</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>148.8</v>
+        <v>1756.8</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0</v>
+        <v>0.142272</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="W7" s="9" t="s">
         <v>73</v>
@@ -17820,13 +17949,13 @@
         <v>92</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>9.67</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>158.47</v>
+        <v>1756.8</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>11.09</v>
+        <v>122.98</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -17892,10 +18021,10 @@
         <v>74</v>
       </c>
       <c r="AW7" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX7" s="10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="AY7" s="14" t="s">
         <v>75</v>
@@ -17931,7 +18060,7 @@
         <v>69</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -17945,22 +18074,22 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>306769</v>
+        <v>307133</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>99</v>
@@ -17972,25 +18101,25 @@
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>5012.28</v>
+        <v>4265.79</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>4567</v>
+        <v>4222.88</v>
       </c>
       <c r="P8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0</v>
+        <v>0.484131</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>0</v>
+        <v>71.4</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
@@ -18002,22 +18131,22 @@
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>40.75</v>
+        <v>63</v>
       </c>
       <c r="W8" s="9" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="X8" s="9" t="s">
         <v>99</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>445.28</v>
+        <v>42.91</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>4567</v>
+        <v>4222.88</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>319.68</v>
+        <v>281.12</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -18083,10 +18212,10 @@
         <v>74</v>
       </c>
       <c r="AW8" s="14" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AX8" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY8" s="14" t="s">
         <v>75</v>
@@ -18122,7 +18251,7 @@
         <v>69</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18136,34 +18265,34 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>307020</v>
+        <v>307171</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>1756.8</v>
+        <v>404.81</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -18172,43 +18301,43 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>1756.8</v>
+        <v>404.81</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.142272</v>
+        <v>0.000858</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>3.42</v>
+        <v>2.43</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="Y9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>1756.8</v>
+        <v>404.81</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>122.98</v>
+        <v>16.19</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18274,10 +18403,10 @@
         <v>74</v>
       </c>
       <c r="AW9" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18313,7 +18442,7 @@
         <v>69</v>
       </c>
       <c r="BJ9" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BK9" s="9" t="s">
         <v>75</v>
@@ -18327,79 +18456,79 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>307073</v>
+        <v>307173</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>7834.72</v>
+        <v>404.81</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>7524.33</v>
+        <v>404.81</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0</v>
+        <v>0.000858</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="Y10" s="12" t="n">
-        <v>310.39</v>
+        <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>7524.33</v>
+        <v>404.81</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>526.7</v>
+        <v>16.19</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18465,10 +18594,10 @@
         <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18504,7 +18633,7 @@
         <v>69</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18518,79 +18647,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>307133</v>
+        <v>307174</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>4265.79</v>
+        <v>404.81</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>4222.88</v>
+        <v>404.81</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.484131</v>
+        <v>0.000858</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>71.4</v>
+        <v>2.43</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>42.91</v>
+        <v>0</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>4222.88</v>
+        <v>404.81</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>281.12</v>
+        <v>16.19</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18656,10 +18785,10 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18695,7 +18824,7 @@
         <v>69</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18709,34 +18838,34 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>307171</v>
+        <v>307231</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>114</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>404.81</v>
+        <v>2929.6</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
@@ -18745,28 +18874,28 @@
         <v>1</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>404.81</v>
+        <v>2929.6</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.000484</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>2.43</v>
+        <v>3.22</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
@@ -18778,10 +18907,10 @@
         <v>0</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>404.81</v>
+        <v>2929.6</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>16.19</v>
+        <v>205.07</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18847,10 +18976,10 @@
         <v>74</v>
       </c>
       <c r="AW12" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>75</v>
@@ -18886,7 +19015,7 @@
         <v>69</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -18900,22 +19029,22 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>307173</v>
+        <v>307235</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>114</v>
@@ -18927,7 +19056,7 @@
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>404.81</v>
+        <v>461.96</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -18936,13 +19065,13 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>404.81</v>
+        <v>461.96</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.002057</v>
       </c>
       <c r="R13" s="12" t="n">
         <v>2.43</v>
@@ -18951,7 +19080,7 @@
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
@@ -18969,10 +19098,10 @@
         <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>404.81</v>
+        <v>461.96</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>16.19</v>
+        <v>18.48</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19038,10 +19167,10 @@
         <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -19077,7 +19206,7 @@
         <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19091,34 +19220,34 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>307174</v>
+        <v>307242</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="I14" s="9" t="s">
         <v>114</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>404.81</v>
+        <v>1887.04</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
@@ -19127,28 +19256,28 @@
         <v>1</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>404.81</v>
+        <v>1887.04</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.007832</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
@@ -19160,10 +19289,10 @@
         <v>0</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>404.81</v>
+        <v>1887.04</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>16.19</v>
+        <v>132.09</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19229,10 +19358,10 @@
         <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>75</v>
@@ -19268,7 +19397,7 @@
         <v>69</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="BK14" s="9" t="s">
         <v>75</v>
@@ -19282,34 +19411,34 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>307231</v>
+        <v>307265</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G15" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H15" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I15" s="9" t="s">
-        <v>133</v>
-      </c>
       <c r="J15" s="9" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>2929.6</v>
+        <v>3702.49</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -19318,43 +19447,43 @@
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>2929.6</v>
+        <v>3437.49</v>
       </c>
       <c r="P15" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q15" s="13" t="n">
-        <v>0.000484</v>
+        <v>0</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="Y15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>2929.6</v>
+        <v>3702.49</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>205.07</v>
+        <v>259.17</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19420,10 +19549,10 @@
         <v>74</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX15" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY15" s="14" t="s">
         <v>75</v>
@@ -19459,7 +19588,7 @@
         <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19473,79 +19602,79 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>307235</v>
+        <v>307278</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H16" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="I16" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="I16" s="9" t="s">
-        <v>133</v>
-      </c>
       <c r="J16" s="9" t="s">
-        <v>69</v>
+        <v>134</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>461.96</v>
+        <v>29709.55</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>461.96</v>
+        <v>29280.46</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.002057</v>
+        <v>0.69578</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>2.43</v>
+        <v>130.96</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>0</v>
+        <v>429.09</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>461.96</v>
+        <v>29280.46</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>18.48</v>
+        <v>1794.18</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19611,10 +19740,10 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX16" s="10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="AY16" s="14" t="s">
         <v>75</v>
@@ -19650,7 +19779,7 @@
         <v>69</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19664,34 +19793,34 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>307242</v>
+        <v>307330</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="H17" s="9" t="s">
         <v>114</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1887.04</v>
+        <v>7078.63</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19700,22 +19829,22 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>1887.04</v>
+        <v>6646.6</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.007832</v>
+        <v>0.0425</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>1.9</v>
+        <v>9.6</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
@@ -19727,16 +19856,16 @@
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>0</v>
+        <v>432.03</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>1887.04</v>
+        <v>6646.6</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>132.09</v>
+        <v>465.26</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19802,10 +19931,10 @@
         <v>74</v>
       </c>
       <c r="AW17" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX17" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY17" s="14" t="s">
         <v>75</v>
@@ -19841,7 +19970,7 @@
         <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19855,34 +19984,34 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>307265</v>
+        <v>307334</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>3702.49</v>
+        <v>4963.92</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
@@ -19891,43 +20020,43 @@
         <v>1</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>3437.49</v>
+        <v>4963.92</v>
       </c>
       <c r="P18" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0</v>
+        <v>0.029904</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>3.5</v>
+        <v>6.84</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="Y18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>3702.49</v>
+        <v>4963.92</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>259.17</v>
+        <v>347.47</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -19993,10 +20122,10 @@
         <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX18" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY18" s="14" t="s">
         <v>75</v>
@@ -20032,7 +20161,7 @@
         <v>69</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20046,79 +20175,79 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>307278</v>
+        <v>307356</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>29709.55</v>
+        <v>2104.02</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>29280.46</v>
+        <v>2104.02</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.69578</v>
+        <v>0.005548</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>130.96</v>
+        <v>1.08</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="W19" s="9" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>429.09</v>
+        <v>0</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>29280.46</v>
+        <v>2104.02</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>1794.18</v>
+        <v>147.28</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20184,10 +20313,10 @@
         <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX19" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY19" s="14" t="s">
         <v>75</v>
@@ -20223,7 +20352,7 @@
         <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20237,79 +20366,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>307330</v>
+        <v>307367</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>142</v>
+        <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>7078.63</v>
+        <v>5671.17</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>6646.6</v>
+        <v>5538.68</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.0425</v>
+        <v>0.314926</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>9.6</v>
+        <v>33.19</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>28</v>
+        <v>55.35</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>432.03</v>
+        <v>132.49</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>6646.6</v>
+        <v>4787.31</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>465.26</v>
+        <v>258.23</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20375,10 +20504,10 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX20" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY20" s="14" t="s">
         <v>75</v>
@@ -20414,7 +20543,7 @@
         <v>69</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="BK20" s="9" t="s">
         <v>75</v>
@@ -20428,79 +20557,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>307334</v>
+        <v>307369</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>142</v>
+        <v>66</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>157</v>
+        <v>114</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>4963.92</v>
+        <v>1825.13</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>4963.92</v>
+        <v>1767.68</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.029904</v>
+        <v>0.025844</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>6.84</v>
+        <v>6.79</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>0</v>
+        <v>57.45</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>4963.92</v>
+        <v>1767.68</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>347.47</v>
+        <v>110.47</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20566,10 +20695,10 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20605,7 +20734,7 @@
         <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20619,34 +20748,34 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>307356</v>
+        <v>307376</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>2104.02</v>
+        <v>499.53</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
@@ -20655,22 +20784,22 @@
         <v>1</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>2104.02</v>
+        <v>499.53</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.005548</v>
+        <v>0.000507</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
@@ -20682,16 +20811,16 @@
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="Y22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>2104.02</v>
+        <v>499.53</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>147.28</v>
+        <v>34.97</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20757,10 +20886,10 @@
         <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX22" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY22" s="14" t="s">
         <v>75</v>
@@ -20796,7 +20925,7 @@
         <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20810,79 +20939,79 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>307367</v>
+        <v>307386</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>168</v>
+        <v>104</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>5671.17</v>
+        <v>481.59</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>5538.68</v>
+        <v>481.59</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.314926</v>
+        <v>0.002268</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>33.19</v>
+        <v>0.44</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>55.35</v>
+        <v>28</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="Y23" s="12" t="n">
-        <v>132.49</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>4787.31</v>
+        <v>481.59</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>258.23</v>
+        <v>19.26</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -20948,10 +21077,10 @@
         <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -20987,7 +21116,7 @@
         <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21001,25 +21130,25 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>307369</v>
+        <v>307424</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>69</v>
@@ -21028,31 +21157,31 @@
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>1825.13</v>
+        <v>1783.2</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>1767.68</v>
+        <v>1624.79</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0.025844</v>
+        <v>0</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>6.79</v>
+        <v>0</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
@@ -21064,16 +21193,16 @@
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>57.45</v>
+        <v>158.41</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>1767.68</v>
+        <v>1624.79</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>110.47</v>
+        <v>65.04</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21082,7 +21211,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="12" t="n">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="AE24" s="12" t="n">
         <v>0</v>
@@ -21139,7 +21268,7 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX24" s="10" t="s">
         <v>77</v>
@@ -21163,25 +21292,25 @@
         <v>75</v>
       </c>
       <c r="BE24" s="14" t="s">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="BF24" s="9" t="s">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="BG24" s="9" t="s">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="BH24" s="14" t="s">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="BI24" s="9" t="s">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="BK24" s="9" t="s">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="BL24" s="9" t="s">
         <v>75</v>
@@ -21192,79 +21321,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>307376</v>
+        <v>307428</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>140</v>
+        <v>97</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>142</v>
+        <v>66</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>499.53</v>
+        <v>785.04</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>499.53</v>
+        <v>785.04</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.000507</v>
+        <v>0.06696</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>1.07</v>
+        <v>2.59</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="W25" s="9" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>499.53</v>
+        <v>785.04</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>34.97</v>
+        <v>54.95</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21330,10 +21459,10 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21369,7 +21498,7 @@
         <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21383,34 +21512,34 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>307386</v>
+        <v>307433</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="I26" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J26" s="9" t="s">
         <v>179</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="I26" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="J26" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>481.59</v>
+        <v>1040.61</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -21419,22 +21548,22 @@
         <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>481.59</v>
+        <v>977.1</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0.002268</v>
+        <v>0</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
@@ -21446,16 +21575,16 @@
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>0</v>
+        <v>63.51</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>481.59</v>
+        <v>977.1</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>19.26</v>
+        <v>68.4</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21521,10 +21650,10 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX26" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY26" s="14" t="s">
         <v>75</v>
@@ -21560,7 +21689,7 @@
         <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21574,52 +21703,52 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>307424</v>
+        <v>307439</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="G27" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>66</v>
-      </c>
       <c r="H27" s="9" t="s">
-        <v>133</v>
+        <v>178</v>
       </c>
       <c r="I27" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J27" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>1783.2</v>
+        <v>2401.84</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>1624.79</v>
+        <v>2401.84</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0</v>
+        <v>0.29576</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>0</v>
+        <v>31.68</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
@@ -21631,22 +21760,22 @@
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>158.41</v>
+        <v>0</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>1624.79</v>
+        <v>2401.84</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>65.04</v>
+        <v>149.08</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21655,7 +21784,7 @@
         <v>0</v>
       </c>
       <c r="AD27" s="12" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="AE27" s="12" t="n">
         <v>0</v>
@@ -21712,10 +21841,10 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX27" s="10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AY27" s="14" t="s">
         <v>75</v>
@@ -21736,25 +21865,25 @@
         <v>75</v>
       </c>
       <c r="BE27" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF27" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG27" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH27" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI27" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ27" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="BF27" s="9" t="s">
-        <v>188</v>
-      </c>
-      <c r="BG27" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="BH27" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="BI27" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="BJ27" s="9" t="s">
-        <v>190</v>
-      </c>
       <c r="BK27" s="9" t="s">
-        <v>191</v>
+        <v>75</v>
       </c>
       <c r="BL27" s="9" t="s">
         <v>75</v>
@@ -21765,79 +21894,79 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>307428</v>
+        <v>307443</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>785.04</v>
+        <v>447.13</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O28" s="12" t="n">
-        <v>785.04</v>
+        <v>433.06</v>
       </c>
       <c r="P28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q28" s="13" t="n">
-        <v>0.06696</v>
+        <v>0.0219</v>
       </c>
       <c r="R28" s="12" t="n">
-        <v>2.59</v>
+        <v>1.7</v>
       </c>
       <c r="S28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T28" s="14" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="U28" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V28" s="12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="W28" s="9" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="X28" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="Y28" s="12" t="n">
-        <v>0</v>
+        <v>14.07</v>
       </c>
       <c r="Z28" s="12" t="n">
-        <v>785.04</v>
+        <v>433.06</v>
       </c>
       <c r="AA28" s="12" t="n">
-        <v>54.95</v>
+        <v>30.31</v>
       </c>
       <c r="AB28" s="12" t="n">
         <v>0</v>
@@ -21903,10 +22032,10 @@
         <v>74</v>
       </c>
       <c r="AW28" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX28" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY28" s="14" t="s">
         <v>75</v>
@@ -21942,7 +22071,7 @@
         <v>69</v>
       </c>
       <c r="BJ28" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="BK28" s="9" t="s">
         <v>75</v>
@@ -21956,79 +22085,79 @@
     </row>
     <row r="29" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="n">
-        <v>307433</v>
+        <v>307444</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
       <c r="E29" s="9"/>
       <c r="F29" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>142</v>
+        <v>66</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="K29" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>1040.61</v>
+        <v>24671.51</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O29" s="12" t="n">
-        <v>977.1</v>
+        <v>23273.18</v>
       </c>
       <c r="P29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q29" s="13" t="n">
-        <v>0</v>
+        <v>3.54421</v>
       </c>
       <c r="R29" s="12" t="n">
-        <v>0</v>
+        <v>399.29</v>
       </c>
       <c r="S29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T29" s="14" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="U29" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V29" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W29" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X29" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="Y29" s="12" t="n">
-        <v>63.51</v>
+        <v>1398.33</v>
       </c>
       <c r="Z29" s="12" t="n">
-        <v>977.1</v>
+        <v>23273.18</v>
       </c>
       <c r="AA29" s="12" t="n">
-        <v>68.4</v>
+        <v>1629.14</v>
       </c>
       <c r="AB29" s="12" t="n">
         <v>0</v>
@@ -22094,10 +22223,10 @@
         <v>74</v>
       </c>
       <c r="AW29" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX29" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY29" s="14" t="s">
         <v>75</v>
@@ -22133,7 +22262,7 @@
         <v>69</v>
       </c>
       <c r="BJ29" s="9" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="BK29" s="9" t="s">
         <v>75</v>
@@ -22147,79 +22276,79 @@
     </row>
     <row r="30" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="n">
-        <v>307439</v>
+        <v>307462</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
       <c r="E30" s="9"/>
       <c r="F30" s="9" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G30" s="10" t="s">
-        <v>203</v>
+        <v>66</v>
       </c>
       <c r="H30" s="9" t="s">
-        <v>197</v>
+        <v>138</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="K30" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>2401.84</v>
+        <v>319.81</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O30" s="12" t="n">
-        <v>2401.84</v>
+        <v>291.4</v>
       </c>
       <c r="P30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q30" s="13" t="n">
-        <v>0.29576</v>
+        <v>0.002146</v>
       </c>
       <c r="R30" s="12" t="n">
-        <v>31.68</v>
+        <v>0.53</v>
       </c>
       <c r="S30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T30" s="14" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="U30" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V30" s="12" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="W30" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X30" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="Y30" s="12" t="n">
-        <v>0</v>
+        <v>28.41</v>
       </c>
       <c r="Z30" s="12" t="n">
-        <v>2401.84</v>
+        <v>291.4</v>
       </c>
       <c r="AA30" s="12" t="n">
-        <v>149.08</v>
+        <v>11.65</v>
       </c>
       <c r="AB30" s="12" t="n">
         <v>0</v>
@@ -22285,10 +22414,10 @@
         <v>74</v>
       </c>
       <c r="AW30" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX30" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY30" s="14" t="s">
         <v>75</v>
@@ -22324,7 +22453,7 @@
         <v>69</v>
       </c>
       <c r="BJ30" s="9" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="BK30" s="9" t="s">
         <v>75</v>
@@ -22338,34 +22467,34 @@
     </row>
     <row r="31" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="n">
-        <v>307443</v>
+        <v>307465</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="9"/>
       <c r="E31" s="9"/>
       <c r="F31" s="9" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>185</v>
+        <v>138</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="K31" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>447.13</v>
+        <v>1140.3</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>0</v>
@@ -22374,43 +22503,43 @@
         <v>1</v>
       </c>
       <c r="O31" s="12" t="n">
-        <v>433.06</v>
+        <v>1039</v>
       </c>
       <c r="P31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q31" s="13" t="n">
-        <v>0.0219</v>
+        <v>0.00479</v>
       </c>
       <c r="R31" s="12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T31" s="14" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="U31" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V31" s="12" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="W31" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X31" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="Y31" s="12" t="n">
-        <v>14.07</v>
+        <v>101.3</v>
       </c>
       <c r="Z31" s="12" t="n">
-        <v>433.06</v>
+        <v>1039</v>
       </c>
       <c r="AA31" s="12" t="n">
-        <v>30.31</v>
+        <v>72.73</v>
       </c>
       <c r="AB31" s="12" t="n">
         <v>0</v>
@@ -22419,7 +22548,7 @@
         <v>0</v>
       </c>
       <c r="AD31" s="12" t="n">
-        <v>0</v>
+        <v>242.33</v>
       </c>
       <c r="AE31" s="12" t="n">
         <v>0</v>
@@ -22476,10 +22605,10 @@
         <v>74</v>
       </c>
       <c r="AW31" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX31" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY31" s="14" t="s">
         <v>75</v>
@@ -22500,25 +22629,25 @@
         <v>75</v>
       </c>
       <c r="BE31" s="14" t="s">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="BF31" s="9" t="s">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="BG31" s="9" t="s">
-        <v>69</v>
+        <v>138</v>
       </c>
       <c r="BH31" s="14" t="s">
-        <v>75</v>
+        <v>206</v>
       </c>
       <c r="BI31" s="9" t="s">
-        <v>69</v>
+        <v>166</v>
       </c>
       <c r="BJ31" s="9" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="BK31" s="9" t="s">
-        <v>75</v>
+        <v>208</v>
       </c>
       <c r="BL31" s="9" t="s">
         <v>75</v>
@@ -22529,52 +22658,52 @@
     </row>
     <row r="32" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="n">
-        <v>307444</v>
+        <v>307471</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="I32" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>212</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="I32" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="K32" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>24671.51</v>
+        <v>7460</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O32" s="12" t="n">
-        <v>23273.18</v>
+        <v>7460</v>
       </c>
       <c r="P32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q32" s="13" t="n">
-        <v>3.54421</v>
+        <v>0.16454</v>
       </c>
       <c r="R32" s="12" t="n">
-        <v>399.29</v>
+        <v>25.2</v>
       </c>
       <c r="S32" s="12" t="n">
         <v>0</v>
@@ -22592,16 +22721,16 @@
         <v>73</v>
       </c>
       <c r="X32" s="9" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="Y32" s="12" t="n">
-        <v>1398.33</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="12" t="n">
-        <v>23273.18</v>
+        <v>7460</v>
       </c>
       <c r="AA32" s="12" t="n">
-        <v>1629.14</v>
+        <v>895.2</v>
       </c>
       <c r="AB32" s="12" t="n">
         <v>0</v>
@@ -22667,10 +22796,10 @@
         <v>74</v>
       </c>
       <c r="AW32" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX32" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY32" s="14" t="s">
         <v>75</v>
@@ -22720,7 +22849,7 @@
     </row>
     <row r="33" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="n">
-        <v>307462</v>
+        <v>307539</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>215</v>
@@ -22735,10 +22864,10 @@
         <v>66</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>217</v>
@@ -22747,25 +22876,25 @@
         <v>70</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>319.81</v>
+        <v>2723.65</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O33" s="12" t="n">
-        <v>291.4</v>
+        <v>2723.65</v>
       </c>
       <c r="P33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q33" s="13" t="n">
-        <v>0.002146</v>
+        <v>0.004185</v>
       </c>
       <c r="R33" s="12" t="n">
-        <v>0.53</v>
+        <v>3.07</v>
       </c>
       <c r="S33" s="12" t="n">
         <v>0</v>
@@ -22777,22 +22906,22 @@
         <v>72</v>
       </c>
       <c r="V33" s="12" t="n">
-        <v>6</v>
+        <v>61.33</v>
       </c>
       <c r="W33" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X33" s="9" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="Y33" s="12" t="n">
-        <v>28.41</v>
+        <v>0</v>
       </c>
       <c r="Z33" s="12" t="n">
-        <v>291.4</v>
+        <v>2723.65</v>
       </c>
       <c r="AA33" s="12" t="n">
-        <v>11.65</v>
+        <v>108.95</v>
       </c>
       <c r="AB33" s="12" t="n">
         <v>0</v>
@@ -22858,10 +22987,10 @@
         <v>74</v>
       </c>
       <c r="AW33" s="14" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AX33" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AY33" s="14" t="s">
         <v>75</v>
@@ -22911,34 +23040,34 @@
     </row>
     <row r="34" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="n">
-        <v>307465</v>
+        <v>307572</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>220</v>
+        <v>104</v>
       </c>
       <c r="C34" s="9"/>
       <c r="D34" s="9"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G34" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="K34" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>1140.3</v>
+        <v>355.13</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>0</v>
@@ -22947,43 +23076,43 @@
         <v>1</v>
       </c>
       <c r="O34" s="12" t="n">
-        <v>1039</v>
+        <v>355.13</v>
       </c>
       <c r="P34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q34" s="13" t="n">
-        <v>0.00479</v>
+        <v>0.00819</v>
       </c>
       <c r="R34" s="12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T34" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="U34" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V34" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W34" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X34" s="9" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="Y34" s="12" t="n">
-        <v>101.3</v>
+        <v>0</v>
       </c>
       <c r="Z34" s="12" t="n">
-        <v>1039</v>
+        <v>355.13</v>
       </c>
       <c r="AA34" s="12" t="n">
-        <v>72.73</v>
+        <v>14.21</v>
       </c>
       <c r="AB34" s="12" t="n">
         <v>0</v>
@@ -22992,7 +23121,7 @@
         <v>0</v>
       </c>
       <c r="AD34" s="12" t="n">
-        <v>242.33</v>
+        <v>0</v>
       </c>
       <c r="AE34" s="12" t="n">
         <v>0</v>
@@ -23049,10 +23178,10 @@
         <v>74</v>
       </c>
       <c r="AW34" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX34" s="10" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="AY34" s="14" t="s">
         <v>75</v>
@@ -23073,25 +23202,25 @@
         <v>75</v>
       </c>
       <c r="BE34" s="14" t="s">
-        <v>223</v>
+        <v>75</v>
       </c>
       <c r="BF34" s="9" t="s">
-        <v>224</v>
+        <v>75</v>
       </c>
       <c r="BG34" s="9" t="s">
-        <v>157</v>
+        <v>69</v>
       </c>
       <c r="BH34" s="14" t="s">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="BI34" s="9" t="s">
-        <v>185</v>
+        <v>69</v>
       </c>
       <c r="BJ34" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="BK34" s="9" t="s">
-        <v>227</v>
+        <v>75</v>
       </c>
       <c r="BL34" s="9" t="s">
         <v>75</v>
@@ -23102,79 +23231,79 @@
     </row>
     <row r="35" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="n">
-        <v>307471</v>
+        <v>307578</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>228</v>
+        <v>104</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9"/>
       <c r="E35" s="9"/>
       <c r="F35" s="9" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="G35" s="10" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>230</v>
+        <v>69</v>
       </c>
       <c r="K35" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>7460</v>
+        <v>355.13</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O35" s="12" t="n">
-        <v>7460</v>
+        <v>355.13</v>
       </c>
       <c r="P35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q35" s="13" t="n">
-        <v>0.16454</v>
+        <v>0.00819</v>
       </c>
       <c r="R35" s="12" t="n">
-        <v>25.2</v>
+        <v>2.17</v>
       </c>
       <c r="S35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T35" s="14" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="U35" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V35" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="W35" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X35" s="9" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="Y35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z35" s="12" t="n">
-        <v>7460</v>
+        <v>355.13</v>
       </c>
       <c r="AA35" s="12" t="n">
-        <v>895.2</v>
+        <v>14.21</v>
       </c>
       <c r="AB35" s="12" t="n">
         <v>0</v>
@@ -23240,10 +23369,10 @@
         <v>74</v>
       </c>
       <c r="AW35" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX35" s="10" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="AY35" s="14" t="s">
         <v>75</v>
@@ -23279,7 +23408,7 @@
         <v>69</v>
       </c>
       <c r="BJ35" s="9" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="BK35" s="9" t="s">
         <v>75</v>
@@ -23293,79 +23422,79 @@
     </row>
     <row r="36" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="n">
-        <v>307539</v>
+        <v>307579</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>233</v>
+        <v>104</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9"/>
       <c r="E36" s="9"/>
       <c r="F36" s="9" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>235</v>
+        <v>69</v>
       </c>
       <c r="K36" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>2723.65</v>
+        <v>355.13</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O36" s="12" t="n">
-        <v>2723.65</v>
+        <v>355.13</v>
       </c>
       <c r="P36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q36" s="13" t="n">
-        <v>0.004185</v>
+        <v>0.00819</v>
       </c>
       <c r="R36" s="12" t="n">
-        <v>3.07</v>
+        <v>2.17</v>
       </c>
       <c r="S36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="U36" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V36" s="12" t="n">
-        <v>61.33</v>
+        <v>0</v>
       </c>
       <c r="W36" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X36" s="9" t="s">
-        <v>217</v>
+        <v>198</v>
       </c>
       <c r="Y36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z36" s="12" t="n">
-        <v>2723.65</v>
+        <v>355.13</v>
       </c>
       <c r="AA36" s="12" t="n">
-        <v>108.95</v>
+        <v>14.21</v>
       </c>
       <c r="AB36" s="12" t="n">
         <v>0</v>
@@ -23431,10 +23560,10 @@
         <v>74</v>
       </c>
       <c r="AW36" s="14" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="AX36" s="10" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="AY36" s="14" t="s">
         <v>75</v>
@@ -23470,7 +23599,7 @@
         <v>69</v>
       </c>
       <c r="BJ36" s="9" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="BK36" s="9" t="s">
         <v>75</v>
@@ -23484,34 +23613,34 @@
     </row>
     <row r="37" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="n">
-        <v>307572</v>
+        <v>307586</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9"/>
       <c r="E37" s="9"/>
       <c r="F37" s="9" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I37" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J37" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="K37" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>355.13</v>
+        <v>2362.82</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>0</v>
@@ -23520,43 +23649,43 @@
         <v>1</v>
       </c>
       <c r="O37" s="12" t="n">
-        <v>355.13</v>
+        <v>2362.82</v>
       </c>
       <c r="P37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q37" s="13" t="n">
-        <v>0.00819</v>
+        <v>0.000824</v>
       </c>
       <c r="R37" s="12" t="n">
-        <v>2.17</v>
+        <v>1.43</v>
       </c>
       <c r="S37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T37" s="14" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="U37" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V37" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W37" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X37" s="9" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="Y37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z37" s="12" t="n">
-        <v>355.13</v>
+        <v>2362.82</v>
       </c>
       <c r="AA37" s="12" t="n">
-        <v>14.21</v>
+        <v>165.4</v>
       </c>
       <c r="AB37" s="12" t="n">
         <v>0</v>
@@ -23622,10 +23751,10 @@
         <v>74</v>
       </c>
       <c r="AW37" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX37" s="10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="AY37" s="14" t="s">
         <v>75</v>
@@ -23661,7 +23790,7 @@
         <v>69</v>
       </c>
       <c r="BJ37" s="9" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="BK37" s="9" t="s">
         <v>75</v>
@@ -23675,34 +23804,34 @@
     </row>
     <row r="38" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="n">
-        <v>307578</v>
+        <v>307598</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>124</v>
+        <v>149</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="9" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="G38" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="I38" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J38" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="J38" s="9" t="s">
-        <v>69</v>
       </c>
       <c r="K38" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>355.13</v>
+        <v>1526.29</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>0</v>
@@ -23711,43 +23840,43 @@
         <v>1</v>
       </c>
       <c r="O38" s="12" t="n">
-        <v>355.13</v>
+        <v>1478.25</v>
       </c>
       <c r="P38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q38" s="13" t="n">
-        <v>0.00819</v>
+        <v>0.00165</v>
       </c>
       <c r="R38" s="12" t="n">
-        <v>2.17</v>
+        <v>0.05</v>
       </c>
       <c r="S38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="U38" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V38" s="12" t="n">
-        <v>0</v>
+        <v>55.12</v>
       </c>
       <c r="W38" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X38" s="9" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="Y38" s="12" t="n">
-        <v>0</v>
+        <v>48.04</v>
       </c>
       <c r="Z38" s="12" t="n">
-        <v>355.13</v>
+        <v>1478.25</v>
       </c>
       <c r="AA38" s="12" t="n">
-        <v>14.21</v>
+        <v>103.48</v>
       </c>
       <c r="AB38" s="12" t="n">
         <v>0</v>
@@ -23813,10 +23942,10 @@
         <v>74</v>
       </c>
       <c r="AW38" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX38" s="10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="AY38" s="14" t="s">
         <v>75</v>
@@ -23852,7 +23981,7 @@
         <v>69</v>
       </c>
       <c r="BJ38" s="9" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="BK38" s="9" t="s">
         <v>75</v>
@@ -23866,34 +23995,34 @@
     </row>
     <row r="39" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="n">
-        <v>307579</v>
+        <v>307601</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9"/>
       <c r="E39" s="9"/>
       <c r="F39" s="9" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>66</v>
+        <v>123</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>69</v>
+        <v>236</v>
       </c>
       <c r="K39" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>355.13</v>
+        <v>3012.18</v>
       </c>
       <c r="M39" s="12" t="n">
         <v>0</v>
@@ -23902,43 +24031,43 @@
         <v>1</v>
       </c>
       <c r="O39" s="12" t="n">
-        <v>355.13</v>
+        <v>2828.34</v>
       </c>
       <c r="P39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q39" s="13" t="n">
-        <v>0.00819</v>
+        <v>0.009216</v>
       </c>
       <c r="R39" s="12" t="n">
-        <v>2.17</v>
+        <v>2.96</v>
       </c>
       <c r="S39" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="U39" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V39" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W39" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X39" s="9" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="Y39" s="12" t="n">
-        <v>0</v>
+        <v>183.84</v>
       </c>
       <c r="Z39" s="12" t="n">
-        <v>355.13</v>
+        <v>2828.34</v>
       </c>
       <c r="AA39" s="12" t="n">
-        <v>14.21</v>
+        <v>197.98</v>
       </c>
       <c r="AB39" s="12" t="n">
         <v>0</v>
@@ -24004,10 +24133,10 @@
         <v>74</v>
       </c>
       <c r="AW39" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AX39" s="10" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="AY39" s="14" t="s">
         <v>75</v>
@@ -24043,7 +24172,7 @@
         <v>69</v>
       </c>
       <c r="BJ39" s="9" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="BK39" s="9" t="s">
         <v>75</v>
@@ -24056,1016 +24185,3499 @@
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4"/>
+      <c r="A40" s="8" t="n">
+        <v>307613</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L40" s="12" t="n">
+        <v>5949.49</v>
+      </c>
+      <c r="M40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O40" s="12" t="n">
+        <v>5420.95</v>
+      </c>
+      <c r="P40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="U40" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V40" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="W40" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X40" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y40" s="12" t="n">
+        <v>528.54</v>
+      </c>
+      <c r="Z40" s="12" t="n">
+        <v>5420.95</v>
+      </c>
+      <c r="AA40" s="12" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="AB40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV40" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW40" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX40" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG40" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH40" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI40" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ40" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="BK40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL40" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM40" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="41" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
+    <row r="41" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="n">
+        <v>307614</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-      <c r="H41" s="17"/>
-      <c r="I41" s="17"/>
-      <c r="J41" s="17"/>
-      <c r="K41" s="17"/>
-      <c r="L41" s="17"/>
-      <c r="M41" s="17"/>
-      <c r="N41" s="17"/>
-      <c r="O41" s="17"/>
-      <c r="P41" s="17"/>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="17"/>
-      <c r="U41" s="17"/>
-      <c r="V41" s="17"/>
+      <c r="G41" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="I41" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>1936.45</v>
+      </c>
+      <c r="M41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O41" s="12" t="n">
+        <v>1792.35</v>
+      </c>
+      <c r="P41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="13" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="R41" s="12" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="S41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="14" t="s">
+        <v>246</v>
+      </c>
+      <c r="U41" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V41" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="W41" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X41" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y41" s="12" t="n">
+        <v>144.1</v>
+      </c>
+      <c r="Z41" s="12" t="n">
+        <v>1792.35</v>
+      </c>
+      <c r="AA41" s="12" t="n">
+        <v>111.31</v>
+      </c>
+      <c r="AB41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV41" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW41" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX41" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG41" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH41" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI41" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ41" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="BK41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL41" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM41" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="42" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="B42" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C42" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="E42" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="F42" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="G42" s="18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H42" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="I42" s="18" t="s">
+    <row r="42" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="8" t="n">
+        <v>307617</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9" t="s">
         <v>248</v>
       </c>
-      <c r="J42" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="K42" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="L42" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="M42" s="18" t="s">
+      <c r="G42" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="I42" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K42" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>450.89</v>
+      </c>
+      <c r="M42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O42" s="12" t="n">
+        <v>436.7</v>
+      </c>
+      <c r="P42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="13" t="n">
+        <v>0.00315</v>
+      </c>
+      <c r="R42" s="12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="S42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="N42" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="O42" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="P42" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q42" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="R42" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="S42" s="18" t="s">
+      <c r="U42" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V42" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="W42" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X42" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y42" s="12" t="n">
+        <v>14.19</v>
+      </c>
+      <c r="Z42" s="12" t="n">
+        <v>436.7</v>
+      </c>
+      <c r="AA42" s="12" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="AB42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV42" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW42" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX42" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG42" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH42" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI42" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ42" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="T42" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="U42" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="V42" s="18" t="s">
-        <v>37</v>
+      <c r="BK42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL42" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM42" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="19" t="n">
-        <v>35</v>
-      </c>
-      <c r="B43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="19" t="n">
-        <v>265</v>
-      </c>
-      <c r="D43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="19" t="n">
-        <v>3623.34</v>
-      </c>
-      <c r="F43" s="19" t="n">
-        <v>121859.18</v>
-      </c>
-      <c r="G43" s="19" t="n">
-        <v>8286.95</v>
-      </c>
-      <c r="H43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="19" t="n">
-        <v>328.83</v>
-      </c>
-      <c r="K43" s="19" t="n">
-        <v>126224.22</v>
-      </c>
-      <c r="L43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="20" t="n">
-        <v>6.143688</v>
-      </c>
-      <c r="S43" s="19" t="n">
-        <v>122335.88</v>
-      </c>
-      <c r="T43" s="19" t="n">
-        <v>126224.22</v>
-      </c>
-      <c r="U43" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="19" t="n">
-        <v>0</v>
+      <c r="A43" s="8" t="n">
+        <v>307633</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K43" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L43" s="12" t="n">
+        <v>2398.04</v>
+      </c>
+      <c r="M43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O43" s="12" t="n">
+        <v>2185</v>
+      </c>
+      <c r="P43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="U43" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V43" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="W43" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X43" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y43" s="12" t="n">
+        <v>213.04</v>
+      </c>
+      <c r="Z43" s="12" t="n">
+        <v>2185</v>
+      </c>
+      <c r="AA43" s="12" t="n">
+        <v>87.4</v>
+      </c>
+      <c r="AB43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV43" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW43" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX43" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG43" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH43" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI43" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ43" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="BK43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL43" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM43" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E44" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="F44" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="G44" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="H44" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="I44" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="J44" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="K44" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="L44" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="M44" s="18" t="s">
-        <v>254</v>
+    <row r="44" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="8" t="n">
+        <v>307639</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="I44" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="K44" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>3239.72</v>
+      </c>
+      <c r="M44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O44" s="12" t="n">
+        <v>3239.72</v>
+      </c>
+      <c r="P44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="13" t="n">
+        <v>3.10659</v>
+      </c>
+      <c r="R44" s="12" t="n">
+        <v>30.71</v>
+      </c>
+      <c r="S44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="U44" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V44" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="W44" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X44" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="12" t="n">
+        <v>3239.72</v>
+      </c>
+      <c r="AA44" s="12" t="n">
+        <v>211.61</v>
+      </c>
+      <c r="AB44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV44" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW44" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX44" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG44" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH44" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI44" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ44" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="BK44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL44" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM44" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="19" t="n">
-        <v>796.71</v>
-      </c>
-      <c r="B45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="19" t="n">
-        <v>49.43</v>
-      </c>
-      <c r="E45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="19" t="n">
-        <v>0</v>
+      <c r="A45" s="8" t="n">
+        <v>307652</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="I45" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="K45" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>28147.58</v>
+      </c>
+      <c r="M45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O45" s="12" t="n">
+        <v>28147.58</v>
+      </c>
+      <c r="P45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="13" t="n">
+        <v>3.06796</v>
+      </c>
+      <c r="R45" s="12" t="n">
+        <v>550.35</v>
+      </c>
+      <c r="S45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="U45" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V45" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="W45" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X45" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="12" t="n">
+        <v>28147.58</v>
+      </c>
+      <c r="AA45" s="12" t="n">
+        <v>1970.33</v>
+      </c>
+      <c r="AB45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV45" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW45" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX45" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF45" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG45" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH45" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI45" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ45" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="BK45" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL45" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM45" s="16" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4"/>
+      <c r="A46" s="8" t="n">
+        <v>307670</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="I46" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K46" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L46" s="12" t="n">
+        <v>32424</v>
+      </c>
+      <c r="M46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O46" s="12" t="n">
+        <v>32424</v>
+      </c>
+      <c r="P46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="13" t="n">
+        <v>5.34636</v>
+      </c>
+      <c r="R46" s="12" t="n">
+        <v>70.96</v>
+      </c>
+      <c r="S46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="U46" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="W46" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X46" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="12" t="n">
+        <v>32424</v>
+      </c>
+      <c r="AA46" s="12" t="n">
+        <v>2269.68</v>
+      </c>
+      <c r="AB46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV46" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW46" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX46" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG46" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH46" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI46" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ46" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="BK46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL46" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM46" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
-    <row r="47" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="21" t="s">
-        <v>255</v>
-      </c>
-      <c r="B47" s="21"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="21"/>
-      <c r="G47" s="21"/>
-      <c r="H47" s="21"/>
-      <c r="I47" s="21"/>
-      <c r="J47" s="21"/>
-      <c r="K47" s="21"/>
-      <c r="L47" s="21"/>
-      <c r="M47" s="21"/>
-      <c r="N47" s="21"/>
-      <c r="O47" s="21"/>
-      <c r="P47" s="21"/>
-      <c r="Q47" s="21"/>
-      <c r="R47" s="21"/>
-      <c r="S47" s="21"/>
-      <c r="T47" s="21"/>
-      <c r="U47" s="21"/>
-      <c r="V47" s="21"/>
-      <c r="W47" s="21"/>
-      <c r="X47" s="21"/>
-      <c r="Y47" s="21"/>
-      <c r="Z47" s="21"/>
-      <c r="AA47" s="21"/>
-      <c r="AB47" s="21"/>
-      <c r="AC47" s="21"/>
-      <c r="AD47" s="21"/>
-      <c r="AE47" s="21"/>
-      <c r="AF47" s="21"/>
-      <c r="AG47" s="21"/>
-      <c r="AH47" s="21"/>
-      <c r="AI47" s="21"/>
-      <c r="AJ47" s="21"/>
-      <c r="AK47" s="21"/>
-      <c r="AL47" s="21"/>
-      <c r="AM47" s="21"/>
-      <c r="AN47" s="21"/>
-      <c r="AO47" s="21"/>
-      <c r="AP47" s="21"/>
-      <c r="AQ47" s="21"/>
-      <c r="AR47" s="21"/>
-      <c r="AS47" s="21"/>
-      <c r="AT47" s="21"/>
-      <c r="AU47" s="21"/>
-      <c r="AV47" s="21"/>
-      <c r="AW47" s="21"/>
-      <c r="AX47" s="21"/>
-      <c r="AY47" s="21"/>
-      <c r="AZ47" s="21"/>
-      <c r="BA47" s="21"/>
-      <c r="BB47" s="21"/>
-      <c r="BC47" s="21"/>
-      <c r="BD47" s="21"/>
-      <c r="BE47" s="21"/>
-      <c r="BF47" s="21"/>
-      <c r="BG47" s="21"/>
-      <c r="BH47" s="21"/>
-      <c r="BI47" s="21"/>
-      <c r="BJ47" s="21"/>
-      <c r="BK47" s="21"/>
-      <c r="BL47" s="21"/>
-      <c r="BM47" s="21"/>
+    <row r="47" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="8" t="n">
+        <v>307671</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="H47" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="I47" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J47" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="K47" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L47" s="12" t="n">
+        <v>8175.04</v>
+      </c>
+      <c r="M47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="O47" s="12" t="n">
+        <v>7795.49</v>
+      </c>
+      <c r="P47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="13" t="n">
+        <v>0.064416</v>
+      </c>
+      <c r="R47" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="S47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="U47" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V47" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="W47" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X47" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y47" s="12" t="n">
+        <v>379.55</v>
+      </c>
+      <c r="Z47" s="12" t="n">
+        <v>7795.49</v>
+      </c>
+      <c r="AA47" s="12" t="n">
+        <v>486.36</v>
+      </c>
+      <c r="AB47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV47" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW47" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX47" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF47" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG47" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH47" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI47" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ47" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="BK47" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL47" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM47" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="4"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
-      <c r="V48" s="4"/>
-      <c r="W48" s="4"/>
-      <c r="X48" s="4"/>
-      <c r="Y48" s="4"/>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
-      <c r="AB48" s="4"/>
-      <c r="AC48" s="4"/>
-      <c r="AD48" s="4"/>
-      <c r="AE48" s="4"/>
-      <c r="AF48" s="4"/>
-      <c r="AG48" s="4"/>
-      <c r="AH48" s="4"/>
-      <c r="AI48" s="4"/>
-      <c r="AJ48" s="4"/>
-      <c r="AK48" s="4"/>
-      <c r="AL48" s="4"/>
-      <c r="AM48" s="4"/>
-      <c r="AN48" s="4"/>
-      <c r="AO48" s="4"/>
-      <c r="AP48" s="4"/>
-      <c r="AQ48" s="4"/>
-      <c r="AR48" s="4"/>
-      <c r="AS48" s="4"/>
-      <c r="AT48" s="4"/>
-      <c r="AU48" s="4"/>
-      <c r="AV48" s="4"/>
-      <c r="AW48" s="4"/>
-      <c r="AX48" s="4"/>
-      <c r="AY48" s="4"/>
-      <c r="AZ48" s="4"/>
-      <c r="BA48" s="4"/>
-      <c r="BB48" s="4"/>
-      <c r="BC48" s="4"/>
-      <c r="BD48" s="4"/>
-      <c r="BE48" s="4"/>
-      <c r="BF48" s="4"/>
-      <c r="BG48" s="4"/>
-      <c r="BH48" s="4"/>
-      <c r="BI48" s="4"/>
-      <c r="BJ48" s="4"/>
-      <c r="BK48" s="4"/>
-      <c r="BL48" s="4"/>
-      <c r="BM48" s="4"/>
+      <c r="A48" s="8" t="n">
+        <v>307672</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H48" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="I48" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J48" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="K48" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L48" s="12" t="n">
+        <v>116731.4</v>
+      </c>
+      <c r="M48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="O48" s="12" t="n">
+        <v>116731.4</v>
+      </c>
+      <c r="P48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="13" t="n">
+        <v>13.7106</v>
+      </c>
+      <c r="R48" s="12" t="n">
+        <v>2125.05</v>
+      </c>
+      <c r="S48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="U48" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V48" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="W48" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X48" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="12" t="n">
+        <v>116731.4</v>
+      </c>
+      <c r="AA48" s="12" t="n">
+        <v>8171.19</v>
+      </c>
+      <c r="AB48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV48" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW48" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX48" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF48" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG48" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH48" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI48" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ48" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="BK48" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL48" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM48" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="4"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="4"/>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-      <c r="V49" s="4"/>
-      <c r="W49" s="4"/>
-      <c r="X49" s="4"/>
-      <c r="Y49" s="4"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
-      <c r="AB49" s="4"/>
-      <c r="AC49" s="4"/>
-      <c r="AD49" s="4"/>
-      <c r="AE49" s="4"/>
-      <c r="AF49" s="4"/>
-      <c r="AG49" s="4"/>
-      <c r="AH49" s="4"/>
-      <c r="AI49" s="4"/>
-      <c r="AJ49" s="4"/>
-      <c r="AK49" s="4"/>
-      <c r="AL49" s="4"/>
-      <c r="AM49" s="4"/>
-      <c r="AN49" s="4"/>
-      <c r="AO49" s="4"/>
-      <c r="AP49" s="4"/>
-      <c r="AQ49" s="4"/>
-      <c r="AR49" s="4"/>
-      <c r="AS49" s="4"/>
-      <c r="AT49" s="4"/>
-      <c r="AU49" s="4"/>
-      <c r="AV49" s="4"/>
-      <c r="AW49" s="4"/>
-      <c r="AX49" s="4"/>
-      <c r="AY49" s="4"/>
-      <c r="AZ49" s="4"/>
-      <c r="BA49" s="4"/>
-      <c r="BB49" s="4"/>
-      <c r="BC49" s="4"/>
-      <c r="BD49" s="4"/>
-      <c r="BE49" s="4"/>
-      <c r="BF49" s="4"/>
-      <c r="BG49" s="4"/>
-      <c r="BH49" s="4"/>
-      <c r="BI49" s="4"/>
-      <c r="BJ49" s="4"/>
-      <c r="BK49" s="4"/>
-      <c r="BL49" s="4"/>
-      <c r="BM49" s="4"/>
+      <c r="A49" s="8" t="n">
+        <v>307673</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="I49" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J49" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="K49" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L49" s="12" t="n">
+        <v>10048.8</v>
+      </c>
+      <c r="M49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O49" s="12" t="n">
+        <v>10048.8</v>
+      </c>
+      <c r="P49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="13" t="n">
+        <v>1.134</v>
+      </c>
+      <c r="R49" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="S49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="U49" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V49" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="W49" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X49" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="12" t="n">
+        <v>10048.8</v>
+      </c>
+      <c r="AA49" s="12" t="n">
+        <v>703.42</v>
+      </c>
+      <c r="AB49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV49" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW49" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX49" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF49" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG49" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH49" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI49" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ49" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="BK49" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL49" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM49" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="4"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
-      <c r="V50" s="4"/>
-      <c r="W50" s="4"/>
-      <c r="X50" s="4"/>
-      <c r="Y50" s="4"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
-      <c r="AB50" s="4"/>
-      <c r="AC50" s="4"/>
-      <c r="AD50" s="4"/>
-      <c r="AE50" s="4"/>
-      <c r="AF50" s="4"/>
-      <c r="AG50" s="4"/>
-      <c r="AH50" s="4"/>
-      <c r="AI50" s="4"/>
-      <c r="AJ50" s="4"/>
-      <c r="AK50" s="4"/>
-      <c r="AL50" s="4"/>
-      <c r="AM50" s="4"/>
-      <c r="AN50" s="4"/>
-      <c r="AO50" s="4"/>
-      <c r="AP50" s="4"/>
-      <c r="AQ50" s="4"/>
-      <c r="AR50" s="4"/>
-      <c r="AS50" s="4"/>
-      <c r="AT50" s="4"/>
-      <c r="AU50" s="4"/>
-      <c r="AV50" s="4"/>
-      <c r="AW50" s="4"/>
-      <c r="AX50" s="4"/>
-      <c r="AY50" s="4"/>
-      <c r="AZ50" s="4"/>
-      <c r="BA50" s="4"/>
-      <c r="BB50" s="4"/>
-      <c r="BC50" s="4"/>
-      <c r="BD50" s="4"/>
-      <c r="BE50" s="4"/>
-      <c r="BF50" s="4"/>
-      <c r="BG50" s="4"/>
-      <c r="BH50" s="4"/>
-      <c r="BI50" s="4"/>
-      <c r="BJ50" s="4"/>
-      <c r="BK50" s="4"/>
-      <c r="BL50" s="4"/>
-      <c r="BM50" s="4"/>
+      <c r="A50" s="8" t="n">
+        <v>307676</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H50" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I50" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J50" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K50" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L50" s="12" t="n">
+        <v>3225.93</v>
+      </c>
+      <c r="M50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O50" s="12" t="n">
+        <v>3029.04</v>
+      </c>
+      <c r="P50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="13" t="n">
+        <v>0.002648</v>
+      </c>
+      <c r="R50" s="12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="U50" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V50" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W50" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X50" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y50" s="12" t="n">
+        <v>196.89</v>
+      </c>
+      <c r="Z50" s="12" t="n">
+        <v>3029.04</v>
+      </c>
+      <c r="AA50" s="12" t="n">
+        <v>212.03</v>
+      </c>
+      <c r="AB50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV50" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW50" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX50" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG50" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH50" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI50" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ50" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="BK50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL50" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM50" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="4"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
-      <c r="X51" s="4"/>
-      <c r="Y51" s="4"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
-      <c r="AB51" s="4"/>
-      <c r="AC51" s="4"/>
-      <c r="AD51" s="4"/>
-      <c r="AE51" s="4"/>
-      <c r="AF51" s="4"/>
-      <c r="AG51" s="4"/>
-      <c r="AH51" s="4"/>
-      <c r="AI51" s="4"/>
-      <c r="AJ51" s="4"/>
-      <c r="AK51" s="4"/>
-      <c r="AL51" s="4"/>
-      <c r="AM51" s="4"/>
-      <c r="AN51" s="4"/>
-      <c r="AO51" s="4"/>
-      <c r="AP51" s="4"/>
-      <c r="AQ51" s="4"/>
-      <c r="AR51" s="4"/>
-      <c r="AS51" s="4"/>
-      <c r="AT51" s="4"/>
-      <c r="AU51" s="4"/>
-      <c r="AV51" s="4"/>
-      <c r="AW51" s="4"/>
-      <c r="AX51" s="4"/>
-      <c r="AY51" s="4"/>
-      <c r="AZ51" s="4"/>
-      <c r="BA51" s="4"/>
-      <c r="BB51" s="4"/>
-      <c r="BC51" s="4"/>
-      <c r="BD51" s="4"/>
-      <c r="BE51" s="4"/>
-      <c r="BF51" s="4"/>
-      <c r="BG51" s="4"/>
-      <c r="BH51" s="4"/>
-      <c r="BI51" s="4"/>
-      <c r="BJ51" s="4"/>
-      <c r="BK51" s="4"/>
-      <c r="BL51" s="4"/>
-      <c r="BM51" s="4"/>
+      <c r="A51" s="8" t="n">
+        <v>307677</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="I51" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J51" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="K51" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L51" s="12" t="n">
+        <v>3543.62</v>
+      </c>
+      <c r="M51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O51" s="12" t="n">
+        <v>3327.34</v>
+      </c>
+      <c r="P51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="13" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="R51" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="U51" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V51" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="W51" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X51" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y51" s="12" t="n">
+        <v>216.28</v>
+      </c>
+      <c r="Z51" s="12" t="n">
+        <v>3327.34</v>
+      </c>
+      <c r="AA51" s="12" t="n">
+        <v>232.91</v>
+      </c>
+      <c r="AB51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV51" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW51" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX51" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF51" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG51" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH51" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI51" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ51" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="BK51" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL51" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM51" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="4"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-      <c r="W52" s="4"/>
-      <c r="X52" s="4"/>
-      <c r="Y52" s="4"/>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
-      <c r="AB52" s="4"/>
-      <c r="AC52" s="4"/>
-      <c r="AD52" s="4"/>
-      <c r="AE52" s="4"/>
-      <c r="AF52" s="4"/>
-      <c r="AG52" s="4"/>
-      <c r="AH52" s="4"/>
-      <c r="AI52" s="4"/>
-      <c r="AJ52" s="4"/>
-      <c r="AK52" s="4"/>
-      <c r="AL52" s="4"/>
-      <c r="AM52" s="4"/>
-      <c r="AN52" s="4"/>
-      <c r="AO52" s="4"/>
-      <c r="AP52" s="4"/>
-      <c r="AQ52" s="4"/>
-      <c r="AR52" s="4"/>
-      <c r="AS52" s="4"/>
-      <c r="AT52" s="4"/>
-      <c r="AU52" s="4"/>
-      <c r="AV52" s="4"/>
-      <c r="AW52" s="4"/>
-      <c r="AX52" s="4"/>
-      <c r="AY52" s="4"/>
-      <c r="AZ52" s="4"/>
-      <c r="BA52" s="4"/>
-      <c r="BB52" s="4"/>
-      <c r="BC52" s="4"/>
-      <c r="BD52" s="4"/>
-      <c r="BE52" s="4"/>
-      <c r="BF52" s="4"/>
-      <c r="BG52" s="4"/>
-      <c r="BH52" s="4"/>
-      <c r="BI52" s="4"/>
-      <c r="BJ52" s="4"/>
-      <c r="BK52" s="4"/>
-      <c r="BL52" s="4"/>
-      <c r="BM52" s="4"/>
+      <c r="A52" s="8" t="n">
+        <v>307683</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H52" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="I52" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="J52" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="K52" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>16066.48</v>
+      </c>
+      <c r="M52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O52" s="12" t="n">
+        <v>16066.48</v>
+      </c>
+      <c r="P52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="13" t="n">
+        <v>1.5876</v>
+      </c>
+      <c r="R52" s="12" t="n">
+        <v>312</v>
+      </c>
+      <c r="S52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="U52" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="V52" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="W52" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="X52" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="Y52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="12" t="n">
+        <v>16066.48</v>
+      </c>
+      <c r="AA52" s="12" t="n">
+        <v>1124.66</v>
+      </c>
+      <c r="AB52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AK52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AN52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AO52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AP52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AQ52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AS52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AT52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AU52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AV52" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="AW52" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="AX52" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BB52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BD52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BE52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BF52" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BG52" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BH52" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="BI52" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="BJ52" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="BK52" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BL52" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="BM52" s="16" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="4"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
-      <c r="X53" s="4"/>
-      <c r="Y53" s="4"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
-      <c r="AB53" s="4"/>
-      <c r="AC53" s="4"/>
-      <c r="AD53" s="4"/>
-      <c r="AE53" s="4"/>
-      <c r="AF53" s="4"/>
-      <c r="AG53" s="4"/>
-      <c r="AH53" s="4"/>
-      <c r="AI53" s="4"/>
-      <c r="AJ53" s="4"/>
-      <c r="AK53" s="4"/>
-      <c r="AL53" s="4"/>
-      <c r="AM53" s="4"/>
-      <c r="AN53" s="4"/>
-      <c r="AO53" s="4"/>
-      <c r="AP53" s="4"/>
-      <c r="AQ53" s="4"/>
-      <c r="AR53" s="4"/>
-      <c r="AS53" s="4"/>
-      <c r="AT53" s="4"/>
-      <c r="AU53" s="4"/>
-      <c r="AV53" s="4"/>
-      <c r="AW53" s="4"/>
-      <c r="AX53" s="4"/>
-      <c r="AY53" s="4"/>
-      <c r="AZ53" s="4"/>
-      <c r="BA53" s="4"/>
-      <c r="BB53" s="4"/>
-      <c r="BC53" s="4"/>
-      <c r="BD53" s="4"/>
-      <c r="BE53" s="4"/>
-      <c r="BF53" s="4"/>
-      <c r="BG53" s="4"/>
-      <c r="BH53" s="4"/>
-      <c r="BI53" s="4"/>
-      <c r="BJ53" s="4"/>
-      <c r="BK53" s="4"/>
-      <c r="BL53" s="4"/>
-      <c r="BM53" s="4"/>
+      <c r="A53" s="4"/>
     </row>
-    <row r="54" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="4"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
-      <c r="X54" s="4"/>
-      <c r="Y54" s="4"/>
-      <c r="Z54" s="4"/>
-      <c r="AA54" s="4"/>
-      <c r="AB54" s="4"/>
-      <c r="AC54" s="4"/>
-      <c r="AD54" s="4"/>
-      <c r="AE54" s="4"/>
-      <c r="AF54" s="4"/>
-      <c r="AG54" s="4"/>
-      <c r="AH54" s="4"/>
-      <c r="AI54" s="4"/>
-      <c r="AJ54" s="4"/>
-      <c r="AK54" s="4"/>
-      <c r="AL54" s="4"/>
-      <c r="AM54" s="4"/>
-      <c r="AN54" s="4"/>
-      <c r="AO54" s="4"/>
-      <c r="AP54" s="4"/>
-      <c r="AQ54" s="4"/>
-      <c r="AR54" s="4"/>
-      <c r="AS54" s="4"/>
-      <c r="AT54" s="4"/>
-      <c r="AU54" s="4"/>
-      <c r="AV54" s="4"/>
-      <c r="AW54" s="4"/>
-      <c r="AX54" s="4"/>
-      <c r="AY54" s="4"/>
-      <c r="AZ54" s="4"/>
-      <c r="BA54" s="4"/>
-      <c r="BB54" s="4"/>
-      <c r="BC54" s="4"/>
-      <c r="BD54" s="4"/>
-      <c r="BE54" s="4"/>
-      <c r="BF54" s="4"/>
-      <c r="BG54" s="4"/>
-      <c r="BH54" s="4"/>
-      <c r="BI54" s="4"/>
-      <c r="BJ54" s="4"/>
-      <c r="BK54" s="4"/>
-      <c r="BL54" s="4"/>
-      <c r="BM54" s="4"/>
+    <row r="54" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
+      <c r="L54" s="17"/>
+      <c r="M54" s="17"/>
+      <c r="N54" s="17"/>
+      <c r="O54" s="17"/>
+      <c r="P54" s="17"/>
+      <c r="Q54" s="17"/>
+      <c r="R54" s="17"/>
+      <c r="S54" s="17"/>
+      <c r="T54" s="17"/>
+      <c r="U54" s="17"/>
+      <c r="V54" s="17"/>
     </row>
-    <row r="55" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="4"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="4"/>
-      <c r="W55" s="4"/>
-      <c r="X55" s="4"/>
-      <c r="Y55" s="4"/>
-      <c r="Z55" s="4"/>
-      <c r="AA55" s="4"/>
-      <c r="AB55" s="4"/>
-      <c r="AC55" s="4"/>
-      <c r="AD55" s="4"/>
-      <c r="AE55" s="4"/>
-      <c r="AF55" s="4"/>
-      <c r="AG55" s="4"/>
-      <c r="AH55" s="4"/>
-      <c r="AI55" s="4"/>
-      <c r="AJ55" s="4"/>
-      <c r="AK55" s="4"/>
-      <c r="AL55" s="4"/>
-      <c r="AM55" s="4"/>
-      <c r="AN55" s="4"/>
-      <c r="AO55" s="4"/>
-      <c r="AP55" s="4"/>
-      <c r="AQ55" s="4"/>
-      <c r="AR55" s="4"/>
-      <c r="AS55" s="4"/>
-      <c r="AT55" s="4"/>
-      <c r="AU55" s="4"/>
-      <c r="AV55" s="4"/>
-      <c r="AW55" s="4"/>
-      <c r="AX55" s="4"/>
-      <c r="AY55" s="4"/>
-      <c r="AZ55" s="4"/>
-      <c r="BA55" s="4"/>
-      <c r="BB55" s="4"/>
-      <c r="BC55" s="4"/>
-      <c r="BD55" s="4"/>
-      <c r="BE55" s="4"/>
-      <c r="BF55" s="4"/>
-      <c r="BG55" s="4"/>
-      <c r="BH55" s="4"/>
-      <c r="BI55" s="4"/>
-      <c r="BJ55" s="4"/>
-      <c r="BK55" s="4"/>
-      <c r="BL55" s="4"/>
-      <c r="BM55" s="4"/>
+    <row r="55" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="E55" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F55" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="H55" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I55" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="J55" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="K55" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="L55" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="M55" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="N55" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="O55" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="P55" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q55" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="R55" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="S55" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="T55" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="U55" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="V55" s="18" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="4"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="4"/>
-      <c r="X56" s="4"/>
-      <c r="Y56" s="4"/>
-      <c r="Z56" s="4"/>
-      <c r="AA56" s="4"/>
-      <c r="AB56" s="4"/>
-      <c r="AC56" s="4"/>
-      <c r="AD56" s="4"/>
-      <c r="AE56" s="4"/>
-      <c r="AF56" s="4"/>
-      <c r="AG56" s="4"/>
-      <c r="AH56" s="4"/>
-      <c r="AI56" s="4"/>
-      <c r="AJ56" s="4"/>
-      <c r="AK56" s="4"/>
-      <c r="AL56" s="4"/>
-      <c r="AM56" s="4"/>
-      <c r="AN56" s="4"/>
-      <c r="AO56" s="4"/>
-      <c r="AP56" s="4"/>
-      <c r="AQ56" s="4"/>
-      <c r="AR56" s="4"/>
-      <c r="AS56" s="4"/>
-      <c r="AT56" s="4"/>
-      <c r="AU56" s="4"/>
-      <c r="AV56" s="4"/>
-      <c r="AW56" s="4"/>
-      <c r="AX56" s="4"/>
-      <c r="AY56" s="4"/>
-      <c r="AZ56" s="4"/>
-      <c r="BA56" s="4"/>
-      <c r="BB56" s="4"/>
-      <c r="BC56" s="4"/>
-      <c r="BD56" s="4"/>
-      <c r="BE56" s="4"/>
-      <c r="BF56" s="4"/>
-      <c r="BG56" s="4"/>
-      <c r="BH56" s="4"/>
-      <c r="BI56" s="4"/>
-      <c r="BJ56" s="4"/>
-      <c r="BK56" s="4"/>
-      <c r="BL56" s="4"/>
-      <c r="BM56" s="4"/>
+      <c r="A56" s="19" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="19" t="n">
+        <v>265</v>
+      </c>
+      <c r="D56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="19" t="n">
+        <v>5227.75</v>
+      </c>
+      <c r="F56" s="19" t="n">
+        <v>350702.02</v>
+      </c>
+      <c r="G56" s="19" t="n">
+        <v>23989.13</v>
+      </c>
+      <c r="H56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="19" t="n">
+        <v>328.83</v>
+      </c>
+      <c r="K56" s="19" t="n">
+        <v>356681.14</v>
+      </c>
+      <c r="L56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" s="20" t="n">
+        <v>33.927302</v>
+      </c>
+      <c r="S56" s="19" t="n">
+        <v>351188.39</v>
+      </c>
+      <c r="T56" s="19" t="n">
+        <v>356681.14</v>
+      </c>
+      <c r="U56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="19" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="57" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="4"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
-      <c r="W57" s="4"/>
-      <c r="X57" s="4"/>
-      <c r="Y57" s="4"/>
-      <c r="Z57" s="4"/>
-      <c r="AA57" s="4"/>
-      <c r="AB57" s="4"/>
-      <c r="AC57" s="4"/>
-      <c r="AD57" s="4"/>
-      <c r="AE57" s="4"/>
-      <c r="AF57" s="4"/>
-      <c r="AG57" s="4"/>
-      <c r="AH57" s="4"/>
-      <c r="AI57" s="4"/>
-      <c r="AJ57" s="4"/>
-      <c r="AK57" s="4"/>
-      <c r="AL57" s="4"/>
-      <c r="AM57" s="4"/>
-      <c r="AN57" s="4"/>
-      <c r="AO57" s="4"/>
-      <c r="AP57" s="4"/>
-      <c r="AQ57" s="4"/>
-      <c r="AR57" s="4"/>
-      <c r="AS57" s="4"/>
-      <c r="AT57" s="4"/>
-      <c r="AU57" s="4"/>
-      <c r="AV57" s="4"/>
-      <c r="AW57" s="4"/>
-      <c r="AX57" s="4"/>
-      <c r="AY57" s="4"/>
-      <c r="AZ57" s="4"/>
-      <c r="BA57" s="4"/>
-      <c r="BB57" s="4"/>
-      <c r="BC57" s="4"/>
-      <c r="BD57" s="4"/>
-      <c r="BE57" s="4"/>
-      <c r="BF57" s="4"/>
-      <c r="BG57" s="4"/>
-      <c r="BH57" s="4"/>
-      <c r="BI57" s="4"/>
-      <c r="BJ57" s="4"/>
-      <c r="BK57" s="4"/>
-      <c r="BL57" s="4"/>
-      <c r="BM57" s="4"/>
+    <row r="57" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C57" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="F57" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="G57" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="I57" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="J57" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="K57" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="L57" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="M57" s="18" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="19" t="n">
+        <v>4108.8</v>
+      </c>
+      <c r="B58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="19" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="E58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="4"/>
+    </row>
+    <row r="60" customFormat="false" ht="14.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="21"/>
+      <c r="H60" s="21"/>
+      <c r="I60" s="21"/>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
+      <c r="L60" s="21"/>
+      <c r="M60" s="21"/>
+      <c r="N60" s="21"/>
+      <c r="O60" s="21"/>
+      <c r="P60" s="21"/>
+      <c r="Q60" s="21"/>
+      <c r="R60" s="21"/>
+      <c r="S60" s="21"/>
+      <c r="T60" s="21"/>
+      <c r="U60" s="21"/>
+      <c r="V60" s="21"/>
+      <c r="W60" s="21"/>
+      <c r="X60" s="21"/>
+      <c r="Y60" s="21"/>
+      <c r="Z60" s="21"/>
+      <c r="AA60" s="21"/>
+      <c r="AB60" s="21"/>
+      <c r="AC60" s="21"/>
+      <c r="AD60" s="21"/>
+      <c r="AE60" s="21"/>
+      <c r="AF60" s="21"/>
+      <c r="AG60" s="21"/>
+      <c r="AH60" s="21"/>
+      <c r="AI60" s="21"/>
+      <c r="AJ60" s="21"/>
+      <c r="AK60" s="21"/>
+      <c r="AL60" s="21"/>
+      <c r="AM60" s="21"/>
+      <c r="AN60" s="21"/>
+      <c r="AO60" s="21"/>
+      <c r="AP60" s="21"/>
+      <c r="AQ60" s="21"/>
+      <c r="AR60" s="21"/>
+      <c r="AS60" s="21"/>
+      <c r="AT60" s="21"/>
+      <c r="AU60" s="21"/>
+      <c r="AV60" s="21"/>
+      <c r="AW60" s="21"/>
+      <c r="AX60" s="21"/>
+      <c r="AY60" s="21"/>
+      <c r="AZ60" s="21"/>
+      <c r="BA60" s="21"/>
+      <c r="BB60" s="21"/>
+      <c r="BC60" s="21"/>
+      <c r="BD60" s="21"/>
+      <c r="BE60" s="21"/>
+      <c r="BF60" s="21"/>
+      <c r="BG60" s="21"/>
+      <c r="BH60" s="21"/>
+      <c r="BI60" s="21"/>
+      <c r="BJ60" s="21"/>
+      <c r="BK60" s="21"/>
+      <c r="BL60" s="21"/>
+      <c r="BM60" s="21"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B61" s="4"/>
+      <c r="C61" s="4"/>
+      <c r="D61" s="4"/>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="4"/>
+      <c r="I61" s="4"/>
+      <c r="J61" s="4"/>
+      <c r="K61" s="4"/>
+      <c r="L61" s="4"/>
+      <c r="M61" s="4"/>
+      <c r="N61" s="4"/>
+      <c r="O61" s="4"/>
+      <c r="P61" s="4"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="4"/>
+      <c r="T61" s="4"/>
+      <c r="U61" s="4"/>
+      <c r="V61" s="4"/>
+      <c r="W61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="4"/>
+      <c r="AB61" s="4"/>
+      <c r="AC61" s="4"/>
+      <c r="AD61" s="4"/>
+      <c r="AE61" s="4"/>
+      <c r="AF61" s="4"/>
+      <c r="AG61" s="4"/>
+      <c r="AH61" s="4"/>
+      <c r="AI61" s="4"/>
+      <c r="AJ61" s="4"/>
+      <c r="AK61" s="4"/>
+      <c r="AL61" s="4"/>
+      <c r="AM61" s="4"/>
+      <c r="AN61" s="4"/>
+      <c r="AO61" s="4"/>
+      <c r="AP61" s="4"/>
+      <c r="AQ61" s="4"/>
+      <c r="AR61" s="4"/>
+      <c r="AS61" s="4"/>
+      <c r="AT61" s="4"/>
+      <c r="AU61" s="4"/>
+      <c r="AV61" s="4"/>
+      <c r="AW61" s="4"/>
+      <c r="AX61" s="4"/>
+      <c r="AY61" s="4"/>
+      <c r="AZ61" s="4"/>
+      <c r="BA61" s="4"/>
+      <c r="BB61" s="4"/>
+      <c r="BC61" s="4"/>
+      <c r="BD61" s="4"/>
+      <c r="BE61" s="4"/>
+      <c r="BF61" s="4"/>
+      <c r="BG61" s="4"/>
+      <c r="BH61" s="4"/>
+      <c r="BI61" s="4"/>
+      <c r="BJ61" s="4"/>
+      <c r="BK61" s="4"/>
+      <c r="BL61" s="4"/>
+      <c r="BM61" s="4"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B62" s="4"/>
+      <c r="C62" s="4"/>
+      <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
+      <c r="G62" s="4"/>
+      <c r="H62" s="4"/>
+      <c r="I62" s="4"/>
+      <c r="J62" s="4"/>
+      <c r="K62" s="4"/>
+      <c r="L62" s="4"/>
+      <c r="M62" s="4"/>
+      <c r="N62" s="4"/>
+      <c r="O62" s="4"/>
+      <c r="P62" s="4"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="4"/>
+      <c r="T62" s="4"/>
+      <c r="U62" s="4"/>
+      <c r="V62" s="4"/>
+      <c r="W62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="4"/>
+      <c r="AB62" s="4"/>
+      <c r="AC62" s="4"/>
+      <c r="AD62" s="4"/>
+      <c r="AE62" s="4"/>
+      <c r="AF62" s="4"/>
+      <c r="AG62" s="4"/>
+      <c r="AH62" s="4"/>
+      <c r="AI62" s="4"/>
+      <c r="AJ62" s="4"/>
+      <c r="AK62" s="4"/>
+      <c r="AL62" s="4"/>
+      <c r="AM62" s="4"/>
+      <c r="AN62" s="4"/>
+      <c r="AO62" s="4"/>
+      <c r="AP62" s="4"/>
+      <c r="AQ62" s="4"/>
+      <c r="AR62" s="4"/>
+      <c r="AS62" s="4"/>
+      <c r="AT62" s="4"/>
+      <c r="AU62" s="4"/>
+      <c r="AV62" s="4"/>
+      <c r="AW62" s="4"/>
+      <c r="AX62" s="4"/>
+      <c r="AY62" s="4"/>
+      <c r="AZ62" s="4"/>
+      <c r="BA62" s="4"/>
+      <c r="BB62" s="4"/>
+      <c r="BC62" s="4"/>
+      <c r="BD62" s="4"/>
+      <c r="BE62" s="4"/>
+      <c r="BF62" s="4"/>
+      <c r="BG62" s="4"/>
+      <c r="BH62" s="4"/>
+      <c r="BI62" s="4"/>
+      <c r="BJ62" s="4"/>
+      <c r="BK62" s="4"/>
+      <c r="BL62" s="4"/>
+      <c r="BM62" s="4"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B63" s="4"/>
+      <c r="C63" s="4"/>
+      <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
+      <c r="G63" s="4"/>
+      <c r="H63" s="4"/>
+      <c r="I63" s="4"/>
+      <c r="J63" s="4"/>
+      <c r="K63" s="4"/>
+      <c r="L63" s="4"/>
+      <c r="M63" s="4"/>
+      <c r="N63" s="4"/>
+      <c r="O63" s="4"/>
+      <c r="P63" s="4"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="4"/>
+      <c r="T63" s="4"/>
+      <c r="U63" s="4"/>
+      <c r="V63" s="4"/>
+      <c r="W63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="4"/>
+      <c r="AB63" s="4"/>
+      <c r="AC63" s="4"/>
+      <c r="AD63" s="4"/>
+      <c r="AE63" s="4"/>
+      <c r="AF63" s="4"/>
+      <c r="AG63" s="4"/>
+      <c r="AH63" s="4"/>
+      <c r="AI63" s="4"/>
+      <c r="AJ63" s="4"/>
+      <c r="AK63" s="4"/>
+      <c r="AL63" s="4"/>
+      <c r="AM63" s="4"/>
+      <c r="AN63" s="4"/>
+      <c r="AO63" s="4"/>
+      <c r="AP63" s="4"/>
+      <c r="AQ63" s="4"/>
+      <c r="AR63" s="4"/>
+      <c r="AS63" s="4"/>
+      <c r="AT63" s="4"/>
+      <c r="AU63" s="4"/>
+      <c r="AV63" s="4"/>
+      <c r="AW63" s="4"/>
+      <c r="AX63" s="4"/>
+      <c r="AY63" s="4"/>
+      <c r="AZ63" s="4"/>
+      <c r="BA63" s="4"/>
+      <c r="BB63" s="4"/>
+      <c r="BC63" s="4"/>
+      <c r="BD63" s="4"/>
+      <c r="BE63" s="4"/>
+      <c r="BF63" s="4"/>
+      <c r="BG63" s="4"/>
+      <c r="BH63" s="4"/>
+      <c r="BI63" s="4"/>
+      <c r="BJ63" s="4"/>
+      <c r="BK63" s="4"/>
+      <c r="BL63" s="4"/>
+      <c r="BM63" s="4"/>
+    </row>
+    <row r="64" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
+      <c r="G64" s="4"/>
+      <c r="H64" s="4"/>
+      <c r="I64" s="4"/>
+      <c r="J64" s="4"/>
+      <c r="K64" s="4"/>
+      <c r="L64" s="4"/>
+      <c r="M64" s="4"/>
+      <c r="N64" s="4"/>
+      <c r="O64" s="4"/>
+      <c r="P64" s="4"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="4"/>
+      <c r="T64" s="4"/>
+      <c r="U64" s="4"/>
+      <c r="V64" s="4"/>
+      <c r="W64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="4"/>
+      <c r="AB64" s="4"/>
+      <c r="AC64" s="4"/>
+      <c r="AD64" s="4"/>
+      <c r="AE64" s="4"/>
+      <c r="AF64" s="4"/>
+      <c r="AG64" s="4"/>
+      <c r="AH64" s="4"/>
+      <c r="AI64" s="4"/>
+      <c r="AJ64" s="4"/>
+      <c r="AK64" s="4"/>
+      <c r="AL64" s="4"/>
+      <c r="AM64" s="4"/>
+      <c r="AN64" s="4"/>
+      <c r="AO64" s="4"/>
+      <c r="AP64" s="4"/>
+      <c r="AQ64" s="4"/>
+      <c r="AR64" s="4"/>
+      <c r="AS64" s="4"/>
+      <c r="AT64" s="4"/>
+      <c r="AU64" s="4"/>
+      <c r="AV64" s="4"/>
+      <c r="AW64" s="4"/>
+      <c r="AX64" s="4"/>
+      <c r="AY64" s="4"/>
+      <c r="AZ64" s="4"/>
+      <c r="BA64" s="4"/>
+      <c r="BB64" s="4"/>
+      <c r="BC64" s="4"/>
+      <c r="BD64" s="4"/>
+      <c r="BE64" s="4"/>
+      <c r="BF64" s="4"/>
+      <c r="BG64" s="4"/>
+      <c r="BH64" s="4"/>
+      <c r="BI64" s="4"/>
+      <c r="BJ64" s="4"/>
+      <c r="BK64" s="4"/>
+      <c r="BL64" s="4"/>
+      <c r="BM64" s="4"/>
+    </row>
+    <row r="65" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65" s="4"/>
+      <c r="C65" s="4"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="4"/>
+      <c r="H65" s="4"/>
+      <c r="I65" s="4"/>
+      <c r="J65" s="4"/>
+      <c r="K65" s="4"/>
+      <c r="L65" s="4"/>
+      <c r="M65" s="4"/>
+      <c r="N65" s="4"/>
+      <c r="O65" s="4"/>
+      <c r="P65" s="4"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="4"/>
+      <c r="T65" s="4"/>
+      <c r="U65" s="4"/>
+      <c r="V65" s="4"/>
+      <c r="W65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="4"/>
+      <c r="AB65" s="4"/>
+      <c r="AC65" s="4"/>
+      <c r="AD65" s="4"/>
+      <c r="AE65" s="4"/>
+      <c r="AF65" s="4"/>
+      <c r="AG65" s="4"/>
+      <c r="AH65" s="4"/>
+      <c r="AI65" s="4"/>
+      <c r="AJ65" s="4"/>
+      <c r="AK65" s="4"/>
+      <c r="AL65" s="4"/>
+      <c r="AM65" s="4"/>
+      <c r="AN65" s="4"/>
+      <c r="AO65" s="4"/>
+      <c r="AP65" s="4"/>
+      <c r="AQ65" s="4"/>
+      <c r="AR65" s="4"/>
+      <c r="AS65" s="4"/>
+      <c r="AT65" s="4"/>
+      <c r="AU65" s="4"/>
+      <c r="AV65" s="4"/>
+      <c r="AW65" s="4"/>
+      <c r="AX65" s="4"/>
+      <c r="AY65" s="4"/>
+      <c r="AZ65" s="4"/>
+      <c r="BA65" s="4"/>
+      <c r="BB65" s="4"/>
+      <c r="BC65" s="4"/>
+      <c r="BD65" s="4"/>
+      <c r="BE65" s="4"/>
+      <c r="BF65" s="4"/>
+      <c r="BG65" s="4"/>
+      <c r="BH65" s="4"/>
+      <c r="BI65" s="4"/>
+      <c r="BJ65" s="4"/>
+      <c r="BK65" s="4"/>
+      <c r="BL65" s="4"/>
+      <c r="BM65" s="4"/>
+    </row>
+    <row r="66" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="4"/>
+      <c r="I66" s="4"/>
+      <c r="J66" s="4"/>
+      <c r="K66" s="4"/>
+      <c r="L66" s="4"/>
+      <c r="M66" s="4"/>
+      <c r="N66" s="4"/>
+      <c r="O66" s="4"/>
+      <c r="P66" s="4"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="4"/>
+      <c r="T66" s="4"/>
+      <c r="U66" s="4"/>
+      <c r="V66" s="4"/>
+      <c r="W66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="4"/>
+      <c r="AB66" s="4"/>
+      <c r="AC66" s="4"/>
+      <c r="AD66" s="4"/>
+      <c r="AE66" s="4"/>
+      <c r="AF66" s="4"/>
+      <c r="AG66" s="4"/>
+      <c r="AH66" s="4"/>
+      <c r="AI66" s="4"/>
+      <c r="AJ66" s="4"/>
+      <c r="AK66" s="4"/>
+      <c r="AL66" s="4"/>
+      <c r="AM66" s="4"/>
+      <c r="AN66" s="4"/>
+      <c r="AO66" s="4"/>
+      <c r="AP66" s="4"/>
+      <c r="AQ66" s="4"/>
+      <c r="AR66" s="4"/>
+      <c r="AS66" s="4"/>
+      <c r="AT66" s="4"/>
+      <c r="AU66" s="4"/>
+      <c r="AV66" s="4"/>
+      <c r="AW66" s="4"/>
+      <c r="AX66" s="4"/>
+      <c r="AY66" s="4"/>
+      <c r="AZ66" s="4"/>
+      <c r="BA66" s="4"/>
+      <c r="BB66" s="4"/>
+      <c r="BC66" s="4"/>
+      <c r="BD66" s="4"/>
+      <c r="BE66" s="4"/>
+      <c r="BF66" s="4"/>
+      <c r="BG66" s="4"/>
+      <c r="BH66" s="4"/>
+      <c r="BI66" s="4"/>
+      <c r="BJ66" s="4"/>
+      <c r="BK66" s="4"/>
+      <c r="BL66" s="4"/>
+      <c r="BM66" s="4"/>
+    </row>
+    <row r="67" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B67" s="4"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
+      <c r="AB67" s="4"/>
+      <c r="AC67" s="4"/>
+      <c r="AD67" s="4"/>
+      <c r="AE67" s="4"/>
+      <c r="AF67" s="4"/>
+      <c r="AG67" s="4"/>
+      <c r="AH67" s="4"/>
+      <c r="AI67" s="4"/>
+      <c r="AJ67" s="4"/>
+      <c r="AK67" s="4"/>
+      <c r="AL67" s="4"/>
+      <c r="AM67" s="4"/>
+      <c r="AN67" s="4"/>
+      <c r="AO67" s="4"/>
+      <c r="AP67" s="4"/>
+      <c r="AQ67" s="4"/>
+      <c r="AR67" s="4"/>
+      <c r="AS67" s="4"/>
+      <c r="AT67" s="4"/>
+      <c r="AU67" s="4"/>
+      <c r="AV67" s="4"/>
+      <c r="AW67" s="4"/>
+      <c r="AX67" s="4"/>
+      <c r="AY67" s="4"/>
+      <c r="AZ67" s="4"/>
+      <c r="BA67" s="4"/>
+      <c r="BB67" s="4"/>
+      <c r="BC67" s="4"/>
+      <c r="BD67" s="4"/>
+      <c r="BE67" s="4"/>
+      <c r="BF67" s="4"/>
+      <c r="BG67" s="4"/>
+      <c r="BH67" s="4"/>
+      <c r="BI67" s="4"/>
+      <c r="BJ67" s="4"/>
+      <c r="BK67" s="4"/>
+      <c r="BL67" s="4"/>
+      <c r="BM67" s="4"/>
+    </row>
+    <row r="68" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="4"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="4"/>
+      <c r="AB68" s="4"/>
+      <c r="AC68" s="4"/>
+      <c r="AD68" s="4"/>
+      <c r="AE68" s="4"/>
+      <c r="AF68" s="4"/>
+      <c r="AG68" s="4"/>
+      <c r="AH68" s="4"/>
+      <c r="AI68" s="4"/>
+      <c r="AJ68" s="4"/>
+      <c r="AK68" s="4"/>
+      <c r="AL68" s="4"/>
+      <c r="AM68" s="4"/>
+      <c r="AN68" s="4"/>
+      <c r="AO68" s="4"/>
+      <c r="AP68" s="4"/>
+      <c r="AQ68" s="4"/>
+      <c r="AR68" s="4"/>
+      <c r="AS68" s="4"/>
+      <c r="AT68" s="4"/>
+      <c r="AU68" s="4"/>
+      <c r="AV68" s="4"/>
+      <c r="AW68" s="4"/>
+      <c r="AX68" s="4"/>
+      <c r="AY68" s="4"/>
+      <c r="AZ68" s="4"/>
+      <c r="BA68" s="4"/>
+      <c r="BB68" s="4"/>
+      <c r="BC68" s="4"/>
+      <c r="BD68" s="4"/>
+      <c r="BE68" s="4"/>
+      <c r="BF68" s="4"/>
+      <c r="BG68" s="4"/>
+      <c r="BH68" s="4"/>
+      <c r="BI68" s="4"/>
+      <c r="BJ68" s="4"/>
+      <c r="BK68" s="4"/>
+      <c r="BL68" s="4"/>
+      <c r="BM68" s="4"/>
+    </row>
+    <row r="69" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B69" s="4"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="4"/>
+      <c r="AB69" s="4"/>
+      <c r="AC69" s="4"/>
+      <c r="AD69" s="4"/>
+      <c r="AE69" s="4"/>
+      <c r="AF69" s="4"/>
+      <c r="AG69" s="4"/>
+      <c r="AH69" s="4"/>
+      <c r="AI69" s="4"/>
+      <c r="AJ69" s="4"/>
+      <c r="AK69" s="4"/>
+      <c r="AL69" s="4"/>
+      <c r="AM69" s="4"/>
+      <c r="AN69" s="4"/>
+      <c r="AO69" s="4"/>
+      <c r="AP69" s="4"/>
+      <c r="AQ69" s="4"/>
+      <c r="AR69" s="4"/>
+      <c r="AS69" s="4"/>
+      <c r="AT69" s="4"/>
+      <c r="AU69" s="4"/>
+      <c r="AV69" s="4"/>
+      <c r="AW69" s="4"/>
+      <c r="AX69" s="4"/>
+      <c r="AY69" s="4"/>
+      <c r="AZ69" s="4"/>
+      <c r="BA69" s="4"/>
+      <c r="BB69" s="4"/>
+      <c r="BC69" s="4"/>
+      <c r="BD69" s="4"/>
+      <c r="BE69" s="4"/>
+      <c r="BF69" s="4"/>
+      <c r="BG69" s="4"/>
+      <c r="BH69" s="4"/>
+      <c r="BI69" s="4"/>
+      <c r="BJ69" s="4"/>
+      <c r="BK69" s="4"/>
+      <c r="BL69" s="4"/>
+      <c r="BM69" s="4"/>
+    </row>
+    <row r="70" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
+      <c r="T70" s="4"/>
+      <c r="U70" s="4"/>
+      <c r="V70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+      <c r="AA70" s="4"/>
+      <c r="AB70" s="4"/>
+      <c r="AC70" s="4"/>
+      <c r="AD70" s="4"/>
+      <c r="AE70" s="4"/>
+      <c r="AF70" s="4"/>
+      <c r="AG70" s="4"/>
+      <c r="AH70" s="4"/>
+      <c r="AI70" s="4"/>
+      <c r="AJ70" s="4"/>
+      <c r="AK70" s="4"/>
+      <c r="AL70" s="4"/>
+      <c r="AM70" s="4"/>
+      <c r="AN70" s="4"/>
+      <c r="AO70" s="4"/>
+      <c r="AP70" s="4"/>
+      <c r="AQ70" s="4"/>
+      <c r="AR70" s="4"/>
+      <c r="AS70" s="4"/>
+      <c r="AT70" s="4"/>
+      <c r="AU70" s="4"/>
+      <c r="AV70" s="4"/>
+      <c r="AW70" s="4"/>
+      <c r="AX70" s="4"/>
+      <c r="AY70" s="4"/>
+      <c r="AZ70" s="4"/>
+      <c r="BA70" s="4"/>
+      <c r="BB70" s="4"/>
+      <c r="BC70" s="4"/>
+      <c r="BD70" s="4"/>
+      <c r="BE70" s="4"/>
+      <c r="BF70" s="4"/>
+      <c r="BG70" s="4"/>
+      <c r="BH70" s="4"/>
+      <c r="BI70" s="4"/>
+      <c r="BJ70" s="4"/>
+      <c r="BK70" s="4"/>
+      <c r="BL70" s="4"/>
+      <c r="BM70" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="64">
     <mergeCell ref="A1:BI1"/>
     <mergeCell ref="BJ1:BM1"/>
     <mergeCell ref="A2:BM2"/>
@@ -25105,18 +27717,31 @@
     <mergeCell ref="B37:E37"/>
     <mergeCell ref="B38:E38"/>
     <mergeCell ref="B39:E39"/>
-    <mergeCell ref="A41:V41"/>
-    <mergeCell ref="A47:BM47"/>
-    <mergeCell ref="A48:BM48"/>
-    <mergeCell ref="A49:BM49"/>
-    <mergeCell ref="A50:BM50"/>
-    <mergeCell ref="A51:BM51"/>
-    <mergeCell ref="A52:BM52"/>
-    <mergeCell ref="A53:BM53"/>
-    <mergeCell ref="A54:BM54"/>
-    <mergeCell ref="A55:BM55"/>
-    <mergeCell ref="A56:BM56"/>
-    <mergeCell ref="A57:BM57"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="A54:V54"/>
+    <mergeCell ref="A60:BM60"/>
+    <mergeCell ref="A61:BM61"/>
+    <mergeCell ref="A62:BM62"/>
+    <mergeCell ref="A63:BM63"/>
+    <mergeCell ref="A64:BM64"/>
+    <mergeCell ref="A65:BM65"/>
+    <mergeCell ref="A66:BM66"/>
+    <mergeCell ref="A67:BM67"/>
+    <mergeCell ref="A68:BM68"/>
+    <mergeCell ref="A69:BM69"/>
+    <mergeCell ref="A70:BM70"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>

--- a/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
+++ b/tratando_tabelas/ac_coelho/entradas_ac_coelho.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2032" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1832" uniqueCount="291">
   <si>
     <t xml:space="preserve">Santri ADM 1.1.5.7 R1</t>
   </si>
   <si>
-    <t xml:space="preserve">Emitido em: 22/05/2026 05:30:31</t>
+    <t xml:space="preserve">Emitido em: 25/05/2026 07:37:38</t>
   </si>
   <si>
     <t xml:space="preserve">Relação de entradas - Sintético</t>
@@ -262,567 +262,453 @@
     <t xml:space="preserve">Não</t>
   </si>
   <si>
-    <t xml:space="preserve">32.615 - MADELUSTRE INDUSTRIAL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">71.328</t>
+    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.976.319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.756,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">757.173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.265,79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - FILIAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">08/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.702,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260527254297000178550010000105531584622070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640.215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.963,92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006402151526143499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640.584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.104,02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006405841317875822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.318 - CORTAG INDUSTRIA E COMERCIO LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">872.917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.671,17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260500808396000521550010008729171646262800</t>
+  </si>
+  <si>
+    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">867.224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.825,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260581604803000157550010008672241503823847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">481,59</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050855671736636271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.065 - LUXMUNDO COMERCIO IMPORTACAO EXPORTACAO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.783,20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.647 - ACCERT TRANSPORTES E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86,50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260529244900000247550010000673361492026159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260505222092001069570010000389411006647635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">642.487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.040,61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006424871547022207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.167 - ATLAS S.A.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">688.063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/07/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.401,84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43260589723837000172550000006880631168529645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.101 - SIMON MATERIAIS ELETRICOS E ELETRONICOS LTDA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">447,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31260507159430000361550010000876141954082958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.620</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.671,51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31260507159430000361550010000876201881086441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.238 - EURO METAIS IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">66.587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">319,81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29260510317038000146550010000665871272565371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.015 - FOCO METALLO FABRICACAO E MONTAGEM DE LUMINARIAS E COMERCIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.140,30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.724.082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.618 - ALFA TRANSPORTES EIRELI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">242,33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260522670837000180550010000233691542222518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260582110818000121570000077240821090348638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.444 - PRIME BRAS SEGURANCA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.460,00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260532296669000169550030000014561732534080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.628 - VFL IMPORTADORA E DISTRIBUIDORA LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.723,65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260505104359000122550010000046771737179198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">355,13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050855751937497947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050856531939175139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.085.654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260597837181002190550010050856541425368248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">643.141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.362,82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006431411980070203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">874.261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.526,29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260500808396000521550010008742611312671522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">643.989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.012,18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006439891906994593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.228 - H. IMPORTS IMPORTACAO E EXPORTACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.949,49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260522091324000204550030000068451624550441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">871.218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.936,45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008712181667035989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">871.209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">450,89</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260552618139002817550030008712091653128395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.356 - H. IMPORTS IMPORTACAO E EXPORTACAO EIRELI-EPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.398,04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260522091324000115550010000517391644084487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19 - TRAMONTINA PLANALTO S/A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.239,72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260500142240000120550010007112461929672564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.765 - PLENA INDUSTRIA E COMERCIO DE ESQUADRIAS DE ALUMINIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.147,58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35260510365014000162550010000461591344097371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.599 - KADESH CALCADOS PROFISSIONAIS LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337.381</t>
   </si>
   <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">05/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">02/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.012,28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260589616460000152550020000713281306751109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">547 - LORENZETTI S/A INDU.BRASILEIRAS ELETROMETALURGICAS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.976.319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">06/08/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.756,80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260561413282000143550010029763191755416419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">669 - BLUKIT INDUSTRIA DE PLASTICOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">757.173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.265,79</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - FILIAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007571731618335301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.856 - DEXCO S.A - METAIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804111200730267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804981991793601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.080.412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050804121347149640</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.929,60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829821661840971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.082.996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">461,96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050829961140036509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">761 - DOCOL FV IND.E COM. DE METAIS SANITARIOS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">638.725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.887,04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006387251174884389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.941 - AQUECE METAIS FABRICACAO E MANUTENCAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">08/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.702,49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260527254297000178550010000105531584622070</t>
-  </si>
-  <si>
-    <t xml:space="preserve">775 - BLUKIT METALURGICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.709,55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260581604803000157550010008671441582155041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">639.745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.078,63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006397451885129080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">640.215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.963,92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006402151526143499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">640.584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.104,02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006405841317875822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.318 - CORTAG INDUSTRIA E COMERCIO LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">872.917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.671,17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260500808396000521550010008729171646262800</t>
-  </si>
-  <si>
-    <t xml:space="preserve">867.224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.825,13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260581604803000157550010008672241503823847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">641.031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">499,53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006410311154255425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.085.567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">481,59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050855671736636271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.065 - LUXMUNDO COMERCIO IMPORTACAO EXPORTACAO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.783,20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.647 - ACCERT TRANSPORTES E LOGISTICA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">86,50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29260529244900000247550010000673361492026159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29260505222092001069570010000389411006647635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">758.826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">785,04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260509641520000158550010007588261717357519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">642.487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.040,61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006424871547022207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.167 - ATLAS S.A.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">688.063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/07/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.401,84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43260589723837000172550000006880631168529645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.101 - SIMON MATERIAIS ELETRICOS E ELETRONICOS LTDA.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">447,13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31260507159430000361550010000876141954082958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">87.620</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.671,51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31260507159430000361550010000876201881086441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.238 - EURO METAIS IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">66.587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">319,81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29260510317038000146550010000665871272565371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.015 - FOCO METALLO FABRICACAO E MONTAGEM DE LUMINARIAS E COMERCIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.140,30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.724.082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.618 - ALFA TRANSPORTES EIRELI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">242,33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260522670837000180550010000233691542222518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260582110818000121570000077240821090348638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.444 - PRIME BRAS SEGURANCA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.460,00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260532296669000169550030000014561732534080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.628 - VFL IMPORTADORA E DISTRIBUIDORA LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.723,65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52260505104359000122550010000046771737179198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.085.575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">355,13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050855751937497947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.085.653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050856531939175139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.085.654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260597837181002190550010050856541425368248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">643.141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.362,82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006431411980070203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">874.261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.526,29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260500808396000521550010008742611312671522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">643.989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19/05/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.012,18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260575339051000141550080006439891906994593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.228 - H. IMPORTS IMPORTACAO E EXPORTACAO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.949,49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42260522091324000204550030000068451624550441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.848 - LEGRAND BRASIL LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">871.218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.936,45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008712181667035989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">871.209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">450,89</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260552618139002817550030008712091653128395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.356 - H. IMPORTS IMPORTACAO E EXPORTACAO EIRELI-EPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.398,04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260522091324000115550010000517391644084487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19 - TRAMONTINA PLANALTO S/A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">711.246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.239,72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52260500142240000120550010007112461929672564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.765 - PLENA INDUSTRIA E COMERCIO DE ESQUADRIAS DE ALUMINIO LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24/06/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.147,58</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35260510365014000162550010000461591344097371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.599 - KADESH CALCADOS PROFISSIONAIS LTDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">337.381</t>
-  </si>
-  <si>
     <t xml:space="preserve">32.424,00</t>
   </si>
   <si>
@@ -884,6 +770,72 @@
   </si>
   <si>
     <t xml:space="preserve">35260510365014000162550010000461581611112280</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.379 - ASSA ABLOY BRASIL INDUSTRIA E COMERCIO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220.876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.088,73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25260502214604000328550030002208761881870307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">711.225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">547,85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52260500142240000120550010007112251212108404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">645.275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.024,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006452751334250174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.940 - BLUMENAU ILUMINACAO LTDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">819.755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.403,36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260579416459000120550010008197551476543872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">646.634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.239,80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006466341219816342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">647.516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19/06/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.630,68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42260575339051000141550080006475161954616188</t>
   </si>
   <si>
     <t xml:space="preserve">Total geral</t>
@@ -17129,7 +17081,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:BM70"/>
+  <dimension ref="A1:BM65"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="1" style="0" width="18"/>
@@ -17692,7 +17644,7 @@
     </row>
     <row r="6" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="n">
-        <v>306769</v>
+        <v>307020</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>80</v>
@@ -17704,67 +17656,67 @@
         <v>81</v>
       </c>
       <c r="G6" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="J6" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>5012.28</v>
+        <v>1756.8</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O6" s="12" t="n">
-        <v>4567</v>
+        <v>1756.8</v>
       </c>
       <c r="P6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q6" s="13" t="n">
-        <v>0</v>
+        <v>0.142272</v>
       </c>
       <c r="R6" s="12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T6" s="14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U6" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V6" s="12" t="n">
-        <v>40.75</v>
+        <v>90</v>
       </c>
       <c r="W6" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X6" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Y6" s="12" t="n">
-        <v>445.28</v>
+        <v>0</v>
       </c>
       <c r="Z6" s="12" t="n">
-        <v>4567</v>
+        <v>1756.8</v>
       </c>
       <c r="AA6" s="12" t="n">
-        <v>319.68</v>
+        <v>122.98</v>
       </c>
       <c r="AB6" s="12" t="n">
         <v>0</v>
@@ -17830,7 +17782,7 @@
         <v>74</v>
       </c>
       <c r="AW6" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AX6" s="10" t="s">
         <v>87</v>
@@ -17883,7 +17835,7 @@
     </row>
     <row r="7" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="n">
-        <v>307020</v>
+        <v>307133</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>89</v>
@@ -17898,64 +17850,64 @@
         <v>66</v>
       </c>
       <c r="H7" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="I7" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="J7" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>93</v>
       </c>
       <c r="K7" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>1756.8</v>
+        <v>4265.79</v>
       </c>
       <c r="M7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O7" s="12" t="n">
-        <v>1756.8</v>
+        <v>4222.88</v>
       </c>
       <c r="P7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q7" s="13" t="n">
-        <v>0.142272</v>
+        <v>0.484131</v>
       </c>
       <c r="R7" s="12" t="n">
-        <v>3.42</v>
+        <v>71.4</v>
       </c>
       <c r="S7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T7" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="U7" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V7" s="12" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="W7" s="9" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="X7" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Y7" s="12" t="n">
-        <v>0</v>
+        <v>42.91</v>
       </c>
       <c r="Z7" s="12" t="n">
-        <v>1756.8</v>
+        <v>4222.88</v>
       </c>
       <c r="AA7" s="12" t="n">
-        <v>122.98</v>
+        <v>281.12</v>
       </c>
       <c r="AB7" s="12" t="n">
         <v>0</v>
@@ -18021,7 +17973,7 @@
         <v>74</v>
       </c>
       <c r="AW7" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX7" s="10" t="s">
         <v>87</v>
@@ -18060,7 +18012,7 @@
         <v>69</v>
       </c>
       <c r="BJ7" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="BK7" s="9" t="s">
         <v>75</v>
@@ -18074,79 +18026,79 @@
     </row>
     <row r="8" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="n">
-        <v>307133</v>
+        <v>307265</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="F8" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="I8" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8" s="9" t="s">
         <v>99</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>100</v>
       </c>
       <c r="K8" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>4265.79</v>
+        <v>3702.49</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O8" s="12" t="n">
-        <v>4222.88</v>
+        <v>3437.49</v>
       </c>
       <c r="P8" s="12" t="n">
-        <v>0</v>
+        <v>265</v>
       </c>
       <c r="Q8" s="13" t="n">
-        <v>0.484131</v>
+        <v>0</v>
       </c>
       <c r="R8" s="12" t="n">
-        <v>71.4</v>
+        <v>3.5</v>
       </c>
       <c r="S8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T8" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U8" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V8" s="12" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="W8" s="9" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="X8" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Y8" s="12" t="n">
-        <v>42.91</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="12" t="n">
-        <v>4222.88</v>
+        <v>3702.49</v>
       </c>
       <c r="AA8" s="12" t="n">
-        <v>281.12</v>
+        <v>259.17</v>
       </c>
       <c r="AB8" s="12" t="n">
         <v>0</v>
@@ -18212,7 +18164,7 @@
         <v>74</v>
       </c>
       <c r="AW8" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX8" s="10" t="s">
         <v>87</v>
@@ -18251,7 +18203,7 @@
         <v>69</v>
       </c>
       <c r="BJ8" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="BK8" s="9" t="s">
         <v>75</v>
@@ -18265,34 +18217,34 @@
     </row>
     <row r="9" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="n">
-        <v>307171</v>
+        <v>307334</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>91</v>
-      </c>
       <c r="I9" s="9" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="K9" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>404.81</v>
+        <v>4963.92</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>0</v>
@@ -18301,43 +18253,43 @@
         <v>1</v>
       </c>
       <c r="O9" s="12" t="n">
-        <v>404.81</v>
+        <v>4963.92</v>
       </c>
       <c r="P9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.029904</v>
       </c>
       <c r="R9" s="12" t="n">
-        <v>2.43</v>
+        <v>6.84</v>
       </c>
       <c r="S9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T9" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="U9" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V9" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W9" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X9" s="9" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="Y9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="12" t="n">
-        <v>404.81</v>
+        <v>4963.92</v>
       </c>
       <c r="AA9" s="12" t="n">
-        <v>16.19</v>
+        <v>347.47</v>
       </c>
       <c r="AB9" s="12" t="n">
         <v>0</v>
@@ -18403,10 +18355,10 @@
         <v>74</v>
       </c>
       <c r="AW9" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX9" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="AY9" s="14" t="s">
         <v>75</v>
@@ -18456,10 +18408,10 @@
     </row>
     <row r="10" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="n">
-        <v>307173</v>
+        <v>307356</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -18468,22 +18420,22 @@
         <v>109</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="K10" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>404.81</v>
+        <v>2104.02</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>0</v>
@@ -18492,43 +18444,43 @@
         <v>1</v>
       </c>
       <c r="O10" s="12" t="n">
-        <v>404.81</v>
+        <v>2104.02</v>
       </c>
       <c r="P10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.005548</v>
       </c>
       <c r="R10" s="12" t="n">
-        <v>2.43</v>
+        <v>1.08</v>
       </c>
       <c r="S10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T10" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="U10" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V10" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W10" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X10" s="9" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="Y10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z10" s="12" t="n">
-        <v>404.81</v>
+        <v>2104.02</v>
       </c>
       <c r="AA10" s="12" t="n">
-        <v>16.19</v>
+        <v>147.28</v>
       </c>
       <c r="AB10" s="12" t="n">
         <v>0</v>
@@ -18594,10 +18546,10 @@
         <v>74</v>
       </c>
       <c r="AW10" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX10" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="AY10" s="14" t="s">
         <v>75</v>
@@ -18633,7 +18585,7 @@
         <v>69</v>
       </c>
       <c r="BJ10" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="BK10" s="9" t="s">
         <v>75</v>
@@ -18647,79 +18599,79 @@
     </row>
     <row r="11" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="n">
-        <v>307174</v>
+        <v>307367</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G11" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="K11" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>404.81</v>
+        <v>5671.17</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>404.81</v>
+        <v>5538.68</v>
       </c>
       <c r="P11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="13" t="n">
-        <v>0.000858</v>
+        <v>0.314926</v>
       </c>
       <c r="R11" s="12" t="n">
-        <v>2.43</v>
+        <v>33.19</v>
       </c>
       <c r="S11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T11" s="14" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="U11" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V11" s="12" t="n">
-        <v>0</v>
+        <v>55.35</v>
       </c>
       <c r="W11" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X11" s="9" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="Y11" s="12" t="n">
-        <v>0</v>
+        <v>132.49</v>
       </c>
       <c r="Z11" s="12" t="n">
-        <v>404.81</v>
+        <v>4787.31</v>
       </c>
       <c r="AA11" s="12" t="n">
-        <v>16.19</v>
+        <v>258.23</v>
       </c>
       <c r="AB11" s="12" t="n">
         <v>0</v>
@@ -18785,10 +18737,10 @@
         <v>74</v>
       </c>
       <c r="AW11" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX11" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="AY11" s="14" t="s">
         <v>75</v>
@@ -18824,7 +18776,7 @@
         <v>69</v>
       </c>
       <c r="BJ11" s="9" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="BK11" s="9" t="s">
         <v>75</v>
@@ -18838,64 +18790,64 @@
     </row>
     <row r="12" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="n">
-        <v>307231</v>
+        <v>307369</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I12" s="9" t="s">
         <v>114</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
       <c r="K12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>2929.6</v>
+        <v>1825.13</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" s="12" t="n">
-        <v>2929.6</v>
+        <v>1767.68</v>
       </c>
       <c r="P12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" s="13" t="n">
-        <v>0.000484</v>
+        <v>0.025844</v>
       </c>
       <c r="R12" s="12" t="n">
-        <v>3.22</v>
+        <v>6.79</v>
       </c>
       <c r="S12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T12" s="14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U12" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V12" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="W12" s="9" t="s">
         <v>73</v>
@@ -18904,13 +18856,13 @@
         <v>114</v>
       </c>
       <c r="Y12" s="12" t="n">
-        <v>0</v>
+        <v>57.45</v>
       </c>
       <c r="Z12" s="12" t="n">
-        <v>2929.6</v>
+        <v>1767.68</v>
       </c>
       <c r="AA12" s="12" t="n">
-        <v>205.07</v>
+        <v>110.47</v>
       </c>
       <c r="AB12" s="12" t="n">
         <v>0</v>
@@ -18976,10 +18928,10 @@
         <v>74</v>
       </c>
       <c r="AW12" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX12" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY12" s="14" t="s">
         <v>75</v>
@@ -19015,7 +18967,7 @@
         <v>69</v>
       </c>
       <c r="BJ12" s="9" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="BK12" s="9" t="s">
         <v>75</v>
@@ -19029,34 +18981,34 @@
     </row>
     <row r="13" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="n">
-        <v>307235</v>
+        <v>307386</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="I13" s="9" t="s">
         <v>114</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>69</v>
+        <v>124</v>
       </c>
       <c r="K13" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>461.96</v>
+        <v>481.59</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>0</v>
@@ -19065,28 +19017,28 @@
         <v>1</v>
       </c>
       <c r="O13" s="12" t="n">
-        <v>461.96</v>
+        <v>481.59</v>
       </c>
       <c r="P13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q13" s="13" t="n">
-        <v>0.002057</v>
+        <v>0.002268</v>
       </c>
       <c r="R13" s="12" t="n">
-        <v>2.43</v>
+        <v>0.44</v>
       </c>
       <c r="S13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T13" s="14" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="U13" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V13" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="W13" s="9" t="s">
         <v>73</v>
@@ -19098,10 +19050,10 @@
         <v>0</v>
       </c>
       <c r="Z13" s="12" t="n">
-        <v>461.96</v>
+        <v>481.59</v>
       </c>
       <c r="AA13" s="12" t="n">
-        <v>18.48</v>
+        <v>19.26</v>
       </c>
       <c r="AB13" s="12" t="n">
         <v>0</v>
@@ -19167,10 +19119,10 @@
         <v>74</v>
       </c>
       <c r="AW13" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX13" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="AY13" s="14" t="s">
         <v>75</v>
@@ -19206,7 +19158,7 @@
         <v>69</v>
       </c>
       <c r="BJ13" s="9" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="BK13" s="9" t="s">
         <v>75</v>
@@ -19220,79 +19172,79 @@
     </row>
     <row r="14" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="n">
-        <v>307242</v>
+        <v>307424</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>124</v>
+        <v>69</v>
       </c>
       <c r="K14" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>1887.04</v>
+        <v>1783.2</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O14" s="12" t="n">
-        <v>1887.04</v>
+        <v>1624.79</v>
       </c>
       <c r="P14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q14" s="13" t="n">
-        <v>0.007832</v>
+        <v>0</v>
       </c>
       <c r="R14" s="12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T14" s="14" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="U14" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V14" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W14" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X14" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="Y14" s="12" t="n">
-        <v>0</v>
+        <v>158.41</v>
       </c>
       <c r="Z14" s="12" t="n">
-        <v>1887.04</v>
+        <v>1624.79</v>
       </c>
       <c r="AA14" s="12" t="n">
-        <v>132.09</v>
+        <v>65.04</v>
       </c>
       <c r="AB14" s="12" t="n">
         <v>0</v>
@@ -19301,7 +19253,7 @@
         <v>0</v>
       </c>
       <c r="AD14" s="12" t="n">
-        <v>0</v>
+        <v>86.5</v>
       </c>
       <c r="AE14" s="12" t="n">
         <v>0</v>
@@ -19358,10 +19310,10 @@
         <v>74</v>
       </c>
       <c r="AW14" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX14" s="10" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="AY14" s="14" t="s">
         <v>75</v>
@@ -19382,25 +19334,25 @@
         <v>75</v>
       </c>
       <c r="BE14" s="14" t="s">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="BF14" s="9" t="s">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="BG14" s="9" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="BH14" s="14" t="s">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="BI14" s="9" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="BJ14" s="9" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="BK14" s="9" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="BL14" s="9" t="s">
         <v>75</v>
@@ -19411,34 +19363,34 @@
     </row>
     <row r="15" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="n">
-        <v>307265</v>
+        <v>307433</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>92</v>
+        <v>137</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="K15" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>3702.49</v>
+        <v>1040.61</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>0</v>
@@ -19447,43 +19399,43 @@
         <v>1</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>3437.49</v>
+        <v>977.1</v>
       </c>
       <c r="P15" s="12" t="n">
-        <v>265</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="13" t="n">
         <v>0</v>
       </c>
       <c r="R15" s="12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T15" s="14" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="U15" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V15" s="12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="W15" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X15" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="Y15" s="12" t="n">
-        <v>0</v>
+        <v>63.51</v>
       </c>
       <c r="Z15" s="12" t="n">
-        <v>3702.49</v>
+        <v>977.1</v>
       </c>
       <c r="AA15" s="12" t="n">
-        <v>259.17</v>
+        <v>68.4</v>
       </c>
       <c r="AB15" s="12" t="n">
         <v>0</v>
@@ -19549,7 +19501,7 @@
         <v>74</v>
       </c>
       <c r="AW15" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX15" s="10" t="s">
         <v>87</v>
@@ -19588,7 +19540,7 @@
         <v>69</v>
       </c>
       <c r="BJ15" s="9" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="BK15" s="9" t="s">
         <v>75</v>
@@ -19602,79 +19554,79 @@
     </row>
     <row r="16" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="n">
-        <v>307278</v>
+        <v>307439</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>66</v>
+        <v>143</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="K16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>29709.55</v>
+        <v>2401.84</v>
       </c>
       <c r="M16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>29280.46</v>
+        <v>2401.84</v>
       </c>
       <c r="P16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>0.69578</v>
+        <v>0.29576</v>
       </c>
       <c r="R16" s="12" t="n">
-        <v>130.96</v>
+        <v>31.68</v>
       </c>
       <c r="S16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T16" s="14" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="U16" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V16" s="12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="W16" s="9" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="X16" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="Y16" s="12" t="n">
-        <v>429.09</v>
+        <v>0</v>
       </c>
       <c r="Z16" s="12" t="n">
-        <v>29280.46</v>
+        <v>2401.84</v>
       </c>
       <c r="AA16" s="12" t="n">
-        <v>1794.18</v>
+        <v>149.08</v>
       </c>
       <c r="AB16" s="12" t="n">
         <v>0</v>
@@ -19740,7 +19692,7 @@
         <v>74</v>
       </c>
       <c r="AW16" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX16" s="10" t="s">
         <v>87</v>
@@ -19779,7 +19731,7 @@
         <v>69</v>
       </c>
       <c r="BJ16" s="9" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="BK16" s="9" t="s">
         <v>75</v>
@@ -19793,34 +19745,34 @@
     </row>
     <row r="17" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="n">
-        <v>307330</v>
+        <v>307443</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="K17" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>7078.63</v>
+        <v>447.13</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>0</v>
@@ -19829,43 +19781,43 @@
         <v>1</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>6646.6</v>
+        <v>433.06</v>
       </c>
       <c r="P17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q17" s="13" t="n">
-        <v>0.0425</v>
+        <v>0.0219</v>
       </c>
       <c r="R17" s="12" t="n">
-        <v>9.6</v>
+        <v>1.7</v>
       </c>
       <c r="S17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T17" s="14" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="U17" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V17" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W17" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="Y17" s="12" t="n">
-        <v>432.03</v>
+        <v>14.07</v>
       </c>
       <c r="Z17" s="12" t="n">
-        <v>6646.6</v>
+        <v>433.06</v>
       </c>
       <c r="AA17" s="12" t="n">
-        <v>465.26</v>
+        <v>30.31</v>
       </c>
       <c r="AB17" s="12" t="n">
         <v>0</v>
@@ -19931,7 +19883,7 @@
         <v>74</v>
       </c>
       <c r="AW17" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX17" s="10" t="s">
         <v>87</v>
@@ -19970,7 +19922,7 @@
         <v>69</v>
       </c>
       <c r="BJ17" s="9" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="BK17" s="9" t="s">
         <v>75</v>
@@ -19984,79 +19936,79 @@
     </row>
     <row r="18" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="n">
-        <v>307334</v>
+        <v>307444</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="C18" s="9"/>
       <c r="D18" s="9"/>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="K18" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>4963.92</v>
+        <v>24671.51</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="O18" s="12" t="n">
-        <v>4963.92</v>
+        <v>23273.18</v>
       </c>
       <c r="P18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q18" s="13" t="n">
-        <v>0.029904</v>
+        <v>3.54421</v>
       </c>
       <c r="R18" s="12" t="n">
-        <v>6.84</v>
+        <v>399.29</v>
       </c>
       <c r="S18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T18" s="14" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="U18" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V18" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="W18" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="Y18" s="12" t="n">
-        <v>0</v>
+        <v>1398.33</v>
       </c>
       <c r="Z18" s="12" t="n">
-        <v>4963.92</v>
+        <v>23273.18</v>
       </c>
       <c r="AA18" s="12" t="n">
-        <v>347.47</v>
+        <v>1629.14</v>
       </c>
       <c r="AB18" s="12" t="n">
         <v>0</v>
@@ -20122,7 +20074,7 @@
         <v>74</v>
       </c>
       <c r="AW18" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX18" s="10" t="s">
         <v>87</v>
@@ -20161,7 +20113,7 @@
         <v>69</v>
       </c>
       <c r="BJ18" s="9" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="BK18" s="9" t="s">
         <v>75</v>
@@ -20175,79 +20127,79 @@
     </row>
     <row r="19" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="n">
-        <v>307356</v>
+        <v>307462</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="9"/>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>123</v>
+        <v>66</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>138</v>
+        <v>105</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="K19" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>2104.02</v>
+        <v>319.81</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="12" t="n">
-        <v>2104.02</v>
+        <v>291.4</v>
       </c>
       <c r="P19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>0.005548</v>
+        <v>0.002146</v>
       </c>
       <c r="R19" s="12" t="n">
-        <v>1.08</v>
+        <v>0.53</v>
       </c>
       <c r="S19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T19" s="14" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="U19" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V19" s="12" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="W19" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X19" s="9" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="Y19" s="12" t="n">
-        <v>0</v>
+        <v>28.41</v>
       </c>
       <c r="Z19" s="12" t="n">
-        <v>2104.02</v>
+        <v>291.4</v>
       </c>
       <c r="AA19" s="12" t="n">
-        <v>147.28</v>
+        <v>11.65</v>
       </c>
       <c r="AB19" s="12" t="n">
         <v>0</v>
@@ -20313,7 +20265,7 @@
         <v>74</v>
       </c>
       <c r="AW19" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX19" s="10" t="s">
         <v>87</v>
@@ -20352,7 +20304,7 @@
         <v>69</v>
       </c>
       <c r="BJ19" s="9" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="BK19" s="9" t="s">
         <v>75</v>
@@ -20366,79 +20318,79 @@
     </row>
     <row r="20" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="n">
-        <v>307367</v>
+        <v>307465</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="K20" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>5671.17</v>
+        <v>1140.3</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O20" s="12" t="n">
-        <v>5538.68</v>
+        <v>1039</v>
       </c>
       <c r="P20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q20" s="13" t="n">
-        <v>0.314926</v>
+        <v>0.00479</v>
       </c>
       <c r="R20" s="12" t="n">
-        <v>33.19</v>
+        <v>0</v>
       </c>
       <c r="S20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T20" s="14" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="U20" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V20" s="12" t="n">
-        <v>55.35</v>
+        <v>28</v>
       </c>
       <c r="W20" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X20" s="9" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="Y20" s="12" t="n">
-        <v>132.49</v>
+        <v>101.3</v>
       </c>
       <c r="Z20" s="12" t="n">
-        <v>4787.31</v>
+        <v>1039</v>
       </c>
       <c r="AA20" s="12" t="n">
-        <v>258.23</v>
+        <v>72.73</v>
       </c>
       <c r="AB20" s="12" t="n">
         <v>0</v>
@@ -20447,7 +20399,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="12" t="n">
-        <v>0</v>
+        <v>242.33</v>
       </c>
       <c r="AE20" s="12" t="n">
         <v>0</v>
@@ -20504,7 +20456,7 @@
         <v>74</v>
       </c>
       <c r="AW20" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX20" s="10" t="s">
         <v>87</v>
@@ -20528,25 +20480,25 @@
         <v>75</v>
       </c>
       <c r="BE20" s="14" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="BF20" s="9" t="s">
-        <v>75</v>
+        <v>164</v>
       </c>
       <c r="BG20" s="9" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="BH20" s="14" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
       <c r="BI20" s="9" t="s">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="BJ20" s="9" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="BK20" s="9" t="s">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="BL20" s="9" t="s">
         <v>75</v>
@@ -20557,79 +20509,79 @@
     </row>
     <row r="21" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="n">
-        <v>307369</v>
+        <v>307471</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>132</v>
+        <v>168</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="9"/>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
       <c r="H21" s="9" t="s">
         <v>114</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>69</v>
+        <v>171</v>
       </c>
       <c r="K21" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>1825.13</v>
+        <v>7460</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O21" s="12" t="n">
-        <v>1767.68</v>
+        <v>7460</v>
       </c>
       <c r="P21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q21" s="13" t="n">
-        <v>0.025844</v>
+        <v>0.16454</v>
       </c>
       <c r="R21" s="12" t="n">
-        <v>6.79</v>
+        <v>25.2</v>
       </c>
       <c r="S21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="14" t="s">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="U21" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V21" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="W21" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X21" s="9" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="Y21" s="12" t="n">
-        <v>57.45</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="12" t="n">
-        <v>1767.68</v>
+        <v>7460</v>
       </c>
       <c r="AA21" s="12" t="n">
-        <v>110.47</v>
+        <v>895.2</v>
       </c>
       <c r="AB21" s="12" t="n">
         <v>0</v>
@@ -20695,10 +20647,10 @@
         <v>74</v>
       </c>
       <c r="AW21" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX21" s="10" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AY21" s="14" t="s">
         <v>75</v>
@@ -20734,7 +20686,7 @@
         <v>69</v>
       </c>
       <c r="BJ21" s="9" t="s">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="BK21" s="9" t="s">
         <v>75</v>
@@ -20748,79 +20700,79 @@
     </row>
     <row r="22" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="n">
-        <v>307376</v>
+        <v>307539</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>121</v>
+        <v>174</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I22" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>151</v>
-      </c>
       <c r="J22" s="9" t="s">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="K22" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>499.53</v>
+        <v>2723.65</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O22" s="12" t="n">
-        <v>499.53</v>
+        <v>2723.65</v>
       </c>
       <c r="P22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q22" s="13" t="n">
-        <v>0.000507</v>
+        <v>0.004185</v>
       </c>
       <c r="R22" s="12" t="n">
-        <v>1.07</v>
+        <v>3.07</v>
       </c>
       <c r="S22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T22" s="14" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="U22" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V22" s="12" t="n">
-        <v>28</v>
+        <v>61.33</v>
       </c>
       <c r="W22" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X22" s="9" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="Y22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z22" s="12" t="n">
-        <v>499.53</v>
+        <v>2723.65</v>
       </c>
       <c r="AA22" s="12" t="n">
-        <v>34.97</v>
+        <v>108.95</v>
       </c>
       <c r="AB22" s="12" t="n">
         <v>0</v>
@@ -20886,7 +20838,7 @@
         <v>74</v>
       </c>
       <c r="AW22" s="14" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="AX22" s="10" t="s">
         <v>87</v>
@@ -20925,7 +20877,7 @@
         <v>69</v>
       </c>
       <c r="BJ22" s="9" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="BK22" s="9" t="s">
         <v>75</v>
@@ -20939,34 +20891,34 @@
     </row>
     <row r="23" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="n">
-        <v>307386</v>
+        <v>307572</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>161</v>
+        <v>69</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>481.59</v>
+        <v>355.13</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>0</v>
@@ -20975,43 +20927,43 @@
         <v>1</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>481.59</v>
+        <v>355.13</v>
       </c>
       <c r="P23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q23" s="13" t="n">
-        <v>0.002268</v>
+        <v>0.00819</v>
       </c>
       <c r="R23" s="12" t="n">
-        <v>0.44</v>
+        <v>2.17</v>
       </c>
       <c r="S23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T23" s="14" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="U23" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V23" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W23" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X23" s="9" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="Y23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z23" s="12" t="n">
-        <v>481.59</v>
+        <v>355.13</v>
       </c>
       <c r="AA23" s="12" t="n">
-        <v>19.26</v>
+        <v>14.21</v>
       </c>
       <c r="AB23" s="12" t="n">
         <v>0</v>
@@ -21077,10 +21029,10 @@
         <v>74</v>
       </c>
       <c r="AW23" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX23" s="10" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="AY23" s="14" t="s">
         <v>75</v>
@@ -21116,7 +21068,7 @@
         <v>69</v>
       </c>
       <c r="BJ23" s="9" t="s">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="BK23" s="9" t="s">
         <v>75</v>
@@ -21130,16 +21082,16 @@
     </row>
     <row r="24" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="n">
-        <v>307424</v>
+        <v>307578</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>164</v>
+        <v>122</v>
       </c>
       <c r="C24" s="9"/>
       <c r="D24" s="9"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>66</v>
@@ -21148,7 +21100,7 @@
         <v>114</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J24" s="9" t="s">
         <v>69</v>
@@ -21157,31 +21109,31 @@
         <v>70</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>1783.2</v>
+        <v>355.13</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="O24" s="12" t="n">
-        <v>1624.79</v>
+        <v>355.13</v>
       </c>
       <c r="P24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q24" s="13" t="n">
-        <v>0</v>
+        <v>0.00819</v>
       </c>
       <c r="R24" s="12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T24" s="14" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="U24" s="15" t="s">
         <v>72</v>
@@ -21193,16 +21145,16 @@
         <v>73</v>
       </c>
       <c r="X24" s="9" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="Y24" s="12" t="n">
-        <v>158.41</v>
+        <v>0</v>
       </c>
       <c r="Z24" s="12" t="n">
-        <v>1624.79</v>
+        <v>355.13</v>
       </c>
       <c r="AA24" s="12" t="n">
-        <v>65.04</v>
+        <v>14.21</v>
       </c>
       <c r="AB24" s="12" t="n">
         <v>0</v>
@@ -21211,7 +21163,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="12" t="n">
-        <v>86.5</v>
+        <v>0</v>
       </c>
       <c r="AE24" s="12" t="n">
         <v>0</v>
@@ -21268,10 +21220,10 @@
         <v>74</v>
       </c>
       <c r="AW24" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX24" s="10" t="s">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AY24" s="14" t="s">
         <v>75</v>
@@ -21292,25 +21244,25 @@
         <v>75</v>
       </c>
       <c r="BE24" s="14" t="s">
-        <v>168</v>
+        <v>75</v>
       </c>
       <c r="BF24" s="9" t="s">
-        <v>169</v>
+        <v>75</v>
       </c>
       <c r="BG24" s="9" t="s">
-        <v>138</v>
+        <v>69</v>
       </c>
       <c r="BH24" s="14" t="s">
-        <v>170</v>
+        <v>75</v>
       </c>
       <c r="BI24" s="9" t="s">
-        <v>166</v>
+        <v>69</v>
       </c>
       <c r="BJ24" s="9" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="BK24" s="9" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="BL24" s="9" t="s">
         <v>75</v>
@@ -21321,79 +21273,79 @@
     </row>
     <row r="25" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="n">
-        <v>307428</v>
+        <v>307579</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
       <c r="E25" s="9"/>
       <c r="F25" s="9" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>66</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>174</v>
+        <v>69</v>
       </c>
       <c r="K25" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>785.04</v>
+        <v>355.13</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O25" s="12" t="n">
-        <v>785.04</v>
+        <v>355.13</v>
       </c>
       <c r="P25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q25" s="13" t="n">
-        <v>0.06696</v>
+        <v>0.00819</v>
       </c>
       <c r="R25" s="12" t="n">
-        <v>2.59</v>
+        <v>2.17</v>
       </c>
       <c r="S25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T25" s="14" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="U25" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V25" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="W25" s="9" t="s">
-        <v>102</v>
+        <v>73</v>
       </c>
       <c r="X25" s="9" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="Y25" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Z25" s="12" t="n">
-        <v>785.04</v>
+        <v>355.13</v>
       </c>
       <c r="AA25" s="12" t="n">
-        <v>54.95</v>
+        <v>14.21</v>
       </c>
       <c r="AB25" s="12" t="n">
         <v>0</v>
@@ -21459,10 +21411,10 @@
         <v>74</v>
       </c>
       <c r="AW25" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX25" s="10" t="s">
-        <v>87</v>
+        <v>181</v>
       </c>
       <c r="AY25" s="14" t="s">
         <v>75</v>
@@ -21498,7 +21450,7 @@
         <v>69</v>
       </c>
       <c r="BJ25" s="9" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="BK25" s="9" t="s">
         <v>75</v>
@@ -21512,34 +21464,34 @@
     </row>
     <row r="26" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="n">
-        <v>307433</v>
+        <v>307586</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="C26" s="9"/>
       <c r="D26" s="9"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K26" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>1040.61</v>
+        <v>2362.82</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>0</v>
@@ -21548,22 +21500,22 @@
         <v>1</v>
       </c>
       <c r="O26" s="12" t="n">
-        <v>977.1</v>
+        <v>2362.82</v>
       </c>
       <c r="P26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q26" s="13" t="n">
-        <v>0</v>
+        <v>0.000824</v>
       </c>
       <c r="R26" s="12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S26" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T26" s="14" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="U26" s="15" t="s">
         <v>72</v>
@@ -21575,16 +21527,16 @@
         <v>73</v>
       </c>
       <c r="X26" s="9" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="Y26" s="12" t="n">
-        <v>63.51</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="12" t="n">
-        <v>977.1</v>
+        <v>2362.82</v>
       </c>
       <c r="AA26" s="12" t="n">
-        <v>68.4</v>
+        <v>165.4</v>
       </c>
       <c r="AB26" s="12" t="n">
         <v>0</v>
@@ -21650,7 +21602,7 @@
         <v>74</v>
       </c>
       <c r="AW26" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX26" s="10" t="s">
         <v>87</v>
@@ -21689,7 +21641,7 @@
         <v>69</v>
       </c>
       <c r="BJ26" s="9" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="BK26" s="9" t="s">
         <v>75</v>
@@ -21703,79 +21655,79 @@
     </row>
     <row r="27" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="n">
-        <v>307439</v>
+        <v>307598</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>182</v>
+        <v>112</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="9"/>
       <c r="E27" s="9"/>
       <c r="F27" s="9" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>184</v>
+        <v>66</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>2401.84</v>
+        <v>1526.29</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O27" s="12" t="n">
-        <v>2401.84</v>
+        <v>1478.25</v>
       </c>
       <c r="P27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="Q27" s="13" t="n">
-        <v>0.29576</v>
+        <v>0.00165</v>
       </c>
       <c r="R27" s="12" t="n">
-        <v>31.68</v>
+        <v>0.05</v>
       </c>
       <c r="S27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="T27" s="14" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="U27" s="15" t="s">
         <v>72</v>
       </c>
       <c r="V27" s="12" t="n">
-        <v>60</v>
+        <v>55.12</v>
       </c>
       <c r="W27" s="9" t="s">
         <v>73</v>
       </c>
       <c r="X27" s="9" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="Y27" s="12" t="n">
-        <v>0</v>
+        <v>48.04</v>
       </c>
       <c r="Z27" s="12" t="n">
-        <v>2401.84</v>
+        <v>1478.25</v>
       </c>
       <c r="AA27" s="12" t="n">
-        <v>149.08</v>
+        <v>103.48</v>
       </c>
       <c r="AB27" s="12" t="n">
         <v>0</v>
@@ -21841,7 +21793,7 @@
         <v>74</v>
       </c>
       <c r="AW27" s="14" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="AX27" s="10" t="s">
         <v>87</v>
@@ -21880,7 +21832,7 @@
         <v>69</v>
       </c>
       <c r="BJ27" s="9" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="BK27" s="9" t="s">
         <v>75</v>
@@ -21894,34 +21846,34 @@
     </row>
     <row r="28" customFormat="false" ht="12.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="n">
-        <v>307443</v>
+        <v>307601</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>188</v>
+        <v>102</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>166</v>
+        <v>188</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="K28" s="11" t="s">
         <v>70</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>447.13</v>
+        <v>3012.18</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>0</v>
@@ -21930,43 +21882,43 @@
         <v>1</v>
       </c>
       <c r="O28" s="12" t